--- a/output/processed_props.xlsx
+++ b/output/processed_props.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1235" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="146">
   <si>
     <t>Player</t>
   </si>
@@ -52,361 +52,364 @@
     <t>Date</t>
   </si>
   <si>
+    <t>Nic Claxton</t>
+  </si>
+  <si>
+    <t>Tyus Jones</t>
+  </si>
+  <si>
     <t>Joan Beringer</t>
   </si>
   <si>
+    <t>James Harden</t>
+  </si>
+  <si>
+    <t>Cam Thomas</t>
+  </si>
+  <si>
+    <t>Kris Dunn</t>
+  </si>
+  <si>
+    <t>Draymond Green</t>
+  </si>
+  <si>
+    <t>Nikola Jokic</t>
+  </si>
+  <si>
+    <t>Nolan Traore</t>
+  </si>
+  <si>
+    <t>Quentin Grimes</t>
+  </si>
+  <si>
+    <t>Jared McCain</t>
+  </si>
+  <si>
+    <t>Bub Carrington</t>
+  </si>
+  <si>
+    <t>LaMelo Ball</t>
+  </si>
+  <si>
+    <t>Grant Williams</t>
+  </si>
+  <si>
+    <t>Wendell Carter Jr.</t>
+  </si>
+  <si>
+    <t>Jarrett Allen</t>
+  </si>
+  <si>
+    <t>AJ Green</t>
+  </si>
+  <si>
+    <t>Aaron Wiggins</t>
+  </si>
+  <si>
+    <t>Jamal Shead</t>
+  </si>
+  <si>
+    <t>Jalen Suggs</t>
+  </si>
+  <si>
+    <t>Dyson Daniels</t>
+  </si>
+  <si>
+    <t>RJ Barrett</t>
+  </si>
+  <si>
+    <t>VJ Edgecombe</t>
+  </si>
+  <si>
+    <t>Kon Knueppel</t>
+  </si>
+  <si>
+    <t>Naz Reid</t>
+  </si>
+  <si>
+    <t>Ryan Rollins</t>
+  </si>
+  <si>
+    <t>Kevin Porter Jr.</t>
+  </si>
+  <si>
+    <t>Immanuel Quickley</t>
+  </si>
+  <si>
+    <t>Michael Porter Jr.</t>
+  </si>
+  <si>
+    <t>Ayo Dosunmu</t>
+  </si>
+  <si>
+    <t>Klay Thompson</t>
+  </si>
+  <si>
+    <t>Jamal Murray</t>
+  </si>
+  <si>
+    <t>Payton Pritchard</t>
+  </si>
+  <si>
+    <t>Donovan Mitchell</t>
+  </si>
+  <si>
+    <t>Tyrese Maxey</t>
+  </si>
+  <si>
+    <t>Kyshawn George</t>
+  </si>
+  <si>
+    <t>Sam Hauser</t>
+  </si>
+  <si>
+    <t>Derrick Jones Jr.</t>
+  </si>
+  <si>
+    <t>Pat Spencer</t>
+  </si>
+  <si>
+    <t>Isaiah Hartenstein</t>
+  </si>
+  <si>
+    <t>Derrick White</t>
+  </si>
+  <si>
+    <t>Bennedict Mathurin</t>
+  </si>
+  <si>
+    <t>Gui Santos</t>
+  </si>
+  <si>
+    <t>Julius Randle</t>
+  </si>
+  <si>
+    <t>Dominick Barlow</t>
+  </si>
+  <si>
+    <t>Dennis Schroder</t>
+  </si>
+  <si>
+    <t>Donte DiVincenzo</t>
+  </si>
+  <si>
+    <t>Brook Lopez</t>
+  </si>
+  <si>
+    <t>Marcus Smart</t>
+  </si>
+  <si>
+    <t>Julian Strawther</t>
+  </si>
+  <si>
+    <t>Max Christie</t>
+  </si>
+  <si>
+    <t>Jock Landale</t>
+  </si>
+  <si>
+    <t>Daniel Gafford</t>
+  </si>
+  <si>
+    <t>Egor Demin</t>
+  </si>
+  <si>
+    <t>Brandon Miller</t>
+  </si>
+  <si>
+    <t>Austin Reaves</t>
+  </si>
+  <si>
+    <t>De'Anthony Melton</t>
+  </si>
+  <si>
+    <t>Jaylon Tyson</t>
+  </si>
+  <si>
+    <t>Anthony Black</t>
+  </si>
+  <si>
+    <t>Brandin Podziemski</t>
+  </si>
+  <si>
+    <t>Myles Turner</t>
+  </si>
+  <si>
+    <t>Desmond Bane</t>
+  </si>
+  <si>
+    <t>Nickeil Alexander-Walker</t>
+  </si>
+  <si>
+    <t>Paolo Banchero</t>
+  </si>
+  <si>
     <t>Jalen Johnson</t>
   </si>
   <si>
+    <t>Evan Mobley</t>
+  </si>
+  <si>
+    <t>Al Horford</t>
+  </si>
+  <si>
+    <t>Chet Holmgren</t>
+  </si>
+  <si>
+    <t>Tim Hardaway Jr.</t>
+  </si>
+  <si>
+    <t>Neemias Queta</t>
+  </si>
+  <si>
+    <t>Joel Embiid</t>
+  </si>
+  <si>
+    <t>Tre Johnson</t>
+  </si>
+  <si>
+    <t>Nikola Vucevic</t>
+  </si>
+  <si>
+    <t>Bilal Coulibaly</t>
+  </si>
+  <si>
+    <t>Jonas Valanciunas</t>
+  </si>
+  <si>
+    <t>Corey Kispert</t>
+  </si>
+  <si>
+    <t>Sam Merrill</t>
+  </si>
+  <si>
+    <t>Cason Wallace</t>
+  </si>
+  <si>
+    <t>Rui Hachimura</t>
+  </si>
+  <si>
+    <t>LeBron James</t>
+  </si>
+  <si>
+    <t>Anthony Edwards</t>
+  </si>
+  <si>
+    <t>Brandon Ingram</t>
+  </si>
+  <si>
+    <t>Jaden McDaniels</t>
+  </si>
+  <si>
+    <t>Tristan Vukcevic</t>
+  </si>
+  <si>
+    <t>Zaccharie Risacher</t>
+  </si>
+  <si>
+    <t>Ryan Kalkbrenner</t>
+  </si>
+  <si>
+    <t>Onyeka Okongwu</t>
+  </si>
+  <si>
+    <t>Deandre Ayton</t>
+  </si>
+  <si>
     <t>Jaylen Brown</t>
   </si>
   <si>
-    <t>Wendell Carter Jr.</t>
-  </si>
-  <si>
-    <t>Aaron Wiggins</t>
-  </si>
-  <si>
-    <t>Nic Claxton</t>
-  </si>
-  <si>
-    <t>Nikola Jokic</t>
-  </si>
-  <si>
-    <t>Draymond Green</t>
-  </si>
-  <si>
-    <t>Nolan Traore</t>
-  </si>
-  <si>
-    <t>Dyson Daniels</t>
-  </si>
-  <si>
-    <t>Chet Holmgren</t>
-  </si>
-  <si>
-    <t>Jarrett Allen</t>
-  </si>
-  <si>
-    <t>Kyshawn George</t>
-  </si>
-  <si>
-    <t>Tyrese Maxey</t>
-  </si>
-  <si>
-    <t>Payton Pritchard</t>
-  </si>
-  <si>
-    <t>Brandin Podziemski</t>
-  </si>
-  <si>
-    <t>LeBron James</t>
-  </si>
-  <si>
-    <t>Tim Hardaway Jr.</t>
-  </si>
-  <si>
-    <t>Cam Thomas</t>
-  </si>
-  <si>
-    <t>Zaccharie Risacher</t>
-  </si>
-  <si>
-    <t>Jamal Shead</t>
-  </si>
-  <si>
-    <t>Brandon Miller</t>
-  </si>
-  <si>
-    <t>Nikola Vucevic</t>
-  </si>
-  <si>
-    <t>Ayo Dosunmu</t>
-  </si>
-  <si>
-    <t>Derrick White</t>
-  </si>
-  <si>
-    <t>Marcus Smart</t>
-  </si>
-  <si>
-    <t>Jamal Murray</t>
-  </si>
-  <si>
-    <t>Myles Turner</t>
-  </si>
-  <si>
-    <t>Ryan Rollins</t>
+    <t>Dean Wade</t>
+  </si>
+  <si>
+    <t>Naji Marshall</t>
+  </si>
+  <si>
+    <t>Noah Clowney</t>
+  </si>
+  <si>
+    <t>CJ McCollum</t>
+  </si>
+  <si>
+    <t>Kyle Kuzma</t>
+  </si>
+  <si>
+    <t>Moses Moody</t>
+  </si>
+  <si>
+    <t>Luka Doncic</t>
   </si>
   <si>
     <t>Baylor Scheierman</t>
   </si>
   <si>
-    <t>VJ Edgecombe</t>
-  </si>
-  <si>
-    <t>Julian Strawther</t>
-  </si>
-  <si>
-    <t>Pat Spencer</t>
-  </si>
-  <si>
-    <t>Joel Embiid</t>
-  </si>
-  <si>
-    <t>Egor Demin</t>
-  </si>
-  <si>
     <t>Kawhi Leonard</t>
   </si>
   <si>
-    <t>AJ Green</t>
-  </si>
-  <si>
-    <t>RJ Barrett</t>
-  </si>
-  <si>
-    <t>Deandre Ayton</t>
-  </si>
-  <si>
-    <t>Austin Reaves</t>
-  </si>
-  <si>
-    <t>Sam Merrill</t>
-  </si>
-  <si>
-    <t>Grant Williams</t>
-  </si>
-  <si>
-    <t>Quentin Grimes</t>
-  </si>
-  <si>
-    <t>Nickeil Alexander-Walker</t>
-  </si>
-  <si>
-    <t>Isaiah Hartenstein</t>
-  </si>
-  <si>
-    <t>Brandon Ingram</t>
-  </si>
-  <si>
-    <t>Donte DiVincenzo</t>
-  </si>
-  <si>
-    <t>LaMelo Ball</t>
-  </si>
-  <si>
-    <t>Jaden McDaniels</t>
-  </si>
-  <si>
-    <t>Tyus Jones</t>
-  </si>
-  <si>
-    <t>Klay Thompson</t>
-  </si>
-  <si>
-    <t>Sam Hauser</t>
-  </si>
-  <si>
-    <t>Kon Knueppel</t>
-  </si>
-  <si>
-    <t>Jock Landale</t>
-  </si>
-  <si>
-    <t>Gui Santos</t>
-  </si>
-  <si>
-    <t>Julius Randle</t>
-  </si>
-  <si>
-    <t>Donovan Mitchell</t>
-  </si>
-  <si>
-    <t>Jared McCain</t>
-  </si>
-  <si>
-    <t>Dean Wade</t>
-  </si>
-  <si>
-    <t>Dominick Barlow</t>
-  </si>
-  <si>
-    <t>Immanuel Quickley</t>
-  </si>
-  <si>
-    <t>Bub Carrington</t>
-  </si>
-  <si>
-    <t>Kevin Porter Jr.</t>
-  </si>
-  <si>
-    <t>Kris Dunn</t>
-  </si>
-  <si>
-    <t>Cason Wallace</t>
-  </si>
-  <si>
-    <t>De'Anthony Melton</t>
+    <t>Christian Braun</t>
+  </si>
+  <si>
+    <t>Kristaps Porzingis</t>
+  </si>
+  <si>
+    <t>Isaiah Joe</t>
   </si>
   <si>
     <t>Collin Murray-Boyles</t>
   </si>
   <si>
-    <t>Paolo Banchero</t>
-  </si>
-  <si>
-    <t>Naz Reid</t>
-  </si>
-  <si>
-    <t>Onyeka Okongwu</t>
-  </si>
-  <si>
-    <t>Evan Mobley</t>
-  </si>
-  <si>
-    <t>Al Horford</t>
-  </si>
-  <si>
-    <t>Kyle Kuzma</t>
-  </si>
-  <si>
-    <t>Anthony Black</t>
-  </si>
-  <si>
-    <t>Luka Doncic</t>
-  </si>
-  <si>
-    <t>Tristan Vukcevic</t>
-  </si>
-  <si>
-    <t>Christian Braun</t>
-  </si>
-  <si>
-    <t>Ryan Kalkbrenner</t>
-  </si>
-  <si>
-    <t>Bennedict Mathurin</t>
-  </si>
-  <si>
-    <t>Noah Clowney</t>
-  </si>
-  <si>
-    <t>Anthony Edwards</t>
-  </si>
-  <si>
-    <t>James Harden</t>
-  </si>
-  <si>
-    <t>Daniel Gafford</t>
-  </si>
-  <si>
-    <t>Michael Porter Jr.</t>
-  </si>
-  <si>
-    <t>Dennis Schroder</t>
-  </si>
-  <si>
-    <t>Jonas Valanciunas</t>
-  </si>
-  <si>
-    <t>Naji Marshall</t>
-  </si>
-  <si>
-    <t>Jaylon Tyson</t>
-  </si>
-  <si>
-    <t>Bilal Coulibaly</t>
-  </si>
-  <si>
-    <t>Rui Hachimura</t>
-  </si>
-  <si>
-    <t>Corey Kispert</t>
-  </si>
-  <si>
-    <t>Brook Lopez</t>
-  </si>
-  <si>
-    <t>Derrick Jones Jr.</t>
-  </si>
-  <si>
-    <t>Tre Johnson</t>
-  </si>
-  <si>
-    <t>Moses Moody</t>
-  </si>
-  <si>
-    <t>CJ McCollum</t>
-  </si>
-  <si>
-    <t>Isaiah Joe</t>
-  </si>
-  <si>
-    <t>Desmond Bane</t>
-  </si>
-  <si>
-    <t>Jalen Suggs</t>
-  </si>
-  <si>
-    <t>Kristaps Porzingis</t>
-  </si>
-  <si>
-    <t>Max Christie</t>
-  </si>
-  <si>
-    <t>Neemias Queta</t>
+    <t>BKN</t>
+  </si>
+  <si>
+    <t>DAL</t>
   </si>
   <si>
     <t>MIN</t>
   </si>
   <si>
+    <t>CLE</t>
+  </si>
+  <si>
+    <t>MIL</t>
+  </si>
+  <si>
+    <t>LAC</t>
+  </si>
+  <si>
+    <t>GS</t>
+  </si>
+  <si>
+    <t>DEN</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>OKC</t>
+  </si>
+  <si>
+    <t>WSH</t>
+  </si>
+  <si>
+    <t>CHA</t>
+  </si>
+  <si>
+    <t>ORL</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
     <t>ATL</t>
   </si>
   <si>
     <t>BOS</t>
   </si>
   <si>
-    <t>ORL</t>
-  </si>
-  <si>
-    <t>OKC</t>
-  </si>
-  <si>
-    <t>BKN</t>
-  </si>
-  <si>
-    <t>DEN</t>
-  </si>
-  <si>
-    <t>GS</t>
-  </si>
-  <si>
-    <t>CLE</t>
-  </si>
-  <si>
-    <t>WSH</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
     <t>LAL</t>
   </si>
   <si>
-    <t>MIL</t>
-  </si>
-  <si>
-    <t>TOR</t>
-  </si>
-  <si>
-    <t>CHA</t>
-  </si>
-  <si>
-    <t>LAC</t>
-  </si>
-  <si>
-    <t>DAL</t>
+    <t>IND</t>
   </si>
   <si>
     <t>GSW</t>
@@ -415,28 +418,25 @@
     <t>WAS</t>
   </si>
   <si>
-    <t>IND</t>
+    <t>PTS</t>
   </si>
   <si>
     <t>PRA</t>
   </si>
   <si>
-    <t>PTS</t>
+    <t>AST</t>
+  </si>
+  <si>
+    <t>REB</t>
   </si>
   <si>
     <t>RA</t>
   </si>
   <si>
-    <t>AST</t>
-  </si>
-  <si>
-    <t>REB</t>
+    <t>Over</t>
   </si>
   <si>
     <t>Under</t>
-  </si>
-  <si>
-    <t>Over</t>
   </si>
   <si>
     <t>S Tier</t>
@@ -854,10 +854,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L174"/>
+  <dimension ref="A1:L172"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" customWidth="1"/>
+    <col min="1" max="1" width="22.7109375" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="5" width="8.7109375" customWidth="1"/>
@@ -915,16 +915,16 @@
         <v>114</v>
       </c>
       <c r="C2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D2" t="s">
         <v>134</v>
       </c>
       <c r="E2">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="F2">
-        <v>3.36</v>
+        <v>26.54</v>
       </c>
       <c r="G2" s="1">
         <v>1</v>
@@ -933,7 +933,7 @@
         <v>139</v>
       </c>
       <c r="I2" s="2">
-        <v>90.91</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J2" s="2">
         <v>1</v>
@@ -953,28 +953,28 @@
         <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="D3" t="s">
         <v>134</v>
       </c>
       <c r="E3">
-        <v>42.5</v>
+        <v>6.5</v>
       </c>
       <c r="F3">
-        <v>26.41</v>
+        <v>11.62</v>
       </c>
       <c r="G3" s="1">
-        <v>1</v>
+        <v>0.998</v>
       </c>
       <c r="H3" t="s">
         <v>139</v>
       </c>
       <c r="I3" s="2">
-        <v>90.91</v>
+        <v>90.55</v>
       </c>
       <c r="J3" s="2">
-        <v>1</v>
+        <v>0.996</v>
       </c>
       <c r="K3" t="s">
         <v>141</v>
@@ -991,28 +991,28 @@
         <v>116</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E4">
-        <v>39.5</v>
+        <v>14.5</v>
       </c>
       <c r="F4">
-        <v>27.26</v>
+        <v>3.26</v>
       </c>
       <c r="G4" s="1">
-        <v>1</v>
+        <v>0.996</v>
       </c>
       <c r="H4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I4" s="2">
-        <v>90.91</v>
+        <v>90.06</v>
       </c>
       <c r="J4" s="2">
-        <v>1</v>
+        <v>0.991</v>
       </c>
       <c r="K4" t="s">
         <v>141</v>
@@ -1029,28 +1029,28 @@
         <v>117</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E5">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="F5">
-        <v>4.6</v>
+        <v>4.09</v>
       </c>
       <c r="G5" s="1">
-        <v>1</v>
+        <v>0.976</v>
       </c>
       <c r="H5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I5" s="2">
-        <v>90.91</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="J5" s="2">
-        <v>1</v>
+        <v>0.949</v>
       </c>
       <c r="K5" t="s">
         <v>141</v>
@@ -1067,28 +1067,28 @@
         <v>118</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E6">
-        <v>14.5</v>
+        <v>1.5</v>
       </c>
       <c r="F6">
-        <v>8.77</v>
+        <v>5.2</v>
       </c>
       <c r="G6" s="1">
-        <v>1</v>
+        <v>0.966</v>
       </c>
       <c r="H6" t="s">
         <v>139</v>
       </c>
       <c r="I6" s="2">
-        <v>90.90000000000001</v>
+        <v>84.38</v>
       </c>
       <c r="J6" s="2">
-        <v>1</v>
+        <v>0.928</v>
       </c>
       <c r="K6" t="s">
         <v>141</v>
@@ -1105,28 +1105,28 @@
         <v>119</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="D7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E7">
-        <v>10.5</v>
+        <v>6.5</v>
       </c>
       <c r="F7">
-        <v>18.64</v>
+        <v>3.1</v>
       </c>
       <c r="G7" s="1">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="H7" t="s">
         <v>140</v>
       </c>
       <c r="I7" s="2">
-        <v>90.89</v>
+        <v>83.25</v>
       </c>
       <c r="J7" s="2">
-        <v>1</v>
+        <v>0.916</v>
       </c>
       <c r="K7" t="s">
         <v>141</v>
@@ -1143,28 +1143,28 @@
         <v>120</v>
       </c>
       <c r="C8" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E8">
-        <v>23.5</v>
+        <v>18.5</v>
       </c>
       <c r="F8">
-        <v>16.05</v>
+        <v>4.47</v>
       </c>
       <c r="G8" s="1">
-        <v>1</v>
+        <v>0.947</v>
       </c>
       <c r="H8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I8" s="2">
-        <v>90.89</v>
+        <v>80.72</v>
       </c>
       <c r="J8" s="2">
-        <v>1</v>
+        <v>0.888</v>
       </c>
       <c r="K8" t="s">
         <v>141</v>
@@ -1181,28 +1181,28 @@
         <v>121</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E9">
-        <v>18.5</v>
+        <v>23.5</v>
       </c>
       <c r="F9">
-        <v>12.33</v>
+        <v>10.21</v>
       </c>
       <c r="G9" s="1">
-        <v>1</v>
+        <v>0.946</v>
       </c>
       <c r="H9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I9" s="2">
-        <v>90.87</v>
+        <v>80.69</v>
       </c>
       <c r="J9" s="2">
-        <v>1</v>
+        <v>0.888</v>
       </c>
       <c r="K9" t="s">
         <v>141</v>
@@ -1216,31 +1216,31 @@
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="D10" t="s">
         <v>134</v>
       </c>
       <c r="E10">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="F10">
-        <v>26.33</v>
+        <v>20.19</v>
       </c>
       <c r="G10" s="1">
-        <v>1</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="H10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I10" s="2">
-        <v>90.84999999999999</v>
+        <v>79.12</v>
       </c>
       <c r="J10" s="2">
-        <v>0.999</v>
+        <v>0.87</v>
       </c>
       <c r="K10" t="s">
         <v>141</v>
@@ -1254,31 +1254,31 @@
         <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C11" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D11" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E11">
-        <v>23.5</v>
+        <v>2.5</v>
       </c>
       <c r="F11">
-        <v>16.73</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>1</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="H11" t="s">
         <v>139</v>
       </c>
       <c r="I11" s="2">
-        <v>90.81999999999999</v>
+        <v>79.06</v>
       </c>
       <c r="J11" s="2">
-        <v>0.999</v>
+        <v>0.87</v>
       </c>
       <c r="K11" t="s">
         <v>141</v>
@@ -1292,31 +1292,31 @@
         <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C12" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D12" t="s">
         <v>134</v>
       </c>
       <c r="E12">
-        <v>29.5</v>
+        <v>11.5</v>
       </c>
       <c r="F12">
-        <v>21.8</v>
+        <v>20.27</v>
       </c>
       <c r="G12" s="1">
-        <v>1</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="H12" t="s">
         <v>139</v>
       </c>
       <c r="I12" s="2">
-        <v>90.81999999999999</v>
+        <v>78.98</v>
       </c>
       <c r="J12" s="2">
-        <v>0.999</v>
+        <v>0.869</v>
       </c>
       <c r="K12" t="s">
         <v>141</v>
@@ -1330,31 +1330,31 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E13">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="F13">
-        <v>21</v>
+        <v>6.33</v>
       </c>
       <c r="G13" s="1">
-        <v>0.999</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="H13" t="s">
         <v>140</v>
       </c>
       <c r="I13" s="2">
-        <v>90.81</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="J13" s="2">
-        <v>0.999</v>
+        <v>0.863</v>
       </c>
       <c r="K13" t="s">
         <v>141</v>
@@ -1368,31 +1368,31 @@
         <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C14" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D14" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E14">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="F14">
-        <v>8.06</v>
+        <v>4.2</v>
       </c>
       <c r="G14" s="1">
-        <v>0.999</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="H14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I14" s="2">
-        <v>90.73999999999999</v>
+        <v>78.37</v>
       </c>
       <c r="J14" s="2">
-        <v>0.998</v>
+        <v>0.862</v>
       </c>
       <c r="K14" t="s">
         <v>141</v>
@@ -1406,31 +1406,31 @@
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C15" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D15" t="s">
         <v>134</v>
       </c>
       <c r="E15">
-        <v>39.5</v>
+        <v>11.5</v>
       </c>
       <c r="F15">
-        <v>31.32</v>
+        <v>19.58</v>
       </c>
       <c r="G15" s="1">
-        <v>0.998</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H15" t="s">
         <v>139</v>
       </c>
       <c r="I15" s="2">
-        <v>90.58</v>
+        <v>78.06</v>
       </c>
       <c r="J15" s="2">
-        <v>0.996</v>
+        <v>0.859</v>
       </c>
       <c r="K15" t="s">
         <v>141</v>
@@ -1444,31 +1444,31 @@
         <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D16" t="s">
         <v>135</v>
       </c>
       <c r="E16">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="F16">
-        <v>24.58</v>
+        <v>8.9</v>
       </c>
       <c r="G16" s="1">
-        <v>0.998</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="H16" t="s">
         <v>140</v>
       </c>
       <c r="I16" s="2">
-        <v>90.5</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="J16" s="2">
-        <v>0.995</v>
+        <v>0.858</v>
       </c>
       <c r="K16" t="s">
         <v>141</v>
@@ -1482,31 +1482,31 @@
         <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C17" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E17">
-        <v>15.5</v>
+        <v>1.5</v>
       </c>
       <c r="F17">
-        <v>10.81</v>
+        <v>4.37</v>
       </c>
       <c r="G17" s="1">
-        <v>0.998</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="H17" t="s">
         <v>139</v>
       </c>
       <c r="I17" s="2">
-        <v>90.5</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="J17" s="2">
-        <v>0.995</v>
+        <v>0.858</v>
       </c>
       <c r="K17" t="s">
         <v>141</v>
@@ -1520,31 +1520,31 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C18" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E18">
-        <v>19.5</v>
+        <v>9.5</v>
       </c>
       <c r="F18">
-        <v>14.23</v>
+        <v>0.48</v>
       </c>
       <c r="G18" s="1">
-        <v>0.997</v>
+        <v>0.921</v>
       </c>
       <c r="H18" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I18" s="2">
-        <v>90.42</v>
+        <v>75.78</v>
       </c>
       <c r="J18" s="2">
-        <v>0.995</v>
+        <v>0.834</v>
       </c>
       <c r="K18" t="s">
         <v>141</v>
@@ -1558,31 +1558,31 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C19" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="D19" t="s">
         <v>134</v>
       </c>
       <c r="E19">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="F19">
-        <v>21.46</v>
+        <v>6.54</v>
       </c>
       <c r="G19" s="1">
-        <v>0.995</v>
+        <v>0.919</v>
       </c>
       <c r="H19" t="s">
         <v>140</v>
       </c>
       <c r="I19" s="2">
-        <v>89.95</v>
+        <v>75.38</v>
       </c>
       <c r="J19" s="2">
-        <v>0.989</v>
+        <v>0.829</v>
       </c>
       <c r="K19" t="s">
         <v>141</v>
@@ -1596,31 +1596,31 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C20" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D20" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E20">
-        <v>19.5</v>
+        <v>4.5</v>
       </c>
       <c r="F20">
-        <v>25.93</v>
+        <v>1.73</v>
       </c>
       <c r="G20" s="1">
-        <v>0.994</v>
+        <v>0.918</v>
       </c>
       <c r="H20" t="s">
         <v>140</v>
       </c>
       <c r="I20" s="2">
-        <v>89.8</v>
+        <v>75.19</v>
       </c>
       <c r="J20" s="2">
-        <v>0.988</v>
+        <v>0.827</v>
       </c>
       <c r="K20" t="s">
         <v>141</v>
@@ -1634,31 +1634,31 @@
         <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="C21" t="s">
         <v>119</v>
       </c>
       <c r="D21" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E21">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="F21">
-        <v>5.6</v>
+        <v>1.87</v>
       </c>
       <c r="G21" s="1">
-        <v>0.993</v>
+        <v>0.917</v>
       </c>
       <c r="H21" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I21" s="2">
-        <v>89.55</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="J21" s="2">
-        <v>0.985</v>
+        <v>0.826</v>
       </c>
       <c r="K21" t="s">
         <v>141</v>
@@ -1672,31 +1672,31 @@
         <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C22" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D22" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E22">
-        <v>14.5</v>
+        <v>23.5</v>
       </c>
       <c r="F22">
-        <v>10.54</v>
+        <v>12.97</v>
       </c>
       <c r="G22" s="1">
-        <v>0.993</v>
+        <v>0.916</v>
       </c>
       <c r="H22" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I22" s="2">
-        <v>89.48999999999999</v>
+        <v>74.94</v>
       </c>
       <c r="J22" s="2">
-        <v>0.984</v>
+        <v>0.824</v>
       </c>
       <c r="K22" t="s">
         <v>141</v>
@@ -1710,31 +1710,31 @@
         <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C23" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="D23" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E23">
-        <v>33.5</v>
+        <v>27.5</v>
       </c>
       <c r="F23">
-        <v>27.39</v>
+        <v>19.59</v>
       </c>
       <c r="G23" s="1">
-        <v>0.99</v>
+        <v>0.913</v>
       </c>
       <c r="H23" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I23" s="2">
-        <v>89.05</v>
+        <v>74.36</v>
       </c>
       <c r="J23" s="2">
-        <v>0.98</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="K23" t="s">
         <v>141</v>
@@ -1748,31 +1748,31 @@
         <v>34</v>
       </c>
       <c r="B24" t="s">
+        <v>122</v>
+      </c>
+      <c r="C24" t="s">
         <v>116</v>
-      </c>
-      <c r="C24" t="s">
-        <v>125</v>
       </c>
       <c r="D24" t="s">
         <v>134</v>
       </c>
       <c r="E24">
-        <v>22.5</v>
+        <v>15.5</v>
       </c>
       <c r="F24">
-        <v>17.74</v>
+        <v>24.26</v>
       </c>
       <c r="G24" s="1">
-        <v>0.988</v>
+        <v>0.909</v>
       </c>
       <c r="H24" t="s">
         <v>139</v>
       </c>
       <c r="I24" s="2">
-        <v>88.65000000000001</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="J24" s="2">
-        <v>0.975</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="K24" t="s">
         <v>141</v>
@@ -1786,31 +1786,31 @@
         <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="C25" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="D25" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E25">
-        <v>20.5</v>
+        <v>30.5</v>
       </c>
       <c r="F25">
-        <v>16.02</v>
+        <v>39.2</v>
       </c>
       <c r="G25" s="1">
-        <v>0.987</v>
+        <v>0.907</v>
       </c>
       <c r="H25" t="s">
         <v>139</v>
       </c>
       <c r="I25" s="2">
-        <v>88.51000000000001</v>
+        <v>73.23</v>
       </c>
       <c r="J25" s="2">
-        <v>0.974</v>
+        <v>0.805</v>
       </c>
       <c r="K25" t="s">
         <v>141</v>
@@ -1827,28 +1827,28 @@
         <v>116</v>
       </c>
       <c r="C26" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D26" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E26">
-        <v>18.5</v>
+        <v>8.5</v>
       </c>
       <c r="F26">
-        <v>14.34</v>
+        <v>5.36</v>
       </c>
       <c r="G26" s="1">
-        <v>0.986</v>
+        <v>0.906</v>
       </c>
       <c r="H26" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I26" s="2">
-        <v>88.23</v>
+        <v>72.88</v>
       </c>
       <c r="J26" s="2">
-        <v>0.971</v>
+        <v>0.802</v>
       </c>
       <c r="K26" t="s">
         <v>141</v>
@@ -1859,34 +1859,34 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C27" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D27" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E27">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="F27">
-        <v>15.81</v>
+        <v>3.96</v>
       </c>
       <c r="G27" s="1">
-        <v>0.985</v>
+        <v>0.905</v>
       </c>
       <c r="H27" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I27" s="2">
-        <v>88.03</v>
+        <v>72.81</v>
       </c>
       <c r="J27" s="2">
-        <v>0.968</v>
+        <v>0.801</v>
       </c>
       <c r="K27" t="s">
         <v>141</v>
@@ -1897,34 +1897,34 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C28" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s">
         <v>135</v>
       </c>
       <c r="E28">
-        <v>24.5</v>
+        <v>27.5</v>
       </c>
       <c r="F28">
-        <v>19.73</v>
+        <v>36.73</v>
       </c>
       <c r="G28" s="1">
-        <v>0.984</v>
+        <v>0.903</v>
       </c>
       <c r="H28" t="s">
         <v>139</v>
       </c>
       <c r="I28" s="2">
-        <v>87.88</v>
+        <v>72.38</v>
       </c>
       <c r="J28" s="2">
-        <v>0.967</v>
+        <v>0.796</v>
       </c>
       <c r="K28" t="s">
         <v>141</v>
@@ -1935,34 +1935,34 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C29" t="s">
         <v>127</v>
       </c>
       <c r="D29" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E29">
-        <v>11.5</v>
+        <v>7.5</v>
       </c>
       <c r="F29">
-        <v>8.43</v>
+        <v>4.44</v>
       </c>
       <c r="G29" s="1">
-        <v>0.983</v>
+        <v>0.901</v>
       </c>
       <c r="H29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I29" s="2">
-        <v>87.65000000000001</v>
+        <v>71.91</v>
       </c>
       <c r="J29" s="2">
-        <v>0.964</v>
+        <v>0.791</v>
       </c>
       <c r="K29" t="s">
         <v>141</v>
@@ -1973,34 +1973,34 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C30" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E30">
-        <v>27.5</v>
+        <v>6.5</v>
       </c>
       <c r="F30">
-        <v>33.51</v>
+        <v>3.83</v>
       </c>
       <c r="G30" s="1">
-        <v>0.981</v>
+        <v>0.9</v>
       </c>
       <c r="H30" t="s">
         <v>140</v>
       </c>
       <c r="I30" s="2">
-        <v>87.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="J30" s="2">
-        <v>0.96</v>
+        <v>0.791</v>
       </c>
       <c r="K30" t="s">
         <v>141</v>
@@ -2011,34 +2011,34 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C31" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D31" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E31">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="F31">
-        <v>16.62</v>
+        <v>5.3</v>
       </c>
       <c r="G31" s="1">
-        <v>0.978</v>
+        <v>0.899</v>
       </c>
       <c r="H31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I31" s="2">
-        <v>86.76000000000001</v>
+        <v>71.56</v>
       </c>
       <c r="J31" s="2">
-        <v>0.954</v>
+        <v>0.787</v>
       </c>
       <c r="K31" t="s">
         <v>141</v>
@@ -2049,34 +2049,34 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C32" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D32" t="s">
         <v>134</v>
       </c>
       <c r="E32">
-        <v>24.5</v>
+        <v>12.5</v>
       </c>
       <c r="F32">
-        <v>29.92</v>
+        <v>4.45</v>
       </c>
       <c r="G32" s="1">
-        <v>0.976</v>
+        <v>0.896</v>
       </c>
       <c r="H32" t="s">
         <v>140</v>
       </c>
       <c r="I32" s="2">
-        <v>86.37</v>
+        <v>71.06</v>
       </c>
       <c r="J32" s="2">
-        <v>0.95</v>
+        <v>0.782</v>
       </c>
       <c r="K32" t="s">
         <v>141</v>
@@ -2087,34 +2087,34 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C33" t="s">
         <v>131</v>
       </c>
       <c r="D33" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E33">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="F33">
-        <v>16.5</v>
+        <v>5.25</v>
       </c>
       <c r="G33" s="1">
-        <v>0.975</v>
+        <v>0.895</v>
       </c>
       <c r="H33" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I33" s="2">
-        <v>86.23</v>
+        <v>70.86</v>
       </c>
       <c r="J33" s="2">
-        <v>0.949</v>
+        <v>0.779</v>
       </c>
       <c r="K33" t="s">
         <v>141</v>
@@ -2125,34 +2125,34 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B34" t="s">
         <v>121</v>
       </c>
       <c r="C34" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="D34" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E34">
-        <v>20.5</v>
+        <v>7.5</v>
       </c>
       <c r="F34">
-        <v>16.54</v>
+        <v>3.84</v>
       </c>
       <c r="G34" s="1">
-        <v>0.974</v>
+        <v>0.895</v>
       </c>
       <c r="H34" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I34" s="2">
-        <v>86.02</v>
+        <v>70.78</v>
       </c>
       <c r="J34" s="2">
-        <v>0.946</v>
+        <v>0.779</v>
       </c>
       <c r="K34" t="s">
         <v>141</v>
@@ -2163,34 +2163,34 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B35" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C35" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="D35" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E35">
-        <v>26.5</v>
+        <v>17.5</v>
       </c>
       <c r="F35">
-        <v>31.99</v>
+        <v>28.87</v>
       </c>
       <c r="G35" s="1">
-        <v>0.974</v>
+        <v>0.894</v>
       </c>
       <c r="H35" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I35" s="2">
-        <v>85.93000000000001</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="J35" s="2">
-        <v>0.945</v>
+        <v>0.778</v>
       </c>
       <c r="K35" t="s">
         <v>141</v>
@@ -2201,34 +2201,34 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C36" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D36" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E36">
-        <v>10.5</v>
+        <v>3.5</v>
       </c>
       <c r="F36">
-        <v>7.8</v>
+        <v>6.57</v>
       </c>
       <c r="G36" s="1">
-        <v>0.973</v>
+        <v>0.893</v>
       </c>
       <c r="H36" t="s">
         <v>139</v>
       </c>
       <c r="I36" s="2">
-        <v>85.81999999999999</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="J36" s="2">
-        <v>0.944</v>
+        <v>0.775</v>
       </c>
       <c r="K36" t="s">
         <v>141</v>
@@ -2239,34 +2239,34 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C37" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D37" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E37">
-        <v>40.5</v>
+        <v>3.5</v>
       </c>
       <c r="F37">
-        <v>34.91</v>
+        <v>6.72</v>
       </c>
       <c r="G37" s="1">
-        <v>0.971</v>
+        <v>0.887</v>
       </c>
       <c r="H37" t="s">
         <v>139</v>
       </c>
       <c r="I37" s="2">
-        <v>85.31999999999999</v>
+        <v>69.41</v>
       </c>
       <c r="J37" s="2">
-        <v>0.9389999999999999</v>
+        <v>0.763</v>
       </c>
       <c r="K37" t="s">
         <v>141</v>
@@ -2277,34 +2277,34 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C38" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E38">
-        <v>9.5</v>
+        <v>12.5</v>
       </c>
       <c r="F38">
-        <v>7</v>
+        <v>5.53</v>
       </c>
       <c r="G38" s="1">
-        <v>0.97</v>
+        <v>0.887</v>
       </c>
       <c r="H38" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I38" s="2">
-        <v>85.27</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="J38" s="2">
-        <v>0.9379999999999999</v>
+        <v>0.763</v>
       </c>
       <c r="K38" t="s">
         <v>141</v>
@@ -2315,34 +2315,34 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C39" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D39" t="s">
         <v>134</v>
       </c>
       <c r="E39">
-        <v>27.5</v>
+        <v>9.5</v>
       </c>
       <c r="F39">
-        <v>23</v>
+        <v>15.92</v>
       </c>
       <c r="G39" s="1">
-        <v>0.97</v>
+        <v>0.886</v>
       </c>
       <c r="H39" t="s">
         <v>139</v>
       </c>
       <c r="I39" s="2">
-        <v>85.09999999999999</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="J39" s="2">
-        <v>0.9360000000000001</v>
+        <v>0.761</v>
       </c>
       <c r="K39" t="s">
         <v>141</v>
@@ -2353,34 +2353,34 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C40" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D40" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E40">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="F40">
-        <v>12.75</v>
+        <v>3.71</v>
       </c>
       <c r="G40" s="1">
-        <v>0.966</v>
+        <v>0.884</v>
       </c>
       <c r="H40" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I40" s="2">
-        <v>84.37</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="J40" s="2">
-        <v>0.928</v>
+        <v>0.757</v>
       </c>
       <c r="K40" t="s">
         <v>141</v>
@@ -2391,34 +2391,34 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C41" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D41" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E41">
-        <v>29.5</v>
+        <v>5.5</v>
       </c>
       <c r="F41">
-        <v>34.61</v>
+        <v>2.52</v>
       </c>
       <c r="G41" s="1">
-        <v>0.959</v>
+        <v>0.884</v>
       </c>
       <c r="H41" t="s">
         <v>140</v>
       </c>
       <c r="I41" s="2">
-        <v>83.05</v>
+        <v>68.69</v>
       </c>
       <c r="J41" s="2">
-        <v>0.914</v>
+        <v>0.756</v>
       </c>
       <c r="K41" t="s">
         <v>141</v>
@@ -2429,34 +2429,34 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B42" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C42" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D42" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E42">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="F42">
-        <v>14.68</v>
+        <v>7.48</v>
       </c>
       <c r="G42" s="1">
-        <v>0.952</v>
+        <v>0.88</v>
       </c>
       <c r="H42" t="s">
         <v>140</v>
       </c>
       <c r="I42" s="2">
-        <v>81.7</v>
+        <v>68.03</v>
       </c>
       <c r="J42" s="2">
-        <v>0.899</v>
+        <v>0.748</v>
       </c>
       <c r="K42" t="s">
         <v>141</v>
@@ -2467,34 +2467,34 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B43" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C43" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D43" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E43">
-        <v>11.5</v>
+        <v>18.5</v>
       </c>
       <c r="F43">
-        <v>14.63</v>
+        <v>11.16</v>
       </c>
       <c r="G43" s="1">
-        <v>0.949</v>
+        <v>0.876</v>
       </c>
       <c r="H43" t="s">
         <v>140</v>
       </c>
       <c r="I43" s="2">
-        <v>81.23999999999999</v>
+        <v>67.28</v>
       </c>
       <c r="J43" s="2">
-        <v>0.894</v>
+        <v>0.74</v>
       </c>
       <c r="K43" t="s">
         <v>141</v>
@@ -2505,34 +2505,34 @@
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B44" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C44" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D44" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E44">
-        <v>15.5</v>
+        <v>2.5</v>
       </c>
       <c r="F44">
-        <v>19.02</v>
+        <v>4.96</v>
       </c>
       <c r="G44" s="1">
-        <v>0.947</v>
+        <v>0.872</v>
       </c>
       <c r="H44" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I44" s="2">
-        <v>80.75</v>
+        <v>66.47</v>
       </c>
       <c r="J44" s="2">
-        <v>0.888</v>
+        <v>0.731</v>
       </c>
       <c r="K44" t="s">
         <v>141</v>
@@ -2543,34 +2543,34 @@
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="B45" t="s">
         <v>115</v>
       </c>
       <c r="C45" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="D45" t="s">
         <v>136</v>
       </c>
       <c r="E45">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="F45">
-        <v>10.05</v>
+        <v>2.49</v>
       </c>
       <c r="G45" s="1">
-        <v>0.946</v>
+        <v>0.871</v>
       </c>
       <c r="H45" t="s">
         <v>140</v>
       </c>
       <c r="I45" s="2">
-        <v>80.62</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="J45" s="2">
-        <v>0.887</v>
+        <v>0.729</v>
       </c>
       <c r="K45" t="s">
         <v>141</v>
@@ -2581,34 +2581,34 @@
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B46" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C46" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D46" t="s">
         <v>134</v>
       </c>
       <c r="E46">
-        <v>23.5</v>
+        <v>11.5</v>
       </c>
       <c r="F46">
-        <v>19.94</v>
+        <v>16.43</v>
       </c>
       <c r="G46" s="1">
-        <v>0.944</v>
+        <v>0.869</v>
       </c>
       <c r="H46" t="s">
         <v>139</v>
       </c>
       <c r="I46" s="2">
-        <v>80.28</v>
+        <v>65.87</v>
       </c>
       <c r="J46" s="2">
-        <v>0.883</v>
+        <v>0.725</v>
       </c>
       <c r="K46" t="s">
         <v>141</v>
@@ -2619,34 +2619,34 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C47" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D47" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E47">
-        <v>34.5</v>
+        <v>3.5</v>
       </c>
       <c r="F47">
-        <v>30.2</v>
+        <v>6.21</v>
       </c>
       <c r="G47" s="1">
-        <v>0.9409999999999999</v>
+        <v>0.866</v>
       </c>
       <c r="H47" t="s">
         <v>139</v>
       </c>
       <c r="I47" s="2">
-        <v>79.69</v>
+        <v>65.37</v>
       </c>
       <c r="J47" s="2">
-        <v>0.877</v>
+        <v>0.719</v>
       </c>
       <c r="K47" t="s">
         <v>141</v>
@@ -2657,34 +2657,34 @@
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B48" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C48" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D48" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E48">
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
       <c r="F48">
-        <v>8.26</v>
+        <v>5.82</v>
       </c>
       <c r="G48" s="1">
-        <v>0.9409999999999999</v>
+        <v>0.865</v>
       </c>
       <c r="H48" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I48" s="2">
-        <v>79.58</v>
+        <v>65.17</v>
       </c>
       <c r="J48" s="2">
-        <v>0.875</v>
+        <v>0.717</v>
       </c>
       <c r="K48" t="s">
         <v>141</v>
@@ -2695,34 +2695,34 @@
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B49" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C49" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="D49" t="s">
         <v>134</v>
       </c>
       <c r="E49">
-        <v>32.5</v>
+        <v>8.5</v>
       </c>
       <c r="F49">
-        <v>28.35</v>
+        <v>1.22</v>
       </c>
       <c r="G49" s="1">
-        <v>0.9399999999999999</v>
+        <v>0.865</v>
       </c>
       <c r="H49" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I49" s="2">
-        <v>79.52</v>
+        <v>65.13</v>
       </c>
       <c r="J49" s="2">
-        <v>0.875</v>
+        <v>0.716</v>
       </c>
       <c r="K49" t="s">
         <v>141</v>
@@ -2733,34 +2733,34 @@
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B50" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D50" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E50">
-        <v>22.5</v>
+        <v>3.5</v>
       </c>
       <c r="F50">
-        <v>19.22</v>
+        <v>1.76</v>
       </c>
       <c r="G50" s="1">
-        <v>0.9330000000000001</v>
+        <v>0.865</v>
       </c>
       <c r="H50" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I50" s="2">
-        <v>78.03</v>
+        <v>65.06</v>
       </c>
       <c r="J50" s="2">
-        <v>0.858</v>
+        <v>0.716</v>
       </c>
       <c r="K50" t="s">
         <v>141</v>
@@ -2771,34 +2771,34 @@
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B51" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="C51" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="D51" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E51">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F51">
-        <v>2.84</v>
+        <v>2.32</v>
       </c>
       <c r="G51" s="1">
-        <v>0.931</v>
+        <v>0.859</v>
       </c>
       <c r="H51" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I51" s="2">
-        <v>77.81999999999999</v>
+        <v>64.05</v>
       </c>
       <c r="J51" s="2">
-        <v>0.856</v>
+        <v>0.705</v>
       </c>
       <c r="K51" t="s">
         <v>141</v>
@@ -2809,34 +2809,34 @@
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="C52" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D52" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E52">
-        <v>12.5</v>
+        <v>1.5</v>
       </c>
       <c r="F52">
-        <v>10.17</v>
+        <v>3.44</v>
       </c>
       <c r="G52" s="1">
-        <v>0.928</v>
+        <v>0.858</v>
       </c>
       <c r="H52" t="s">
         <v>139</v>
       </c>
       <c r="I52" s="2">
-        <v>77.2</v>
+        <v>63.71</v>
       </c>
       <c r="J52" s="2">
-        <v>0.849</v>
+        <v>0.701</v>
       </c>
       <c r="K52" t="s">
         <v>141</v>
@@ -2847,34 +2847,34 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="C53" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D53" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E53">
-        <v>14.5</v>
+        <v>2.5</v>
       </c>
       <c r="F53">
-        <v>17.52</v>
+        <v>4.79</v>
       </c>
       <c r="G53" s="1">
-        <v>0.925</v>
+        <v>0.857</v>
       </c>
       <c r="H53" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I53" s="2">
-        <v>76.65000000000001</v>
+        <v>63.57</v>
       </c>
       <c r="J53" s="2">
-        <v>0.843</v>
+        <v>0.699</v>
       </c>
       <c r="K53" t="s">
         <v>141</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B54" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C54" t="s">
         <v>132</v>
@@ -2897,22 +2897,22 @@
         <v>135</v>
       </c>
       <c r="E54">
-        <v>20.5</v>
+        <v>18.5</v>
       </c>
       <c r="F54">
-        <v>24</v>
+        <v>26.1</v>
       </c>
       <c r="G54" s="1">
-        <v>0.924</v>
+        <v>0.853</v>
       </c>
       <c r="H54" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I54" s="2">
-        <v>76.33</v>
+        <v>62.91</v>
       </c>
       <c r="J54" s="2">
-        <v>0.84</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="K54" t="s">
         <v>141</v>
@@ -2923,34 +2923,34 @@
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B55" t="s">
         <v>115</v>
       </c>
       <c r="C55" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="D55" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E55">
-        <v>15.5</v>
+        <v>3.5</v>
       </c>
       <c r="F55">
-        <v>13.07</v>
+        <v>6.05</v>
       </c>
       <c r="G55" s="1">
-        <v>0.91</v>
+        <v>0.853</v>
       </c>
       <c r="H55" t="s">
         <v>139</v>
       </c>
       <c r="I55" s="2">
-        <v>73.75</v>
+        <v>62.9</v>
       </c>
       <c r="J55" s="2">
-        <v>0.8110000000000001</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="K55" t="s">
         <v>141</v>
@@ -2961,34 +2961,34 @@
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="B56" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C56" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D56" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E56">
-        <v>11.5</v>
+        <v>9.5</v>
       </c>
       <c r="F56">
-        <v>13.99</v>
+        <v>5.78</v>
       </c>
       <c r="G56" s="1">
-        <v>0.908</v>
+        <v>0.852</v>
       </c>
       <c r="H56" t="s">
         <v>140</v>
       </c>
       <c r="I56" s="2">
-        <v>73.37</v>
+        <v>62.6</v>
       </c>
       <c r="J56" s="2">
-        <v>0.8070000000000001</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="K56" t="s">
         <v>141</v>
@@ -2999,34 +2999,34 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B57" t="s">
+        <v>128</v>
+      </c>
+      <c r="C57" t="s">
         <v>114</v>
       </c>
-      <c r="C57" t="s">
-        <v>124</v>
-      </c>
       <c r="D57" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E57">
-        <v>34.5</v>
+        <v>6.5</v>
       </c>
       <c r="F57">
-        <v>30.81</v>
+        <v>3.29</v>
       </c>
       <c r="G57" s="1">
-        <v>0.908</v>
+        <v>0.849</v>
       </c>
       <c r="H57" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I57" s="2">
-        <v>73.33</v>
+        <v>62.08</v>
       </c>
       <c r="J57" s="2">
-        <v>0.8070000000000001</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="K57" t="s">
         <v>141</v>
@@ -3037,34 +3037,34 @@
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C58" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="D58" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E58">
-        <v>34.5</v>
+        <v>7.5</v>
       </c>
       <c r="F58">
-        <v>30.86</v>
+        <v>4.17</v>
       </c>
       <c r="G58" s="1">
-        <v>0.905</v>
+        <v>0.845</v>
       </c>
       <c r="H58" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I58" s="2">
-        <v>72.8</v>
+        <v>61.36</v>
       </c>
       <c r="J58" s="2">
-        <v>0.801</v>
+        <v>0.675</v>
       </c>
       <c r="K58" t="s">
         <v>141</v>
@@ -3075,34 +3075,34 @@
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C59" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D59" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E59">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="F59">
-        <v>13.91</v>
+        <v>2.66</v>
       </c>
       <c r="G59" s="1">
-        <v>0.902</v>
+        <v>0.84</v>
       </c>
       <c r="H59" t="s">
         <v>140</v>
       </c>
       <c r="I59" s="2">
-        <v>72.19</v>
+        <v>60.43</v>
       </c>
       <c r="J59" s="2">
-        <v>0.794</v>
+        <v>0.665</v>
       </c>
       <c r="K59" t="s">
         <v>141</v>
@@ -3113,34 +3113,34 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C60" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D60" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E60">
-        <v>10.5</v>
+        <v>33.5</v>
       </c>
       <c r="F60">
-        <v>12.78</v>
+        <v>25.92</v>
       </c>
       <c r="G60" s="1">
-        <v>0.899</v>
+        <v>0.839</v>
       </c>
       <c r="H60" t="s">
         <v>140</v>
       </c>
       <c r="I60" s="2">
-        <v>71.59999999999999</v>
+        <v>60.2</v>
       </c>
       <c r="J60" s="2">
-        <v>0.788</v>
+        <v>0.662</v>
       </c>
       <c r="K60" t="s">
         <v>141</v>
@@ -3151,34 +3151,34 @@
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C61" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D61" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E61">
-        <v>8.5</v>
+        <v>20.5</v>
       </c>
       <c r="F61">
-        <v>6.87</v>
+        <v>29.31</v>
       </c>
       <c r="G61" s="1">
-        <v>0.894</v>
+        <v>0.839</v>
       </c>
       <c r="H61" t="s">
         <v>139</v>
       </c>
       <c r="I61" s="2">
-        <v>70.62</v>
+        <v>60.13</v>
       </c>
       <c r="J61" s="2">
-        <v>0.777</v>
+        <v>0.661</v>
       </c>
       <c r="K61" t="s">
         <v>141</v>
@@ -3189,34 +3189,34 @@
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C62" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D62" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E62">
-        <v>28.5</v>
+        <v>19.5</v>
       </c>
       <c r="F62">
-        <v>25.4</v>
+        <v>26.12</v>
       </c>
       <c r="G62" s="1">
-        <v>0.89</v>
+        <v>0.838</v>
       </c>
       <c r="H62" t="s">
         <v>139</v>
       </c>
       <c r="I62" s="2">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="J62" s="2">
-        <v>0.77</v>
+        <v>0.66</v>
       </c>
       <c r="K62" t="s">
         <v>141</v>
@@ -3227,34 +3227,34 @@
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B63" t="s">
+        <v>117</v>
+      </c>
+      <c r="C63" t="s">
         <v>123</v>
       </c>
-      <c r="C63" t="s">
-        <v>128</v>
-      </c>
       <c r="D63" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E63">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="F63">
-        <v>8.75</v>
+        <v>5.5</v>
       </c>
       <c r="G63" s="1">
-        <v>0.881</v>
+        <v>0.838</v>
       </c>
       <c r="H63" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I63" s="2">
-        <v>68.22</v>
+        <v>59.97</v>
       </c>
       <c r="J63" s="2">
-        <v>0.75</v>
+        <v>0.66</v>
       </c>
       <c r="K63" t="s">
         <v>141</v>
@@ -3265,34 +3265,34 @@
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B64" t="s">
         <v>126</v>
       </c>
       <c r="C64" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D64" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E64">
-        <v>18.5</v>
+        <v>3.5</v>
       </c>
       <c r="F64">
-        <v>21.21</v>
+        <v>5.84</v>
       </c>
       <c r="G64" s="1">
-        <v>0.88</v>
+        <v>0.834</v>
       </c>
       <c r="H64" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I64" s="2">
-        <v>68.05</v>
+        <v>59.23</v>
       </c>
       <c r="J64" s="2">
-        <v>0.749</v>
+        <v>0.652</v>
       </c>
       <c r="K64" t="s">
         <v>141</v>
@@ -3303,34 +3303,34 @@
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C65" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D65" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E65">
-        <v>7.5</v>
+        <v>15.5</v>
       </c>
       <c r="F65">
-        <v>9.25</v>
+        <v>11.06</v>
       </c>
       <c r="G65" s="1">
-        <v>0.875</v>
+        <v>0.83</v>
       </c>
       <c r="H65" t="s">
         <v>140</v>
       </c>
       <c r="I65" s="2">
-        <v>67.13</v>
+        <v>58.48</v>
       </c>
       <c r="J65" s="2">
-        <v>0.738</v>
+        <v>0.643</v>
       </c>
       <c r="K65" t="s">
         <v>141</v>
@@ -3341,34 +3341,34 @@
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B66" t="s">
         <v>118</v>
       </c>
       <c r="C66" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D66" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E66">
         <v>11.5</v>
       </c>
       <c r="F66">
-        <v>9.77</v>
+        <v>4.38</v>
       </c>
       <c r="G66" s="1">
-        <v>0.865</v>
+        <v>0.83</v>
       </c>
       <c r="H66" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I66" s="2">
-        <v>65.15000000000001</v>
+        <v>58.42</v>
       </c>
       <c r="J66" s="2">
-        <v>0.717</v>
+        <v>0.643</v>
       </c>
       <c r="K66" t="s">
         <v>141</v>
@@ -3379,34 +3379,34 @@
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C67" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D67" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E67">
-        <v>19.5</v>
+        <v>3.5</v>
       </c>
       <c r="F67">
-        <v>22.09</v>
+        <v>5.77</v>
       </c>
       <c r="G67" s="1">
-        <v>0.865</v>
+        <v>0.827</v>
       </c>
       <c r="H67" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I67" s="2">
-        <v>65.12</v>
+        <v>57.87</v>
       </c>
       <c r="J67" s="2">
-        <v>0.716</v>
+        <v>0.637</v>
       </c>
       <c r="K67" t="s">
         <v>141</v>
@@ -3417,34 +3417,34 @@
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C68" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D68" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E68">
-        <v>8.5</v>
+        <v>26.5</v>
       </c>
       <c r="F68">
-        <v>7.08</v>
+        <v>32.25</v>
       </c>
       <c r="G68" s="1">
-        <v>0.857</v>
+        <v>0.824</v>
       </c>
       <c r="H68" t="s">
         <v>139</v>
       </c>
       <c r="I68" s="2">
-        <v>63.65</v>
+        <v>57.37</v>
       </c>
       <c r="J68" s="2">
-        <v>0.7</v>
+        <v>0.631</v>
       </c>
       <c r="K68" t="s">
         <v>141</v>
@@ -3455,34 +3455,34 @@
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="C69" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D69" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E69">
-        <v>12.5</v>
+        <v>22.5</v>
       </c>
       <c r="F69">
-        <v>10.75</v>
+        <v>29.31</v>
       </c>
       <c r="G69" s="1">
-        <v>0.857</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H69" t="s">
         <v>139</v>
       </c>
       <c r="I69" s="2">
-        <v>63.55</v>
+        <v>55.84</v>
       </c>
       <c r="J69" s="2">
-        <v>0.699</v>
+        <v>0.614</v>
       </c>
       <c r="K69" t="s">
         <v>141</v>
@@ -3493,34 +3493,34 @@
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="B70" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C70" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D70" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E70">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="F70">
-        <v>5.94</v>
+        <v>4.41</v>
       </c>
       <c r="G70" s="1">
-        <v>0.853</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H70" t="s">
         <v>139</v>
       </c>
       <c r="I70" s="2">
-        <v>62.89</v>
+        <v>55.68</v>
       </c>
       <c r="J70" s="2">
-        <v>0.6919999999999999</v>
+        <v>0.612</v>
       </c>
       <c r="K70" t="s">
         <v>141</v>
@@ -3531,34 +3531,34 @@
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="C71" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D71" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E71">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="F71">
-        <v>16.56</v>
+        <v>6.36</v>
       </c>
       <c r="G71" s="1">
-        <v>0.844</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H71" t="s">
         <v>140</v>
       </c>
       <c r="I71" s="2">
-        <v>61.18</v>
+        <v>55.14</v>
       </c>
       <c r="J71" s="2">
-        <v>0.673</v>
+        <v>0.607</v>
       </c>
       <c r="K71" t="s">
         <v>141</v>
@@ -3569,34 +3569,34 @@
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C72" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D72" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E72">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="F72">
-        <v>14.41</v>
+        <v>3.86</v>
       </c>
       <c r="G72" s="1">
-        <v>0.843</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="H72" t="s">
         <v>140</v>
       </c>
       <c r="I72" s="2">
-        <v>60.87</v>
+        <v>54.25</v>
       </c>
       <c r="J72" s="2">
-        <v>0.67</v>
+        <v>0.597</v>
       </c>
       <c r="K72" t="s">
         <v>141</v>
@@ -3607,34 +3607,34 @@
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B73" t="s">
+        <v>120</v>
+      </c>
+      <c r="C73" t="s">
         <v>121</v>
       </c>
-      <c r="C73" t="s">
-        <v>120</v>
-      </c>
       <c r="D73" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E73">
         <v>8.5</v>
       </c>
       <c r="F73">
-        <v>7.17</v>
+        <v>4.94</v>
       </c>
       <c r="G73" s="1">
-        <v>0.84</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="H73" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I73" s="2">
-        <v>60.36</v>
+        <v>54.03</v>
       </c>
       <c r="J73" s="2">
-        <v>0.664</v>
+        <v>0.594</v>
       </c>
       <c r="K73" t="s">
         <v>141</v>
@@ -3645,34 +3645,34 @@
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C74" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D74" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E74">
-        <v>20.5</v>
+        <v>8.5</v>
       </c>
       <c r="F74">
-        <v>22.88</v>
+        <v>5.16</v>
       </c>
       <c r="G74" s="1">
-        <v>0.84</v>
+        <v>0.804</v>
       </c>
       <c r="H74" t="s">
         <v>140</v>
       </c>
       <c r="I74" s="2">
-        <v>60.35</v>
+        <v>53.46</v>
       </c>
       <c r="J74" s="2">
-        <v>0.664</v>
+        <v>0.588</v>
       </c>
       <c r="K74" t="s">
         <v>141</v>
@@ -3683,13 +3683,13 @@
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C75" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D75" t="s">
         <v>135</v>
@@ -3698,19 +3698,19 @@
         <v>15.5</v>
       </c>
       <c r="F75">
-        <v>17.49</v>
+        <v>24.21</v>
       </c>
       <c r="G75" s="1">
-        <v>0.829</v>
+        <v>0.802</v>
       </c>
       <c r="H75" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I75" s="2">
-        <v>58.31</v>
+        <v>53.02</v>
       </c>
       <c r="J75" s="2">
-        <v>0.641</v>
+        <v>0.583</v>
       </c>
       <c r="K75" t="s">
         <v>141</v>
@@ -3721,34 +3721,34 @@
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C76" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D76" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E76">
-        <v>45.5</v>
+        <v>6.5</v>
       </c>
       <c r="F76">
-        <v>42.43</v>
+        <v>3.82</v>
       </c>
       <c r="G76" s="1">
-        <v>0.827</v>
+        <v>0.801</v>
       </c>
       <c r="H76" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I76" s="2">
-        <v>57.9</v>
+        <v>52.85</v>
       </c>
       <c r="J76" s="2">
-        <v>0.637</v>
+        <v>0.581</v>
       </c>
       <c r="K76" t="s">
         <v>141</v>
@@ -3759,34 +3759,34 @@
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C77" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="D77" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E77">
-        <v>5.5</v>
+        <v>26.5</v>
       </c>
       <c r="F77">
-        <v>3.75</v>
+        <v>31.68</v>
       </c>
       <c r="G77" s="1">
-        <v>0.824</v>
+        <v>0.795</v>
       </c>
       <c r="H77" t="s">
         <v>139</v>
       </c>
       <c r="I77" s="2">
-        <v>57.22</v>
+        <v>51.8</v>
       </c>
       <c r="J77" s="2">
-        <v>0.629</v>
+        <v>0.57</v>
       </c>
       <c r="K77" t="s">
         <v>141</v>
@@ -3797,34 +3797,34 @@
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C78" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D78" t="s">
         <v>137</v>
       </c>
       <c r="E78">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="F78">
-        <v>4.6</v>
+        <v>4.22</v>
       </c>
       <c r="G78" s="1">
-        <v>0.8179999999999999</v>
+        <v>0.793</v>
       </c>
       <c r="H78" t="s">
         <v>139</v>
       </c>
       <c r="I78" s="2">
-        <v>56.21</v>
+        <v>51.35</v>
       </c>
       <c r="J78" s="2">
-        <v>0.618</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K78" t="s">
         <v>141</v>
@@ -3835,34 +3835,34 @@
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="C79" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D79" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E79">
-        <v>18.5</v>
+        <v>7.5</v>
       </c>
       <c r="F79">
-        <v>20.55</v>
+        <v>4.88</v>
       </c>
       <c r="G79" s="1">
-        <v>0.8179999999999999</v>
+        <v>0.789</v>
       </c>
       <c r="H79" t="s">
         <v>140</v>
       </c>
       <c r="I79" s="2">
-        <v>56.08</v>
+        <v>50.67</v>
       </c>
       <c r="J79" s="2">
-        <v>0.617</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="K79" t="s">
         <v>141</v>
@@ -3873,34 +3873,34 @@
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C80" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D80" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E80">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="F80">
-        <v>7.28</v>
+        <v>13.87</v>
       </c>
       <c r="G80" s="1">
-        <v>0.8179999999999999</v>
+        <v>0.789</v>
       </c>
       <c r="H80" t="s">
         <v>139</v>
       </c>
       <c r="I80" s="2">
-        <v>56.07</v>
+        <v>50.63</v>
       </c>
       <c r="J80" s="2">
-        <v>0.617</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="K80" t="s">
         <v>141</v>
@@ -3911,34 +3911,34 @@
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C81" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="D81" t="s">
         <v>137</v>
       </c>
       <c r="E81">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="F81">
-        <v>4.35</v>
+        <v>2.86</v>
       </c>
       <c r="G81" s="1">
-        <v>0.8090000000000001</v>
+        <v>0.782</v>
       </c>
       <c r="H81" t="s">
         <v>140</v>
       </c>
       <c r="I81" s="2">
-        <v>54.47</v>
+        <v>49.32</v>
       </c>
       <c r="J81" s="2">
-        <v>0.599</v>
+        <v>0.543</v>
       </c>
       <c r="K81" t="s">
         <v>141</v>
@@ -3949,34 +3949,34 @@
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="B82" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C82" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D82" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E82">
-        <v>11.5</v>
+        <v>2.5</v>
       </c>
       <c r="F82">
-        <v>10.12</v>
+        <v>4.13</v>
       </c>
       <c r="G82" s="1">
-        <v>0.8070000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="H82" t="s">
         <v>139</v>
       </c>
       <c r="I82" s="2">
-        <v>54.14</v>
+        <v>48.95</v>
       </c>
       <c r="J82" s="2">
-        <v>0.595</v>
+        <v>0.538</v>
       </c>
       <c r="K82" t="s">
         <v>141</v>
@@ -3987,34 +3987,34 @@
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B83" t="s">
+        <v>128</v>
+      </c>
+      <c r="C83" t="s">
         <v>114</v>
       </c>
-      <c r="C83" t="s">
-        <v>124</v>
-      </c>
       <c r="D83" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E83">
-        <v>39.5</v>
+        <v>2.5</v>
       </c>
       <c r="F83">
-        <v>36.88</v>
+        <v>4.12</v>
       </c>
       <c r="G83" s="1">
-        <v>0.805</v>
+        <v>0.78</v>
       </c>
       <c r="H83" t="s">
         <v>139</v>
       </c>
       <c r="I83" s="2">
-        <v>53.77</v>
+        <v>48.82</v>
       </c>
       <c r="J83" s="2">
-        <v>0.591</v>
+        <v>0.537</v>
       </c>
       <c r="K83" t="s">
         <v>141</v>
@@ -4025,34 +4025,34 @@
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B84" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C84" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D84" t="s">
         <v>137</v>
       </c>
       <c r="E84">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="F84">
-        <v>6.41</v>
+        <v>4.1</v>
       </c>
       <c r="G84" s="1">
-        <v>0.802</v>
+        <v>0.776</v>
       </c>
       <c r="H84" t="s">
         <v>139</v>
       </c>
       <c r="I84" s="2">
-        <v>53.05</v>
+        <v>48.09</v>
       </c>
       <c r="J84" s="2">
-        <v>0.584</v>
+        <v>0.529</v>
       </c>
       <c r="K84" t="s">
         <v>141</v>
@@ -4063,34 +4063,34 @@
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B85" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C85" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="D85" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E85">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="F85">
-        <v>5.61</v>
+        <v>5.25</v>
       </c>
       <c r="G85" s="1">
-        <v>0.796</v>
+        <v>0.769</v>
       </c>
       <c r="H85" t="s">
         <v>139</v>
       </c>
       <c r="I85" s="2">
-        <v>51.91</v>
+        <v>46.78</v>
       </c>
       <c r="J85" s="2">
-        <v>0.571</v>
+        <v>0.515</v>
       </c>
       <c r="K85" t="s">
         <v>141</v>
@@ -4101,34 +4101,34 @@
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B86" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="C86" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D86" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E86">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="F86">
-        <v>10.85</v>
+        <v>3.19</v>
       </c>
       <c r="G86" s="1">
-        <v>0.793</v>
+        <v>0.768</v>
       </c>
       <c r="H86" t="s">
         <v>140</v>
       </c>
       <c r="I86" s="2">
-        <v>51.46</v>
+        <v>46.67</v>
       </c>
       <c r="J86" s="2">
-        <v>0.5659999999999999</v>
+        <v>0.513</v>
       </c>
       <c r="K86" t="s">
         <v>141</v>
@@ -4139,34 +4139,34 @@
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B87" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C87" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D87" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E87">
-        <v>13.5</v>
+        <v>6.5</v>
       </c>
       <c r="F87">
-        <v>15.08</v>
+        <v>4.36</v>
       </c>
       <c r="G87" s="1">
-        <v>0.792</v>
+        <v>0.768</v>
       </c>
       <c r="H87" t="s">
         <v>140</v>
       </c>
       <c r="I87" s="2">
-        <v>51.28</v>
+        <v>46.6</v>
       </c>
       <c r="J87" s="2">
-        <v>0.5639999999999999</v>
+        <v>0.513</v>
       </c>
       <c r="K87" t="s">
         <v>141</v>
@@ -4177,34 +4177,34 @@
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="B88" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="C88" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="D88" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E88">
-        <v>1.5</v>
+        <v>39.5</v>
       </c>
       <c r="F88">
-        <v>2.91</v>
+        <v>49.5</v>
       </c>
       <c r="G88" s="1">
-        <v>0.787</v>
+        <v>0.765</v>
       </c>
       <c r="H88" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I88" s="2">
-        <v>50.2</v>
+        <v>45.96</v>
       </c>
       <c r="J88" s="2">
-        <v>0.552</v>
+        <v>0.506</v>
       </c>
       <c r="K88" t="s">
         <v>141</v>
@@ -4215,34 +4215,34 @@
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>97</v>
+        <v>23</v>
       </c>
       <c r="B89" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C89" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D89" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E89">
-        <v>13.5</v>
+        <v>2.5</v>
       </c>
       <c r="F89">
-        <v>12.12</v>
+        <v>4.01</v>
       </c>
       <c r="G89" s="1">
-        <v>0.786</v>
+        <v>0.764</v>
       </c>
       <c r="H89" t="s">
         <v>139</v>
       </c>
       <c r="I89" s="2">
-        <v>50.11</v>
+        <v>45.83</v>
       </c>
       <c r="J89" s="2">
-        <v>0.551</v>
+        <v>0.504</v>
       </c>
       <c r="K89" t="s">
         <v>141</v>
@@ -4253,34 +4253,34 @@
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B90" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C90" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="D90" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E90">
-        <v>28.5</v>
+        <v>3.5</v>
       </c>
       <c r="F90">
-        <v>26.49</v>
+        <v>5.2</v>
       </c>
       <c r="G90" s="1">
-        <v>0.782</v>
+        <v>0.762</v>
       </c>
       <c r="H90" t="s">
         <v>139</v>
       </c>
       <c r="I90" s="2">
-        <v>49.37</v>
+        <v>45.45</v>
       </c>
       <c r="J90" s="2">
-        <v>0.543</v>
+        <v>0.5</v>
       </c>
       <c r="K90" t="s">
         <v>141</v>
@@ -4291,34 +4291,34 @@
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="B91" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="C91" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D91" t="s">
         <v>138</v>
       </c>
       <c r="E91">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="F91">
-        <v>2.83</v>
+        <v>10.53</v>
       </c>
       <c r="G91" s="1">
-        <v>0.774</v>
+        <v>0.76</v>
       </c>
       <c r="H91" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I91" s="2">
-        <v>47.74</v>
+        <v>45.02</v>
       </c>
       <c r="J91" s="2">
-        <v>0.525</v>
+        <v>0.495</v>
       </c>
       <c r="K91" t="s">
         <v>141</v>
@@ -4329,34 +4329,34 @@
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B92" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C92" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D92" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E92">
-        <v>9.5</v>
+        <v>5.5</v>
       </c>
       <c r="F92">
-        <v>8.470000000000001</v>
+        <v>4.19</v>
       </c>
       <c r="G92" s="1">
-        <v>0.76</v>
+        <v>0.755</v>
       </c>
       <c r="H92" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I92" s="2">
-        <v>45.07</v>
+        <v>44.07</v>
       </c>
       <c r="J92" s="2">
-        <v>0.496</v>
+        <v>0.485</v>
       </c>
       <c r="K92" t="s">
         <v>141</v>
@@ -4367,34 +4367,34 @@
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="B93" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C93" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D93" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E93">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="F93">
-        <v>11.64</v>
+        <v>24.07</v>
       </c>
       <c r="G93" s="1">
-        <v>0.748</v>
+        <v>0.753</v>
       </c>
       <c r="H93" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I93" s="2">
-        <v>42.8</v>
+        <v>43.71</v>
       </c>
       <c r="J93" s="2">
-        <v>0.471</v>
+        <v>0.481</v>
       </c>
       <c r="K93" t="s">
         <v>141</v>
@@ -4405,22 +4405,22 @@
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="B94" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="C94" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="D94" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E94">
-        <v>22.5</v>
+        <v>8.5</v>
       </c>
       <c r="F94">
-        <v>24.1</v>
+        <v>3.53</v>
       </c>
       <c r="G94" s="1">
         <v>0.743</v>
@@ -4429,7 +4429,7 @@
         <v>140</v>
       </c>
       <c r="I94" s="2">
-        <v>41.88</v>
+        <v>41.91</v>
       </c>
       <c r="J94" s="2">
         <v>0.461</v>
@@ -4443,34 +4443,34 @@
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B95" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C95" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D95" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E95">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="F95">
-        <v>3.41</v>
+        <v>2.65</v>
       </c>
       <c r="G95" s="1">
-        <v>0.743</v>
+        <v>0.742</v>
       </c>
       <c r="H95" t="s">
         <v>139</v>
       </c>
       <c r="I95" s="2">
-        <v>41.82</v>
+        <v>41.7</v>
       </c>
       <c r="J95" s="2">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="K95" t="s">
         <v>141</v>
@@ -4481,34 +4481,34 @@
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B96" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C96" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D96" t="s">
         <v>134</v>
       </c>
       <c r="E96">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="F96">
-        <v>13.69</v>
+        <v>18.48</v>
       </c>
       <c r="G96" s="1">
-        <v>0.74</v>
+        <v>0.742</v>
       </c>
       <c r="H96" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I96" s="2">
-        <v>41.37</v>
+        <v>41.64</v>
       </c>
       <c r="J96" s="2">
-        <v>0.455</v>
+        <v>0.458</v>
       </c>
       <c r="K96" t="s">
         <v>141</v>
@@ -4519,34 +4519,34 @@
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="B97" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="C97" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D97" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E97">
-        <v>10.5</v>
+        <v>7.5</v>
       </c>
       <c r="F97">
-        <v>9.51</v>
+        <v>5.67</v>
       </c>
       <c r="G97" s="1">
-        <v>0.739</v>
+        <v>0.741</v>
       </c>
       <c r="H97" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I97" s="2">
-        <v>41.15</v>
+        <v>41.54</v>
       </c>
       <c r="J97" s="2">
-        <v>0.453</v>
+        <v>0.457</v>
       </c>
       <c r="K97" t="s">
         <v>141</v>
@@ -4557,34 +4557,34 @@
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C98" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="D98" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E98">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="F98">
-        <v>8.59</v>
+        <v>6.05</v>
       </c>
       <c r="G98" s="1">
-        <v>0.733</v>
+        <v>0.736</v>
       </c>
       <c r="H98" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I98" s="2">
-        <v>40.03</v>
+        <v>40.59</v>
       </c>
       <c r="J98" s="2">
-        <v>0.44</v>
+        <v>0.446</v>
       </c>
       <c r="K98" t="s">
         <v>141</v>
@@ -4595,34 +4595,34 @@
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="C99" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D99" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E99">
-        <v>2.5</v>
+        <v>28.5</v>
       </c>
       <c r="F99">
-        <v>3.79</v>
+        <v>21.53</v>
       </c>
       <c r="G99" s="1">
-        <v>0.729</v>
+        <v>0.732</v>
       </c>
       <c r="H99" t="s">
         <v>140</v>
       </c>
       <c r="I99" s="2">
-        <v>39.19</v>
+        <v>39.76</v>
       </c>
       <c r="J99" s="2">
-        <v>0.431</v>
+        <v>0.437</v>
       </c>
       <c r="K99" t="s">
         <v>141</v>
@@ -4633,34 +4633,34 @@
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="B100" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C100" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D100" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E100">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="F100">
-        <v>2.58</v>
+        <v>3.48</v>
       </c>
       <c r="G100" s="1">
-        <v>0.728</v>
+        <v>0.73</v>
       </c>
       <c r="H100" t="s">
         <v>140</v>
       </c>
       <c r="I100" s="2">
-        <v>39</v>
+        <v>39.3</v>
       </c>
       <c r="J100" s="2">
-        <v>0.429</v>
+        <v>0.432</v>
       </c>
       <c r="K100" t="s">
         <v>141</v>
@@ -4671,34 +4671,34 @@
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B101" t="s">
         <v>126</v>
       </c>
       <c r="C101" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D101" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E101">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="F101">
-        <v>6.12</v>
+        <v>2.62</v>
       </c>
       <c r="G101" s="1">
-        <v>0.727</v>
+        <v>0.729</v>
       </c>
       <c r="H101" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I101" s="2">
-        <v>38.86</v>
+        <v>39.18</v>
       </c>
       <c r="J101" s="2">
-        <v>0.427</v>
+        <v>0.431</v>
       </c>
       <c r="K101" t="s">
         <v>141</v>
@@ -4709,34 +4709,34 @@
     </row>
     <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="B102" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C102" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D102" t="s">
         <v>137</v>
       </c>
       <c r="E102">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="F102">
-        <v>2.57</v>
+        <v>6.7</v>
       </c>
       <c r="G102" s="1">
-        <v>0.727</v>
+        <v>0.728</v>
       </c>
       <c r="H102" t="s">
         <v>140</v>
       </c>
       <c r="I102" s="2">
-        <v>38.86</v>
+        <v>39.02</v>
       </c>
       <c r="J102" s="2">
-        <v>0.427</v>
+        <v>0.429</v>
       </c>
       <c r="K102" t="s">
         <v>141</v>
@@ -4747,22 +4747,22 @@
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>45</v>
+        <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C103" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D103" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E103">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="F103">
-        <v>7.04</v>
+        <v>13.43</v>
       </c>
       <c r="G103" s="1">
         <v>0.723</v>
@@ -4771,7 +4771,7 @@
         <v>139</v>
       </c>
       <c r="I103" s="2">
-        <v>38.1</v>
+        <v>38.11</v>
       </c>
       <c r="J103" s="2">
         <v>0.419</v>
@@ -4785,34 +4785,34 @@
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="B104" t="s">
+        <v>117</v>
+      </c>
+      <c r="C104" t="s">
         <v>123</v>
       </c>
-      <c r="C104" t="s">
-        <v>128</v>
-      </c>
       <c r="D104" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E104">
-        <v>17.5</v>
+        <v>4.5</v>
       </c>
       <c r="F104">
-        <v>18.77</v>
+        <v>6.05</v>
       </c>
       <c r="G104" s="1">
-        <v>0.722</v>
+        <v>0.721</v>
       </c>
       <c r="H104" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I104" s="2">
-        <v>37.82</v>
+        <v>37.72</v>
       </c>
       <c r="J104" s="2">
-        <v>0.416</v>
+        <v>0.415</v>
       </c>
       <c r="K104" t="s">
         <v>141</v>
@@ -4823,34 +4823,34 @@
     </row>
     <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="B105" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C105" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D105" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E105">
-        <v>1.5</v>
+        <v>13.5</v>
       </c>
       <c r="F105">
-        <v>2.53</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="G105" s="1">
-        <v>0.719</v>
+        <v>0.716</v>
       </c>
       <c r="H105" t="s">
         <v>140</v>
       </c>
       <c r="I105" s="2">
-        <v>37.32</v>
+        <v>36.78</v>
       </c>
       <c r="J105" s="2">
-        <v>0.411</v>
+        <v>0.405</v>
       </c>
       <c r="K105" t="s">
         <v>141</v>
@@ -4867,28 +4867,28 @@
         <v>115</v>
       </c>
       <c r="C106" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="D106" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E106">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="F106">
-        <v>7.72</v>
+        <v>4.92</v>
       </c>
       <c r="G106" s="1">
-        <v>0.714</v>
+        <v>0.716</v>
       </c>
       <c r="H106" t="s">
         <v>139</v>
       </c>
       <c r="I106" s="2">
-        <v>36.24</v>
+        <v>36.75</v>
       </c>
       <c r="J106" s="2">
-        <v>0.399</v>
+        <v>0.404</v>
       </c>
       <c r="K106" t="s">
         <v>141</v>
@@ -4899,34 +4899,34 @@
     </row>
     <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="B107" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C107" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D107" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E107">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F107">
-        <v>1.89</v>
+        <v>2.51</v>
       </c>
       <c r="G107" s="1">
-        <v>0.708</v>
+        <v>0.715</v>
       </c>
       <c r="H107" t="s">
         <v>139</v>
       </c>
       <c r="I107" s="2">
-        <v>35.12</v>
+        <v>36.59</v>
       </c>
       <c r="J107" s="2">
-        <v>0.386</v>
+        <v>0.403</v>
       </c>
       <c r="K107" t="s">
         <v>141</v>
@@ -4937,34 +4937,34 @@
     </row>
     <row r="108" spans="1:12">
       <c r="A108" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="B108" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C108" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D108" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E108">
-        <v>9.5</v>
+        <v>2.5</v>
       </c>
       <c r="F108">
-        <v>8.119999999999999</v>
+        <v>3.68</v>
       </c>
       <c r="G108" s="1">
-        <v>0.701</v>
+        <v>0.712</v>
       </c>
       <c r="H108" t="s">
         <v>139</v>
       </c>
       <c r="I108" s="2">
-        <v>33.89</v>
+        <v>35.92</v>
       </c>
       <c r="J108" s="2">
-        <v>0.373</v>
+        <v>0.395</v>
       </c>
       <c r="K108" t="s">
         <v>141</v>
@@ -4975,34 +4975,34 @@
     </row>
     <row r="109" spans="1:12">
       <c r="A109" t="s">
-        <v>103</v>
+        <v>29</v>
       </c>
       <c r="B109" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C109" t="s">
         <v>117</v>
       </c>
       <c r="D109" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E109">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="F109">
-        <v>7.77</v>
+        <v>4.84</v>
       </c>
       <c r="G109" s="1">
-        <v>0.701</v>
+        <v>0.711</v>
       </c>
       <c r="H109" t="s">
         <v>139</v>
       </c>
       <c r="I109" s="2">
-        <v>33.83</v>
+        <v>35.76</v>
       </c>
       <c r="J109" s="2">
-        <v>0.372</v>
+        <v>0.393</v>
       </c>
       <c r="K109" t="s">
         <v>141</v>
@@ -5013,34 +5013,34 @@
     </row>
     <row r="110" spans="1:12">
       <c r="A110" t="s">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="B110" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C110" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D110" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E110">
-        <v>19.5</v>
+        <v>4.5</v>
       </c>
       <c r="F110">
-        <v>18.37</v>
+        <v>3.57</v>
       </c>
       <c r="G110" s="1">
-        <v>0.701</v>
+        <v>0.699</v>
       </c>
       <c r="H110" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I110" s="2">
-        <v>33.77</v>
+        <v>33.42</v>
       </c>
       <c r="J110" s="2">
-        <v>0.371</v>
+        <v>0.368</v>
       </c>
       <c r="K110" t="s">
         <v>141</v>
@@ -5051,34 +5051,34 @@
     </row>
     <row r="111" spans="1:12">
       <c r="A111" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B111" t="s">
         <v>130</v>
       </c>
       <c r="C111" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D111" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E111">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="F111">
-        <v>8.25</v>
+        <v>3.57</v>
       </c>
       <c r="G111" s="1">
-        <v>0.7</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H111" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I111" s="2">
-        <v>33.59</v>
+        <v>32.13</v>
       </c>
       <c r="J111" s="2">
-        <v>0.369</v>
+        <v>0.353</v>
       </c>
       <c r="K111" t="s">
         <v>141</v>
@@ -5089,34 +5089,34 @@
     </row>
     <row r="112" spans="1:12">
       <c r="A112" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="B112" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C112" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D112" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E112">
-        <v>18.5</v>
+        <v>1.5</v>
       </c>
       <c r="F112">
-        <v>19.65</v>
+        <v>2.4</v>
       </c>
       <c r="G112" s="1">
-        <v>0.699</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="H112" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I112" s="2">
-        <v>33.37</v>
+        <v>32.01</v>
       </c>
       <c r="J112" s="2">
-        <v>0.367</v>
+        <v>0.352</v>
       </c>
       <c r="K112" t="s">
         <v>141</v>
@@ -5127,34 +5127,34 @@
     </row>
     <row r="113" spans="1:12">
       <c r="A113" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="B113" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C113" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="D113" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E113">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F113">
-        <v>3.59</v>
+        <v>2.39</v>
       </c>
       <c r="G113" s="1">
-        <v>0.695</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="H113" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I113" s="2">
-        <v>32.66</v>
+        <v>31.51</v>
       </c>
       <c r="J113" s="2">
-        <v>0.359</v>
+        <v>0.347</v>
       </c>
       <c r="K113" t="s">
         <v>141</v>
@@ -5165,34 +5165,34 @@
     </row>
     <row r="114" spans="1:12">
       <c r="A114" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="B114" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C114" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="D114" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E114">
-        <v>12.5</v>
+        <v>4.5</v>
       </c>
       <c r="F114">
-        <v>11.67</v>
+        <v>5.81</v>
       </c>
       <c r="G114" s="1">
-        <v>0.6860000000000001</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H114" t="s">
         <v>139</v>
       </c>
       <c r="I114" s="2">
-        <v>31</v>
+        <v>31.43</v>
       </c>
       <c r="J114" s="2">
-        <v>0.341</v>
+        <v>0.346</v>
       </c>
       <c r="K114" t="s">
         <v>141</v>
@@ -5203,34 +5203,34 @@
     </row>
     <row r="115" spans="1:12">
       <c r="A115" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="B115" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C115" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D115" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E115">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="F115">
-        <v>2.83</v>
+        <v>5.9</v>
       </c>
       <c r="G115" s="1">
-        <v>0.6850000000000001</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H115" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I115" s="2">
-        <v>30.79</v>
+        <v>30.4</v>
       </c>
       <c r="J115" s="2">
-        <v>0.339</v>
+        <v>0.334</v>
       </c>
       <c r="K115" t="s">
         <v>141</v>
@@ -5241,34 +5241,34 @@
     </row>
     <row r="116" spans="1:12">
       <c r="A116" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="B116" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="C116" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="D116" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E116">
-        <v>12.5</v>
+        <v>9.5</v>
       </c>
       <c r="F116">
-        <v>13.38</v>
+        <v>12.81</v>
       </c>
       <c r="G116" s="1">
-        <v>0.6850000000000001</v>
+        <v>0.681</v>
       </c>
       <c r="H116" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I116" s="2">
-        <v>30.7</v>
+        <v>30.03</v>
       </c>
       <c r="J116" s="2">
-        <v>0.338</v>
+        <v>0.33</v>
       </c>
       <c r="K116" t="s">
         <v>141</v>
@@ -5279,13 +5279,13 @@
     </row>
     <row r="117" spans="1:12">
       <c r="A117" t="s">
-        <v>109</v>
+        <v>50</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C117" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D117" t="s">
         <v>137</v>
@@ -5294,19 +5294,19 @@
         <v>3.5</v>
       </c>
       <c r="F117">
-        <v>2.84</v>
+        <v>4.63</v>
       </c>
       <c r="G117" s="1">
-        <v>0.6830000000000001</v>
+        <v>0.679</v>
       </c>
       <c r="H117" t="s">
         <v>139</v>
       </c>
       <c r="I117" s="2">
-        <v>30.37</v>
+        <v>29.59</v>
       </c>
       <c r="J117" s="2">
-        <v>0.334</v>
+        <v>0.326</v>
       </c>
       <c r="K117" t="s">
         <v>141</v>
@@ -5317,34 +5317,34 @@
     </row>
     <row r="118" spans="1:12">
       <c r="A118" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B118" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="C118" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="D118" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E118">
-        <v>11.5</v>
+        <v>3.5</v>
       </c>
       <c r="F118">
-        <v>12.32</v>
+        <v>4.88</v>
       </c>
       <c r="G118" s="1">
-        <v>0.68</v>
+        <v>0.675</v>
       </c>
       <c r="H118" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I118" s="2">
-        <v>29.78</v>
+        <v>28.82</v>
       </c>
       <c r="J118" s="2">
-        <v>0.328</v>
+        <v>0.317</v>
       </c>
       <c r="K118" t="s">
         <v>141</v>
@@ -5355,34 +5355,34 @@
     </row>
     <row r="119" spans="1:12">
       <c r="A119" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B119" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C119" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="D119" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E119">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="F119">
-        <v>13.35</v>
+        <v>2.39</v>
       </c>
       <c r="G119" s="1">
-        <v>0.68</v>
+        <v>0.673</v>
       </c>
       <c r="H119" t="s">
         <v>140</v>
       </c>
       <c r="I119" s="2">
-        <v>29.72</v>
+        <v>28.55</v>
       </c>
       <c r="J119" s="2">
-        <v>0.327</v>
+        <v>0.314</v>
       </c>
       <c r="K119" t="s">
         <v>141</v>
@@ -5393,34 +5393,34 @@
     </row>
     <row r="120" spans="1:12">
       <c r="A120" t="s">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="B120" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C120" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="D120" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E120">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F120">
-        <v>4.63</v>
+        <v>5.93</v>
       </c>
       <c r="G120" s="1">
-        <v>0.679</v>
+        <v>0.673</v>
       </c>
       <c r="H120" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I120" s="2">
-        <v>29.67</v>
+        <v>28.39</v>
       </c>
       <c r="J120" s="2">
-        <v>0.326</v>
+        <v>0.312</v>
       </c>
       <c r="K120" t="s">
         <v>141</v>
@@ -5431,34 +5431,34 @@
     </row>
     <row r="121" spans="1:12">
       <c r="A121" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B121" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C121" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="D121" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E121">
-        <v>19.5</v>
+        <v>4.5</v>
       </c>
       <c r="F121">
-        <v>18.52</v>
+        <v>3.79</v>
       </c>
       <c r="G121" s="1">
-        <v>0.675</v>
+        <v>0.666</v>
       </c>
       <c r="H121" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I121" s="2">
-        <v>28.91</v>
+        <v>27.2</v>
       </c>
       <c r="J121" s="2">
-        <v>0.318</v>
+        <v>0.299</v>
       </c>
       <c r="K121" t="s">
         <v>141</v>
@@ -5469,34 +5469,34 @@
     </row>
     <row r="122" spans="1:12">
       <c r="A122" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="B122" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C122" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E122">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="F122">
-        <v>5.65</v>
+        <v>2.27</v>
       </c>
       <c r="G122" s="1">
-        <v>0.666</v>
+        <v>0.661</v>
       </c>
       <c r="H122" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I122" s="2">
-        <v>27.1</v>
+        <v>26.2</v>
       </c>
       <c r="J122" s="2">
-        <v>0.298</v>
+        <v>0.288</v>
       </c>
       <c r="K122" t="s">
         <v>141</v>
@@ -5507,34 +5507,34 @@
     </row>
     <row r="123" spans="1:12">
       <c r="A123" t="s">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="B123" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C123" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="D123" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E123">
-        <v>8.5</v>
+        <v>13.5</v>
       </c>
       <c r="F123">
-        <v>7.92</v>
+        <v>10.82</v>
       </c>
       <c r="G123" s="1">
-        <v>0.661</v>
+        <v>0.66</v>
       </c>
       <c r="H123" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I123" s="2">
-        <v>26.15</v>
+        <v>25.98</v>
       </c>
       <c r="J123" s="2">
-        <v>0.288</v>
+        <v>0.286</v>
       </c>
       <c r="K123" t="s">
         <v>141</v>
@@ -5545,34 +5545,34 @@
     </row>
     <row r="124" spans="1:12">
       <c r="A124" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B124" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="C124" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D124" t="s">
         <v>137</v>
       </c>
       <c r="E124">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="F124">
-        <v>3.34</v>
+        <v>6.56</v>
       </c>
       <c r="G124" s="1">
-        <v>0.649</v>
+        <v>0.655</v>
       </c>
       <c r="H124" t="s">
         <v>140</v>
       </c>
       <c r="I124" s="2">
-        <v>23.84</v>
+        <v>25.13</v>
       </c>
       <c r="J124" s="2">
-        <v>0.262</v>
+        <v>0.276</v>
       </c>
       <c r="K124" t="s">
         <v>141</v>
@@ -5583,34 +5583,34 @@
     </row>
     <row r="125" spans="1:12">
       <c r="A125" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="B125" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="C125" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D125" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E125">
-        <v>3.5</v>
+        <v>29.5</v>
       </c>
       <c r="F125">
-        <v>4.44</v>
+        <v>34.35</v>
       </c>
       <c r="G125" s="1">
-        <v>0.648</v>
+        <v>0.643</v>
       </c>
       <c r="H125" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I125" s="2">
-        <v>23.66</v>
+        <v>22.81</v>
       </c>
       <c r="J125" s="2">
-        <v>0.26</v>
+        <v>0.251</v>
       </c>
       <c r="K125" t="s">
         <v>141</v>
@@ -5621,34 +5621,34 @@
     </row>
     <row r="126" spans="1:12">
       <c r="A126" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="B126" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C126" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D126" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E126">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="F126">
-        <v>4.82</v>
+        <v>14.42</v>
       </c>
       <c r="G126" s="1">
-        <v>0.647</v>
+        <v>0.636</v>
       </c>
       <c r="H126" t="s">
         <v>139</v>
       </c>
       <c r="I126" s="2">
-        <v>23.54</v>
+        <v>21.4</v>
       </c>
       <c r="J126" s="2">
-        <v>0.259</v>
+        <v>0.235</v>
       </c>
       <c r="K126" t="s">
         <v>141</v>
@@ -5659,34 +5659,34 @@
     </row>
     <row r="127" spans="1:12">
       <c r="A127" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B127" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C127" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D127" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E127">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="F127">
-        <v>8.02</v>
+        <v>4.47</v>
       </c>
       <c r="G127" s="1">
-        <v>0.644</v>
+        <v>0.635</v>
       </c>
       <c r="H127" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I127" s="2">
-        <v>23</v>
+        <v>21.31</v>
       </c>
       <c r="J127" s="2">
-        <v>0.253</v>
+        <v>0.234</v>
       </c>
       <c r="K127" t="s">
         <v>141</v>
@@ -5697,34 +5697,34 @@
     </row>
     <row r="128" spans="1:12">
       <c r="A128" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B128" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="C128" t="s">
         <v>129</v>
       </c>
       <c r="D128" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E128">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="F128">
-        <v>4.42</v>
+        <v>6.73</v>
       </c>
       <c r="G128" s="1">
-        <v>0.643</v>
+        <v>0.634</v>
       </c>
       <c r="H128" t="s">
         <v>140</v>
       </c>
       <c r="I128" s="2">
-        <v>22.79</v>
+        <v>20.98</v>
       </c>
       <c r="J128" s="2">
-        <v>0.251</v>
+        <v>0.231</v>
       </c>
       <c r="K128" t="s">
         <v>141</v>
@@ -5735,34 +5735,34 @@
     </row>
     <row r="129" spans="1:12">
       <c r="A129" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="B129" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C129" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="D129" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E129">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="F129">
-        <v>4.34</v>
+        <v>2.39</v>
       </c>
       <c r="G129" s="1">
-        <v>0.63</v>
+        <v>0.627</v>
       </c>
       <c r="H129" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I129" s="2">
-        <v>20.21</v>
+        <v>19.76</v>
       </c>
       <c r="J129" s="2">
-        <v>0.222</v>
+        <v>0.217</v>
       </c>
       <c r="K129" t="s">
         <v>141</v>
@@ -5773,34 +5773,34 @@
     </row>
     <row r="130" spans="1:12">
       <c r="A130" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="B130" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C130" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D130" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E130">
         <v>2.5</v>
       </c>
       <c r="F130">
-        <v>3.24</v>
+        <v>2.26</v>
       </c>
       <c r="G130" s="1">
-        <v>0.629</v>
+        <v>0.626</v>
       </c>
       <c r="H130" t="s">
         <v>140</v>
       </c>
       <c r="I130" s="2">
-        <v>20.03</v>
+        <v>19.51</v>
       </c>
       <c r="J130" s="2">
-        <v>0.22</v>
+        <v>0.215</v>
       </c>
       <c r="K130" t="s">
         <v>141</v>
@@ -5811,34 +5811,34 @@
     </row>
     <row r="131" spans="1:12">
       <c r="A131" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="B131" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="C131" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D131" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E131">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="F131">
-        <v>2.13</v>
+        <v>4.99</v>
       </c>
       <c r="G131" s="1">
-        <v>0.628</v>
+        <v>0.622</v>
       </c>
       <c r="H131" t="s">
         <v>140</v>
       </c>
       <c r="I131" s="2">
-        <v>19.87</v>
+        <v>18.81</v>
       </c>
       <c r="J131" s="2">
-        <v>0.219</v>
+        <v>0.207</v>
       </c>
       <c r="K131" t="s">
         <v>141</v>
@@ -5849,34 +5849,34 @@
     </row>
     <row r="132" spans="1:12">
       <c r="A132" t="s">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="B132" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C132" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D132" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E132">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F132">
-        <v>4.32</v>
+        <v>5.37</v>
       </c>
       <c r="G132" s="1">
-        <v>0.627</v>
+        <v>0.622</v>
       </c>
       <c r="H132" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I132" s="2">
-        <v>19.64</v>
+        <v>18.78</v>
       </c>
       <c r="J132" s="2">
-        <v>0.216</v>
+        <v>0.207</v>
       </c>
       <c r="K132" t="s">
         <v>141</v>
@@ -5887,34 +5887,34 @@
     </row>
     <row r="133" spans="1:12">
       <c r="A133" t="s">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="B133" t="s">
         <v>121</v>
       </c>
       <c r="C133" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="D133" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E133">
-        <v>3.5</v>
+        <v>18.5</v>
       </c>
       <c r="F133">
-        <v>4.3</v>
+        <v>21.01</v>
       </c>
       <c r="G133" s="1">
         <v>0.622</v>
       </c>
       <c r="H133" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I133" s="2">
-        <v>18.78</v>
+        <v>18.67</v>
       </c>
       <c r="J133" s="2">
-        <v>0.207</v>
+        <v>0.205</v>
       </c>
       <c r="K133" t="s">
         <v>141</v>
@@ -5925,31 +5925,31 @@
     </row>
     <row r="134" spans="1:12">
       <c r="A134" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="B134" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C134" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D134" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E134">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="F134">
-        <v>4.29</v>
+        <v>6.48</v>
       </c>
       <c r="G134" s="1">
         <v>0.621</v>
       </c>
       <c r="H134" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I134" s="2">
-        <v>18.58</v>
+        <v>18.57</v>
       </c>
       <c r="J134" s="2">
         <v>0.204</v>
@@ -5963,34 +5963,34 @@
     </row>
     <row r="135" spans="1:12">
       <c r="A135" t="s">
-        <v>31</v>
+        <v>111</v>
       </c>
       <c r="B135" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C135" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D135" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E135">
         <v>3.5</v>
       </c>
       <c r="F135">
-        <v>4.27</v>
+        <v>3.23</v>
       </c>
       <c r="G135" s="1">
-        <v>0.617</v>
+        <v>0.62</v>
       </c>
       <c r="H135" t="s">
         <v>140</v>
       </c>
       <c r="I135" s="2">
-        <v>17.79</v>
+        <v>18.42</v>
       </c>
       <c r="J135" s="2">
-        <v>0.196</v>
+        <v>0.203</v>
       </c>
       <c r="K135" t="s">
         <v>141</v>
@@ -6001,34 +6001,34 @@
     </row>
     <row r="136" spans="1:12">
       <c r="A136" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="B136" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C136" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D136" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E136">
         <v>2.5</v>
       </c>
       <c r="F136">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="G136" s="1">
-        <v>0.614</v>
+        <v>0.62</v>
       </c>
       <c r="H136" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I136" s="2">
-        <v>17.13</v>
+        <v>18.3</v>
       </c>
       <c r="J136" s="2">
-        <v>0.188</v>
+        <v>0.201</v>
       </c>
       <c r="K136" t="s">
         <v>141</v>
@@ -6039,34 +6039,34 @@
     </row>
     <row r="137" spans="1:12">
       <c r="A137" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="B137" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C137" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D137" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E137">
-        <v>22.5</v>
+        <v>9.5</v>
       </c>
       <c r="F137">
-        <v>21.83</v>
+        <v>10.71</v>
       </c>
       <c r="G137" s="1">
-        <v>0.612</v>
+        <v>0.62</v>
       </c>
       <c r="H137" t="s">
         <v>139</v>
       </c>
       <c r="I137" s="2">
-        <v>16.91</v>
+        <v>18.29</v>
       </c>
       <c r="J137" s="2">
-        <v>0.186</v>
+        <v>0.201</v>
       </c>
       <c r="K137" t="s">
         <v>141</v>
@@ -6077,34 +6077,34 @@
     </row>
     <row r="138" spans="1:12">
       <c r="A138" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="B138" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="C138" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D138" t="s">
         <v>134</v>
       </c>
       <c r="E138">
-        <v>23.5</v>
+        <v>11.5</v>
       </c>
       <c r="F138">
-        <v>22.82</v>
+        <v>9.23</v>
       </c>
       <c r="G138" s="1">
-        <v>0.612</v>
+        <v>0.618</v>
       </c>
       <c r="H138" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I138" s="2">
-        <v>16.78</v>
+        <v>17.93</v>
       </c>
       <c r="J138" s="2">
-        <v>0.185</v>
+        <v>0.197</v>
       </c>
       <c r="K138" t="s">
         <v>141</v>
@@ -6121,28 +6121,28 @@
         <v>118</v>
       </c>
       <c r="C139" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D139" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E139">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F139">
-        <v>4.17</v>
+        <v>2.46</v>
       </c>
       <c r="G139" s="1">
-        <v>0.6</v>
+        <v>0.618</v>
       </c>
       <c r="H139" t="s">
         <v>140</v>
       </c>
       <c r="I139" s="2">
-        <v>14.52</v>
+        <v>17.93</v>
       </c>
       <c r="J139" s="2">
-        <v>0.16</v>
+        <v>0.197</v>
       </c>
       <c r="K139" t="s">
         <v>141</v>
@@ -6153,34 +6153,34 @@
     </row>
     <row r="140" spans="1:12">
       <c r="A140" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B140" t="s">
         <v>123</v>
       </c>
       <c r="C140" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D140" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E140">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="F140">
-        <v>2.02</v>
+        <v>9.02</v>
       </c>
       <c r="G140" s="1">
-        <v>0.6</v>
+        <v>0.617</v>
       </c>
       <c r="H140" t="s">
         <v>140</v>
       </c>
       <c r="I140" s="2">
-        <v>14.46</v>
+        <v>17.8</v>
       </c>
       <c r="J140" s="2">
-        <v>0.159</v>
+        <v>0.196</v>
       </c>
       <c r="K140" t="s">
         <v>141</v>
@@ -6191,34 +6191,34 @@
     </row>
     <row r="141" spans="1:12">
       <c r="A141" t="s">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="B141" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="C141" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D141" t="s">
         <v>137</v>
       </c>
       <c r="E141">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="F141">
-        <v>4.12</v>
+        <v>5.95</v>
       </c>
       <c r="G141" s="1">
-        <v>0.59</v>
+        <v>0.615</v>
       </c>
       <c r="H141" t="s">
         <v>140</v>
       </c>
       <c r="I141" s="2">
-        <v>12.69</v>
+        <v>17.38</v>
       </c>
       <c r="J141" s="2">
-        <v>0.14</v>
+        <v>0.191</v>
       </c>
       <c r="K141" t="s">
         <v>141</v>
@@ -6229,34 +6229,34 @@
     </row>
     <row r="142" spans="1:12">
       <c r="A142" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B142" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C142" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D142" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E142">
-        <v>1.5</v>
+        <v>12.5</v>
       </c>
       <c r="F142">
-        <v>1.95</v>
+        <v>10.65</v>
       </c>
       <c r="G142" s="1">
-        <v>0.582</v>
+        <v>0.611</v>
       </c>
       <c r="H142" t="s">
         <v>140</v>
       </c>
       <c r="I142" s="2">
-        <v>11.03</v>
+        <v>16.66</v>
       </c>
       <c r="J142" s="2">
-        <v>0.121</v>
+        <v>0.183</v>
       </c>
       <c r="K142" t="s">
         <v>141</v>
@@ -6267,37 +6267,37 @@
     </row>
     <row r="143" spans="1:12">
       <c r="A143" t="s">
-        <v>50</v>
+        <v>112</v>
       </c>
       <c r="B143" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C143" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D143" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E143">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="F143">
-        <v>7.13</v>
+        <v>4.21</v>
       </c>
       <c r="G143" s="1">
-        <v>0.58</v>
+        <v>0.607</v>
       </c>
       <c r="H143" t="s">
         <v>139</v>
       </c>
       <c r="I143" s="2">
-        <v>10.71</v>
+        <v>15.82</v>
       </c>
       <c r="J143" s="2">
-        <v>0.118</v>
+        <v>0.174</v>
       </c>
       <c r="K143" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L143" t="s">
         <v>145</v>
@@ -6305,37 +6305,37 @@
     </row>
     <row r="144" spans="1:12">
       <c r="A144" t="s">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="B144" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C144" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D144" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E144">
         <v>2.5</v>
       </c>
       <c r="F144">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="G144" s="1">
-        <v>0.576</v>
+        <v>0.606</v>
       </c>
       <c r="H144" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I144" s="2">
-        <v>9.949999999999999</v>
+        <v>15.77</v>
       </c>
       <c r="J144" s="2">
-        <v>0.109</v>
+        <v>0.173</v>
       </c>
       <c r="K144" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L144" t="s">
         <v>145</v>
@@ -6343,37 +6343,37 @@
     </row>
     <row r="145" spans="1:12">
       <c r="A145" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B145" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C145" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="D145" t="s">
         <v>137</v>
       </c>
       <c r="E145">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="F145">
-        <v>1.91</v>
+        <v>5.48</v>
       </c>
       <c r="G145" s="1">
-        <v>0.57</v>
+        <v>0.606</v>
       </c>
       <c r="H145" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I145" s="2">
-        <v>8.859999999999999</v>
+        <v>15.61</v>
       </c>
       <c r="J145" s="2">
-        <v>0.098</v>
+        <v>0.172</v>
       </c>
       <c r="K145" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L145" t="s">
         <v>145</v>
@@ -6381,37 +6381,37 @@
     </row>
     <row r="146" spans="1:12">
       <c r="A146" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B146" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C146" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D146" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E146">
-        <v>3.5</v>
+        <v>18.5</v>
       </c>
       <c r="F146">
-        <v>4.02</v>
+        <v>16.08</v>
       </c>
       <c r="G146" s="1">
-        <v>0.57</v>
+        <v>0.599</v>
       </c>
       <c r="H146" t="s">
         <v>140</v>
       </c>
       <c r="I146" s="2">
-        <v>8.859999999999999</v>
+        <v>14.43</v>
       </c>
       <c r="J146" s="2">
-        <v>0.097</v>
+        <v>0.159</v>
       </c>
       <c r="K146" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L146" t="s">
         <v>145</v>
@@ -6419,37 +6419,37 @@
     </row>
     <row r="147" spans="1:12">
       <c r="A147" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B147" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="C147" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D147" t="s">
         <v>137</v>
       </c>
       <c r="E147">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="F147">
-        <v>1.91</v>
+        <v>6.05</v>
       </c>
       <c r="G147" s="1">
-        <v>0.5679999999999999</v>
+        <v>0.599</v>
       </c>
       <c r="H147" t="s">
         <v>140</v>
       </c>
       <c r="I147" s="2">
-        <v>8.43</v>
+        <v>14.35</v>
       </c>
       <c r="J147" s="2">
-        <v>0.093</v>
+        <v>0.158</v>
       </c>
       <c r="K147" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L147" t="s">
         <v>145</v>
@@ -6457,37 +6457,37 @@
     </row>
     <row r="148" spans="1:12">
       <c r="A148" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="B148" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C148" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D148" t="s">
         <v>138</v>
       </c>
       <c r="E148">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="F148">
-        <v>4</v>
+        <v>7.54</v>
       </c>
       <c r="G148" s="1">
-        <v>0.5669999999999999</v>
+        <v>0.597</v>
       </c>
       <c r="H148" t="s">
         <v>140</v>
       </c>
       <c r="I148" s="2">
-        <v>8.199999999999999</v>
+        <v>13.95</v>
       </c>
       <c r="J148" s="2">
-        <v>0.09</v>
+        <v>0.153</v>
       </c>
       <c r="K148" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L148" t="s">
         <v>145</v>
@@ -6495,37 +6495,37 @@
     </row>
     <row r="149" spans="1:12">
       <c r="A149" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="B149" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C149" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="D149" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E149">
         <v>4.5</v>
       </c>
       <c r="F149">
-        <v>5.02</v>
+        <v>5.19</v>
       </c>
       <c r="G149" s="1">
-        <v>0.5629999999999999</v>
+        <v>0.592</v>
       </c>
       <c r="H149" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I149" s="2">
-        <v>7.48</v>
+        <v>13.03</v>
       </c>
       <c r="J149" s="2">
-        <v>0.082</v>
+        <v>0.143</v>
       </c>
       <c r="K149" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L149" t="s">
         <v>145</v>
@@ -6533,37 +6533,37 @@
     </row>
     <row r="150" spans="1:12">
       <c r="A150" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="B150" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C150" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D150" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E150">
-        <v>1.5</v>
+        <v>12.5</v>
       </c>
       <c r="F150">
-        <v>1.88</v>
+        <v>14.14</v>
       </c>
       <c r="G150" s="1">
-        <v>0.5620000000000001</v>
+        <v>0.584</v>
       </c>
       <c r="H150" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I150" s="2">
-        <v>7.23</v>
+        <v>11.58</v>
       </c>
       <c r="J150" s="2">
-        <v>0.08</v>
+        <v>0.127</v>
       </c>
       <c r="K150" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L150" t="s">
         <v>145</v>
@@ -6571,37 +6571,37 @@
     </row>
     <row r="151" spans="1:12">
       <c r="A151" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="B151" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="C151" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D151" t="s">
         <v>137</v>
       </c>
       <c r="E151">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="F151">
-        <v>1.5</v>
+        <v>4.08</v>
       </c>
       <c r="G151" s="1">
-        <v>0.5590000000000001</v>
+        <v>0.583</v>
       </c>
       <c r="H151" t="s">
         <v>139</v>
       </c>
       <c r="I151" s="2">
-        <v>6.7</v>
+        <v>11.27</v>
       </c>
       <c r="J151" s="2">
-        <v>0.074</v>
+        <v>0.124</v>
       </c>
       <c r="K151" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L151" t="s">
         <v>145</v>
@@ -6609,34 +6609,34 @@
     </row>
     <row r="152" spans="1:12">
       <c r="A152" t="s">
-        <v>111</v>
+        <v>46</v>
       </c>
       <c r="B152" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C152" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D152" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E152">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="F152">
-        <v>3.4</v>
+        <v>6.35</v>
       </c>
       <c r="G152" s="1">
-        <v>0.5590000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H152" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I152" s="2">
-        <v>6.67</v>
+        <v>10.68</v>
       </c>
       <c r="J152" s="2">
-        <v>0.073</v>
+        <v>0.117</v>
       </c>
       <c r="K152" t="s">
         <v>142</v>
@@ -6647,37 +6647,37 @@
     </row>
     <row r="153" spans="1:12">
       <c r="A153" t="s">
-        <v>107</v>
+        <v>65</v>
       </c>
       <c r="B153" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C153" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="D153" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E153">
         <v>3.5</v>
       </c>
       <c r="F153">
-        <v>3.48</v>
+        <v>4.41</v>
       </c>
       <c r="G153" s="1">
-        <v>0.542</v>
+        <v>0.579</v>
       </c>
       <c r="H153" t="s">
         <v>139</v>
       </c>
       <c r="I153" s="2">
-        <v>3.47</v>
+        <v>10.47</v>
       </c>
       <c r="J153" s="2">
-        <v>0.038</v>
+        <v>0.115</v>
       </c>
       <c r="K153" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L153" t="s">
         <v>145</v>
@@ -6685,37 +6685,37 @@
     </row>
     <row r="154" spans="1:12">
       <c r="A154" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="B154" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C154" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D154" t="s">
         <v>137</v>
       </c>
       <c r="E154">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F154">
-        <v>2.52</v>
+        <v>4.33</v>
       </c>
       <c r="G154" s="1">
-        <v>0.539</v>
+        <v>0.578</v>
       </c>
       <c r="H154" t="s">
         <v>139</v>
       </c>
       <c r="I154" s="2">
-        <v>2.95</v>
+        <v>10.26</v>
       </c>
       <c r="J154" s="2">
-        <v>0.032</v>
+        <v>0.113</v>
       </c>
       <c r="K154" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L154" t="s">
         <v>145</v>
@@ -6723,37 +6723,37 @@
     </row>
     <row r="155" spans="1:12">
       <c r="A155" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B155" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C155" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D155" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E155">
-        <v>13.5</v>
+        <v>6.5</v>
       </c>
       <c r="F155">
-        <v>13.32</v>
+        <v>6.27</v>
       </c>
       <c r="G155" s="1">
-        <v>0.539</v>
+        <v>0.577</v>
       </c>
       <c r="H155" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I155" s="2">
-        <v>2.91</v>
+        <v>10.13</v>
       </c>
       <c r="J155" s="2">
-        <v>0.032</v>
+        <v>0.111</v>
       </c>
       <c r="K155" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L155" t="s">
         <v>145</v>
@@ -6761,37 +6761,37 @@
     </row>
     <row r="156" spans="1:12">
       <c r="A156" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B156" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="C156" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="D156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E156">
         <v>4.5</v>
       </c>
       <c r="F156">
-        <v>4.87</v>
+        <v>5.08</v>
       </c>
       <c r="G156" s="1">
-        <v>0.536</v>
+        <v>0.574</v>
       </c>
       <c r="H156" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I156" s="2">
-        <v>2.35</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="J156" s="2">
-        <v>0.026</v>
+        <v>0.105</v>
       </c>
       <c r="K156" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L156" t="s">
         <v>145</v>
@@ -6799,37 +6799,37 @@
     </row>
     <row r="157" spans="1:12">
       <c r="A157" t="s">
-        <v>26</v>
+        <v>112</v>
       </c>
       <c r="B157" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C157" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D157" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E157">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="F157">
-        <v>5.47</v>
+        <v>11.23</v>
       </c>
       <c r="G157" s="1">
-        <v>0.534</v>
+        <v>0.571</v>
       </c>
       <c r="H157" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I157" s="2">
-        <v>1.89</v>
+        <v>9</v>
       </c>
       <c r="J157" s="2">
-        <v>0.021</v>
+        <v>0.099</v>
       </c>
       <c r="K157" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L157" t="s">
         <v>145</v>
@@ -6837,37 +6837,37 @@
     </row>
     <row r="158" spans="1:12">
       <c r="A158" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="B158" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C158" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D158" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E158">
-        <v>2.5</v>
+        <v>12.5</v>
       </c>
       <c r="F158">
-        <v>2.55</v>
+        <v>11.43</v>
       </c>
       <c r="G158" s="1">
-        <v>0.532</v>
+        <v>0.569</v>
       </c>
       <c r="H158" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I158" s="2">
-        <v>1.56</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="J158" s="2">
-        <v>0.017</v>
+        <v>0.095</v>
       </c>
       <c r="K158" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L158" t="s">
         <v>145</v>
@@ -6875,37 +6875,37 @@
     </row>
     <row r="159" spans="1:12">
       <c r="A159" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B159" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C159" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D159" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E159">
         <v>4.5</v>
       </c>
       <c r="F159">
-        <v>4.83</v>
+        <v>4.47</v>
       </c>
       <c r="G159" s="1">
-        <v>0.53</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="H159" t="s">
         <v>140</v>
       </c>
       <c r="I159" s="2">
-        <v>1.19</v>
+        <v>8.43</v>
       </c>
       <c r="J159" s="2">
-        <v>0.013</v>
+        <v>0.093</v>
       </c>
       <c r="K159" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L159" t="s">
         <v>145</v>
@@ -6913,37 +6913,37 @@
     </row>
     <row r="160" spans="1:12">
       <c r="A160" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="B160" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C160" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D160" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E160">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="F160">
-        <v>3.82</v>
+        <v>2.11</v>
       </c>
       <c r="G160" s="1">
-        <v>0.53</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H160" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I160" s="2">
-        <v>1.18</v>
+        <v>8.07</v>
       </c>
       <c r="J160" s="2">
-        <v>0.013</v>
+        <v>0.089</v>
       </c>
       <c r="K160" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L160" t="s">
         <v>145</v>
@@ -6951,37 +6951,37 @@
     </row>
     <row r="161" spans="1:12">
       <c r="A161" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="B161" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="C161" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D161" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E161">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="F161">
-        <v>4.79</v>
+        <v>7.98</v>
       </c>
       <c r="G161" s="1">
-        <v>0.523</v>
+        <v>0.554</v>
       </c>
       <c r="H161" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I161" s="2">
-        <v>-0.23</v>
+        <v>5.69</v>
       </c>
       <c r="J161" s="2">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="K161" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L161" t="s">
         <v>145</v>
@@ -6989,37 +6989,37 @@
     </row>
     <row r="162" spans="1:12">
       <c r="A162" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="B162" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C162" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D162" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E162">
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="F162">
-        <v>8.43</v>
+        <v>4.95</v>
       </c>
       <c r="G162" s="1">
-        <v>0.519</v>
+        <v>0.551</v>
       </c>
       <c r="H162" t="s">
         <v>139</v>
       </c>
       <c r="I162" s="2">
-        <v>-1.01</v>
+        <v>5.16</v>
       </c>
       <c r="J162" s="2">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="K162" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L162" t="s">
         <v>145</v>
@@ -7027,37 +7027,37 @@
     </row>
     <row r="163" spans="1:12">
       <c r="A163" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B163" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C163" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D163" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E163">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="F163">
-        <v>5.56</v>
+        <v>1.95</v>
       </c>
       <c r="G163" s="1">
-        <v>0.518</v>
+        <v>0.548</v>
       </c>
       <c r="H163" t="s">
         <v>139</v>
       </c>
       <c r="I163" s="2">
-        <v>-1.11</v>
+        <v>4.68</v>
       </c>
       <c r="J163" s="2">
-        <v>0</v>
+        <v>0.052</v>
       </c>
       <c r="K163" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L163" t="s">
         <v>145</v>
@@ -7065,37 +7065,37 @@
     </row>
     <row r="164" spans="1:12">
       <c r="A164" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="B164" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C164" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="D164" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E164">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F164">
-        <v>3.76</v>
+        <v>2.62</v>
       </c>
       <c r="G164" s="1">
-        <v>0.518</v>
+        <v>0.541</v>
       </c>
       <c r="H164" t="s">
         <v>140</v>
       </c>
       <c r="I164" s="2">
-        <v>-1.17</v>
+        <v>3.27</v>
       </c>
       <c r="J164" s="2">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="K164" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L164" t="s">
         <v>145</v>
@@ -7103,37 +7103,37 @@
     </row>
     <row r="165" spans="1:12">
       <c r="A165" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="B165" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C165" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D165" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E165">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="F165">
-        <v>9.57</v>
+        <v>4.77</v>
       </c>
       <c r="G165" s="1">
-        <v>0.517</v>
+        <v>0.536</v>
       </c>
       <c r="H165" t="s">
         <v>140</v>
       </c>
       <c r="I165" s="2">
-        <v>-1.26</v>
+        <v>2.31</v>
       </c>
       <c r="J165" s="2">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="K165" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L165" t="s">
         <v>145</v>
@@ -7141,37 +7141,37 @@
     </row>
     <row r="166" spans="1:12">
       <c r="A166" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="B166" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C166" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D166" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E166">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F166">
-        <v>4.58</v>
+        <v>3.84</v>
       </c>
       <c r="G166" s="1">
-        <v>0.517</v>
+        <v>0.534</v>
       </c>
       <c r="H166" t="s">
         <v>139</v>
       </c>
       <c r="I166" s="2">
-        <v>-1.37</v>
+        <v>2.04</v>
       </c>
       <c r="J166" s="2">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="K166" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L166" t="s">
         <v>145</v>
@@ -7179,37 +7179,37 @@
     </row>
     <row r="167" spans="1:12">
       <c r="A167" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="B167" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C167" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D167" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E167">
-        <v>1.5</v>
+        <v>13.5</v>
       </c>
       <c r="F167">
-        <v>1.73</v>
+        <v>12.94</v>
       </c>
       <c r="G167" s="1">
-        <v>0.516</v>
+        <v>0.534</v>
       </c>
       <c r="H167" t="s">
         <v>140</v>
       </c>
       <c r="I167" s="2">
-        <v>-1.54</v>
+        <v>1.91</v>
       </c>
       <c r="J167" s="2">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="K167" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L167" t="s">
         <v>145</v>
@@ -7217,37 +7217,37 @@
     </row>
     <row r="168" spans="1:12">
       <c r="A168" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="B168" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C168" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="D168" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E168">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="F168">
-        <v>1.65</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G168" s="1">
-        <v>0.51</v>
+        <v>0.532</v>
       </c>
       <c r="H168" t="s">
         <v>139</v>
       </c>
       <c r="I168" s="2">
-        <v>-2.69</v>
+        <v>1.54</v>
       </c>
       <c r="J168" s="2">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="K168" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L168" t="s">
         <v>145</v>
@@ -7255,34 +7255,34 @@
     </row>
     <row r="169" spans="1:12">
       <c r="A169" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="B169" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C169" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="D169" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E169">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="F169">
-        <v>5.62</v>
+        <v>3.64</v>
       </c>
       <c r="G169" s="1">
-        <v>0.508</v>
+        <v>0.527</v>
       </c>
       <c r="H169" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I169" s="2">
-        <v>-3.07</v>
+        <v>0.61</v>
       </c>
       <c r="J169" s="2">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="K169" t="s">
         <v>144</v>
@@ -7293,31 +7293,31 @@
     </row>
     <row r="170" spans="1:12">
       <c r="A170" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B170" t="s">
         <v>114</v>
       </c>
       <c r="C170" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D170" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E170">
-        <v>4.5</v>
+        <v>22.5</v>
       </c>
       <c r="F170">
-        <v>4.7</v>
+        <v>21.88</v>
       </c>
       <c r="G170" s="1">
-        <v>0.505</v>
+        <v>0.523</v>
       </c>
       <c r="H170" t="s">
         <v>140</v>
       </c>
       <c r="I170" s="2">
-        <v>-3.67</v>
+        <v>-0.11</v>
       </c>
       <c r="J170" s="2">
         <v>0</v>
@@ -7331,31 +7331,31 @@
     </row>
     <row r="171" spans="1:12">
       <c r="A171" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B171" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C171" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="D171" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E171">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="F171">
-        <v>4.69</v>
+        <v>7.74</v>
       </c>
       <c r="G171" s="1">
-        <v>0.503</v>
+        <v>0.518</v>
       </c>
       <c r="H171" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I171" s="2">
-        <v>-3.97</v>
+        <v>-1.16</v>
       </c>
       <c r="J171" s="2">
         <v>0</v>
@@ -7369,31 +7369,31 @@
     </row>
     <row r="172" spans="1:12">
       <c r="A172" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B172" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C172" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="D172" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E172">
-        <v>5.5</v>
+        <v>29.5</v>
       </c>
       <c r="F172">
-        <v>5.69</v>
+        <v>29.5</v>
       </c>
       <c r="G172" s="1">
-        <v>0.503</v>
+        <v>0.5</v>
       </c>
       <c r="H172" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I172" s="2">
-        <v>-4.06</v>
+        <v>-4.53</v>
       </c>
       <c r="J172" s="2">
         <v>0</v>
@@ -7405,84 +7405,8 @@
         <v>145</v>
       </c>
     </row>
-    <row r="173" spans="1:12">
-      <c r="A173" t="s">
-        <v>99</v>
-      </c>
-      <c r="B173" t="s">
-        <v>122</v>
-      </c>
-      <c r="C173" t="s">
-        <v>118</v>
-      </c>
-      <c r="D173" t="s">
-        <v>138</v>
-      </c>
-      <c r="E173">
-        <v>3.5</v>
-      </c>
-      <c r="F173">
-        <v>3.68</v>
-      </c>
-      <c r="G173" s="1">
-        <v>0.502</v>
-      </c>
-      <c r="H173" t="s">
-        <v>140</v>
-      </c>
-      <c r="I173" s="2">
-        <v>-4.13</v>
-      </c>
-      <c r="J173" s="2">
-        <v>0</v>
-      </c>
-      <c r="K173" t="s">
-        <v>144</v>
-      </c>
-      <c r="L173" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="174" spans="1:12">
-      <c r="A174" t="s">
-        <v>51</v>
-      </c>
-      <c r="B174" t="s">
-        <v>125</v>
-      </c>
-      <c r="C174" t="s">
-        <v>116</v>
-      </c>
-      <c r="D174" t="s">
-        <v>137</v>
-      </c>
-      <c r="E174">
-        <v>4.5</v>
-      </c>
-      <c r="F174">
-        <v>4.66</v>
-      </c>
-      <c r="G174" s="1">
-        <v>0.502</v>
-      </c>
-      <c r="H174" t="s">
-        <v>139</v>
-      </c>
-      <c r="I174" s="2">
-        <v>-4.14</v>
-      </c>
-      <c r="J174" s="2">
-        <v>0</v>
-      </c>
-      <c r="K174" t="s">
-        <v>144</v>
-      </c>
-      <c r="L174" t="s">
-        <v>145</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="K2:K174">
+  <conditionalFormatting sqref="K2:K172">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="S Tier">
       <formula>NOT(ISERROR(SEARCH("S Tier",K2)))</formula>
     </cfRule>

--- a/output/processed_props.xlsx
+++ b/output/processed_props.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="146">
   <si>
     <t>Player</t>
   </si>
@@ -52,391 +52,391 @@
     <t>Date</t>
   </si>
   <si>
+    <t>Joan Beringer</t>
+  </si>
+  <si>
     <t>Nic Claxton</t>
   </si>
   <si>
+    <t>Tristan Vukcevic</t>
+  </si>
+  <si>
+    <t>Jared McCain</t>
+  </si>
+  <si>
+    <t>Aaron Wiggins</t>
+  </si>
+  <si>
+    <t>Brandin Podziemski</t>
+  </si>
+  <si>
+    <t>Naz Reid</t>
+  </si>
+  <si>
+    <t>Julian Strawther</t>
+  </si>
+  <si>
+    <t>Brandon Miller</t>
+  </si>
+  <si>
+    <t>Wendell Carter Jr.</t>
+  </si>
+  <si>
+    <t>Ryan Kalkbrenner</t>
+  </si>
+  <si>
+    <t>Kawhi Leonard</t>
+  </si>
+  <si>
+    <t>Quentin Grimes</t>
+  </si>
+  <si>
+    <t>Nolan Traore</t>
+  </si>
+  <si>
+    <t>Kyshawn George</t>
+  </si>
+  <si>
+    <t>Brook Lopez</t>
+  </si>
+  <si>
+    <t>Bub Carrington</t>
+  </si>
+  <si>
     <t>Tyus Jones</t>
   </si>
   <si>
-    <t>Joan Beringer</t>
+    <t>Jonas Valanciunas</t>
+  </si>
+  <si>
+    <t>Joel Embiid</t>
+  </si>
+  <si>
+    <t>Pat Spencer</t>
+  </si>
+  <si>
+    <t>Derrick White</t>
+  </si>
+  <si>
+    <t>Tyrese Maxey</t>
+  </si>
+  <si>
+    <t>Anthony Edwards</t>
+  </si>
+  <si>
+    <t>Draymond Green</t>
+  </si>
+  <si>
+    <t>AJ Green</t>
+  </si>
+  <si>
+    <t>Jarrett Allen</t>
+  </si>
+  <si>
+    <t>Dyson Daniels</t>
+  </si>
+  <si>
+    <t>Payton Pritchard</t>
+  </si>
+  <si>
+    <t>VJ Edgecombe</t>
+  </si>
+  <si>
+    <t>Julius Randle</t>
+  </si>
+  <si>
+    <t>Tim Hardaway Jr.</t>
+  </si>
+  <si>
+    <t>Kris Dunn</t>
+  </si>
+  <si>
+    <t>Jalen Johnson</t>
+  </si>
+  <si>
+    <t>Jaylen Brown</t>
+  </si>
+  <si>
+    <t>Derrick Jones Jr.</t>
+  </si>
+  <si>
+    <t>Bilal Coulibaly</t>
+  </si>
+  <si>
+    <t>Austin Reaves</t>
+  </si>
+  <si>
+    <t>RJ Barrett</t>
+  </si>
+  <si>
+    <t>Chet Holmgren</t>
+  </si>
+  <si>
+    <t>Donte DiVincenzo</t>
+  </si>
+  <si>
+    <t>Immanuel Quickley</t>
+  </si>
+  <si>
+    <t>LaMelo Ball</t>
+  </si>
+  <si>
+    <t>Rui Hachimura</t>
+  </si>
+  <si>
+    <t>Isaiah Joe</t>
+  </si>
+  <si>
+    <t>Jock Landale</t>
+  </si>
+  <si>
+    <t>Marcus Smart</t>
+  </si>
+  <si>
+    <t>Deandre Ayton</t>
   </si>
   <si>
     <t>James Harden</t>
   </si>
   <si>
+    <t>Jamal Shead</t>
+  </si>
+  <si>
+    <t>CJ McCollum</t>
+  </si>
+  <si>
+    <t>Naji Marshall</t>
+  </si>
+  <si>
+    <t>Ayo Dosunmu</t>
+  </si>
+  <si>
+    <t>Sam Hauser</t>
+  </si>
+  <si>
+    <t>Dominick Barlow</t>
+  </si>
+  <si>
+    <t>Evan Mobley</t>
+  </si>
+  <si>
+    <t>Desmond Bane</t>
+  </si>
+  <si>
+    <t>Kon Knueppel</t>
+  </si>
+  <si>
+    <t>Tre Johnson</t>
+  </si>
+  <si>
     <t>Cam Thomas</t>
   </si>
   <si>
-    <t>Kris Dunn</t>
-  </si>
-  <si>
-    <t>Draymond Green</t>
+    <t>Ryan Rollins</t>
+  </si>
+  <si>
+    <t>Baylor Scheierman</t>
+  </si>
+  <si>
+    <t>Nickeil Alexander-Walker</t>
+  </si>
+  <si>
+    <t>Donovan Mitchell</t>
+  </si>
+  <si>
+    <t>Dennis Schroder</t>
+  </si>
+  <si>
+    <t>Brandon Ingram</t>
   </si>
   <si>
     <t>Nikola Jokic</t>
   </si>
   <si>
-    <t>Nolan Traore</t>
-  </si>
-  <si>
-    <t>Quentin Grimes</t>
-  </si>
-  <si>
-    <t>Jared McCain</t>
-  </si>
-  <si>
-    <t>Bub Carrington</t>
-  </si>
-  <si>
-    <t>LaMelo Ball</t>
+    <t>Egor Demin</t>
+  </si>
+  <si>
+    <t>Neemias Queta</t>
+  </si>
+  <si>
+    <t>Paolo Banchero</t>
+  </si>
+  <si>
+    <t>Onyeka Okongwu</t>
+  </si>
+  <si>
+    <t>Jamal Murray</t>
+  </si>
+  <si>
+    <t>Jaylon Tyson</t>
+  </si>
+  <si>
+    <t>LeBron James</t>
   </si>
   <si>
     <t>Grant Williams</t>
   </si>
   <si>
-    <t>Wendell Carter Jr.</t>
-  </si>
-  <si>
-    <t>Jarrett Allen</t>
-  </si>
-  <si>
-    <t>AJ Green</t>
-  </si>
-  <si>
-    <t>Aaron Wiggins</t>
-  </si>
-  <si>
-    <t>Jamal Shead</t>
+    <t>Jaden McDaniels</t>
+  </si>
+  <si>
+    <t>Michael Porter Jr.</t>
+  </si>
+  <si>
+    <t>Al Horford</t>
+  </si>
+  <si>
+    <t>Kristaps Porzingis</t>
+  </si>
+  <si>
+    <t>Bennedict Mathurin</t>
+  </si>
+  <si>
+    <t>Noah Clowney</t>
+  </si>
+  <si>
+    <t>Cason Wallace</t>
+  </si>
+  <si>
+    <t>Collin Murray-Boyles</t>
+  </si>
+  <si>
+    <t>Gui Santos</t>
+  </si>
+  <si>
+    <t>Moses Moody</t>
+  </si>
+  <si>
+    <t>Anthony Black</t>
+  </si>
+  <si>
+    <t>Zaccharie Risacher</t>
+  </si>
+  <si>
+    <t>Sam Merrill</t>
+  </si>
+  <si>
+    <t>Myles Turner</t>
+  </si>
+  <si>
+    <t>Nikola Vucevic</t>
+  </si>
+  <si>
+    <t>De'Anthony Melton</t>
+  </si>
+  <si>
+    <t>Daniel Gafford</t>
+  </si>
+  <si>
+    <t>Max Christie</t>
+  </si>
+  <si>
+    <t>Dean Wade</t>
+  </si>
+  <si>
+    <t>Klay Thompson</t>
+  </si>
+  <si>
+    <t>Kyle Kuzma</t>
+  </si>
+  <si>
+    <t>Christian Braun</t>
+  </si>
+  <si>
+    <t>Kevin Porter Jr.</t>
   </si>
   <si>
     <t>Jalen Suggs</t>
   </si>
   <si>
-    <t>Dyson Daniels</t>
-  </si>
-  <si>
-    <t>RJ Barrett</t>
-  </si>
-  <si>
-    <t>VJ Edgecombe</t>
-  </si>
-  <si>
-    <t>Kon Knueppel</t>
-  </si>
-  <si>
-    <t>Naz Reid</t>
-  </si>
-  <si>
-    <t>Ryan Rollins</t>
-  </si>
-  <si>
-    <t>Kevin Porter Jr.</t>
-  </si>
-  <si>
-    <t>Immanuel Quickley</t>
-  </si>
-  <si>
-    <t>Michael Porter Jr.</t>
-  </si>
-  <si>
-    <t>Ayo Dosunmu</t>
-  </si>
-  <si>
-    <t>Klay Thompson</t>
-  </si>
-  <si>
-    <t>Jamal Murray</t>
-  </si>
-  <si>
-    <t>Payton Pritchard</t>
-  </si>
-  <si>
-    <t>Donovan Mitchell</t>
-  </si>
-  <si>
-    <t>Tyrese Maxey</t>
-  </si>
-  <si>
-    <t>Kyshawn George</t>
-  </si>
-  <si>
-    <t>Sam Hauser</t>
-  </si>
-  <si>
-    <t>Derrick Jones Jr.</t>
-  </si>
-  <si>
-    <t>Pat Spencer</t>
-  </si>
-  <si>
     <t>Isaiah Hartenstein</t>
   </si>
   <si>
-    <t>Derrick White</t>
-  </si>
-  <si>
-    <t>Bennedict Mathurin</t>
-  </si>
-  <si>
-    <t>Gui Santos</t>
-  </si>
-  <si>
-    <t>Julius Randle</t>
-  </si>
-  <si>
-    <t>Dominick Barlow</t>
-  </si>
-  <si>
-    <t>Dennis Schroder</t>
-  </si>
-  <si>
-    <t>Donte DiVincenzo</t>
-  </si>
-  <si>
-    <t>Brook Lopez</t>
-  </si>
-  <si>
-    <t>Marcus Smart</t>
-  </si>
-  <si>
-    <t>Julian Strawther</t>
-  </si>
-  <si>
-    <t>Max Christie</t>
-  </si>
-  <si>
-    <t>Jock Landale</t>
-  </si>
-  <si>
-    <t>Daniel Gafford</t>
-  </si>
-  <si>
-    <t>Egor Demin</t>
-  </si>
-  <si>
-    <t>Brandon Miller</t>
-  </si>
-  <si>
-    <t>Austin Reaves</t>
-  </si>
-  <si>
-    <t>De'Anthony Melton</t>
-  </si>
-  <si>
-    <t>Jaylon Tyson</t>
-  </si>
-  <si>
-    <t>Anthony Black</t>
-  </si>
-  <si>
-    <t>Brandin Podziemski</t>
-  </si>
-  <si>
-    <t>Myles Turner</t>
-  </si>
-  <si>
-    <t>Desmond Bane</t>
-  </si>
-  <si>
-    <t>Nickeil Alexander-Walker</t>
-  </si>
-  <si>
-    <t>Paolo Banchero</t>
-  </si>
-  <si>
-    <t>Jalen Johnson</t>
-  </si>
-  <si>
-    <t>Evan Mobley</t>
-  </si>
-  <si>
-    <t>Al Horford</t>
-  </si>
-  <si>
-    <t>Chet Holmgren</t>
-  </si>
-  <si>
-    <t>Tim Hardaway Jr.</t>
-  </si>
-  <si>
-    <t>Neemias Queta</t>
-  </si>
-  <si>
-    <t>Joel Embiid</t>
-  </si>
-  <si>
-    <t>Tre Johnson</t>
-  </si>
-  <si>
-    <t>Nikola Vucevic</t>
-  </si>
-  <si>
-    <t>Bilal Coulibaly</t>
-  </si>
-  <si>
-    <t>Jonas Valanciunas</t>
-  </si>
-  <si>
     <t>Corey Kispert</t>
   </si>
   <si>
-    <t>Sam Merrill</t>
-  </si>
-  <si>
-    <t>Cason Wallace</t>
-  </si>
-  <si>
-    <t>Rui Hachimura</t>
-  </si>
-  <si>
-    <t>LeBron James</t>
-  </si>
-  <si>
-    <t>Anthony Edwards</t>
-  </si>
-  <si>
-    <t>Brandon Ingram</t>
-  </si>
-  <si>
-    <t>Jaden McDaniels</t>
-  </si>
-  <si>
-    <t>Tristan Vukcevic</t>
-  </si>
-  <si>
-    <t>Zaccharie Risacher</t>
-  </si>
-  <si>
-    <t>Ryan Kalkbrenner</t>
-  </si>
-  <si>
-    <t>Onyeka Okongwu</t>
-  </si>
-  <si>
-    <t>Deandre Ayton</t>
-  </si>
-  <si>
-    <t>Jaylen Brown</t>
-  </si>
-  <si>
-    <t>Dean Wade</t>
-  </si>
-  <si>
-    <t>Naji Marshall</t>
-  </si>
-  <si>
-    <t>Noah Clowney</t>
-  </si>
-  <si>
-    <t>CJ McCollum</t>
-  </si>
-  <si>
-    <t>Kyle Kuzma</t>
-  </si>
-  <si>
-    <t>Moses Moody</t>
-  </si>
-  <si>
     <t>Luka Doncic</t>
   </si>
   <si>
-    <t>Baylor Scheierman</t>
-  </si>
-  <si>
-    <t>Kawhi Leonard</t>
-  </si>
-  <si>
-    <t>Christian Braun</t>
-  </si>
-  <si>
-    <t>Kristaps Porzingis</t>
-  </si>
-  <si>
-    <t>Isaiah Joe</t>
-  </si>
-  <si>
-    <t>Collin Murray-Boyles</t>
+    <t>MIN</t>
   </si>
   <si>
     <t>BKN</t>
   </si>
   <si>
+    <t>WSH</t>
+  </si>
+  <si>
+    <t>OKC</t>
+  </si>
+  <si>
+    <t>GS</t>
+  </si>
+  <si>
+    <t>DEN</t>
+  </si>
+  <si>
+    <t>CHA</t>
+  </si>
+  <si>
+    <t>ORL</t>
+  </si>
+  <si>
+    <t>LAC</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
     <t>DAL</t>
   </si>
   <si>
-    <t>MIN</t>
+    <t>BOS</t>
+  </si>
+  <si>
+    <t>MIL</t>
   </si>
   <si>
     <t>CLE</t>
   </si>
   <si>
-    <t>MIL</t>
-  </si>
-  <si>
-    <t>LAC</t>
-  </si>
-  <si>
-    <t>GS</t>
-  </si>
-  <si>
-    <t>DEN</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>OKC</t>
-  </si>
-  <si>
-    <t>WSH</t>
-  </si>
-  <si>
-    <t>CHA</t>
-  </si>
-  <si>
-    <t>ORL</t>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>LAL</t>
   </si>
   <si>
     <t>TOR</t>
   </si>
   <si>
-    <t>ATL</t>
-  </si>
-  <si>
-    <t>BOS</t>
-  </si>
-  <si>
-    <t>LAL</t>
+    <t>GSW</t>
+  </si>
+  <si>
+    <t>WAS</t>
   </si>
   <si>
     <t>IND</t>
   </si>
   <si>
-    <t>GSW</t>
-  </si>
-  <si>
-    <t>WAS</t>
+    <t>PRA</t>
   </si>
   <si>
     <t>PTS</t>
   </si>
   <si>
-    <t>PRA</t>
+    <t>REB</t>
   </si>
   <si>
     <t>AST</t>
   </si>
   <si>
-    <t>REB</t>
-  </si>
-  <si>
     <t>RA</t>
   </si>
   <si>
+    <t>Under</t>
+  </si>
+  <si>
     <t>Over</t>
-  </si>
-  <si>
-    <t>Under</t>
   </si>
   <si>
     <t>S Tier</t>
@@ -854,7 +854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L172"/>
+  <dimension ref="A1:L162"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
@@ -915,28 +915,28 @@
         <v>114</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D2" t="s">
         <v>134</v>
       </c>
       <c r="E2">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="F2">
-        <v>26.54</v>
+        <v>3.83</v>
       </c>
       <c r="G2" s="1">
-        <v>1</v>
+        <v>0.994</v>
       </c>
       <c r="H2" t="s">
         <v>139</v>
       </c>
       <c r="I2" s="2">
-        <v>90.90000000000001</v>
+        <v>89.67</v>
       </c>
       <c r="J2" s="2">
-        <v>1</v>
+        <v>0.986</v>
       </c>
       <c r="K2" t="s">
         <v>141</v>
@@ -953,28 +953,28 @@
         <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E3">
-        <v>6.5</v>
+        <v>10.5</v>
       </c>
       <c r="F3">
-        <v>11.62</v>
+        <v>17.32</v>
       </c>
       <c r="G3" s="1">
-        <v>0.998</v>
+        <v>0.952</v>
       </c>
       <c r="H3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I3" s="2">
-        <v>90.55</v>
+        <v>81.66</v>
       </c>
       <c r="J3" s="2">
-        <v>0.996</v>
+        <v>0.898</v>
       </c>
       <c r="K3" t="s">
         <v>141</v>
@@ -991,28 +991,28 @@
         <v>116</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E4">
-        <v>14.5</v>
+        <v>5.5</v>
       </c>
       <c r="F4">
-        <v>3.26</v>
+        <v>3.48</v>
       </c>
       <c r="G4" s="1">
-        <v>0.996</v>
+        <v>0.86</v>
       </c>
       <c r="H4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I4" s="2">
-        <v>90.06</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="J4" s="2">
-        <v>0.991</v>
+        <v>0.707</v>
       </c>
       <c r="K4" t="s">
         <v>141</v>
@@ -1029,28 +1029,28 @@
         <v>117</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E5">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="F5">
-        <v>4.09</v>
+        <v>1.34</v>
       </c>
       <c r="G5" s="1">
-        <v>0.976</v>
+        <v>0.835</v>
       </c>
       <c r="H5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I5" s="2">
-        <v>86.29000000000001</v>
+        <v>59.47</v>
       </c>
       <c r="J5" s="2">
-        <v>0.949</v>
+        <v>0.654</v>
       </c>
       <c r="K5" t="s">
         <v>141</v>
@@ -1064,31 +1064,31 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C6" t="s">
         <v>127</v>
       </c>
       <c r="D6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E6">
-        <v>1.5</v>
+        <v>14.5</v>
       </c>
       <c r="F6">
-        <v>5.2</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="G6" s="1">
-        <v>0.966</v>
+        <v>0.831</v>
       </c>
       <c r="H6" t="s">
         <v>139</v>
       </c>
       <c r="I6" s="2">
-        <v>84.38</v>
+        <v>58.57</v>
       </c>
       <c r="J6" s="2">
-        <v>0.928</v>
+        <v>0.644</v>
       </c>
       <c r="K6" t="s">
         <v>141</v>
@@ -1102,31 +1102,31 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" t="s">
         <v>119</v>
       </c>
-      <c r="C7" t="s">
-        <v>126</v>
-      </c>
       <c r="D7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E7">
-        <v>6.5</v>
+        <v>15.5</v>
       </c>
       <c r="F7">
-        <v>3.1</v>
+        <v>11.1</v>
       </c>
       <c r="G7" s="1">
-        <v>0.96</v>
+        <v>0.828</v>
       </c>
       <c r="H7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I7" s="2">
-        <v>83.25</v>
+        <v>57.99</v>
       </c>
       <c r="J7" s="2">
-        <v>0.916</v>
+        <v>0.638</v>
       </c>
       <c r="K7" t="s">
         <v>141</v>
@@ -1140,31 +1140,31 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E8">
-        <v>18.5</v>
+        <v>8.5</v>
       </c>
       <c r="F8">
-        <v>4.47</v>
+        <v>6.47</v>
       </c>
       <c r="G8" s="1">
-        <v>0.947</v>
+        <v>0.796</v>
       </c>
       <c r="H8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I8" s="2">
-        <v>80.72</v>
+        <v>51.9</v>
       </c>
       <c r="J8" s="2">
-        <v>0.888</v>
+        <v>0.571</v>
       </c>
       <c r="K8" t="s">
         <v>141</v>
@@ -1178,31 +1178,31 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E9">
-        <v>23.5</v>
+        <v>2.5</v>
       </c>
       <c r="F9">
-        <v>10.21</v>
+        <v>1.55</v>
       </c>
       <c r="G9" s="1">
-        <v>0.946</v>
+        <v>0.795</v>
       </c>
       <c r="H9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I9" s="2">
-        <v>80.69</v>
+        <v>51.82</v>
       </c>
       <c r="J9" s="2">
-        <v>0.888</v>
+        <v>0.57</v>
       </c>
       <c r="K9" t="s">
         <v>141</v>
@@ -1216,31 +1216,31 @@
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C10" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D10" t="s">
         <v>134</v>
       </c>
       <c r="E10">
-        <v>10.5</v>
+        <v>33.5</v>
       </c>
       <c r="F10">
-        <v>20.19</v>
+        <v>27.25</v>
       </c>
       <c r="G10" s="1">
-        <v>0.9379999999999999</v>
+        <v>0.793</v>
       </c>
       <c r="H10" t="s">
         <v>139</v>
       </c>
       <c r="I10" s="2">
-        <v>79.12</v>
+        <v>51.37</v>
       </c>
       <c r="J10" s="2">
-        <v>0.87</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K10" t="s">
         <v>141</v>
@@ -1254,31 +1254,31 @@
         <v>21</v>
       </c>
       <c r="B11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" t="s">
         <v>122</v>
       </c>
-      <c r="C11" t="s">
-        <v>116</v>
-      </c>
       <c r="D11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E11">
-        <v>2.5</v>
+        <v>19.5</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>14.02</v>
       </c>
       <c r="G11" s="1">
-        <v>0.9379999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="H11" t="s">
         <v>139</v>
       </c>
       <c r="I11" s="2">
-        <v>79.06</v>
+        <v>48.93</v>
       </c>
       <c r="J11" s="2">
-        <v>0.87</v>
+        <v>0.538</v>
       </c>
       <c r="K11" t="s">
         <v>141</v>
@@ -1292,31 +1292,31 @@
         <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C12" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E12">
-        <v>11.5</v>
+        <v>7.5</v>
       </c>
       <c r="F12">
-        <v>20.27</v>
+        <v>5.74</v>
       </c>
       <c r="G12" s="1">
-        <v>0.9379999999999999</v>
+        <v>0.779</v>
       </c>
       <c r="H12" t="s">
         <v>139</v>
       </c>
       <c r="I12" s="2">
-        <v>78.98</v>
+        <v>48.71</v>
       </c>
       <c r="J12" s="2">
-        <v>0.869</v>
+        <v>0.536</v>
       </c>
       <c r="K12" t="s">
         <v>141</v>
@@ -1330,31 +1330,31 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C13" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D13" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E13">
-        <v>10.5</v>
+        <v>4.5</v>
       </c>
       <c r="F13">
-        <v>6.33</v>
+        <v>3.05</v>
       </c>
       <c r="G13" s="1">
-        <v>0.9350000000000001</v>
+        <v>0.779</v>
       </c>
       <c r="H13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I13" s="2">
-        <v>78.45999999999999</v>
+        <v>48.71</v>
       </c>
       <c r="J13" s="2">
-        <v>0.863</v>
+        <v>0.536</v>
       </c>
       <c r="K13" t="s">
         <v>141</v>
@@ -1368,31 +1368,31 @@
         <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C14" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="D14" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E14">
-        <v>7.5</v>
+        <v>15.5</v>
       </c>
       <c r="F14">
-        <v>4.2</v>
+        <v>20.18</v>
       </c>
       <c r="G14" s="1">
-        <v>0.9340000000000001</v>
+        <v>0.779</v>
       </c>
       <c r="H14" t="s">
         <v>140</v>
       </c>
       <c r="I14" s="2">
-        <v>78.37</v>
+        <v>48.69</v>
       </c>
       <c r="J14" s="2">
-        <v>0.862</v>
+        <v>0.536</v>
       </c>
       <c r="K14" t="s">
         <v>141</v>
@@ -1406,31 +1406,31 @@
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C15" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E15">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="F15">
-        <v>19.58</v>
+        <v>15.31</v>
       </c>
       <c r="G15" s="1">
-        <v>0.9330000000000001</v>
+        <v>0.777</v>
       </c>
       <c r="H15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I15" s="2">
-        <v>78.06</v>
+        <v>48.43</v>
       </c>
       <c r="J15" s="2">
-        <v>0.859</v>
+        <v>0.533</v>
       </c>
       <c r="K15" t="s">
         <v>141</v>
@@ -1444,31 +1444,31 @@
         <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D16" t="s">
         <v>135</v>
       </c>
       <c r="E16">
-        <v>19.5</v>
+        <v>12.5</v>
       </c>
       <c r="F16">
-        <v>8.9</v>
+        <v>8.16</v>
       </c>
       <c r="G16" s="1">
-        <v>0.9320000000000001</v>
+        <v>0.774</v>
       </c>
       <c r="H16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I16" s="2">
-        <v>77.98999999999999</v>
+        <v>47.84</v>
       </c>
       <c r="J16" s="2">
-        <v>0.858</v>
+        <v>0.526</v>
       </c>
       <c r="K16" t="s">
         <v>141</v>
@@ -1482,31 +1482,31 @@
         <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C17" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D17" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E17">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="F17">
-        <v>4.37</v>
+        <v>6.37</v>
       </c>
       <c r="G17" s="1">
-        <v>0.9320000000000001</v>
+        <v>0.773</v>
       </c>
       <c r="H17" t="s">
         <v>139</v>
       </c>
       <c r="I17" s="2">
-        <v>77.98999999999999</v>
+        <v>47.6</v>
       </c>
       <c r="J17" s="2">
-        <v>0.858</v>
+        <v>0.524</v>
       </c>
       <c r="K17" t="s">
         <v>141</v>
@@ -1520,31 +1520,31 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C18" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E18">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="F18">
-        <v>0.48</v>
+        <v>8.52</v>
       </c>
       <c r="G18" s="1">
-        <v>0.921</v>
+        <v>0.764</v>
       </c>
       <c r="H18" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I18" s="2">
-        <v>75.78</v>
+        <v>45.84</v>
       </c>
       <c r="J18" s="2">
-        <v>0.834</v>
+        <v>0.504</v>
       </c>
       <c r="K18" t="s">
         <v>141</v>
@@ -1558,31 +1558,31 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C19" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="D19" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E19">
-        <v>14.5</v>
+        <v>5.5</v>
       </c>
       <c r="F19">
-        <v>6.54</v>
+        <v>3.86</v>
       </c>
       <c r="G19" s="1">
-        <v>0.919</v>
+        <v>0.76</v>
       </c>
       <c r="H19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I19" s="2">
-        <v>75.38</v>
+        <v>45.12</v>
       </c>
       <c r="J19" s="2">
-        <v>0.829</v>
+        <v>0.496</v>
       </c>
       <c r="K19" t="s">
         <v>141</v>
@@ -1596,31 +1596,31 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C20" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="D20" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E20">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="F20">
-        <v>1.73</v>
+        <v>0.93</v>
       </c>
       <c r="G20" s="1">
-        <v>0.918</v>
+        <v>0.76</v>
       </c>
       <c r="H20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I20" s="2">
-        <v>75.19</v>
+        <v>45.09</v>
       </c>
       <c r="J20" s="2">
-        <v>0.827</v>
+        <v>0.496</v>
       </c>
       <c r="K20" t="s">
         <v>141</v>
@@ -1634,31 +1634,31 @@
         <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C21" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E21">
-        <v>5.5</v>
+        <v>26.5</v>
       </c>
       <c r="F21">
-        <v>1.87</v>
+        <v>30.94</v>
       </c>
       <c r="G21" s="1">
-        <v>0.917</v>
+        <v>0.76</v>
       </c>
       <c r="H21" t="s">
         <v>140</v>
       </c>
       <c r="I21" s="2">
-        <v>75.06999999999999</v>
+        <v>45.05</v>
       </c>
       <c r="J21" s="2">
-        <v>0.826</v>
+        <v>0.496</v>
       </c>
       <c r="K21" t="s">
         <v>141</v>
@@ -1672,31 +1672,31 @@
         <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E22">
-        <v>23.5</v>
+        <v>20.5</v>
       </c>
       <c r="F22">
-        <v>12.97</v>
+        <v>13.29</v>
       </c>
       <c r="G22" s="1">
-        <v>0.916</v>
+        <v>0.756</v>
       </c>
       <c r="H22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I22" s="2">
-        <v>74.94</v>
+        <v>44.26</v>
       </c>
       <c r="J22" s="2">
-        <v>0.824</v>
+        <v>0.487</v>
       </c>
       <c r="K22" t="s">
         <v>141</v>
@@ -1710,31 +1710,31 @@
         <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D23" t="s">
         <v>135</v>
       </c>
       <c r="E23">
-        <v>27.5</v>
+        <v>18.5</v>
       </c>
       <c r="F23">
-        <v>19.59</v>
+        <v>14.25</v>
       </c>
       <c r="G23" s="1">
-        <v>0.913</v>
+        <v>0.749</v>
       </c>
       <c r="H23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I23" s="2">
-        <v>74.36</v>
+        <v>42.92</v>
       </c>
       <c r="J23" s="2">
-        <v>0.8179999999999999</v>
+        <v>0.472</v>
       </c>
       <c r="K23" t="s">
         <v>141</v>
@@ -1745,34 +1745,34 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C24" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="D24" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E24">
-        <v>15.5</v>
+        <v>6.5</v>
       </c>
       <c r="F24">
-        <v>24.26</v>
+        <v>7.67</v>
       </c>
       <c r="G24" s="1">
-        <v>0.909</v>
+        <v>0.746</v>
       </c>
       <c r="H24" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I24" s="2">
-        <v>73.54000000000001</v>
+        <v>42.45</v>
       </c>
       <c r="J24" s="2">
-        <v>0.8090000000000001</v>
+        <v>0.467</v>
       </c>
       <c r="K24" t="s">
         <v>141</v>
@@ -1783,34 +1783,34 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C25" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E25">
-        <v>30.5</v>
+        <v>6.5</v>
       </c>
       <c r="F25">
-        <v>39.2</v>
+        <v>4.68</v>
       </c>
       <c r="G25" s="1">
-        <v>0.907</v>
+        <v>0.744</v>
       </c>
       <c r="H25" t="s">
         <v>139</v>
       </c>
       <c r="I25" s="2">
-        <v>73.23</v>
+        <v>42.06</v>
       </c>
       <c r="J25" s="2">
-        <v>0.805</v>
+        <v>0.463</v>
       </c>
       <c r="K25" t="s">
         <v>141</v>
@@ -1821,34 +1821,34 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D26" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E26">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="F26">
-        <v>5.36</v>
+        <v>5.13</v>
       </c>
       <c r="G26" s="1">
-        <v>0.906</v>
+        <v>0.743</v>
       </c>
       <c r="H26" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I26" s="2">
-        <v>72.88</v>
+        <v>41.86</v>
       </c>
       <c r="J26" s="2">
-        <v>0.802</v>
+        <v>0.46</v>
       </c>
       <c r="K26" t="s">
         <v>141</v>
@@ -1859,34 +1859,34 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D27" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E27">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="F27">
-        <v>3.96</v>
+        <v>4.75</v>
       </c>
       <c r="G27" s="1">
-        <v>0.905</v>
+        <v>0.742</v>
       </c>
       <c r="H27" t="s">
         <v>139</v>
       </c>
       <c r="I27" s="2">
-        <v>72.81</v>
+        <v>41.68</v>
       </c>
       <c r="J27" s="2">
-        <v>0.801</v>
+        <v>0.458</v>
       </c>
       <c r="K27" t="s">
         <v>141</v>
@@ -1900,31 +1900,31 @@
         <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C28" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D28" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E28">
-        <v>27.5</v>
+        <v>14.5</v>
       </c>
       <c r="F28">
-        <v>36.73</v>
+        <v>10.01</v>
       </c>
       <c r="G28" s="1">
-        <v>0.903</v>
+        <v>0.736</v>
       </c>
       <c r="H28" t="s">
         <v>139</v>
       </c>
       <c r="I28" s="2">
-        <v>72.38</v>
+        <v>40.47</v>
       </c>
       <c r="J28" s="2">
-        <v>0.796</v>
+        <v>0.445</v>
       </c>
       <c r="K28" t="s">
         <v>141</v>
@@ -1938,31 +1938,31 @@
         <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D29" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E29">
-        <v>7.5</v>
+        <v>13.5</v>
       </c>
       <c r="F29">
-        <v>4.44</v>
+        <v>19.84</v>
       </c>
       <c r="G29" s="1">
-        <v>0.901</v>
+        <v>0.735</v>
       </c>
       <c r="H29" t="s">
         <v>140</v>
       </c>
       <c r="I29" s="2">
-        <v>71.91</v>
+        <v>40.26</v>
       </c>
       <c r="J29" s="2">
-        <v>0.791</v>
+        <v>0.443</v>
       </c>
       <c r="K29" t="s">
         <v>141</v>
@@ -1976,31 +1976,31 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C30" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D30" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E30">
-        <v>6.5</v>
+        <v>23.5</v>
       </c>
       <c r="F30">
-        <v>3.83</v>
+        <v>18.74</v>
       </c>
       <c r="G30" s="1">
-        <v>0.9</v>
+        <v>0.734</v>
       </c>
       <c r="H30" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I30" s="2">
-        <v>71.90000000000001</v>
+        <v>40.13</v>
       </c>
       <c r="J30" s="2">
-        <v>0.791</v>
+        <v>0.441</v>
       </c>
       <c r="K30" t="s">
         <v>141</v>
@@ -2014,31 +2014,31 @@
         <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="C31" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D31" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E31">
-        <v>2.5</v>
+        <v>17.5</v>
       </c>
       <c r="F31">
-        <v>5.3</v>
+        <v>23.06</v>
       </c>
       <c r="G31" s="1">
-        <v>0.899</v>
+        <v>0.729</v>
       </c>
       <c r="H31" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I31" s="2">
-        <v>71.56</v>
+        <v>39.24</v>
       </c>
       <c r="J31" s="2">
-        <v>0.787</v>
+        <v>0.432</v>
       </c>
       <c r="K31" t="s">
         <v>141</v>
@@ -2052,31 +2052,31 @@
         <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C32" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D32" t="s">
         <v>134</v>
       </c>
       <c r="E32">
-        <v>12.5</v>
+        <v>24.5</v>
       </c>
       <c r="F32">
-        <v>4.45</v>
+        <v>29.69</v>
       </c>
       <c r="G32" s="1">
-        <v>0.896</v>
+        <v>0.729</v>
       </c>
       <c r="H32" t="s">
         <v>140</v>
       </c>
       <c r="I32" s="2">
-        <v>71.06</v>
+        <v>39.23</v>
       </c>
       <c r="J32" s="2">
-        <v>0.782</v>
+        <v>0.432</v>
       </c>
       <c r="K32" t="s">
         <v>141</v>
@@ -2090,31 +2090,31 @@
         <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C33" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="D33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E33">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="F33">
-        <v>5.25</v>
+        <v>7.01</v>
       </c>
       <c r="G33" s="1">
-        <v>0.895</v>
+        <v>0.728</v>
       </c>
       <c r="H33" t="s">
         <v>139</v>
       </c>
       <c r="I33" s="2">
-        <v>70.86</v>
+        <v>39.02</v>
       </c>
       <c r="J33" s="2">
-        <v>0.779</v>
+        <v>0.429</v>
       </c>
       <c r="K33" t="s">
         <v>141</v>
@@ -2128,31 +2128,31 @@
         <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D34" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E34">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="F34">
-        <v>3.84</v>
+        <v>1.05</v>
       </c>
       <c r="G34" s="1">
-        <v>0.895</v>
+        <v>0.726</v>
       </c>
       <c r="H34" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I34" s="2">
-        <v>70.78</v>
+        <v>38.66</v>
       </c>
       <c r="J34" s="2">
-        <v>0.779</v>
+        <v>0.425</v>
       </c>
       <c r="K34" t="s">
         <v>141</v>
@@ -2166,31 +2166,31 @@
         <v>44</v>
       </c>
       <c r="B35" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C35" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D35" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E35">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="F35">
-        <v>28.87</v>
+        <v>8.57</v>
       </c>
       <c r="G35" s="1">
-        <v>0.894</v>
+        <v>0.726</v>
       </c>
       <c r="H35" t="s">
         <v>139</v>
       </c>
       <c r="I35" s="2">
-        <v>70.70999999999999</v>
+        <v>38.62</v>
       </c>
       <c r="J35" s="2">
-        <v>0.778</v>
+        <v>0.425</v>
       </c>
       <c r="K35" t="s">
         <v>141</v>
@@ -2204,31 +2204,31 @@
         <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="C36" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D36" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E36">
-        <v>3.5</v>
+        <v>23.5</v>
       </c>
       <c r="F36">
-        <v>6.57</v>
+        <v>16.56</v>
       </c>
       <c r="G36" s="1">
-        <v>0.893</v>
+        <v>0.724</v>
       </c>
       <c r="H36" t="s">
         <v>139</v>
       </c>
       <c r="I36" s="2">
-        <v>70.48999999999999</v>
+        <v>38.17</v>
       </c>
       <c r="J36" s="2">
-        <v>0.775</v>
+        <v>0.42</v>
       </c>
       <c r="K36" t="s">
         <v>141</v>
@@ -2242,31 +2242,31 @@
         <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C37" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="D37" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E37">
-        <v>3.5</v>
+        <v>28.5</v>
       </c>
       <c r="F37">
-        <v>6.72</v>
+        <v>21.82</v>
       </c>
       <c r="G37" s="1">
-        <v>0.887</v>
+        <v>0.724</v>
       </c>
       <c r="H37" t="s">
         <v>139</v>
       </c>
       <c r="I37" s="2">
-        <v>69.41</v>
+        <v>38.15</v>
       </c>
       <c r="J37" s="2">
-        <v>0.763</v>
+        <v>0.42</v>
       </c>
       <c r="K37" t="s">
         <v>141</v>
@@ -2280,31 +2280,31 @@
         <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C38" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D38" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E38">
-        <v>12.5</v>
+        <v>4.5</v>
       </c>
       <c r="F38">
-        <v>5.53</v>
+        <v>3.54</v>
       </c>
       <c r="G38" s="1">
-        <v>0.887</v>
+        <v>0.717</v>
       </c>
       <c r="H38" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I38" s="2">
-        <v>69.34999999999999</v>
+        <v>36.97</v>
       </c>
       <c r="J38" s="2">
-        <v>0.763</v>
+        <v>0.407</v>
       </c>
       <c r="K38" t="s">
         <v>141</v>
@@ -2318,31 +2318,31 @@
         <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="C39" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D39" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E39">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="F39">
-        <v>15.92</v>
+        <v>12.89</v>
       </c>
       <c r="G39" s="1">
-        <v>0.886</v>
+        <v>0.716</v>
       </c>
       <c r="H39" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I39" s="2">
-        <v>69.18000000000001</v>
+        <v>36.6</v>
       </c>
       <c r="J39" s="2">
-        <v>0.761</v>
+        <v>0.403</v>
       </c>
       <c r="K39" t="s">
         <v>141</v>
@@ -2356,31 +2356,31 @@
         <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C40" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D40" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E40">
-        <v>1.5</v>
+        <v>29.5</v>
       </c>
       <c r="F40">
-        <v>3.71</v>
+        <v>35.43</v>
       </c>
       <c r="G40" s="1">
-        <v>0.884</v>
+        <v>0.714</v>
       </c>
       <c r="H40" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I40" s="2">
-        <v>68.84999999999999</v>
+        <v>36.34</v>
       </c>
       <c r="J40" s="2">
-        <v>0.757</v>
+        <v>0.4</v>
       </c>
       <c r="K40" t="s">
         <v>141</v>
@@ -2394,31 +2394,31 @@
         <v>50</v>
       </c>
       <c r="B41" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C41" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E41">
-        <v>5.5</v>
+        <v>27.5</v>
       </c>
       <c r="F41">
-        <v>2.52</v>
+        <v>24.23</v>
       </c>
       <c r="G41" s="1">
-        <v>0.884</v>
+        <v>0.713</v>
       </c>
       <c r="H41" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I41" s="2">
-        <v>68.69</v>
+        <v>36.18</v>
       </c>
       <c r="J41" s="2">
-        <v>0.756</v>
+        <v>0.398</v>
       </c>
       <c r="K41" t="s">
         <v>141</v>
@@ -2432,31 +2432,31 @@
         <v>51</v>
       </c>
       <c r="B42" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C42" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="D42" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E42">
-        <v>13.5</v>
+        <v>8.5</v>
       </c>
       <c r="F42">
-        <v>7.48</v>
+        <v>6.65</v>
       </c>
       <c r="G42" s="1">
-        <v>0.88</v>
+        <v>0.713</v>
       </c>
       <c r="H42" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I42" s="2">
-        <v>68.03</v>
+        <v>36.04</v>
       </c>
       <c r="J42" s="2">
-        <v>0.748</v>
+        <v>0.396</v>
       </c>
       <c r="K42" t="s">
         <v>141</v>
@@ -2470,31 +2470,31 @@
         <v>52</v>
       </c>
       <c r="B43" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="C43" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D43" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E43">
-        <v>18.5</v>
+        <v>9.5</v>
       </c>
       <c r="F43">
-        <v>11.16</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G43" s="1">
-        <v>0.876</v>
+        <v>0.712</v>
       </c>
       <c r="H43" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I43" s="2">
-        <v>67.28</v>
+        <v>35.97</v>
       </c>
       <c r="J43" s="2">
-        <v>0.74</v>
+        <v>0.396</v>
       </c>
       <c r="K43" t="s">
         <v>141</v>
@@ -2508,31 +2508,31 @@
         <v>53</v>
       </c>
       <c r="B44" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="C44" t="s">
         <v>126</v>
       </c>
       <c r="D44" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E44">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="F44">
-        <v>4.96</v>
+        <v>5.35</v>
       </c>
       <c r="G44" s="1">
-        <v>0.872</v>
+        <v>0.71</v>
       </c>
       <c r="H44" t="s">
         <v>139</v>
       </c>
       <c r="I44" s="2">
-        <v>66.47</v>
+        <v>35.49</v>
       </c>
       <c r="J44" s="2">
-        <v>0.731</v>
+        <v>0.39</v>
       </c>
       <c r="K44" t="s">
         <v>141</v>
@@ -2543,34 +2543,34 @@
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="B45" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C45" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D45" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E45">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="F45">
-        <v>2.49</v>
+        <v>10.78</v>
       </c>
       <c r="G45" s="1">
-        <v>0.871</v>
+        <v>0.709</v>
       </c>
       <c r="H45" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I45" s="2">
-        <v>66.23999999999999</v>
+        <v>35.39</v>
       </c>
       <c r="J45" s="2">
-        <v>0.729</v>
+        <v>0.389</v>
       </c>
       <c r="K45" t="s">
         <v>141</v>
@@ -2581,34 +2581,34 @@
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B46" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="C46" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D46" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E46">
-        <v>11.5</v>
+        <v>2.5</v>
       </c>
       <c r="F46">
-        <v>16.43</v>
+        <v>3.66</v>
       </c>
       <c r="G46" s="1">
-        <v>0.869</v>
+        <v>0.708</v>
       </c>
       <c r="H46" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I46" s="2">
-        <v>65.87</v>
+        <v>35.12</v>
       </c>
       <c r="J46" s="2">
-        <v>0.725</v>
+        <v>0.386</v>
       </c>
       <c r="K46" t="s">
         <v>141</v>
@@ -2619,34 +2619,34 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B47" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="C47" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D47" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E47">
         <v>3.5</v>
       </c>
       <c r="F47">
-        <v>6.21</v>
+        <v>2.73</v>
       </c>
       <c r="G47" s="1">
-        <v>0.866</v>
+        <v>0.708</v>
       </c>
       <c r="H47" t="s">
         <v>139</v>
       </c>
       <c r="I47" s="2">
-        <v>65.37</v>
+        <v>35.09</v>
       </c>
       <c r="J47" s="2">
-        <v>0.719</v>
+        <v>0.386</v>
       </c>
       <c r="K47" t="s">
         <v>141</v>
@@ -2657,34 +2657,34 @@
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B48" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="C48" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D48" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E48">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="F48">
-        <v>5.82</v>
+        <v>5.16</v>
       </c>
       <c r="G48" s="1">
-        <v>0.865</v>
+        <v>0.704</v>
       </c>
       <c r="H48" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I48" s="2">
-        <v>65.17</v>
+        <v>34.48</v>
       </c>
       <c r="J48" s="2">
-        <v>0.717</v>
+        <v>0.379</v>
       </c>
       <c r="K48" t="s">
         <v>141</v>
@@ -2695,34 +2695,34 @@
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B49" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C49" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D49" t="s">
         <v>134</v>
       </c>
       <c r="E49">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
       <c r="F49">
-        <v>1.22</v>
+        <v>15.13</v>
       </c>
       <c r="G49" s="1">
-        <v>0.865</v>
+        <v>0.703</v>
       </c>
       <c r="H49" t="s">
         <v>140</v>
       </c>
       <c r="I49" s="2">
-        <v>65.13</v>
+        <v>34.19</v>
       </c>
       <c r="J49" s="2">
-        <v>0.716</v>
+        <v>0.376</v>
       </c>
       <c r="K49" t="s">
         <v>141</v>
@@ -2733,34 +2733,34 @@
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B50" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="C50" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D50" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E50">
-        <v>3.5</v>
+        <v>9.5</v>
       </c>
       <c r="F50">
-        <v>1.76</v>
+        <v>13.21</v>
       </c>
       <c r="G50" s="1">
-        <v>0.865</v>
+        <v>0.701</v>
       </c>
       <c r="H50" t="s">
         <v>140</v>
       </c>
       <c r="I50" s="2">
-        <v>65.06</v>
+        <v>33.77</v>
       </c>
       <c r="J50" s="2">
-        <v>0.716</v>
+        <v>0.371</v>
       </c>
       <c r="K50" t="s">
         <v>141</v>
@@ -2771,34 +2771,34 @@
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B51" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="C51" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D51" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E51">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="F51">
-        <v>2.32</v>
+        <v>13.7</v>
       </c>
       <c r="G51" s="1">
-        <v>0.859</v>
+        <v>0.697</v>
       </c>
       <c r="H51" t="s">
         <v>140</v>
       </c>
       <c r="I51" s="2">
-        <v>64.05</v>
+        <v>33.07</v>
       </c>
       <c r="J51" s="2">
-        <v>0.705</v>
+        <v>0.364</v>
       </c>
       <c r="K51" t="s">
         <v>141</v>
@@ -2809,34 +2809,34 @@
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B52" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="C52" t="s">
         <v>126</v>
       </c>
       <c r="D52" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E52">
-        <v>1.5</v>
+        <v>14.5</v>
       </c>
       <c r="F52">
-        <v>3.44</v>
+        <v>11.32</v>
       </c>
       <c r="G52" s="1">
-        <v>0.858</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H52" t="s">
         <v>139</v>
       </c>
       <c r="I52" s="2">
-        <v>63.71</v>
+        <v>32.2</v>
       </c>
       <c r="J52" s="2">
-        <v>0.701</v>
+        <v>0.354</v>
       </c>
       <c r="K52" t="s">
         <v>141</v>
@@ -2847,34 +2847,34 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B53" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C53" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="D53" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E53">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F53">
-        <v>4.79</v>
+        <v>2.79</v>
       </c>
       <c r="G53" s="1">
-        <v>0.857</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H53" t="s">
         <v>139</v>
       </c>
       <c r="I53" s="2">
-        <v>63.57</v>
+        <v>32.09</v>
       </c>
       <c r="J53" s="2">
-        <v>0.699</v>
+        <v>0.353</v>
       </c>
       <c r="K53" t="s">
         <v>141</v>
@@ -2885,34 +2885,34 @@
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B54" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C54" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D54" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E54">
-        <v>18.5</v>
+        <v>10.5</v>
       </c>
       <c r="F54">
-        <v>26.1</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="G54" s="1">
-        <v>0.853</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="H54" t="s">
         <v>139</v>
       </c>
       <c r="I54" s="2">
-        <v>62.91</v>
+        <v>31.83</v>
       </c>
       <c r="J54" s="2">
-        <v>0.6919999999999999</v>
+        <v>0.35</v>
       </c>
       <c r="K54" t="s">
         <v>141</v>
@@ -2923,34 +2923,34 @@
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B55" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C55" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="D55" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E55">
-        <v>3.5</v>
+        <v>12.5</v>
       </c>
       <c r="F55">
-        <v>6.05</v>
+        <v>9.33</v>
       </c>
       <c r="G55" s="1">
-        <v>0.853</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H55" t="s">
         <v>139</v>
       </c>
       <c r="I55" s="2">
-        <v>62.9</v>
+        <v>31.74</v>
       </c>
       <c r="J55" s="2">
-        <v>0.6919999999999999</v>
+        <v>0.349</v>
       </c>
       <c r="K55" t="s">
         <v>141</v>
@@ -2961,34 +2961,34 @@
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="B56" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C56" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D56" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E56">
         <v>9.5</v>
       </c>
       <c r="F56">
-        <v>5.78</v>
+        <v>12.08</v>
       </c>
       <c r="G56" s="1">
-        <v>0.852</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="H56" t="s">
         <v>140</v>
       </c>
       <c r="I56" s="2">
-        <v>62.6</v>
+        <v>30.98</v>
       </c>
       <c r="J56" s="2">
-        <v>0.6889999999999999</v>
+        <v>0.341</v>
       </c>
       <c r="K56" t="s">
         <v>141</v>
@@ -2999,34 +2999,34 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B57" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C57" t="s">
         <v>114</v>
       </c>
       <c r="D57" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E57">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="F57">
-        <v>3.29</v>
+        <v>5.37</v>
       </c>
       <c r="G57" s="1">
-        <v>0.849</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="H57" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I57" s="2">
-        <v>62.08</v>
+        <v>30.29</v>
       </c>
       <c r="J57" s="2">
-        <v>0.6830000000000001</v>
+        <v>0.333</v>
       </c>
       <c r="K57" t="s">
         <v>141</v>
@@ -3037,34 +3037,34 @@
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B58" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="C58" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="D58" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E58">
-        <v>7.5</v>
+        <v>21.5</v>
       </c>
       <c r="F58">
-        <v>4.17</v>
+        <v>25.01</v>
       </c>
       <c r="G58" s="1">
-        <v>0.845</v>
+        <v>0.68</v>
       </c>
       <c r="H58" t="s">
         <v>140</v>
       </c>
       <c r="I58" s="2">
-        <v>61.36</v>
+        <v>29.89</v>
       </c>
       <c r="J58" s="2">
-        <v>0.675</v>
+        <v>0.329</v>
       </c>
       <c r="K58" t="s">
         <v>141</v>
@@ -3075,34 +3075,34 @@
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="B59" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C59" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D59" t="s">
         <v>134</v>
       </c>
       <c r="E59">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="F59">
-        <v>2.66</v>
+        <v>20.3</v>
       </c>
       <c r="G59" s="1">
-        <v>0.84</v>
+        <v>0.68</v>
       </c>
       <c r="H59" t="s">
         <v>140</v>
       </c>
       <c r="I59" s="2">
-        <v>60.43</v>
+        <v>29.78</v>
       </c>
       <c r="J59" s="2">
-        <v>0.665</v>
+        <v>0.328</v>
       </c>
       <c r="K59" t="s">
         <v>141</v>
@@ -3113,34 +3113,34 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B60" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C60" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="D60" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E60">
-        <v>33.5</v>
+        <v>7.5</v>
       </c>
       <c r="F60">
-        <v>25.92</v>
+        <v>6.7</v>
       </c>
       <c r="G60" s="1">
-        <v>0.839</v>
+        <v>0.68</v>
       </c>
       <c r="H60" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I60" s="2">
-        <v>60.2</v>
+        <v>29.76</v>
       </c>
       <c r="J60" s="2">
-        <v>0.662</v>
+        <v>0.327</v>
       </c>
       <c r="K60" t="s">
         <v>141</v>
@@ -3151,34 +3151,34 @@
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B61" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C61" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D61" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E61">
         <v>20.5</v>
       </c>
       <c r="F61">
-        <v>29.31</v>
+        <v>23.76</v>
       </c>
       <c r="G61" s="1">
-        <v>0.839</v>
+        <v>0.677</v>
       </c>
       <c r="H61" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I61" s="2">
-        <v>60.13</v>
+        <v>29.25</v>
       </c>
       <c r="J61" s="2">
-        <v>0.661</v>
+        <v>0.322</v>
       </c>
       <c r="K61" t="s">
         <v>141</v>
@@ -3189,34 +3189,34 @@
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="B62" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C62" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D62" t="s">
         <v>135</v>
       </c>
       <c r="E62">
-        <v>19.5</v>
+        <v>11.5</v>
       </c>
       <c r="F62">
-        <v>26.12</v>
+        <v>14.11</v>
       </c>
       <c r="G62" s="1">
-        <v>0.838</v>
+        <v>0.676</v>
       </c>
       <c r="H62" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I62" s="2">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="J62" s="2">
-        <v>0.66</v>
+        <v>0.319</v>
       </c>
       <c r="K62" t="s">
         <v>141</v>
@@ -3227,34 +3227,34 @@
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B63" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C63" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D63" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E63">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="F63">
-        <v>5.5</v>
+        <v>2.35</v>
       </c>
       <c r="G63" s="1">
-        <v>0.838</v>
+        <v>0.674</v>
       </c>
       <c r="H63" t="s">
         <v>140</v>
       </c>
       <c r="I63" s="2">
-        <v>59.97</v>
+        <v>28.61</v>
       </c>
       <c r="J63" s="2">
-        <v>0.66</v>
+        <v>0.315</v>
       </c>
       <c r="K63" t="s">
         <v>141</v>
@@ -3265,34 +3265,34 @@
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B64" t="s">
         <v>126</v>
       </c>
       <c r="C64" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D64" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E64">
-        <v>3.5</v>
+        <v>15.5</v>
       </c>
       <c r="F64">
-        <v>5.84</v>
+        <v>19.72</v>
       </c>
       <c r="G64" s="1">
-        <v>0.834</v>
+        <v>0.673</v>
       </c>
       <c r="H64" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I64" s="2">
-        <v>59.23</v>
+        <v>28.46</v>
       </c>
       <c r="J64" s="2">
-        <v>0.652</v>
+        <v>0.313</v>
       </c>
       <c r="K64" t="s">
         <v>141</v>
@@ -3303,34 +3303,34 @@
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B65" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C65" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D65" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E65">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="F65">
-        <v>11.06</v>
+        <v>20.95</v>
       </c>
       <c r="G65" s="1">
-        <v>0.83</v>
+        <v>0.671</v>
       </c>
       <c r="H65" t="s">
         <v>140</v>
       </c>
       <c r="I65" s="2">
-        <v>58.48</v>
+        <v>28.15</v>
       </c>
       <c r="J65" s="2">
-        <v>0.643</v>
+        <v>0.31</v>
       </c>
       <c r="K65" t="s">
         <v>141</v>
@@ -3341,34 +3341,34 @@
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B66" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C66" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D66" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E66">
-        <v>11.5</v>
+        <v>4.5</v>
       </c>
       <c r="F66">
-        <v>4.38</v>
+        <v>6.18</v>
       </c>
       <c r="G66" s="1">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
       <c r="H66" t="s">
         <v>140</v>
       </c>
       <c r="I66" s="2">
-        <v>58.42</v>
+        <v>27.94</v>
       </c>
       <c r="J66" s="2">
-        <v>0.643</v>
+        <v>0.307</v>
       </c>
       <c r="K66" t="s">
         <v>141</v>
@@ -3379,13 +3379,13 @@
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B67" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C67" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D67" t="s">
         <v>137</v>
@@ -3394,19 +3394,19 @@
         <v>3.5</v>
       </c>
       <c r="F67">
-        <v>5.77</v>
+        <v>4.77</v>
       </c>
       <c r="G67" s="1">
-        <v>0.827</v>
+        <v>0.669</v>
       </c>
       <c r="H67" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I67" s="2">
-        <v>57.87</v>
+        <v>27.81</v>
       </c>
       <c r="J67" s="2">
-        <v>0.637</v>
+        <v>0.306</v>
       </c>
       <c r="K67" t="s">
         <v>141</v>
@@ -3417,34 +3417,34 @@
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B68" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C68" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D68" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E68">
-        <v>26.5</v>
+        <v>9.5</v>
       </c>
       <c r="F68">
-        <v>32.25</v>
+        <v>7.68</v>
       </c>
       <c r="G68" s="1">
-        <v>0.824</v>
+        <v>0.659</v>
       </c>
       <c r="H68" t="s">
         <v>139</v>
       </c>
       <c r="I68" s="2">
-        <v>57.37</v>
+        <v>25.9</v>
       </c>
       <c r="J68" s="2">
-        <v>0.631</v>
+        <v>0.285</v>
       </c>
       <c r="K68" t="s">
         <v>141</v>
@@ -3455,34 +3455,34 @@
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B69" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C69" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D69" t="s">
         <v>134</v>
       </c>
       <c r="E69">
-        <v>22.5</v>
+        <v>13.5</v>
       </c>
       <c r="F69">
-        <v>29.31</v>
+        <v>16.89</v>
       </c>
       <c r="G69" s="1">
-        <v>0.8159999999999999</v>
+        <v>0.659</v>
       </c>
       <c r="H69" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I69" s="2">
-        <v>55.84</v>
+        <v>25.76</v>
       </c>
       <c r="J69" s="2">
-        <v>0.614</v>
+        <v>0.283</v>
       </c>
       <c r="K69" t="s">
         <v>141</v>
@@ -3493,34 +3493,34 @@
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="B70" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="C70" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D70" t="s">
         <v>137</v>
       </c>
       <c r="E70">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F70">
-        <v>4.41</v>
+        <v>2.95</v>
       </c>
       <c r="G70" s="1">
-        <v>0.8149999999999999</v>
+        <v>0.658</v>
       </c>
       <c r="H70" t="s">
         <v>139</v>
       </c>
       <c r="I70" s="2">
-        <v>55.68</v>
+        <v>25.6</v>
       </c>
       <c r="J70" s="2">
-        <v>0.612</v>
+        <v>0.282</v>
       </c>
       <c r="K70" t="s">
         <v>141</v>
@@ -3531,34 +3531,34 @@
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B71" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C71" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="D71" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E71">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="F71">
-        <v>6.36</v>
+        <v>11.96</v>
       </c>
       <c r="G71" s="1">
-        <v>0.8129999999999999</v>
+        <v>0.657</v>
       </c>
       <c r="H71" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I71" s="2">
-        <v>55.14</v>
+        <v>25.43</v>
       </c>
       <c r="J71" s="2">
-        <v>0.607</v>
+        <v>0.28</v>
       </c>
       <c r="K71" t="s">
         <v>141</v>
@@ -3569,34 +3569,34 @@
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B72" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C72" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D72" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E72">
-        <v>6.5</v>
+        <v>10.5</v>
       </c>
       <c r="F72">
-        <v>3.86</v>
+        <v>7.33</v>
       </c>
       <c r="G72" s="1">
-        <v>0.8080000000000001</v>
+        <v>0.656</v>
       </c>
       <c r="H72" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I72" s="2">
-        <v>54.25</v>
+        <v>25.28</v>
       </c>
       <c r="J72" s="2">
-        <v>0.597</v>
+        <v>0.278</v>
       </c>
       <c r="K72" t="s">
         <v>141</v>
@@ -3607,34 +3607,34 @@
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B73" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C73" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D73" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E73">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="F73">
-        <v>4.94</v>
+        <v>1.39</v>
       </c>
       <c r="G73" s="1">
-        <v>0.8070000000000001</v>
+        <v>0.656</v>
       </c>
       <c r="H73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I73" s="2">
-        <v>54.03</v>
+        <v>25.19</v>
       </c>
       <c r="J73" s="2">
-        <v>0.594</v>
+        <v>0.277</v>
       </c>
       <c r="K73" t="s">
         <v>141</v>
@@ -3645,34 +3645,34 @@
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B74" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C74" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D74" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E74">
-        <v>8.5</v>
+        <v>22.5</v>
       </c>
       <c r="F74">
-        <v>5.16</v>
+        <v>25.53</v>
       </c>
       <c r="G74" s="1">
-        <v>0.804</v>
+        <v>0.656</v>
       </c>
       <c r="H74" t="s">
         <v>140</v>
       </c>
       <c r="I74" s="2">
-        <v>53.46</v>
+        <v>25.15</v>
       </c>
       <c r="J74" s="2">
-        <v>0.588</v>
+        <v>0.277</v>
       </c>
       <c r="K74" t="s">
         <v>141</v>
@@ -3683,34 +3683,34 @@
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B75" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C75" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="D75" t="s">
         <v>135</v>
       </c>
       <c r="E75">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="F75">
-        <v>24.21</v>
+        <v>16.95</v>
       </c>
       <c r="G75" s="1">
-        <v>0.802</v>
+        <v>0.655</v>
       </c>
       <c r="H75" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I75" s="2">
-        <v>53.02</v>
+        <v>25.12</v>
       </c>
       <c r="J75" s="2">
-        <v>0.583</v>
+        <v>0.276</v>
       </c>
       <c r="K75" t="s">
         <v>141</v>
@@ -3721,34 +3721,34 @@
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B76" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C76" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D76" t="s">
         <v>137</v>
       </c>
       <c r="E76">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="F76">
-        <v>3.82</v>
+        <v>6.6</v>
       </c>
       <c r="G76" s="1">
-        <v>0.801</v>
+        <v>0.653</v>
       </c>
       <c r="H76" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I76" s="2">
-        <v>52.85</v>
+        <v>24.7</v>
       </c>
       <c r="J76" s="2">
-        <v>0.581</v>
+        <v>0.272</v>
       </c>
       <c r="K76" t="s">
         <v>141</v>
@@ -3759,34 +3759,34 @@
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="B77" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C77" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="D77" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E77">
-        <v>26.5</v>
+        <v>12.5</v>
       </c>
       <c r="F77">
-        <v>31.68</v>
+        <v>14.84</v>
       </c>
       <c r="G77" s="1">
-        <v>0.795</v>
+        <v>0.649</v>
       </c>
       <c r="H77" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I77" s="2">
-        <v>51.8</v>
+        <v>23.83</v>
       </c>
       <c r="J77" s="2">
-        <v>0.57</v>
+        <v>0.262</v>
       </c>
       <c r="K77" t="s">
         <v>141</v>
@@ -3797,34 +3797,34 @@
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B78" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C78" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D78" t="s">
         <v>137</v>
       </c>
       <c r="E78">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F78">
-        <v>4.22</v>
+        <v>1.56</v>
       </c>
       <c r="G78" s="1">
-        <v>0.793</v>
+        <v>0.645</v>
       </c>
       <c r="H78" t="s">
         <v>139</v>
       </c>
       <c r="I78" s="2">
-        <v>51.35</v>
+        <v>23.18</v>
       </c>
       <c r="J78" s="2">
-        <v>0.5649999999999999</v>
+        <v>0.255</v>
       </c>
       <c r="K78" t="s">
         <v>141</v>
@@ -3835,34 +3835,34 @@
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B79" t="s">
         <v>129</v>
       </c>
       <c r="C79" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D79" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E79">
-        <v>7.5</v>
+        <v>19.5</v>
       </c>
       <c r="F79">
-        <v>4.88</v>
+        <v>16.22</v>
       </c>
       <c r="G79" s="1">
-        <v>0.789</v>
+        <v>0.645</v>
       </c>
       <c r="H79" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I79" s="2">
-        <v>50.67</v>
+        <v>23.1</v>
       </c>
       <c r="J79" s="2">
-        <v>0.5570000000000001</v>
+        <v>0.254</v>
       </c>
       <c r="K79" t="s">
         <v>141</v>
@@ -3873,34 +3873,34 @@
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B80" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C80" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D80" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E80">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="F80">
-        <v>13.87</v>
+        <v>13.46</v>
       </c>
       <c r="G80" s="1">
-        <v>0.789</v>
+        <v>0.642</v>
       </c>
       <c r="H80" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I80" s="2">
-        <v>50.63</v>
+        <v>22.57</v>
       </c>
       <c r="J80" s="2">
-        <v>0.5570000000000001</v>
+        <v>0.248</v>
       </c>
       <c r="K80" t="s">
         <v>141</v>
@@ -3914,7 +3914,7 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C81" t="s">
         <v>132</v>
@@ -3923,22 +3923,22 @@
         <v>137</v>
       </c>
       <c r="E81">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="F81">
-        <v>2.86</v>
+        <v>2.2</v>
       </c>
       <c r="G81" s="1">
-        <v>0.782</v>
+        <v>0.641</v>
       </c>
       <c r="H81" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I81" s="2">
-        <v>49.32</v>
+        <v>22.39</v>
       </c>
       <c r="J81" s="2">
-        <v>0.543</v>
+        <v>0.246</v>
       </c>
       <c r="K81" t="s">
         <v>141</v>
@@ -3949,34 +3949,34 @@
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C82" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D82" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E82">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="F82">
-        <v>4.13</v>
+        <v>7.49</v>
       </c>
       <c r="G82" s="1">
-        <v>0.78</v>
+        <v>0.637</v>
       </c>
       <c r="H82" t="s">
         <v>139</v>
       </c>
       <c r="I82" s="2">
-        <v>48.95</v>
+        <v>21.54</v>
       </c>
       <c r="J82" s="2">
-        <v>0.538</v>
+        <v>0.237</v>
       </c>
       <c r="K82" t="s">
         <v>141</v>
@@ -3987,34 +3987,34 @@
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B83" t="s">
+        <v>115</v>
+      </c>
+      <c r="C83" t="s">
         <v>128</v>
       </c>
-      <c r="C83" t="s">
-        <v>114</v>
-      </c>
       <c r="D83" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E83">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="F83">
-        <v>4.12</v>
+        <v>10.57</v>
       </c>
       <c r="G83" s="1">
-        <v>0.78</v>
+        <v>0.636</v>
       </c>
       <c r="H83" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I83" s="2">
-        <v>48.82</v>
+        <v>21.5</v>
       </c>
       <c r="J83" s="2">
-        <v>0.537</v>
+        <v>0.236</v>
       </c>
       <c r="K83" t="s">
         <v>141</v>
@@ -4025,34 +4025,34 @@
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C84" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D84" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E84">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="F84">
-        <v>4.1</v>
+        <v>7.09</v>
       </c>
       <c r="G84" s="1">
-        <v>0.776</v>
+        <v>0.634</v>
       </c>
       <c r="H84" t="s">
         <v>139</v>
       </c>
       <c r="I84" s="2">
-        <v>48.09</v>
+        <v>21.05</v>
       </c>
       <c r="J84" s="2">
-        <v>0.529</v>
+        <v>0.232</v>
       </c>
       <c r="K84" t="s">
         <v>141</v>
@@ -4063,34 +4063,34 @@
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="B85" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C85" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D85" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E85">
-        <v>3.5</v>
+        <v>19.5</v>
       </c>
       <c r="F85">
-        <v>5.25</v>
+        <v>17.97</v>
       </c>
       <c r="G85" s="1">
-        <v>0.769</v>
+        <v>0.632</v>
       </c>
       <c r="H85" t="s">
         <v>139</v>
       </c>
       <c r="I85" s="2">
-        <v>46.78</v>
+        <v>20.72</v>
       </c>
       <c r="J85" s="2">
-        <v>0.515</v>
+        <v>0.228</v>
       </c>
       <c r="K85" t="s">
         <v>141</v>
@@ -4101,34 +4101,34 @@
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="B86" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C86" t="s">
         <v>129</v>
       </c>
       <c r="D86" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E86">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="F86">
-        <v>3.19</v>
+        <v>1.32</v>
       </c>
       <c r="G86" s="1">
-        <v>0.768</v>
+        <v>0.628</v>
       </c>
       <c r="H86" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I86" s="2">
-        <v>46.67</v>
+        <v>19.96</v>
       </c>
       <c r="J86" s="2">
-        <v>0.513</v>
+        <v>0.22</v>
       </c>
       <c r="K86" t="s">
         <v>141</v>
@@ -4139,34 +4139,34 @@
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B87" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="C87" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D87" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E87">
-        <v>6.5</v>
+        <v>18.5</v>
       </c>
       <c r="F87">
-        <v>4.36</v>
+        <v>21.34</v>
       </c>
       <c r="G87" s="1">
-        <v>0.768</v>
+        <v>0.627</v>
       </c>
       <c r="H87" t="s">
         <v>140</v>
       </c>
       <c r="I87" s="2">
-        <v>46.6</v>
+        <v>19.62</v>
       </c>
       <c r="J87" s="2">
-        <v>0.513</v>
+        <v>0.216</v>
       </c>
       <c r="K87" t="s">
         <v>141</v>
@@ -4177,34 +4177,34 @@
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B88" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C88" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D88" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E88">
-        <v>39.5</v>
+        <v>9.5</v>
       </c>
       <c r="F88">
-        <v>49.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G88" s="1">
-        <v>0.765</v>
+        <v>0.625</v>
       </c>
       <c r="H88" t="s">
         <v>139</v>
       </c>
       <c r="I88" s="2">
-        <v>45.96</v>
+        <v>19.4</v>
       </c>
       <c r="J88" s="2">
-        <v>0.506</v>
+        <v>0.213</v>
       </c>
       <c r="K88" t="s">
         <v>141</v>
@@ -4215,13 +4215,13 @@
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="B89" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C89" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D89" t="s">
         <v>137</v>
@@ -4230,19 +4230,19 @@
         <v>2.5</v>
       </c>
       <c r="F89">
-        <v>4.01</v>
+        <v>3.22</v>
       </c>
       <c r="G89" s="1">
-        <v>0.764</v>
+        <v>0.624</v>
       </c>
       <c r="H89" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I89" s="2">
-        <v>45.83</v>
+        <v>19.13</v>
       </c>
       <c r="J89" s="2">
-        <v>0.504</v>
+        <v>0.21</v>
       </c>
       <c r="K89" t="s">
         <v>141</v>
@@ -4253,34 +4253,34 @@
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B90" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C90" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="D90" t="s">
         <v>136</v>
       </c>
       <c r="E90">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F90">
-        <v>5.2</v>
+        <v>4.19</v>
       </c>
       <c r="G90" s="1">
-        <v>0.762</v>
+        <v>0.622</v>
       </c>
       <c r="H90" t="s">
         <v>139</v>
       </c>
       <c r="I90" s="2">
-        <v>45.45</v>
+        <v>18.78</v>
       </c>
       <c r="J90" s="2">
-        <v>0.5</v>
+        <v>0.207</v>
       </c>
       <c r="K90" t="s">
         <v>141</v>
@@ -4291,34 +4291,34 @@
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="B91" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C91" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="D91" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E91">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="F91">
-        <v>10.53</v>
+        <v>2.44</v>
       </c>
       <c r="G91" s="1">
-        <v>0.76</v>
+        <v>0.622</v>
       </c>
       <c r="H91" t="s">
         <v>139</v>
       </c>
       <c r="I91" s="2">
-        <v>45.02</v>
+        <v>18.71</v>
       </c>
       <c r="J91" s="2">
-        <v>0.495</v>
+        <v>0.206</v>
       </c>
       <c r="K91" t="s">
         <v>141</v>
@@ -4329,34 +4329,34 @@
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C92" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D92" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E92">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="F92">
-        <v>4.19</v>
+        <v>9</v>
       </c>
       <c r="G92" s="1">
-        <v>0.755</v>
+        <v>0.618</v>
       </c>
       <c r="H92" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I92" s="2">
-        <v>44.07</v>
+        <v>18.01</v>
       </c>
       <c r="J92" s="2">
-        <v>0.485</v>
+        <v>0.198</v>
       </c>
       <c r="K92" t="s">
         <v>141</v>
@@ -4367,34 +4367,34 @@
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="C93" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D93" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E93">
-        <v>18.5</v>
+        <v>5.5</v>
       </c>
       <c r="F93">
-        <v>24.07</v>
+        <v>5</v>
       </c>
       <c r="G93" s="1">
-        <v>0.753</v>
+        <v>0.617</v>
       </c>
       <c r="H93" t="s">
         <v>139</v>
       </c>
       <c r="I93" s="2">
-        <v>43.71</v>
+        <v>17.86</v>
       </c>
       <c r="J93" s="2">
-        <v>0.481</v>
+        <v>0.197</v>
       </c>
       <c r="K93" t="s">
         <v>141</v>
@@ -4405,34 +4405,34 @@
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C94" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D94" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E94">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="F94">
-        <v>3.53</v>
+        <v>3.4</v>
       </c>
       <c r="G94" s="1">
-        <v>0.743</v>
+        <v>0.617</v>
       </c>
       <c r="H94" t="s">
         <v>140</v>
       </c>
       <c r="I94" s="2">
-        <v>41.91</v>
+        <v>17.76</v>
       </c>
       <c r="J94" s="2">
-        <v>0.461</v>
+        <v>0.195</v>
       </c>
       <c r="K94" t="s">
         <v>141</v>
@@ -4443,34 +4443,34 @@
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C95" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="D95" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E95">
-        <v>1.5</v>
+        <v>19.5</v>
       </c>
       <c r="F95">
-        <v>2.65</v>
+        <v>17.44</v>
       </c>
       <c r="G95" s="1">
-        <v>0.742</v>
+        <v>0.616</v>
       </c>
       <c r="H95" t="s">
         <v>139</v>
       </c>
       <c r="I95" s="2">
-        <v>41.7</v>
+        <v>17.57</v>
       </c>
       <c r="J95" s="2">
-        <v>0.459</v>
+        <v>0.193</v>
       </c>
       <c r="K95" t="s">
         <v>141</v>
@@ -4481,34 +4481,34 @@
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C96" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D96" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E96">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="F96">
-        <v>18.48</v>
+        <v>4.07</v>
       </c>
       <c r="G96" s="1">
-        <v>0.742</v>
+        <v>0.616</v>
       </c>
       <c r="H96" t="s">
         <v>139</v>
       </c>
       <c r="I96" s="2">
-        <v>41.64</v>
+        <v>17.56</v>
       </c>
       <c r="J96" s="2">
-        <v>0.458</v>
+        <v>0.193</v>
       </c>
       <c r="K96" t="s">
         <v>141</v>
@@ -4519,34 +4519,34 @@
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="B97" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="C97" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D97" t="s">
         <v>137</v>
       </c>
       <c r="E97">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="F97">
-        <v>5.67</v>
+        <v>3.28</v>
       </c>
       <c r="G97" s="1">
-        <v>0.741</v>
+        <v>0.608</v>
       </c>
       <c r="H97" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I97" s="2">
-        <v>41.54</v>
+        <v>16.02</v>
       </c>
       <c r="J97" s="2">
-        <v>0.457</v>
+        <v>0.176</v>
       </c>
       <c r="K97" t="s">
         <v>141</v>
@@ -4557,34 +4557,34 @@
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B98" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C98" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="D98" t="s">
         <v>137</v>
       </c>
       <c r="E98">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="F98">
-        <v>6.05</v>
+        <v>1.55</v>
       </c>
       <c r="G98" s="1">
-        <v>0.736</v>
+        <v>0.607</v>
       </c>
       <c r="H98" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I98" s="2">
-        <v>40.59</v>
+        <v>15.84</v>
       </c>
       <c r="J98" s="2">
-        <v>0.446</v>
+        <v>0.174</v>
       </c>
       <c r="K98" t="s">
         <v>141</v>
@@ -4595,34 +4595,34 @@
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C99" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D99" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E99">
-        <v>28.5</v>
+        <v>8.5</v>
       </c>
       <c r="F99">
-        <v>21.53</v>
+        <v>6.44</v>
       </c>
       <c r="G99" s="1">
-        <v>0.732</v>
+        <v>0.607</v>
       </c>
       <c r="H99" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I99" s="2">
-        <v>39.76</v>
+        <v>15.79</v>
       </c>
       <c r="J99" s="2">
-        <v>0.437</v>
+        <v>0.174</v>
       </c>
       <c r="K99" t="s">
         <v>141</v>
@@ -4633,34 +4633,34 @@
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C100" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D100" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E100">
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="F100">
-        <v>3.48</v>
+        <v>14.32</v>
       </c>
       <c r="G100" s="1">
-        <v>0.73</v>
+        <v>0.606</v>
       </c>
       <c r="H100" t="s">
         <v>140</v>
       </c>
       <c r="I100" s="2">
-        <v>39.3</v>
+        <v>15.75</v>
       </c>
       <c r="J100" s="2">
-        <v>0.432</v>
+        <v>0.173</v>
       </c>
       <c r="K100" t="s">
         <v>141</v>
@@ -4671,34 +4671,34 @@
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="B101" t="s">
         <v>126</v>
       </c>
       <c r="C101" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D101" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E101">
-        <v>3.5</v>
+        <v>11.5</v>
       </c>
       <c r="F101">
-        <v>2.62</v>
+        <v>9.49</v>
       </c>
       <c r="G101" s="1">
-        <v>0.729</v>
+        <v>0.606</v>
       </c>
       <c r="H101" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I101" s="2">
-        <v>39.18</v>
+        <v>15.74</v>
       </c>
       <c r="J101" s="2">
-        <v>0.431</v>
+        <v>0.173</v>
       </c>
       <c r="K101" t="s">
         <v>141</v>
@@ -4709,34 +4709,34 @@
     </row>
     <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C102" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="D102" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E102">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="F102">
-        <v>6.7</v>
+        <v>10.99</v>
       </c>
       <c r="G102" s="1">
-        <v>0.728</v>
+        <v>0.605</v>
       </c>
       <c r="H102" t="s">
         <v>140</v>
       </c>
       <c r="I102" s="2">
-        <v>39.02</v>
+        <v>15.58</v>
       </c>
       <c r="J102" s="2">
-        <v>0.429</v>
+        <v>0.171</v>
       </c>
       <c r="K102" t="s">
         <v>141</v>
@@ -4747,34 +4747,34 @@
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C103" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D103" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E103">
-        <v>10.5</v>
+        <v>3.5</v>
       </c>
       <c r="F103">
-        <v>13.43</v>
+        <v>3.2</v>
       </c>
       <c r="G103" s="1">
-        <v>0.723</v>
+        <v>0.603</v>
       </c>
       <c r="H103" t="s">
         <v>139</v>
       </c>
       <c r="I103" s="2">
-        <v>38.11</v>
+        <v>15.12</v>
       </c>
       <c r="J103" s="2">
-        <v>0.419</v>
+        <v>0.166</v>
       </c>
       <c r="K103" t="s">
         <v>141</v>
@@ -4785,34 +4785,34 @@
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>15</v>
+        <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C104" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="D104" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E104">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="F104">
-        <v>6.05</v>
+        <v>7.03</v>
       </c>
       <c r="G104" s="1">
-        <v>0.721</v>
+        <v>0.6</v>
       </c>
       <c r="H104" t="s">
         <v>139</v>
       </c>
       <c r="I104" s="2">
-        <v>37.72</v>
+        <v>14.55</v>
       </c>
       <c r="J104" s="2">
-        <v>0.415</v>
+        <v>0.16</v>
       </c>
       <c r="K104" t="s">
         <v>141</v>
@@ -4823,34 +4823,34 @@
     </row>
     <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="B105" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="C105" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D105" t="s">
         <v>134</v>
       </c>
       <c r="E105">
-        <v>13.5</v>
+        <v>25.5</v>
       </c>
       <c r="F105">
-        <v>8.779999999999999</v>
+        <v>27.89</v>
       </c>
       <c r="G105" s="1">
-        <v>0.716</v>
+        <v>0.599</v>
       </c>
       <c r="H105" t="s">
         <v>140</v>
       </c>
       <c r="I105" s="2">
-        <v>36.78</v>
+        <v>14.3</v>
       </c>
       <c r="J105" s="2">
-        <v>0.405</v>
+        <v>0.157</v>
       </c>
       <c r="K105" t="s">
         <v>141</v>
@@ -4861,34 +4861,34 @@
     </row>
     <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>102</v>
+        <v>31</v>
       </c>
       <c r="B106" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C106" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="D106" t="s">
         <v>136</v>
       </c>
       <c r="E106">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="F106">
-        <v>4.92</v>
+        <v>7.97</v>
       </c>
       <c r="G106" s="1">
-        <v>0.716</v>
+        <v>0.598</v>
       </c>
       <c r="H106" t="s">
         <v>139</v>
       </c>
       <c r="I106" s="2">
-        <v>36.75</v>
+        <v>14.13</v>
       </c>
       <c r="J106" s="2">
-        <v>0.404</v>
+        <v>0.155</v>
       </c>
       <c r="K106" t="s">
         <v>141</v>
@@ -4899,34 +4899,34 @@
     </row>
     <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B107" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="C107" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D107" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E107">
-        <v>1.5</v>
+        <v>23.5</v>
       </c>
       <c r="F107">
-        <v>2.51</v>
+        <v>21.68</v>
       </c>
       <c r="G107" s="1">
-        <v>0.715</v>
+        <v>0.597</v>
       </c>
       <c r="H107" t="s">
         <v>139</v>
       </c>
       <c r="I107" s="2">
-        <v>36.59</v>
+        <v>13.98</v>
       </c>
       <c r="J107" s="2">
-        <v>0.403</v>
+        <v>0.154</v>
       </c>
       <c r="K107" t="s">
         <v>141</v>
@@ -4937,34 +4937,34 @@
     </row>
     <row r="108" spans="1:12">
       <c r="A108" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="B108" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C108" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D108" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E108">
-        <v>2.5</v>
+        <v>15.5</v>
       </c>
       <c r="F108">
-        <v>3.68</v>
+        <v>17.01</v>
       </c>
       <c r="G108" s="1">
-        <v>0.712</v>
+        <v>0.597</v>
       </c>
       <c r="H108" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I108" s="2">
-        <v>35.92</v>
+        <v>13.91</v>
       </c>
       <c r="J108" s="2">
-        <v>0.395</v>
+        <v>0.153</v>
       </c>
       <c r="K108" t="s">
         <v>141</v>
@@ -4975,34 +4975,34 @@
     </row>
     <row r="109" spans="1:12">
       <c r="A109" t="s">
-        <v>29</v>
+        <v>105</v>
       </c>
       <c r="B109" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C109" t="s">
         <v>117</v>
       </c>
       <c r="D109" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E109">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="F109">
-        <v>4.84</v>
+        <v>6.37</v>
       </c>
       <c r="G109" s="1">
-        <v>0.711</v>
+        <v>0.596</v>
       </c>
       <c r="H109" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I109" s="2">
-        <v>35.76</v>
+        <v>13.79</v>
       </c>
       <c r="J109" s="2">
-        <v>0.393</v>
+        <v>0.152</v>
       </c>
       <c r="K109" t="s">
         <v>141</v>
@@ -5013,34 +5013,34 @@
     </row>
     <row r="110" spans="1:12">
       <c r="A110" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="B110" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C110" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D110" t="s">
         <v>136</v>
       </c>
       <c r="E110">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="F110">
-        <v>3.57</v>
+        <v>7.03</v>
       </c>
       <c r="G110" s="1">
-        <v>0.699</v>
+        <v>0.596</v>
       </c>
       <c r="H110" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I110" s="2">
-        <v>33.42</v>
+        <v>13.69</v>
       </c>
       <c r="J110" s="2">
-        <v>0.368</v>
+        <v>0.151</v>
       </c>
       <c r="K110" t="s">
         <v>141</v>
@@ -5051,34 +5051,34 @@
     </row>
     <row r="111" spans="1:12">
       <c r="A111" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="B111" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C111" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D111" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E111">
-        <v>2.5</v>
+        <v>17.5</v>
       </c>
       <c r="F111">
-        <v>3.57</v>
+        <v>15.82</v>
       </c>
       <c r="G111" s="1">
-        <v>0.6919999999999999</v>
+        <v>0.595</v>
       </c>
       <c r="H111" t="s">
         <v>139</v>
       </c>
       <c r="I111" s="2">
-        <v>32.13</v>
+        <v>13.66</v>
       </c>
       <c r="J111" s="2">
-        <v>0.353</v>
+        <v>0.15</v>
       </c>
       <c r="K111" t="s">
         <v>141</v>
@@ -5089,34 +5089,34 @@
     </row>
     <row r="112" spans="1:12">
       <c r="A112" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="B112" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C112" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="D112" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E112">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="F112">
-        <v>2.4</v>
+        <v>8.68</v>
       </c>
       <c r="G112" s="1">
-        <v>0.6909999999999999</v>
+        <v>0.591</v>
       </c>
       <c r="H112" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I112" s="2">
-        <v>32.01</v>
+        <v>12.86</v>
       </c>
       <c r="J112" s="2">
-        <v>0.352</v>
+        <v>0.141</v>
       </c>
       <c r="K112" t="s">
         <v>141</v>
@@ -5127,10 +5127,10 @@
     </row>
     <row r="113" spans="1:12">
       <c r="A113" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="B113" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C113" t="s">
         <v>119</v>
@@ -5139,22 +5139,22 @@
         <v>136</v>
       </c>
       <c r="E113">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="F113">
-        <v>2.39</v>
+        <v>5.2</v>
       </c>
       <c r="G113" s="1">
-        <v>0.6889999999999999</v>
+        <v>0.591</v>
       </c>
       <c r="H113" t="s">
         <v>139</v>
       </c>
       <c r="I113" s="2">
-        <v>31.51</v>
+        <v>12.84</v>
       </c>
       <c r="J113" s="2">
-        <v>0.347</v>
+        <v>0.141</v>
       </c>
       <c r="K113" t="s">
         <v>141</v>
@@ -5165,34 +5165,34 @@
     </row>
     <row r="114" spans="1:12">
       <c r="A114" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="B114" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="C114" t="s">
         <v>126</v>
       </c>
       <c r="D114" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E114">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="F114">
-        <v>5.81</v>
+        <v>2.08</v>
       </c>
       <c r="G114" s="1">
-        <v>0.6879999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="H114" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I114" s="2">
-        <v>31.43</v>
+        <v>12.64</v>
       </c>
       <c r="J114" s="2">
-        <v>0.346</v>
+        <v>0.139</v>
       </c>
       <c r="K114" t="s">
         <v>141</v>
@@ -5203,34 +5203,34 @@
     </row>
     <row r="115" spans="1:12">
       <c r="A115" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B115" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C115" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D115" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E115">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="F115">
-        <v>5.9</v>
+        <v>8.67</v>
       </c>
       <c r="G115" s="1">
-        <v>0.6830000000000001</v>
+        <v>0.587</v>
       </c>
       <c r="H115" t="s">
         <v>140</v>
       </c>
       <c r="I115" s="2">
-        <v>30.4</v>
+        <v>12.15</v>
       </c>
       <c r="J115" s="2">
-        <v>0.334</v>
+        <v>0.134</v>
       </c>
       <c r="K115" t="s">
         <v>141</v>
@@ -5241,34 +5241,34 @@
     </row>
     <row r="116" spans="1:12">
       <c r="A116" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B116" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="C116" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D116" t="s">
         <v>134</v>
       </c>
       <c r="E116">
-        <v>9.5</v>
+        <v>18.5</v>
       </c>
       <c r="F116">
-        <v>12.81</v>
+        <v>20.28</v>
       </c>
       <c r="G116" s="1">
-        <v>0.681</v>
+        <v>0.587</v>
       </c>
       <c r="H116" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I116" s="2">
-        <v>30.03</v>
+        <v>12.06</v>
       </c>
       <c r="J116" s="2">
-        <v>0.33</v>
+        <v>0.133</v>
       </c>
       <c r="K116" t="s">
         <v>141</v>
@@ -5279,34 +5279,34 @@
     </row>
     <row r="117" spans="1:12">
       <c r="A117" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="B117" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C117" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="D117" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E117">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="F117">
-        <v>4.63</v>
+        <v>8.68</v>
       </c>
       <c r="G117" s="1">
-        <v>0.679</v>
+        <v>0.586</v>
       </c>
       <c r="H117" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I117" s="2">
-        <v>29.59</v>
+        <v>11.83</v>
       </c>
       <c r="J117" s="2">
-        <v>0.326</v>
+        <v>0.13</v>
       </c>
       <c r="K117" t="s">
         <v>141</v>
@@ -5317,34 +5317,34 @@
     </row>
     <row r="118" spans="1:12">
       <c r="A118" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B118" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C118" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D118" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E118">
-        <v>3.5</v>
+        <v>19.5</v>
       </c>
       <c r="F118">
-        <v>4.88</v>
+        <v>20.94</v>
       </c>
       <c r="G118" s="1">
-        <v>0.675</v>
+        <v>0.585</v>
       </c>
       <c r="H118" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I118" s="2">
-        <v>28.82</v>
+        <v>11.71</v>
       </c>
       <c r="J118" s="2">
-        <v>0.317</v>
+        <v>0.129</v>
       </c>
       <c r="K118" t="s">
         <v>141</v>
@@ -5355,34 +5355,34 @@
     </row>
     <row r="119" spans="1:12">
       <c r="A119" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B119" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C119" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D119" t="s">
         <v>136</v>
       </c>
       <c r="E119">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="F119">
-        <v>2.39</v>
+        <v>5.34</v>
       </c>
       <c r="G119" s="1">
-        <v>0.673</v>
+        <v>0.583</v>
       </c>
       <c r="H119" t="s">
         <v>140</v>
       </c>
       <c r="I119" s="2">
-        <v>28.55</v>
+        <v>11.21</v>
       </c>
       <c r="J119" s="2">
-        <v>0.314</v>
+        <v>0.123</v>
       </c>
       <c r="K119" t="s">
         <v>141</v>
@@ -5393,34 +5393,34 @@
     </row>
     <row r="120" spans="1:12">
       <c r="A120" t="s">
-        <v>39</v>
+        <v>110</v>
       </c>
       <c r="B120" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C120" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D120" t="s">
         <v>137</v>
       </c>
       <c r="E120">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="F120">
-        <v>5.93</v>
+        <v>5.21</v>
       </c>
       <c r="G120" s="1">
-        <v>0.673</v>
+        <v>0.581</v>
       </c>
       <c r="H120" t="s">
         <v>139</v>
       </c>
       <c r="I120" s="2">
-        <v>28.39</v>
+        <v>10.99</v>
       </c>
       <c r="J120" s="2">
-        <v>0.312</v>
+        <v>0.121</v>
       </c>
       <c r="K120" t="s">
         <v>141</v>
@@ -5431,34 +5431,34 @@
     </row>
     <row r="121" spans="1:12">
       <c r="A121" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="B121" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C121" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D121" t="s">
         <v>136</v>
       </c>
       <c r="E121">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="F121">
-        <v>3.79</v>
+        <v>2.36</v>
       </c>
       <c r="G121" s="1">
-        <v>0.666</v>
+        <v>0.581</v>
       </c>
       <c r="H121" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I121" s="2">
-        <v>27.2</v>
+        <v>10.93</v>
       </c>
       <c r="J121" s="2">
-        <v>0.299</v>
+        <v>0.12</v>
       </c>
       <c r="K121" t="s">
         <v>141</v>
@@ -5469,37 +5469,37 @@
     </row>
     <row r="122" spans="1:12">
       <c r="A122" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="B122" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C122" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D122" t="s">
         <v>136</v>
       </c>
       <c r="E122">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F122">
-        <v>2.27</v>
+        <v>2.37</v>
       </c>
       <c r="G122" s="1">
-        <v>0.661</v>
+        <v>0.578</v>
       </c>
       <c r="H122" t="s">
         <v>139</v>
       </c>
       <c r="I122" s="2">
-        <v>26.2</v>
+        <v>10.28</v>
       </c>
       <c r="J122" s="2">
-        <v>0.288</v>
+        <v>0.113</v>
       </c>
       <c r="K122" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L122" t="s">
         <v>145</v>
@@ -5507,37 +5507,37 @@
     </row>
     <row r="123" spans="1:12">
       <c r="A123" t="s">
-        <v>106</v>
+        <v>44</v>
       </c>
       <c r="B123" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C123" t="s">
         <v>121</v>
       </c>
       <c r="D123" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E123">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="F123">
-        <v>10.82</v>
+        <v>8.5</v>
       </c>
       <c r="G123" s="1">
-        <v>0.66</v>
+        <v>0.577</v>
       </c>
       <c r="H123" t="s">
         <v>140</v>
       </c>
       <c r="I123" s="2">
-        <v>25.98</v>
+        <v>10.11</v>
       </c>
       <c r="J123" s="2">
-        <v>0.286</v>
+        <v>0.111</v>
       </c>
       <c r="K123" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L123" t="s">
         <v>145</v>
@@ -5545,37 +5545,37 @@
     </row>
     <row r="124" spans="1:12">
       <c r="A124" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="B124" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C124" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D124" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E124">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="F124">
-        <v>6.56</v>
+        <v>4.05</v>
       </c>
       <c r="G124" s="1">
-        <v>0.655</v>
+        <v>0.576</v>
       </c>
       <c r="H124" t="s">
         <v>140</v>
       </c>
       <c r="I124" s="2">
-        <v>25.13</v>
+        <v>10.02</v>
       </c>
       <c r="J124" s="2">
-        <v>0.276</v>
+        <v>0.11</v>
       </c>
       <c r="K124" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L124" t="s">
         <v>145</v>
@@ -5583,37 +5583,37 @@
     </row>
     <row r="125" spans="1:12">
       <c r="A125" t="s">
-        <v>107</v>
+        <v>37</v>
       </c>
       <c r="B125" t="s">
+        <v>126</v>
+      </c>
+      <c r="C125" t="s">
         <v>130</v>
       </c>
-      <c r="C125" t="s">
-        <v>129</v>
-      </c>
       <c r="D125" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E125">
-        <v>29.5</v>
+        <v>1.5</v>
       </c>
       <c r="F125">
-        <v>34.35</v>
+        <v>1.92</v>
       </c>
       <c r="G125" s="1">
-        <v>0.643</v>
+        <v>0.572</v>
       </c>
       <c r="H125" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I125" s="2">
-        <v>22.81</v>
+        <v>9.17</v>
       </c>
       <c r="J125" s="2">
-        <v>0.251</v>
+        <v>0.101</v>
       </c>
       <c r="K125" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L125" t="s">
         <v>145</v>
@@ -5621,37 +5621,37 @@
     </row>
     <row r="126" spans="1:12">
       <c r="A126" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="B126" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C126" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D126" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E126">
-        <v>12.5</v>
+        <v>4.5</v>
       </c>
       <c r="F126">
-        <v>14.42</v>
+        <v>4.74</v>
       </c>
       <c r="G126" s="1">
-        <v>0.636</v>
+        <v>0.571</v>
       </c>
       <c r="H126" t="s">
         <v>139</v>
       </c>
       <c r="I126" s="2">
-        <v>21.4</v>
+        <v>8.93</v>
       </c>
       <c r="J126" s="2">
-        <v>0.235</v>
+        <v>0.098</v>
       </c>
       <c r="K126" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L126" t="s">
         <v>145</v>
@@ -5659,37 +5659,37 @@
     </row>
     <row r="127" spans="1:12">
       <c r="A127" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B127" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C127" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D127" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E127">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F127">
-        <v>4.47</v>
+        <v>3.08</v>
       </c>
       <c r="G127" s="1">
-        <v>0.635</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="H127" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I127" s="2">
-        <v>21.31</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="J127" s="2">
-        <v>0.234</v>
+        <v>0.093</v>
       </c>
       <c r="K127" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L127" t="s">
         <v>145</v>
@@ -5697,37 +5697,37 @@
     </row>
     <row r="128" spans="1:12">
       <c r="A128" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="B128" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C128" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D128" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E128">
-        <v>7.5</v>
+        <v>11.5</v>
       </c>
       <c r="F128">
-        <v>6.73</v>
+        <v>12.57</v>
       </c>
       <c r="G128" s="1">
-        <v>0.634</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="H128" t="s">
         <v>140</v>
       </c>
       <c r="I128" s="2">
-        <v>20.98</v>
+        <v>8.44</v>
       </c>
       <c r="J128" s="2">
-        <v>0.231</v>
+        <v>0.093</v>
       </c>
       <c r="K128" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L128" t="s">
         <v>145</v>
@@ -5735,37 +5735,37 @@
     </row>
     <row r="129" spans="1:12">
       <c r="A129" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B129" t="s">
         <v>129</v>
       </c>
       <c r="C129" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D129" t="s">
         <v>136</v>
       </c>
       <c r="E129">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="F129">
-        <v>2.39</v>
+        <v>7.53</v>
       </c>
       <c r="G129" s="1">
-        <v>0.627</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H129" t="s">
         <v>139</v>
       </c>
       <c r="I129" s="2">
-        <v>19.76</v>
+        <v>7.62</v>
       </c>
       <c r="J129" s="2">
-        <v>0.217</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="K129" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L129" t="s">
         <v>145</v>
@@ -5773,37 +5773,37 @@
     </row>
     <row r="130" spans="1:12">
       <c r="A130" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C130" t="s">
         <v>129</v>
       </c>
       <c r="D130" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E130">
-        <v>2.5</v>
+        <v>12.5</v>
       </c>
       <c r="F130">
-        <v>2.26</v>
+        <v>11.47</v>
       </c>
       <c r="G130" s="1">
-        <v>0.626</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="H130" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I130" s="2">
-        <v>19.51</v>
+        <v>7.2</v>
       </c>
       <c r="J130" s="2">
-        <v>0.215</v>
+        <v>0.079</v>
       </c>
       <c r="K130" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L130" t="s">
         <v>145</v>
@@ -5811,37 +5811,37 @@
     </row>
     <row r="131" spans="1:12">
       <c r="A131" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="B131" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C131" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D131" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E131">
-        <v>5.5</v>
+        <v>25.5</v>
       </c>
       <c r="F131">
-        <v>4.99</v>
+        <v>26.61</v>
       </c>
       <c r="G131" s="1">
-        <v>0.622</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="H131" t="s">
         <v>140</v>
       </c>
       <c r="I131" s="2">
-        <v>18.81</v>
+        <v>6.8</v>
       </c>
       <c r="J131" s="2">
-        <v>0.207</v>
+        <v>0.075</v>
       </c>
       <c r="K131" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L131" t="s">
         <v>145</v>
@@ -5849,37 +5849,37 @@
     </row>
     <row r="132" spans="1:12">
       <c r="A132" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="B132" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="C132" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D132" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E132">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="F132">
-        <v>5.37</v>
+        <v>2.45</v>
       </c>
       <c r="G132" s="1">
-        <v>0.622</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H132" t="s">
         <v>139</v>
       </c>
       <c r="I132" s="2">
-        <v>18.78</v>
+        <v>6.36</v>
       </c>
       <c r="J132" s="2">
-        <v>0.207</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K132" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L132" t="s">
         <v>145</v>
@@ -5887,37 +5887,37 @@
     </row>
     <row r="133" spans="1:12">
       <c r="A133" t="s">
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="B133" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C133" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D133" t="s">
         <v>135</v>
       </c>
       <c r="E133">
-        <v>18.5</v>
+        <v>29.5</v>
       </c>
       <c r="F133">
-        <v>21.01</v>
+        <v>31.05</v>
       </c>
       <c r="G133" s="1">
-        <v>0.622</v>
+        <v>0.555</v>
       </c>
       <c r="H133" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I133" s="2">
-        <v>18.67</v>
+        <v>5.87</v>
       </c>
       <c r="J133" s="2">
-        <v>0.205</v>
+        <v>0.065</v>
       </c>
       <c r="K133" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L133" t="s">
         <v>145</v>
@@ -5925,37 +5925,37 @@
     </row>
     <row r="134" spans="1:12">
       <c r="A134" t="s">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="B134" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="C134" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D134" t="s">
         <v>137</v>
       </c>
       <c r="E134">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="F134">
-        <v>6.48</v>
+        <v>1.86</v>
       </c>
       <c r="G134" s="1">
-        <v>0.621</v>
+        <v>0.553</v>
       </c>
       <c r="H134" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I134" s="2">
-        <v>18.57</v>
+        <v>5.64</v>
       </c>
       <c r="J134" s="2">
-        <v>0.204</v>
+        <v>0.062</v>
       </c>
       <c r="K134" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L134" t="s">
         <v>145</v>
@@ -5963,37 +5963,37 @@
     </row>
     <row r="135" spans="1:12">
       <c r="A135" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B135" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="C135" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D135" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E135">
-        <v>3.5</v>
+        <v>29.5</v>
       </c>
       <c r="F135">
-        <v>3.23</v>
+        <v>31.27</v>
       </c>
       <c r="G135" s="1">
-        <v>0.62</v>
+        <v>0.553</v>
       </c>
       <c r="H135" t="s">
         <v>140</v>
       </c>
       <c r="I135" s="2">
-        <v>18.42</v>
+        <v>5.63</v>
       </c>
       <c r="J135" s="2">
-        <v>0.203</v>
+        <v>0.062</v>
       </c>
       <c r="K135" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L135" t="s">
         <v>145</v>
@@ -6001,37 +6001,37 @@
     </row>
     <row r="136" spans="1:12">
       <c r="A136" t="s">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="B136" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C136" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D136" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E136">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F136">
-        <v>2.26</v>
+        <v>1.85</v>
       </c>
       <c r="G136" s="1">
-        <v>0.62</v>
+        <v>0.552</v>
       </c>
       <c r="H136" t="s">
         <v>140</v>
       </c>
       <c r="I136" s="2">
-        <v>18.3</v>
+        <v>5.47</v>
       </c>
       <c r="J136" s="2">
-        <v>0.201</v>
+        <v>0.06</v>
       </c>
       <c r="K136" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L136" t="s">
         <v>145</v>
@@ -6039,37 +6039,37 @@
     </row>
     <row r="137" spans="1:12">
       <c r="A137" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B137" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C137" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D137" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E137">
-        <v>9.5</v>
+        <v>5.5</v>
       </c>
       <c r="F137">
-        <v>10.71</v>
+        <v>5.48</v>
       </c>
       <c r="G137" s="1">
-        <v>0.62</v>
+        <v>0.552</v>
       </c>
       <c r="H137" t="s">
         <v>139</v>
       </c>
       <c r="I137" s="2">
-        <v>18.29</v>
+        <v>5.4</v>
       </c>
       <c r="J137" s="2">
-        <v>0.201</v>
+        <v>0.059</v>
       </c>
       <c r="K137" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L137" t="s">
         <v>145</v>
@@ -6077,37 +6077,37 @@
     </row>
     <row r="138" spans="1:12">
       <c r="A138" t="s">
-        <v>103</v>
+        <v>48</v>
       </c>
       <c r="B138" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C138" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D138" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E138">
-        <v>11.5</v>
+        <v>2.5</v>
       </c>
       <c r="F138">
-        <v>9.23</v>
+        <v>2.53</v>
       </c>
       <c r="G138" s="1">
-        <v>0.618</v>
+        <v>0.551</v>
       </c>
       <c r="H138" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I138" s="2">
-        <v>17.93</v>
+        <v>5.11</v>
       </c>
       <c r="J138" s="2">
-        <v>0.197</v>
+        <v>0.056</v>
       </c>
       <c r="K138" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L138" t="s">
         <v>145</v>
@@ -6115,37 +6115,37 @@
     </row>
     <row r="139" spans="1:12">
       <c r="A139" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="B139" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C139" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D139" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E139">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="F139">
-        <v>2.46</v>
+        <v>7.88</v>
       </c>
       <c r="G139" s="1">
-        <v>0.618</v>
+        <v>0.548</v>
       </c>
       <c r="H139" t="s">
         <v>140</v>
       </c>
       <c r="I139" s="2">
-        <v>17.93</v>
+        <v>4.57</v>
       </c>
       <c r="J139" s="2">
-        <v>0.197</v>
+        <v>0.05</v>
       </c>
       <c r="K139" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L139" t="s">
         <v>145</v>
@@ -6153,37 +6153,37 @@
     </row>
     <row r="140" spans="1:12">
       <c r="A140" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="B140" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C140" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D140" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E140">
-        <v>11.5</v>
+        <v>2.5</v>
       </c>
       <c r="F140">
-        <v>9.02</v>
+        <v>2.56</v>
       </c>
       <c r="G140" s="1">
-        <v>0.617</v>
+        <v>0.547</v>
       </c>
       <c r="H140" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I140" s="2">
-        <v>17.8</v>
+        <v>4.44</v>
       </c>
       <c r="J140" s="2">
-        <v>0.196</v>
+        <v>0.049</v>
       </c>
       <c r="K140" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L140" t="s">
         <v>145</v>
@@ -6191,37 +6191,37 @@
     </row>
     <row r="141" spans="1:12">
       <c r="A141" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B141" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="C141" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D141" t="s">
         <v>137</v>
       </c>
       <c r="E141">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="F141">
-        <v>5.95</v>
+        <v>8.34</v>
       </c>
       <c r="G141" s="1">
-        <v>0.615</v>
+        <v>0.546</v>
       </c>
       <c r="H141" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I141" s="2">
-        <v>17.38</v>
+        <v>4.15</v>
       </c>
       <c r="J141" s="2">
-        <v>0.191</v>
+        <v>0.046</v>
       </c>
       <c r="K141" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L141" t="s">
         <v>145</v>
@@ -6229,37 +6229,37 @@
     </row>
     <row r="142" spans="1:12">
       <c r="A142" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B142" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C142" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D142" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E142">
-        <v>12.5</v>
+        <v>4.5</v>
       </c>
       <c r="F142">
-        <v>10.65</v>
+        <v>4.9</v>
       </c>
       <c r="G142" s="1">
-        <v>0.611</v>
+        <v>0.541</v>
       </c>
       <c r="H142" t="s">
         <v>140</v>
       </c>
       <c r="I142" s="2">
-        <v>16.66</v>
+        <v>3.38</v>
       </c>
       <c r="J142" s="2">
-        <v>0.183</v>
+        <v>0.037</v>
       </c>
       <c r="K142" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L142" t="s">
         <v>145</v>
@@ -6267,10 +6267,10 @@
     </row>
     <row r="143" spans="1:12">
       <c r="A143" t="s">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="B143" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C143" t="s">
         <v>117</v>
@@ -6279,25 +6279,25 @@
         <v>137</v>
       </c>
       <c r="E143">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F143">
-        <v>4.21</v>
+        <v>2.8</v>
       </c>
       <c r="G143" s="1">
-        <v>0.607</v>
+        <v>0.539</v>
       </c>
       <c r="H143" t="s">
         <v>139</v>
       </c>
       <c r="I143" s="2">
-        <v>15.82</v>
+        <v>2.97</v>
       </c>
       <c r="J143" s="2">
-        <v>0.174</v>
+        <v>0.033</v>
       </c>
       <c r="K143" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L143" t="s">
         <v>145</v>
@@ -6305,37 +6305,37 @@
     </row>
     <row r="144" spans="1:12">
       <c r="A144" t="s">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c r="B144" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C144" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D144" t="s">
         <v>136</v>
       </c>
       <c r="E144">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F144">
-        <v>2.39</v>
+        <v>3.86</v>
       </c>
       <c r="G144" s="1">
-        <v>0.606</v>
+        <v>0.539</v>
       </c>
       <c r="H144" t="s">
         <v>140</v>
       </c>
       <c r="I144" s="2">
-        <v>15.77</v>
+        <v>2.96</v>
       </c>
       <c r="J144" s="2">
-        <v>0.173</v>
+        <v>0.033</v>
       </c>
       <c r="K144" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L144" t="s">
         <v>145</v>
@@ -6343,37 +6343,37 @@
     </row>
     <row r="145" spans="1:12">
       <c r="A145" t="s">
-        <v>24</v>
+        <v>112</v>
       </c>
       <c r="B145" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C145" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="D145" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E145">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="F145">
-        <v>5.48</v>
+        <v>8.01</v>
       </c>
       <c r="G145" s="1">
-        <v>0.606</v>
+        <v>0.536</v>
       </c>
       <c r="H145" t="s">
         <v>139</v>
       </c>
       <c r="I145" s="2">
-        <v>15.61</v>
+        <v>2.31</v>
       </c>
       <c r="J145" s="2">
-        <v>0.172</v>
+        <v>0.025</v>
       </c>
       <c r="K145" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L145" t="s">
         <v>145</v>
@@ -6381,37 +6381,37 @@
     </row>
     <row r="146" spans="1:12">
       <c r="A146" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="B146" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C146" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="D146" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E146">
-        <v>18.5</v>
+        <v>1.5</v>
       </c>
       <c r="F146">
-        <v>16.08</v>
+        <v>1.79</v>
       </c>
       <c r="G146" s="1">
-        <v>0.599</v>
+        <v>0.535</v>
       </c>
       <c r="H146" t="s">
         <v>140</v>
       </c>
       <c r="I146" s="2">
-        <v>14.43</v>
+        <v>2.13</v>
       </c>
       <c r="J146" s="2">
-        <v>0.159</v>
+        <v>0.023</v>
       </c>
       <c r="K146" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L146" t="s">
         <v>145</v>
@@ -6419,37 +6419,37 @@
     </row>
     <row r="147" spans="1:12">
       <c r="A147" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="B147" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C147" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D147" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E147">
-        <v>6.5</v>
+        <v>11.5</v>
       </c>
       <c r="F147">
-        <v>6.05</v>
+        <v>11.95</v>
       </c>
       <c r="G147" s="1">
-        <v>0.599</v>
+        <v>0.534</v>
       </c>
       <c r="H147" t="s">
         <v>140</v>
       </c>
       <c r="I147" s="2">
-        <v>14.35</v>
+        <v>1.89</v>
       </c>
       <c r="J147" s="2">
-        <v>0.158</v>
+        <v>0.021</v>
       </c>
       <c r="K147" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L147" t="s">
         <v>145</v>
@@ -6457,37 +6457,37 @@
     </row>
     <row r="148" spans="1:12">
       <c r="A148" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B148" t="s">
+        <v>117</v>
+      </c>
+      <c r="C148" t="s">
         <v>127</v>
       </c>
-      <c r="C148" t="s">
-        <v>118</v>
-      </c>
       <c r="D148" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E148">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="F148">
-        <v>7.54</v>
+        <v>9.81</v>
       </c>
       <c r="G148" s="1">
-        <v>0.597</v>
+        <v>0.531</v>
       </c>
       <c r="H148" t="s">
         <v>140</v>
       </c>
       <c r="I148" s="2">
-        <v>13.95</v>
+        <v>1.3</v>
       </c>
       <c r="J148" s="2">
-        <v>0.153</v>
+        <v>0.014</v>
       </c>
       <c r="K148" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L148" t="s">
         <v>145</v>
@@ -6495,37 +6495,37 @@
     </row>
     <row r="149" spans="1:12">
       <c r="A149" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B149" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C149" t="s">
         <v>130</v>
       </c>
       <c r="D149" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E149">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="F149">
-        <v>5.19</v>
+        <v>3.21</v>
       </c>
       <c r="G149" s="1">
-        <v>0.592</v>
+        <v>0.529</v>
       </c>
       <c r="H149" t="s">
         <v>139</v>
       </c>
       <c r="I149" s="2">
-        <v>13.03</v>
+        <v>0.91</v>
       </c>
       <c r="J149" s="2">
-        <v>0.143</v>
+        <v>0.01</v>
       </c>
       <c r="K149" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L149" t="s">
         <v>145</v>
@@ -6533,37 +6533,37 @@
     </row>
     <row r="150" spans="1:12">
       <c r="A150" t="s">
-        <v>105</v>
+        <v>49</v>
       </c>
       <c r="B150" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C150" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D150" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E150">
-        <v>12.5</v>
+        <v>4.5</v>
       </c>
       <c r="F150">
-        <v>14.14</v>
+        <v>4.52</v>
       </c>
       <c r="G150" s="1">
-        <v>0.584</v>
+        <v>0.528</v>
       </c>
       <c r="H150" t="s">
         <v>139</v>
       </c>
       <c r="I150" s="2">
-        <v>11.58</v>
+        <v>0.77</v>
       </c>
       <c r="J150" s="2">
-        <v>0.127</v>
+        <v>0.008</v>
       </c>
       <c r="K150" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L150" t="s">
         <v>145</v>
@@ -6571,37 +6571,37 @@
     </row>
     <row r="151" spans="1:12">
       <c r="A151" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="B151" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C151" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D151" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E151">
-        <v>3.5</v>
+        <v>25.5</v>
       </c>
       <c r="F151">
-        <v>4.08</v>
+        <v>26.29</v>
       </c>
       <c r="G151" s="1">
-        <v>0.583</v>
+        <v>0.526</v>
       </c>
       <c r="H151" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I151" s="2">
-        <v>11.27</v>
+        <v>0.34</v>
       </c>
       <c r="J151" s="2">
-        <v>0.124</v>
+        <v>0.004</v>
       </c>
       <c r="K151" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L151" t="s">
         <v>145</v>
@@ -6609,37 +6609,37 @@
     </row>
     <row r="152" spans="1:12">
       <c r="A152" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="B152" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C152" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D152" t="s">
         <v>136</v>
       </c>
       <c r="E152">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="F152">
-        <v>6.35</v>
+        <v>2.78</v>
       </c>
       <c r="G152" s="1">
-        <v>0.58</v>
+        <v>0.525</v>
       </c>
       <c r="H152" t="s">
         <v>140</v>
       </c>
       <c r="I152" s="2">
-        <v>10.68</v>
+        <v>0.21</v>
       </c>
       <c r="J152" s="2">
-        <v>0.117</v>
+        <v>0.002</v>
       </c>
       <c r="K152" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L152" t="s">
         <v>145</v>
@@ -6647,37 +6647,37 @@
     </row>
     <row r="153" spans="1:12">
       <c r="A153" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="B153" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C153" t="s">
         <v>128</v>
       </c>
       <c r="D153" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E153">
-        <v>3.5</v>
+        <v>22.5</v>
       </c>
       <c r="F153">
-        <v>4.41</v>
+        <v>21.95</v>
       </c>
       <c r="G153" s="1">
-        <v>0.579</v>
+        <v>0.521</v>
       </c>
       <c r="H153" t="s">
         <v>139</v>
       </c>
       <c r="I153" s="2">
-        <v>10.47</v>
+        <v>-0.62</v>
       </c>
       <c r="J153" s="2">
-        <v>0.115</v>
+        <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L153" t="s">
         <v>145</v>
@@ -6685,37 +6685,37 @@
     </row>
     <row r="154" spans="1:12">
       <c r="A154" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B154" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="C154" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D154" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E154">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="F154">
-        <v>4.33</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G154" s="1">
-        <v>0.578</v>
+        <v>0.516</v>
       </c>
       <c r="H154" t="s">
         <v>139</v>
       </c>
       <c r="I154" s="2">
-        <v>10.26</v>
+        <v>-1.53</v>
       </c>
       <c r="J154" s="2">
-        <v>0.113</v>
+        <v>0</v>
       </c>
       <c r="K154" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L154" t="s">
         <v>145</v>
@@ -6723,37 +6723,37 @@
     </row>
     <row r="155" spans="1:12">
       <c r="A155" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="B155" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C155" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D155" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E155">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="F155">
-        <v>6.27</v>
+        <v>3.74</v>
       </c>
       <c r="G155" s="1">
-        <v>0.577</v>
+        <v>0.515</v>
       </c>
       <c r="H155" t="s">
         <v>140</v>
       </c>
       <c r="I155" s="2">
-        <v>10.13</v>
+        <v>-1.66</v>
       </c>
       <c r="J155" s="2">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="K155" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L155" t="s">
         <v>145</v>
@@ -6761,37 +6761,37 @@
     </row>
     <row r="156" spans="1:12">
       <c r="A156" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="B156" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C156" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="D156" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E156">
-        <v>4.5</v>
+        <v>13.5</v>
       </c>
       <c r="F156">
-        <v>5.08</v>
+        <v>13.78</v>
       </c>
       <c r="G156" s="1">
-        <v>0.574</v>
+        <v>0.515</v>
       </c>
       <c r="H156" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I156" s="2">
-        <v>9.550000000000001</v>
+        <v>-1.69</v>
       </c>
       <c r="J156" s="2">
-        <v>0.105</v>
+        <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L156" t="s">
         <v>145</v>
@@ -6799,37 +6799,37 @@
     </row>
     <row r="157" spans="1:12">
       <c r="A157" t="s">
-        <v>112</v>
+        <v>18</v>
       </c>
       <c r="B157" t="s">
+        <v>114</v>
+      </c>
+      <c r="C157" t="s">
         <v>123</v>
       </c>
-      <c r="C157" t="s">
-        <v>117</v>
-      </c>
       <c r="D157" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E157">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="F157">
-        <v>11.23</v>
+        <v>16.71</v>
       </c>
       <c r="G157" s="1">
-        <v>0.571</v>
+        <v>0.515</v>
       </c>
       <c r="H157" t="s">
         <v>140</v>
       </c>
       <c r="I157" s="2">
-        <v>9</v>
+        <v>-1.74</v>
       </c>
       <c r="J157" s="2">
-        <v>0.099</v>
+        <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L157" t="s">
         <v>145</v>
@@ -6837,37 +6837,37 @@
     </row>
     <row r="158" spans="1:12">
       <c r="A158" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B158" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C158" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D158" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E158">
-        <v>12.5</v>
+        <v>3.5</v>
       </c>
       <c r="F158">
-        <v>11.43</v>
+        <v>3.76</v>
       </c>
       <c r="G158" s="1">
-        <v>0.569</v>
+        <v>0.514</v>
       </c>
       <c r="H158" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I158" s="2">
-        <v>8.640000000000001</v>
+        <v>-1.9</v>
       </c>
       <c r="J158" s="2">
-        <v>0.095</v>
+        <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L158" t="s">
         <v>145</v>
@@ -6875,37 +6875,37 @@
     </row>
     <row r="159" spans="1:12">
       <c r="A159" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="B159" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="C159" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D159" t="s">
         <v>136</v>
       </c>
       <c r="E159">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="F159">
-        <v>4.47</v>
+        <v>2.65</v>
       </c>
       <c r="G159" s="1">
-        <v>0.5679999999999999</v>
+        <v>0.506</v>
       </c>
       <c r="H159" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I159" s="2">
-        <v>8.43</v>
+        <v>-3.48</v>
       </c>
       <c r="J159" s="2">
-        <v>0.093</v>
+        <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L159" t="s">
         <v>145</v>
@@ -6913,37 +6913,37 @@
     </row>
     <row r="160" spans="1:12">
       <c r="A160" t="s">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="B160" t="s">
         <v>120</v>
       </c>
       <c r="C160" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="D160" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E160">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="F160">
-        <v>2.11</v>
+        <v>3.66</v>
       </c>
       <c r="G160" s="1">
-        <v>0.5659999999999999</v>
+        <v>0.502</v>
       </c>
       <c r="H160" t="s">
         <v>139</v>
       </c>
       <c r="I160" s="2">
-        <v>8.07</v>
+        <v>-4.24</v>
       </c>
       <c r="J160" s="2">
-        <v>0.089</v>
+        <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L160" t="s">
         <v>145</v>
@@ -6951,10 +6951,10 @@
     </row>
     <row r="161" spans="1:12">
       <c r="A161" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="B161" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C161" t="s">
         <v>130</v>
@@ -6963,25 +6963,25 @@
         <v>134</v>
       </c>
       <c r="E161">
-        <v>7.5</v>
+        <v>30.5</v>
       </c>
       <c r="F161">
-        <v>7.98</v>
+        <v>30.49</v>
       </c>
       <c r="G161" s="1">
-        <v>0.554</v>
+        <v>0.5</v>
       </c>
       <c r="H161" t="s">
         <v>139</v>
       </c>
       <c r="I161" s="2">
-        <v>5.69</v>
+        <v>-4.47</v>
       </c>
       <c r="J161" s="2">
-        <v>0.063</v>
+        <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L161" t="s">
         <v>145</v>
@@ -6989,424 +6989,44 @@
     </row>
     <row r="162" spans="1:12">
       <c r="A162" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="B162" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C162" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="D162" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E162">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="F162">
-        <v>4.95</v>
+        <v>2.68</v>
       </c>
       <c r="G162" s="1">
-        <v>0.551</v>
+        <v>0.5</v>
       </c>
       <c r="H162" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I162" s="2">
-        <v>5.16</v>
+        <v>-4.49</v>
       </c>
       <c r="J162" s="2">
-        <v>0.057</v>
+        <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L162" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="163" spans="1:12">
-      <c r="A163" t="s">
-        <v>63</v>
-      </c>
-      <c r="B163" t="s">
-        <v>128</v>
-      </c>
-      <c r="C163" t="s">
-        <v>114</v>
-      </c>
-      <c r="D163" t="s">
-        <v>136</v>
-      </c>
-      <c r="E163">
-        <v>1.5</v>
-      </c>
-      <c r="F163">
-        <v>1.95</v>
-      </c>
-      <c r="G163" s="1">
-        <v>0.548</v>
-      </c>
-      <c r="H163" t="s">
-        <v>139</v>
-      </c>
-      <c r="I163" s="2">
-        <v>4.68</v>
-      </c>
-      <c r="J163" s="2">
-        <v>0.052</v>
-      </c>
-      <c r="K163" t="s">
-        <v>142</v>
-      </c>
-      <c r="L163" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="164" spans="1:12">
-      <c r="A164" t="s">
-        <v>25</v>
-      </c>
-      <c r="B164" t="s">
-        <v>125</v>
-      </c>
-      <c r="C164" t="s">
-        <v>133</v>
-      </c>
-      <c r="D164" t="s">
-        <v>136</v>
-      </c>
-      <c r="E164">
-        <v>2.5</v>
-      </c>
-      <c r="F164">
-        <v>2.62</v>
-      </c>
-      <c r="G164" s="1">
-        <v>0.541</v>
-      </c>
-      <c r="H164" t="s">
-        <v>140</v>
-      </c>
-      <c r="I164" s="2">
-        <v>3.27</v>
-      </c>
-      <c r="J164" s="2">
-        <v>0.036</v>
-      </c>
-      <c r="K164" t="s">
-        <v>143</v>
-      </c>
-      <c r="L164" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="165" spans="1:12">
-      <c r="A165" t="s">
-        <v>108</v>
-      </c>
-      <c r="B165" t="s">
-        <v>129</v>
-      </c>
-      <c r="C165" t="s">
-        <v>130</v>
-      </c>
-      <c r="D165" t="s">
-        <v>137</v>
-      </c>
-      <c r="E165">
-        <v>4.5</v>
-      </c>
-      <c r="F165">
-        <v>4.77</v>
-      </c>
-      <c r="G165" s="1">
-        <v>0.536</v>
-      </c>
-      <c r="H165" t="s">
-        <v>140</v>
-      </c>
-      <c r="I165" s="2">
-        <v>2.31</v>
-      </c>
-      <c r="J165" s="2">
-        <v>0.025</v>
-      </c>
-      <c r="K165" t="s">
-        <v>143</v>
-      </c>
-      <c r="L165" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="166" spans="1:12">
-      <c r="A166" t="s">
-        <v>66</v>
-      </c>
-      <c r="B166" t="s">
-        <v>125</v>
-      </c>
-      <c r="C166" t="s">
-        <v>133</v>
-      </c>
-      <c r="D166" t="s">
-        <v>136</v>
-      </c>
-      <c r="E166">
-        <v>3.5</v>
-      </c>
-      <c r="F166">
-        <v>3.84</v>
-      </c>
-      <c r="G166" s="1">
-        <v>0.534</v>
-      </c>
-      <c r="H166" t="s">
-        <v>139</v>
-      </c>
-      <c r="I166" s="2">
-        <v>2.04</v>
-      </c>
-      <c r="J166" s="2">
-        <v>0.022</v>
-      </c>
-      <c r="K166" t="s">
-        <v>143</v>
-      </c>
-      <c r="L166" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="167" spans="1:12">
-      <c r="A167" t="s">
-        <v>83</v>
-      </c>
-      <c r="B167" t="s">
-        <v>124</v>
-      </c>
-      <c r="C167" t="s">
-        <v>125</v>
-      </c>
-      <c r="D167" t="s">
-        <v>134</v>
-      </c>
-      <c r="E167">
-        <v>13.5</v>
-      </c>
-      <c r="F167">
-        <v>12.94</v>
-      </c>
-      <c r="G167" s="1">
-        <v>0.534</v>
-      </c>
-      <c r="H167" t="s">
-        <v>140</v>
-      </c>
-      <c r="I167" s="2">
-        <v>1.91</v>
-      </c>
-      <c r="J167" s="2">
-        <v>0.021</v>
-      </c>
-      <c r="K167" t="s">
-        <v>143</v>
-      </c>
-      <c r="L167" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="168" spans="1:12">
-      <c r="A168" t="s">
-        <v>113</v>
-      </c>
-      <c r="B168" t="s">
-        <v>127</v>
-      </c>
-      <c r="C168" t="s">
-        <v>118</v>
-      </c>
-      <c r="D168" t="s">
-        <v>134</v>
-      </c>
-      <c r="E168">
-        <v>9.5</v>
-      </c>
-      <c r="F168">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="G168" s="1">
-        <v>0.532</v>
-      </c>
-      <c r="H168" t="s">
-        <v>139</v>
-      </c>
-      <c r="I168" s="2">
-        <v>1.54</v>
-      </c>
-      <c r="J168" s="2">
-        <v>0.017</v>
-      </c>
-      <c r="K168" t="s">
-        <v>143</v>
-      </c>
-      <c r="L168" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="169" spans="1:12">
-      <c r="A169" t="s">
-        <v>104</v>
-      </c>
-      <c r="B169" t="s">
-        <v>128</v>
-      </c>
-      <c r="C169" t="s">
-        <v>114</v>
-      </c>
-      <c r="D169" t="s">
-        <v>136</v>
-      </c>
-      <c r="E169">
-        <v>3.5</v>
-      </c>
-      <c r="F169">
-        <v>3.64</v>
-      </c>
-      <c r="G169" s="1">
-        <v>0.527</v>
-      </c>
-      <c r="H169" t="s">
-        <v>140</v>
-      </c>
-      <c r="I169" s="2">
-        <v>0.61</v>
-      </c>
-      <c r="J169" s="2">
-        <v>0.007</v>
-      </c>
-      <c r="K169" t="s">
-        <v>144</v>
-      </c>
-      <c r="L169" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="170" spans="1:12">
-      <c r="A170" t="s">
-        <v>40</v>
-      </c>
-      <c r="B170" t="s">
-        <v>114</v>
-      </c>
-      <c r="C170" t="s">
-        <v>128</v>
-      </c>
-      <c r="D170" t="s">
-        <v>134</v>
-      </c>
-      <c r="E170">
-        <v>22.5</v>
-      </c>
-      <c r="F170">
-        <v>21.88</v>
-      </c>
-      <c r="G170" s="1">
-        <v>0.523</v>
-      </c>
-      <c r="H170" t="s">
-        <v>140</v>
-      </c>
-      <c r="I170" s="2">
-        <v>-0.11</v>
-      </c>
-      <c r="J170" s="2">
-        <v>0</v>
-      </c>
-      <c r="K170" t="s">
-        <v>144</v>
-      </c>
-      <c r="L170" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="171" spans="1:12">
-      <c r="A171" t="s">
-        <v>64</v>
-      </c>
-      <c r="B171" t="s">
-        <v>115</v>
-      </c>
-      <c r="C171" t="s">
-        <v>131</v>
-      </c>
-      <c r="D171" t="s">
-        <v>134</v>
-      </c>
-      <c r="E171">
-        <v>7.5</v>
-      </c>
-      <c r="F171">
-        <v>7.74</v>
-      </c>
-      <c r="G171" s="1">
-        <v>0.518</v>
-      </c>
-      <c r="H171" t="s">
-        <v>139</v>
-      </c>
-      <c r="I171" s="2">
-        <v>-1.16</v>
-      </c>
-      <c r="J171" s="2">
-        <v>0</v>
-      </c>
-      <c r="K171" t="s">
-        <v>144</v>
-      </c>
-      <c r="L171" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="172" spans="1:12">
-      <c r="A172" t="s">
-        <v>19</v>
-      </c>
-      <c r="B172" t="s">
-        <v>121</v>
-      </c>
-      <c r="C172" t="s">
-        <v>132</v>
-      </c>
-      <c r="D172" t="s">
-        <v>134</v>
-      </c>
-      <c r="E172">
-        <v>29.5</v>
-      </c>
-      <c r="F172">
-        <v>29.5</v>
-      </c>
-      <c r="G172" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="H172" t="s">
-        <v>139</v>
-      </c>
-      <c r="I172" s="2">
-        <v>-4.53</v>
-      </c>
-      <c r="J172" s="2">
-        <v>0</v>
-      </c>
-      <c r="K172" t="s">
-        <v>144</v>
-      </c>
-      <c r="L172" t="s">
-        <v>145</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="K2:K172">
+  <conditionalFormatting sqref="K2:K162">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="S Tier">
       <formula>NOT(ISERROR(SEARCH("S Tier",K2)))</formula>
     </cfRule>

--- a/output/processed_props.xlsx
+++ b/output/processed_props.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="146">
   <si>
     <t>Player</t>
   </si>
@@ -55,360 +55,360 @@
     <t>Joan Beringer</t>
   </si>
   <si>
+    <t>Jonas Valanciunas</t>
+  </si>
+  <si>
+    <t>Joel Embiid</t>
+  </si>
+  <si>
+    <t>RJ Barrett</t>
+  </si>
+  <si>
+    <t>Tim Hardaway Jr.</t>
+  </si>
+  <si>
+    <t>Ayo Dosunmu</t>
+  </si>
+  <si>
+    <t>Brandon Ingram</t>
+  </si>
+  <si>
+    <t>Jalen Johnson</t>
+  </si>
+  <si>
+    <t>Derrick White</t>
+  </si>
+  <si>
+    <t>Desmond Bane</t>
+  </si>
+  <si>
+    <t>Aaron Wiggins</t>
+  </si>
+  <si>
+    <t>CJ McCollum</t>
+  </si>
+  <si>
+    <t>Chet Holmgren</t>
+  </si>
+  <si>
+    <t>Brandon Miller</t>
+  </si>
+  <si>
+    <t>Tyus Jones</t>
+  </si>
+  <si>
+    <t>Dyson Daniels</t>
+  </si>
+  <si>
+    <t>Jared McCain</t>
+  </si>
+  <si>
+    <t>Tyrese Maxey</t>
+  </si>
+  <si>
+    <t>Bilal Coulibaly</t>
+  </si>
+  <si>
+    <t>Kawhi Leonard</t>
+  </si>
+  <si>
+    <t>Ryan Kalkbrenner</t>
+  </si>
+  <si>
+    <t>Jock Landale</t>
+  </si>
+  <si>
+    <t>Nikola Vucevic</t>
+  </si>
+  <si>
+    <t>LaMelo Ball</t>
+  </si>
+  <si>
+    <t>Jaylen Brown</t>
+  </si>
+  <si>
+    <t>Cam Thomas</t>
+  </si>
+  <si>
+    <t>Brook Lopez</t>
+  </si>
+  <si>
+    <t>Jaylon Tyson</t>
+  </si>
+  <si>
+    <t>Donovan Mitchell</t>
+  </si>
+  <si>
+    <t>Bub Carrington</t>
+  </si>
+  <si>
+    <t>Kyshawn George</t>
+  </si>
+  <si>
+    <t>Kristaps Porzingis</t>
+  </si>
+  <si>
+    <t>Immanuel Quickley</t>
+  </si>
+  <si>
+    <t>Anthony Edwards</t>
+  </si>
+  <si>
+    <t>Grant Williams</t>
+  </si>
+  <si>
+    <t>Neemias Queta</t>
+  </si>
+  <si>
+    <t>Kris Dunn</t>
+  </si>
+  <si>
+    <t>Al Horford</t>
+  </si>
+  <si>
+    <t>Jalen Suggs</t>
+  </si>
+  <si>
+    <t>Kyle Kuzma</t>
+  </si>
+  <si>
     <t>Nic Claxton</t>
   </si>
   <si>
+    <t>Egor Demin</t>
+  </si>
+  <si>
+    <t>Jaden McDaniels</t>
+  </si>
+  <si>
+    <t>Draymond Green</t>
+  </si>
+  <si>
+    <t>Anthony Black</t>
+  </si>
+  <si>
+    <t>Kon Knueppel</t>
+  </si>
+  <si>
+    <t>Brandin Podziemski</t>
+  </si>
+  <si>
     <t>Tristan Vukcevic</t>
   </si>
   <si>
-    <t>Jared McCain</t>
-  </si>
-  <si>
-    <t>Aaron Wiggins</t>
-  </si>
-  <si>
-    <t>Brandin Podziemski</t>
+    <t>De'Anthony Melton</t>
+  </si>
+  <si>
+    <t>Nolan Traore</t>
+  </si>
+  <si>
+    <t>Julius Randle</t>
+  </si>
+  <si>
+    <t>Evan Mobley</t>
+  </si>
+  <si>
+    <t>Sam Hauser</t>
+  </si>
+  <si>
+    <t>Klay Thompson</t>
+  </si>
+  <si>
+    <t>Daniel Gafford</t>
+  </si>
+  <si>
+    <t>Bennedict Mathurin</t>
+  </si>
+  <si>
+    <t>Jarrett Allen</t>
+  </si>
+  <si>
+    <t>Dennis Schroder</t>
+  </si>
+  <si>
+    <t>Kevin Porter Jr.</t>
+  </si>
+  <si>
+    <t>Jamal Shead</t>
+  </si>
+  <si>
+    <t>Ryan Rollins</t>
+  </si>
+  <si>
+    <t>Sam Merrill</t>
+  </si>
+  <si>
+    <t>Onyeka Okongwu</t>
+  </si>
+  <si>
+    <t>LeBron James</t>
   </si>
   <si>
     <t>Naz Reid</t>
   </si>
   <si>
+    <t>Corey Kispert</t>
+  </si>
+  <si>
+    <t>Payton Pritchard</t>
+  </si>
+  <si>
+    <t>Cason Wallace</t>
+  </si>
+  <si>
+    <t>Wendell Carter Jr.</t>
+  </si>
+  <si>
+    <t>VJ Edgecombe</t>
+  </si>
+  <si>
+    <t>Jamal Murray</t>
+  </si>
+  <si>
     <t>Julian Strawther</t>
   </si>
   <si>
-    <t>Brandon Miller</t>
-  </si>
-  <si>
-    <t>Wendell Carter Jr.</t>
-  </si>
-  <si>
-    <t>Ryan Kalkbrenner</t>
-  </si>
-  <si>
-    <t>Kawhi Leonard</t>
+    <t>Austin Reaves</t>
+  </si>
+  <si>
+    <t>Isaiah Joe</t>
+  </si>
+  <si>
+    <t>Naji Marshall</t>
+  </si>
+  <si>
+    <t>Paolo Banchero</t>
+  </si>
+  <si>
+    <t>Derrick Jones Jr.</t>
+  </si>
+  <si>
+    <t>Marcus Smart</t>
+  </si>
+  <si>
+    <t>Donte DiVincenzo</t>
+  </si>
+  <si>
+    <t>Luka Doncic</t>
+  </si>
+  <si>
+    <t>Dominick Barlow</t>
+  </si>
+  <si>
+    <t>Nickeil Alexander-Walker</t>
+  </si>
+  <si>
+    <t>Gui Santos</t>
+  </si>
+  <si>
+    <t>Myles Turner</t>
+  </si>
+  <si>
+    <t>James Harden</t>
+  </si>
+  <si>
+    <t>Rui Hachimura</t>
+  </si>
+  <si>
+    <t>Noah Clowney</t>
   </si>
   <si>
     <t>Quentin Grimes</t>
   </si>
   <si>
-    <t>Nolan Traore</t>
-  </si>
-  <si>
-    <t>Kyshawn George</t>
-  </si>
-  <si>
-    <t>Brook Lopez</t>
-  </si>
-  <si>
-    <t>Bub Carrington</t>
-  </si>
-  <si>
-    <t>Tyus Jones</t>
-  </si>
-  <si>
-    <t>Jonas Valanciunas</t>
-  </si>
-  <si>
-    <t>Joel Embiid</t>
-  </si>
-  <si>
     <t>Pat Spencer</t>
   </si>
   <si>
-    <t>Derrick White</t>
-  </si>
-  <si>
-    <t>Tyrese Maxey</t>
-  </si>
-  <si>
-    <t>Anthony Edwards</t>
-  </si>
-  <si>
-    <t>Draymond Green</t>
+    <t>Nikola Jokic</t>
+  </si>
+  <si>
+    <t>Michael Porter Jr.</t>
+  </si>
+  <si>
+    <t>Isaiah Hartenstein</t>
+  </si>
+  <si>
+    <t>Collin Murray-Boyles</t>
+  </si>
+  <si>
+    <t>Deandre Ayton</t>
   </si>
   <si>
     <t>AJ Green</t>
   </si>
   <si>
-    <t>Jarrett Allen</t>
-  </si>
-  <si>
-    <t>Dyson Daniels</t>
-  </si>
-  <si>
-    <t>Payton Pritchard</t>
-  </si>
-  <si>
-    <t>VJ Edgecombe</t>
-  </si>
-  <si>
-    <t>Julius Randle</t>
-  </si>
-  <si>
-    <t>Tim Hardaway Jr.</t>
-  </si>
-  <si>
-    <t>Kris Dunn</t>
-  </si>
-  <si>
-    <t>Jalen Johnson</t>
-  </si>
-  <si>
-    <t>Jaylen Brown</t>
-  </si>
-  <si>
-    <t>Derrick Jones Jr.</t>
-  </si>
-  <si>
-    <t>Bilal Coulibaly</t>
-  </si>
-  <si>
-    <t>Austin Reaves</t>
-  </si>
-  <si>
-    <t>RJ Barrett</t>
-  </si>
-  <si>
-    <t>Chet Holmgren</t>
-  </si>
-  <si>
-    <t>Donte DiVincenzo</t>
-  </si>
-  <si>
-    <t>Immanuel Quickley</t>
-  </si>
-  <si>
-    <t>LaMelo Ball</t>
-  </si>
-  <si>
-    <t>Rui Hachimura</t>
-  </si>
-  <si>
-    <t>Isaiah Joe</t>
-  </si>
-  <si>
-    <t>Jock Landale</t>
-  </si>
-  <si>
-    <t>Marcus Smart</t>
-  </si>
-  <si>
-    <t>Deandre Ayton</t>
-  </si>
-  <si>
-    <t>James Harden</t>
-  </si>
-  <si>
-    <t>Jamal Shead</t>
-  </si>
-  <si>
-    <t>CJ McCollum</t>
-  </si>
-  <si>
-    <t>Naji Marshall</t>
-  </si>
-  <si>
-    <t>Ayo Dosunmu</t>
-  </si>
-  <si>
-    <t>Sam Hauser</t>
-  </si>
-  <si>
-    <t>Dominick Barlow</t>
-  </si>
-  <si>
-    <t>Evan Mobley</t>
-  </si>
-  <si>
-    <t>Desmond Bane</t>
-  </si>
-  <si>
-    <t>Kon Knueppel</t>
+    <t>Baylor Scheierman</t>
+  </si>
+  <si>
+    <t>Zaccharie Risacher</t>
+  </si>
+  <si>
+    <t>Max Christie</t>
+  </si>
+  <si>
+    <t>Christian Braun</t>
   </si>
   <si>
     <t>Tre Johnson</t>
   </si>
   <si>
-    <t>Cam Thomas</t>
-  </si>
-  <si>
-    <t>Ryan Rollins</t>
-  </si>
-  <si>
-    <t>Baylor Scheierman</t>
-  </si>
-  <si>
-    <t>Nickeil Alexander-Walker</t>
-  </si>
-  <si>
-    <t>Donovan Mitchell</t>
-  </si>
-  <si>
-    <t>Dennis Schroder</t>
-  </si>
-  <si>
-    <t>Brandon Ingram</t>
-  </si>
-  <si>
-    <t>Nikola Jokic</t>
-  </si>
-  <si>
-    <t>Egor Demin</t>
-  </si>
-  <si>
-    <t>Neemias Queta</t>
-  </si>
-  <si>
-    <t>Paolo Banchero</t>
-  </si>
-  <si>
-    <t>Onyeka Okongwu</t>
-  </si>
-  <si>
-    <t>Jamal Murray</t>
-  </si>
-  <si>
-    <t>Jaylon Tyson</t>
-  </si>
-  <si>
-    <t>LeBron James</t>
-  </si>
-  <si>
-    <t>Grant Williams</t>
-  </si>
-  <si>
-    <t>Jaden McDaniels</t>
-  </si>
-  <si>
-    <t>Michael Porter Jr.</t>
-  </si>
-  <si>
-    <t>Al Horford</t>
-  </si>
-  <si>
-    <t>Kristaps Porzingis</t>
-  </si>
-  <si>
-    <t>Bennedict Mathurin</t>
-  </si>
-  <si>
-    <t>Noah Clowney</t>
-  </si>
-  <si>
-    <t>Cason Wallace</t>
-  </si>
-  <si>
-    <t>Collin Murray-Boyles</t>
-  </si>
-  <si>
-    <t>Gui Santos</t>
-  </si>
-  <si>
     <t>Moses Moody</t>
   </si>
   <si>
-    <t>Anthony Black</t>
-  </si>
-  <si>
-    <t>Zaccharie Risacher</t>
-  </si>
-  <si>
-    <t>Sam Merrill</t>
-  </si>
-  <si>
-    <t>Myles Turner</t>
-  </si>
-  <si>
-    <t>Nikola Vucevic</t>
-  </si>
-  <si>
-    <t>De'Anthony Melton</t>
-  </si>
-  <si>
-    <t>Daniel Gafford</t>
-  </si>
-  <si>
-    <t>Max Christie</t>
-  </si>
-  <si>
     <t>Dean Wade</t>
   </si>
   <si>
-    <t>Klay Thompson</t>
-  </si>
-  <si>
-    <t>Kyle Kuzma</t>
-  </si>
-  <si>
-    <t>Christian Braun</t>
-  </si>
-  <si>
-    <t>Kevin Porter Jr.</t>
-  </si>
-  <si>
-    <t>Jalen Suggs</t>
-  </si>
-  <si>
-    <t>Isaiah Hartenstein</t>
-  </si>
-  <si>
-    <t>Corey Kispert</t>
-  </si>
-  <si>
-    <t>Luka Doncic</t>
-  </si>
-  <si>
     <t>MIN</t>
   </si>
   <si>
+    <t>DEN</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>BOS</t>
+  </si>
+  <si>
+    <t>ORL</t>
+  </si>
+  <si>
+    <t>OKC</t>
+  </si>
+  <si>
+    <t>CHA</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>WSH</t>
+  </si>
+  <si>
+    <t>LAC</t>
+  </si>
+  <si>
+    <t>MIL</t>
+  </si>
+  <si>
+    <t>CLE</t>
+  </si>
+  <si>
+    <t>GS</t>
+  </si>
+  <si>
     <t>BKN</t>
   </si>
   <si>
-    <t>WSH</t>
-  </si>
-  <si>
-    <t>OKC</t>
-  </si>
-  <si>
-    <t>GS</t>
-  </si>
-  <si>
-    <t>DEN</t>
-  </si>
-  <si>
-    <t>CHA</t>
-  </si>
-  <si>
-    <t>ORL</t>
-  </si>
-  <si>
-    <t>LAC</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>BOS</t>
-  </si>
-  <si>
-    <t>MIL</t>
-  </si>
-  <si>
-    <t>CLE</t>
-  </si>
-  <si>
-    <t>ATL</t>
-  </si>
-  <si>
     <t>LAL</t>
   </si>
   <si>
-    <t>TOR</t>
-  </si>
-  <si>
     <t>GSW</t>
   </si>
   <si>
@@ -418,16 +418,16 @@
     <t>IND</t>
   </si>
   <si>
+    <t>REB</t>
+  </si>
+  <si>
+    <t>AST</t>
+  </si>
+  <si>
+    <t>PTS</t>
+  </si>
+  <si>
     <t>PRA</t>
-  </si>
-  <si>
-    <t>PTS</t>
-  </si>
-  <si>
-    <t>REB</t>
-  </si>
-  <si>
-    <t>AST</t>
   </si>
   <si>
     <t>RA</t>
@@ -854,7 +854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L162"/>
+  <dimension ref="A1:L164"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
@@ -864,7 +864,8 @@
     <col min="6" max="6" width="9.7109375" customWidth="1"/>
     <col min="7" max="7" width="9.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="9.7109375" customWidth="1"/>
-    <col min="9" max="10" width="9.7109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="9.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" style="2" customWidth="1"/>
     <col min="11" max="11" width="10.7109375" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" customWidth="1"/>
   </cols>
@@ -915,28 +916,28 @@
         <v>114</v>
       </c>
       <c r="C2" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D2" t="s">
         <v>134</v>
       </c>
       <c r="E2">
-        <v>14.5</v>
+        <v>5.5</v>
       </c>
       <c r="F2">
-        <v>3.83</v>
+        <v>2.98</v>
       </c>
       <c r="G2" s="1">
-        <v>0.994</v>
+        <v>0.918</v>
       </c>
       <c r="H2" t="s">
         <v>139</v>
       </c>
       <c r="I2" s="2">
-        <v>89.67</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="J2" s="2">
-        <v>0.986</v>
+        <v>0.1035</v>
       </c>
       <c r="K2" t="s">
         <v>141</v>
@@ -953,28 +954,28 @@
         <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D3" t="s">
         <v>135</v>
       </c>
       <c r="E3">
-        <v>10.5</v>
+        <v>1.5</v>
       </c>
       <c r="F3">
-        <v>17.32</v>
+        <v>0.64</v>
       </c>
       <c r="G3" s="1">
-        <v>0.952</v>
+        <v>0.848</v>
       </c>
       <c r="H3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I3" s="2">
-        <v>81.66</v>
+        <v>61.8</v>
       </c>
       <c r="J3" s="2">
-        <v>0.898</v>
+        <v>0.17</v>
       </c>
       <c r="K3" t="s">
         <v>141</v>
@@ -991,28 +992,28 @@
         <v>116</v>
       </c>
       <c r="C4" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D4" t="s">
         <v>136</v>
       </c>
       <c r="E4">
-        <v>5.5</v>
+        <v>26.5</v>
       </c>
       <c r="F4">
-        <v>3.48</v>
+        <v>31.32</v>
       </c>
       <c r="G4" s="1">
-        <v>0.86</v>
+        <v>0.778</v>
       </c>
       <c r="H4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I4" s="2">
-        <v>64.23999999999999</v>
+        <v>48.61</v>
       </c>
       <c r="J4" s="2">
-        <v>0.707</v>
+        <v>0.1337</v>
       </c>
       <c r="K4" t="s">
         <v>141</v>
@@ -1029,28 +1030,28 @@
         <v>117</v>
       </c>
       <c r="C5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D5" t="s">
         <v>137</v>
       </c>
       <c r="E5">
-        <v>2.5</v>
+        <v>27.5</v>
       </c>
       <c r="F5">
-        <v>1.34</v>
+        <v>23.21</v>
       </c>
       <c r="G5" s="1">
-        <v>0.835</v>
+        <v>0.77</v>
       </c>
       <c r="H5" t="s">
         <v>139</v>
       </c>
       <c r="I5" s="2">
-        <v>59.47</v>
+        <v>46.94</v>
       </c>
       <c r="J5" s="2">
-        <v>0.654</v>
+        <v>0.0645</v>
       </c>
       <c r="K5" t="s">
         <v>141</v>
@@ -1064,31 +1065,31 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D6" t="s">
         <v>135</v>
       </c>
       <c r="E6">
-        <v>14.5</v>
+        <v>1.5</v>
       </c>
       <c r="F6">
-        <v>9.039999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="G6" s="1">
-        <v>0.831</v>
+        <v>0.758</v>
       </c>
       <c r="H6" t="s">
         <v>139</v>
       </c>
       <c r="I6" s="2">
-        <v>58.57</v>
+        <v>44.65</v>
       </c>
       <c r="J6" s="2">
-        <v>0.644</v>
+        <v>0.1228</v>
       </c>
       <c r="K6" t="s">
         <v>141</v>
@@ -1102,31 +1103,31 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E7">
-        <v>15.5</v>
+        <v>3.5</v>
       </c>
       <c r="F7">
-        <v>11.1</v>
+        <v>2.35</v>
       </c>
       <c r="G7" s="1">
-        <v>0.828</v>
+        <v>0.757</v>
       </c>
       <c r="H7" t="s">
         <v>139</v>
       </c>
       <c r="I7" s="2">
-        <v>57.99</v>
+        <v>44.46</v>
       </c>
       <c r="J7" s="2">
-        <v>0.638</v>
+        <v>0.0611</v>
       </c>
       <c r="K7" t="s">
         <v>141</v>
@@ -1140,31 +1141,31 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E8">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="F8">
-        <v>6.47</v>
+        <v>2.46</v>
       </c>
       <c r="G8" s="1">
-        <v>0.796</v>
+        <v>0.749</v>
       </c>
       <c r="H8" t="s">
         <v>139</v>
       </c>
       <c r="I8" s="2">
-        <v>51.9</v>
+        <v>42.94</v>
       </c>
       <c r="J8" s="2">
-        <v>0.571</v>
+        <v>0.1181</v>
       </c>
       <c r="K8" t="s">
         <v>141</v>
@@ -1178,31 +1179,31 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E9">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="F9">
-        <v>1.55</v>
+        <v>5.41</v>
       </c>
       <c r="G9" s="1">
-        <v>0.795</v>
+        <v>0.743</v>
       </c>
       <c r="H9" t="s">
         <v>139</v>
       </c>
       <c r="I9" s="2">
-        <v>51.82</v>
+        <v>41.76</v>
       </c>
       <c r="J9" s="2">
-        <v>0.57</v>
+        <v>0.1148</v>
       </c>
       <c r="K9" t="s">
         <v>141</v>
@@ -1216,31 +1217,31 @@
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C10" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D10" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E10">
-        <v>33.5</v>
+        <v>27.5</v>
       </c>
       <c r="F10">
-        <v>27.25</v>
+        <v>23.54</v>
       </c>
       <c r="G10" s="1">
-        <v>0.793</v>
+        <v>0.738</v>
       </c>
       <c r="H10" t="s">
         <v>139</v>
       </c>
       <c r="I10" s="2">
-        <v>51.37</v>
+        <v>40.96</v>
       </c>
       <c r="J10" s="2">
-        <v>0.5649999999999999</v>
+        <v>0.0563</v>
       </c>
       <c r="K10" t="s">
         <v>141</v>
@@ -1254,31 +1255,31 @@
         <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C11" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D11" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E11">
-        <v>19.5</v>
+        <v>25.5</v>
       </c>
       <c r="F11">
-        <v>14.02</v>
+        <v>30.11</v>
       </c>
       <c r="G11" s="1">
-        <v>0.78</v>
+        <v>0.728</v>
       </c>
       <c r="H11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I11" s="2">
-        <v>48.93</v>
+        <v>38.94</v>
       </c>
       <c r="J11" s="2">
-        <v>0.538</v>
+        <v>0.1071</v>
       </c>
       <c r="K11" t="s">
         <v>141</v>
@@ -1292,31 +1293,31 @@
         <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C12" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E12">
-        <v>7.5</v>
+        <v>20.5</v>
       </c>
       <c r="F12">
-        <v>5.74</v>
+        <v>16.5</v>
       </c>
       <c r="G12" s="1">
-        <v>0.779</v>
+        <v>0.725</v>
       </c>
       <c r="H12" t="s">
         <v>139</v>
       </c>
       <c r="I12" s="2">
-        <v>48.71</v>
+        <v>38.48</v>
       </c>
       <c r="J12" s="2">
-        <v>0.536</v>
+        <v>0.0529</v>
       </c>
       <c r="K12" t="s">
         <v>141</v>
@@ -1330,31 +1331,31 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E13">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F13">
-        <v>3.05</v>
+        <v>2.58</v>
       </c>
       <c r="G13" s="1">
-        <v>0.779</v>
+        <v>0.725</v>
       </c>
       <c r="H13" t="s">
         <v>139</v>
       </c>
       <c r="I13" s="2">
-        <v>48.71</v>
+        <v>38.37</v>
       </c>
       <c r="J13" s="2">
-        <v>0.536</v>
+        <v>0.1055</v>
       </c>
       <c r="K13" t="s">
         <v>141</v>
@@ -1368,31 +1369,31 @@
         <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C14" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="D14" t="s">
         <v>134</v>
       </c>
       <c r="E14">
-        <v>15.5</v>
+        <v>8.5</v>
       </c>
       <c r="F14">
-        <v>20.18</v>
+        <v>6.51</v>
       </c>
       <c r="G14" s="1">
-        <v>0.779</v>
+        <v>0.722</v>
       </c>
       <c r="H14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I14" s="2">
-        <v>48.69</v>
+        <v>37.93</v>
       </c>
       <c r="J14" s="2">
-        <v>0.536</v>
+        <v>0.1043</v>
       </c>
       <c r="K14" t="s">
         <v>141</v>
@@ -1406,31 +1407,31 @@
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C15" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E15">
-        <v>10.5</v>
+        <v>33.5</v>
       </c>
       <c r="F15">
-        <v>15.31</v>
+        <v>29</v>
       </c>
       <c r="G15" s="1">
-        <v>0.777</v>
+        <v>0.722</v>
       </c>
       <c r="H15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I15" s="2">
-        <v>48.43</v>
+        <v>37.8</v>
       </c>
       <c r="J15" s="2">
-        <v>0.533</v>
+        <v>0.1039</v>
       </c>
       <c r="K15" t="s">
         <v>141</v>
@@ -1444,31 +1445,31 @@
         <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C16" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="D16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E16">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="F16">
-        <v>8.16</v>
+        <v>5.47</v>
       </c>
       <c r="G16" s="1">
-        <v>0.774</v>
+        <v>0.72</v>
       </c>
       <c r="H16" t="s">
         <v>139</v>
       </c>
       <c r="I16" s="2">
-        <v>47.84</v>
+        <v>37.5</v>
       </c>
       <c r="J16" s="2">
-        <v>0.526</v>
+        <v>0.0516</v>
       </c>
       <c r="K16" t="s">
         <v>141</v>
@@ -1482,31 +1483,31 @@
         <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C17" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E17">
-        <v>8.5</v>
+        <v>23.5</v>
       </c>
       <c r="F17">
-        <v>6.37</v>
+        <v>19.05</v>
       </c>
       <c r="G17" s="1">
-        <v>0.773</v>
+        <v>0.72</v>
       </c>
       <c r="H17" t="s">
         <v>139</v>
       </c>
       <c r="I17" s="2">
-        <v>47.6</v>
+        <v>37.49</v>
       </c>
       <c r="J17" s="2">
-        <v>0.524</v>
+        <v>0.1031</v>
       </c>
       <c r="K17" t="s">
         <v>141</v>
@@ -1520,31 +1521,31 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C18" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="D18" t="s">
         <v>135</v>
       </c>
       <c r="E18">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="F18">
-        <v>8.52</v>
+        <v>1.85</v>
       </c>
       <c r="G18" s="1">
-        <v>0.764</v>
+        <v>0.718</v>
       </c>
       <c r="H18" t="s">
         <v>139</v>
       </c>
       <c r="I18" s="2">
-        <v>45.84</v>
+        <v>37.05</v>
       </c>
       <c r="J18" s="2">
-        <v>0.504</v>
+        <v>0.0509</v>
       </c>
       <c r="K18" t="s">
         <v>141</v>
@@ -1558,31 +1559,31 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="D19" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E19">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="F19">
-        <v>3.86</v>
+        <v>5.01</v>
       </c>
       <c r="G19" s="1">
-        <v>0.76</v>
+        <v>0.716</v>
       </c>
       <c r="H19" t="s">
         <v>139</v>
       </c>
       <c r="I19" s="2">
-        <v>45.12</v>
+        <v>36.78</v>
       </c>
       <c r="J19" s="2">
-        <v>0.496</v>
+        <v>0.1011</v>
       </c>
       <c r="K19" t="s">
         <v>141</v>
@@ -1596,31 +1597,31 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C20" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="D20" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E20">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="F20">
-        <v>0.93</v>
+        <v>12.87</v>
       </c>
       <c r="G20" s="1">
-        <v>0.76</v>
+        <v>0.714</v>
       </c>
       <c r="H20" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I20" s="2">
-        <v>45.09</v>
+        <v>36.24</v>
       </c>
       <c r="J20" s="2">
-        <v>0.496</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="K20" t="s">
         <v>141</v>
@@ -1634,31 +1635,31 @@
         <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C21" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D21" t="s">
         <v>135</v>
       </c>
       <c r="E21">
-        <v>26.5</v>
+        <v>4.5</v>
       </c>
       <c r="F21">
-        <v>30.94</v>
+        <v>3.51</v>
       </c>
       <c r="G21" s="1">
-        <v>0.76</v>
+        <v>0.712</v>
       </c>
       <c r="H21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I21" s="2">
-        <v>45.05</v>
+        <v>35.99</v>
       </c>
       <c r="J21" s="2">
-        <v>0.496</v>
+        <v>0.0495</v>
       </c>
       <c r="K21" t="s">
         <v>141</v>
@@ -1672,31 +1673,31 @@
         <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C22" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="D22" t="s">
         <v>134</v>
       </c>
       <c r="E22">
-        <v>20.5</v>
+        <v>7.5</v>
       </c>
       <c r="F22">
-        <v>13.29</v>
+        <v>6.24</v>
       </c>
       <c r="G22" s="1">
-        <v>0.756</v>
+        <v>0.711</v>
       </c>
       <c r="H22" t="s">
         <v>139</v>
       </c>
       <c r="I22" s="2">
-        <v>44.26</v>
+        <v>35.67</v>
       </c>
       <c r="J22" s="2">
-        <v>0.487</v>
+        <v>0.049</v>
       </c>
       <c r="K22" t="s">
         <v>141</v>
@@ -1710,7 +1711,7 @@
         <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C23" t="s">
         <v>129</v>
@@ -1719,22 +1720,22 @@
         <v>135</v>
       </c>
       <c r="E23">
-        <v>18.5</v>
+        <v>1.5</v>
       </c>
       <c r="F23">
-        <v>14.25</v>
+        <v>1.17</v>
       </c>
       <c r="G23" s="1">
-        <v>0.749</v>
+        <v>0.709</v>
       </c>
       <c r="H23" t="s">
         <v>139</v>
       </c>
       <c r="I23" s="2">
-        <v>42.92</v>
+        <v>35.35</v>
       </c>
       <c r="J23" s="2">
-        <v>0.472</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="K23" t="s">
         <v>141</v>
@@ -1745,34 +1746,34 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C24" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D24" t="s">
         <v>135</v>
       </c>
       <c r="E24">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="F24">
-        <v>7.67</v>
+        <v>1.96</v>
       </c>
       <c r="G24" s="1">
-        <v>0.746</v>
+        <v>0.697</v>
       </c>
       <c r="H24" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I24" s="2">
-        <v>42.45</v>
+        <v>33.1</v>
       </c>
       <c r="J24" s="2">
-        <v>0.467</v>
+        <v>0.0455</v>
       </c>
       <c r="K24" t="s">
         <v>141</v>
@@ -1783,34 +1784,34 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="D25" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E25">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="F25">
-        <v>4.68</v>
+        <v>6.33</v>
       </c>
       <c r="G25" s="1">
-        <v>0.744</v>
+        <v>0.697</v>
       </c>
       <c r="H25" t="s">
         <v>139</v>
       </c>
       <c r="I25" s="2">
-        <v>42.06</v>
+        <v>33.07</v>
       </c>
       <c r="J25" s="2">
-        <v>0.463</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="K25" t="s">
         <v>141</v>
@@ -1821,34 +1822,34 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C26" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="D26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E26">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="F26">
-        <v>5.13</v>
+        <v>3.66</v>
       </c>
       <c r="G26" s="1">
-        <v>0.743</v>
+        <v>0.694</v>
       </c>
       <c r="H26" t="s">
         <v>139</v>
       </c>
       <c r="I26" s="2">
-        <v>41.86</v>
+        <v>32.53</v>
       </c>
       <c r="J26" s="2">
-        <v>0.46</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="K26" t="s">
         <v>141</v>
@@ -1859,34 +1860,34 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C27" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D27" t="s">
         <v>135</v>
       </c>
       <c r="E27">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="F27">
-        <v>4.75</v>
+        <v>2.08</v>
       </c>
       <c r="G27" s="1">
-        <v>0.742</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H27" t="s">
         <v>139</v>
       </c>
       <c r="I27" s="2">
-        <v>41.68</v>
+        <v>32.18</v>
       </c>
       <c r="J27" s="2">
-        <v>0.458</v>
+        <v>0.0442</v>
       </c>
       <c r="K27" t="s">
         <v>141</v>
@@ -1897,34 +1898,34 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C28" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D28" t="s">
         <v>134</v>
       </c>
       <c r="E28">
-        <v>14.5</v>
+        <v>5.5</v>
       </c>
       <c r="F28">
-        <v>10.01</v>
+        <v>4.48</v>
       </c>
       <c r="G28" s="1">
-        <v>0.736</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H28" t="s">
         <v>139</v>
       </c>
       <c r="I28" s="2">
-        <v>40.47</v>
+        <v>32.02</v>
       </c>
       <c r="J28" s="2">
-        <v>0.445</v>
+        <v>0.044</v>
       </c>
       <c r="K28" t="s">
         <v>141</v>
@@ -1935,34 +1936,34 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29" t="s">
         <v>127</v>
       </c>
       <c r="C29" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D29" t="s">
         <v>135</v>
       </c>
       <c r="E29">
-        <v>13.5</v>
+        <v>1.5</v>
       </c>
       <c r="F29">
-        <v>19.84</v>
+        <v>1.39</v>
       </c>
       <c r="G29" s="1">
-        <v>0.735</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="H29" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I29" s="2">
-        <v>40.26</v>
+        <v>31.94</v>
       </c>
       <c r="J29" s="2">
-        <v>0.443</v>
+        <v>0.0439</v>
       </c>
       <c r="K29" t="s">
         <v>141</v>
@@ -1973,34 +1974,34 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C30" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D30" t="s">
         <v>134</v>
       </c>
       <c r="E30">
-        <v>23.5</v>
+        <v>3.5</v>
       </c>
       <c r="F30">
-        <v>18.74</v>
+        <v>2.83</v>
       </c>
       <c r="G30" s="1">
-        <v>0.734</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="H30" t="s">
         <v>139</v>
       </c>
       <c r="I30" s="2">
-        <v>40.13</v>
+        <v>30.83</v>
       </c>
       <c r="J30" s="2">
-        <v>0.441</v>
+        <v>0.0848</v>
       </c>
       <c r="K30" t="s">
         <v>141</v>
@@ -2011,34 +2012,34 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C31" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D31" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E31">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="F31">
-        <v>23.06</v>
+        <v>9.17</v>
       </c>
       <c r="G31" s="1">
-        <v>0.729</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="H31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I31" s="2">
-        <v>39.24</v>
+        <v>30.75</v>
       </c>
       <c r="J31" s="2">
-        <v>0.432</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="K31" t="s">
         <v>141</v>
@@ -2049,34 +2050,34 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C32" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D32" t="s">
         <v>134</v>
       </c>
       <c r="E32">
-        <v>24.5</v>
+        <v>3.5</v>
       </c>
       <c r="F32">
-        <v>29.69</v>
+        <v>3.04</v>
       </c>
       <c r="G32" s="1">
-        <v>0.729</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H32" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I32" s="2">
-        <v>39.23</v>
+        <v>30.33</v>
       </c>
       <c r="J32" s="2">
-        <v>0.432</v>
+        <v>0.0417</v>
       </c>
       <c r="K32" t="s">
         <v>141</v>
@@ -2087,34 +2088,34 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="C33" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D33" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E33">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="F33">
-        <v>7.01</v>
+        <v>1.31</v>
       </c>
       <c r="G33" s="1">
-        <v>0.728</v>
+        <v>0.68</v>
       </c>
       <c r="H33" t="s">
         <v>139</v>
       </c>
       <c r="I33" s="2">
-        <v>39.02</v>
+        <v>29.91</v>
       </c>
       <c r="J33" s="2">
-        <v>0.429</v>
+        <v>0.0411</v>
       </c>
       <c r="K33" t="s">
         <v>141</v>
@@ -2125,34 +2126,34 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B34" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C34" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D34" t="s">
         <v>137</v>
       </c>
       <c r="E34">
-        <v>1.5</v>
+        <v>28.5</v>
       </c>
       <c r="F34">
-        <v>1.05</v>
+        <v>25.25</v>
       </c>
       <c r="G34" s="1">
-        <v>0.726</v>
+        <v>0.679</v>
       </c>
       <c r="H34" t="s">
         <v>139</v>
       </c>
       <c r="I34" s="2">
-        <v>38.66</v>
+        <v>29.69</v>
       </c>
       <c r="J34" s="2">
-        <v>0.425</v>
+        <v>0.0408</v>
       </c>
       <c r="K34" t="s">
         <v>141</v>
@@ -2163,34 +2164,34 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C35" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D35" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E35">
-        <v>10.5</v>
+        <v>3.5</v>
       </c>
       <c r="F35">
-        <v>8.57</v>
+        <v>2.86</v>
       </c>
       <c r="G35" s="1">
-        <v>0.726</v>
+        <v>0.676</v>
       </c>
       <c r="H35" t="s">
         <v>139</v>
       </c>
       <c r="I35" s="2">
-        <v>38.62</v>
+        <v>29.02</v>
       </c>
       <c r="J35" s="2">
-        <v>0.425</v>
+        <v>0.0798</v>
       </c>
       <c r="K35" t="s">
         <v>141</v>
@@ -2201,34 +2202,34 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B36" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C36" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D36" t="s">
         <v>135</v>
       </c>
       <c r="E36">
-        <v>23.5</v>
+        <v>2.5</v>
       </c>
       <c r="F36">
-        <v>16.56</v>
+        <v>2.05</v>
       </c>
       <c r="G36" s="1">
-        <v>0.724</v>
+        <v>0.674</v>
       </c>
       <c r="H36" t="s">
         <v>139</v>
       </c>
       <c r="I36" s="2">
-        <v>38.17</v>
+        <v>28.75</v>
       </c>
       <c r="J36" s="2">
-        <v>0.42</v>
+        <v>0.0395</v>
       </c>
       <c r="K36" t="s">
         <v>141</v>
@@ -2239,34 +2240,34 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B37" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C37" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D37" t="s">
         <v>135</v>
       </c>
       <c r="E37">
-        <v>28.5</v>
+        <v>1.5</v>
       </c>
       <c r="F37">
-        <v>21.82</v>
+        <v>1.34</v>
       </c>
       <c r="G37" s="1">
-        <v>0.724</v>
+        <v>0.672</v>
       </c>
       <c r="H37" t="s">
         <v>139</v>
       </c>
       <c r="I37" s="2">
-        <v>38.15</v>
+        <v>28.3</v>
       </c>
       <c r="J37" s="2">
-        <v>0.42</v>
+        <v>0.0389</v>
       </c>
       <c r="K37" t="s">
         <v>141</v>
@@ -2277,34 +2278,34 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B38" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C38" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D38" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E38">
         <v>4.5</v>
       </c>
       <c r="F38">
-        <v>3.54</v>
+        <v>3.76</v>
       </c>
       <c r="G38" s="1">
-        <v>0.717</v>
+        <v>0.671</v>
       </c>
       <c r="H38" t="s">
         <v>139</v>
       </c>
       <c r="I38" s="2">
-        <v>36.97</v>
+        <v>28.12</v>
       </c>
       <c r="J38" s="2">
-        <v>0.407</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="K38" t="s">
         <v>141</v>
@@ -2315,34 +2316,34 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B39" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="C39" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D39" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E39">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="F39">
-        <v>12.89</v>
+        <v>13.46</v>
       </c>
       <c r="G39" s="1">
-        <v>0.716</v>
+        <v>0.671</v>
       </c>
       <c r="H39" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I39" s="2">
-        <v>36.6</v>
+        <v>28.08</v>
       </c>
       <c r="J39" s="2">
-        <v>0.403</v>
+        <v>0.0386</v>
       </c>
       <c r="K39" t="s">
         <v>141</v>
@@ -2353,10 +2354,10 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B40" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C40" t="s">
         <v>125</v>
@@ -2365,22 +2366,22 @@
         <v>134</v>
       </c>
       <c r="E40">
-        <v>29.5</v>
+        <v>3.5</v>
       </c>
       <c r="F40">
-        <v>35.43</v>
+        <v>3.02</v>
       </c>
       <c r="G40" s="1">
-        <v>0.714</v>
+        <v>0.668</v>
       </c>
       <c r="H40" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I40" s="2">
-        <v>36.34</v>
+        <v>27.48</v>
       </c>
       <c r="J40" s="2">
-        <v>0.4</v>
+        <v>0.0378</v>
       </c>
       <c r="K40" t="s">
         <v>141</v>
@@ -2391,34 +2392,34 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B41" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C41" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D41" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E41">
-        <v>27.5</v>
+        <v>2.5</v>
       </c>
       <c r="F41">
-        <v>24.23</v>
+        <v>2.43</v>
       </c>
       <c r="G41" s="1">
-        <v>0.713</v>
+        <v>0.665</v>
       </c>
       <c r="H41" t="s">
         <v>139</v>
       </c>
       <c r="I41" s="2">
-        <v>36.18</v>
+        <v>27.04</v>
       </c>
       <c r="J41" s="2">
-        <v>0.398</v>
+        <v>0.0372</v>
       </c>
       <c r="K41" t="s">
         <v>141</v>
@@ -2429,34 +2430,34 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B42" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="C42" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D42" t="s">
         <v>136</v>
       </c>
       <c r="E42">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="F42">
-        <v>6.65</v>
+        <v>12.25</v>
       </c>
       <c r="G42" s="1">
-        <v>0.713</v>
+        <v>0.665</v>
       </c>
       <c r="H42" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I42" s="2">
-        <v>36.04</v>
+        <v>26.9</v>
       </c>
       <c r="J42" s="2">
-        <v>0.396</v>
+        <v>0.074</v>
       </c>
       <c r="K42" t="s">
         <v>141</v>
@@ -2467,34 +2468,34 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B43" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="C43" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D43" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E43">
-        <v>9.5</v>
+        <v>3.5</v>
       </c>
       <c r="F43">
-        <v>8.109999999999999</v>
+        <v>2.94</v>
       </c>
       <c r="G43" s="1">
-        <v>0.712</v>
+        <v>0.662</v>
       </c>
       <c r="H43" t="s">
         <v>139</v>
       </c>
       <c r="I43" s="2">
-        <v>35.97</v>
+        <v>26.29</v>
       </c>
       <c r="J43" s="2">
-        <v>0.396</v>
+        <v>0.0723</v>
       </c>
       <c r="K43" t="s">
         <v>141</v>
@@ -2505,34 +2506,34 @@
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B44" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="C44" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="D44" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E44">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="F44">
-        <v>5.35</v>
+        <v>3.83</v>
       </c>
       <c r="G44" s="1">
-        <v>0.71</v>
+        <v>0.661</v>
       </c>
       <c r="H44" t="s">
         <v>139</v>
       </c>
       <c r="I44" s="2">
-        <v>35.49</v>
+        <v>26.23</v>
       </c>
       <c r="J44" s="2">
-        <v>0.39</v>
+        <v>0.0361</v>
       </c>
       <c r="K44" t="s">
         <v>141</v>
@@ -2543,34 +2544,34 @@
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B45" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C45" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="D45" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E45">
-        <v>12.5</v>
+        <v>4.5</v>
       </c>
       <c r="F45">
-        <v>10.78</v>
+        <v>3.83</v>
       </c>
       <c r="G45" s="1">
-        <v>0.709</v>
+        <v>0.659</v>
       </c>
       <c r="H45" t="s">
         <v>139</v>
       </c>
       <c r="I45" s="2">
-        <v>35.39</v>
+        <v>25.81</v>
       </c>
       <c r="J45" s="2">
-        <v>0.389</v>
+        <v>0.0355</v>
       </c>
       <c r="K45" t="s">
         <v>141</v>
@@ -2581,10 +2582,10 @@
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B46" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C46" t="s">
         <v>125</v>
@@ -2593,22 +2594,22 @@
         <v>136</v>
       </c>
       <c r="E46">
-        <v>2.5</v>
+        <v>15.5</v>
       </c>
       <c r="F46">
-        <v>3.66</v>
+        <v>13.04</v>
       </c>
       <c r="G46" s="1">
-        <v>0.708</v>
+        <v>0.655</v>
       </c>
       <c r="H46" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I46" s="2">
-        <v>35.12</v>
+        <v>25.07</v>
       </c>
       <c r="J46" s="2">
-        <v>0.386</v>
+        <v>0.0689</v>
       </c>
       <c r="K46" t="s">
         <v>141</v>
@@ -2619,34 +2620,34 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B47" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C47" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D47" t="s">
         <v>136</v>
       </c>
       <c r="E47">
-        <v>3.5</v>
+        <v>20.5</v>
       </c>
       <c r="F47">
-        <v>2.73</v>
+        <v>23.28</v>
       </c>
       <c r="G47" s="1">
-        <v>0.708</v>
+        <v>0.653</v>
       </c>
       <c r="H47" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I47" s="2">
-        <v>35.09</v>
+        <v>24.62</v>
       </c>
       <c r="J47" s="2">
-        <v>0.386</v>
+        <v>0.0677</v>
       </c>
       <c r="K47" t="s">
         <v>141</v>
@@ -2657,7 +2658,7 @@
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B48" t="s">
         <v>128</v>
@@ -2666,25 +2667,25 @@
         <v>115</v>
       </c>
       <c r="D48" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E48">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="F48">
-        <v>5.16</v>
+        <v>3.11</v>
       </c>
       <c r="G48" s="1">
-        <v>0.704</v>
+        <v>0.65</v>
       </c>
       <c r="H48" t="s">
         <v>139</v>
       </c>
       <c r="I48" s="2">
-        <v>34.48</v>
+        <v>24.11</v>
       </c>
       <c r="J48" s="2">
-        <v>0.379</v>
+        <v>0.0332</v>
       </c>
       <c r="K48" t="s">
         <v>141</v>
@@ -2695,34 +2696,34 @@
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B49" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C49" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D49" t="s">
         <v>134</v>
       </c>
       <c r="E49">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="F49">
-        <v>15.13</v>
+        <v>4.82</v>
       </c>
       <c r="G49" s="1">
-        <v>0.703</v>
+        <v>0.648</v>
       </c>
       <c r="H49" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I49" s="2">
-        <v>34.19</v>
+        <v>23.62</v>
       </c>
       <c r="J49" s="2">
-        <v>0.376</v>
+        <v>0.0325</v>
       </c>
       <c r="K49" t="s">
         <v>141</v>
@@ -2733,34 +2734,34 @@
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B50" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C50" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D50" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E50">
-        <v>9.5</v>
+        <v>19.5</v>
       </c>
       <c r="F50">
-        <v>13.21</v>
+        <v>21.98</v>
       </c>
       <c r="G50" s="1">
-        <v>0.701</v>
+        <v>0.644</v>
       </c>
       <c r="H50" t="s">
         <v>140</v>
       </c>
       <c r="I50" s="2">
-        <v>33.77</v>
+        <v>23.02</v>
       </c>
       <c r="J50" s="2">
-        <v>0.371</v>
+        <v>0.0316</v>
       </c>
       <c r="K50" t="s">
         <v>141</v>
@@ -2771,34 +2772,34 @@
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B51" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C51" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D51" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E51">
-        <v>12.5</v>
+        <v>4.5</v>
       </c>
       <c r="F51">
-        <v>13.7</v>
+        <v>6.05</v>
       </c>
       <c r="G51" s="1">
-        <v>0.697</v>
+        <v>0.644</v>
       </c>
       <c r="H51" t="s">
         <v>140</v>
       </c>
       <c r="I51" s="2">
-        <v>33.07</v>
+        <v>22.97</v>
       </c>
       <c r="J51" s="2">
-        <v>0.364</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="K51" t="s">
         <v>141</v>
@@ -2809,34 +2810,34 @@
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="B52" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C52" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D52" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E52">
-        <v>14.5</v>
+        <v>3.5</v>
       </c>
       <c r="F52">
-        <v>11.32</v>
+        <v>3.02</v>
       </c>
       <c r="G52" s="1">
-        <v>0.6919999999999999</v>
+        <v>0.642</v>
       </c>
       <c r="H52" t="s">
         <v>139</v>
       </c>
       <c r="I52" s="2">
-        <v>32.2</v>
+        <v>22.57</v>
       </c>
       <c r="J52" s="2">
-        <v>0.354</v>
+        <v>0.031</v>
       </c>
       <c r="K52" t="s">
         <v>141</v>
@@ -2850,31 +2851,31 @@
         <v>62</v>
       </c>
       <c r="B53" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C53" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D53" t="s">
         <v>136</v>
       </c>
       <c r="E53">
-        <v>3.5</v>
+        <v>21.5</v>
       </c>
       <c r="F53">
-        <v>2.79</v>
+        <v>18.43</v>
       </c>
       <c r="G53" s="1">
-        <v>0.6919999999999999</v>
+        <v>0.642</v>
       </c>
       <c r="H53" t="s">
         <v>139</v>
       </c>
       <c r="I53" s="2">
-        <v>32.09</v>
+        <v>22.56</v>
       </c>
       <c r="J53" s="2">
-        <v>0.353</v>
+        <v>0.031</v>
       </c>
       <c r="K53" t="s">
         <v>141</v>
@@ -2888,31 +2889,31 @@
         <v>63</v>
       </c>
       <c r="B54" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C54" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D54" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E54">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="F54">
-        <v>8.880000000000001</v>
+        <v>2.31</v>
       </c>
       <c r="G54" s="1">
-        <v>0.6909999999999999</v>
+        <v>0.642</v>
       </c>
       <c r="H54" t="s">
         <v>139</v>
       </c>
       <c r="I54" s="2">
-        <v>31.83</v>
+        <v>22.51</v>
       </c>
       <c r="J54" s="2">
-        <v>0.35</v>
+        <v>0.031</v>
       </c>
       <c r="K54" t="s">
         <v>141</v>
@@ -2926,31 +2927,31 @@
         <v>64</v>
       </c>
       <c r="B55" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C55" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="D55" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E55">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="F55">
-        <v>9.33</v>
+        <v>17.05</v>
       </c>
       <c r="G55" s="1">
-        <v>0.6899999999999999</v>
+        <v>0.641</v>
       </c>
       <c r="H55" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I55" s="2">
-        <v>31.74</v>
+        <v>22.31</v>
       </c>
       <c r="J55" s="2">
-        <v>0.349</v>
+        <v>0.0307</v>
       </c>
       <c r="K55" t="s">
         <v>141</v>
@@ -2964,31 +2965,31 @@
         <v>65</v>
       </c>
       <c r="B56" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C56" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D56" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E56">
-        <v>9.5</v>
+        <v>17.5</v>
       </c>
       <c r="F56">
-        <v>12.08</v>
+        <v>15</v>
       </c>
       <c r="G56" s="1">
-        <v>0.6860000000000001</v>
+        <v>0.641</v>
       </c>
       <c r="H56" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I56" s="2">
-        <v>30.98</v>
+        <v>22.31</v>
       </c>
       <c r="J56" s="2">
-        <v>0.341</v>
+        <v>0.0307</v>
       </c>
       <c r="K56" t="s">
         <v>141</v>
@@ -3005,28 +3006,28 @@
         <v>123</v>
       </c>
       <c r="C57" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D57" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E57">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="F57">
-        <v>5.37</v>
+        <v>6.69</v>
       </c>
       <c r="G57" s="1">
-        <v>0.6820000000000001</v>
+        <v>0.638</v>
       </c>
       <c r="H57" t="s">
         <v>139</v>
       </c>
       <c r="I57" s="2">
-        <v>30.29</v>
+        <v>21.78</v>
       </c>
       <c r="J57" s="2">
-        <v>0.333</v>
+        <v>0.03</v>
       </c>
       <c r="K57" t="s">
         <v>141</v>
@@ -3040,31 +3041,31 @@
         <v>67</v>
       </c>
       <c r="B58" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C58" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D58" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E58">
-        <v>21.5</v>
+        <v>2.5</v>
       </c>
       <c r="F58">
-        <v>25.01</v>
+        <v>3.28</v>
       </c>
       <c r="G58" s="1">
-        <v>0.68</v>
+        <v>0.637</v>
       </c>
       <c r="H58" t="s">
         <v>140</v>
       </c>
       <c r="I58" s="2">
-        <v>29.89</v>
+        <v>21.67</v>
       </c>
       <c r="J58" s="2">
-        <v>0.329</v>
+        <v>0.0596</v>
       </c>
       <c r="K58" t="s">
         <v>141</v>
@@ -3075,34 +3076,34 @@
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="B59" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C59" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D59" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E59">
-        <v>15.5</v>
+        <v>25.5</v>
       </c>
       <c r="F59">
-        <v>20.3</v>
+        <v>30.41</v>
       </c>
       <c r="G59" s="1">
-        <v>0.68</v>
+        <v>0.637</v>
       </c>
       <c r="H59" t="s">
         <v>140</v>
       </c>
       <c r="I59" s="2">
-        <v>29.78</v>
+        <v>21.65</v>
       </c>
       <c r="J59" s="2">
-        <v>0.328</v>
+        <v>0.0595</v>
       </c>
       <c r="K59" t="s">
         <v>141</v>
@@ -3113,34 +3114,34 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B60" t="s">
+        <v>127</v>
+      </c>
+      <c r="C60" t="s">
         <v>121</v>
       </c>
-      <c r="C60" t="s">
-        <v>122</v>
-      </c>
       <c r="D60" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E60">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="F60">
-        <v>6.7</v>
+        <v>3.05</v>
       </c>
       <c r="G60" s="1">
-        <v>0.68</v>
+        <v>0.636</v>
       </c>
       <c r="H60" t="s">
         <v>139</v>
       </c>
       <c r="I60" s="2">
-        <v>29.76</v>
+        <v>21.38</v>
       </c>
       <c r="J60" s="2">
-        <v>0.327</v>
+        <v>0.0588</v>
       </c>
       <c r="K60" t="s">
         <v>141</v>
@@ -3151,34 +3152,34 @@
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B61" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C61" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="D61" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E61">
-        <v>20.5</v>
+        <v>11.5</v>
       </c>
       <c r="F61">
-        <v>23.76</v>
+        <v>13.12</v>
       </c>
       <c r="G61" s="1">
-        <v>0.677</v>
+        <v>0.635</v>
       </c>
       <c r="H61" t="s">
         <v>140</v>
       </c>
       <c r="I61" s="2">
-        <v>29.25</v>
+        <v>21.26</v>
       </c>
       <c r="J61" s="2">
-        <v>0.322</v>
+        <v>0.0292</v>
       </c>
       <c r="K61" t="s">
         <v>141</v>
@@ -3189,34 +3190,34 @@
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="B62" t="s">
         <v>117</v>
       </c>
       <c r="C62" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D62" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E62">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="F62">
-        <v>14.11</v>
+        <v>12.32</v>
       </c>
       <c r="G62" s="1">
-        <v>0.676</v>
+        <v>0.635</v>
       </c>
       <c r="H62" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I62" s="2">
-        <v>29</v>
+        <v>21.16</v>
       </c>
       <c r="J62" s="2">
-        <v>0.319</v>
+        <v>0.0291</v>
       </c>
       <c r="K62" t="s">
         <v>141</v>
@@ -3227,34 +3228,34 @@
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B63" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C63" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D63" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E63">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="F63">
-        <v>2.35</v>
+        <v>5.44</v>
       </c>
       <c r="G63" s="1">
-        <v>0.674</v>
+        <v>0.633</v>
       </c>
       <c r="H63" t="s">
         <v>140</v>
       </c>
       <c r="I63" s="2">
-        <v>28.61</v>
+        <v>20.78</v>
       </c>
       <c r="J63" s="2">
-        <v>0.315</v>
+        <v>0.0286</v>
       </c>
       <c r="K63" t="s">
         <v>141</v>
@@ -3265,34 +3266,34 @@
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B64" t="s">
         <v>126</v>
       </c>
       <c r="C64" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="D64" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E64">
         <v>15.5</v>
       </c>
       <c r="F64">
-        <v>19.72</v>
+        <v>18.7</v>
       </c>
       <c r="G64" s="1">
-        <v>0.673</v>
+        <v>0.633</v>
       </c>
       <c r="H64" t="s">
         <v>140</v>
       </c>
       <c r="I64" s="2">
-        <v>28.46</v>
+        <v>20.78</v>
       </c>
       <c r="J64" s="2">
-        <v>0.313</v>
+        <v>0.0286</v>
       </c>
       <c r="K64" t="s">
         <v>141</v>
@@ -3303,34 +3304,34 @@
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B65" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C65" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D65" t="s">
         <v>135</v>
       </c>
       <c r="E65">
-        <v>18.5</v>
+        <v>1.5</v>
       </c>
       <c r="F65">
-        <v>20.95</v>
+        <v>1.39</v>
       </c>
       <c r="G65" s="1">
-        <v>0.671</v>
+        <v>0.63</v>
       </c>
       <c r="H65" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I65" s="2">
-        <v>28.15</v>
+        <v>20.36</v>
       </c>
       <c r="J65" s="2">
-        <v>0.31</v>
+        <v>0.056</v>
       </c>
       <c r="K65" t="s">
         <v>141</v>
@@ -3341,10 +3342,10 @@
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B66" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C66" t="s">
         <v>129</v>
@@ -3353,22 +3354,22 @@
         <v>136</v>
       </c>
       <c r="E66">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="F66">
-        <v>6.18</v>
+        <v>16.5</v>
       </c>
       <c r="G66" s="1">
-        <v>0.67</v>
+        <v>0.628</v>
       </c>
       <c r="H66" t="s">
         <v>140</v>
       </c>
       <c r="I66" s="2">
-        <v>27.94</v>
+        <v>19.86</v>
       </c>
       <c r="J66" s="2">
-        <v>0.307</v>
+        <v>0.0546</v>
       </c>
       <c r="K66" t="s">
         <v>141</v>
@@ -3379,34 +3380,34 @@
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B67" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C67" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D67" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E67">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="F67">
-        <v>4.77</v>
+        <v>5.92</v>
       </c>
       <c r="G67" s="1">
-        <v>0.669</v>
+        <v>0.628</v>
       </c>
       <c r="H67" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I67" s="2">
-        <v>27.81</v>
+        <v>19.85</v>
       </c>
       <c r="J67" s="2">
-        <v>0.306</v>
+        <v>0.0546</v>
       </c>
       <c r="K67" t="s">
         <v>141</v>
@@ -3417,34 +3418,34 @@
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B68" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="C68" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D68" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E68">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="F68">
-        <v>7.68</v>
+        <v>7.75</v>
       </c>
       <c r="G68" s="1">
-        <v>0.659</v>
+        <v>0.627</v>
       </c>
       <c r="H68" t="s">
         <v>139</v>
       </c>
       <c r="I68" s="2">
-        <v>25.9</v>
+        <v>19.78</v>
       </c>
       <c r="J68" s="2">
-        <v>0.285</v>
+        <v>0.0272</v>
       </c>
       <c r="K68" t="s">
         <v>141</v>
@@ -3455,34 +3456,34 @@
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B69" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C69" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D69" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E69">
         <v>13.5</v>
       </c>
       <c r="F69">
-        <v>16.89</v>
+        <v>11.67</v>
       </c>
       <c r="G69" s="1">
-        <v>0.659</v>
+        <v>0.625</v>
       </c>
       <c r="H69" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I69" s="2">
-        <v>25.76</v>
+        <v>19.35</v>
       </c>
       <c r="J69" s="2">
-        <v>0.283</v>
+        <v>0.0532</v>
       </c>
       <c r="K69" t="s">
         <v>141</v>
@@ -3493,34 +3494,34 @@
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B70" t="s">
+        <v>119</v>
+      </c>
+      <c r="C70" t="s">
         <v>130</v>
       </c>
-      <c r="C70" t="s">
-        <v>126</v>
-      </c>
       <c r="D70" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E70">
-        <v>3.5</v>
+        <v>9.5</v>
       </c>
       <c r="F70">
-        <v>2.95</v>
+        <v>10.55</v>
       </c>
       <c r="G70" s="1">
-        <v>0.658</v>
+        <v>0.625</v>
       </c>
       <c r="H70" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I70" s="2">
-        <v>25.6</v>
+        <v>19.26</v>
       </c>
       <c r="J70" s="2">
-        <v>0.282</v>
+        <v>0.0265</v>
       </c>
       <c r="K70" t="s">
         <v>141</v>
@@ -3531,34 +3532,34 @@
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="B71" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C71" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="D71" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E71">
-        <v>13.5</v>
+        <v>2.5</v>
       </c>
       <c r="F71">
-        <v>11.96</v>
+        <v>2.25</v>
       </c>
       <c r="G71" s="1">
-        <v>0.657</v>
+        <v>0.623</v>
       </c>
       <c r="H71" t="s">
         <v>139</v>
       </c>
       <c r="I71" s="2">
-        <v>25.43</v>
+        <v>18.96</v>
       </c>
       <c r="J71" s="2">
-        <v>0.28</v>
+        <v>0.0521</v>
       </c>
       <c r="K71" t="s">
         <v>141</v>
@@ -3572,31 +3573,31 @@
         <v>79</v>
       </c>
       <c r="B72" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C72" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D72" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E72">
-        <v>10.5</v>
+        <v>3.5</v>
       </c>
       <c r="F72">
-        <v>7.33</v>
+        <v>4.3</v>
       </c>
       <c r="G72" s="1">
-        <v>0.656</v>
+        <v>0.623</v>
       </c>
       <c r="H72" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I72" s="2">
-        <v>25.28</v>
+        <v>18.85</v>
       </c>
       <c r="J72" s="2">
-        <v>0.278</v>
+        <v>0.0259</v>
       </c>
       <c r="K72" t="s">
         <v>141</v>
@@ -3610,31 +3611,31 @@
         <v>80</v>
       </c>
       <c r="B73" t="s">
+        <v>120</v>
+      </c>
+      <c r="C73" t="s">
         <v>125</v>
-      </c>
-      <c r="C73" t="s">
-        <v>129</v>
       </c>
       <c r="D73" t="s">
         <v>137</v>
       </c>
       <c r="E73">
-        <v>1.5</v>
+        <v>19.5</v>
       </c>
       <c r="F73">
-        <v>1.39</v>
+        <v>17.27</v>
       </c>
       <c r="G73" s="1">
-        <v>0.656</v>
+        <v>0.622</v>
       </c>
       <c r="H73" t="s">
         <v>139</v>
       </c>
       <c r="I73" s="2">
-        <v>25.19</v>
+        <v>18.74</v>
       </c>
       <c r="J73" s="2">
-        <v>0.277</v>
+        <v>0.0515</v>
       </c>
       <c r="K73" t="s">
         <v>141</v>
@@ -3648,31 +3649,31 @@
         <v>81</v>
       </c>
       <c r="B74" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C74" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D74" t="s">
         <v>135</v>
       </c>
       <c r="E74">
-        <v>22.5</v>
+        <v>3.5</v>
       </c>
       <c r="F74">
-        <v>25.53</v>
+        <v>3.21</v>
       </c>
       <c r="G74" s="1">
-        <v>0.656</v>
+        <v>0.622</v>
       </c>
       <c r="H74" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I74" s="2">
-        <v>25.15</v>
+        <v>18.72</v>
       </c>
       <c r="J74" s="2">
-        <v>0.277</v>
+        <v>0.0515</v>
       </c>
       <c r="K74" t="s">
         <v>141</v>
@@ -3686,31 +3687,31 @@
         <v>82</v>
       </c>
       <c r="B75" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="C75" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="D75" t="s">
         <v>135</v>
       </c>
       <c r="E75">
-        <v>14.5</v>
+        <v>7.5</v>
       </c>
       <c r="F75">
-        <v>16.95</v>
+        <v>6.84</v>
       </c>
       <c r="G75" s="1">
-        <v>0.655</v>
+        <v>0.621</v>
       </c>
       <c r="H75" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I75" s="2">
-        <v>25.12</v>
+        <v>18.63</v>
       </c>
       <c r="J75" s="2">
-        <v>0.276</v>
+        <v>0.0512</v>
       </c>
       <c r="K75" t="s">
         <v>141</v>
@@ -3724,31 +3725,31 @@
         <v>83</v>
       </c>
       <c r="B76" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C76" t="s">
         <v>131</v>
       </c>
       <c r="D76" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E76">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="F76">
-        <v>6.6</v>
+        <v>2.21</v>
       </c>
       <c r="G76" s="1">
-        <v>0.653</v>
+        <v>0.621</v>
       </c>
       <c r="H76" t="s">
         <v>139</v>
       </c>
       <c r="I76" s="2">
-        <v>24.7</v>
+        <v>18.6</v>
       </c>
       <c r="J76" s="2">
-        <v>0.272</v>
+        <v>0.0256</v>
       </c>
       <c r="K76" t="s">
         <v>141</v>
@@ -3759,34 +3760,34 @@
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="B77" t="s">
         <v>119</v>
       </c>
       <c r="C77" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D77" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E77">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="F77">
-        <v>14.84</v>
+        <v>8.6</v>
       </c>
       <c r="G77" s="1">
-        <v>0.649</v>
+        <v>0.621</v>
       </c>
       <c r="H77" t="s">
         <v>140</v>
       </c>
       <c r="I77" s="2">
-        <v>23.83</v>
+        <v>18.6</v>
       </c>
       <c r="J77" s="2">
-        <v>0.262</v>
+        <v>0.0256</v>
       </c>
       <c r="K77" t="s">
         <v>141</v>
@@ -3800,31 +3801,31 @@
         <v>84</v>
       </c>
       <c r="B78" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C78" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D78" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E78">
-        <v>1.5</v>
+        <v>20.5</v>
       </c>
       <c r="F78">
-        <v>1.56</v>
+        <v>23.2</v>
       </c>
       <c r="G78" s="1">
-        <v>0.645</v>
+        <v>0.619</v>
       </c>
       <c r="H78" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I78" s="2">
-        <v>23.18</v>
+        <v>18.22</v>
       </c>
       <c r="J78" s="2">
-        <v>0.255</v>
+        <v>0.0251</v>
       </c>
       <c r="K78" t="s">
         <v>141</v>
@@ -3838,31 +3839,31 @@
         <v>85</v>
       </c>
       <c r="B79" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C79" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D79" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E79">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="F79">
-        <v>16.22</v>
+        <v>20.42</v>
       </c>
       <c r="G79" s="1">
-        <v>0.645</v>
+        <v>0.619</v>
       </c>
       <c r="H79" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I79" s="2">
-        <v>23.1</v>
+        <v>18.15</v>
       </c>
       <c r="J79" s="2">
-        <v>0.254</v>
+        <v>0.025</v>
       </c>
       <c r="K79" t="s">
         <v>141</v>
@@ -3876,31 +3877,31 @@
         <v>86</v>
       </c>
       <c r="B80" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C80" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D80" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E80">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="F80">
-        <v>13.46</v>
+        <v>9.52</v>
       </c>
       <c r="G80" s="1">
-        <v>0.642</v>
+        <v>0.618</v>
       </c>
       <c r="H80" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I80" s="2">
-        <v>22.57</v>
+        <v>18.01</v>
       </c>
       <c r="J80" s="2">
-        <v>0.248</v>
+        <v>0.0248</v>
       </c>
       <c r="K80" t="s">
         <v>141</v>
@@ -3911,34 +3912,34 @@
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B81" t="s">
         <v>120</v>
       </c>
       <c r="C81" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D81" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E81">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="F81">
-        <v>2.2</v>
+        <v>6.88</v>
       </c>
       <c r="G81" s="1">
-        <v>0.641</v>
+        <v>0.615</v>
       </c>
       <c r="H81" t="s">
         <v>139</v>
       </c>
       <c r="I81" s="2">
-        <v>22.39</v>
+        <v>17.49</v>
       </c>
       <c r="J81" s="2">
-        <v>0.246</v>
+        <v>0.0481</v>
       </c>
       <c r="K81" t="s">
         <v>141</v>
@@ -3949,34 +3950,34 @@
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B82" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="C82" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D82" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E82">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="F82">
-        <v>7.49</v>
+        <v>1.44</v>
       </c>
       <c r="G82" s="1">
-        <v>0.637</v>
+        <v>0.613</v>
       </c>
       <c r="H82" t="s">
         <v>139</v>
       </c>
       <c r="I82" s="2">
-        <v>21.54</v>
+        <v>17.04</v>
       </c>
       <c r="J82" s="2">
-        <v>0.237</v>
+        <v>0.0234</v>
       </c>
       <c r="K82" t="s">
         <v>141</v>
@@ -3987,34 +3988,34 @@
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B83" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="C83" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="D83" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E83">
-        <v>9.5</v>
+        <v>2.5</v>
       </c>
       <c r="F83">
-        <v>10.57</v>
+        <v>3.22</v>
       </c>
       <c r="G83" s="1">
-        <v>0.636</v>
+        <v>0.613</v>
       </c>
       <c r="H83" t="s">
         <v>140</v>
       </c>
       <c r="I83" s="2">
-        <v>21.5</v>
+        <v>17.01</v>
       </c>
       <c r="J83" s="2">
-        <v>0.236</v>
+        <v>0.0234</v>
       </c>
       <c r="K83" t="s">
         <v>141</v>
@@ -4025,34 +4026,34 @@
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B84" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C84" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D84" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E84">
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="F84">
-        <v>7.09</v>
+        <v>4.08</v>
       </c>
       <c r="G84" s="1">
-        <v>0.634</v>
+        <v>0.613</v>
       </c>
       <c r="H84" t="s">
         <v>139</v>
       </c>
       <c r="I84" s="2">
-        <v>21.05</v>
+        <v>16.98</v>
       </c>
       <c r="J84" s="2">
-        <v>0.232</v>
+        <v>0.0233</v>
       </c>
       <c r="K84" t="s">
         <v>141</v>
@@ -4063,34 +4064,34 @@
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="B85" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C85" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D85" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E85">
-        <v>19.5</v>
+        <v>7.5</v>
       </c>
       <c r="F85">
-        <v>17.97</v>
+        <v>7.03</v>
       </c>
       <c r="G85" s="1">
-        <v>0.632</v>
+        <v>0.611</v>
       </c>
       <c r="H85" t="s">
         <v>139</v>
       </c>
       <c r="I85" s="2">
-        <v>20.72</v>
+        <v>16.64</v>
       </c>
       <c r="J85" s="2">
-        <v>0.228</v>
+        <v>0.0458</v>
       </c>
       <c r="K85" t="s">
         <v>141</v>
@@ -4101,34 +4102,34 @@
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="B86" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C86" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D86" t="s">
         <v>137</v>
       </c>
       <c r="E86">
-        <v>1.5</v>
+        <v>15.5</v>
       </c>
       <c r="F86">
-        <v>1.32</v>
+        <v>18.28</v>
       </c>
       <c r="G86" s="1">
-        <v>0.628</v>
+        <v>0.607</v>
       </c>
       <c r="H86" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I86" s="2">
-        <v>19.96</v>
+        <v>15.8</v>
       </c>
       <c r="J86" s="2">
-        <v>0.22</v>
+        <v>0.0435</v>
       </c>
       <c r="K86" t="s">
         <v>141</v>
@@ -4139,34 +4140,34 @@
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="B87" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C87" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D87" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E87">
-        <v>18.5</v>
+        <v>2.5</v>
       </c>
       <c r="F87">
-        <v>21.34</v>
+        <v>2.41</v>
       </c>
       <c r="G87" s="1">
-        <v>0.627</v>
+        <v>0.603</v>
       </c>
       <c r="H87" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I87" s="2">
-        <v>19.62</v>
+        <v>15.12</v>
       </c>
       <c r="J87" s="2">
-        <v>0.216</v>
+        <v>0.0208</v>
       </c>
       <c r="K87" t="s">
         <v>141</v>
@@ -4177,34 +4178,34 @@
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B88" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C88" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D88" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E88">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="F88">
-        <v>8.800000000000001</v>
+        <v>4.55</v>
       </c>
       <c r="G88" s="1">
-        <v>0.625</v>
+        <v>0.602</v>
       </c>
       <c r="H88" t="s">
         <v>139</v>
       </c>
       <c r="I88" s="2">
-        <v>19.4</v>
+        <v>14.98</v>
       </c>
       <c r="J88" s="2">
-        <v>0.213</v>
+        <v>0.0412</v>
       </c>
       <c r="K88" t="s">
         <v>141</v>
@@ -4215,34 +4216,34 @@
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="B89" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C89" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D89" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E89">
         <v>2.5</v>
       </c>
       <c r="F89">
-        <v>3.22</v>
+        <v>2.28</v>
       </c>
       <c r="G89" s="1">
-        <v>0.624</v>
+        <v>0.602</v>
       </c>
       <c r="H89" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I89" s="2">
-        <v>19.13</v>
+        <v>14.95</v>
       </c>
       <c r="J89" s="2">
-        <v>0.21</v>
+        <v>0.0411</v>
       </c>
       <c r="K89" t="s">
         <v>141</v>
@@ -4253,34 +4254,34 @@
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B90" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="C90" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="D90" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E90">
         <v>4.5</v>
       </c>
       <c r="F90">
-        <v>4.19</v>
+        <v>4.15</v>
       </c>
       <c r="G90" s="1">
-        <v>0.622</v>
+        <v>0.6</v>
       </c>
       <c r="H90" t="s">
         <v>139</v>
       </c>
       <c r="I90" s="2">
-        <v>18.78</v>
+        <v>14.55</v>
       </c>
       <c r="J90" s="2">
-        <v>0.207</v>
+        <v>0.02</v>
       </c>
       <c r="K90" t="s">
         <v>141</v>
@@ -4291,34 +4292,34 @@
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="B91" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C91" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D91" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E91">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F91">
-        <v>2.44</v>
+        <v>4.38</v>
       </c>
       <c r="G91" s="1">
-        <v>0.622</v>
+        <v>0.599</v>
       </c>
       <c r="H91" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I91" s="2">
-        <v>18.71</v>
+        <v>14.44</v>
       </c>
       <c r="J91" s="2">
-        <v>0.206</v>
+        <v>0.0397</v>
       </c>
       <c r="K91" t="s">
         <v>141</v>
@@ -4329,34 +4330,34 @@
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B92" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="C92" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="D92" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E92">
-        <v>11.5</v>
+        <v>20.5</v>
       </c>
       <c r="F92">
-        <v>9</v>
+        <v>19.02</v>
       </c>
       <c r="G92" s="1">
-        <v>0.618</v>
+        <v>0.598</v>
       </c>
       <c r="H92" t="s">
         <v>139</v>
       </c>
       <c r="I92" s="2">
-        <v>18.01</v>
+        <v>14.19</v>
       </c>
       <c r="J92" s="2">
-        <v>0.198</v>
+        <v>0.0195</v>
       </c>
       <c r="K92" t="s">
         <v>141</v>
@@ -4367,34 +4368,34 @@
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B93" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C93" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D93" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E93">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="F93">
-        <v>5</v>
+        <v>1.39</v>
       </c>
       <c r="G93" s="1">
-        <v>0.617</v>
+        <v>0.596</v>
       </c>
       <c r="H93" t="s">
         <v>139</v>
       </c>
       <c r="I93" s="2">
-        <v>17.86</v>
+        <v>13.8</v>
       </c>
       <c r="J93" s="2">
-        <v>0.197</v>
+        <v>0.0379</v>
       </c>
       <c r="K93" t="s">
         <v>141</v>
@@ -4405,34 +4406,34 @@
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B94" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C94" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D94" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E94">
-        <v>2.5</v>
+        <v>12.5</v>
       </c>
       <c r="F94">
-        <v>3.4</v>
+        <v>13.07</v>
       </c>
       <c r="G94" s="1">
-        <v>0.617</v>
+        <v>0.596</v>
       </c>
       <c r="H94" t="s">
         <v>140</v>
       </c>
       <c r="I94" s="2">
-        <v>17.76</v>
+        <v>13.75</v>
       </c>
       <c r="J94" s="2">
-        <v>0.195</v>
+        <v>0.0378</v>
       </c>
       <c r="K94" t="s">
         <v>141</v>
@@ -4443,34 +4444,34 @@
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B95" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="C95" t="s">
         <v>119</v>
       </c>
       <c r="D95" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E95">
-        <v>19.5</v>
+        <v>12.5</v>
       </c>
       <c r="F95">
-        <v>17.44</v>
+        <v>14.26</v>
       </c>
       <c r="G95" s="1">
-        <v>0.616</v>
+        <v>0.592</v>
       </c>
       <c r="H95" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I95" s="2">
-        <v>17.57</v>
+        <v>13.09</v>
       </c>
       <c r="J95" s="2">
-        <v>0.193</v>
+        <v>0.018</v>
       </c>
       <c r="K95" t="s">
         <v>141</v>
@@ -4481,34 +4482,34 @@
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B96" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C96" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="D96" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E96">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="F96">
-        <v>4.07</v>
+        <v>13.9</v>
       </c>
       <c r="G96" s="1">
-        <v>0.616</v>
+        <v>0.591</v>
       </c>
       <c r="H96" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I96" s="2">
-        <v>17.56</v>
+        <v>12.74</v>
       </c>
       <c r="J96" s="2">
-        <v>0.193</v>
+        <v>0.035</v>
       </c>
       <c r="K96" t="s">
         <v>141</v>
@@ -4519,34 +4520,34 @@
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="B97" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C97" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D97" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E97">
         <v>3.5</v>
       </c>
       <c r="F97">
-        <v>3.28</v>
+        <v>3.55</v>
       </c>
       <c r="G97" s="1">
-        <v>0.608</v>
+        <v>0.59</v>
       </c>
       <c r="H97" t="s">
         <v>139</v>
       </c>
       <c r="I97" s="2">
-        <v>16.02</v>
+        <v>12.54</v>
       </c>
       <c r="J97" s="2">
-        <v>0.176</v>
+        <v>0.0345</v>
       </c>
       <c r="K97" t="s">
         <v>141</v>
@@ -4557,34 +4558,34 @@
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="B98" t="s">
+        <v>129</v>
+      </c>
+      <c r="C98" t="s">
         <v>118</v>
       </c>
-      <c r="C98" t="s">
-        <v>119</v>
-      </c>
       <c r="D98" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E98">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="F98">
-        <v>1.55</v>
+        <v>9.81</v>
       </c>
       <c r="G98" s="1">
-        <v>0.607</v>
+        <v>0.588</v>
       </c>
       <c r="H98" t="s">
         <v>139</v>
       </c>
       <c r="I98" s="2">
-        <v>15.84</v>
+        <v>12.28</v>
       </c>
       <c r="J98" s="2">
-        <v>0.174</v>
+        <v>0.0338</v>
       </c>
       <c r="K98" t="s">
         <v>141</v>
@@ -4595,34 +4596,34 @@
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="B99" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C99" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D99" t="s">
         <v>135</v>
       </c>
       <c r="E99">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="F99">
-        <v>6.44</v>
+        <v>1.98</v>
       </c>
       <c r="G99" s="1">
-        <v>0.607</v>
+        <v>0.588</v>
       </c>
       <c r="H99" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I99" s="2">
-        <v>15.79</v>
+        <v>12.17</v>
       </c>
       <c r="J99" s="2">
-        <v>0.174</v>
+        <v>0.0167</v>
       </c>
       <c r="K99" t="s">
         <v>141</v>
@@ -4636,31 +4637,31 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="C100" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D100" t="s">
         <v>134</v>
       </c>
       <c r="E100">
-        <v>11.5</v>
+        <v>2.5</v>
       </c>
       <c r="F100">
-        <v>14.32</v>
+        <v>2.34</v>
       </c>
       <c r="G100" s="1">
-        <v>0.606</v>
+        <v>0.588</v>
       </c>
       <c r="H100" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I100" s="2">
-        <v>15.75</v>
+        <v>12.16</v>
       </c>
       <c r="J100" s="2">
-        <v>0.173</v>
+        <v>0.0167</v>
       </c>
       <c r="K100" t="s">
         <v>141</v>
@@ -4671,10 +4672,10 @@
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="B101" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C101" t="s">
         <v>130</v>
@@ -4683,22 +4684,22 @@
         <v>135</v>
       </c>
       <c r="E101">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="F101">
-        <v>9.49</v>
+        <v>1.44</v>
       </c>
       <c r="G101" s="1">
-        <v>0.606</v>
+        <v>0.585</v>
       </c>
       <c r="H101" t="s">
         <v>139</v>
       </c>
       <c r="I101" s="2">
-        <v>15.74</v>
+        <v>11.76</v>
       </c>
       <c r="J101" s="2">
-        <v>0.173</v>
+        <v>0.0162</v>
       </c>
       <c r="K101" t="s">
         <v>141</v>
@@ -4709,34 +4710,34 @@
     </row>
     <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C102" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="D102" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E102">
-        <v>9.5</v>
+        <v>20.5</v>
       </c>
       <c r="F102">
-        <v>10.99</v>
+        <v>18.31</v>
       </c>
       <c r="G102" s="1">
-        <v>0.605</v>
+        <v>0.583</v>
       </c>
       <c r="H102" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I102" s="2">
-        <v>15.58</v>
+        <v>11.35</v>
       </c>
       <c r="J102" s="2">
-        <v>0.171</v>
+        <v>0.0156</v>
       </c>
       <c r="K102" t="s">
         <v>141</v>
@@ -4747,34 +4748,34 @@
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="B103" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C103" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D103" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E103">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="F103">
-        <v>3.2</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G103" s="1">
-        <v>0.603</v>
+        <v>0.581</v>
       </c>
       <c r="H103" t="s">
         <v>139</v>
       </c>
       <c r="I103" s="2">
-        <v>15.12</v>
+        <v>10.83</v>
       </c>
       <c r="J103" s="2">
-        <v>0.166</v>
+        <v>0.0298</v>
       </c>
       <c r="K103" t="s">
         <v>141</v>
@@ -4785,34 +4786,34 @@
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B104" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C104" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D104" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E104">
-        <v>7.5</v>
+        <v>13.5</v>
       </c>
       <c r="F104">
-        <v>7.03</v>
+        <v>12.96</v>
       </c>
       <c r="G104" s="1">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="H104" t="s">
         <v>139</v>
       </c>
       <c r="I104" s="2">
-        <v>14.55</v>
+        <v>10.73</v>
       </c>
       <c r="J104" s="2">
-        <v>0.16</v>
+        <v>0.0295</v>
       </c>
       <c r="K104" t="s">
         <v>141</v>
@@ -4823,37 +4824,37 @@
     </row>
     <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="B105" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C105" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D105" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E105">
-        <v>25.5</v>
+        <v>2.5</v>
       </c>
       <c r="F105">
-        <v>27.89</v>
+        <v>3.01</v>
       </c>
       <c r="G105" s="1">
-        <v>0.599</v>
+        <v>0.58</v>
       </c>
       <c r="H105" t="s">
         <v>140</v>
       </c>
       <c r="I105" s="2">
-        <v>14.3</v>
+        <v>10.67</v>
       </c>
       <c r="J105" s="2">
-        <v>0.157</v>
+        <v>0.0293</v>
       </c>
       <c r="K105" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L105" t="s">
         <v>145</v>
@@ -4861,37 +4862,37 @@
     </row>
     <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="B106" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C106" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="D106" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E106">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="F106">
-        <v>7.97</v>
+        <v>1.5</v>
       </c>
       <c r="G106" s="1">
-        <v>0.598</v>
+        <v>0.578</v>
       </c>
       <c r="H106" t="s">
         <v>139</v>
       </c>
       <c r="I106" s="2">
-        <v>14.13</v>
+        <v>10.4</v>
       </c>
       <c r="J106" s="2">
-        <v>0.155</v>
+        <v>0.0286</v>
       </c>
       <c r="K106" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L106" t="s">
         <v>145</v>
@@ -4899,37 +4900,37 @@
     </row>
     <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B107" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C107" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D107" t="s">
         <v>134</v>
       </c>
       <c r="E107">
-        <v>23.5</v>
+        <v>8.5</v>
       </c>
       <c r="F107">
-        <v>21.68</v>
+        <v>8.15</v>
       </c>
       <c r="G107" s="1">
-        <v>0.597</v>
+        <v>0.575</v>
       </c>
       <c r="H107" t="s">
         <v>139</v>
       </c>
       <c r="I107" s="2">
-        <v>13.98</v>
+        <v>9.85</v>
       </c>
       <c r="J107" s="2">
-        <v>0.154</v>
+        <v>0.0135</v>
       </c>
       <c r="K107" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L107" t="s">
         <v>145</v>
@@ -4937,37 +4938,37 @@
     </row>
     <row r="108" spans="1:12">
       <c r="A108" t="s">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="B108" t="s">
+        <v>127</v>
+      </c>
+      <c r="C108" t="s">
         <v>121</v>
       </c>
-      <c r="C108" t="s">
-        <v>122</v>
-      </c>
       <c r="D108" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E108">
-        <v>15.5</v>
+        <v>21.5</v>
       </c>
       <c r="F108">
-        <v>17.01</v>
+        <v>22.88</v>
       </c>
       <c r="G108" s="1">
-        <v>0.597</v>
+        <v>0.573</v>
       </c>
       <c r="H108" t="s">
         <v>140</v>
       </c>
       <c r="I108" s="2">
-        <v>13.91</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="J108" s="2">
-        <v>0.153</v>
+        <v>0.013</v>
       </c>
       <c r="K108" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L108" t="s">
         <v>145</v>
@@ -4975,37 +4976,37 @@
     </row>
     <row r="109" spans="1:12">
       <c r="A109" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B109" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="C109" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="D109" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E109">
-        <v>5.5</v>
+        <v>9.5</v>
       </c>
       <c r="F109">
-        <v>6.37</v>
+        <v>10.36</v>
       </c>
       <c r="G109" s="1">
-        <v>0.596</v>
+        <v>0.572</v>
       </c>
       <c r="H109" t="s">
         <v>140</v>
       </c>
       <c r="I109" s="2">
-        <v>13.79</v>
+        <v>9.19</v>
       </c>
       <c r="J109" s="2">
-        <v>0.152</v>
+        <v>0.0126</v>
       </c>
       <c r="K109" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L109" t="s">
         <v>145</v>
@@ -5013,37 +5014,37 @@
     </row>
     <row r="110" spans="1:12">
       <c r="A110" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="B110" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C110" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D110" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E110">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="F110">
-        <v>7.03</v>
+        <v>5.29</v>
       </c>
       <c r="G110" s="1">
-        <v>0.596</v>
+        <v>0.572</v>
       </c>
       <c r="H110" t="s">
         <v>139</v>
       </c>
       <c r="I110" s="2">
-        <v>13.69</v>
+        <v>9.15</v>
       </c>
       <c r="J110" s="2">
-        <v>0.151</v>
+        <v>0.0126</v>
       </c>
       <c r="K110" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L110" t="s">
         <v>145</v>
@@ -5051,37 +5052,37 @@
     </row>
     <row r="111" spans="1:12">
       <c r="A111" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="B111" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C111" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="D111" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E111">
-        <v>17.5</v>
+        <v>3.5</v>
       </c>
       <c r="F111">
-        <v>15.82</v>
+        <v>3.48</v>
       </c>
       <c r="G111" s="1">
-        <v>0.595</v>
+        <v>0.571</v>
       </c>
       <c r="H111" t="s">
         <v>139</v>
       </c>
       <c r="I111" s="2">
-        <v>13.66</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="J111" s="2">
-        <v>0.15</v>
+        <v>0.0247</v>
       </c>
       <c r="K111" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L111" t="s">
         <v>145</v>
@@ -5089,37 +5090,37 @@
     </row>
     <row r="112" spans="1:12">
       <c r="A112" t="s">
-        <v>107</v>
+        <v>38</v>
       </c>
       <c r="B112" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C112" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D112" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E112">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="F112">
-        <v>8.68</v>
+        <v>1.92</v>
       </c>
       <c r="G112" s="1">
-        <v>0.591</v>
+        <v>0.571</v>
       </c>
       <c r="H112" t="s">
         <v>140</v>
       </c>
       <c r="I112" s="2">
-        <v>12.86</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="J112" s="2">
-        <v>0.141</v>
+        <v>0.0247</v>
       </c>
       <c r="K112" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L112" t="s">
         <v>145</v>
@@ -5127,10 +5128,10 @@
     </row>
     <row r="113" spans="1:12">
       <c r="A113" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B113" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="C113" t="s">
         <v>119</v>
@@ -5139,25 +5140,25 @@
         <v>136</v>
       </c>
       <c r="E113">
-        <v>5.5</v>
+        <v>9.5</v>
       </c>
       <c r="F113">
-        <v>5.2</v>
+        <v>10.74</v>
       </c>
       <c r="G113" s="1">
-        <v>0.591</v>
+        <v>0.57</v>
       </c>
       <c r="H113" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I113" s="2">
-        <v>12.84</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J113" s="2">
-        <v>0.141</v>
+        <v>0.0121</v>
       </c>
       <c r="K113" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L113" t="s">
         <v>145</v>
@@ -5165,37 +5166,37 @@
     </row>
     <row r="114" spans="1:12">
       <c r="A114" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B114" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C114" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D114" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E114">
-        <v>1.5</v>
+        <v>20.5</v>
       </c>
       <c r="F114">
-        <v>2.08</v>
+        <v>22.35</v>
       </c>
       <c r="G114" s="1">
-        <v>0.59</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H114" t="s">
         <v>140</v>
       </c>
       <c r="I114" s="2">
-        <v>12.64</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="J114" s="2">
-        <v>0.139</v>
+        <v>0.0112</v>
       </c>
       <c r="K114" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L114" t="s">
         <v>145</v>
@@ -5203,37 +5204,37 @@
     </row>
     <row r="115" spans="1:12">
       <c r="A115" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="B115" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C115" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="D115" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E115">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="F115">
-        <v>8.67</v>
+        <v>1.9</v>
       </c>
       <c r="G115" s="1">
-        <v>0.587</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="H115" t="s">
         <v>140</v>
       </c>
       <c r="I115" s="2">
-        <v>12.15</v>
+        <v>7.85</v>
       </c>
       <c r="J115" s="2">
-        <v>0.134</v>
+        <v>0.0108</v>
       </c>
       <c r="K115" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L115" t="s">
         <v>145</v>
@@ -5241,37 +5242,37 @@
     </row>
     <row r="116" spans="1:12">
       <c r="A116" t="s">
-        <v>108</v>
+        <v>50</v>
       </c>
       <c r="B116" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C116" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D116" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E116">
-        <v>18.5</v>
+        <v>11.5</v>
       </c>
       <c r="F116">
-        <v>20.28</v>
+        <v>12.37</v>
       </c>
       <c r="G116" s="1">
-        <v>0.587</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="H116" t="s">
         <v>140</v>
       </c>
       <c r="I116" s="2">
-        <v>12.06</v>
+        <v>7.83</v>
       </c>
       <c r="J116" s="2">
-        <v>0.133</v>
+        <v>0.0108</v>
       </c>
       <c r="K116" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L116" t="s">
         <v>145</v>
@@ -5279,37 +5280,37 @@
     </row>
     <row r="117" spans="1:12">
       <c r="A117" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="B117" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C117" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D117" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E117">
-        <v>7.5</v>
+        <v>13.5</v>
       </c>
       <c r="F117">
-        <v>8.68</v>
+        <v>14.77</v>
       </c>
       <c r="G117" s="1">
-        <v>0.586</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="H117" t="s">
         <v>140</v>
       </c>
       <c r="I117" s="2">
-        <v>11.83</v>
+        <v>7.13</v>
       </c>
       <c r="J117" s="2">
-        <v>0.13</v>
+        <v>0.0196</v>
       </c>
       <c r="K117" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L117" t="s">
         <v>145</v>
@@ -5317,37 +5318,37 @@
     </row>
     <row r="118" spans="1:12">
       <c r="A118" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C118" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D118" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E118">
-        <v>19.5</v>
+        <v>1.5</v>
       </c>
       <c r="F118">
-        <v>20.94</v>
+        <v>2.15</v>
       </c>
       <c r="G118" s="1">
-        <v>0.585</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="H118" t="s">
         <v>140</v>
       </c>
       <c r="I118" s="2">
-        <v>11.71</v>
+        <v>7.05</v>
       </c>
       <c r="J118" s="2">
-        <v>0.129</v>
+        <v>0.0097</v>
       </c>
       <c r="K118" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L118" t="s">
         <v>145</v>
@@ -5355,37 +5356,37 @@
     </row>
     <row r="119" spans="1:12">
       <c r="A119" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B119" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C119" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="D119" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E119">
-        <v>4.5</v>
+        <v>15.5</v>
       </c>
       <c r="F119">
-        <v>5.34</v>
+        <v>16.4</v>
       </c>
       <c r="G119" s="1">
-        <v>0.583</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H119" t="s">
         <v>140</v>
       </c>
       <c r="I119" s="2">
-        <v>11.21</v>
+        <v>6.92</v>
       </c>
       <c r="J119" s="2">
-        <v>0.123</v>
+        <v>0.019</v>
       </c>
       <c r="K119" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L119" t="s">
         <v>145</v>
@@ -5393,37 +5394,37 @@
     </row>
     <row r="120" spans="1:12">
       <c r="A120" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="B120" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C120" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D120" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E120">
-        <v>5.5</v>
+        <v>28.5</v>
       </c>
       <c r="F120">
-        <v>5.21</v>
+        <v>30.31</v>
       </c>
       <c r="G120" s="1">
-        <v>0.581</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H120" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I120" s="2">
-        <v>10.99</v>
+        <v>6.84</v>
       </c>
       <c r="J120" s="2">
-        <v>0.121</v>
+        <v>0.0188</v>
       </c>
       <c r="K120" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L120" t="s">
         <v>145</v>
@@ -5431,37 +5432,37 @@
     </row>
     <row r="121" spans="1:12">
       <c r="A121" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="B121" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C121" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D121" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E121">
-        <v>2.5</v>
+        <v>13.5</v>
       </c>
       <c r="F121">
-        <v>2.36</v>
+        <v>12.25</v>
       </c>
       <c r="G121" s="1">
-        <v>0.581</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="H121" t="s">
         <v>139</v>
       </c>
       <c r="I121" s="2">
-        <v>10.93</v>
+        <v>6.75</v>
       </c>
       <c r="J121" s="2">
-        <v>0.12</v>
+        <v>0.0185</v>
       </c>
       <c r="K121" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L121" t="s">
         <v>145</v>
@@ -5469,34 +5470,34 @@
     </row>
     <row r="122" spans="1:12">
       <c r="A122" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="B122" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C122" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="D122" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E122">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="F122">
-        <v>2.37</v>
+        <v>7.03</v>
       </c>
       <c r="G122" s="1">
-        <v>0.578</v>
+        <v>0.555</v>
       </c>
       <c r="H122" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I122" s="2">
-        <v>10.28</v>
+        <v>5.94</v>
       </c>
       <c r="J122" s="2">
-        <v>0.113</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="K122" t="s">
         <v>142</v>
@@ -5507,34 +5508,34 @@
     </row>
     <row r="123" spans="1:12">
       <c r="A123" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="B123" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C123" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D123" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E123">
-        <v>7.5</v>
+        <v>25.5</v>
       </c>
       <c r="F123">
-        <v>8.5</v>
+        <v>26.8</v>
       </c>
       <c r="G123" s="1">
-        <v>0.577</v>
+        <v>0.554</v>
       </c>
       <c r="H123" t="s">
         <v>140</v>
       </c>
       <c r="I123" s="2">
-        <v>10.11</v>
+        <v>5.8</v>
       </c>
       <c r="J123" s="2">
-        <v>0.111</v>
+        <v>0.016</v>
       </c>
       <c r="K123" t="s">
         <v>142</v>
@@ -5545,34 +5546,34 @@
     </row>
     <row r="124" spans="1:12">
       <c r="A124" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="B124" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C124" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D124" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E124">
-        <v>3.5</v>
+        <v>18.5</v>
       </c>
       <c r="F124">
-        <v>4.05</v>
+        <v>19.05</v>
       </c>
       <c r="G124" s="1">
-        <v>0.576</v>
+        <v>0.553</v>
       </c>
       <c r="H124" t="s">
         <v>140</v>
       </c>
       <c r="I124" s="2">
-        <v>10.02</v>
+        <v>5.63</v>
       </c>
       <c r="J124" s="2">
-        <v>0.11</v>
+        <v>0.0155</v>
       </c>
       <c r="K124" t="s">
         <v>142</v>
@@ -5583,34 +5584,34 @@
     </row>
     <row r="125" spans="1:12">
       <c r="A125" t="s">
-        <v>37</v>
+        <v>95</v>
       </c>
       <c r="B125" t="s">
         <v>126</v>
       </c>
       <c r="C125" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="D125" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E125">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="F125">
-        <v>1.92</v>
+        <v>7.92</v>
       </c>
       <c r="G125" s="1">
-        <v>0.572</v>
+        <v>0.553</v>
       </c>
       <c r="H125" t="s">
         <v>140</v>
       </c>
       <c r="I125" s="2">
-        <v>9.17</v>
+        <v>5.48</v>
       </c>
       <c r="J125" s="2">
-        <v>0.101</v>
+        <v>0.0151</v>
       </c>
       <c r="K125" t="s">
         <v>142</v>
@@ -5621,34 +5622,34 @@
     </row>
     <row r="126" spans="1:12">
       <c r="A126" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="B126" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="C126" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D126" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E126">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="F126">
-        <v>4.74</v>
+        <v>1.85</v>
       </c>
       <c r="G126" s="1">
-        <v>0.571</v>
+        <v>0.551</v>
       </c>
       <c r="H126" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I126" s="2">
-        <v>8.93</v>
+        <v>5.28</v>
       </c>
       <c r="J126" s="2">
-        <v>0.098</v>
+        <v>0.0145</v>
       </c>
       <c r="K126" t="s">
         <v>142</v>
@@ -5659,34 +5660,34 @@
     </row>
     <row r="127" spans="1:12">
       <c r="A127" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="B127" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C127" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D127" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E127">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F127">
-        <v>3.08</v>
+        <v>3.44</v>
       </c>
       <c r="G127" s="1">
-        <v>0.5679999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="H127" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I127" s="2">
-        <v>8.460000000000001</v>
+        <v>5.05</v>
       </c>
       <c r="J127" s="2">
-        <v>0.093</v>
+        <v>0.0069</v>
       </c>
       <c r="K127" t="s">
         <v>142</v>
@@ -5697,34 +5698,34 @@
     </row>
     <row r="128" spans="1:12">
       <c r="A128" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="B128" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C128" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D128" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E128">
-        <v>11.5</v>
+        <v>2.5</v>
       </c>
       <c r="F128">
-        <v>12.57</v>
+        <v>2.88</v>
       </c>
       <c r="G128" s="1">
-        <v>0.5679999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="H128" t="s">
         <v>140</v>
       </c>
       <c r="I128" s="2">
-        <v>8.44</v>
+        <v>4.94</v>
       </c>
       <c r="J128" s="2">
-        <v>0.093</v>
+        <v>0.0136</v>
       </c>
       <c r="K128" t="s">
         <v>142</v>
@@ -5735,34 +5736,34 @@
     </row>
     <row r="129" spans="1:12">
       <c r="A129" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B129" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C129" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="D129" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E129">
-        <v>7.5</v>
+        <v>18.5</v>
       </c>
       <c r="F129">
-        <v>7.53</v>
+        <v>19.47</v>
       </c>
       <c r="G129" s="1">
-        <v>0.5639999999999999</v>
+        <v>0.548</v>
       </c>
       <c r="H129" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I129" s="2">
-        <v>7.62</v>
+        <v>4.59</v>
       </c>
       <c r="J129" s="2">
-        <v>0.08400000000000001</v>
+        <v>0.0126</v>
       </c>
       <c r="K129" t="s">
         <v>142</v>
@@ -5773,34 +5774,34 @@
     </row>
     <row r="130" spans="1:12">
       <c r="A130" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="B130" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C130" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D130" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E130">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="F130">
-        <v>11.47</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="G130" s="1">
-        <v>0.5620000000000001</v>
+        <v>0.547</v>
       </c>
       <c r="H130" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I130" s="2">
-        <v>7.2</v>
+        <v>4.39</v>
       </c>
       <c r="J130" s="2">
-        <v>0.079</v>
+        <v>0.0121</v>
       </c>
       <c r="K130" t="s">
         <v>142</v>
@@ -5811,34 +5812,34 @@
     </row>
     <row r="131" spans="1:12">
       <c r="A131" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="B131" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C131" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D131" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E131">
-        <v>25.5</v>
+        <v>1.5</v>
       </c>
       <c r="F131">
-        <v>26.61</v>
+        <v>1.83</v>
       </c>
       <c r="G131" s="1">
-        <v>0.5590000000000001</v>
+        <v>0.546</v>
       </c>
       <c r="H131" t="s">
         <v>140</v>
       </c>
       <c r="I131" s="2">
-        <v>6.8</v>
+        <v>4.32</v>
       </c>
       <c r="J131" s="2">
-        <v>0.075</v>
+        <v>0.0119</v>
       </c>
       <c r="K131" t="s">
         <v>142</v>
@@ -5849,34 +5850,34 @@
     </row>
     <row r="132" spans="1:12">
       <c r="A132" t="s">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="B132" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="C132" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="D132" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E132">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="F132">
-        <v>2.45</v>
+        <v>7.95</v>
       </c>
       <c r="G132" s="1">
-        <v>0.5570000000000001</v>
+        <v>0.546</v>
       </c>
       <c r="H132" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I132" s="2">
-        <v>6.36</v>
+        <v>4.3</v>
       </c>
       <c r="J132" s="2">
-        <v>0.07000000000000001</v>
+        <v>0.0118</v>
       </c>
       <c r="K132" t="s">
         <v>142</v>
@@ -5887,34 +5888,34 @@
     </row>
     <row r="133" spans="1:12">
       <c r="A133" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="B133" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="C133" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D133" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E133">
-        <v>29.5</v>
+        <v>17.5</v>
       </c>
       <c r="F133">
-        <v>31.05</v>
+        <v>18.35</v>
       </c>
       <c r="G133" s="1">
-        <v>0.555</v>
+        <v>0.545</v>
       </c>
       <c r="H133" t="s">
         <v>140</v>
       </c>
       <c r="I133" s="2">
-        <v>5.87</v>
+        <v>4.03</v>
       </c>
       <c r="J133" s="2">
-        <v>0.065</v>
+        <v>0.0111</v>
       </c>
       <c r="K133" t="s">
         <v>142</v>
@@ -5925,37 +5926,37 @@
     </row>
     <row r="134" spans="1:12">
       <c r="A134" t="s">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="B134" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C134" t="s">
         <v>122</v>
       </c>
       <c r="D134" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E134">
         <v>1.5</v>
       </c>
       <c r="F134">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="G134" s="1">
-        <v>0.553</v>
+        <v>0.544</v>
       </c>
       <c r="H134" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I134" s="2">
-        <v>5.64</v>
+        <v>3.79</v>
       </c>
       <c r="J134" s="2">
-        <v>0.062</v>
+        <v>0.0052</v>
       </c>
       <c r="K134" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L134" t="s">
         <v>145</v>
@@ -5963,37 +5964,37 @@
     </row>
     <row r="135" spans="1:12">
       <c r="A135" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B135" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C135" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D135" t="s">
         <v>135</v>
       </c>
       <c r="E135">
-        <v>29.5</v>
+        <v>1.5</v>
       </c>
       <c r="F135">
-        <v>31.27</v>
+        <v>1.82</v>
       </c>
       <c r="G135" s="1">
-        <v>0.553</v>
+        <v>0.543</v>
       </c>
       <c r="H135" t="s">
         <v>140</v>
       </c>
       <c r="I135" s="2">
-        <v>5.63</v>
+        <v>3.72</v>
       </c>
       <c r="J135" s="2">
-        <v>0.062</v>
+        <v>0.0051</v>
       </c>
       <c r="K135" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L135" t="s">
         <v>145</v>
@@ -6001,37 +6002,37 @@
     </row>
     <row r="136" spans="1:12">
       <c r="A136" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="B136" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C136" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D136" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E136">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="F136">
-        <v>1.85</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G136" s="1">
-        <v>0.552</v>
+        <v>0.541</v>
       </c>
       <c r="H136" t="s">
         <v>140</v>
       </c>
       <c r="I136" s="2">
-        <v>5.47</v>
+        <v>3.21</v>
       </c>
       <c r="J136" s="2">
-        <v>0.06</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="K136" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L136" t="s">
         <v>145</v>
@@ -6039,37 +6040,37 @@
     </row>
     <row r="137" spans="1:12">
       <c r="A137" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="B137" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C137" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D137" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E137">
         <v>5.5</v>
       </c>
       <c r="F137">
-        <v>5.48</v>
+        <v>5.44</v>
       </c>
       <c r="G137" s="1">
-        <v>0.552</v>
+        <v>0.54</v>
       </c>
       <c r="H137" t="s">
         <v>139</v>
       </c>
       <c r="I137" s="2">
-        <v>5.4</v>
+        <v>3.09</v>
       </c>
       <c r="J137" s="2">
-        <v>0.059</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="K137" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L137" t="s">
         <v>145</v>
@@ -6077,37 +6078,37 @@
     </row>
     <row r="138" spans="1:12">
       <c r="A138" t="s">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="B138" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C138" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D138" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E138">
         <v>2.5</v>
       </c>
       <c r="F138">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
       <c r="G138" s="1">
-        <v>0.551</v>
+        <v>0.54</v>
       </c>
       <c r="H138" t="s">
         <v>139</v>
       </c>
       <c r="I138" s="2">
-        <v>5.11</v>
+        <v>3.06</v>
       </c>
       <c r="J138" s="2">
-        <v>0.056</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="K138" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L138" t="s">
         <v>145</v>
@@ -6115,37 +6116,37 @@
     </row>
     <row r="139" spans="1:12">
       <c r="A139" t="s">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="B139" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C139" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D139" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E139">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="F139">
-        <v>7.88</v>
+        <v>3.86</v>
       </c>
       <c r="G139" s="1">
-        <v>0.548</v>
+        <v>0.54</v>
       </c>
       <c r="H139" t="s">
         <v>140</v>
       </c>
       <c r="I139" s="2">
-        <v>4.57</v>
+        <v>3.03</v>
       </c>
       <c r="J139" s="2">
-        <v>0.05</v>
+        <v>0.0042</v>
       </c>
       <c r="K139" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L139" t="s">
         <v>145</v>
@@ -6153,37 +6154,37 @@
     </row>
     <row r="140" spans="1:12">
       <c r="A140" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="B140" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C140" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="D140" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E140">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F140">
-        <v>2.56</v>
+        <v>3.5</v>
       </c>
       <c r="G140" s="1">
-        <v>0.547</v>
+        <v>0.537</v>
       </c>
       <c r="H140" t="s">
         <v>139</v>
       </c>
       <c r="I140" s="2">
-        <v>4.44</v>
+        <v>2.48</v>
       </c>
       <c r="J140" s="2">
-        <v>0.049</v>
+        <v>0.0068</v>
       </c>
       <c r="K140" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L140" t="s">
         <v>145</v>
@@ -6191,37 +6192,37 @@
     </row>
     <row r="141" spans="1:12">
       <c r="A141" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B141" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="C141" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D141" t="s">
         <v>137</v>
       </c>
       <c r="E141">
-        <v>8.5</v>
+        <v>26.5</v>
       </c>
       <c r="F141">
-        <v>8.34</v>
+        <v>27.17</v>
       </c>
       <c r="G141" s="1">
-        <v>0.546</v>
+        <v>0.536</v>
       </c>
       <c r="H141" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I141" s="2">
-        <v>4.15</v>
+        <v>2.28</v>
       </c>
       <c r="J141" s="2">
-        <v>0.046</v>
+        <v>0.0031</v>
       </c>
       <c r="K141" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L141" t="s">
         <v>145</v>
@@ -6229,34 +6230,34 @@
     </row>
     <row r="142" spans="1:12">
       <c r="A142" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="B142" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C142" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D142" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E142">
-        <v>4.5</v>
+        <v>29.5</v>
       </c>
       <c r="F142">
-        <v>4.9</v>
+        <v>30.67</v>
       </c>
       <c r="G142" s="1">
-        <v>0.541</v>
+        <v>0.535</v>
       </c>
       <c r="H142" t="s">
         <v>140</v>
       </c>
       <c r="I142" s="2">
-        <v>3.38</v>
+        <v>2.18</v>
       </c>
       <c r="J142" s="2">
-        <v>0.037</v>
+        <v>0.006</v>
       </c>
       <c r="K142" t="s">
         <v>143</v>
@@ -6267,34 +6268,34 @@
     </row>
     <row r="143" spans="1:12">
       <c r="A143" t="s">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="B143" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C143" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D143" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E143">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="F143">
-        <v>2.8</v>
+        <v>9.83</v>
       </c>
       <c r="G143" s="1">
-        <v>0.539</v>
+        <v>0.534</v>
       </c>
       <c r="H143" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I143" s="2">
-        <v>2.97</v>
+        <v>1.9</v>
       </c>
       <c r="J143" s="2">
-        <v>0.033</v>
+        <v>0.0026</v>
       </c>
       <c r="K143" t="s">
         <v>143</v>
@@ -6305,34 +6306,34 @@
     </row>
     <row r="144" spans="1:12">
       <c r="A144" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="B144" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C144" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D144" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E144">
-        <v>3.5</v>
+        <v>22.5</v>
       </c>
       <c r="F144">
-        <v>3.86</v>
+        <v>23.4</v>
       </c>
       <c r="G144" s="1">
-        <v>0.539</v>
+        <v>0.532</v>
       </c>
       <c r="H144" t="s">
         <v>140</v>
       </c>
       <c r="I144" s="2">
-        <v>2.96</v>
+        <v>1.54</v>
       </c>
       <c r="J144" s="2">
-        <v>0.033</v>
+        <v>0.0021</v>
       </c>
       <c r="K144" t="s">
         <v>143</v>
@@ -6343,37 +6344,37 @@
     </row>
     <row r="145" spans="1:12">
       <c r="A145" t="s">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="B145" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C145" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="D145" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E145">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="F145">
-        <v>8.01</v>
+        <v>7.9</v>
       </c>
       <c r="G145" s="1">
-        <v>0.536</v>
+        <v>0.529</v>
       </c>
       <c r="H145" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I145" s="2">
-        <v>2.31</v>
+        <v>1</v>
       </c>
       <c r="J145" s="2">
-        <v>0.025</v>
+        <v>0.0014</v>
       </c>
       <c r="K145" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L145" t="s">
         <v>145</v>
@@ -6381,37 +6382,37 @@
     </row>
     <row r="146" spans="1:12">
       <c r="A146" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="B146" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="C146" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D146" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E146">
-        <v>1.5</v>
+        <v>19.5</v>
       </c>
       <c r="F146">
-        <v>1.79</v>
+        <v>19.05</v>
       </c>
       <c r="G146" s="1">
-        <v>0.535</v>
+        <v>0.527</v>
       </c>
       <c r="H146" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I146" s="2">
-        <v>2.13</v>
+        <v>0.66</v>
       </c>
       <c r="J146" s="2">
-        <v>0.023</v>
+        <v>0.0018</v>
       </c>
       <c r="K146" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L146" t="s">
         <v>145</v>
@@ -6419,37 +6420,37 @@
     </row>
     <row r="147" spans="1:12">
       <c r="A147" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="B147" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C147" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D147" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E147">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="F147">
-        <v>11.95</v>
+        <v>5.84</v>
       </c>
       <c r="G147" s="1">
-        <v>0.534</v>
+        <v>0.527</v>
       </c>
       <c r="H147" t="s">
         <v>140</v>
       </c>
       <c r="I147" s="2">
-        <v>1.89</v>
+        <v>0.62</v>
       </c>
       <c r="J147" s="2">
-        <v>0.021</v>
+        <v>0.0017</v>
       </c>
       <c r="K147" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L147" t="s">
         <v>145</v>
@@ -6457,34 +6458,34 @@
     </row>
     <row r="148" spans="1:12">
       <c r="A148" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="B148" t="s">
+        <v>126</v>
+      </c>
+      <c r="C148" t="s">
         <v>117</v>
       </c>
-      <c r="C148" t="s">
-        <v>127</v>
-      </c>
       <c r="D148" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E148">
-        <v>9.5</v>
+        <v>18.5</v>
       </c>
       <c r="F148">
-        <v>9.81</v>
+        <v>17.98</v>
       </c>
       <c r="G148" s="1">
-        <v>0.531</v>
+        <v>0.526</v>
       </c>
       <c r="H148" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I148" s="2">
-        <v>1.3</v>
+        <v>0.35</v>
       </c>
       <c r="J148" s="2">
-        <v>0.014</v>
+        <v>0.0005</v>
       </c>
       <c r="K148" t="s">
         <v>144</v>
@@ -6495,34 +6496,34 @@
     </row>
     <row r="149" spans="1:12">
       <c r="A149" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B149" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C149" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="D149" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E149">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="F149">
-        <v>3.21</v>
+        <v>7.63</v>
       </c>
       <c r="G149" s="1">
-        <v>0.529</v>
+        <v>0.525</v>
       </c>
       <c r="H149" t="s">
         <v>139</v>
       </c>
       <c r="I149" s="2">
-        <v>0.91</v>
+        <v>0.27</v>
       </c>
       <c r="J149" s="2">
-        <v>0.01</v>
+        <v>0.0004</v>
       </c>
       <c r="K149" t="s">
         <v>144</v>
@@ -6533,34 +6534,34 @@
     </row>
     <row r="150" spans="1:12">
       <c r="A150" t="s">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="B150" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C150" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D150" t="s">
         <v>136</v>
       </c>
       <c r="E150">
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="F150">
-        <v>4.52</v>
+        <v>11.78</v>
       </c>
       <c r="G150" s="1">
-        <v>0.528</v>
+        <v>0.525</v>
       </c>
       <c r="H150" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I150" s="2">
-        <v>0.77</v>
+        <v>0.23</v>
       </c>
       <c r="J150" s="2">
-        <v>0.008</v>
+        <v>0.0003</v>
       </c>
       <c r="K150" t="s">
         <v>144</v>
@@ -6571,34 +6572,34 @@
     </row>
     <row r="151" spans="1:12">
       <c r="A151" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B151" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C151" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D151" t="s">
         <v>135</v>
       </c>
       <c r="E151">
-        <v>25.5</v>
+        <v>1.5</v>
       </c>
       <c r="F151">
-        <v>26.29</v>
+        <v>1.76</v>
       </c>
       <c r="G151" s="1">
-        <v>0.526</v>
+        <v>0.525</v>
       </c>
       <c r="H151" t="s">
         <v>140</v>
       </c>
       <c r="I151" s="2">
-        <v>0.34</v>
+        <v>0.16</v>
       </c>
       <c r="J151" s="2">
-        <v>0.004</v>
+        <v>0.0004</v>
       </c>
       <c r="K151" t="s">
         <v>144</v>
@@ -6609,34 +6610,34 @@
     </row>
     <row r="152" spans="1:12">
       <c r="A152" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B152" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C152" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="D152" t="s">
         <v>136</v>
       </c>
       <c r="E152">
-        <v>2.5</v>
+        <v>11.5</v>
       </c>
       <c r="F152">
-        <v>2.78</v>
+        <v>11.83</v>
       </c>
       <c r="G152" s="1">
-        <v>0.525</v>
+        <v>0.524</v>
       </c>
       <c r="H152" t="s">
         <v>140</v>
       </c>
       <c r="I152" s="2">
-        <v>0.21</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J152" s="2">
-        <v>0.002</v>
+        <v>0.0001</v>
       </c>
       <c r="K152" t="s">
         <v>144</v>
@@ -6647,31 +6648,31 @@
     </row>
     <row r="153" spans="1:12">
       <c r="A153" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="B153" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C153" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="D153" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E153">
-        <v>22.5</v>
+        <v>29.5</v>
       </c>
       <c r="F153">
-        <v>21.95</v>
+        <v>30.16</v>
       </c>
       <c r="G153" s="1">
-        <v>0.521</v>
+        <v>0.523</v>
       </c>
       <c r="H153" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I153" s="2">
-        <v>-0.62</v>
+        <v>-0.12</v>
       </c>
       <c r="J153" s="2">
         <v>0</v>
@@ -6685,31 +6686,31 @@
     </row>
     <row r="154" spans="1:12">
       <c r="A154" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B154" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C154" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D154" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E154">
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="F154">
-        <v>8.210000000000001</v>
+        <v>12.89</v>
       </c>
       <c r="G154" s="1">
-        <v>0.516</v>
+        <v>0.52</v>
       </c>
       <c r="H154" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I154" s="2">
-        <v>-1.53</v>
+        <v>-0.66</v>
       </c>
       <c r="J154" s="2">
         <v>0</v>
@@ -6723,31 +6724,31 @@
     </row>
     <row r="155" spans="1:12">
       <c r="A155" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B155" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C155" t="s">
         <v>127</v>
       </c>
       <c r="D155" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E155">
-        <v>3.5</v>
+        <v>23.5</v>
       </c>
       <c r="F155">
-        <v>3.74</v>
+        <v>23.87</v>
       </c>
       <c r="G155" s="1">
-        <v>0.515</v>
+        <v>0.519</v>
       </c>
       <c r="H155" t="s">
         <v>140</v>
       </c>
       <c r="I155" s="2">
-        <v>-1.66</v>
+        <v>-0.85</v>
       </c>
       <c r="J155" s="2">
         <v>0</v>
@@ -6761,31 +6762,31 @@
     </row>
     <row r="156" spans="1:12">
       <c r="A156" t="s">
-        <v>30</v>
+        <v>113</v>
       </c>
       <c r="B156" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C156" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D156" t="s">
         <v>134</v>
       </c>
       <c r="E156">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="F156">
-        <v>13.78</v>
+        <v>3.65</v>
       </c>
       <c r="G156" s="1">
-        <v>0.515</v>
+        <v>0.519</v>
       </c>
       <c r="H156" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I156" s="2">
-        <v>-1.69</v>
+        <v>-0.99</v>
       </c>
       <c r="J156" s="2">
         <v>0</v>
@@ -6799,31 +6800,31 @@
     </row>
     <row r="157" spans="1:12">
       <c r="A157" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="B157" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C157" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D157" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E157">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="F157">
-        <v>16.71</v>
+        <v>11.13</v>
       </c>
       <c r="G157" s="1">
-        <v>0.515</v>
+        <v>0.518</v>
       </c>
       <c r="H157" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I157" s="2">
-        <v>-1.74</v>
+        <v>-1.16</v>
       </c>
       <c r="J157" s="2">
         <v>0</v>
@@ -6837,31 +6838,31 @@
     </row>
     <row r="158" spans="1:12">
       <c r="A158" t="s">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="B158" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C158" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="D158" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E158">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="F158">
-        <v>3.76</v>
+        <v>5.57</v>
       </c>
       <c r="G158" s="1">
-        <v>0.514</v>
+        <v>0.508</v>
       </c>
       <c r="H158" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I158" s="2">
-        <v>-1.9</v>
+        <v>-3.07</v>
       </c>
       <c r="J158" s="2">
         <v>0</v>
@@ -6875,31 +6876,31 @@
     </row>
     <row r="159" spans="1:12">
       <c r="A159" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="B159" t="s">
         <v>115</v>
       </c>
       <c r="C159" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D159" t="s">
         <v>136</v>
       </c>
       <c r="E159">
-        <v>2.5</v>
+        <v>24.5</v>
       </c>
       <c r="F159">
-        <v>2.65</v>
+        <v>24.72</v>
       </c>
       <c r="G159" s="1">
-        <v>0.506</v>
+        <v>0.508</v>
       </c>
       <c r="H159" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I159" s="2">
-        <v>-3.48</v>
+        <v>-3.1</v>
       </c>
       <c r="J159" s="2">
         <v>0</v>
@@ -6913,31 +6914,31 @@
     </row>
     <row r="160" spans="1:12">
       <c r="A160" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="B160" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C160" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="D160" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E160">
         <v>3.5</v>
       </c>
       <c r="F160">
-        <v>3.66</v>
+        <v>3.71</v>
       </c>
       <c r="G160" s="1">
-        <v>0.502</v>
+        <v>0.507</v>
       </c>
       <c r="H160" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I160" s="2">
-        <v>-4.24</v>
+        <v>-3.15</v>
       </c>
       <c r="J160" s="2">
         <v>0</v>
@@ -6951,31 +6952,31 @@
     </row>
     <row r="161" spans="1:12">
       <c r="A161" t="s">
-        <v>109</v>
+        <v>67</v>
       </c>
       <c r="B161" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C161" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D161" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E161">
-        <v>30.5</v>
+        <v>32.5</v>
       </c>
       <c r="F161">
-        <v>30.49</v>
+        <v>32.36</v>
       </c>
       <c r="G161" s="1">
-        <v>0.5</v>
+        <v>0.506</v>
       </c>
       <c r="H161" t="s">
         <v>139</v>
       </c>
       <c r="I161" s="2">
-        <v>-4.47</v>
+        <v>-3.45</v>
       </c>
       <c r="J161" s="2">
         <v>0</v>
@@ -6992,28 +6993,28 @@
         <v>106</v>
       </c>
       <c r="B162" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C162" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="D162" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E162">
         <v>2.5</v>
       </c>
       <c r="F162">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="G162" s="1">
-        <v>0.5</v>
+        <v>0.504</v>
       </c>
       <c r="H162" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I162" s="2">
-        <v>-4.49</v>
+        <v>-3.87</v>
       </c>
       <c r="J162" s="2">
         <v>0</v>
@@ -7025,8 +7026,84 @@
         <v>145</v>
       </c>
     </row>
+    <row r="163" spans="1:12">
+      <c r="A163" t="s">
+        <v>89</v>
+      </c>
+      <c r="B163" t="s">
+        <v>130</v>
+      </c>
+      <c r="C163" t="s">
+        <v>119</v>
+      </c>
+      <c r="D163" t="s">
+        <v>134</v>
+      </c>
+      <c r="E163">
+        <v>2.5</v>
+      </c>
+      <c r="F163">
+        <v>2.76</v>
+      </c>
+      <c r="G163" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="H163" t="s">
+        <v>139</v>
+      </c>
+      <c r="I163" s="2">
+        <v>-4.5</v>
+      </c>
+      <c r="J163" s="2">
+        <v>0</v>
+      </c>
+      <c r="K163" t="s">
+        <v>144</v>
+      </c>
+      <c r="L163" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12">
+      <c r="A164" t="s">
+        <v>18</v>
+      </c>
+      <c r="B164" t="s">
+        <v>117</v>
+      </c>
+      <c r="C164" t="s">
+        <v>126</v>
+      </c>
+      <c r="D164" t="s">
+        <v>136</v>
+      </c>
+      <c r="E164">
+        <v>24.5</v>
+      </c>
+      <c r="F164">
+        <v>24.51</v>
+      </c>
+      <c r="G164" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="H164" t="s">
+        <v>140</v>
+      </c>
+      <c r="I164" s="2">
+        <v>-4.5</v>
+      </c>
+      <c r="J164" s="2">
+        <v>0</v>
+      </c>
+      <c r="K164" t="s">
+        <v>144</v>
+      </c>
+      <c r="L164" t="s">
+        <v>145</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="K2:K162">
+  <conditionalFormatting sqref="K2:K164">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="S Tier">
       <formula>NOT(ISERROR(SEARCH("S Tier",K2)))</formula>
     </cfRule>

--- a/output/processed_props.xlsx
+++ b/output/processed_props.xlsx
@@ -58,91 +58,100 @@
     <t>Jonas Valanciunas</t>
   </si>
   <si>
+    <t>RJ Barrett</t>
+  </si>
+  <si>
     <t>Joel Embiid</t>
   </si>
   <si>
-    <t>RJ Barrett</t>
+    <t>Ayo Dosunmu</t>
+  </si>
+  <si>
+    <t>Kyshawn George</t>
   </si>
   <si>
     <t>Tim Hardaway Jr.</t>
   </si>
   <si>
-    <t>Ayo Dosunmu</t>
+    <t>Ryan Kalkbrenner</t>
   </si>
   <si>
     <t>Brandon Ingram</t>
   </si>
   <si>
+    <t>Desmond Bane</t>
+  </si>
+  <si>
     <t>Jalen Johnson</t>
   </si>
   <si>
+    <t>Jaylen Brown</t>
+  </si>
+  <si>
+    <t>CJ McCollum</t>
+  </si>
+  <si>
+    <t>Tyus Jones</t>
+  </si>
+  <si>
+    <t>Aaron Wiggins</t>
+  </si>
+  <si>
+    <t>Kawhi Leonard</t>
+  </si>
+  <si>
     <t>Derrick White</t>
   </si>
   <si>
-    <t>Desmond Bane</t>
-  </si>
-  <si>
-    <t>Aaron Wiggins</t>
-  </si>
-  <si>
-    <t>CJ McCollum</t>
+    <t>Jared McCain</t>
+  </si>
+  <si>
+    <t>Tyrese Maxey</t>
   </si>
   <si>
     <t>Chet Holmgren</t>
   </si>
   <si>
+    <t>Bilal Coulibaly</t>
+  </si>
+  <si>
+    <t>Nikola Vucevic</t>
+  </si>
+  <si>
+    <t>LeBron James</t>
+  </si>
+  <si>
     <t>Brandon Miller</t>
   </si>
   <si>
-    <t>Tyus Jones</t>
-  </si>
-  <si>
     <t>Dyson Daniels</t>
   </si>
   <si>
-    <t>Jared McCain</t>
-  </si>
-  <si>
-    <t>Tyrese Maxey</t>
-  </si>
-  <si>
-    <t>Bilal Coulibaly</t>
-  </si>
-  <si>
-    <t>Kawhi Leonard</t>
-  </si>
-  <si>
-    <t>Ryan Kalkbrenner</t>
+    <t>Jaylon Tyson</t>
+  </si>
+  <si>
+    <t>Bub Carrington</t>
+  </si>
+  <si>
+    <t>Cam Thomas</t>
   </si>
   <si>
     <t>Jock Landale</t>
   </si>
   <si>
-    <t>Nikola Vucevic</t>
+    <t>Donovan Mitchell</t>
   </si>
   <si>
     <t>LaMelo Ball</t>
   </si>
   <si>
-    <t>Jaylen Brown</t>
-  </si>
-  <si>
-    <t>Cam Thomas</t>
+    <t>Anthony Edwards</t>
   </si>
   <si>
     <t>Brook Lopez</t>
   </si>
   <si>
-    <t>Jaylon Tyson</t>
-  </si>
-  <si>
-    <t>Donovan Mitchell</t>
-  </si>
-  <si>
-    <t>Bub Carrington</t>
-  </si>
-  <si>
-    <t>Kyshawn George</t>
+    <t>Tristan Vukcevic</t>
   </si>
   <si>
     <t>Kristaps Porzingis</t>
@@ -151,210 +160,201 @@
     <t>Immanuel Quickley</t>
   </si>
   <si>
-    <t>Anthony Edwards</t>
+    <t>Neemias Queta</t>
+  </si>
+  <si>
+    <t>Kris Dunn</t>
   </si>
   <si>
     <t>Grant Williams</t>
   </si>
   <si>
-    <t>Neemias Queta</t>
-  </si>
-  <si>
-    <t>Kris Dunn</t>
+    <t>Kyle Kuzma</t>
+  </si>
+  <si>
+    <t>Jaden McDaniels</t>
+  </si>
+  <si>
+    <t>Jalen Suggs</t>
+  </si>
+  <si>
+    <t>Brandin Podziemski</t>
+  </si>
+  <si>
+    <t>Egor Demin</t>
+  </si>
+  <si>
+    <t>Draymond Green</t>
+  </si>
+  <si>
+    <t>Nic Claxton</t>
+  </si>
+  <si>
+    <t>Jamal Shead</t>
+  </si>
+  <si>
+    <t>De'Anthony Melton</t>
+  </si>
+  <si>
+    <t>Anthony Black</t>
+  </si>
+  <si>
+    <t>Ryan Rollins</t>
+  </si>
+  <si>
+    <t>Bennedict Mathurin</t>
   </si>
   <si>
     <t>Al Horford</t>
   </si>
   <si>
-    <t>Jalen Suggs</t>
-  </si>
-  <si>
-    <t>Kyle Kuzma</t>
-  </si>
-  <si>
-    <t>Nic Claxton</t>
-  </si>
-  <si>
-    <t>Egor Demin</t>
-  </si>
-  <si>
-    <t>Jaden McDaniels</t>
-  </si>
-  <si>
-    <t>Draymond Green</t>
-  </si>
-  <si>
-    <t>Anthony Black</t>
+    <t>Daniel Gafford</t>
+  </si>
+  <si>
+    <t>Julius Randle</t>
+  </si>
+  <si>
+    <t>Onyeka Okongwu</t>
+  </si>
+  <si>
+    <t>Naz Reid</t>
+  </si>
+  <si>
+    <t>Kevin Porter Jr.</t>
+  </si>
+  <si>
+    <t>Jarrett Allen</t>
+  </si>
+  <si>
+    <t>Evan Mobley</t>
+  </si>
+  <si>
+    <t>Corey Kispert</t>
+  </si>
+  <si>
+    <t>Isaiah Joe</t>
+  </si>
+  <si>
+    <t>VJ Edgecombe</t>
+  </si>
+  <si>
+    <t>Sam Merrill</t>
   </si>
   <si>
     <t>Kon Knueppel</t>
   </si>
   <si>
-    <t>Brandin Podziemski</t>
-  </si>
-  <si>
-    <t>Tristan Vukcevic</t>
-  </si>
-  <si>
-    <t>De'Anthony Melton</t>
+    <t>Dennis Schroder</t>
+  </si>
+  <si>
+    <t>Julian Strawther</t>
+  </si>
+  <si>
+    <t>Klay Thompson</t>
+  </si>
+  <si>
+    <t>Payton Pritchard</t>
   </si>
   <si>
     <t>Nolan Traore</t>
   </si>
   <si>
-    <t>Julius Randle</t>
-  </si>
-  <si>
-    <t>Evan Mobley</t>
+    <t>Cason Wallace</t>
+  </si>
+  <si>
+    <t>Donte DiVincenzo</t>
+  </si>
+  <si>
+    <t>Jamal Murray</t>
+  </si>
+  <si>
+    <t>Wendell Carter Jr.</t>
+  </si>
+  <si>
+    <t>Luka Doncic</t>
+  </si>
+  <si>
+    <t>Austin Reaves</t>
+  </si>
+  <si>
+    <t>Derrick Jones Jr.</t>
+  </si>
+  <si>
+    <t>Naji Marshall</t>
+  </si>
+  <si>
+    <t>Paolo Banchero</t>
+  </si>
+  <si>
+    <t>Marcus Smart</t>
+  </si>
+  <si>
+    <t>Myles Turner</t>
+  </si>
+  <si>
+    <t>Dominick Barlow</t>
+  </si>
+  <si>
+    <t>Pat Spencer</t>
+  </si>
+  <si>
+    <t>James Harden</t>
+  </si>
+  <si>
+    <t>Nickeil Alexander-Walker</t>
+  </si>
+  <si>
+    <t>Rui Hachimura</t>
+  </si>
+  <si>
+    <t>Noah Clowney</t>
+  </si>
+  <si>
+    <t>Gui Santos</t>
+  </si>
+  <si>
+    <t>Isaiah Hartenstein</t>
+  </si>
+  <si>
+    <t>Deandre Ayton</t>
+  </si>
+  <si>
+    <t>Nikola Jokic</t>
+  </si>
+  <si>
+    <t>Michael Porter Jr.</t>
+  </si>
+  <si>
+    <t>Collin Murray-Boyles</t>
   </si>
   <si>
     <t>Sam Hauser</t>
   </si>
   <si>
-    <t>Klay Thompson</t>
-  </si>
-  <si>
-    <t>Daniel Gafford</t>
-  </si>
-  <si>
-    <t>Bennedict Mathurin</t>
-  </si>
-  <si>
-    <t>Jarrett Allen</t>
-  </si>
-  <si>
-    <t>Dennis Schroder</t>
-  </si>
-  <si>
-    <t>Kevin Porter Jr.</t>
-  </si>
-  <si>
-    <t>Jamal Shead</t>
-  </si>
-  <si>
-    <t>Ryan Rollins</t>
-  </si>
-  <si>
-    <t>Sam Merrill</t>
-  </si>
-  <si>
-    <t>Onyeka Okongwu</t>
-  </si>
-  <si>
-    <t>LeBron James</t>
-  </si>
-  <si>
-    <t>Naz Reid</t>
-  </si>
-  <si>
-    <t>Corey Kispert</t>
-  </si>
-  <si>
-    <t>Payton Pritchard</t>
-  </si>
-  <si>
-    <t>Cason Wallace</t>
-  </si>
-  <si>
-    <t>Wendell Carter Jr.</t>
-  </si>
-  <si>
-    <t>VJ Edgecombe</t>
-  </si>
-  <si>
-    <t>Jamal Murray</t>
-  </si>
-  <si>
-    <t>Julian Strawther</t>
-  </si>
-  <si>
-    <t>Austin Reaves</t>
-  </si>
-  <si>
-    <t>Isaiah Joe</t>
-  </si>
-  <si>
-    <t>Naji Marshall</t>
-  </si>
-  <si>
-    <t>Paolo Banchero</t>
-  </si>
-  <si>
-    <t>Derrick Jones Jr.</t>
-  </si>
-  <si>
-    <t>Marcus Smart</t>
-  </si>
-  <si>
-    <t>Donte DiVincenzo</t>
-  </si>
-  <si>
-    <t>Luka Doncic</t>
-  </si>
-  <si>
-    <t>Dominick Barlow</t>
-  </si>
-  <si>
-    <t>Nickeil Alexander-Walker</t>
-  </si>
-  <si>
-    <t>Gui Santos</t>
-  </si>
-  <si>
-    <t>Myles Turner</t>
-  </si>
-  <si>
-    <t>James Harden</t>
-  </si>
-  <si>
-    <t>Rui Hachimura</t>
-  </si>
-  <si>
-    <t>Noah Clowney</t>
-  </si>
-  <si>
     <t>Quentin Grimes</t>
   </si>
   <si>
-    <t>Pat Spencer</t>
-  </si>
-  <si>
-    <t>Nikola Jokic</t>
-  </si>
-  <si>
-    <t>Michael Porter Jr.</t>
-  </si>
-  <si>
-    <t>Isaiah Hartenstein</t>
-  </si>
-  <si>
-    <t>Collin Murray-Boyles</t>
-  </si>
-  <si>
-    <t>Deandre Ayton</t>
+    <t>Baylor Scheierman</t>
+  </si>
+  <si>
+    <t>Zaccharie Risacher</t>
+  </si>
+  <si>
+    <t>Max Christie</t>
+  </si>
+  <si>
+    <t>Tre Johnson</t>
+  </si>
+  <si>
+    <t>Moses Moody</t>
   </si>
   <si>
     <t>AJ Green</t>
   </si>
   <si>
-    <t>Baylor Scheierman</t>
-  </si>
-  <si>
-    <t>Zaccharie Risacher</t>
-  </si>
-  <si>
-    <t>Max Christie</t>
-  </si>
-  <si>
     <t>Christian Braun</t>
   </si>
   <si>
-    <t>Tre Johnson</t>
-  </si>
-  <si>
-    <t>Moses Moody</t>
-  </si>
-  <si>
     <t>Dean Wade</t>
   </si>
   <si>
@@ -364,10 +364,19 @@
     <t>DEN</t>
   </si>
   <si>
+    <t>TOR</t>
+  </si>
+  <si>
     <t>PHI</t>
   </si>
   <si>
-    <t>TOR</t>
+    <t>WSH</t>
+  </si>
+  <si>
+    <t>CHA</t>
+  </si>
+  <si>
+    <t>ORL</t>
   </si>
   <si>
     <t>ATL</t>
@@ -376,39 +385,30 @@
     <t>BOS</t>
   </si>
   <si>
-    <t>ORL</t>
+    <t>DAL</t>
   </si>
   <si>
     <t>OKC</t>
   </si>
   <si>
-    <t>CHA</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>WSH</t>
-  </si>
-  <si>
     <t>LAC</t>
   </si>
   <si>
+    <t>LAL</t>
+  </si>
+  <si>
+    <t>CLE</t>
+  </si>
+  <si>
     <t>MIL</t>
   </si>
   <si>
-    <t>CLE</t>
-  </si>
-  <si>
     <t>GS</t>
   </si>
   <si>
     <t>BKN</t>
   </si>
   <si>
-    <t>LAL</t>
-  </si>
-  <si>
     <t>GSW</t>
   </si>
   <si>
@@ -424,10 +424,10 @@
     <t>AST</t>
   </si>
   <si>
+    <t>PRA</t>
+  </si>
+  <si>
     <t>PTS</t>
-  </si>
-  <si>
-    <t>PRA</t>
   </si>
   <si>
     <t>RA</t>
@@ -916,7 +916,7 @@
         <v>114</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D2" t="s">
         <v>134</v>
@@ -925,19 +925,19 @@
         <v>5.5</v>
       </c>
       <c r="F2">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="G2" s="1">
-        <v>0.918</v>
+        <v>0.921</v>
       </c>
       <c r="H2" t="s">
         <v>139</v>
       </c>
       <c r="I2" s="2">
-        <v>75.23999999999999</v>
+        <v>75.87</v>
       </c>
       <c r="J2" s="2">
-        <v>0.1035</v>
+        <v>0.1043</v>
       </c>
       <c r="K2" t="s">
         <v>141</v>
@@ -963,19 +963,19 @@
         <v>1.5</v>
       </c>
       <c r="F3">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="G3" s="1">
-        <v>0.848</v>
+        <v>0.854</v>
       </c>
       <c r="H3" t="s">
         <v>139</v>
       </c>
       <c r="I3" s="2">
-        <v>61.8</v>
+        <v>62.96</v>
       </c>
       <c r="J3" s="2">
-        <v>0.17</v>
+        <v>0.1731</v>
       </c>
       <c r="K3" t="s">
         <v>141</v>
@@ -992,28 +992,28 @@
         <v>116</v>
       </c>
       <c r="C4" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D4" t="s">
         <v>136</v>
       </c>
       <c r="E4">
-        <v>26.5</v>
+        <v>27.5</v>
       </c>
       <c r="F4">
-        <v>31.32</v>
+        <v>22.68</v>
       </c>
       <c r="G4" s="1">
-        <v>0.778</v>
+        <v>0.796</v>
       </c>
       <c r="H4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I4" s="2">
-        <v>48.61</v>
+        <v>52.05</v>
       </c>
       <c r="J4" s="2">
-        <v>0.1337</v>
+        <v>0.0716</v>
       </c>
       <c r="K4" t="s">
         <v>141</v>
@@ -1030,28 +1030,28 @@
         <v>117</v>
       </c>
       <c r="C5" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D5" t="s">
         <v>137</v>
       </c>
       <c r="E5">
-        <v>27.5</v>
+        <v>26.5</v>
       </c>
       <c r="F5">
-        <v>23.21</v>
+        <v>31.53</v>
       </c>
       <c r="G5" s="1">
-        <v>0.77</v>
+        <v>0.788</v>
       </c>
       <c r="H5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I5" s="2">
-        <v>46.94</v>
+        <v>50.45</v>
       </c>
       <c r="J5" s="2">
-        <v>0.0645</v>
+        <v>0.1387</v>
       </c>
       <c r="K5" t="s">
         <v>141</v>
@@ -1065,19 +1065,19 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C6" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="D6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E6">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="F6">
-        <v>0.96</v>
+        <v>2.34</v>
       </c>
       <c r="G6" s="1">
         <v>0.758</v>
@@ -1086,10 +1086,10 @@
         <v>139</v>
       </c>
       <c r="I6" s="2">
-        <v>44.65</v>
+        <v>44.64</v>
       </c>
       <c r="J6" s="2">
-        <v>0.1228</v>
+        <v>0.0614</v>
       </c>
       <c r="K6" t="s">
         <v>141</v>
@@ -1103,31 +1103,31 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E7">
-        <v>3.5</v>
+        <v>12.5</v>
       </c>
       <c r="F7">
-        <v>2.35</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G7" s="1">
-        <v>0.757</v>
+        <v>0.749</v>
       </c>
       <c r="H7" t="s">
         <v>139</v>
       </c>
       <c r="I7" s="2">
-        <v>44.46</v>
+        <v>43</v>
       </c>
       <c r="J7" s="2">
-        <v>0.0611</v>
+        <v>0.0591</v>
       </c>
       <c r="K7" t="s">
         <v>141</v>
@@ -1141,31 +1141,31 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C8" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D8" t="s">
         <v>135</v>
       </c>
       <c r="E8">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="F8">
-        <v>2.46</v>
+        <v>0.99</v>
       </c>
       <c r="G8" s="1">
-        <v>0.749</v>
+        <v>0.746</v>
       </c>
       <c r="H8" t="s">
         <v>139</v>
       </c>
       <c r="I8" s="2">
-        <v>42.94</v>
+        <v>42.43</v>
       </c>
       <c r="J8" s="2">
-        <v>0.1181</v>
+        <v>0.1167</v>
       </c>
       <c r="K8" t="s">
         <v>141</v>
@@ -1179,31 +1179,31 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E9">
         <v>7.5</v>
       </c>
       <c r="F9">
-        <v>5.41</v>
+        <v>5.99</v>
       </c>
       <c r="G9" s="1">
-        <v>0.743</v>
+        <v>0.746</v>
       </c>
       <c r="H9" t="s">
         <v>139</v>
       </c>
       <c r="I9" s="2">
-        <v>41.76</v>
+        <v>42.42</v>
       </c>
       <c r="J9" s="2">
-        <v>0.1148</v>
+        <v>0.0583</v>
       </c>
       <c r="K9" t="s">
         <v>141</v>
@@ -1217,31 +1217,31 @@
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C10" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D10" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E10">
-        <v>27.5</v>
+        <v>3.5</v>
       </c>
       <c r="F10">
-        <v>23.54</v>
+        <v>2.5</v>
       </c>
       <c r="G10" s="1">
-        <v>0.738</v>
+        <v>0.742</v>
       </c>
       <c r="H10" t="s">
         <v>139</v>
       </c>
       <c r="I10" s="2">
-        <v>40.96</v>
+        <v>41.73</v>
       </c>
       <c r="J10" s="2">
-        <v>0.0563</v>
+        <v>0.1148</v>
       </c>
       <c r="K10" t="s">
         <v>141</v>
@@ -1261,25 +1261,25 @@
         <v>125</v>
       </c>
       <c r="D11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E11">
         <v>25.5</v>
       </c>
       <c r="F11">
-        <v>30.11</v>
+        <v>30.44</v>
       </c>
       <c r="G11" s="1">
-        <v>0.728</v>
+        <v>0.742</v>
       </c>
       <c r="H11" t="s">
         <v>140</v>
       </c>
       <c r="I11" s="2">
-        <v>38.94</v>
+        <v>41.68</v>
       </c>
       <c r="J11" s="2">
-        <v>0.1071</v>
+        <v>0.1146</v>
       </c>
       <c r="K11" t="s">
         <v>141</v>
@@ -1296,28 +1296,28 @@
         <v>121</v>
       </c>
       <c r="C12" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E12">
-        <v>20.5</v>
+        <v>7.5</v>
       </c>
       <c r="F12">
-        <v>16.5</v>
+        <v>5.46</v>
       </c>
       <c r="G12" s="1">
-        <v>0.725</v>
+        <v>0.739</v>
       </c>
       <c r="H12" t="s">
         <v>139</v>
       </c>
       <c r="I12" s="2">
-        <v>38.48</v>
+        <v>41.1</v>
       </c>
       <c r="J12" s="2">
-        <v>0.0529</v>
+        <v>0.113</v>
       </c>
       <c r="K12" t="s">
         <v>141</v>
@@ -1331,31 +1331,31 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E13">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F13">
-        <v>2.58</v>
+        <v>3.47</v>
       </c>
       <c r="G13" s="1">
-        <v>0.725</v>
+        <v>0.73</v>
       </c>
       <c r="H13" t="s">
         <v>139</v>
       </c>
       <c r="I13" s="2">
-        <v>38.37</v>
+        <v>39.44</v>
       </c>
       <c r="J13" s="2">
-        <v>0.1055</v>
+        <v>0.1085</v>
       </c>
       <c r="K13" t="s">
         <v>141</v>
@@ -1372,28 +1372,28 @@
         <v>121</v>
       </c>
       <c r="C14" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D14" t="s">
         <v>134</v>
       </c>
       <c r="E14">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="F14">
-        <v>6.51</v>
+        <v>2.56</v>
       </c>
       <c r="G14" s="1">
-        <v>0.722</v>
+        <v>0.728</v>
       </c>
       <c r="H14" t="s">
         <v>139</v>
       </c>
       <c r="I14" s="2">
-        <v>37.93</v>
+        <v>38.92</v>
       </c>
       <c r="J14" s="2">
-        <v>0.1043</v>
+        <v>0.107</v>
       </c>
       <c r="K14" t="s">
         <v>141</v>
@@ -1407,31 +1407,31 @@
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D15" t="s">
         <v>137</v>
       </c>
       <c r="E15">
-        <v>33.5</v>
+        <v>6.5</v>
       </c>
       <c r="F15">
-        <v>29</v>
+        <v>5.44</v>
       </c>
       <c r="G15" s="1">
-        <v>0.722</v>
+        <v>0.727</v>
       </c>
       <c r="H15" t="s">
         <v>139</v>
       </c>
       <c r="I15" s="2">
-        <v>37.8</v>
+        <v>38.7</v>
       </c>
       <c r="J15" s="2">
-        <v>0.1039</v>
+        <v>0.0532</v>
       </c>
       <c r="K15" t="s">
         <v>141</v>
@@ -1445,31 +1445,31 @@
         <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C16" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D16" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E16">
-        <v>6.5</v>
+        <v>14.5</v>
       </c>
       <c r="F16">
-        <v>5.47</v>
+        <v>11.11</v>
       </c>
       <c r="G16" s="1">
-        <v>0.72</v>
+        <v>0.724</v>
       </c>
       <c r="H16" t="s">
         <v>139</v>
       </c>
       <c r="I16" s="2">
-        <v>37.5</v>
+        <v>38.14</v>
       </c>
       <c r="J16" s="2">
-        <v>0.0516</v>
+        <v>0.0524</v>
       </c>
       <c r="K16" t="s">
         <v>141</v>
@@ -1483,31 +1483,31 @@
         <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C17" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="D17" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E17">
-        <v>23.5</v>
+        <v>4.5</v>
       </c>
       <c r="F17">
-        <v>19.05</v>
+        <v>3.45</v>
       </c>
       <c r="G17" s="1">
-        <v>0.72</v>
+        <v>0.722</v>
       </c>
       <c r="H17" t="s">
         <v>139</v>
       </c>
       <c r="I17" s="2">
-        <v>37.49</v>
+        <v>37.85</v>
       </c>
       <c r="J17" s="2">
-        <v>0.1031</v>
+        <v>0.052</v>
       </c>
       <c r="K17" t="s">
         <v>141</v>
@@ -1521,31 +1521,31 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E18">
-        <v>2.5</v>
+        <v>27.5</v>
       </c>
       <c r="F18">
-        <v>1.85</v>
+        <v>23.89</v>
       </c>
       <c r="G18" s="1">
-        <v>0.718</v>
+        <v>0.72</v>
       </c>
       <c r="H18" t="s">
         <v>139</v>
       </c>
       <c r="I18" s="2">
-        <v>37.05</v>
+        <v>37.36</v>
       </c>
       <c r="J18" s="2">
-        <v>0.0509</v>
+        <v>0.0514</v>
       </c>
       <c r="K18" t="s">
         <v>141</v>
@@ -1559,31 +1559,31 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="C19" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="D19" t="s">
         <v>135</v>
       </c>
       <c r="E19">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="F19">
-        <v>5.01</v>
+        <v>1.84</v>
       </c>
       <c r="G19" s="1">
-        <v>0.716</v>
+        <v>0.719</v>
       </c>
       <c r="H19" t="s">
         <v>139</v>
       </c>
       <c r="I19" s="2">
-        <v>36.78</v>
+        <v>37.3</v>
       </c>
       <c r="J19" s="2">
-        <v>0.1011</v>
+        <v>0.0513</v>
       </c>
       <c r="K19" t="s">
         <v>141</v>
@@ -1597,31 +1597,31 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C20" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E20">
-        <v>10.5</v>
+        <v>6.5</v>
       </c>
       <c r="F20">
-        <v>12.87</v>
+        <v>4.99</v>
       </c>
       <c r="G20" s="1">
-        <v>0.714</v>
+        <v>0.719</v>
       </c>
       <c r="H20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I20" s="2">
-        <v>36.24</v>
+        <v>37.17</v>
       </c>
       <c r="J20" s="2">
-        <v>0.09959999999999999</v>
+        <v>0.1022</v>
       </c>
       <c r="K20" t="s">
         <v>141</v>
@@ -1635,31 +1635,31 @@
         <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C21" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="D21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E21">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="F21">
-        <v>3.51</v>
+        <v>6.56</v>
       </c>
       <c r="G21" s="1">
-        <v>0.712</v>
+        <v>0.718</v>
       </c>
       <c r="H21" t="s">
         <v>139</v>
       </c>
       <c r="I21" s="2">
-        <v>35.99</v>
+        <v>37.16</v>
       </c>
       <c r="J21" s="2">
-        <v>0.0495</v>
+        <v>0.1022</v>
       </c>
       <c r="K21" t="s">
         <v>141</v>
@@ -1673,31 +1673,31 @@
         <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C22" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="D22" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E22">
-        <v>7.5</v>
+        <v>10.5</v>
       </c>
       <c r="F22">
-        <v>6.24</v>
+        <v>12.91</v>
       </c>
       <c r="G22" s="1">
-        <v>0.711</v>
+        <v>0.718</v>
       </c>
       <c r="H22" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I22" s="2">
-        <v>35.67</v>
+        <v>36.98</v>
       </c>
       <c r="J22" s="2">
-        <v>0.049</v>
+        <v>0.1017</v>
       </c>
       <c r="K22" t="s">
         <v>141</v>
@@ -1711,31 +1711,31 @@
         <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C23" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D23" t="s">
         <v>135</v>
       </c>
       <c r="E23">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F23">
-        <v>1.17</v>
+        <v>1.87</v>
       </c>
       <c r="G23" s="1">
-        <v>0.709</v>
+        <v>0.715</v>
       </c>
       <c r="H23" t="s">
         <v>139</v>
       </c>
       <c r="I23" s="2">
-        <v>35.35</v>
+        <v>36.58</v>
       </c>
       <c r="J23" s="2">
-        <v>0.09719999999999999</v>
+        <v>0.0503</v>
       </c>
       <c r="K23" t="s">
         <v>141</v>
@@ -1749,31 +1749,31 @@
         <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C24" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D24" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E24">
-        <v>2.5</v>
+        <v>19.5</v>
       </c>
       <c r="F24">
-        <v>1.96</v>
+        <v>14.55</v>
       </c>
       <c r="G24" s="1">
-        <v>0.697</v>
+        <v>0.712</v>
       </c>
       <c r="H24" t="s">
         <v>139</v>
       </c>
       <c r="I24" s="2">
-        <v>33.1</v>
+        <v>35.97</v>
       </c>
       <c r="J24" s="2">
-        <v>0.0455</v>
+        <v>0.0989</v>
       </c>
       <c r="K24" t="s">
         <v>141</v>
@@ -1787,31 +1787,31 @@
         <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C25" t="s">
         <v>132</v>
       </c>
       <c r="D25" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E25">
-        <v>7.5</v>
+        <v>33.5</v>
       </c>
       <c r="F25">
-        <v>6.33</v>
+        <v>29.26</v>
       </c>
       <c r="G25" s="1">
-        <v>0.697</v>
+        <v>0.71</v>
       </c>
       <c r="H25" t="s">
         <v>139</v>
       </c>
       <c r="I25" s="2">
-        <v>33.07</v>
+        <v>35.61</v>
       </c>
       <c r="J25" s="2">
-        <v>0.09089999999999999</v>
+        <v>0.0979</v>
       </c>
       <c r="K25" t="s">
         <v>141</v>
@@ -1825,31 +1825,31 @@
         <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C26" t="s">
         <v>130</v>
       </c>
       <c r="D26" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E26">
-        <v>4.5</v>
+        <v>23.5</v>
       </c>
       <c r="F26">
-        <v>3.66</v>
+        <v>19.35</v>
       </c>
       <c r="G26" s="1">
-        <v>0.694</v>
+        <v>0.707</v>
       </c>
       <c r="H26" t="s">
         <v>139</v>
       </c>
       <c r="I26" s="2">
-        <v>32.53</v>
+        <v>34.95</v>
       </c>
       <c r="J26" s="2">
-        <v>0.08939999999999999</v>
+        <v>0.0961</v>
       </c>
       <c r="K26" t="s">
         <v>141</v>
@@ -1863,31 +1863,31 @@
         <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C27" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D27" t="s">
         <v>135</v>
       </c>
       <c r="E27">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F27">
-        <v>2.08</v>
+        <v>1.34</v>
       </c>
       <c r="G27" s="1">
-        <v>0.6919999999999999</v>
+        <v>0.705</v>
       </c>
       <c r="H27" t="s">
         <v>139</v>
       </c>
       <c r="I27" s="2">
-        <v>32.18</v>
+        <v>34.67</v>
       </c>
       <c r="J27" s="2">
-        <v>0.0442</v>
+        <v>0.0477</v>
       </c>
       <c r="K27" t="s">
         <v>141</v>
@@ -1901,31 +1901,31 @@
         <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D28" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E28">
-        <v>5.5</v>
+        <v>17.5</v>
       </c>
       <c r="F28">
-        <v>4.48</v>
+        <v>15.51</v>
       </c>
       <c r="G28" s="1">
-        <v>0.6919999999999999</v>
+        <v>0.704</v>
       </c>
       <c r="H28" t="s">
         <v>139</v>
       </c>
       <c r="I28" s="2">
-        <v>32.02</v>
+        <v>34.35</v>
       </c>
       <c r="J28" s="2">
-        <v>0.044</v>
+        <v>0.0945</v>
       </c>
       <c r="K28" t="s">
         <v>141</v>
@@ -1939,31 +1939,31 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C29" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D29" t="s">
         <v>135</v>
       </c>
       <c r="E29">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F29">
-        <v>1.39</v>
+        <v>2.04</v>
       </c>
       <c r="G29" s="1">
-        <v>0.6909999999999999</v>
+        <v>0.701</v>
       </c>
       <c r="H29" t="s">
         <v>139</v>
       </c>
       <c r="I29" s="2">
-        <v>31.94</v>
+        <v>33.78</v>
       </c>
       <c r="J29" s="2">
-        <v>0.0439</v>
+        <v>0.0465</v>
       </c>
       <c r="K29" t="s">
         <v>141</v>
@@ -1977,31 +1977,31 @@
         <v>40</v>
       </c>
       <c r="B30" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C30" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D30" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E30">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="F30">
-        <v>2.83</v>
+        <v>1.19</v>
       </c>
       <c r="G30" s="1">
-        <v>0.6850000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="H30" t="s">
         <v>139</v>
       </c>
       <c r="I30" s="2">
-        <v>30.83</v>
+        <v>33.69</v>
       </c>
       <c r="J30" s="2">
-        <v>0.0848</v>
+        <v>0.0927</v>
       </c>
       <c r="K30" t="s">
         <v>141</v>
@@ -2015,31 +2015,31 @@
         <v>41</v>
       </c>
       <c r="B31" t="s">
+        <v>127</v>
+      </c>
+      <c r="C31" t="s">
         <v>124</v>
       </c>
-      <c r="C31" t="s">
-        <v>122</v>
-      </c>
       <c r="D31" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E31">
-        <v>10.5</v>
+        <v>3.5</v>
       </c>
       <c r="F31">
-        <v>9.17</v>
+        <v>2.76</v>
       </c>
       <c r="G31" s="1">
-        <v>0.6850000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="H31" t="s">
         <v>139</v>
       </c>
       <c r="I31" s="2">
-        <v>30.75</v>
+        <v>33.68</v>
       </c>
       <c r="J31" s="2">
-        <v>0.08459999999999999</v>
+        <v>0.0926</v>
       </c>
       <c r="K31" t="s">
         <v>141</v>
@@ -2053,31 +2053,31 @@
         <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C32" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="D32" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E32">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="F32">
-        <v>3.04</v>
+        <v>6.35</v>
       </c>
       <c r="G32" s="1">
-        <v>0.6830000000000001</v>
+        <v>0.694</v>
       </c>
       <c r="H32" t="s">
         <v>139</v>
       </c>
       <c r="I32" s="2">
-        <v>30.33</v>
+        <v>32.48</v>
       </c>
       <c r="J32" s="2">
-        <v>0.0417</v>
+        <v>0.0893</v>
       </c>
       <c r="K32" t="s">
         <v>141</v>
@@ -2091,31 +2091,31 @@
         <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D33" t="s">
         <v>135</v>
       </c>
       <c r="E33">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="F33">
-        <v>1.31</v>
+        <v>2.83</v>
       </c>
       <c r="G33" s="1">
-        <v>0.68</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H33" t="s">
         <v>139</v>
       </c>
       <c r="I33" s="2">
-        <v>29.91</v>
+        <v>30.43</v>
       </c>
       <c r="J33" s="2">
-        <v>0.0411</v>
+        <v>0.0837</v>
       </c>
       <c r="K33" t="s">
         <v>141</v>
@@ -2129,31 +2129,31 @@
         <v>44</v>
       </c>
       <c r="B34" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C34" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D34" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E34">
-        <v>28.5</v>
+        <v>8.5</v>
       </c>
       <c r="F34">
-        <v>25.25</v>
+        <v>7.16</v>
       </c>
       <c r="G34" s="1">
-        <v>0.679</v>
+        <v>0.681</v>
       </c>
       <c r="H34" t="s">
         <v>139</v>
       </c>
       <c r="I34" s="2">
-        <v>29.69</v>
+        <v>30.02</v>
       </c>
       <c r="J34" s="2">
-        <v>0.0408</v>
+        <v>0.0413</v>
       </c>
       <c r="K34" t="s">
         <v>141</v>
@@ -2167,31 +2167,31 @@
         <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C35" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D35" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E35">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="F35">
-        <v>2.86</v>
+        <v>4.63</v>
       </c>
       <c r="G35" s="1">
-        <v>0.676</v>
+        <v>0.68</v>
       </c>
       <c r="H35" t="s">
         <v>139</v>
       </c>
       <c r="I35" s="2">
-        <v>29.02</v>
+        <v>29.77</v>
       </c>
       <c r="J35" s="2">
-        <v>0.0798</v>
+        <v>0.0409</v>
       </c>
       <c r="K35" t="s">
         <v>141</v>
@@ -2205,31 +2205,31 @@
         <v>46</v>
       </c>
       <c r="B36" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C36" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="D36" t="s">
         <v>135</v>
       </c>
       <c r="E36">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F36">
-        <v>2.05</v>
+        <v>1.31</v>
       </c>
       <c r="G36" s="1">
-        <v>0.674</v>
+        <v>0.68</v>
       </c>
       <c r="H36" t="s">
         <v>139</v>
       </c>
       <c r="I36" s="2">
-        <v>28.75</v>
+        <v>29.73</v>
       </c>
       <c r="J36" s="2">
-        <v>0.0395</v>
+        <v>0.0409</v>
       </c>
       <c r="K36" t="s">
         <v>141</v>
@@ -2243,31 +2243,31 @@
         <v>47</v>
       </c>
       <c r="B37" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C37" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D37" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E37">
-        <v>1.5</v>
+        <v>28.5</v>
       </c>
       <c r="F37">
-        <v>1.34</v>
+        <v>25.27</v>
       </c>
       <c r="G37" s="1">
-        <v>0.672</v>
+        <v>0.678</v>
       </c>
       <c r="H37" t="s">
         <v>139</v>
       </c>
       <c r="I37" s="2">
-        <v>28.3</v>
+        <v>29.46</v>
       </c>
       <c r="J37" s="2">
-        <v>0.0389</v>
+        <v>0.0405</v>
       </c>
       <c r="K37" t="s">
         <v>141</v>
@@ -2281,31 +2281,31 @@
         <v>48</v>
       </c>
       <c r="B38" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C38" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D38" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E38">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="F38">
-        <v>3.76</v>
+        <v>1.32</v>
       </c>
       <c r="G38" s="1">
-        <v>0.671</v>
+        <v>0.677</v>
       </c>
       <c r="H38" t="s">
         <v>139</v>
       </c>
       <c r="I38" s="2">
-        <v>28.12</v>
+        <v>29.33</v>
       </c>
       <c r="J38" s="2">
-        <v>0.07729999999999999</v>
+        <v>0.0403</v>
       </c>
       <c r="K38" t="s">
         <v>141</v>
@@ -2319,31 +2319,31 @@
         <v>49</v>
       </c>
       <c r="B39" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C39" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D39" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E39">
-        <v>16.5</v>
+        <v>4.5</v>
       </c>
       <c r="F39">
-        <v>13.46</v>
+        <v>3.74</v>
       </c>
       <c r="G39" s="1">
-        <v>0.671</v>
+        <v>0.675</v>
       </c>
       <c r="H39" t="s">
         <v>139</v>
       </c>
       <c r="I39" s="2">
-        <v>28.08</v>
+        <v>28.81</v>
       </c>
       <c r="J39" s="2">
-        <v>0.0386</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="K39" t="s">
         <v>141</v>
@@ -2357,31 +2357,31 @@
         <v>50</v>
       </c>
       <c r="B40" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C40" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D40" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E40">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F40">
-        <v>3.02</v>
+        <v>2.06</v>
       </c>
       <c r="G40" s="1">
-        <v>0.668</v>
+        <v>0.674</v>
       </c>
       <c r="H40" t="s">
         <v>139</v>
       </c>
       <c r="I40" s="2">
-        <v>27.48</v>
+        <v>28.58</v>
       </c>
       <c r="J40" s="2">
-        <v>0.0378</v>
+        <v>0.0393</v>
       </c>
       <c r="K40" t="s">
         <v>141</v>
@@ -2395,10 +2395,10 @@
         <v>51</v>
       </c>
       <c r="B41" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C41" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D41" t="s">
         <v>135</v>
@@ -2407,19 +2407,19 @@
         <v>2.5</v>
       </c>
       <c r="F41">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="G41" s="1">
-        <v>0.665</v>
+        <v>0.667</v>
       </c>
       <c r="H41" t="s">
         <v>139</v>
       </c>
       <c r="I41" s="2">
-        <v>27.04</v>
+        <v>27.33</v>
       </c>
       <c r="J41" s="2">
-        <v>0.0372</v>
+        <v>0.0376</v>
       </c>
       <c r="K41" t="s">
         <v>141</v>
@@ -2433,31 +2433,31 @@
         <v>52</v>
       </c>
       <c r="B42" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="C42" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D42" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E42">
-        <v>10.5</v>
+        <v>4.5</v>
       </c>
       <c r="F42">
-        <v>12.25</v>
+        <v>3.82</v>
       </c>
       <c r="G42" s="1">
-        <v>0.665</v>
+        <v>0.664</v>
       </c>
       <c r="H42" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I42" s="2">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="J42" s="2">
-        <v>0.074</v>
+        <v>0.0367</v>
       </c>
       <c r="K42" t="s">
         <v>141</v>
@@ -2471,31 +2471,31 @@
         <v>53</v>
       </c>
       <c r="B43" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C43" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D43" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E43">
         <v>3.5</v>
       </c>
       <c r="F43">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="G43" s="1">
-        <v>0.662</v>
+        <v>0.663</v>
       </c>
       <c r="H43" t="s">
         <v>139</v>
       </c>
       <c r="I43" s="2">
-        <v>26.29</v>
+        <v>26.59</v>
       </c>
       <c r="J43" s="2">
-        <v>0.0723</v>
+        <v>0.0366</v>
       </c>
       <c r="K43" t="s">
         <v>141</v>
@@ -2509,19 +2509,19 @@
         <v>54</v>
       </c>
       <c r="B44" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="C44" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D44" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E44">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F44">
-        <v>3.83</v>
+        <v>3.04</v>
       </c>
       <c r="G44" s="1">
         <v>0.661</v>
@@ -2530,7 +2530,7 @@
         <v>139</v>
       </c>
       <c r="I44" s="2">
-        <v>26.23</v>
+        <v>26.24</v>
       </c>
       <c r="J44" s="2">
         <v>0.0361</v>
@@ -2547,31 +2547,31 @@
         <v>55</v>
       </c>
       <c r="B45" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C45" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D45" t="s">
         <v>135</v>
       </c>
       <c r="E45">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F45">
-        <v>3.83</v>
+        <v>2.96</v>
       </c>
       <c r="G45" s="1">
-        <v>0.659</v>
+        <v>0.655</v>
       </c>
       <c r="H45" t="s">
         <v>139</v>
       </c>
       <c r="I45" s="2">
-        <v>25.81</v>
+        <v>25.11</v>
       </c>
       <c r="J45" s="2">
-        <v>0.0355</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="K45" t="s">
         <v>141</v>
@@ -2585,19 +2585,19 @@
         <v>56</v>
       </c>
       <c r="B46" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="C46" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D46" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E46">
-        <v>15.5</v>
+        <v>4.5</v>
       </c>
       <c r="F46">
-        <v>13.04</v>
+        <v>3.85</v>
       </c>
       <c r="G46" s="1">
         <v>0.655</v>
@@ -2606,10 +2606,10 @@
         <v>139</v>
       </c>
       <c r="I46" s="2">
-        <v>25.07</v>
+        <v>25.11</v>
       </c>
       <c r="J46" s="2">
-        <v>0.0689</v>
+        <v>0.0345</v>
       </c>
       <c r="K46" t="s">
         <v>141</v>
@@ -2623,31 +2623,31 @@
         <v>57</v>
       </c>
       <c r="B47" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C47" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="D47" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E47">
-        <v>20.5</v>
+        <v>10.5</v>
       </c>
       <c r="F47">
-        <v>23.28</v>
+        <v>12.14</v>
       </c>
       <c r="G47" s="1">
-        <v>0.653</v>
+        <v>0.655</v>
       </c>
       <c r="H47" t="s">
         <v>140</v>
       </c>
       <c r="I47" s="2">
-        <v>24.62</v>
+        <v>25.1</v>
       </c>
       <c r="J47" s="2">
-        <v>0.0677</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K47" t="s">
         <v>141</v>
@@ -2661,31 +2661,31 @@
         <v>58</v>
       </c>
       <c r="B48" t="s">
+        <v>116</v>
+      </c>
+      <c r="C48" t="s">
         <v>128</v>
       </c>
-      <c r="C48" t="s">
-        <v>115</v>
-      </c>
       <c r="D48" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E48">
-        <v>3.5</v>
+        <v>14.5</v>
       </c>
       <c r="F48">
-        <v>3.11</v>
+        <v>12.02</v>
       </c>
       <c r="G48" s="1">
-        <v>0.65</v>
+        <v>0.653</v>
       </c>
       <c r="H48" t="s">
         <v>139</v>
       </c>
       <c r="I48" s="2">
-        <v>24.11</v>
+        <v>24.62</v>
       </c>
       <c r="J48" s="2">
-        <v>0.0332</v>
+        <v>0.0339</v>
       </c>
       <c r="K48" t="s">
         <v>141</v>
@@ -2699,31 +2699,31 @@
         <v>59</v>
       </c>
       <c r="B49" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C49" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D49" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E49">
-        <v>5.5</v>
+        <v>19.5</v>
       </c>
       <c r="F49">
-        <v>4.82</v>
+        <v>22.13</v>
       </c>
       <c r="G49" s="1">
-        <v>0.648</v>
+        <v>0.652</v>
       </c>
       <c r="H49" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I49" s="2">
-        <v>23.62</v>
+        <v>24.53</v>
       </c>
       <c r="J49" s="2">
-        <v>0.0325</v>
+        <v>0.0337</v>
       </c>
       <c r="K49" t="s">
         <v>141</v>
@@ -2737,31 +2737,31 @@
         <v>60</v>
       </c>
       <c r="B50" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C50" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="D50" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E50">
-        <v>19.5</v>
+        <v>4.5</v>
       </c>
       <c r="F50">
-        <v>21.98</v>
+        <v>3.89</v>
       </c>
       <c r="G50" s="1">
-        <v>0.644</v>
+        <v>0.65</v>
       </c>
       <c r="H50" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I50" s="2">
-        <v>23.02</v>
+        <v>24.04</v>
       </c>
       <c r="J50" s="2">
-        <v>0.0316</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="K50" t="s">
         <v>141</v>
@@ -2775,31 +2775,31 @@
         <v>61</v>
       </c>
       <c r="B51" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C51" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D51" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E51">
         <v>4.5</v>
       </c>
       <c r="F51">
-        <v>6.05</v>
+        <v>5.54</v>
       </c>
       <c r="G51" s="1">
-        <v>0.644</v>
+        <v>0.649</v>
       </c>
       <c r="H51" t="s">
         <v>140</v>
       </c>
       <c r="I51" s="2">
-        <v>22.97</v>
+        <v>23.86</v>
       </c>
       <c r="J51" s="2">
-        <v>0.06320000000000001</v>
+        <v>0.0328</v>
       </c>
       <c r="K51" t="s">
         <v>141</v>
@@ -2810,34 +2810,34 @@
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="B52" t="s">
+        <v>125</v>
+      </c>
+      <c r="C52" t="s">
         <v>120</v>
-      </c>
-      <c r="C52" t="s">
-        <v>125</v>
       </c>
       <c r="D52" t="s">
         <v>135</v>
       </c>
       <c r="E52">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F52">
-        <v>3.02</v>
+        <v>3.34</v>
       </c>
       <c r="G52" s="1">
-        <v>0.642</v>
+        <v>0.648</v>
       </c>
       <c r="H52" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I52" s="2">
-        <v>22.57</v>
+        <v>23.72</v>
       </c>
       <c r="J52" s="2">
-        <v>0.031</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="K52" t="s">
         <v>141</v>
@@ -2848,34 +2848,34 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B53" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="C53" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D53" t="s">
         <v>136</v>
       </c>
       <c r="E53">
-        <v>21.5</v>
+        <v>16.5</v>
       </c>
       <c r="F53">
-        <v>18.43</v>
+        <v>13.92</v>
       </c>
       <c r="G53" s="1">
-        <v>0.642</v>
+        <v>0.646</v>
       </c>
       <c r="H53" t="s">
         <v>139</v>
       </c>
       <c r="I53" s="2">
-        <v>22.56</v>
+        <v>23.36</v>
       </c>
       <c r="J53" s="2">
-        <v>0.031</v>
+        <v>0.0321</v>
       </c>
       <c r="K53" t="s">
         <v>141</v>
@@ -2886,34 +2886,34 @@
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B54" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C54" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="D54" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E54">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="F54">
-        <v>2.31</v>
+        <v>6.62</v>
       </c>
       <c r="G54" s="1">
-        <v>0.642</v>
+        <v>0.645</v>
       </c>
       <c r="H54" t="s">
         <v>139</v>
       </c>
       <c r="I54" s="2">
-        <v>22.51</v>
+        <v>23.07</v>
       </c>
       <c r="J54" s="2">
-        <v>0.031</v>
+        <v>0.0317</v>
       </c>
       <c r="K54" t="s">
         <v>141</v>
@@ -2924,34 +2924,34 @@
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B55" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C55" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="D55" t="s">
         <v>137</v>
       </c>
       <c r="E55">
-        <v>14.5</v>
+        <v>21.5</v>
       </c>
       <c r="F55">
-        <v>17.05</v>
+        <v>18.42</v>
       </c>
       <c r="G55" s="1">
-        <v>0.641</v>
+        <v>0.643</v>
       </c>
       <c r="H55" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I55" s="2">
-        <v>22.31</v>
+        <v>22.68</v>
       </c>
       <c r="J55" s="2">
-        <v>0.0307</v>
+        <v>0.0312</v>
       </c>
       <c r="K55" t="s">
         <v>141</v>
@@ -2962,34 +2962,34 @@
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B56" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C56" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D56" t="s">
         <v>137</v>
       </c>
       <c r="E56">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="F56">
-        <v>15</v>
+        <v>16.68</v>
       </c>
       <c r="G56" s="1">
-        <v>0.641</v>
+        <v>0.639</v>
       </c>
       <c r="H56" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I56" s="2">
-        <v>22.31</v>
+        <v>21.93</v>
       </c>
       <c r="J56" s="2">
-        <v>0.0307</v>
+        <v>0.0603</v>
       </c>
       <c r="K56" t="s">
         <v>141</v>
@@ -3000,34 +3000,34 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B57" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C57" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="D57" t="s">
         <v>134</v>
       </c>
       <c r="E57">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="F57">
-        <v>6.69</v>
+        <v>7.69</v>
       </c>
       <c r="G57" s="1">
-        <v>0.638</v>
+        <v>0.636</v>
       </c>
       <c r="H57" t="s">
         <v>139</v>
       </c>
       <c r="I57" s="2">
-        <v>21.78</v>
+        <v>21.41</v>
       </c>
       <c r="J57" s="2">
-        <v>0.03</v>
+        <v>0.0294</v>
       </c>
       <c r="K57" t="s">
         <v>141</v>
@@ -3038,34 +3038,34 @@
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B58" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C58" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D58" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E58">
-        <v>2.5</v>
+        <v>11.5</v>
       </c>
       <c r="F58">
-        <v>3.28</v>
+        <v>13.13</v>
       </c>
       <c r="G58" s="1">
-        <v>0.637</v>
+        <v>0.636</v>
       </c>
       <c r="H58" t="s">
         <v>140</v>
       </c>
       <c r="I58" s="2">
-        <v>21.67</v>
+        <v>21.37</v>
       </c>
       <c r="J58" s="2">
-        <v>0.0596</v>
+        <v>0.0294</v>
       </c>
       <c r="K58" t="s">
         <v>141</v>
@@ -3076,34 +3076,34 @@
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B59" t="s">
         <v>127</v>
       </c>
       <c r="C59" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D59" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E59">
         <v>25.5</v>
       </c>
       <c r="F59">
-        <v>30.41</v>
+        <v>30.33</v>
       </c>
       <c r="G59" s="1">
-        <v>0.637</v>
+        <v>0.635</v>
       </c>
       <c r="H59" t="s">
         <v>140</v>
       </c>
       <c r="I59" s="2">
-        <v>21.65</v>
+        <v>21.25</v>
       </c>
       <c r="J59" s="2">
-        <v>0.0595</v>
+        <v>0.0584</v>
       </c>
       <c r="K59" t="s">
         <v>141</v>
@@ -3114,34 +3114,34 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B60" t="s">
         <v>127</v>
       </c>
       <c r="C60" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D60" t="s">
         <v>135</v>
       </c>
       <c r="E60">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F60">
-        <v>3.05</v>
+        <v>2.35</v>
       </c>
       <c r="G60" s="1">
-        <v>0.636</v>
+        <v>0.634</v>
       </c>
       <c r="H60" t="s">
         <v>139</v>
       </c>
       <c r="I60" s="2">
-        <v>21.38</v>
+        <v>20.97</v>
       </c>
       <c r="J60" s="2">
-        <v>0.0588</v>
+        <v>0.0288</v>
       </c>
       <c r="K60" t="s">
         <v>141</v>
@@ -3152,34 +3152,34 @@
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B61" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C61" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="D61" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E61">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="F61">
-        <v>13.12</v>
+        <v>11.56</v>
       </c>
       <c r="G61" s="1">
-        <v>0.635</v>
+        <v>0.633</v>
       </c>
       <c r="H61" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I61" s="2">
-        <v>21.26</v>
+        <v>20.78</v>
       </c>
       <c r="J61" s="2">
-        <v>0.0292</v>
+        <v>0.0571</v>
       </c>
       <c r="K61" t="s">
         <v>141</v>
@@ -3190,34 +3190,34 @@
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B62" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C62" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D62" t="s">
         <v>137</v>
       </c>
       <c r="E62">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="F62">
-        <v>12.32</v>
+        <v>14.9</v>
       </c>
       <c r="G62" s="1">
-        <v>0.635</v>
+        <v>0.632</v>
       </c>
       <c r="H62" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I62" s="2">
-        <v>21.16</v>
+        <v>20.74</v>
       </c>
       <c r="J62" s="2">
-        <v>0.0291</v>
+        <v>0.0285</v>
       </c>
       <c r="K62" t="s">
         <v>141</v>
@@ -3228,34 +3228,34 @@
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B63" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C63" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D63" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E63">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F63">
-        <v>5.44</v>
+        <v>3.17</v>
       </c>
       <c r="G63" s="1">
-        <v>0.633</v>
+        <v>0.63</v>
       </c>
       <c r="H63" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I63" s="2">
-        <v>20.78</v>
+        <v>20.27</v>
       </c>
       <c r="J63" s="2">
-        <v>0.0286</v>
+        <v>0.0558</v>
       </c>
       <c r="K63" t="s">
         <v>141</v>
@@ -3266,34 +3266,34 @@
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="B64" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C64" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D64" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E64">
-        <v>15.5</v>
+        <v>1.5</v>
       </c>
       <c r="F64">
-        <v>18.7</v>
+        <v>1.39</v>
       </c>
       <c r="G64" s="1">
-        <v>0.633</v>
+        <v>0.63</v>
       </c>
       <c r="H64" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I64" s="2">
-        <v>20.78</v>
+        <v>20.2</v>
       </c>
       <c r="J64" s="2">
-        <v>0.0286</v>
+        <v>0.0556</v>
       </c>
       <c r="K64" t="s">
         <v>141</v>
@@ -3304,34 +3304,34 @@
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B65" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C65" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="D65" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E65">
-        <v>1.5</v>
+        <v>30.5</v>
       </c>
       <c r="F65">
-        <v>1.39</v>
+        <v>32.67</v>
       </c>
       <c r="G65" s="1">
         <v>0.63</v>
       </c>
       <c r="H65" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I65" s="2">
-        <v>20.36</v>
+        <v>20.19</v>
       </c>
       <c r="J65" s="2">
-        <v>0.056</v>
+        <v>0.0555</v>
       </c>
       <c r="K65" t="s">
         <v>141</v>
@@ -3342,34 +3342,34 @@
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="B66" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C66" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D66" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E66">
-        <v>14.5</v>
+        <v>7.5</v>
       </c>
       <c r="F66">
-        <v>16.5</v>
+        <v>8.67</v>
       </c>
       <c r="G66" s="1">
-        <v>0.628</v>
+        <v>0.629</v>
       </c>
       <c r="H66" t="s">
         <v>140</v>
       </c>
       <c r="I66" s="2">
-        <v>19.86</v>
+        <v>20.12</v>
       </c>
       <c r="J66" s="2">
-        <v>0.0546</v>
+        <v>0.0277</v>
       </c>
       <c r="K66" t="s">
         <v>141</v>
@@ -3380,34 +3380,34 @@
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B67" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C67" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D67" t="s">
         <v>135</v>
       </c>
       <c r="E67">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="F67">
-        <v>5.92</v>
+        <v>3.08</v>
       </c>
       <c r="G67" s="1">
-        <v>0.628</v>
+        <v>0.629</v>
       </c>
       <c r="H67" t="s">
         <v>139</v>
       </c>
       <c r="I67" s="2">
-        <v>19.85</v>
+        <v>20.09</v>
       </c>
       <c r="J67" s="2">
-        <v>0.0546</v>
+        <v>0.0553</v>
       </c>
       <c r="K67" t="s">
         <v>141</v>
@@ -3418,34 +3418,34 @@
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B68" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C68" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="D68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E68">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="F68">
-        <v>7.75</v>
+        <v>2.18</v>
       </c>
       <c r="G68" s="1">
-        <v>0.627</v>
+        <v>0.628</v>
       </c>
       <c r="H68" t="s">
         <v>139</v>
       </c>
       <c r="I68" s="2">
-        <v>19.78</v>
+        <v>19.95</v>
       </c>
       <c r="J68" s="2">
-        <v>0.0272</v>
+        <v>0.0274</v>
       </c>
       <c r="K68" t="s">
         <v>141</v>
@@ -3456,34 +3456,34 @@
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B69" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C69" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D69" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E69">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="F69">
-        <v>11.67</v>
+        <v>15.25</v>
       </c>
       <c r="G69" s="1">
-        <v>0.625</v>
+        <v>0.627</v>
       </c>
       <c r="H69" t="s">
         <v>139</v>
       </c>
       <c r="I69" s="2">
-        <v>19.35</v>
+        <v>19.67</v>
       </c>
       <c r="J69" s="2">
-        <v>0.0532</v>
+        <v>0.027</v>
       </c>
       <c r="K69" t="s">
         <v>141</v>
@@ -3494,34 +3494,34 @@
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B70" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C70" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D70" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E70">
-        <v>9.5</v>
+        <v>5.5</v>
       </c>
       <c r="F70">
-        <v>10.55</v>
+        <v>6.68</v>
       </c>
       <c r="G70" s="1">
-        <v>0.625</v>
+        <v>0.626</v>
       </c>
       <c r="H70" t="s">
         <v>140</v>
       </c>
       <c r="I70" s="2">
-        <v>19.26</v>
+        <v>19.56</v>
       </c>
       <c r="J70" s="2">
-        <v>0.0265</v>
+        <v>0.0269</v>
       </c>
       <c r="K70" t="s">
         <v>141</v>
@@ -3532,34 +3532,34 @@
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="B71" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C71" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D71" t="s">
         <v>135</v>
       </c>
       <c r="E71">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="F71">
-        <v>2.25</v>
+        <v>5.92</v>
       </c>
       <c r="G71" s="1">
-        <v>0.623</v>
+        <v>0.626</v>
       </c>
       <c r="H71" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I71" s="2">
-        <v>18.96</v>
+        <v>19.54</v>
       </c>
       <c r="J71" s="2">
-        <v>0.0521</v>
+        <v>0.0537</v>
       </c>
       <c r="K71" t="s">
         <v>141</v>
@@ -3570,34 +3570,34 @@
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="B72" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C72" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D72" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E72">
-        <v>3.5</v>
+        <v>19.5</v>
       </c>
       <c r="F72">
-        <v>4.3</v>
+        <v>22.69</v>
       </c>
       <c r="G72" s="1">
-        <v>0.623</v>
+        <v>0.625</v>
       </c>
       <c r="H72" t="s">
         <v>140</v>
       </c>
       <c r="I72" s="2">
-        <v>18.85</v>
+        <v>19.34</v>
       </c>
       <c r="J72" s="2">
-        <v>0.0259</v>
+        <v>0.0266</v>
       </c>
       <c r="K72" t="s">
         <v>141</v>
@@ -3608,34 +3608,34 @@
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B73" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C73" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D73" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E73">
-        <v>19.5</v>
+        <v>3.5</v>
       </c>
       <c r="F73">
-        <v>17.27</v>
+        <v>4.31</v>
       </c>
       <c r="G73" s="1">
-        <v>0.622</v>
+        <v>0.624</v>
       </c>
       <c r="H73" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I73" s="2">
-        <v>18.74</v>
+        <v>19.14</v>
       </c>
       <c r="J73" s="2">
-        <v>0.0515</v>
+        <v>0.0263</v>
       </c>
       <c r="K73" t="s">
         <v>141</v>
@@ -3646,34 +3646,34 @@
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B74" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C74" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D74" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E74">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F74">
-        <v>3.21</v>
+        <v>4.03</v>
       </c>
       <c r="G74" s="1">
-        <v>0.622</v>
+        <v>0.623</v>
       </c>
       <c r="H74" t="s">
         <v>139</v>
       </c>
       <c r="I74" s="2">
-        <v>18.72</v>
+        <v>19</v>
       </c>
       <c r="J74" s="2">
-        <v>0.0515</v>
+        <v>0.0261</v>
       </c>
       <c r="K74" t="s">
         <v>141</v>
@@ -3684,34 +3684,34 @@
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="B75" t="s">
+        <v>129</v>
+      </c>
+      <c r="C75" t="s">
         <v>115</v>
-      </c>
-      <c r="C75" t="s">
-        <v>131</v>
       </c>
       <c r="D75" t="s">
         <v>135</v>
       </c>
       <c r="E75">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="F75">
-        <v>6.84</v>
+        <v>2.32</v>
       </c>
       <c r="G75" s="1">
-        <v>0.621</v>
+        <v>0.622</v>
       </c>
       <c r="H75" t="s">
         <v>139</v>
       </c>
       <c r="I75" s="2">
-        <v>18.63</v>
+        <v>18.83</v>
       </c>
       <c r="J75" s="2">
-        <v>0.0512</v>
+        <v>0.0259</v>
       </c>
       <c r="K75" t="s">
         <v>141</v>
@@ -3722,13 +3722,13 @@
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="B76" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C76" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="D76" t="s">
         <v>135</v>
@@ -3737,7 +3737,7 @@
         <v>2.5</v>
       </c>
       <c r="F76">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
       <c r="G76" s="1">
         <v>0.621</v>
@@ -3746,10 +3746,10 @@
         <v>139</v>
       </c>
       <c r="I76" s="2">
-        <v>18.6</v>
+        <v>18.46</v>
       </c>
       <c r="J76" s="2">
-        <v>0.0256</v>
+        <v>0.0508</v>
       </c>
       <c r="K76" t="s">
         <v>141</v>
@@ -3760,34 +3760,34 @@
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="B77" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C77" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D77" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E77">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="F77">
-        <v>8.6</v>
+        <v>3.12</v>
       </c>
       <c r="G77" s="1">
-        <v>0.621</v>
+        <v>0.619</v>
       </c>
       <c r="H77" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I77" s="2">
-        <v>18.6</v>
+        <v>18.25</v>
       </c>
       <c r="J77" s="2">
-        <v>0.0256</v>
+        <v>0.0251</v>
       </c>
       <c r="K77" t="s">
         <v>141</v>
@@ -3798,34 +3798,34 @@
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="C78" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="D78" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E78">
-        <v>20.5</v>
+        <v>7.5</v>
       </c>
       <c r="F78">
-        <v>23.2</v>
+        <v>6.86</v>
       </c>
       <c r="G78" s="1">
         <v>0.619</v>
       </c>
       <c r="H78" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I78" s="2">
-        <v>18.22</v>
+        <v>18.09</v>
       </c>
       <c r="J78" s="2">
-        <v>0.0251</v>
+        <v>0.0497</v>
       </c>
       <c r="K78" t="s">
         <v>141</v>
@@ -3836,34 +3836,34 @@
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C79" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D79" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E79">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="F79">
-        <v>20.42</v>
+        <v>17.36</v>
       </c>
       <c r="G79" s="1">
-        <v>0.619</v>
+        <v>0.617</v>
       </c>
       <c r="H79" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I79" s="2">
-        <v>18.15</v>
+        <v>17.82</v>
       </c>
       <c r="J79" s="2">
-        <v>0.025</v>
+        <v>0.049</v>
       </c>
       <c r="K79" t="s">
         <v>141</v>
@@ -3874,34 +3874,34 @@
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C80" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="D80" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E80">
-        <v>10.5</v>
+        <v>7.5</v>
       </c>
       <c r="F80">
-        <v>9.52</v>
+        <v>6.91</v>
       </c>
       <c r="G80" s="1">
-        <v>0.618</v>
+        <v>0.616</v>
       </c>
       <c r="H80" t="s">
         <v>139</v>
       </c>
       <c r="I80" s="2">
-        <v>18.01</v>
+        <v>17.64</v>
       </c>
       <c r="J80" s="2">
-        <v>0.0248</v>
+        <v>0.0485</v>
       </c>
       <c r="K80" t="s">
         <v>141</v>
@@ -3912,34 +3912,34 @@
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C81" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D81" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E81">
-        <v>7.5</v>
+        <v>20.5</v>
       </c>
       <c r="F81">
-        <v>6.88</v>
+        <v>23.08</v>
       </c>
       <c r="G81" s="1">
-        <v>0.615</v>
+        <v>0.614</v>
       </c>
       <c r="H81" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I81" s="2">
-        <v>17.49</v>
+        <v>17.21</v>
       </c>
       <c r="J81" s="2">
-        <v>0.0481</v>
+        <v>0.0237</v>
       </c>
       <c r="K81" t="s">
         <v>141</v>
@@ -3950,7 +3950,7 @@
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B82" t="s">
         <v>125</v>
@@ -3965,19 +3965,19 @@
         <v>1.5</v>
       </c>
       <c r="F82">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="G82" s="1">
-        <v>0.613</v>
+        <v>0.611</v>
       </c>
       <c r="H82" t="s">
         <v>139</v>
       </c>
       <c r="I82" s="2">
-        <v>17.04</v>
+        <v>16.73</v>
       </c>
       <c r="J82" s="2">
-        <v>0.0234</v>
+        <v>0.023</v>
       </c>
       <c r="K82" t="s">
         <v>141</v>
@@ -3988,34 +3988,34 @@
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="B83" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="C83" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="D83" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E83">
-        <v>2.5</v>
+        <v>15.5</v>
       </c>
       <c r="F83">
-        <v>3.22</v>
+        <v>18.39</v>
       </c>
       <c r="G83" s="1">
-        <v>0.613</v>
+        <v>0.611</v>
       </c>
       <c r="H83" t="s">
         <v>140</v>
       </c>
       <c r="I83" s="2">
-        <v>17.01</v>
+        <v>16.57</v>
       </c>
       <c r="J83" s="2">
-        <v>0.0234</v>
+        <v>0.0456</v>
       </c>
       <c r="K83" t="s">
         <v>141</v>
@@ -4026,34 +4026,34 @@
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B84" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C84" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="D84" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E84">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="F84">
-        <v>4.08</v>
+        <v>9.59</v>
       </c>
       <c r="G84" s="1">
-        <v>0.613</v>
+        <v>0.61</v>
       </c>
       <c r="H84" t="s">
         <v>139</v>
       </c>
       <c r="I84" s="2">
-        <v>16.98</v>
+        <v>16.44</v>
       </c>
       <c r="J84" s="2">
-        <v>0.0233</v>
+        <v>0.0226</v>
       </c>
       <c r="K84" t="s">
         <v>141</v>
@@ -4064,13 +4064,13 @@
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B85" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C85" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D85" t="s">
         <v>134</v>
@@ -4079,19 +4079,19 @@
         <v>7.5</v>
       </c>
       <c r="F85">
-        <v>7.03</v>
+        <v>6.92</v>
       </c>
       <c r="G85" s="1">
-        <v>0.611</v>
+        <v>0.61</v>
       </c>
       <c r="H85" t="s">
         <v>139</v>
       </c>
       <c r="I85" s="2">
-        <v>16.64</v>
+        <v>16.39</v>
       </c>
       <c r="J85" s="2">
-        <v>0.0458</v>
+        <v>0.0451</v>
       </c>
       <c r="K85" t="s">
         <v>141</v>
@@ -4102,34 +4102,34 @@
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="B86" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="C86" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="D86" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E86">
-        <v>15.5</v>
+        <v>2.5</v>
       </c>
       <c r="F86">
-        <v>18.28</v>
+        <v>3.21</v>
       </c>
       <c r="G86" s="1">
-        <v>0.607</v>
+        <v>0.61</v>
       </c>
       <c r="H86" t="s">
         <v>140</v>
       </c>
       <c r="I86" s="2">
-        <v>15.8</v>
+        <v>16.38</v>
       </c>
       <c r="J86" s="2">
-        <v>0.0435</v>
+        <v>0.0225</v>
       </c>
       <c r="K86" t="s">
         <v>141</v>
@@ -4140,13 +4140,13 @@
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B87" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C87" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="D87" t="s">
         <v>135</v>
@@ -4155,19 +4155,19 @@
         <v>2.5</v>
       </c>
       <c r="F87">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="G87" s="1">
-        <v>0.603</v>
+        <v>0.609</v>
       </c>
       <c r="H87" t="s">
         <v>139</v>
       </c>
       <c r="I87" s="2">
-        <v>15.12</v>
+        <v>16.36</v>
       </c>
       <c r="J87" s="2">
-        <v>0.0208</v>
+        <v>0.045</v>
       </c>
       <c r="K87" t="s">
         <v>141</v>
@@ -4178,34 +4178,34 @@
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B88" t="s">
+        <v>128</v>
+      </c>
+      <c r="C88" t="s">
         <v>116</v>
       </c>
-      <c r="C88" t="s">
-        <v>114</v>
-      </c>
       <c r="D88" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E88">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="F88">
-        <v>4.55</v>
+        <v>1.35</v>
       </c>
       <c r="G88" s="1">
-        <v>0.602</v>
+        <v>0.609</v>
       </c>
       <c r="H88" t="s">
         <v>139</v>
       </c>
       <c r="I88" s="2">
-        <v>14.98</v>
+        <v>16.19</v>
       </c>
       <c r="J88" s="2">
-        <v>0.0412</v>
+        <v>0.0445</v>
       </c>
       <c r="K88" t="s">
         <v>141</v>
@@ -4216,34 +4216,34 @@
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B89" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C89" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="D89" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E89">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="F89">
-        <v>2.28</v>
+        <v>4.5</v>
       </c>
       <c r="G89" s="1">
-        <v>0.602</v>
+        <v>0.607</v>
       </c>
       <c r="H89" t="s">
         <v>139</v>
       </c>
       <c r="I89" s="2">
-        <v>14.95</v>
+        <v>15.95</v>
       </c>
       <c r="J89" s="2">
-        <v>0.0411</v>
+        <v>0.0439</v>
       </c>
       <c r="K89" t="s">
         <v>141</v>
@@ -4254,34 +4254,34 @@
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B90" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C90" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D90" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E90">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="F90">
-        <v>4.15</v>
+        <v>5.07</v>
       </c>
       <c r="G90" s="1">
-        <v>0.6</v>
+        <v>0.606</v>
       </c>
       <c r="H90" t="s">
         <v>139</v>
       </c>
       <c r="I90" s="2">
-        <v>14.55</v>
+        <v>15.74</v>
       </c>
       <c r="J90" s="2">
-        <v>0.02</v>
+        <v>0.0216</v>
       </c>
       <c r="K90" t="s">
         <v>141</v>
@@ -4292,34 +4292,34 @@
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B91" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C91" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D91" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E91">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F91">
-        <v>4.38</v>
+        <v>4.15</v>
       </c>
       <c r="G91" s="1">
         <v>0.599</v>
       </c>
       <c r="H91" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I91" s="2">
-        <v>14.44</v>
+        <v>14.45</v>
       </c>
       <c r="J91" s="2">
-        <v>0.0397</v>
+        <v>0.0199</v>
       </c>
       <c r="K91" t="s">
         <v>141</v>
@@ -4333,31 +4333,31 @@
         <v>94</v>
       </c>
       <c r="B92" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C92" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D92" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E92">
-        <v>20.5</v>
+        <v>12.5</v>
       </c>
       <c r="F92">
-        <v>19.02</v>
+        <v>13.07</v>
       </c>
       <c r="G92" s="1">
-        <v>0.598</v>
+        <v>0.596</v>
       </c>
       <c r="H92" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I92" s="2">
-        <v>14.19</v>
+        <v>13.79</v>
       </c>
       <c r="J92" s="2">
-        <v>0.0195</v>
+        <v>0.0379</v>
       </c>
       <c r="K92" t="s">
         <v>141</v>
@@ -4368,34 +4368,34 @@
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="B93" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C93" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D93" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E93">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="F93">
-        <v>1.39</v>
+        <v>12.77</v>
       </c>
       <c r="G93" s="1">
-        <v>0.596</v>
+        <v>0.594</v>
       </c>
       <c r="H93" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I93" s="2">
-        <v>13.8</v>
+        <v>13.43</v>
       </c>
       <c r="J93" s="2">
-        <v>0.0379</v>
+        <v>0.0185</v>
       </c>
       <c r="K93" t="s">
         <v>141</v>
@@ -4406,34 +4406,34 @@
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C94" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D94" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E94">
-        <v>12.5</v>
+        <v>3.5</v>
       </c>
       <c r="F94">
-        <v>13.07</v>
+        <v>4.33</v>
       </c>
       <c r="G94" s="1">
-        <v>0.596</v>
+        <v>0.591</v>
       </c>
       <c r="H94" t="s">
         <v>140</v>
       </c>
       <c r="I94" s="2">
-        <v>13.75</v>
+        <v>12.74</v>
       </c>
       <c r="J94" s="2">
-        <v>0.0378</v>
+        <v>0.035</v>
       </c>
       <c r="K94" t="s">
         <v>141</v>
@@ -4444,34 +4444,34 @@
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C95" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D95" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E95">
         <v>12.5</v>
       </c>
       <c r="F95">
-        <v>14.26</v>
+        <v>14.21</v>
       </c>
       <c r="G95" s="1">
-        <v>0.592</v>
+        <v>0.589</v>
       </c>
       <c r="H95" t="s">
         <v>140</v>
       </c>
       <c r="I95" s="2">
-        <v>13.09</v>
+        <v>12.54</v>
       </c>
       <c r="J95" s="2">
-        <v>0.018</v>
+        <v>0.0172</v>
       </c>
       <c r="K95" t="s">
         <v>141</v>
@@ -4482,7 +4482,7 @@
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B96" t="s">
         <v>115</v>
@@ -4491,25 +4491,25 @@
         <v>131</v>
       </c>
       <c r="D96" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E96">
         <v>12.5</v>
       </c>
       <c r="F96">
-        <v>13.9</v>
+        <v>13.86</v>
       </c>
       <c r="G96" s="1">
-        <v>0.591</v>
+        <v>0.588</v>
       </c>
       <c r="H96" t="s">
         <v>140</v>
       </c>
       <c r="I96" s="2">
-        <v>12.74</v>
+        <v>12.19</v>
       </c>
       <c r="J96" s="2">
-        <v>0.035</v>
+        <v>0.0335</v>
       </c>
       <c r="K96" t="s">
         <v>141</v>
@@ -4520,34 +4520,34 @@
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B97" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="C97" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D97" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E97">
-        <v>3.5</v>
+        <v>11.5</v>
       </c>
       <c r="F97">
-        <v>3.55</v>
+        <v>9.82</v>
       </c>
       <c r="G97" s="1">
-        <v>0.59</v>
+        <v>0.587</v>
       </c>
       <c r="H97" t="s">
         <v>139</v>
       </c>
       <c r="I97" s="2">
-        <v>12.54</v>
+        <v>12.14</v>
       </c>
       <c r="J97" s="2">
-        <v>0.0345</v>
+        <v>0.0334</v>
       </c>
       <c r="K97" t="s">
         <v>141</v>
@@ -4558,34 +4558,34 @@
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>98</v>
+        <v>15</v>
       </c>
       <c r="B98" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="C98" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D98" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E98">
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
       <c r="F98">
-        <v>9.81</v>
+        <v>8.07</v>
       </c>
       <c r="G98" s="1">
-        <v>0.588</v>
+        <v>0.587</v>
       </c>
       <c r="H98" t="s">
         <v>139</v>
       </c>
       <c r="I98" s="2">
-        <v>12.28</v>
+        <v>12.03</v>
       </c>
       <c r="J98" s="2">
-        <v>0.0338</v>
+        <v>0.0331</v>
       </c>
       <c r="K98" t="s">
         <v>141</v>
@@ -4596,34 +4596,34 @@
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C99" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D99" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E99">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="F99">
-        <v>1.98</v>
+        <v>5.23</v>
       </c>
       <c r="G99" s="1">
-        <v>0.588</v>
+        <v>0.586</v>
       </c>
       <c r="H99" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I99" s="2">
-        <v>12.17</v>
+        <v>11.94</v>
       </c>
       <c r="J99" s="2">
-        <v>0.0167</v>
+        <v>0.0164</v>
       </c>
       <c r="K99" t="s">
         <v>141</v>
@@ -4637,31 +4637,31 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="C100" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="D100" t="s">
         <v>134</v>
       </c>
       <c r="E100">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="F100">
-        <v>2.34</v>
+        <v>8.07</v>
       </c>
       <c r="G100" s="1">
-        <v>0.588</v>
+        <v>0.585</v>
       </c>
       <c r="H100" t="s">
         <v>139</v>
       </c>
       <c r="I100" s="2">
-        <v>12.16</v>
+        <v>11.7</v>
       </c>
       <c r="J100" s="2">
-        <v>0.0167</v>
+        <v>0.0161</v>
       </c>
       <c r="K100" t="s">
         <v>141</v>
@@ -4672,34 +4672,34 @@
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="B101" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C101" t="s">
         <v>130</v>
       </c>
       <c r="D101" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E101">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="F101">
-        <v>1.44</v>
+        <v>3.6</v>
       </c>
       <c r="G101" s="1">
-        <v>0.585</v>
+        <v>0.582</v>
       </c>
       <c r="H101" t="s">
         <v>139</v>
       </c>
       <c r="I101" s="2">
-        <v>11.76</v>
+        <v>11.03</v>
       </c>
       <c r="J101" s="2">
-        <v>0.0162</v>
+        <v>0.0303</v>
       </c>
       <c r="K101" t="s">
         <v>141</v>
@@ -4713,34 +4713,34 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C102" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D102" t="s">
         <v>137</v>
       </c>
       <c r="E102">
-        <v>20.5</v>
+        <v>9.5</v>
       </c>
       <c r="F102">
-        <v>18.31</v>
+        <v>10.89</v>
       </c>
       <c r="G102" s="1">
-        <v>0.583</v>
+        <v>0.578</v>
       </c>
       <c r="H102" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I102" s="2">
-        <v>11.35</v>
+        <v>10.38</v>
       </c>
       <c r="J102" s="2">
-        <v>0.0156</v>
+        <v>0.0143</v>
       </c>
       <c r="K102" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L102" t="s">
         <v>145</v>
@@ -4748,37 +4748,37 @@
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C103" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="D103" t="s">
         <v>134</v>
       </c>
       <c r="E103">
-        <v>8.5</v>
+        <v>13.5</v>
       </c>
       <c r="F103">
-        <v>8.130000000000001</v>
+        <v>12.99</v>
       </c>
       <c r="G103" s="1">
-        <v>0.581</v>
+        <v>0.578</v>
       </c>
       <c r="H103" t="s">
         <v>139</v>
       </c>
       <c r="I103" s="2">
-        <v>10.83</v>
+        <v>10.33</v>
       </c>
       <c r="J103" s="2">
-        <v>0.0298</v>
+        <v>0.0284</v>
       </c>
       <c r="K103" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L103" t="s">
         <v>145</v>
@@ -4786,37 +4786,37 @@
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="B104" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="C104" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D104" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E104">
-        <v>13.5</v>
+        <v>1.5</v>
       </c>
       <c r="F104">
-        <v>12.96</v>
+        <v>1.5</v>
       </c>
       <c r="G104" s="1">
-        <v>0.58</v>
+        <v>0.577</v>
       </c>
       <c r="H104" t="s">
         <v>139</v>
       </c>
       <c r="I104" s="2">
-        <v>10.73</v>
+        <v>10.23</v>
       </c>
       <c r="J104" s="2">
-        <v>0.0295</v>
+        <v>0.0281</v>
       </c>
       <c r="K104" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L104" t="s">
         <v>145</v>
@@ -4827,10 +4827,10 @@
         <v>102</v>
       </c>
       <c r="B105" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C105" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D105" t="s">
         <v>135</v>
@@ -4839,19 +4839,19 @@
         <v>2.5</v>
       </c>
       <c r="F105">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="G105" s="1">
-        <v>0.58</v>
+        <v>0.575</v>
       </c>
       <c r="H105" t="s">
         <v>140</v>
       </c>
       <c r="I105" s="2">
-        <v>10.67</v>
+        <v>9.69</v>
       </c>
       <c r="J105" s="2">
-        <v>0.0293</v>
+        <v>0.0267</v>
       </c>
       <c r="K105" t="s">
         <v>142</v>
@@ -4862,34 +4862,34 @@
     </row>
     <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="B106" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="C106" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="D106" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E106">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="F106">
-        <v>1.5</v>
+        <v>5.28</v>
       </c>
       <c r="G106" s="1">
-        <v>0.578</v>
+        <v>0.574</v>
       </c>
       <c r="H106" t="s">
         <v>139</v>
       </c>
       <c r="I106" s="2">
-        <v>10.4</v>
+        <v>9.49</v>
       </c>
       <c r="J106" s="2">
-        <v>0.0286</v>
+        <v>0.0131</v>
       </c>
       <c r="K106" t="s">
         <v>142</v>
@@ -4900,34 +4900,34 @@
     </row>
     <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B107" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C107" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D107" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E107">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="F107">
-        <v>8.15</v>
+        <v>1.47</v>
       </c>
       <c r="G107" s="1">
-        <v>0.575</v>
+        <v>0.572</v>
       </c>
       <c r="H107" t="s">
         <v>139</v>
       </c>
       <c r="I107" s="2">
-        <v>9.85</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="J107" s="2">
-        <v>0.0135</v>
+        <v>0.0127</v>
       </c>
       <c r="K107" t="s">
         <v>142</v>
@@ -4938,34 +4938,34 @@
     </row>
     <row r="108" spans="1:12">
       <c r="A108" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="B108" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C108" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D108" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E108">
-        <v>21.5</v>
+        <v>19.5</v>
       </c>
       <c r="F108">
-        <v>22.88</v>
+        <v>20.86</v>
       </c>
       <c r="G108" s="1">
-        <v>0.573</v>
+        <v>0.571</v>
       </c>
       <c r="H108" t="s">
         <v>140</v>
       </c>
       <c r="I108" s="2">
-        <v>9.449999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="J108" s="2">
-        <v>0.013</v>
+        <v>0.0123</v>
       </c>
       <c r="K108" t="s">
         <v>142</v>
@@ -4976,34 +4976,34 @@
     </row>
     <row r="109" spans="1:12">
       <c r="A109" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B109" t="s">
         <v>117</v>
       </c>
       <c r="C109" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D109" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E109">
-        <v>9.5</v>
+        <v>2.5</v>
       </c>
       <c r="F109">
-        <v>10.36</v>
+        <v>2.4</v>
       </c>
       <c r="G109" s="1">
-        <v>0.572</v>
+        <v>0.571</v>
       </c>
       <c r="H109" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I109" s="2">
-        <v>9.19</v>
+        <v>8.92</v>
       </c>
       <c r="J109" s="2">
-        <v>0.0126</v>
+        <v>0.0123</v>
       </c>
       <c r="K109" t="s">
         <v>142</v>
@@ -5014,34 +5014,34 @@
     </row>
     <row r="110" spans="1:12">
       <c r="A110" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="B110" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C110" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D110" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E110">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="F110">
-        <v>5.29</v>
+        <v>1.91</v>
       </c>
       <c r="G110" s="1">
-        <v>0.572</v>
+        <v>0.57</v>
       </c>
       <c r="H110" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I110" s="2">
-        <v>9.15</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J110" s="2">
-        <v>0.0126</v>
+        <v>0.0242</v>
       </c>
       <c r="K110" t="s">
         <v>142</v>
@@ -5052,34 +5052,34 @@
     </row>
     <row r="111" spans="1:12">
       <c r="A111" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B111" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C111" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D111" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E111">
-        <v>3.5</v>
+        <v>12.5</v>
       </c>
       <c r="F111">
-        <v>3.48</v>
+        <v>13.84</v>
       </c>
       <c r="G111" s="1">
-        <v>0.571</v>
+        <v>0.569</v>
       </c>
       <c r="H111" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I111" s="2">
-        <v>8.970000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="J111" s="2">
-        <v>0.0247</v>
+        <v>0.0119</v>
       </c>
       <c r="K111" t="s">
         <v>142</v>
@@ -5090,34 +5090,34 @@
     </row>
     <row r="112" spans="1:12">
       <c r="A112" t="s">
-        <v>38</v>
+        <v>105</v>
       </c>
       <c r="B112" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C112" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D112" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E112">
-        <v>1.5</v>
+        <v>15.5</v>
       </c>
       <c r="F112">
-        <v>1.92</v>
+        <v>16.49</v>
       </c>
       <c r="G112" s="1">
-        <v>0.571</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H112" t="s">
         <v>140</v>
       </c>
       <c r="I112" s="2">
-        <v>8.970000000000001</v>
+        <v>8.02</v>
       </c>
       <c r="J112" s="2">
-        <v>0.0247</v>
+        <v>0.0221</v>
       </c>
       <c r="K112" t="s">
         <v>142</v>
@@ -5128,34 +5128,34 @@
     </row>
     <row r="113" spans="1:12">
       <c r="A113" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B113" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C113" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="D113" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E113">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="F113">
-        <v>10.74</v>
+        <v>2.16</v>
       </c>
       <c r="G113" s="1">
-        <v>0.57</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H113" t="s">
         <v>140</v>
       </c>
       <c r="I113" s="2">
-        <v>8.800000000000001</v>
+        <v>7.69</v>
       </c>
       <c r="J113" s="2">
-        <v>0.0121</v>
+        <v>0.0106</v>
       </c>
       <c r="K113" t="s">
         <v>142</v>
@@ -5166,34 +5166,34 @@
     </row>
     <row r="114" spans="1:12">
       <c r="A114" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B114" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C114" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D114" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E114">
-        <v>20.5</v>
+        <v>3.5</v>
       </c>
       <c r="F114">
-        <v>22.35</v>
+        <v>3.53</v>
       </c>
       <c r="G114" s="1">
-        <v>0.5659999999999999</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H114" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I114" s="2">
-        <v>8.109999999999999</v>
+        <v>7.43</v>
       </c>
       <c r="J114" s="2">
-        <v>0.0112</v>
+        <v>0.0204</v>
       </c>
       <c r="K114" t="s">
         <v>142</v>
@@ -5204,34 +5204,34 @@
     </row>
     <row r="115" spans="1:12">
       <c r="A115" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B115" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C115" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="D115" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E115">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="F115">
-        <v>1.9</v>
+        <v>10.25</v>
       </c>
       <c r="G115" s="1">
-        <v>0.5649999999999999</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H115" t="s">
         <v>140</v>
       </c>
       <c r="I115" s="2">
-        <v>7.85</v>
+        <v>7.42</v>
       </c>
       <c r="J115" s="2">
-        <v>0.0108</v>
+        <v>0.0102</v>
       </c>
       <c r="K115" t="s">
         <v>142</v>
@@ -5242,34 +5242,34 @@
     </row>
     <row r="116" spans="1:12">
       <c r="A116" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="B116" t="s">
+        <v>125</v>
+      </c>
+      <c r="C116" t="s">
         <v>120</v>
       </c>
-      <c r="C116" t="s">
-        <v>125</v>
-      </c>
       <c r="D116" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E116">
-        <v>11.5</v>
+        <v>28.5</v>
       </c>
       <c r="F116">
-        <v>12.37</v>
+        <v>30.37</v>
       </c>
       <c r="G116" s="1">
-        <v>0.5649999999999999</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="H116" t="s">
         <v>140</v>
       </c>
       <c r="I116" s="2">
-        <v>7.83</v>
+        <v>7.23</v>
       </c>
       <c r="J116" s="2">
-        <v>0.0108</v>
+        <v>0.0199</v>
       </c>
       <c r="K116" t="s">
         <v>142</v>
@@ -5280,34 +5280,34 @@
     </row>
     <row r="117" spans="1:12">
       <c r="A117" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="B117" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C117" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D117" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E117">
         <v>13.5</v>
       </c>
       <c r="F117">
-        <v>14.77</v>
+        <v>12.24</v>
       </c>
       <c r="G117" s="1">
-        <v>0.5610000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H117" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I117" s="2">
-        <v>7.13</v>
+        <v>6.84</v>
       </c>
       <c r="J117" s="2">
-        <v>0.0196</v>
+        <v>0.0188</v>
       </c>
       <c r="K117" t="s">
         <v>142</v>
@@ -5318,34 +5318,34 @@
     </row>
     <row r="118" spans="1:12">
       <c r="A118" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B118" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C118" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D118" t="s">
         <v>135</v>
       </c>
       <c r="E118">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F118">
-        <v>2.15</v>
+        <v>2.92</v>
       </c>
       <c r="G118" s="1">
-        <v>0.5610000000000001</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H118" t="s">
         <v>140</v>
       </c>
       <c r="I118" s="2">
-        <v>7.05</v>
+        <v>6.5</v>
       </c>
       <c r="J118" s="2">
-        <v>0.0097</v>
+        <v>0.0179</v>
       </c>
       <c r="K118" t="s">
         <v>142</v>
@@ -5356,34 +5356,34 @@
     </row>
     <row r="119" spans="1:12">
       <c r="A119" t="s">
-        <v>99</v>
+        <v>28</v>
       </c>
       <c r="B119" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C119" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D119" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E119">
-        <v>15.5</v>
+        <v>6.5</v>
       </c>
       <c r="F119">
-        <v>16.4</v>
+        <v>7.05</v>
       </c>
       <c r="G119" s="1">
-        <v>0.5600000000000001</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H119" t="s">
         <v>140</v>
       </c>
       <c r="I119" s="2">
-        <v>6.92</v>
+        <v>6.39</v>
       </c>
       <c r="J119" s="2">
-        <v>0.019</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="K119" t="s">
         <v>142</v>
@@ -5394,34 +5394,34 @@
     </row>
     <row r="120" spans="1:12">
       <c r="A120" t="s">
-        <v>31</v>
+        <v>104</v>
       </c>
       <c r="B120" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C120" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D120" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E120">
-        <v>28.5</v>
+        <v>9.5</v>
       </c>
       <c r="F120">
-        <v>30.31</v>
+        <v>10.26</v>
       </c>
       <c r="G120" s="1">
-        <v>0.5600000000000001</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H120" t="s">
         <v>140</v>
       </c>
       <c r="I120" s="2">
-        <v>6.84</v>
+        <v>6.37</v>
       </c>
       <c r="J120" s="2">
-        <v>0.0188</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="K120" t="s">
         <v>142</v>
@@ -5432,34 +5432,34 @@
     </row>
     <row r="121" spans="1:12">
       <c r="A121" t="s">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="B121" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C121" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="D121" t="s">
         <v>137</v>
       </c>
       <c r="E121">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="F121">
-        <v>12.25</v>
+        <v>13.6</v>
       </c>
       <c r="G121" s="1">
-        <v>0.5590000000000001</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H121" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I121" s="2">
-        <v>6.75</v>
+        <v>6.32</v>
       </c>
       <c r="J121" s="2">
-        <v>0.0185</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="K121" t="s">
         <v>142</v>
@@ -5470,34 +5470,34 @@
     </row>
     <row r="122" spans="1:12">
       <c r="A122" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="B122" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C122" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D122" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E122">
-        <v>6.5</v>
+        <v>12.5</v>
       </c>
       <c r="F122">
-        <v>7.03</v>
+        <v>13.21</v>
       </c>
       <c r="G122" s="1">
-        <v>0.555</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H122" t="s">
         <v>140</v>
       </c>
       <c r="I122" s="2">
-        <v>5.94</v>
+        <v>6.25</v>
       </c>
       <c r="J122" s="2">
-        <v>0.008200000000000001</v>
+        <v>0.0086</v>
       </c>
       <c r="K122" t="s">
         <v>142</v>
@@ -5508,34 +5508,34 @@
     </row>
     <row r="123" spans="1:12">
       <c r="A123" t="s">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="B123" t="s">
         <v>118</v>
       </c>
       <c r="C123" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D123" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E123">
-        <v>25.5</v>
+        <v>1.5</v>
       </c>
       <c r="F123">
-        <v>26.8</v>
+        <v>1.63</v>
       </c>
       <c r="G123" s="1">
-        <v>0.554</v>
+        <v>0.556</v>
       </c>
       <c r="H123" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I123" s="2">
-        <v>5.8</v>
+        <v>6.14</v>
       </c>
       <c r="J123" s="2">
-        <v>0.016</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="K123" t="s">
         <v>142</v>
@@ -5546,34 +5546,34 @@
     </row>
     <row r="124" spans="1:12">
       <c r="A124" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="B124" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C124" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="D124" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E124">
-        <v>18.5</v>
+        <v>3.5</v>
       </c>
       <c r="F124">
-        <v>19.05</v>
+        <v>3.41</v>
       </c>
       <c r="G124" s="1">
-        <v>0.553</v>
+        <v>0.555</v>
       </c>
       <c r="H124" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I124" s="2">
-        <v>5.63</v>
+        <v>5.98</v>
       </c>
       <c r="J124" s="2">
-        <v>0.0155</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="K124" t="s">
         <v>142</v>
@@ -5584,34 +5584,34 @@
     </row>
     <row r="125" spans="1:12">
       <c r="A125" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="B125" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C125" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D125" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E125">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="F125">
-        <v>7.92</v>
+        <v>1.86</v>
       </c>
       <c r="G125" s="1">
-        <v>0.553</v>
+        <v>0.554</v>
       </c>
       <c r="H125" t="s">
         <v>140</v>
       </c>
       <c r="I125" s="2">
-        <v>5.48</v>
+        <v>5.75</v>
       </c>
       <c r="J125" s="2">
-        <v>0.0151</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="K125" t="s">
         <v>142</v>
@@ -5622,34 +5622,34 @@
     </row>
     <row r="126" spans="1:12">
       <c r="A126" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B126" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="C126" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D126" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E126">
-        <v>1.5</v>
+        <v>14.5</v>
       </c>
       <c r="F126">
-        <v>1.85</v>
+        <v>15.95</v>
       </c>
       <c r="G126" s="1">
-        <v>0.551</v>
+        <v>0.552</v>
       </c>
       <c r="H126" t="s">
         <v>140</v>
       </c>
       <c r="I126" s="2">
-        <v>5.28</v>
+        <v>5.31</v>
       </c>
       <c r="J126" s="2">
-        <v>0.0145</v>
+        <v>0.0146</v>
       </c>
       <c r="K126" t="s">
         <v>142</v>
@@ -5660,34 +5660,34 @@
     </row>
     <row r="127" spans="1:12">
       <c r="A127" t="s">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="B127" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C127" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D127" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E127">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="F127">
-        <v>3.44</v>
+        <v>1.85</v>
       </c>
       <c r="G127" s="1">
         <v>0.55</v>
       </c>
       <c r="H127" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I127" s="2">
-        <v>5.05</v>
+        <v>5.09</v>
       </c>
       <c r="J127" s="2">
-        <v>0.0069</v>
+        <v>0.007</v>
       </c>
       <c r="K127" t="s">
         <v>142</v>
@@ -5698,22 +5698,22 @@
     </row>
     <row r="128" spans="1:12">
       <c r="A128" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="B128" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C128" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="D128" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E128">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="F128">
-        <v>2.88</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G128" s="1">
         <v>0.55</v>
@@ -5722,10 +5722,10 @@
         <v>140</v>
       </c>
       <c r="I128" s="2">
-        <v>4.94</v>
+        <v>4.98</v>
       </c>
       <c r="J128" s="2">
-        <v>0.0136</v>
+        <v>0.0137</v>
       </c>
       <c r="K128" t="s">
         <v>142</v>
@@ -5736,34 +5736,34 @@
     </row>
     <row r="129" spans="1:12">
       <c r="A129" t="s">
-        <v>110</v>
+        <v>26</v>
       </c>
       <c r="B129" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C129" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D129" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E129">
-        <v>18.5</v>
+        <v>3.5</v>
       </c>
       <c r="F129">
-        <v>19.47</v>
+        <v>3.91</v>
       </c>
       <c r="G129" s="1">
-        <v>0.548</v>
+        <v>0.549</v>
       </c>
       <c r="H129" t="s">
         <v>140</v>
       </c>
       <c r="I129" s="2">
-        <v>4.59</v>
+        <v>4.84</v>
       </c>
       <c r="J129" s="2">
-        <v>0.0126</v>
+        <v>0.0066</v>
       </c>
       <c r="K129" t="s">
         <v>142</v>
@@ -5774,22 +5774,22 @@
     </row>
     <row r="130" spans="1:12">
       <c r="A130" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="B130" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C130" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D130" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E130">
         <v>7.5</v>
       </c>
       <c r="F130">
-        <v>8.630000000000001</v>
+        <v>7.87</v>
       </c>
       <c r="G130" s="1">
         <v>0.547</v>
@@ -5798,7 +5798,7 @@
         <v>140</v>
       </c>
       <c r="I130" s="2">
-        <v>4.39</v>
+        <v>4.42</v>
       </c>
       <c r="J130" s="2">
         <v>0.0121</v>
@@ -5812,34 +5812,34 @@
     </row>
     <row r="131" spans="1:12">
       <c r="A131" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="B131" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C131" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D131" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E131">
-        <v>1.5</v>
+        <v>18.5</v>
       </c>
       <c r="F131">
-        <v>1.83</v>
+        <v>19.5</v>
       </c>
       <c r="G131" s="1">
-        <v>0.546</v>
+        <v>0.547</v>
       </c>
       <c r="H131" t="s">
         <v>140</v>
       </c>
       <c r="I131" s="2">
-        <v>4.32</v>
+        <v>4.37</v>
       </c>
       <c r="J131" s="2">
-        <v>0.0119</v>
+        <v>0.012</v>
       </c>
       <c r="K131" t="s">
         <v>142</v>
@@ -5850,22 +5850,22 @@
     </row>
     <row r="132" spans="1:12">
       <c r="A132" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="B132" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C132" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D132" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E132">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="F132">
-        <v>7.95</v>
+        <v>1.83</v>
       </c>
       <c r="G132" s="1">
         <v>0.546</v>
@@ -5874,10 +5874,10 @@
         <v>140</v>
       </c>
       <c r="I132" s="2">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="J132" s="2">
-        <v>0.0118</v>
+        <v>0.0114</v>
       </c>
       <c r="K132" t="s">
         <v>142</v>
@@ -5888,22 +5888,22 @@
     </row>
     <row r="133" spans="1:12">
       <c r="A133" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="B133" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C133" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D133" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E133">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="F133">
-        <v>18.35</v>
+        <v>18.96</v>
       </c>
       <c r="G133" s="1">
         <v>0.545</v>
@@ -5912,13 +5912,13 @@
         <v>140</v>
       </c>
       <c r="I133" s="2">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="J133" s="2">
-        <v>0.0111</v>
+        <v>0.011</v>
       </c>
       <c r="K133" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L133" t="s">
         <v>145</v>
@@ -5926,34 +5926,34 @@
     </row>
     <row r="134" spans="1:12">
       <c r="A134" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="B134" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C134" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="D134" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E134">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="F134">
-        <v>1.67</v>
+        <v>5.42</v>
       </c>
       <c r="G134" s="1">
-        <v>0.544</v>
+        <v>0.545</v>
       </c>
       <c r="H134" t="s">
         <v>139</v>
       </c>
       <c r="I134" s="2">
-        <v>3.79</v>
+        <v>3.95</v>
       </c>
       <c r="J134" s="2">
-        <v>0.0052</v>
+        <v>0.0109</v>
       </c>
       <c r="K134" t="s">
         <v>143</v>
@@ -5964,13 +5964,13 @@
     </row>
     <row r="135" spans="1:12">
       <c r="A135" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="B135" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C135" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D135" t="s">
         <v>135</v>
@@ -5982,16 +5982,16 @@
         <v>1.82</v>
       </c>
       <c r="G135" s="1">
-        <v>0.543</v>
+        <v>0.544</v>
       </c>
       <c r="H135" t="s">
         <v>140</v>
       </c>
       <c r="I135" s="2">
-        <v>3.72</v>
+        <v>3.78</v>
       </c>
       <c r="J135" s="2">
-        <v>0.0051</v>
+        <v>0.0104</v>
       </c>
       <c r="K135" t="s">
         <v>143</v>
@@ -6002,34 +6002,34 @@
     </row>
     <row r="136" spans="1:12">
       <c r="A136" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B136" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="C136" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D136" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E136">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="F136">
-        <v>9.210000000000001</v>
+        <v>9.92</v>
       </c>
       <c r="G136" s="1">
-        <v>0.541</v>
+        <v>0.543</v>
       </c>
       <c r="H136" t="s">
         <v>140</v>
       </c>
       <c r="I136" s="2">
-        <v>3.21</v>
+        <v>3.59</v>
       </c>
       <c r="J136" s="2">
-        <v>0.008800000000000001</v>
+        <v>0.0049</v>
       </c>
       <c r="K136" t="s">
         <v>143</v>
@@ -6040,34 +6040,34 @@
     </row>
     <row r="137" spans="1:12">
       <c r="A137" t="s">
-        <v>57</v>
+        <v>112</v>
       </c>
       <c r="B137" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C137" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D137" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E137">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="F137">
-        <v>5.44</v>
+        <v>12.08</v>
       </c>
       <c r="G137" s="1">
         <v>0.54</v>
       </c>
       <c r="H137" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I137" s="2">
-        <v>3.09</v>
+        <v>3.13</v>
       </c>
       <c r="J137" s="2">
-        <v>0.008500000000000001</v>
+        <v>0.0086</v>
       </c>
       <c r="K137" t="s">
         <v>143</v>
@@ -6078,34 +6078,34 @@
     </row>
     <row r="138" spans="1:12">
       <c r="A138" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B138" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="C138" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D138" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E138">
-        <v>2.5</v>
+        <v>32.5</v>
       </c>
       <c r="F138">
-        <v>2.69</v>
+        <v>31.81</v>
       </c>
       <c r="G138" s="1">
-        <v>0.54</v>
+        <v>0.539</v>
       </c>
       <c r="H138" t="s">
         <v>139</v>
       </c>
       <c r="I138" s="2">
-        <v>3.06</v>
+        <v>2.96</v>
       </c>
       <c r="J138" s="2">
-        <v>0.008399999999999999</v>
+        <v>0.0081</v>
       </c>
       <c r="K138" t="s">
         <v>143</v>
@@ -6116,34 +6116,34 @@
     </row>
     <row r="139" spans="1:12">
       <c r="A139" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="B139" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C139" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D139" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E139">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F139">
-        <v>3.86</v>
+        <v>2.83</v>
       </c>
       <c r="G139" s="1">
-        <v>0.54</v>
+        <v>0.538</v>
       </c>
       <c r="H139" t="s">
         <v>140</v>
       </c>
       <c r="I139" s="2">
-        <v>3.03</v>
+        <v>2.77</v>
       </c>
       <c r="J139" s="2">
-        <v>0.0042</v>
+        <v>0.0038</v>
       </c>
       <c r="K139" t="s">
         <v>143</v>
@@ -6154,28 +6154,28 @@
     </row>
     <row r="140" spans="1:12">
       <c r="A140" t="s">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="B140" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C140" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D140" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E140">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="F140">
-        <v>3.5</v>
+        <v>7.86</v>
       </c>
       <c r="G140" s="1">
         <v>0.537</v>
       </c>
       <c r="H140" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I140" s="2">
         <v>2.48</v>
@@ -6192,10 +6192,10 @@
     </row>
     <row r="141" spans="1:12">
       <c r="A141" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B141" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="C141" t="s">
         <v>116</v>
@@ -6204,22 +6204,22 @@
         <v>137</v>
       </c>
       <c r="E141">
-        <v>26.5</v>
+        <v>18.5</v>
       </c>
       <c r="F141">
-        <v>27.17</v>
+        <v>17.8</v>
       </c>
       <c r="G141" s="1">
-        <v>0.536</v>
+        <v>0.534</v>
       </c>
       <c r="H141" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I141" s="2">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="J141" s="2">
-        <v>0.0031</v>
+        <v>0.0028</v>
       </c>
       <c r="K141" t="s">
         <v>143</v>
@@ -6230,34 +6230,34 @@
     </row>
     <row r="142" spans="1:12">
       <c r="A142" t="s">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="B142" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C142" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="D142" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E142">
-        <v>29.5</v>
+        <v>7.5</v>
       </c>
       <c r="F142">
-        <v>30.67</v>
+        <v>7.95</v>
       </c>
       <c r="G142" s="1">
-        <v>0.535</v>
+        <v>0.533</v>
       </c>
       <c r="H142" t="s">
         <v>140</v>
       </c>
       <c r="I142" s="2">
-        <v>2.18</v>
+        <v>1.67</v>
       </c>
       <c r="J142" s="2">
-        <v>0.006</v>
+        <v>0.0023</v>
       </c>
       <c r="K142" t="s">
         <v>143</v>
@@ -6268,34 +6268,34 @@
     </row>
     <row r="143" spans="1:12">
       <c r="A143" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="B143" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="C143" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D143" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E143">
-        <v>9.5</v>
+        <v>5.5</v>
       </c>
       <c r="F143">
-        <v>9.83</v>
+        <v>5.86</v>
       </c>
       <c r="G143" s="1">
-        <v>0.534</v>
+        <v>0.532</v>
       </c>
       <c r="H143" t="s">
         <v>140</v>
       </c>
       <c r="I143" s="2">
-        <v>1.9</v>
+        <v>1.59</v>
       </c>
       <c r="J143" s="2">
-        <v>0.0026</v>
+        <v>0.0044</v>
       </c>
       <c r="K143" t="s">
         <v>143</v>
@@ -6306,37 +6306,37 @@
     </row>
     <row r="144" spans="1:12">
       <c r="A144" t="s">
-        <v>34</v>
+        <v>108</v>
       </c>
       <c r="B144" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C144" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D144" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E144">
-        <v>22.5</v>
+        <v>3.5</v>
       </c>
       <c r="F144">
-        <v>23.4</v>
+        <v>3.53</v>
       </c>
       <c r="G144" s="1">
-        <v>0.532</v>
+        <v>0.531</v>
       </c>
       <c r="H144" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I144" s="2">
-        <v>1.54</v>
+        <v>1.31</v>
       </c>
       <c r="J144" s="2">
-        <v>0.0021</v>
+        <v>0.0036</v>
       </c>
       <c r="K144" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L144" t="s">
         <v>145</v>
@@ -6344,34 +6344,34 @@
     </row>
     <row r="145" spans="1:12">
       <c r="A145" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="B145" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C145" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D145" t="s">
         <v>136</v>
       </c>
       <c r="E145">
-        <v>7.5</v>
+        <v>22.5</v>
       </c>
       <c r="F145">
-        <v>7.9</v>
+        <v>23.35</v>
       </c>
       <c r="G145" s="1">
-        <v>0.529</v>
+        <v>0.53</v>
       </c>
       <c r="H145" t="s">
         <v>140</v>
       </c>
       <c r="I145" s="2">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="J145" s="2">
-        <v>0.0014</v>
+        <v>0.0016</v>
       </c>
       <c r="K145" t="s">
         <v>144</v>
@@ -6382,34 +6382,34 @@
     </row>
     <row r="146" spans="1:12">
       <c r="A146" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="B146" t="s">
         <v>127</v>
       </c>
       <c r="C146" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D146" t="s">
         <v>136</v>
       </c>
       <c r="E146">
-        <v>19.5</v>
+        <v>13.5</v>
       </c>
       <c r="F146">
-        <v>19.05</v>
+        <v>14.05</v>
       </c>
       <c r="G146" s="1">
         <v>0.527</v>
       </c>
       <c r="H146" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I146" s="2">
-        <v>0.66</v>
+        <v>0.55</v>
       </c>
       <c r="J146" s="2">
-        <v>0.0018</v>
+        <v>0.0015</v>
       </c>
       <c r="K146" t="s">
         <v>144</v>
@@ -6420,34 +6420,34 @@
     </row>
     <row r="147" spans="1:12">
       <c r="A147" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="B147" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C147" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="D147" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E147">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="F147">
-        <v>5.84</v>
+        <v>2.74</v>
       </c>
       <c r="G147" s="1">
         <v>0.527</v>
       </c>
       <c r="H147" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I147" s="2">
-        <v>0.62</v>
+        <v>0.52</v>
       </c>
       <c r="J147" s="2">
-        <v>0.0017</v>
+        <v>0.0014</v>
       </c>
       <c r="K147" t="s">
         <v>144</v>
@@ -6458,34 +6458,34 @@
     </row>
     <row r="148" spans="1:12">
       <c r="A148" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B148" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C148" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="D148" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E148">
-        <v>18.5</v>
+        <v>1.5</v>
       </c>
       <c r="F148">
-        <v>17.98</v>
+        <v>1.77</v>
       </c>
       <c r="G148" s="1">
         <v>0.526</v>
       </c>
       <c r="H148" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I148" s="2">
-        <v>0.35</v>
+        <v>0.42</v>
       </c>
       <c r="J148" s="2">
-        <v>0.0005</v>
+        <v>0.0011</v>
       </c>
       <c r="K148" t="s">
         <v>144</v>
@@ -6496,34 +6496,34 @@
     </row>
     <row r="149" spans="1:12">
       <c r="A149" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="B149" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C149" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D149" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E149">
-        <v>7.5</v>
+        <v>29.5</v>
       </c>
       <c r="F149">
-        <v>7.63</v>
+        <v>30.35</v>
       </c>
       <c r="G149" s="1">
-        <v>0.525</v>
+        <v>0.526</v>
       </c>
       <c r="H149" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I149" s="2">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="J149" s="2">
-        <v>0.0004</v>
+        <v>0.0009</v>
       </c>
       <c r="K149" t="s">
         <v>144</v>
@@ -6534,34 +6534,34 @@
     </row>
     <row r="150" spans="1:12">
       <c r="A150" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="B150" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C150" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D150" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E150">
-        <v>11.5</v>
+        <v>3.5</v>
       </c>
       <c r="F150">
-        <v>11.78</v>
+        <v>3.62</v>
       </c>
       <c r="G150" s="1">
-        <v>0.525</v>
+        <v>0.526</v>
       </c>
       <c r="H150" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I150" s="2">
-        <v>0.23</v>
+        <v>0.33</v>
       </c>
       <c r="J150" s="2">
-        <v>0.0003</v>
+        <v>0.0009</v>
       </c>
       <c r="K150" t="s">
         <v>144</v>
@@ -6572,22 +6572,22 @@
     </row>
     <row r="151" spans="1:12">
       <c r="A151" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="B151" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C151" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D151" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E151">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="F151">
-        <v>1.76</v>
+        <v>9.75</v>
       </c>
       <c r="G151" s="1">
         <v>0.525</v>
@@ -6596,10 +6596,10 @@
         <v>140</v>
       </c>
       <c r="I151" s="2">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="J151" s="2">
-        <v>0.0004</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K151" t="s">
         <v>144</v>
@@ -6610,22 +6610,22 @@
     </row>
     <row r="152" spans="1:12">
       <c r="A152" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="B152" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C152" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D152" t="s">
         <v>136</v>
       </c>
       <c r="E152">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="F152">
-        <v>11.83</v>
+        <v>10.8</v>
       </c>
       <c r="G152" s="1">
         <v>0.524</v>
@@ -6634,10 +6634,10 @@
         <v>140</v>
       </c>
       <c r="I152" s="2">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="J152" s="2">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="K152" t="s">
         <v>144</v>
@@ -6648,31 +6648,31 @@
     </row>
     <row r="153" spans="1:12">
       <c r="A153" t="s">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="B153" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="C153" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D153" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E153">
-        <v>29.5</v>
+        <v>9.5</v>
       </c>
       <c r="F153">
-        <v>30.16</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="G153" s="1">
-        <v>0.523</v>
+        <v>0.522</v>
       </c>
       <c r="H153" t="s">
         <v>140</v>
       </c>
       <c r="I153" s="2">
-        <v>-0.12</v>
+        <v>-0.27</v>
       </c>
       <c r="J153" s="2">
         <v>0</v>
@@ -6686,31 +6686,31 @@
     </row>
     <row r="154" spans="1:12">
       <c r="A154" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="B154" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C154" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D154" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E154">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="F154">
-        <v>12.89</v>
+        <v>11.05</v>
       </c>
       <c r="G154" s="1">
-        <v>0.52</v>
+        <v>0.522</v>
       </c>
       <c r="H154" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I154" s="2">
-        <v>-0.66</v>
+        <v>-0.43</v>
       </c>
       <c r="J154" s="2">
         <v>0</v>
@@ -6724,31 +6724,31 @@
     </row>
     <row r="155" spans="1:12">
       <c r="A155" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B155" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C155" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D155" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E155">
-        <v>23.5</v>
+        <v>17.5</v>
       </c>
       <c r="F155">
-        <v>23.87</v>
+        <v>17.87</v>
       </c>
       <c r="G155" s="1">
-        <v>0.519</v>
+        <v>0.52</v>
       </c>
       <c r="H155" t="s">
         <v>140</v>
       </c>
       <c r="I155" s="2">
-        <v>-0.85</v>
+        <v>-0.79</v>
       </c>
       <c r="J155" s="2">
         <v>0</v>
@@ -6762,31 +6762,31 @@
     </row>
     <row r="156" spans="1:12">
       <c r="A156" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="B156" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C156" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D156" t="s">
         <v>134</v>
       </c>
       <c r="E156">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F156">
-        <v>3.65</v>
+        <v>2.69</v>
       </c>
       <c r="G156" s="1">
-        <v>0.519</v>
+        <v>0.52</v>
       </c>
       <c r="H156" t="s">
         <v>139</v>
       </c>
       <c r="I156" s="2">
-        <v>-0.99</v>
+        <v>-0.82</v>
       </c>
       <c r="J156" s="2">
         <v>0</v>
@@ -6800,31 +6800,31 @@
     </row>
     <row r="157" spans="1:12">
       <c r="A157" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="B157" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C157" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D157" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E157">
-        <v>11.5</v>
+        <v>2.5</v>
       </c>
       <c r="F157">
-        <v>11.13</v>
+        <v>2.61</v>
       </c>
       <c r="G157" s="1">
-        <v>0.518</v>
+        <v>0.516</v>
       </c>
       <c r="H157" t="s">
         <v>139</v>
       </c>
       <c r="I157" s="2">
-        <v>-1.16</v>
+        <v>-1.54</v>
       </c>
       <c r="J157" s="2">
         <v>0</v>
@@ -6838,31 +6838,31 @@
     </row>
     <row r="158" spans="1:12">
       <c r="A158" t="s">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="B158" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C158" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="D158" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E158">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="F158">
-        <v>5.57</v>
+        <v>11.7</v>
       </c>
       <c r="G158" s="1">
-        <v>0.508</v>
+        <v>0.515</v>
       </c>
       <c r="H158" t="s">
         <v>140</v>
       </c>
       <c r="I158" s="2">
-        <v>-3.07</v>
+        <v>-1.68</v>
       </c>
       <c r="J158" s="2">
         <v>0</v>
@@ -6876,31 +6876,31 @@
     </row>
     <row r="159" spans="1:12">
       <c r="A159" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="B159" t="s">
+        <v>129</v>
+      </c>
+      <c r="C159" t="s">
         <v>115</v>
-      </c>
-      <c r="C159" t="s">
-        <v>131</v>
       </c>
       <c r="D159" t="s">
         <v>136</v>
       </c>
       <c r="E159">
-        <v>24.5</v>
+        <v>19.5</v>
       </c>
       <c r="F159">
-        <v>24.72</v>
+        <v>19.26</v>
       </c>
       <c r="G159" s="1">
-        <v>0.508</v>
+        <v>0.514</v>
       </c>
       <c r="H159" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I159" s="2">
-        <v>-3.1</v>
+        <v>-1.9</v>
       </c>
       <c r="J159" s="2">
         <v>0</v>
@@ -6914,31 +6914,31 @@
     </row>
     <row r="160" spans="1:12">
       <c r="A160" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="B160" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C160" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D160" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E160">
-        <v>3.5</v>
+        <v>11.5</v>
       </c>
       <c r="F160">
-        <v>3.71</v>
+        <v>11.64</v>
       </c>
       <c r="G160" s="1">
-        <v>0.507</v>
+        <v>0.513</v>
       </c>
       <c r="H160" t="s">
         <v>140</v>
       </c>
       <c r="I160" s="2">
-        <v>-3.15</v>
+        <v>-2.1</v>
       </c>
       <c r="J160" s="2">
         <v>0</v>
@@ -6952,31 +6952,31 @@
     </row>
     <row r="161" spans="1:12">
       <c r="A161" t="s">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="B161" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C161" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D161" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E161">
-        <v>32.5</v>
+        <v>7.5</v>
       </c>
       <c r="F161">
-        <v>32.36</v>
+        <v>7.75</v>
       </c>
       <c r="G161" s="1">
-        <v>0.506</v>
+        <v>0.511</v>
       </c>
       <c r="H161" t="s">
         <v>139</v>
       </c>
       <c r="I161" s="2">
-        <v>-3.45</v>
+        <v>-2.4</v>
       </c>
       <c r="J161" s="2">
         <v>0</v>
@@ -6990,31 +6990,31 @@
     </row>
     <row r="162" spans="1:12">
       <c r="A162" t="s">
-        <v>106</v>
+        <v>43</v>
       </c>
       <c r="B162" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="C162" t="s">
         <v>117</v>
       </c>
       <c r="D162" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E162">
-        <v>2.5</v>
+        <v>29.5</v>
       </c>
       <c r="F162">
-        <v>2.66</v>
+        <v>29.78</v>
       </c>
       <c r="G162" s="1">
-        <v>0.504</v>
+        <v>0.51</v>
       </c>
       <c r="H162" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I162" s="2">
-        <v>-3.87</v>
+        <v>-2.65</v>
       </c>
       <c r="J162" s="2">
         <v>0</v>
@@ -7028,31 +7028,31 @@
     </row>
     <row r="163" spans="1:12">
       <c r="A163" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B163" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="C163" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="D163" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E163">
-        <v>2.5</v>
+        <v>24.5</v>
       </c>
       <c r="F163">
-        <v>2.76</v>
+        <v>24.7</v>
       </c>
       <c r="G163" s="1">
-        <v>0.5</v>
+        <v>0.507</v>
       </c>
       <c r="H163" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I163" s="2">
-        <v>-4.5</v>
+        <v>-3.22</v>
       </c>
       <c r="J163" s="2">
         <v>0</v>
@@ -7066,31 +7066,31 @@
     </row>
     <row r="164" spans="1:12">
       <c r="A164" t="s">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="B164" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="C164" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D164" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E164">
-        <v>24.5</v>
+        <v>22.5</v>
       </c>
       <c r="F164">
-        <v>24.51</v>
+        <v>22.32</v>
       </c>
       <c r="G164" s="1">
-        <v>0.5</v>
+        <v>0.507</v>
       </c>
       <c r="H164" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I164" s="2">
-        <v>-4.5</v>
+        <v>-3.29</v>
       </c>
       <c r="J164" s="2">
         <v>0</v>

--- a/output/processed_props.xlsx
+++ b/output/processed_props.xlsx
@@ -52,105 +52,201 @@
     <t>Date</t>
   </si>
   <si>
+    <t>Jonas Valanciunas</t>
+  </si>
+  <si>
+    <t>Joel Embiid</t>
+  </si>
+  <si>
+    <t>Tim Hardaway Jr.</t>
+  </si>
+  <si>
+    <t>Desmond Bane</t>
+  </si>
+  <si>
+    <t>Jalen Johnson</t>
+  </si>
+  <si>
+    <t>CJ McCollum</t>
+  </si>
+  <si>
+    <t>Tyrese Maxey</t>
+  </si>
+  <si>
+    <t>Bilal Coulibaly</t>
+  </si>
+  <si>
+    <t>Brandon Miller</t>
+  </si>
+  <si>
+    <t>Dyson Daniels</t>
+  </si>
+  <si>
+    <t>Bub Carrington</t>
+  </si>
+  <si>
+    <t>Jock Landale</t>
+  </si>
+  <si>
+    <t>Donovan Mitchell</t>
+  </si>
+  <si>
+    <t>LaMelo Ball</t>
+  </si>
+  <si>
+    <t>Kris Dunn</t>
+  </si>
+  <si>
+    <t>Egor Demin</t>
+  </si>
+  <si>
+    <t>Nic Claxton</t>
+  </si>
+  <si>
+    <t>Anthony Black</t>
+  </si>
+  <si>
+    <t>Bennedict Mathurin</t>
+  </si>
+  <si>
+    <t>Onyeka Okongwu</t>
+  </si>
+  <si>
+    <t>Jarrett Allen</t>
+  </si>
+  <si>
+    <t>Corey Kispert</t>
+  </si>
+  <si>
+    <t>VJ Edgecombe</t>
+  </si>
+  <si>
+    <t>Sam Merrill</t>
+  </si>
+  <si>
+    <t>Kon Knueppel</t>
+  </si>
+  <si>
+    <t>Dennis Schroder</t>
+  </si>
+  <si>
+    <t>Nolan Traore</t>
+  </si>
+  <si>
+    <t>Jamal Murray</t>
+  </si>
+  <si>
+    <t>Wendell Carter Jr.</t>
+  </si>
+  <si>
+    <t>Paolo Banchero</t>
+  </si>
+  <si>
+    <t>Myles Turner</t>
+  </si>
+  <si>
+    <t>Dominick Barlow</t>
+  </si>
+  <si>
+    <t>James Harden</t>
+  </si>
+  <si>
+    <t>Nickeil Alexander-Walker</t>
+  </si>
+  <si>
+    <t>Julian Strawther</t>
+  </si>
+  <si>
+    <t>Noah Clowney</t>
+  </si>
+  <si>
+    <t>Nikola Jokic</t>
+  </si>
+  <si>
+    <t>Michael Porter Jr.</t>
+  </si>
+  <si>
+    <t>Brook Lopez</t>
+  </si>
+  <si>
+    <t>Quentin Grimes</t>
+  </si>
+  <si>
+    <t>Kawhi Leonard</t>
+  </si>
+  <si>
+    <t>Zaccharie Risacher</t>
+  </si>
+  <si>
+    <t>Max Christie</t>
+  </si>
+  <si>
+    <t>Pat Spencer</t>
+  </si>
+  <si>
+    <t>Christian Braun</t>
+  </si>
+  <si>
+    <t>Naz Reid</t>
+  </si>
+  <si>
+    <t>Kevin Porter Jr.</t>
+  </si>
+  <si>
+    <t>Daniel Gafford</t>
+  </si>
+  <si>
     <t>Joan Beringer</t>
   </si>
   <si>
-    <t>Jonas Valanciunas</t>
-  </si>
-  <si>
     <t>RJ Barrett</t>
   </si>
   <si>
-    <t>Joel Embiid</t>
-  </si>
-  <si>
     <t>Ayo Dosunmu</t>
   </si>
   <si>
     <t>Kyshawn George</t>
   </si>
   <si>
-    <t>Tim Hardaway Jr.</t>
-  </si>
-  <si>
     <t>Ryan Kalkbrenner</t>
   </si>
   <si>
     <t>Brandon Ingram</t>
   </si>
   <si>
-    <t>Desmond Bane</t>
-  </si>
-  <si>
-    <t>Jalen Johnson</t>
-  </si>
-  <si>
     <t>Jaylen Brown</t>
   </si>
   <si>
-    <t>CJ McCollum</t>
-  </si>
-  <si>
     <t>Tyus Jones</t>
   </si>
   <si>
     <t>Aaron Wiggins</t>
   </si>
   <si>
-    <t>Kawhi Leonard</t>
-  </si>
-  <si>
     <t>Derrick White</t>
   </si>
   <si>
     <t>Jared McCain</t>
   </si>
   <si>
-    <t>Tyrese Maxey</t>
-  </si>
-  <si>
     <t>Chet Holmgren</t>
   </si>
   <si>
-    <t>Bilal Coulibaly</t>
-  </si>
-  <si>
     <t>Nikola Vucevic</t>
   </si>
   <si>
     <t>LeBron James</t>
   </si>
   <si>
-    <t>Brandon Miller</t>
-  </si>
-  <si>
-    <t>Dyson Daniels</t>
-  </si>
-  <si>
     <t>Jaylon Tyson</t>
   </si>
   <si>
-    <t>Bub Carrington</t>
-  </si>
-  <si>
     <t>Cam Thomas</t>
   </si>
   <si>
-    <t>Jock Landale</t>
-  </si>
-  <si>
-    <t>Donovan Mitchell</t>
-  </si>
-  <si>
-    <t>LaMelo Ball</t>
-  </si>
-  <si>
     <t>Anthony Edwards</t>
   </si>
   <si>
-    <t>Brook Lopez</t>
-  </si>
-  <si>
     <t>Tristan Vukcevic</t>
   </si>
   <si>
@@ -163,9 +259,6 @@
     <t>Neemias Queta</t>
   </si>
   <si>
-    <t>Kris Dunn</t>
-  </si>
-  <si>
     <t>Grant Williams</t>
   </si>
   <si>
@@ -181,96 +274,42 @@
     <t>Brandin Podziemski</t>
   </si>
   <si>
-    <t>Egor Demin</t>
-  </si>
-  <si>
     <t>Draymond Green</t>
   </si>
   <si>
-    <t>Nic Claxton</t>
-  </si>
-  <si>
     <t>Jamal Shead</t>
   </si>
   <si>
     <t>De'Anthony Melton</t>
   </si>
   <si>
-    <t>Anthony Black</t>
-  </si>
-  <si>
     <t>Ryan Rollins</t>
   </si>
   <si>
-    <t>Bennedict Mathurin</t>
-  </si>
-  <si>
     <t>Al Horford</t>
   </si>
   <si>
-    <t>Daniel Gafford</t>
-  </si>
-  <si>
     <t>Julius Randle</t>
   </si>
   <si>
-    <t>Onyeka Okongwu</t>
-  </si>
-  <si>
-    <t>Naz Reid</t>
-  </si>
-  <si>
-    <t>Kevin Porter Jr.</t>
-  </si>
-  <si>
-    <t>Jarrett Allen</t>
-  </si>
-  <si>
     <t>Evan Mobley</t>
   </si>
   <si>
-    <t>Corey Kispert</t>
-  </si>
-  <si>
     <t>Isaiah Joe</t>
   </si>
   <si>
-    <t>VJ Edgecombe</t>
-  </si>
-  <si>
-    <t>Sam Merrill</t>
-  </si>
-  <si>
-    <t>Kon Knueppel</t>
-  </si>
-  <si>
-    <t>Dennis Schroder</t>
-  </si>
-  <si>
-    <t>Julian Strawther</t>
-  </si>
-  <si>
     <t>Klay Thompson</t>
   </si>
   <si>
     <t>Payton Pritchard</t>
   </si>
   <si>
-    <t>Nolan Traore</t>
-  </si>
-  <si>
     <t>Cason Wallace</t>
   </si>
   <si>
     <t>Donte DiVincenzo</t>
   </si>
   <si>
-    <t>Jamal Murray</t>
-  </si>
-  <si>
-    <t>Wendell Carter Jr.</t>
-  </si>
-  <si>
     <t>Luka Doncic</t>
   </si>
   <si>
@@ -283,33 +322,12 @@
     <t>Naji Marshall</t>
   </si>
   <si>
-    <t>Paolo Banchero</t>
-  </si>
-  <si>
     <t>Marcus Smart</t>
   </si>
   <si>
-    <t>Myles Turner</t>
-  </si>
-  <si>
-    <t>Dominick Barlow</t>
-  </si>
-  <si>
-    <t>Pat Spencer</t>
-  </si>
-  <si>
-    <t>James Harden</t>
-  </si>
-  <si>
-    <t>Nickeil Alexander-Walker</t>
-  </si>
-  <si>
     <t>Rui Hachimura</t>
   </si>
   <si>
-    <t>Noah Clowney</t>
-  </si>
-  <si>
     <t>Gui Santos</t>
   </si>
   <si>
@@ -319,30 +337,15 @@
     <t>Deandre Ayton</t>
   </si>
   <si>
-    <t>Nikola Jokic</t>
-  </si>
-  <si>
-    <t>Michael Porter Jr.</t>
-  </si>
-  <si>
     <t>Collin Murray-Boyles</t>
   </si>
   <si>
     <t>Sam Hauser</t>
   </si>
   <si>
-    <t>Quentin Grimes</t>
-  </si>
-  <si>
     <t>Baylor Scheierman</t>
   </si>
   <si>
-    <t>Zaccharie Risacher</t>
-  </si>
-  <si>
-    <t>Max Christie</t>
-  </si>
-  <si>
     <t>Tre Johnson</t>
   </si>
   <si>
@@ -352,63 +355,60 @@
     <t>AJ Green</t>
   </si>
   <si>
-    <t>Christian Braun</t>
-  </si>
-  <si>
     <t>Dean Wade</t>
   </si>
   <si>
+    <t>DEN</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>ORL</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>WSH</t>
+  </si>
+  <si>
+    <t>CHA</t>
+  </si>
+  <si>
+    <t>CLE</t>
+  </si>
+  <si>
+    <t>LAC</t>
+  </si>
+  <si>
+    <t>BKN</t>
+  </si>
+  <si>
+    <t>MIL</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>GS</t>
+  </si>
+  <si>
     <t>MIN</t>
   </si>
   <si>
-    <t>DEN</t>
-  </si>
-  <si>
     <t>TOR</t>
   </si>
   <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>WSH</t>
-  </si>
-  <si>
-    <t>CHA</t>
-  </si>
-  <si>
-    <t>ORL</t>
-  </si>
-  <si>
-    <t>ATL</t>
-  </si>
-  <si>
     <t>BOS</t>
   </si>
   <si>
-    <t>DAL</t>
-  </si>
-  <si>
     <t>OKC</t>
   </si>
   <si>
-    <t>LAC</t>
-  </si>
-  <si>
     <t>LAL</t>
   </si>
   <si>
-    <t>CLE</t>
-  </si>
-  <si>
-    <t>MIL</t>
-  </si>
-  <si>
-    <t>GS</t>
-  </si>
-  <si>
-    <t>BKN</t>
-  </si>
-  <si>
     <t>GSW</t>
   </si>
   <si>
@@ -418,16 +418,16 @@
     <t>IND</t>
   </si>
   <si>
+    <t>AST</t>
+  </si>
+  <si>
+    <t>PTS</t>
+  </si>
+  <si>
+    <t>PRA</t>
+  </si>
+  <si>
     <t>REB</t>
-  </si>
-  <si>
-    <t>AST</t>
-  </si>
-  <si>
-    <t>PRA</t>
-  </si>
-  <si>
-    <t>PTS</t>
   </si>
   <si>
     <t>RA</t>
@@ -857,7 +857,7 @@
   <dimension ref="A1:L164"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="5" width="8.7109375" customWidth="1"/>
@@ -916,28 +916,28 @@
         <v>114</v>
       </c>
       <c r="C2" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="D2" t="s">
         <v>134</v>
       </c>
       <c r="E2">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="F2">
-        <v>2.95</v>
+        <v>0.62</v>
       </c>
       <c r="G2" s="1">
-        <v>0.921</v>
+        <v>0.854</v>
       </c>
       <c r="H2" t="s">
         <v>139</v>
       </c>
       <c r="I2" s="2">
-        <v>75.87</v>
+        <v>62.96</v>
       </c>
       <c r="J2" s="2">
-        <v>0.1043</v>
+        <v>0.1731</v>
       </c>
       <c r="K2" t="s">
         <v>141</v>
@@ -954,28 +954,28 @@
         <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D3" t="s">
         <v>135</v>
       </c>
       <c r="E3">
-        <v>1.5</v>
+        <v>26.5</v>
       </c>
       <c r="F3">
-        <v>0.62</v>
+        <v>31.53</v>
       </c>
       <c r="G3" s="1">
-        <v>0.854</v>
+        <v>0.788</v>
       </c>
       <c r="H3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I3" s="2">
-        <v>62.96</v>
+        <v>50.45</v>
       </c>
       <c r="J3" s="2">
-        <v>0.1731</v>
+        <v>0.1387</v>
       </c>
       <c r="K3" t="s">
         <v>141</v>
@@ -989,31 +989,31 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E4">
-        <v>27.5</v>
+        <v>1.5</v>
       </c>
       <c r="F4">
-        <v>22.68</v>
+        <v>0.99</v>
       </c>
       <c r="G4" s="1">
-        <v>0.796</v>
+        <v>0.746</v>
       </c>
       <c r="H4" t="s">
         <v>139</v>
       </c>
       <c r="I4" s="2">
-        <v>52.05</v>
+        <v>42.43</v>
       </c>
       <c r="J4" s="2">
-        <v>0.0716</v>
+        <v>0.1167</v>
       </c>
       <c r="K4" t="s">
         <v>141</v>
@@ -1027,31 +1027,31 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C5" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="D5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E5">
-        <v>26.5</v>
+        <v>25.5</v>
       </c>
       <c r="F5">
-        <v>31.53</v>
+        <v>30.44</v>
       </c>
       <c r="G5" s="1">
-        <v>0.788</v>
+        <v>0.742</v>
       </c>
       <c r="H5" t="s">
         <v>140</v>
       </c>
       <c r="I5" s="2">
-        <v>50.45</v>
+        <v>41.68</v>
       </c>
       <c r="J5" s="2">
-        <v>0.1387</v>
+        <v>0.1146</v>
       </c>
       <c r="K5" t="s">
         <v>141</v>
@@ -1065,31 +1065,31 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D6" t="s">
         <v>134</v>
       </c>
       <c r="E6">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="F6">
-        <v>2.34</v>
+        <v>5.46</v>
       </c>
       <c r="G6" s="1">
-        <v>0.758</v>
+        <v>0.739</v>
       </c>
       <c r="H6" t="s">
         <v>139</v>
       </c>
       <c r="I6" s="2">
-        <v>44.64</v>
+        <v>41.1</v>
       </c>
       <c r="J6" s="2">
-        <v>0.0614</v>
+        <v>0.113</v>
       </c>
       <c r="K6" t="s">
         <v>141</v>
@@ -1103,31 +1103,31 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D7" t="s">
         <v>137</v>
       </c>
       <c r="E7">
-        <v>12.5</v>
+        <v>3.5</v>
       </c>
       <c r="F7">
-        <v>8.640000000000001</v>
+        <v>2.56</v>
       </c>
       <c r="G7" s="1">
-        <v>0.749</v>
+        <v>0.728</v>
       </c>
       <c r="H7" t="s">
         <v>139</v>
       </c>
       <c r="I7" s="2">
-        <v>43</v>
+        <v>38.92</v>
       </c>
       <c r="J7" s="2">
-        <v>0.0591</v>
+        <v>0.107</v>
       </c>
       <c r="K7" t="s">
         <v>141</v>
@@ -1144,28 +1144,28 @@
         <v>115</v>
       </c>
       <c r="C8" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E8">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="F8">
-        <v>0.99</v>
+        <v>4.99</v>
       </c>
       <c r="G8" s="1">
-        <v>0.746</v>
+        <v>0.719</v>
       </c>
       <c r="H8" t="s">
         <v>139</v>
       </c>
       <c r="I8" s="2">
-        <v>42.43</v>
+        <v>37.17</v>
       </c>
       <c r="J8" s="2">
-        <v>0.1167</v>
+        <v>0.1022</v>
       </c>
       <c r="K8" t="s">
         <v>141</v>
@@ -1179,31 +1179,31 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" t="s">
         <v>119</v>
       </c>
-      <c r="C9" t="s">
-        <v>132</v>
-      </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E9">
-        <v>7.5</v>
+        <v>10.5</v>
       </c>
       <c r="F9">
-        <v>5.99</v>
+        <v>12.91</v>
       </c>
       <c r="G9" s="1">
-        <v>0.746</v>
+        <v>0.718</v>
       </c>
       <c r="H9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I9" s="2">
-        <v>42.42</v>
+        <v>36.98</v>
       </c>
       <c r="J9" s="2">
-        <v>0.0583</v>
+        <v>0.1017</v>
       </c>
       <c r="K9" t="s">
         <v>141</v>
@@ -1217,31 +1217,31 @@
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C10" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E10">
-        <v>3.5</v>
+        <v>33.5</v>
       </c>
       <c r="F10">
-        <v>2.5</v>
+        <v>29.26</v>
       </c>
       <c r="G10" s="1">
-        <v>0.742</v>
+        <v>0.71</v>
       </c>
       <c r="H10" t="s">
         <v>139</v>
       </c>
       <c r="I10" s="2">
-        <v>41.73</v>
+        <v>35.61</v>
       </c>
       <c r="J10" s="2">
-        <v>0.1148</v>
+        <v>0.0979</v>
       </c>
       <c r="K10" t="s">
         <v>141</v>
@@ -1255,31 +1255,31 @@
         <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D11" t="s">
         <v>136</v>
       </c>
       <c r="E11">
-        <v>25.5</v>
+        <v>23.5</v>
       </c>
       <c r="F11">
-        <v>30.44</v>
+        <v>19.35</v>
       </c>
       <c r="G11" s="1">
-        <v>0.742</v>
+        <v>0.707</v>
       </c>
       <c r="H11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I11" s="2">
-        <v>41.68</v>
+        <v>34.95</v>
       </c>
       <c r="J11" s="2">
-        <v>0.1146</v>
+        <v>0.0961</v>
       </c>
       <c r="K11" t="s">
         <v>141</v>
@@ -1293,31 +1293,31 @@
         <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C12" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="D12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E12">
-        <v>7.5</v>
+        <v>17.5</v>
       </c>
       <c r="F12">
-        <v>5.46</v>
+        <v>15.51</v>
       </c>
       <c r="G12" s="1">
-        <v>0.739</v>
+        <v>0.704</v>
       </c>
       <c r="H12" t="s">
         <v>139</v>
       </c>
       <c r="I12" s="2">
-        <v>41.1</v>
+        <v>34.35</v>
       </c>
       <c r="J12" s="2">
-        <v>0.113</v>
+        <v>0.0945</v>
       </c>
       <c r="K12" t="s">
         <v>141</v>
@@ -1331,31 +1331,31 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
+        <v>117</v>
+      </c>
+      <c r="C13" t="s">
         <v>122</v>
       </c>
-      <c r="C13" t="s">
-        <v>126</v>
-      </c>
       <c r="D13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E13">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="F13">
-        <v>3.47</v>
+        <v>1.19</v>
       </c>
       <c r="G13" s="1">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="H13" t="s">
         <v>139</v>
       </c>
       <c r="I13" s="2">
-        <v>39.44</v>
+        <v>33.69</v>
       </c>
       <c r="J13" s="2">
-        <v>0.1085</v>
+        <v>0.0927</v>
       </c>
       <c r="K13" t="s">
         <v>141</v>
@@ -1369,31 +1369,31 @@
         <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D14" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E14">
         <v>3.5</v>
       </c>
       <c r="F14">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="G14" s="1">
-        <v>0.728</v>
+        <v>0.7</v>
       </c>
       <c r="H14" t="s">
         <v>139</v>
       </c>
       <c r="I14" s="2">
-        <v>38.92</v>
+        <v>33.68</v>
       </c>
       <c r="J14" s="2">
-        <v>0.107</v>
+        <v>0.0926</v>
       </c>
       <c r="K14" t="s">
         <v>141</v>
@@ -1407,31 +1407,31 @@
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D15" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E15">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="F15">
-        <v>5.44</v>
+        <v>6.35</v>
       </c>
       <c r="G15" s="1">
-        <v>0.727</v>
+        <v>0.694</v>
       </c>
       <c r="H15" t="s">
         <v>139</v>
       </c>
       <c r="I15" s="2">
-        <v>38.7</v>
+        <v>32.48</v>
       </c>
       <c r="J15" s="2">
-        <v>0.0532</v>
+        <v>0.0893</v>
       </c>
       <c r="K15" t="s">
         <v>141</v>
@@ -1445,31 +1445,31 @@
         <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C16" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D16" t="s">
         <v>137</v>
       </c>
       <c r="E16">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="F16">
-        <v>11.11</v>
+        <v>3.74</v>
       </c>
       <c r="G16" s="1">
-        <v>0.724</v>
+        <v>0.675</v>
       </c>
       <c r="H16" t="s">
         <v>139</v>
       </c>
       <c r="I16" s="2">
-        <v>38.14</v>
+        <v>28.81</v>
       </c>
       <c r="J16" s="2">
-        <v>0.0524</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="K16" t="s">
         <v>141</v>
@@ -1483,31 +1483,31 @@
         <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C17" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E17">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F17">
-        <v>3.45</v>
+        <v>2.96</v>
       </c>
       <c r="G17" s="1">
-        <v>0.722</v>
+        <v>0.655</v>
       </c>
       <c r="H17" t="s">
         <v>139</v>
       </c>
       <c r="I17" s="2">
-        <v>37.85</v>
+        <v>25.11</v>
       </c>
       <c r="J17" s="2">
-        <v>0.052</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="K17" t="s">
         <v>141</v>
@@ -1524,28 +1524,28 @@
         <v>122</v>
       </c>
       <c r="C18" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E18">
-        <v>27.5</v>
+        <v>10.5</v>
       </c>
       <c r="F18">
-        <v>23.89</v>
+        <v>12.14</v>
       </c>
       <c r="G18" s="1">
-        <v>0.72</v>
+        <v>0.655</v>
       </c>
       <c r="H18" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I18" s="2">
-        <v>37.36</v>
+        <v>25.1</v>
       </c>
       <c r="J18" s="2">
-        <v>0.0514</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K18" t="s">
         <v>141</v>
@@ -1559,31 +1559,31 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E19">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="F19">
-        <v>1.84</v>
+        <v>3.89</v>
       </c>
       <c r="G19" s="1">
-        <v>0.719</v>
+        <v>0.65</v>
       </c>
       <c r="H19" t="s">
         <v>139</v>
       </c>
       <c r="I19" s="2">
-        <v>37.3</v>
+        <v>24.04</v>
       </c>
       <c r="J19" s="2">
-        <v>0.0513</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="K19" t="s">
         <v>141</v>
@@ -1597,31 +1597,31 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C20" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E20">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="F20">
-        <v>4.99</v>
+        <v>3.34</v>
       </c>
       <c r="G20" s="1">
-        <v>0.719</v>
+        <v>0.648</v>
       </c>
       <c r="H20" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I20" s="2">
-        <v>37.17</v>
+        <v>23.72</v>
       </c>
       <c r="J20" s="2">
-        <v>0.1022</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="K20" t="s">
         <v>141</v>
@@ -1635,31 +1635,31 @@
         <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C21" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D21" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E21">
-        <v>8.5</v>
+        <v>14.5</v>
       </c>
       <c r="F21">
-        <v>6.56</v>
+        <v>16.68</v>
       </c>
       <c r="G21" s="1">
-        <v>0.718</v>
+        <v>0.639</v>
       </c>
       <c r="H21" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I21" s="2">
-        <v>37.16</v>
+        <v>21.93</v>
       </c>
       <c r="J21" s="2">
-        <v>0.1022</v>
+        <v>0.0603</v>
       </c>
       <c r="K21" t="s">
         <v>141</v>
@@ -1673,31 +1673,31 @@
         <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C22" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="D22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E22">
-        <v>10.5</v>
+        <v>25.5</v>
       </c>
       <c r="F22">
-        <v>12.91</v>
+        <v>30.33</v>
       </c>
       <c r="G22" s="1">
-        <v>0.718</v>
+        <v>0.635</v>
       </c>
       <c r="H22" t="s">
         <v>140</v>
       </c>
       <c r="I22" s="2">
-        <v>36.98</v>
+        <v>21.25</v>
       </c>
       <c r="J22" s="2">
-        <v>0.1017</v>
+        <v>0.0584</v>
       </c>
       <c r="K22" t="s">
         <v>141</v>
@@ -1711,31 +1711,31 @@
         <v>33</v>
       </c>
       <c r="B23" t="s">
+        <v>117</v>
+      </c>
+      <c r="C23" t="s">
         <v>122</v>
       </c>
-      <c r="C23" t="s">
-        <v>126</v>
-      </c>
       <c r="D23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E23">
-        <v>2.5</v>
+        <v>13.5</v>
       </c>
       <c r="F23">
-        <v>1.87</v>
+        <v>11.56</v>
       </c>
       <c r="G23" s="1">
-        <v>0.715</v>
+        <v>0.633</v>
       </c>
       <c r="H23" t="s">
         <v>139</v>
       </c>
       <c r="I23" s="2">
-        <v>36.58</v>
+        <v>20.78</v>
       </c>
       <c r="J23" s="2">
-        <v>0.0503</v>
+        <v>0.0571</v>
       </c>
       <c r="K23" t="s">
         <v>141</v>
@@ -1749,31 +1749,31 @@
         <v>34</v>
       </c>
       <c r="B24" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" t="s">
         <v>126</v>
       </c>
-      <c r="C24" t="s">
-        <v>122</v>
-      </c>
       <c r="D24" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E24">
-        <v>19.5</v>
+        <v>3.5</v>
       </c>
       <c r="F24">
-        <v>14.55</v>
+        <v>3.17</v>
       </c>
       <c r="G24" s="1">
-        <v>0.712</v>
+        <v>0.63</v>
       </c>
       <c r="H24" t="s">
         <v>139</v>
       </c>
       <c r="I24" s="2">
-        <v>35.97</v>
+        <v>20.27</v>
       </c>
       <c r="J24" s="2">
-        <v>0.0989</v>
+        <v>0.0558</v>
       </c>
       <c r="K24" t="s">
         <v>141</v>
@@ -1787,31 +1787,31 @@
         <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C25" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D25" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E25">
-        <v>33.5</v>
+        <v>1.5</v>
       </c>
       <c r="F25">
-        <v>29.26</v>
+        <v>1.39</v>
       </c>
       <c r="G25" s="1">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="H25" t="s">
         <v>139</v>
       </c>
       <c r="I25" s="2">
-        <v>35.61</v>
+        <v>20.2</v>
       </c>
       <c r="J25" s="2">
-        <v>0.0979</v>
+        <v>0.0556</v>
       </c>
       <c r="K25" t="s">
         <v>141</v>
@@ -1825,31 +1825,31 @@
         <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C26" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D26" t="s">
         <v>136</v>
       </c>
       <c r="E26">
-        <v>23.5</v>
+        <v>30.5</v>
       </c>
       <c r="F26">
-        <v>19.35</v>
+        <v>32.67</v>
       </c>
       <c r="G26" s="1">
-        <v>0.707</v>
+        <v>0.63</v>
       </c>
       <c r="H26" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I26" s="2">
-        <v>34.95</v>
+        <v>20.19</v>
       </c>
       <c r="J26" s="2">
-        <v>0.0961</v>
+        <v>0.0555</v>
       </c>
       <c r="K26" t="s">
         <v>141</v>
@@ -1863,31 +1863,31 @@
         <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C27" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D27" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E27">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="F27">
-        <v>1.34</v>
+        <v>3.08</v>
       </c>
       <c r="G27" s="1">
-        <v>0.705</v>
+        <v>0.629</v>
       </c>
       <c r="H27" t="s">
         <v>139</v>
       </c>
       <c r="I27" s="2">
-        <v>34.67</v>
+        <v>20.09</v>
       </c>
       <c r="J27" s="2">
-        <v>0.0477</v>
+        <v>0.0553</v>
       </c>
       <c r="K27" t="s">
         <v>141</v>
@@ -1901,31 +1901,31 @@
         <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E28">
-        <v>17.5</v>
+        <v>4.5</v>
       </c>
       <c r="F28">
-        <v>15.51</v>
+        <v>5.92</v>
       </c>
       <c r="G28" s="1">
-        <v>0.704</v>
+        <v>0.626</v>
       </c>
       <c r="H28" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I28" s="2">
-        <v>34.35</v>
+        <v>19.54</v>
       </c>
       <c r="J28" s="2">
-        <v>0.0945</v>
+        <v>0.0537</v>
       </c>
       <c r="K28" t="s">
         <v>141</v>
@@ -1936,34 +1936,34 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E29">
         <v>2.5</v>
       </c>
       <c r="F29">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="G29" s="1">
-        <v>0.701</v>
+        <v>0.621</v>
       </c>
       <c r="H29" t="s">
         <v>139</v>
       </c>
       <c r="I29" s="2">
-        <v>33.78</v>
+        <v>18.46</v>
       </c>
       <c r="J29" s="2">
-        <v>0.0465</v>
+        <v>0.0508</v>
       </c>
       <c r="K29" t="s">
         <v>141</v>
@@ -1974,34 +1974,34 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C30" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D30" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E30">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="F30">
-        <v>1.19</v>
+        <v>6.86</v>
       </c>
       <c r="G30" s="1">
-        <v>0.7</v>
+        <v>0.619</v>
       </c>
       <c r="H30" t="s">
         <v>139</v>
       </c>
       <c r="I30" s="2">
-        <v>33.69</v>
+        <v>18.09</v>
       </c>
       <c r="J30" s="2">
-        <v>0.0927</v>
+        <v>0.0497</v>
       </c>
       <c r="K30" t="s">
         <v>141</v>
@@ -2012,34 +2012,34 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="C31" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D31" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E31">
-        <v>3.5</v>
+        <v>19.5</v>
       </c>
       <c r="F31">
-        <v>2.76</v>
+        <v>17.36</v>
       </c>
       <c r="G31" s="1">
-        <v>0.7</v>
+        <v>0.617</v>
       </c>
       <c r="H31" t="s">
         <v>139</v>
       </c>
       <c r="I31" s="2">
-        <v>33.68</v>
+        <v>17.82</v>
       </c>
       <c r="J31" s="2">
-        <v>0.0926</v>
+        <v>0.049</v>
       </c>
       <c r="K31" t="s">
         <v>141</v>
@@ -2050,34 +2050,34 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="B32" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D32" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E32">
-        <v>7.5</v>
+        <v>15.5</v>
       </c>
       <c r="F32">
-        <v>6.35</v>
+        <v>18.39</v>
       </c>
       <c r="G32" s="1">
-        <v>0.694</v>
+        <v>0.611</v>
       </c>
       <c r="H32" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I32" s="2">
-        <v>32.48</v>
+        <v>16.57</v>
       </c>
       <c r="J32" s="2">
-        <v>0.0893</v>
+        <v>0.0456</v>
       </c>
       <c r="K32" t="s">
         <v>141</v>
@@ -2088,34 +2088,34 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C33" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D33" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E33">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="F33">
-        <v>2.83</v>
+        <v>6.92</v>
       </c>
       <c r="G33" s="1">
-        <v>0.6830000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H33" t="s">
         <v>139</v>
       </c>
       <c r="I33" s="2">
-        <v>30.43</v>
+        <v>16.39</v>
       </c>
       <c r="J33" s="2">
-        <v>0.0837</v>
+        <v>0.0451</v>
       </c>
       <c r="K33" t="s">
         <v>141</v>
@@ -2126,34 +2126,34 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C34" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D34" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E34">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="F34">
-        <v>7.16</v>
+        <v>2.25</v>
       </c>
       <c r="G34" s="1">
-        <v>0.681</v>
+        <v>0.609</v>
       </c>
       <c r="H34" t="s">
         <v>139</v>
       </c>
       <c r="I34" s="2">
-        <v>30.02</v>
+        <v>16.36</v>
       </c>
       <c r="J34" s="2">
-        <v>0.0413</v>
+        <v>0.045</v>
       </c>
       <c r="K34" t="s">
         <v>141</v>
@@ -2164,34 +2164,34 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C35" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="D35" t="s">
         <v>134</v>
       </c>
       <c r="E35">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="F35">
-        <v>4.63</v>
+        <v>1.35</v>
       </c>
       <c r="G35" s="1">
-        <v>0.68</v>
+        <v>0.609</v>
       </c>
       <c r="H35" t="s">
         <v>139</v>
       </c>
       <c r="I35" s="2">
-        <v>29.77</v>
+        <v>16.19</v>
       </c>
       <c r="J35" s="2">
-        <v>0.0409</v>
+        <v>0.0445</v>
       </c>
       <c r="K35" t="s">
         <v>141</v>
@@ -2202,34 +2202,34 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C36" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="D36" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E36">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="F36">
-        <v>1.31</v>
+        <v>4.5</v>
       </c>
       <c r="G36" s="1">
-        <v>0.68</v>
+        <v>0.607</v>
       </c>
       <c r="H36" t="s">
         <v>139</v>
       </c>
       <c r="I36" s="2">
-        <v>29.73</v>
+        <v>15.95</v>
       </c>
       <c r="J36" s="2">
-        <v>0.0409</v>
+        <v>0.0439</v>
       </c>
       <c r="K36" t="s">
         <v>141</v>
@@ -2240,34 +2240,34 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C37" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D37" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E37">
-        <v>28.5</v>
+        <v>12.5</v>
       </c>
       <c r="F37">
-        <v>25.27</v>
+        <v>13.07</v>
       </c>
       <c r="G37" s="1">
-        <v>0.678</v>
+        <v>0.596</v>
       </c>
       <c r="H37" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I37" s="2">
-        <v>29.46</v>
+        <v>13.79</v>
       </c>
       <c r="J37" s="2">
-        <v>0.0405</v>
+        <v>0.0379</v>
       </c>
       <c r="K37" t="s">
         <v>141</v>
@@ -2278,34 +2278,34 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B38" t="s">
+        <v>117</v>
+      </c>
+      <c r="C38" t="s">
         <v>122</v>
       </c>
-      <c r="C38" t="s">
-        <v>126</v>
-      </c>
       <c r="D38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E38">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="F38">
-        <v>1.32</v>
+        <v>4.33</v>
       </c>
       <c r="G38" s="1">
-        <v>0.677</v>
+        <v>0.591</v>
       </c>
       <c r="H38" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I38" s="2">
-        <v>29.33</v>
+        <v>12.74</v>
       </c>
       <c r="J38" s="2">
-        <v>0.0403</v>
+        <v>0.035</v>
       </c>
       <c r="K38" t="s">
         <v>141</v>
@@ -2316,34 +2316,34 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="C39" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D39" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E39">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="F39">
-        <v>3.74</v>
+        <v>13.86</v>
       </c>
       <c r="G39" s="1">
-        <v>0.675</v>
+        <v>0.588</v>
       </c>
       <c r="H39" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I39" s="2">
-        <v>28.81</v>
+        <v>12.19</v>
       </c>
       <c r="J39" s="2">
-        <v>0.07920000000000001</v>
+        <v>0.0335</v>
       </c>
       <c r="K39" t="s">
         <v>141</v>
@@ -2354,34 +2354,34 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C40" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="D40" t="s">
         <v>135</v>
       </c>
       <c r="E40">
-        <v>2.5</v>
+        <v>11.5</v>
       </c>
       <c r="F40">
-        <v>2.06</v>
+        <v>9.82</v>
       </c>
       <c r="G40" s="1">
-        <v>0.674</v>
+        <v>0.587</v>
       </c>
       <c r="H40" t="s">
         <v>139</v>
       </c>
       <c r="I40" s="2">
-        <v>28.58</v>
+        <v>12.14</v>
       </c>
       <c r="J40" s="2">
-        <v>0.0393</v>
+        <v>0.0334</v>
       </c>
       <c r="K40" t="s">
         <v>141</v>
@@ -2392,34 +2392,34 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="B41" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="C41" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D41" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E41">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="F41">
-        <v>2.42</v>
+        <v>8.07</v>
       </c>
       <c r="G41" s="1">
-        <v>0.667</v>
+        <v>0.587</v>
       </c>
       <c r="H41" t="s">
         <v>139</v>
       </c>
       <c r="I41" s="2">
-        <v>27.33</v>
+        <v>12.03</v>
       </c>
       <c r="J41" s="2">
-        <v>0.0376</v>
+        <v>0.0331</v>
       </c>
       <c r="K41" t="s">
         <v>141</v>
@@ -2430,34 +2430,34 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C42" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D42" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E42">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F42">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="G42" s="1">
-        <v>0.664</v>
+        <v>0.582</v>
       </c>
       <c r="H42" t="s">
         <v>139</v>
       </c>
       <c r="I42" s="2">
-        <v>26.7</v>
+        <v>11.03</v>
       </c>
       <c r="J42" s="2">
-        <v>0.0367</v>
+        <v>0.0303</v>
       </c>
       <c r="K42" t="s">
         <v>141</v>
@@ -2468,37 +2468,37 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C43" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="D43" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E43">
-        <v>3.5</v>
+        <v>13.5</v>
       </c>
       <c r="F43">
-        <v>3.05</v>
+        <v>12.99</v>
       </c>
       <c r="G43" s="1">
-        <v>0.663</v>
+        <v>0.578</v>
       </c>
       <c r="H43" t="s">
         <v>139</v>
       </c>
       <c r="I43" s="2">
-        <v>26.59</v>
+        <v>10.33</v>
       </c>
       <c r="J43" s="2">
-        <v>0.0366</v>
+        <v>0.0284</v>
       </c>
       <c r="K43" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L43" t="s">
         <v>145</v>
@@ -2506,37 +2506,37 @@
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="B44" t="s">
+        <v>120</v>
+      </c>
+      <c r="C44" t="s">
         <v>129</v>
       </c>
-      <c r="C44" t="s">
-        <v>115</v>
-      </c>
       <c r="D44" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E44">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="F44">
-        <v>3.04</v>
+        <v>1.5</v>
       </c>
       <c r="G44" s="1">
-        <v>0.661</v>
+        <v>0.577</v>
       </c>
       <c r="H44" t="s">
         <v>139</v>
       </c>
       <c r="I44" s="2">
-        <v>26.24</v>
+        <v>10.23</v>
       </c>
       <c r="J44" s="2">
-        <v>0.0361</v>
+        <v>0.0281</v>
       </c>
       <c r="K44" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L44" t="s">
         <v>145</v>
@@ -2544,37 +2544,37 @@
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C45" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D45" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E45">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F45">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="G45" s="1">
-        <v>0.655</v>
+        <v>0.575</v>
       </c>
       <c r="H45" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I45" s="2">
-        <v>25.11</v>
+        <v>9.69</v>
       </c>
       <c r="J45" s="2">
-        <v>0.06909999999999999</v>
+        <v>0.0267</v>
       </c>
       <c r="K45" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L45" t="s">
         <v>145</v>
@@ -2582,37 +2582,37 @@
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B46" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C46" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D46" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E46">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="F46">
-        <v>3.85</v>
+        <v>1.91</v>
       </c>
       <c r="G46" s="1">
-        <v>0.655</v>
+        <v>0.57</v>
       </c>
       <c r="H46" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I46" s="2">
-        <v>25.11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J46" s="2">
-        <v>0.0345</v>
+        <v>0.0242</v>
       </c>
       <c r="K46" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L46" t="s">
         <v>145</v>
@@ -2620,37 +2620,37 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B47" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="C47" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D47" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E47">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="F47">
-        <v>12.14</v>
+        <v>16.49</v>
       </c>
       <c r="G47" s="1">
-        <v>0.655</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H47" t="s">
         <v>140</v>
       </c>
       <c r="I47" s="2">
-        <v>25.1</v>
+        <v>8.02</v>
       </c>
       <c r="J47" s="2">
-        <v>0.06900000000000001</v>
+        <v>0.0221</v>
       </c>
       <c r="K47" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L47" t="s">
         <v>145</v>
@@ -2658,37 +2658,37 @@
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="B48" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C48" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D48" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E48">
-        <v>14.5</v>
+        <v>3.5</v>
       </c>
       <c r="F48">
-        <v>12.02</v>
+        <v>3.53</v>
       </c>
       <c r="G48" s="1">
-        <v>0.653</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H48" t="s">
         <v>139</v>
       </c>
       <c r="I48" s="2">
-        <v>24.62</v>
+        <v>7.43</v>
       </c>
       <c r="J48" s="2">
-        <v>0.0339</v>
+        <v>0.0204</v>
       </c>
       <c r="K48" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L48" t="s">
         <v>145</v>
@@ -2696,37 +2696,37 @@
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B49" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C49" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D49" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E49">
-        <v>19.5</v>
+        <v>28.5</v>
       </c>
       <c r="F49">
-        <v>22.13</v>
+        <v>30.37</v>
       </c>
       <c r="G49" s="1">
-        <v>0.652</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="H49" t="s">
         <v>140</v>
       </c>
       <c r="I49" s="2">
-        <v>24.53</v>
+        <v>7.23</v>
       </c>
       <c r="J49" s="2">
-        <v>0.0337</v>
+        <v>0.0199</v>
       </c>
       <c r="K49" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L49" t="s">
         <v>145</v>
@@ -2734,37 +2734,37 @@
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B50" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C50" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D50" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E50">
-        <v>4.5</v>
+        <v>13.5</v>
       </c>
       <c r="F50">
-        <v>3.89</v>
+        <v>12.24</v>
       </c>
       <c r="G50" s="1">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H50" t="s">
         <v>139</v>
       </c>
       <c r="I50" s="2">
-        <v>24.04</v>
+        <v>6.84</v>
       </c>
       <c r="J50" s="2">
-        <v>0.06610000000000001</v>
+        <v>0.0188</v>
       </c>
       <c r="K50" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L50" t="s">
         <v>145</v>
@@ -2772,37 +2772,37 @@
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B51" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C51" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="D51" t="s">
         <v>134</v>
       </c>
       <c r="E51">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="F51">
-        <v>5.54</v>
+        <v>2.92</v>
       </c>
       <c r="G51" s="1">
-        <v>0.649</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H51" t="s">
         <v>140</v>
       </c>
       <c r="I51" s="2">
-        <v>23.86</v>
+        <v>6.5</v>
       </c>
       <c r="J51" s="2">
-        <v>0.0328</v>
+        <v>0.0179</v>
       </c>
       <c r="K51" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L51" t="s">
         <v>145</v>
@@ -2810,37 +2810,37 @@
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="B52" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C52" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D52" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E52">
-        <v>2.5</v>
+        <v>14.5</v>
       </c>
       <c r="F52">
-        <v>3.34</v>
+        <v>15.95</v>
       </c>
       <c r="G52" s="1">
-        <v>0.648</v>
+        <v>0.552</v>
       </c>
       <c r="H52" t="s">
         <v>140</v>
       </c>
       <c r="I52" s="2">
-        <v>23.72</v>
+        <v>5.31</v>
       </c>
       <c r="J52" s="2">
-        <v>0.06519999999999999</v>
+        <v>0.0146</v>
       </c>
       <c r="K52" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L52" t="s">
         <v>145</v>
@@ -2848,37 +2848,37 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="B53" t="s">
+        <v>120</v>
+      </c>
+      <c r="C53" t="s">
         <v>129</v>
       </c>
-      <c r="C53" t="s">
-        <v>115</v>
-      </c>
       <c r="D53" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E53">
-        <v>16.5</v>
+        <v>7.5</v>
       </c>
       <c r="F53">
-        <v>13.92</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G53" s="1">
-        <v>0.646</v>
+        <v>0.55</v>
       </c>
       <c r="H53" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I53" s="2">
-        <v>23.36</v>
+        <v>4.98</v>
       </c>
       <c r="J53" s="2">
-        <v>0.0321</v>
+        <v>0.0137</v>
       </c>
       <c r="K53" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L53" t="s">
         <v>145</v>
@@ -2886,37 +2886,37 @@
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="B54" t="s">
         <v>123</v>
       </c>
       <c r="C54" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D54" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E54">
         <v>7.5</v>
       </c>
       <c r="F54">
-        <v>6.62</v>
+        <v>7.87</v>
       </c>
       <c r="G54" s="1">
-        <v>0.645</v>
+        <v>0.547</v>
       </c>
       <c r="H54" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I54" s="2">
-        <v>23.07</v>
+        <v>4.42</v>
       </c>
       <c r="J54" s="2">
-        <v>0.0317</v>
+        <v>0.0121</v>
       </c>
       <c r="K54" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L54" t="s">
         <v>145</v>
@@ -2924,37 +2924,37 @@
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="B55" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C55" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D55" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E55">
-        <v>21.5</v>
+        <v>18.5</v>
       </c>
       <c r="F55">
-        <v>18.42</v>
+        <v>19.5</v>
       </c>
       <c r="G55" s="1">
-        <v>0.643</v>
+        <v>0.547</v>
       </c>
       <c r="H55" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I55" s="2">
-        <v>22.68</v>
+        <v>4.37</v>
       </c>
       <c r="J55" s="2">
-        <v>0.0312</v>
+        <v>0.012</v>
       </c>
       <c r="K55" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L55" t="s">
         <v>145</v>
@@ -2962,37 +2962,37 @@
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
+        <v>116</v>
+      </c>
+      <c r="C56" t="s">
         <v>121</v>
       </c>
-      <c r="C56" t="s">
-        <v>130</v>
-      </c>
       <c r="D56" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E56">
-        <v>14.5</v>
+        <v>1.5</v>
       </c>
       <c r="F56">
-        <v>16.68</v>
+        <v>1.83</v>
       </c>
       <c r="G56" s="1">
-        <v>0.639</v>
+        <v>0.546</v>
       </c>
       <c r="H56" t="s">
         <v>140</v>
       </c>
       <c r="I56" s="2">
-        <v>21.93</v>
+        <v>4.15</v>
       </c>
       <c r="J56" s="2">
-        <v>0.0603</v>
+        <v>0.0114</v>
       </c>
       <c r="K56" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L56" t="s">
         <v>145</v>
@@ -3000,37 +3000,37 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="B57" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C57" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D57" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E57">
-        <v>8.5</v>
+        <v>18.5</v>
       </c>
       <c r="F57">
-        <v>7.69</v>
+        <v>18.96</v>
       </c>
       <c r="G57" s="1">
-        <v>0.636</v>
+        <v>0.545</v>
       </c>
       <c r="H57" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I57" s="2">
-        <v>21.41</v>
+        <v>3.99</v>
       </c>
       <c r="J57" s="2">
-        <v>0.0294</v>
+        <v>0.011</v>
       </c>
       <c r="K57" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L57" t="s">
         <v>145</v>
@@ -3038,37 +3038,37 @@
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C58" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="D58" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E58">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="F58">
-        <v>13.13</v>
+        <v>5.42</v>
       </c>
       <c r="G58" s="1">
-        <v>0.636</v>
+        <v>0.545</v>
       </c>
       <c r="H58" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I58" s="2">
-        <v>21.37</v>
+        <v>3.95</v>
       </c>
       <c r="J58" s="2">
-        <v>0.0294</v>
+        <v>0.0109</v>
       </c>
       <c r="K58" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L58" t="s">
         <v>145</v>
@@ -3076,37 +3076,37 @@
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="B59" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C59" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D59" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E59">
-        <v>25.5</v>
+        <v>1.5</v>
       </c>
       <c r="F59">
-        <v>30.33</v>
+        <v>1.82</v>
       </c>
       <c r="G59" s="1">
-        <v>0.635</v>
+        <v>0.544</v>
       </c>
       <c r="H59" t="s">
         <v>140</v>
       </c>
       <c r="I59" s="2">
-        <v>21.25</v>
+        <v>3.78</v>
       </c>
       <c r="J59" s="2">
-        <v>0.0584</v>
+        <v>0.0104</v>
       </c>
       <c r="K59" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L59" t="s">
         <v>145</v>
@@ -3114,37 +3114,37 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B60" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C60" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D60" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E60">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="F60">
-        <v>2.35</v>
+        <v>9.92</v>
       </c>
       <c r="G60" s="1">
-        <v>0.634</v>
+        <v>0.543</v>
       </c>
       <c r="H60" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I60" s="2">
-        <v>20.97</v>
+        <v>3.59</v>
       </c>
       <c r="J60" s="2">
-        <v>0.0288</v>
+        <v>0.0049</v>
       </c>
       <c r="K60" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L60" t="s">
         <v>145</v>
@@ -3152,37 +3152,37 @@
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="B61" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C61" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D61" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E61">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="F61">
-        <v>11.56</v>
+        <v>12.08</v>
       </c>
       <c r="G61" s="1">
-        <v>0.633</v>
+        <v>0.54</v>
       </c>
       <c r="H61" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I61" s="2">
-        <v>20.78</v>
+        <v>3.13</v>
       </c>
       <c r="J61" s="2">
-        <v>0.0571</v>
+        <v>0.0086</v>
       </c>
       <c r="K61" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L61" t="s">
         <v>145</v>
@@ -3190,37 +3190,37 @@
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="B62" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C62" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D62" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E62">
-        <v>12.5</v>
+        <v>32.5</v>
       </c>
       <c r="F62">
-        <v>14.9</v>
+        <v>31.81</v>
       </c>
       <c r="G62" s="1">
-        <v>0.632</v>
+        <v>0.539</v>
       </c>
       <c r="H62" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I62" s="2">
-        <v>20.74</v>
+        <v>2.96</v>
       </c>
       <c r="J62" s="2">
-        <v>0.0285</v>
+        <v>0.0081</v>
       </c>
       <c r="K62" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L62" t="s">
         <v>145</v>
@@ -3228,37 +3228,37 @@
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="B63" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="C63" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D63" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E63">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F63">
-        <v>3.17</v>
+        <v>2.83</v>
       </c>
       <c r="G63" s="1">
-        <v>0.63</v>
+        <v>0.538</v>
       </c>
       <c r="H63" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I63" s="2">
-        <v>20.27</v>
+        <v>2.77</v>
       </c>
       <c r="J63" s="2">
-        <v>0.0558</v>
+        <v>0.0038</v>
       </c>
       <c r="K63" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L63" t="s">
         <v>145</v>
@@ -3266,37 +3266,37 @@
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="C64" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="D64" t="s">
         <v>135</v>
       </c>
       <c r="E64">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="F64">
-        <v>1.39</v>
+        <v>7.86</v>
       </c>
       <c r="G64" s="1">
-        <v>0.63</v>
+        <v>0.537</v>
       </c>
       <c r="H64" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I64" s="2">
-        <v>20.2</v>
+        <v>2.48</v>
       </c>
       <c r="J64" s="2">
-        <v>0.0556</v>
+        <v>0.0068</v>
       </c>
       <c r="K64" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L64" t="s">
         <v>145</v>
@@ -3304,37 +3304,37 @@
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B65" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C65" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D65" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E65">
-        <v>30.5</v>
+        <v>18.5</v>
       </c>
       <c r="F65">
-        <v>32.67</v>
+        <v>17.8</v>
       </c>
       <c r="G65" s="1">
-        <v>0.63</v>
+        <v>0.534</v>
       </c>
       <c r="H65" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I65" s="2">
-        <v>20.19</v>
+        <v>2</v>
       </c>
       <c r="J65" s="2">
-        <v>0.0555</v>
+        <v>0.0028</v>
       </c>
       <c r="K65" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L65" t="s">
         <v>145</v>
@@ -3342,37 +3342,37 @@
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B66" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C66" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="D66" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E66">
         <v>7.5</v>
       </c>
       <c r="F66">
-        <v>8.67</v>
+        <v>7.95</v>
       </c>
       <c r="G66" s="1">
-        <v>0.629</v>
+        <v>0.533</v>
       </c>
       <c r="H66" t="s">
         <v>140</v>
       </c>
       <c r="I66" s="2">
-        <v>20.12</v>
+        <v>1.67</v>
       </c>
       <c r="J66" s="2">
-        <v>0.0277</v>
+        <v>0.0023</v>
       </c>
       <c r="K66" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L66" t="s">
         <v>145</v>
@@ -3380,37 +3380,37 @@
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="B67" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C67" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D67" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E67">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="F67">
-        <v>3.08</v>
+        <v>5.86</v>
       </c>
       <c r="G67" s="1">
-        <v>0.629</v>
+        <v>0.532</v>
       </c>
       <c r="H67" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I67" s="2">
-        <v>20.09</v>
+        <v>1.59</v>
       </c>
       <c r="J67" s="2">
-        <v>0.0553</v>
+        <v>0.0044</v>
       </c>
       <c r="K67" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L67" t="s">
         <v>145</v>
@@ -3418,37 +3418,37 @@
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="B68" t="s">
+        <v>126</v>
+      </c>
+      <c r="C68" t="s">
         <v>115</v>
       </c>
-      <c r="C68" t="s">
-        <v>131</v>
-      </c>
       <c r="D68" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E68">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="F68">
-        <v>2.18</v>
+        <v>2.95</v>
       </c>
       <c r="G68" s="1">
-        <v>0.628</v>
+        <v>0.921</v>
       </c>
       <c r="H68" t="s">
         <v>139</v>
       </c>
       <c r="I68" s="2">
-        <v>19.95</v>
+        <v>75.87</v>
       </c>
       <c r="J68" s="2">
-        <v>0.0274</v>
+        <v>0.1043</v>
       </c>
       <c r="K68" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L68" t="s">
         <v>145</v>
@@ -3456,37 +3456,37 @@
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="B69" t="s">
+        <v>127</v>
+      </c>
+      <c r="C69" t="s">
         <v>123</v>
-      </c>
-      <c r="C69" t="s">
-        <v>133</v>
       </c>
       <c r="D69" t="s">
         <v>136</v>
       </c>
       <c r="E69">
-        <v>17.5</v>
+        <v>27.5</v>
       </c>
       <c r="F69">
-        <v>15.25</v>
+        <v>22.68</v>
       </c>
       <c r="G69" s="1">
-        <v>0.627</v>
+        <v>0.796</v>
       </c>
       <c r="H69" t="s">
         <v>139</v>
       </c>
       <c r="I69" s="2">
-        <v>19.67</v>
+        <v>52.05</v>
       </c>
       <c r="J69" s="2">
-        <v>0.027</v>
+        <v>0.0716</v>
       </c>
       <c r="K69" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L69" t="s">
         <v>145</v>
@@ -3494,37 +3494,37 @@
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="B70" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C70" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D70" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E70">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="F70">
-        <v>6.68</v>
+        <v>2.34</v>
       </c>
       <c r="G70" s="1">
-        <v>0.626</v>
+        <v>0.758</v>
       </c>
       <c r="H70" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I70" s="2">
-        <v>19.56</v>
+        <v>44.64</v>
       </c>
       <c r="J70" s="2">
-        <v>0.0269</v>
+        <v>0.0614</v>
       </c>
       <c r="K70" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L70" t="s">
         <v>145</v>
@@ -3532,37 +3532,37 @@
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="B71" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="C71" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D71" t="s">
         <v>135</v>
       </c>
       <c r="E71">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="F71">
-        <v>5.92</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G71" s="1">
-        <v>0.626</v>
+        <v>0.749</v>
       </c>
       <c r="H71" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I71" s="2">
-        <v>19.54</v>
+        <v>43</v>
       </c>
       <c r="J71" s="2">
-        <v>0.0537</v>
+        <v>0.0591</v>
       </c>
       <c r="K71" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L71" t="s">
         <v>145</v>
@@ -3570,37 +3570,37 @@
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="B72" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C72" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="D72" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E72">
-        <v>19.5</v>
+        <v>7.5</v>
       </c>
       <c r="F72">
-        <v>22.69</v>
+        <v>5.99</v>
       </c>
       <c r="G72" s="1">
-        <v>0.625</v>
+        <v>0.746</v>
       </c>
       <c r="H72" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I72" s="2">
-        <v>19.34</v>
+        <v>42.42</v>
       </c>
       <c r="J72" s="2">
-        <v>0.0266</v>
+        <v>0.0583</v>
       </c>
       <c r="K72" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L72" t="s">
         <v>145</v>
@@ -3608,13 +3608,13 @@
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="B73" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C73" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D73" t="s">
         <v>134</v>
@@ -3623,22 +3623,22 @@
         <v>3.5</v>
       </c>
       <c r="F73">
-        <v>4.31</v>
+        <v>2.5</v>
       </c>
       <c r="G73" s="1">
-        <v>0.624</v>
+        <v>0.742</v>
       </c>
       <c r="H73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I73" s="2">
-        <v>19.14</v>
+        <v>41.73</v>
       </c>
       <c r="J73" s="2">
-        <v>0.0263</v>
+        <v>0.0574</v>
       </c>
       <c r="K73" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L73" t="s">
         <v>145</v>
@@ -3646,13 +3646,13 @@
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="B74" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="C74" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="D74" t="s">
         <v>134</v>
@@ -3661,22 +3661,22 @@
         <v>4.5</v>
       </c>
       <c r="F74">
-        <v>4.03</v>
+        <v>3.47</v>
       </c>
       <c r="G74" s="1">
-        <v>0.623</v>
+        <v>0.73</v>
       </c>
       <c r="H74" t="s">
         <v>139</v>
       </c>
       <c r="I74" s="2">
-        <v>19</v>
+        <v>39.44</v>
       </c>
       <c r="J74" s="2">
-        <v>0.0261</v>
+        <v>0.0542</v>
       </c>
       <c r="K74" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L74" t="s">
         <v>145</v>
@@ -3684,37 +3684,37 @@
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B75" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C75" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="D75" t="s">
         <v>135</v>
       </c>
       <c r="E75">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="F75">
-        <v>2.32</v>
+        <v>5.44</v>
       </c>
       <c r="G75" s="1">
-        <v>0.622</v>
+        <v>0.727</v>
       </c>
       <c r="H75" t="s">
         <v>139</v>
       </c>
       <c r="I75" s="2">
-        <v>18.83</v>
+        <v>38.7</v>
       </c>
       <c r="J75" s="2">
-        <v>0.0259</v>
+        <v>0.0532</v>
       </c>
       <c r="K75" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L75" t="s">
         <v>145</v>
@@ -3722,37 +3722,37 @@
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="B76" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C76" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D76" t="s">
         <v>135</v>
       </c>
       <c r="E76">
-        <v>2.5</v>
+        <v>14.5</v>
       </c>
       <c r="F76">
-        <v>2.26</v>
+        <v>11.11</v>
       </c>
       <c r="G76" s="1">
-        <v>0.621</v>
+        <v>0.724</v>
       </c>
       <c r="H76" t="s">
         <v>139</v>
       </c>
       <c r="I76" s="2">
-        <v>18.46</v>
+        <v>38.14</v>
       </c>
       <c r="J76" s="2">
-        <v>0.0508</v>
+        <v>0.0524</v>
       </c>
       <c r="K76" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L76" t="s">
         <v>145</v>
@@ -3760,37 +3760,37 @@
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B77" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C77" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D77" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E77">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F77">
-        <v>3.12</v>
+        <v>3.45</v>
       </c>
       <c r="G77" s="1">
-        <v>0.619</v>
+        <v>0.722</v>
       </c>
       <c r="H77" t="s">
         <v>139</v>
       </c>
       <c r="I77" s="2">
-        <v>18.25</v>
+        <v>37.85</v>
       </c>
       <c r="J77" s="2">
-        <v>0.0251</v>
+        <v>0.052</v>
       </c>
       <c r="K77" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L77" t="s">
         <v>145</v>
@@ -3798,37 +3798,37 @@
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="B78" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="C78" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D78" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E78">
-        <v>7.5</v>
+        <v>27.5</v>
       </c>
       <c r="F78">
-        <v>6.86</v>
+        <v>23.89</v>
       </c>
       <c r="G78" s="1">
-        <v>0.619</v>
+        <v>0.72</v>
       </c>
       <c r="H78" t="s">
         <v>139</v>
       </c>
       <c r="I78" s="2">
-        <v>18.09</v>
+        <v>37.36</v>
       </c>
       <c r="J78" s="2">
-        <v>0.0497</v>
+        <v>0.0514</v>
       </c>
       <c r="K78" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L78" t="s">
         <v>145</v>
@@ -3836,37 +3836,37 @@
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="B79" t="s">
+        <v>129</v>
+      </c>
+      <c r="C79" t="s">
         <v>120</v>
       </c>
-      <c r="C79" t="s">
-        <v>125</v>
-      </c>
       <c r="D79" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E79">
-        <v>19.5</v>
+        <v>2.5</v>
       </c>
       <c r="F79">
-        <v>17.36</v>
+        <v>1.84</v>
       </c>
       <c r="G79" s="1">
-        <v>0.617</v>
+        <v>0.719</v>
       </c>
       <c r="H79" t="s">
         <v>139</v>
       </c>
       <c r="I79" s="2">
-        <v>17.82</v>
+        <v>37.3</v>
       </c>
       <c r="J79" s="2">
-        <v>0.049</v>
+        <v>0.0513</v>
       </c>
       <c r="K79" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L79" t="s">
         <v>145</v>
@@ -3874,37 +3874,37 @@
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="B80" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C80" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D80" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E80">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="F80">
-        <v>6.91</v>
+        <v>6.56</v>
       </c>
       <c r="G80" s="1">
-        <v>0.616</v>
+        <v>0.718</v>
       </c>
       <c r="H80" t="s">
         <v>139</v>
       </c>
       <c r="I80" s="2">
-        <v>17.64</v>
+        <v>37.16</v>
       </c>
       <c r="J80" s="2">
-        <v>0.0485</v>
+        <v>0.0511</v>
       </c>
       <c r="K80" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L80" t="s">
         <v>145</v>
@@ -3912,37 +3912,37 @@
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="B81" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C81" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="D81" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E81">
-        <v>20.5</v>
+        <v>2.5</v>
       </c>
       <c r="F81">
-        <v>23.08</v>
+        <v>1.87</v>
       </c>
       <c r="G81" s="1">
-        <v>0.614</v>
+        <v>0.715</v>
       </c>
       <c r="H81" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I81" s="2">
-        <v>17.21</v>
+        <v>36.58</v>
       </c>
       <c r="J81" s="2">
-        <v>0.0237</v>
+        <v>0.0503</v>
       </c>
       <c r="K81" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L81" t="s">
         <v>145</v>
@@ -3950,37 +3950,37 @@
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="B82" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C82" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D82" t="s">
         <v>135</v>
       </c>
       <c r="E82">
-        <v>1.5</v>
+        <v>19.5</v>
       </c>
       <c r="F82">
-        <v>1.45</v>
+        <v>14.55</v>
       </c>
       <c r="G82" s="1">
-        <v>0.611</v>
+        <v>0.712</v>
       </c>
       <c r="H82" t="s">
         <v>139</v>
       </c>
       <c r="I82" s="2">
-        <v>16.73</v>
+        <v>35.97</v>
       </c>
       <c r="J82" s="2">
-        <v>0.023</v>
+        <v>0.0495</v>
       </c>
       <c r="K82" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L82" t="s">
         <v>145</v>
@@ -3988,37 +3988,37 @@
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="B83" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C83" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D83" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E83">
-        <v>15.5</v>
+        <v>1.5</v>
       </c>
       <c r="F83">
-        <v>18.39</v>
+        <v>1.34</v>
       </c>
       <c r="G83" s="1">
-        <v>0.611</v>
+        <v>0.705</v>
       </c>
       <c r="H83" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I83" s="2">
-        <v>16.57</v>
+        <v>34.67</v>
       </c>
       <c r="J83" s="2">
-        <v>0.0456</v>
+        <v>0.0477</v>
       </c>
       <c r="K83" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L83" t="s">
         <v>145</v>
@@ -4026,37 +4026,37 @@
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="B84" t="s">
         <v>123</v>
       </c>
       <c r="C84" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D84" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E84">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="F84">
-        <v>9.59</v>
+        <v>2.04</v>
       </c>
       <c r="G84" s="1">
-        <v>0.61</v>
+        <v>0.701</v>
       </c>
       <c r="H84" t="s">
         <v>139</v>
       </c>
       <c r="I84" s="2">
-        <v>16.44</v>
+        <v>33.78</v>
       </c>
       <c r="J84" s="2">
-        <v>0.0226</v>
+        <v>0.0465</v>
       </c>
       <c r="K84" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L84" t="s">
         <v>145</v>
@@ -4064,37 +4064,37 @@
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="B85" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C85" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D85" t="s">
         <v>134</v>
       </c>
       <c r="E85">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="F85">
-        <v>6.92</v>
+        <v>2.83</v>
       </c>
       <c r="G85" s="1">
-        <v>0.61</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H85" t="s">
         <v>139</v>
       </c>
       <c r="I85" s="2">
-        <v>16.39</v>
+        <v>30.43</v>
       </c>
       <c r="J85" s="2">
-        <v>0.0451</v>
+        <v>0.0418</v>
       </c>
       <c r="K85" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L85" t="s">
         <v>145</v>
@@ -4102,37 +4102,37 @@
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="B86" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C86" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D86" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E86">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="F86">
-        <v>3.21</v>
+        <v>7.16</v>
       </c>
       <c r="G86" s="1">
-        <v>0.61</v>
+        <v>0.681</v>
       </c>
       <c r="H86" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I86" s="2">
-        <v>16.38</v>
+        <v>30.02</v>
       </c>
       <c r="J86" s="2">
-        <v>0.0225</v>
+        <v>0.0413</v>
       </c>
       <c r="K86" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L86" t="s">
         <v>145</v>
@@ -4140,37 +4140,37 @@
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="B87" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C87" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="D87" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E87">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="F87">
-        <v>2.25</v>
+        <v>4.63</v>
       </c>
       <c r="G87" s="1">
-        <v>0.609</v>
+        <v>0.68</v>
       </c>
       <c r="H87" t="s">
         <v>139</v>
       </c>
       <c r="I87" s="2">
-        <v>16.36</v>
+        <v>29.77</v>
       </c>
       <c r="J87" s="2">
-        <v>0.045</v>
+        <v>0.0409</v>
       </c>
       <c r="K87" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L87" t="s">
         <v>145</v>
@@ -4178,37 +4178,37 @@
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="B88" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C88" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D88" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E88">
         <v>1.5</v>
       </c>
       <c r="F88">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="G88" s="1">
-        <v>0.609</v>
+        <v>0.68</v>
       </c>
       <c r="H88" t="s">
         <v>139</v>
       </c>
       <c r="I88" s="2">
-        <v>16.19</v>
+        <v>29.73</v>
       </c>
       <c r="J88" s="2">
-        <v>0.0445</v>
+        <v>0.0409</v>
       </c>
       <c r="K88" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L88" t="s">
         <v>145</v>
@@ -4216,37 +4216,37 @@
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="B89" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="C89" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D89" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E89">
-        <v>4.5</v>
+        <v>28.5</v>
       </c>
       <c r="F89">
-        <v>4.5</v>
+        <v>25.27</v>
       </c>
       <c r="G89" s="1">
-        <v>0.607</v>
+        <v>0.678</v>
       </c>
       <c r="H89" t="s">
         <v>139</v>
       </c>
       <c r="I89" s="2">
-        <v>15.95</v>
+        <v>29.46</v>
       </c>
       <c r="J89" s="2">
-        <v>0.0439</v>
+        <v>0.0405</v>
       </c>
       <c r="K89" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L89" t="s">
         <v>145</v>
@@ -4254,37 +4254,37 @@
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="B90" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C90" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="D90" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E90">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="F90">
-        <v>5.07</v>
+        <v>1.32</v>
       </c>
       <c r="G90" s="1">
-        <v>0.606</v>
+        <v>0.677</v>
       </c>
       <c r="H90" t="s">
         <v>139</v>
       </c>
       <c r="I90" s="2">
-        <v>15.74</v>
+        <v>29.33</v>
       </c>
       <c r="J90" s="2">
-        <v>0.0216</v>
+        <v>0.0403</v>
       </c>
       <c r="K90" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L90" t="s">
         <v>145</v>
@@ -4292,37 +4292,37 @@
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B91" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C91" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="D91" t="s">
         <v>134</v>
       </c>
       <c r="E91">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="F91">
-        <v>4.15</v>
+        <v>2.06</v>
       </c>
       <c r="G91" s="1">
-        <v>0.599</v>
+        <v>0.674</v>
       </c>
       <c r="H91" t="s">
         <v>139</v>
       </c>
       <c r="I91" s="2">
-        <v>14.45</v>
+        <v>28.58</v>
       </c>
       <c r="J91" s="2">
-        <v>0.0199</v>
+        <v>0.0393</v>
       </c>
       <c r="K91" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L91" t="s">
         <v>145</v>
@@ -4330,37 +4330,37 @@
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="B92" t="s">
+        <v>123</v>
+      </c>
+      <c r="C92" t="s">
         <v>127</v>
       </c>
-      <c r="C92" t="s">
-        <v>124</v>
-      </c>
       <c r="D92" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E92">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="F92">
-        <v>13.07</v>
+        <v>2.42</v>
       </c>
       <c r="G92" s="1">
-        <v>0.596</v>
+        <v>0.667</v>
       </c>
       <c r="H92" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I92" s="2">
-        <v>13.79</v>
+        <v>27.33</v>
       </c>
       <c r="J92" s="2">
-        <v>0.0379</v>
+        <v>0.0376</v>
       </c>
       <c r="K92" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L92" t="s">
         <v>145</v>
@@ -4368,37 +4368,37 @@
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="B93" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C93" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D93" t="s">
         <v>137</v>
       </c>
       <c r="E93">
-        <v>11.5</v>
+        <v>4.5</v>
       </c>
       <c r="F93">
-        <v>12.77</v>
+        <v>3.82</v>
       </c>
       <c r="G93" s="1">
-        <v>0.594</v>
+        <v>0.664</v>
       </c>
       <c r="H93" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I93" s="2">
-        <v>13.43</v>
+        <v>26.7</v>
       </c>
       <c r="J93" s="2">
-        <v>0.0185</v>
+        <v>0.0367</v>
       </c>
       <c r="K93" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L93" t="s">
         <v>145</v>
@@ -4406,37 +4406,37 @@
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B94" t="s">
+        <v>116</v>
+      </c>
+      <c r="C94" t="s">
         <v>121</v>
       </c>
-      <c r="C94" t="s">
-        <v>130</v>
-      </c>
       <c r="D94" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E94">
         <v>3.5</v>
       </c>
       <c r="F94">
-        <v>4.33</v>
+        <v>3.05</v>
       </c>
       <c r="G94" s="1">
-        <v>0.591</v>
+        <v>0.663</v>
       </c>
       <c r="H94" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I94" s="2">
-        <v>12.74</v>
+        <v>26.59</v>
       </c>
       <c r="J94" s="2">
-        <v>0.035</v>
+        <v>0.0366</v>
       </c>
       <c r="K94" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L94" t="s">
         <v>145</v>
@@ -4444,37 +4444,37 @@
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B95" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C95" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D95" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E95">
-        <v>12.5</v>
+        <v>3.5</v>
       </c>
       <c r="F95">
-        <v>14.21</v>
+        <v>3.04</v>
       </c>
       <c r="G95" s="1">
-        <v>0.589</v>
+        <v>0.661</v>
       </c>
       <c r="H95" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I95" s="2">
-        <v>12.54</v>
+        <v>26.24</v>
       </c>
       <c r="J95" s="2">
-        <v>0.0172</v>
+        <v>0.0361</v>
       </c>
       <c r="K95" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L95" t="s">
         <v>145</v>
@@ -4482,37 +4482,37 @@
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B96" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C96" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="D96" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E96">
-        <v>12.5</v>
+        <v>4.5</v>
       </c>
       <c r="F96">
-        <v>13.86</v>
+        <v>3.85</v>
       </c>
       <c r="G96" s="1">
-        <v>0.588</v>
+        <v>0.655</v>
       </c>
       <c r="H96" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I96" s="2">
-        <v>12.19</v>
+        <v>25.11</v>
       </c>
       <c r="J96" s="2">
-        <v>0.0335</v>
+        <v>0.0345</v>
       </c>
       <c r="K96" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L96" t="s">
         <v>145</v>
@@ -4520,37 +4520,37 @@
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B97" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C97" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D97" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E97">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="F97">
-        <v>9.82</v>
+        <v>12.02</v>
       </c>
       <c r="G97" s="1">
-        <v>0.587</v>
+        <v>0.653</v>
       </c>
       <c r="H97" t="s">
         <v>139</v>
       </c>
       <c r="I97" s="2">
-        <v>12.14</v>
+        <v>24.62</v>
       </c>
       <c r="J97" s="2">
-        <v>0.0334</v>
+        <v>0.0339</v>
       </c>
       <c r="K97" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L97" t="s">
         <v>145</v>
@@ -4558,37 +4558,37 @@
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="B98" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C98" t="s">
         <v>114</v>
       </c>
       <c r="D98" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E98">
-        <v>8.5</v>
+        <v>19.5</v>
       </c>
       <c r="F98">
-        <v>8.07</v>
+        <v>22.13</v>
       </c>
       <c r="G98" s="1">
-        <v>0.587</v>
+        <v>0.652</v>
       </c>
       <c r="H98" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I98" s="2">
-        <v>12.03</v>
+        <v>24.53</v>
       </c>
       <c r="J98" s="2">
-        <v>0.0331</v>
+        <v>0.0337</v>
       </c>
       <c r="K98" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L98" t="s">
         <v>145</v>
@@ -4596,37 +4596,37 @@
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B99" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C99" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D99" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E99">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F99">
-        <v>5.23</v>
+        <v>5.54</v>
       </c>
       <c r="G99" s="1">
-        <v>0.586</v>
+        <v>0.649</v>
       </c>
       <c r="H99" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I99" s="2">
-        <v>11.94</v>
+        <v>23.86</v>
       </c>
       <c r="J99" s="2">
-        <v>0.0164</v>
+        <v>0.0328</v>
       </c>
       <c r="K99" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L99" t="s">
         <v>145</v>
@@ -4634,37 +4634,37 @@
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B100" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C100" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="D100" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E100">
-        <v>8.5</v>
+        <v>16.5</v>
       </c>
       <c r="F100">
-        <v>8.07</v>
+        <v>13.92</v>
       </c>
       <c r="G100" s="1">
-        <v>0.585</v>
+        <v>0.646</v>
       </c>
       <c r="H100" t="s">
         <v>139</v>
       </c>
       <c r="I100" s="2">
-        <v>11.7</v>
+        <v>23.36</v>
       </c>
       <c r="J100" s="2">
-        <v>0.0161</v>
+        <v>0.0321</v>
       </c>
       <c r="K100" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L100" t="s">
         <v>145</v>
@@ -4672,37 +4672,37 @@
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="B101" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C101" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D101" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E101">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="F101">
-        <v>3.6</v>
+        <v>6.62</v>
       </c>
       <c r="G101" s="1">
-        <v>0.582</v>
+        <v>0.645</v>
       </c>
       <c r="H101" t="s">
         <v>139</v>
       </c>
       <c r="I101" s="2">
-        <v>11.03</v>
+        <v>23.07</v>
       </c>
       <c r="J101" s="2">
-        <v>0.0303</v>
+        <v>0.0317</v>
       </c>
       <c r="K101" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L101" t="s">
         <v>145</v>
@@ -4710,37 +4710,37 @@
     </row>
     <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="B102" t="s">
         <v>126</v>
       </c>
       <c r="C102" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D102" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E102">
-        <v>9.5</v>
+        <v>21.5</v>
       </c>
       <c r="F102">
-        <v>10.89</v>
+        <v>18.42</v>
       </c>
       <c r="G102" s="1">
-        <v>0.578</v>
+        <v>0.643</v>
       </c>
       <c r="H102" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I102" s="2">
-        <v>10.38</v>
+        <v>22.68</v>
       </c>
       <c r="J102" s="2">
-        <v>0.0143</v>
+        <v>0.0312</v>
       </c>
       <c r="K102" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L102" t="s">
         <v>145</v>
@@ -4748,37 +4748,37 @@
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="B103" t="s">
+        <v>126</v>
+      </c>
+      <c r="C103" t="s">
         <v>115</v>
       </c>
-      <c r="C103" t="s">
-        <v>131</v>
-      </c>
       <c r="D103" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E103">
-        <v>13.5</v>
+        <v>8.5</v>
       </c>
       <c r="F103">
-        <v>12.99</v>
+        <v>7.69</v>
       </c>
       <c r="G103" s="1">
-        <v>0.578</v>
+        <v>0.636</v>
       </c>
       <c r="H103" t="s">
         <v>139</v>
       </c>
       <c r="I103" s="2">
-        <v>10.33</v>
+        <v>21.41</v>
       </c>
       <c r="J103" s="2">
-        <v>0.0284</v>
+        <v>0.0294</v>
       </c>
       <c r="K103" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L103" t="s">
         <v>145</v>
@@ -4786,37 +4786,37 @@
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B104" t="s">
+        <v>123</v>
+      </c>
+      <c r="C104" t="s">
         <v>127</v>
       </c>
-      <c r="C104" t="s">
-        <v>124</v>
-      </c>
       <c r="D104" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E104">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="F104">
-        <v>1.5</v>
+        <v>13.13</v>
       </c>
       <c r="G104" s="1">
-        <v>0.577</v>
+        <v>0.636</v>
       </c>
       <c r="H104" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I104" s="2">
-        <v>10.23</v>
+        <v>21.37</v>
       </c>
       <c r="J104" s="2">
-        <v>0.0281</v>
+        <v>0.0294</v>
       </c>
       <c r="K104" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L104" t="s">
         <v>145</v>
@@ -4824,37 +4824,37 @@
     </row>
     <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B105" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C105" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D105" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E105">
         <v>2.5</v>
       </c>
       <c r="F105">
-        <v>2.99</v>
+        <v>2.35</v>
       </c>
       <c r="G105" s="1">
-        <v>0.575</v>
+        <v>0.634</v>
       </c>
       <c r="H105" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I105" s="2">
-        <v>9.69</v>
+        <v>20.97</v>
       </c>
       <c r="J105" s="2">
-        <v>0.0267</v>
+        <v>0.0288</v>
       </c>
       <c r="K105" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L105" t="s">
         <v>145</v>
@@ -4862,37 +4862,37 @@
     </row>
     <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B106" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="C106" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D106" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E106">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="F106">
-        <v>5.28</v>
+        <v>14.9</v>
       </c>
       <c r="G106" s="1">
-        <v>0.574</v>
+        <v>0.632</v>
       </c>
       <c r="H106" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I106" s="2">
-        <v>9.49</v>
+        <v>20.74</v>
       </c>
       <c r="J106" s="2">
-        <v>0.0131</v>
+        <v>0.0285</v>
       </c>
       <c r="K106" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L106" t="s">
         <v>145</v>
@@ -4900,37 +4900,37 @@
     </row>
     <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="B107" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C107" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D107" t="s">
         <v>135</v>
       </c>
       <c r="E107">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="F107">
-        <v>1.47</v>
+        <v>8.67</v>
       </c>
       <c r="G107" s="1">
-        <v>0.572</v>
+        <v>0.629</v>
       </c>
       <c r="H107" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I107" s="2">
-        <v>9.220000000000001</v>
+        <v>20.12</v>
       </c>
       <c r="J107" s="2">
-        <v>0.0127</v>
+        <v>0.0277</v>
       </c>
       <c r="K107" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L107" t="s">
         <v>145</v>
@@ -4938,37 +4938,37 @@
     </row>
     <row r="108" spans="1:12">
       <c r="A108" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B108" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C108" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="D108" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E108">
-        <v>19.5</v>
+        <v>2.5</v>
       </c>
       <c r="F108">
-        <v>20.86</v>
+        <v>2.18</v>
       </c>
       <c r="G108" s="1">
-        <v>0.571</v>
+        <v>0.628</v>
       </c>
       <c r="H108" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I108" s="2">
-        <v>8.93</v>
+        <v>19.95</v>
       </c>
       <c r="J108" s="2">
-        <v>0.0123</v>
+        <v>0.0274</v>
       </c>
       <c r="K108" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L108" t="s">
         <v>145</v>
@@ -4976,37 +4976,37 @@
     </row>
     <row r="109" spans="1:12">
       <c r="A109" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="B109" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C109" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D109" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E109">
-        <v>2.5</v>
+        <v>17.5</v>
       </c>
       <c r="F109">
-        <v>2.4</v>
+        <v>15.25</v>
       </c>
       <c r="G109" s="1">
-        <v>0.571</v>
+        <v>0.627</v>
       </c>
       <c r="H109" t="s">
         <v>139</v>
       </c>
       <c r="I109" s="2">
-        <v>8.92</v>
+        <v>19.67</v>
       </c>
       <c r="J109" s="2">
-        <v>0.0123</v>
+        <v>0.027</v>
       </c>
       <c r="K109" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L109" t="s">
         <v>145</v>
@@ -5014,37 +5014,37 @@
     </row>
     <row r="110" spans="1:12">
       <c r="A110" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="B110" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C110" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="D110" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E110">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="F110">
-        <v>1.91</v>
+        <v>6.68</v>
       </c>
       <c r="G110" s="1">
-        <v>0.57</v>
+        <v>0.626</v>
       </c>
       <c r="H110" t="s">
         <v>140</v>
       </c>
       <c r="I110" s="2">
-        <v>8.800000000000001</v>
+        <v>19.56</v>
       </c>
       <c r="J110" s="2">
-        <v>0.0242</v>
+        <v>0.0269</v>
       </c>
       <c r="K110" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L110" t="s">
         <v>145</v>
@@ -5052,37 +5052,37 @@
     </row>
     <row r="111" spans="1:12">
       <c r="A111" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="B111" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C111" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D111" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E111">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="F111">
-        <v>13.84</v>
+        <v>22.69</v>
       </c>
       <c r="G111" s="1">
-        <v>0.569</v>
+        <v>0.625</v>
       </c>
       <c r="H111" t="s">
         <v>140</v>
       </c>
       <c r="I111" s="2">
-        <v>8.69</v>
+        <v>19.34</v>
       </c>
       <c r="J111" s="2">
-        <v>0.0119</v>
+        <v>0.0266</v>
       </c>
       <c r="K111" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L111" t="s">
         <v>145</v>
@@ -5090,37 +5090,37 @@
     </row>
     <row r="112" spans="1:12">
       <c r="A112" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B112" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="C112" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D112" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E112">
-        <v>15.5</v>
+        <v>3.5</v>
       </c>
       <c r="F112">
-        <v>16.49</v>
+        <v>4.31</v>
       </c>
       <c r="G112" s="1">
-        <v>0.5659999999999999</v>
+        <v>0.624</v>
       </c>
       <c r="H112" t="s">
         <v>140</v>
       </c>
       <c r="I112" s="2">
-        <v>8.02</v>
+        <v>19.14</v>
       </c>
       <c r="J112" s="2">
-        <v>0.0221</v>
+        <v>0.0263</v>
       </c>
       <c r="K112" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L112" t="s">
         <v>145</v>
@@ -5128,37 +5128,37 @@
     </row>
     <row r="113" spans="1:12">
       <c r="A113" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="B113" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C113" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D113" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E113">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="F113">
-        <v>2.16</v>
+        <v>4.03</v>
       </c>
       <c r="G113" s="1">
-        <v>0.5639999999999999</v>
+        <v>0.623</v>
       </c>
       <c r="H113" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I113" s="2">
-        <v>7.69</v>
+        <v>19</v>
       </c>
       <c r="J113" s="2">
-        <v>0.0106</v>
+        <v>0.0261</v>
       </c>
       <c r="K113" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L113" t="s">
         <v>145</v>
@@ -5166,37 +5166,37 @@
     </row>
     <row r="114" spans="1:12">
       <c r="A114" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="B114" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C114" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D114" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E114">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F114">
-        <v>3.53</v>
+        <v>2.32</v>
       </c>
       <c r="G114" s="1">
-        <v>0.5629999999999999</v>
+        <v>0.622</v>
       </c>
       <c r="H114" t="s">
         <v>139</v>
       </c>
       <c r="I114" s="2">
-        <v>7.43</v>
+        <v>18.83</v>
       </c>
       <c r="J114" s="2">
-        <v>0.0204</v>
+        <v>0.0259</v>
       </c>
       <c r="K114" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L114" t="s">
         <v>145</v>
@@ -5204,37 +5204,37 @@
     </row>
     <row r="115" spans="1:12">
       <c r="A115" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="B115" t="s">
         <v>116</v>
       </c>
       <c r="C115" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D115" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E115">
-        <v>9.5</v>
+        <v>3.5</v>
       </c>
       <c r="F115">
-        <v>10.25</v>
+        <v>3.12</v>
       </c>
       <c r="G115" s="1">
-        <v>0.5629999999999999</v>
+        <v>0.619</v>
       </c>
       <c r="H115" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I115" s="2">
-        <v>7.42</v>
+        <v>18.25</v>
       </c>
       <c r="J115" s="2">
-        <v>0.0102</v>
+        <v>0.0251</v>
       </c>
       <c r="K115" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L115" t="s">
         <v>145</v>
@@ -5242,37 +5242,37 @@
     </row>
     <row r="116" spans="1:12">
       <c r="A116" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="B116" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C116" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D116" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E116">
-        <v>28.5</v>
+        <v>7.5</v>
       </c>
       <c r="F116">
-        <v>30.37</v>
+        <v>6.91</v>
       </c>
       <c r="G116" s="1">
-        <v>0.5620000000000001</v>
+        <v>0.616</v>
       </c>
       <c r="H116" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I116" s="2">
-        <v>7.23</v>
+        <v>17.64</v>
       </c>
       <c r="J116" s="2">
-        <v>0.0199</v>
+        <v>0.0243</v>
       </c>
       <c r="K116" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L116" t="s">
         <v>145</v>
@@ -5280,37 +5280,37 @@
     </row>
     <row r="117" spans="1:12">
       <c r="A117" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B117" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C117" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D117" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E117">
-        <v>13.5</v>
+        <v>20.5</v>
       </c>
       <c r="F117">
-        <v>12.24</v>
+        <v>23.08</v>
       </c>
       <c r="G117" s="1">
-        <v>0.5600000000000001</v>
+        <v>0.614</v>
       </c>
       <c r="H117" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I117" s="2">
-        <v>6.84</v>
+        <v>17.21</v>
       </c>
       <c r="J117" s="2">
-        <v>0.0188</v>
+        <v>0.0237</v>
       </c>
       <c r="K117" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L117" t="s">
         <v>145</v>
@@ -5318,37 +5318,37 @@
     </row>
     <row r="118" spans="1:12">
       <c r="A118" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B118" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C118" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="D118" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E118">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F118">
-        <v>2.92</v>
+        <v>1.45</v>
       </c>
       <c r="G118" s="1">
-        <v>0.5580000000000001</v>
+        <v>0.611</v>
       </c>
       <c r="H118" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I118" s="2">
-        <v>6.5</v>
+        <v>16.73</v>
       </c>
       <c r="J118" s="2">
-        <v>0.0179</v>
+        <v>0.023</v>
       </c>
       <c r="K118" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L118" t="s">
         <v>145</v>
@@ -5356,37 +5356,37 @@
     </row>
     <row r="119" spans="1:12">
       <c r="A119" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="B119" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C119" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="D119" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E119">
-        <v>6.5</v>
+        <v>10.5</v>
       </c>
       <c r="F119">
-        <v>7.05</v>
+        <v>9.59</v>
       </c>
       <c r="G119" s="1">
-        <v>0.5570000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H119" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I119" s="2">
-        <v>6.39</v>
+        <v>16.44</v>
       </c>
       <c r="J119" s="2">
-        <v>0.008800000000000001</v>
+        <v>0.0226</v>
       </c>
       <c r="K119" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L119" t="s">
         <v>145</v>
@@ -5394,37 +5394,37 @@
     </row>
     <row r="120" spans="1:12">
       <c r="A120" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B120" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C120" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D120" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E120">
-        <v>9.5</v>
+        <v>2.5</v>
       </c>
       <c r="F120">
-        <v>10.26</v>
+        <v>3.21</v>
       </c>
       <c r="G120" s="1">
-        <v>0.5570000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H120" t="s">
         <v>140</v>
       </c>
       <c r="I120" s="2">
-        <v>6.37</v>
+        <v>16.38</v>
       </c>
       <c r="J120" s="2">
-        <v>0.008800000000000001</v>
+        <v>0.0225</v>
       </c>
       <c r="K120" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L120" t="s">
         <v>145</v>
@@ -5432,37 +5432,37 @@
     </row>
     <row r="121" spans="1:12">
       <c r="A121" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B121" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C121" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D121" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E121">
-        <v>12.5</v>
+        <v>5.5</v>
       </c>
       <c r="F121">
-        <v>13.6</v>
+        <v>5.07</v>
       </c>
       <c r="G121" s="1">
-        <v>0.5570000000000001</v>
+        <v>0.606</v>
       </c>
       <c r="H121" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I121" s="2">
-        <v>6.32</v>
+        <v>15.74</v>
       </c>
       <c r="J121" s="2">
-        <v>0.008699999999999999</v>
+        <v>0.0216</v>
       </c>
       <c r="K121" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L121" t="s">
         <v>145</v>
@@ -5470,37 +5470,37 @@
     </row>
     <row r="122" spans="1:12">
       <c r="A122" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="B122" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C122" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D122" t="s">
         <v>137</v>
       </c>
       <c r="E122">
-        <v>12.5</v>
+        <v>4.5</v>
       </c>
       <c r="F122">
-        <v>13.21</v>
+        <v>4.15</v>
       </c>
       <c r="G122" s="1">
-        <v>0.5570000000000001</v>
+        <v>0.599</v>
       </c>
       <c r="H122" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I122" s="2">
-        <v>6.25</v>
+        <v>14.45</v>
       </c>
       <c r="J122" s="2">
-        <v>0.0086</v>
+        <v>0.0199</v>
       </c>
       <c r="K122" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L122" t="s">
         <v>145</v>
@@ -5508,37 +5508,37 @@
     </row>
     <row r="123" spans="1:12">
       <c r="A123" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="B123" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C123" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D123" t="s">
         <v>135</v>
       </c>
       <c r="E123">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="F123">
-        <v>1.63</v>
+        <v>12.77</v>
       </c>
       <c r="G123" s="1">
-        <v>0.556</v>
+        <v>0.594</v>
       </c>
       <c r="H123" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I123" s="2">
-        <v>6.14</v>
+        <v>13.43</v>
       </c>
       <c r="J123" s="2">
-        <v>0.008399999999999999</v>
+        <v>0.0185</v>
       </c>
       <c r="K123" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L123" t="s">
         <v>145</v>
@@ -5546,37 +5546,37 @@
     </row>
     <row r="124" spans="1:12">
       <c r="A124" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C124" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D124" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E124">
-        <v>3.5</v>
+        <v>12.5</v>
       </c>
       <c r="F124">
-        <v>3.41</v>
+        <v>14.21</v>
       </c>
       <c r="G124" s="1">
-        <v>0.555</v>
+        <v>0.589</v>
       </c>
       <c r="H124" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I124" s="2">
-        <v>5.98</v>
+        <v>12.54</v>
       </c>
       <c r="J124" s="2">
-        <v>0.008200000000000001</v>
+        <v>0.0172</v>
       </c>
       <c r="K124" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L124" t="s">
         <v>145</v>
@@ -5584,37 +5584,37 @@
     </row>
     <row r="125" spans="1:12">
       <c r="A125" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B125" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C125" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D125" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E125">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="F125">
-        <v>1.86</v>
+        <v>5.23</v>
       </c>
       <c r="G125" s="1">
-        <v>0.554</v>
+        <v>0.586</v>
       </c>
       <c r="H125" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I125" s="2">
-        <v>5.75</v>
+        <v>11.94</v>
       </c>
       <c r="J125" s="2">
-        <v>0.007900000000000001</v>
+        <v>0.0164</v>
       </c>
       <c r="K125" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L125" t="s">
         <v>145</v>
@@ -5622,37 +5622,37 @@
     </row>
     <row r="126" spans="1:12">
       <c r="A126" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B126" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="C126" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D126" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E126">
-        <v>14.5</v>
+        <v>8.5</v>
       </c>
       <c r="F126">
-        <v>15.95</v>
+        <v>8.07</v>
       </c>
       <c r="G126" s="1">
-        <v>0.552</v>
+        <v>0.585</v>
       </c>
       <c r="H126" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I126" s="2">
-        <v>5.31</v>
+        <v>11.7</v>
       </c>
       <c r="J126" s="2">
-        <v>0.0146</v>
+        <v>0.0161</v>
       </c>
       <c r="K126" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L126" t="s">
         <v>145</v>
@@ -5660,37 +5660,37 @@
     </row>
     <row r="127" spans="1:12">
       <c r="A127" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B127" t="s">
+        <v>130</v>
+      </c>
+      <c r="C127" t="s">
         <v>128</v>
-      </c>
-      <c r="C127" t="s">
-        <v>116</v>
       </c>
       <c r="D127" t="s">
         <v>135</v>
       </c>
       <c r="E127">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="F127">
-        <v>1.85</v>
+        <v>10.89</v>
       </c>
       <c r="G127" s="1">
-        <v>0.55</v>
+        <v>0.578</v>
       </c>
       <c r="H127" t="s">
         <v>140</v>
       </c>
       <c r="I127" s="2">
-        <v>5.09</v>
+        <v>10.38</v>
       </c>
       <c r="J127" s="2">
-        <v>0.007</v>
+        <v>0.0143</v>
       </c>
       <c r="K127" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L127" t="s">
         <v>145</v>
@@ -5698,37 +5698,37 @@
     </row>
     <row r="128" spans="1:12">
       <c r="A128" t="s">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="B128" t="s">
         <v>127</v>
       </c>
       <c r="C128" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D128" t="s">
         <v>137</v>
       </c>
       <c r="E128">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="F128">
-        <v>8.710000000000001</v>
+        <v>5.28</v>
       </c>
       <c r="G128" s="1">
-        <v>0.55</v>
+        <v>0.574</v>
       </c>
       <c r="H128" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I128" s="2">
-        <v>4.98</v>
+        <v>9.49</v>
       </c>
       <c r="J128" s="2">
-        <v>0.0137</v>
+        <v>0.0131</v>
       </c>
       <c r="K128" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L128" t="s">
         <v>145</v>
@@ -5736,37 +5736,37 @@
     </row>
     <row r="129" spans="1:12">
       <c r="A129" t="s">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="B129" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C129" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D129" t="s">
         <v>134</v>
       </c>
       <c r="E129">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="F129">
-        <v>3.91</v>
+        <v>1.47</v>
       </c>
       <c r="G129" s="1">
-        <v>0.549</v>
+        <v>0.572</v>
       </c>
       <c r="H129" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I129" s="2">
-        <v>4.84</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="J129" s="2">
-        <v>0.0066</v>
+        <v>0.0127</v>
       </c>
       <c r="K129" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L129" t="s">
         <v>145</v>
@@ -5774,37 +5774,37 @@
     </row>
     <row r="130" spans="1:12">
       <c r="A130" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="B130" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C130" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D130" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E130">
-        <v>7.5</v>
+        <v>19.5</v>
       </c>
       <c r="F130">
-        <v>7.87</v>
+        <v>20.86</v>
       </c>
       <c r="G130" s="1">
-        <v>0.547</v>
+        <v>0.571</v>
       </c>
       <c r="H130" t="s">
         <v>140</v>
       </c>
       <c r="I130" s="2">
-        <v>4.42</v>
+        <v>8.93</v>
       </c>
       <c r="J130" s="2">
-        <v>0.0121</v>
+        <v>0.0123</v>
       </c>
       <c r="K130" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L130" t="s">
         <v>145</v>
@@ -5812,37 +5812,37 @@
     </row>
     <row r="131" spans="1:12">
       <c r="A131" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="B131" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C131" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D131" t="s">
         <v>137</v>
       </c>
       <c r="E131">
-        <v>18.5</v>
+        <v>2.5</v>
       </c>
       <c r="F131">
-        <v>19.5</v>
+        <v>2.4</v>
       </c>
       <c r="G131" s="1">
-        <v>0.547</v>
+        <v>0.571</v>
       </c>
       <c r="H131" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I131" s="2">
-        <v>4.37</v>
+        <v>8.92</v>
       </c>
       <c r="J131" s="2">
-        <v>0.012</v>
+        <v>0.0123</v>
       </c>
       <c r="K131" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L131" t="s">
         <v>145</v>
@@ -5850,37 +5850,37 @@
     </row>
     <row r="132" spans="1:12">
       <c r="A132" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B132" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C132" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D132" t="s">
         <v>135</v>
       </c>
       <c r="E132">
-        <v>1.5</v>
+        <v>12.5</v>
       </c>
       <c r="F132">
-        <v>1.83</v>
+        <v>13.84</v>
       </c>
       <c r="G132" s="1">
-        <v>0.546</v>
+        <v>0.569</v>
       </c>
       <c r="H132" t="s">
         <v>140</v>
       </c>
       <c r="I132" s="2">
-        <v>4.15</v>
+        <v>8.69</v>
       </c>
       <c r="J132" s="2">
-        <v>0.0114</v>
+        <v>0.0119</v>
       </c>
       <c r="K132" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L132" t="s">
         <v>145</v>
@@ -5888,37 +5888,37 @@
     </row>
     <row r="133" spans="1:12">
       <c r="A133" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="B133" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C133" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="D133" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E133">
-        <v>18.5</v>
+        <v>1.5</v>
       </c>
       <c r="F133">
-        <v>18.96</v>
+        <v>2.16</v>
       </c>
       <c r="G133" s="1">
-        <v>0.545</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H133" t="s">
         <v>140</v>
       </c>
       <c r="I133" s="2">
-        <v>3.99</v>
+        <v>7.69</v>
       </c>
       <c r="J133" s="2">
-        <v>0.011</v>
+        <v>0.0106</v>
       </c>
       <c r="K133" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L133" t="s">
         <v>145</v>
@@ -5926,37 +5926,37 @@
     </row>
     <row r="134" spans="1:12">
       <c r="A134" t="s">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="B134" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C134" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D134" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E134">
-        <v>5.5</v>
+        <v>9.5</v>
       </c>
       <c r="F134">
-        <v>5.42</v>
+        <v>10.25</v>
       </c>
       <c r="G134" s="1">
-        <v>0.545</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H134" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I134" s="2">
-        <v>3.95</v>
+        <v>7.42</v>
       </c>
       <c r="J134" s="2">
-        <v>0.0109</v>
+        <v>0.0102</v>
       </c>
       <c r="K134" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L134" t="s">
         <v>145</v>
@@ -5964,37 +5964,37 @@
     </row>
     <row r="135" spans="1:12">
       <c r="A135" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="B135" t="s">
+        <v>128</v>
+      </c>
+      <c r="C135" t="s">
         <v>130</v>
       </c>
-      <c r="C135" t="s">
-        <v>121</v>
-      </c>
       <c r="D135" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E135">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="F135">
-        <v>1.82</v>
+        <v>7.05</v>
       </c>
       <c r="G135" s="1">
-        <v>0.544</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H135" t="s">
         <v>140</v>
       </c>
       <c r="I135" s="2">
-        <v>3.78</v>
+        <v>6.39</v>
       </c>
       <c r="J135" s="2">
-        <v>0.0104</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="K135" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L135" t="s">
         <v>145</v>
@@ -6002,37 +6002,37 @@
     </row>
     <row r="136" spans="1:12">
       <c r="A136" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="B136" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C136" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="D136" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E136">
         <v>9.5</v>
       </c>
       <c r="F136">
-        <v>9.92</v>
+        <v>10.26</v>
       </c>
       <c r="G136" s="1">
-        <v>0.543</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H136" t="s">
         <v>140</v>
       </c>
       <c r="I136" s="2">
-        <v>3.59</v>
+        <v>6.37</v>
       </c>
       <c r="J136" s="2">
-        <v>0.0049</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="K136" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L136" t="s">
         <v>145</v>
@@ -6040,37 +6040,37 @@
     </row>
     <row r="137" spans="1:12">
       <c r="A137" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="B137" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C137" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="D137" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E137">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="F137">
-        <v>12.08</v>
+        <v>13.6</v>
       </c>
       <c r="G137" s="1">
-        <v>0.54</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H137" t="s">
         <v>140</v>
       </c>
       <c r="I137" s="2">
-        <v>3.13</v>
+        <v>6.32</v>
       </c>
       <c r="J137" s="2">
-        <v>0.0086</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="K137" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L137" t="s">
         <v>145</v>
@@ -6078,37 +6078,37 @@
     </row>
     <row r="138" spans="1:12">
       <c r="A138" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B138" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C138" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D138" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E138">
-        <v>32.5</v>
+        <v>12.5</v>
       </c>
       <c r="F138">
-        <v>31.81</v>
+        <v>13.21</v>
       </c>
       <c r="G138" s="1">
-        <v>0.539</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H138" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I138" s="2">
-        <v>2.96</v>
+        <v>6.25</v>
       </c>
       <c r="J138" s="2">
-        <v>0.0081</v>
+        <v>0.0086</v>
       </c>
       <c r="K138" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L138" t="s">
         <v>145</v>
@@ -6116,37 +6116,37 @@
     </row>
     <row r="139" spans="1:12">
       <c r="A139" t="s">
-        <v>67</v>
+        <v>110</v>
       </c>
       <c r="B139" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C139" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D139" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E139">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F139">
-        <v>2.83</v>
+        <v>1.63</v>
       </c>
       <c r="G139" s="1">
-        <v>0.538</v>
+        <v>0.556</v>
       </c>
       <c r="H139" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I139" s="2">
-        <v>2.77</v>
+        <v>6.14</v>
       </c>
       <c r="J139" s="2">
-        <v>0.0038</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="K139" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L139" t="s">
         <v>145</v>
@@ -6154,37 +6154,37 @@
     </row>
     <row r="140" spans="1:12">
       <c r="A140" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="B140" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="C140" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="D140" t="s">
         <v>137</v>
       </c>
       <c r="E140">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="F140">
-        <v>7.86</v>
+        <v>3.41</v>
       </c>
       <c r="G140" s="1">
-        <v>0.537</v>
+        <v>0.555</v>
       </c>
       <c r="H140" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I140" s="2">
-        <v>2.48</v>
+        <v>5.98</v>
       </c>
       <c r="J140" s="2">
-        <v>0.0068</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="K140" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L140" t="s">
         <v>145</v>
@@ -6192,37 +6192,37 @@
     </row>
     <row r="141" spans="1:12">
       <c r="A141" t="s">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="B141" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C141" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D141" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E141">
-        <v>18.5</v>
+        <v>1.5</v>
       </c>
       <c r="F141">
-        <v>17.8</v>
+        <v>1.86</v>
       </c>
       <c r="G141" s="1">
-        <v>0.534</v>
+        <v>0.554</v>
       </c>
       <c r="H141" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I141" s="2">
-        <v>2</v>
+        <v>5.75</v>
       </c>
       <c r="J141" s="2">
-        <v>0.0028</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="K141" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L141" t="s">
         <v>145</v>
@@ -6230,37 +6230,37 @@
     </row>
     <row r="142" spans="1:12">
       <c r="A142" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="B142" t="s">
         <v>123</v>
       </c>
       <c r="C142" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D142" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E142">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="F142">
-        <v>7.95</v>
+        <v>1.85</v>
       </c>
       <c r="G142" s="1">
-        <v>0.533</v>
+        <v>0.55</v>
       </c>
       <c r="H142" t="s">
         <v>140</v>
       </c>
       <c r="I142" s="2">
-        <v>1.67</v>
+        <v>5.09</v>
       </c>
       <c r="J142" s="2">
-        <v>0.0023</v>
+        <v>0.007</v>
       </c>
       <c r="K142" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L142" t="s">
         <v>145</v>
@@ -6268,37 +6268,37 @@
     </row>
     <row r="143" spans="1:12">
       <c r="A143" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B143" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="C143" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D143" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E143">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="F143">
-        <v>5.86</v>
+        <v>3.91</v>
       </c>
       <c r="G143" s="1">
-        <v>0.532</v>
+        <v>0.549</v>
       </c>
       <c r="H143" t="s">
         <v>140</v>
       </c>
       <c r="I143" s="2">
-        <v>1.59</v>
+        <v>4.84</v>
       </c>
       <c r="J143" s="2">
-        <v>0.0044</v>
+        <v>0.0066</v>
       </c>
       <c r="K143" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L143" t="s">
         <v>145</v>
@@ -6306,16 +6306,16 @@
     </row>
     <row r="144" spans="1:12">
       <c r="A144" t="s">
-        <v>108</v>
+        <v>54</v>
       </c>
       <c r="B144" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C144" t="s">
         <v>133</v>
       </c>
       <c r="D144" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E144">
         <v>3.5</v>
@@ -6344,13 +6344,13 @@
     </row>
     <row r="145" spans="1:12">
       <c r="A145" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="B145" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C145" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D145" t="s">
         <v>136</v>
@@ -6382,13 +6382,13 @@
     </row>
     <row r="146" spans="1:12">
       <c r="A146" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="B146" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C146" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D146" t="s">
         <v>136</v>
@@ -6420,16 +6420,16 @@
     </row>
     <row r="147" spans="1:12">
       <c r="A147" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="B147" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C147" t="s">
         <v>131</v>
       </c>
       <c r="D147" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E147">
         <v>2.5</v>
@@ -6458,16 +6458,16 @@
     </row>
     <row r="148" spans="1:12">
       <c r="A148" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="B148" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C148" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D148" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E148">
         <v>1.5</v>
@@ -6496,16 +6496,16 @@
     </row>
     <row r="149" spans="1:12">
       <c r="A149" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="B149" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C149" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D149" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E149">
         <v>29.5</v>
@@ -6523,7 +6523,7 @@
         <v>0.34</v>
       </c>
       <c r="J149" s="2">
-        <v>0.0009</v>
+        <v>0.0005</v>
       </c>
       <c r="K149" t="s">
         <v>144</v>
@@ -6537,13 +6537,13 @@
         <v>113</v>
       </c>
       <c r="B150" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C150" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D150" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E150">
         <v>3.5</v>
@@ -6572,16 +6572,16 @@
     </row>
     <row r="151" spans="1:12">
       <c r="A151" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="B151" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C151" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D151" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E151">
         <v>9.5</v>
@@ -6613,10 +6613,10 @@
         <v>113</v>
       </c>
       <c r="B152" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C152" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D152" t="s">
         <v>136</v>
@@ -6648,16 +6648,16 @@
     </row>
     <row r="153" spans="1:12">
       <c r="A153" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B153" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C153" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D153" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E153">
         <v>9.5</v>
@@ -6686,16 +6686,16 @@
     </row>
     <row r="154" spans="1:12">
       <c r="A154" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="B154" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C154" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D154" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E154">
         <v>11.5</v>
@@ -6724,7 +6724,7 @@
     </row>
     <row r="155" spans="1:12">
       <c r="A155" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B155" t="s">
         <v>118</v>
@@ -6762,16 +6762,16 @@
     </row>
     <row r="156" spans="1:12">
       <c r="A156" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B156" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C156" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D156" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E156">
         <v>2.5</v>
@@ -6800,16 +6800,16 @@
     </row>
     <row r="157" spans="1:12">
       <c r="A157" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B157" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C157" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D157" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E157">
         <v>2.5</v>
@@ -6838,7 +6838,7 @@
     </row>
     <row r="158" spans="1:12">
       <c r="A158" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="B158" t="s">
         <v>119</v>
@@ -6847,7 +6847,7 @@
         <v>132</v>
       </c>
       <c r="D158" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E158">
         <v>11.5</v>
@@ -6876,13 +6876,13 @@
     </row>
     <row r="159" spans="1:12">
       <c r="A159" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B159" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C159" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D159" t="s">
         <v>136</v>
@@ -6914,16 +6914,16 @@
     </row>
     <row r="160" spans="1:12">
       <c r="A160" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B160" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C160" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D160" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E160">
         <v>11.5</v>
@@ -6952,16 +6952,16 @@
     </row>
     <row r="161" spans="1:12">
       <c r="A161" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B161" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C161" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D161" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E161">
         <v>7.5</v>
@@ -6990,16 +6990,16 @@
     </row>
     <row r="162" spans="1:12">
       <c r="A162" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="B162" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="C162" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D162" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E162">
         <v>29.5</v>
@@ -7028,16 +7028,16 @@
     </row>
     <row r="163" spans="1:12">
       <c r="A163" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="B163" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C163" t="s">
         <v>131</v>
       </c>
       <c r="D163" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E163">
         <v>24.5</v>
@@ -7066,16 +7066,16 @@
     </row>
     <row r="164" spans="1:12">
       <c r="A164" t="s">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="B164" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C164" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D164" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E164">
         <v>22.5</v>

--- a/output/processed_props.xlsx
+++ b/output/processed_props.xlsx
@@ -55,27 +55,45 @@
     <t>Jonas Valanciunas</t>
   </si>
   <si>
+    <t>Joan Beringer</t>
+  </si>
+  <si>
     <t>Joel Embiid</t>
   </si>
   <si>
     <t>Tim Hardaway Jr.</t>
   </si>
   <si>
+    <t>Brandon Ingram</t>
+  </si>
+  <si>
     <t>Desmond Bane</t>
   </si>
   <si>
     <t>Jalen Johnson</t>
   </si>
   <si>
+    <t>Jaylen Brown</t>
+  </si>
+  <si>
     <t>CJ McCollum</t>
   </si>
   <si>
     <t>Tyrese Maxey</t>
   </si>
   <si>
+    <t>Chet Holmgren</t>
+  </si>
+  <si>
     <t>Bilal Coulibaly</t>
   </si>
   <si>
+    <t>RJ Barrett</t>
+  </si>
+  <si>
+    <t>LeBron James</t>
+  </si>
+  <si>
     <t>Brandon Miller</t>
   </si>
   <si>
@@ -94,30 +112,81 @@
     <t>LaMelo Ball</t>
   </si>
   <si>
+    <t>Ayo Dosunmu</t>
+  </si>
+  <si>
+    <t>Anthony Edwards</t>
+  </si>
+  <si>
+    <t>Kyshawn George</t>
+  </si>
+  <si>
+    <t>Ryan Kalkbrenner</t>
+  </si>
+  <si>
     <t>Kris Dunn</t>
   </si>
   <si>
+    <t>Tyus Jones</t>
+  </si>
+  <si>
+    <t>Aaron Wiggins</t>
+  </si>
+  <si>
+    <t>Kawhi Leonard</t>
+  </si>
+  <si>
+    <t>Derrick White</t>
+  </si>
+  <si>
+    <t>Jared McCain</t>
+  </si>
+  <si>
+    <t>Nikola Vucevic</t>
+  </si>
+  <si>
     <t>Egor Demin</t>
   </si>
   <si>
     <t>Nic Claxton</t>
   </si>
   <si>
+    <t>Jaylon Tyson</t>
+  </si>
+  <si>
     <t>Anthony Black</t>
   </si>
   <si>
     <t>Bennedict Mathurin</t>
   </si>
   <si>
+    <t>Cam Thomas</t>
+  </si>
+  <si>
     <t>Onyeka Okongwu</t>
   </si>
   <si>
     <t>Jarrett Allen</t>
   </si>
   <si>
+    <t>Brook Lopez</t>
+  </si>
+  <si>
+    <t>Tristan Vukcevic</t>
+  </si>
+  <si>
+    <t>Kristaps Porzingis</t>
+  </si>
+  <si>
     <t>Corey Kispert</t>
   </si>
   <si>
+    <t>Immanuel Quickley</t>
+  </si>
+  <si>
+    <t>Neemias Queta</t>
+  </si>
+  <si>
     <t>VJ Edgecombe</t>
   </si>
   <si>
@@ -130,249 +199,195 @@
     <t>Dennis Schroder</t>
   </si>
   <si>
+    <t>Grant Williams</t>
+  </si>
+  <si>
     <t>Nolan Traore</t>
   </si>
   <si>
+    <t>Kyle Kuzma</t>
+  </si>
+  <si>
+    <t>Jaden McDaniels</t>
+  </si>
+  <si>
+    <t>Jalen Suggs</t>
+  </si>
+  <si>
+    <t>Brandin Podziemski</t>
+  </si>
+  <si>
     <t>Jamal Murray</t>
   </si>
   <si>
     <t>Wendell Carter Jr.</t>
   </si>
   <si>
+    <t>Luka Doncic</t>
+  </si>
+  <si>
+    <t>Draymond Green</t>
+  </si>
+  <si>
+    <t>Jamal Shead</t>
+  </si>
+  <si>
+    <t>De'Anthony Melton</t>
+  </si>
+  <si>
+    <t>Ryan Rollins</t>
+  </si>
+  <si>
     <t>Paolo Banchero</t>
   </si>
   <si>
+    <t>Al Horford</t>
+  </si>
+  <si>
     <t>Myles Turner</t>
   </si>
   <si>
+    <t>Daniel Gafford</t>
+  </si>
+  <si>
     <t>Dominick Barlow</t>
   </si>
   <si>
+    <t>Julius Randle</t>
+  </si>
+  <si>
+    <t>Naz Reid</t>
+  </si>
+  <si>
+    <t>Kevin Porter Jr.</t>
+  </si>
+  <si>
+    <t>Evan Mobley</t>
+  </si>
+  <si>
+    <t>Isaiah Joe</t>
+  </si>
+  <si>
+    <t>Julian Strawther</t>
+  </si>
+  <si>
     <t>James Harden</t>
   </si>
   <si>
+    <t>Klay Thompson</t>
+  </si>
+  <si>
+    <t>Payton Pritchard</t>
+  </si>
+  <si>
+    <t>Cason Wallace</t>
+  </si>
+  <si>
+    <t>Donte DiVincenzo</t>
+  </si>
+  <si>
     <t>Nickeil Alexander-Walker</t>
   </si>
   <si>
-    <t>Julian Strawther</t>
-  </si>
-  <si>
     <t>Noah Clowney</t>
   </si>
   <si>
+    <t>Austin Reaves</t>
+  </si>
+  <si>
+    <t>Derrick Jones Jr.</t>
+  </si>
+  <si>
+    <t>Naji Marshall</t>
+  </si>
+  <si>
+    <t>Marcus Smart</t>
+  </si>
+  <si>
+    <t>Pat Spencer</t>
+  </si>
+  <si>
     <t>Nikola Jokic</t>
   </si>
   <si>
     <t>Michael Porter Jr.</t>
   </si>
   <si>
-    <t>Brook Lopez</t>
+    <t>Rui Hachimura</t>
+  </si>
+  <si>
+    <t>Gui Santos</t>
+  </si>
+  <si>
+    <t>Isaiah Hartenstein</t>
   </si>
   <si>
     <t>Quentin Grimes</t>
   </si>
   <si>
-    <t>Kawhi Leonard</t>
+    <t>Deandre Ayton</t>
   </si>
   <si>
     <t>Zaccharie Risacher</t>
   </si>
   <si>
+    <t>Collin Murray-Boyles</t>
+  </si>
+  <si>
     <t>Max Christie</t>
   </si>
   <si>
-    <t>Pat Spencer</t>
+    <t>Sam Hauser</t>
+  </si>
+  <si>
+    <t>Baylor Scheierman</t>
+  </si>
+  <si>
+    <t>Tre Johnson</t>
+  </si>
+  <si>
+    <t>Moses Moody</t>
+  </si>
+  <si>
+    <t>AJ Green</t>
   </si>
   <si>
     <t>Christian Braun</t>
   </si>
   <si>
-    <t>Naz Reid</t>
-  </si>
-  <si>
-    <t>Kevin Porter Jr.</t>
-  </si>
-  <si>
-    <t>Daniel Gafford</t>
-  </si>
-  <si>
-    <t>Joan Beringer</t>
-  </si>
-  <si>
-    <t>RJ Barrett</t>
-  </si>
-  <si>
-    <t>Ayo Dosunmu</t>
-  </si>
-  <si>
-    <t>Kyshawn George</t>
-  </si>
-  <si>
-    <t>Ryan Kalkbrenner</t>
-  </si>
-  <si>
-    <t>Brandon Ingram</t>
-  </si>
-  <si>
-    <t>Jaylen Brown</t>
-  </si>
-  <si>
-    <t>Tyus Jones</t>
-  </si>
-  <si>
-    <t>Aaron Wiggins</t>
-  </si>
-  <si>
-    <t>Derrick White</t>
-  </si>
-  <si>
-    <t>Jared McCain</t>
-  </si>
-  <si>
-    <t>Chet Holmgren</t>
-  </si>
-  <si>
-    <t>Nikola Vucevic</t>
-  </si>
-  <si>
-    <t>LeBron James</t>
-  </si>
-  <si>
-    <t>Jaylon Tyson</t>
-  </si>
-  <si>
-    <t>Cam Thomas</t>
-  </si>
-  <si>
-    <t>Anthony Edwards</t>
-  </si>
-  <si>
-    <t>Tristan Vukcevic</t>
-  </si>
-  <si>
-    <t>Kristaps Porzingis</t>
-  </si>
-  <si>
-    <t>Immanuel Quickley</t>
-  </si>
-  <si>
-    <t>Neemias Queta</t>
-  </si>
-  <si>
-    <t>Grant Williams</t>
-  </si>
-  <si>
-    <t>Kyle Kuzma</t>
-  </si>
-  <si>
-    <t>Jaden McDaniels</t>
-  </si>
-  <si>
-    <t>Jalen Suggs</t>
-  </si>
-  <si>
-    <t>Brandin Podziemski</t>
-  </si>
-  <si>
-    <t>Draymond Green</t>
-  </si>
-  <si>
-    <t>Jamal Shead</t>
-  </si>
-  <si>
-    <t>De'Anthony Melton</t>
-  </si>
-  <si>
-    <t>Ryan Rollins</t>
-  </si>
-  <si>
-    <t>Al Horford</t>
-  </si>
-  <si>
-    <t>Julius Randle</t>
-  </si>
-  <si>
-    <t>Evan Mobley</t>
-  </si>
-  <si>
-    <t>Isaiah Joe</t>
-  </si>
-  <si>
-    <t>Klay Thompson</t>
-  </si>
-  <si>
-    <t>Payton Pritchard</t>
-  </si>
-  <si>
-    <t>Cason Wallace</t>
-  </si>
-  <si>
-    <t>Donte DiVincenzo</t>
-  </si>
-  <si>
-    <t>Luka Doncic</t>
-  </si>
-  <si>
-    <t>Austin Reaves</t>
-  </si>
-  <si>
-    <t>Derrick Jones Jr.</t>
-  </si>
-  <si>
-    <t>Naji Marshall</t>
-  </si>
-  <si>
-    <t>Marcus Smart</t>
-  </si>
-  <si>
-    <t>Rui Hachimura</t>
-  </si>
-  <si>
-    <t>Gui Santos</t>
-  </si>
-  <si>
-    <t>Isaiah Hartenstein</t>
-  </si>
-  <si>
-    <t>Deandre Ayton</t>
-  </si>
-  <si>
-    <t>Collin Murray-Boyles</t>
-  </si>
-  <si>
-    <t>Sam Hauser</t>
-  </si>
-  <si>
-    <t>Baylor Scheierman</t>
-  </si>
-  <si>
-    <t>Tre Johnson</t>
-  </si>
-  <si>
-    <t>Moses Moody</t>
-  </si>
-  <si>
-    <t>AJ Green</t>
-  </si>
-  <si>
     <t>Dean Wade</t>
   </si>
   <si>
     <t>DEN</t>
   </si>
   <si>
+    <t>MIN</t>
+  </si>
+  <si>
     <t>PHI</t>
   </si>
   <si>
+    <t>TOR</t>
+  </si>
+  <si>
     <t>ORL</t>
   </si>
   <si>
     <t>ATL</t>
   </si>
   <si>
+    <t>BOS</t>
+  </si>
+  <si>
+    <t>OKC</t>
+  </si>
+  <si>
     <t>WSH</t>
   </si>
   <si>
+    <t>LAL</t>
+  </si>
+  <si>
     <t>CHA</t>
   </si>
   <si>
@@ -382,33 +397,18 @@
     <t>LAC</t>
   </si>
   <si>
+    <t>DAL</t>
+  </si>
+  <si>
     <t>BKN</t>
   </si>
   <si>
     <t>MIL</t>
   </si>
   <si>
-    <t>DAL</t>
-  </si>
-  <si>
     <t>GS</t>
   </si>
   <si>
-    <t>MIN</t>
-  </si>
-  <si>
-    <t>TOR</t>
-  </si>
-  <si>
-    <t>BOS</t>
-  </si>
-  <si>
-    <t>OKC</t>
-  </si>
-  <si>
-    <t>LAL</t>
-  </si>
-  <si>
     <t>GSW</t>
   </si>
   <si>
@@ -421,13 +421,13 @@
     <t>AST</t>
   </si>
   <si>
+    <t>REB</t>
+  </si>
+  <si>
     <t>PTS</t>
   </si>
   <si>
     <t>PRA</t>
-  </si>
-  <si>
-    <t>REB</t>
   </si>
   <si>
     <t>RA</t>
@@ -857,7 +857,7 @@
   <dimension ref="A1:L164"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" customWidth="1"/>
+    <col min="1" max="1" width="22.7109375" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="5" width="8.7109375" customWidth="1"/>
@@ -954,28 +954,28 @@
         <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="D3" t="s">
         <v>135</v>
       </c>
       <c r="E3">
-        <v>26.5</v>
+        <v>5.5</v>
       </c>
       <c r="F3">
-        <v>31.53</v>
+        <v>2.95</v>
       </c>
       <c r="G3" s="1">
-        <v>0.788</v>
+        <v>0.891</v>
       </c>
       <c r="H3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I3" s="2">
-        <v>50.45</v>
+        <v>53.11</v>
       </c>
       <c r="J3" s="2">
-        <v>0.1387</v>
+        <v>0.1043</v>
       </c>
       <c r="K3" t="s">
         <v>141</v>
@@ -989,31 +989,31 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C4" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E4">
-        <v>1.5</v>
+        <v>26.5</v>
       </c>
       <c r="F4">
-        <v>0.99</v>
+        <v>31.53</v>
       </c>
       <c r="G4" s="1">
-        <v>0.746</v>
+        <v>0.788</v>
       </c>
       <c r="H4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I4" s="2">
-        <v>42.43</v>
+        <v>50.45</v>
       </c>
       <c r="J4" s="2">
-        <v>0.1167</v>
+        <v>0.1387</v>
       </c>
       <c r="K4" t="s">
         <v>141</v>
@@ -1027,31 +1027,31 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C5" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E5">
-        <v>25.5</v>
+        <v>1.5</v>
       </c>
       <c r="F5">
-        <v>30.44</v>
+        <v>0.99</v>
       </c>
       <c r="G5" s="1">
-        <v>0.742</v>
+        <v>0.746</v>
       </c>
       <c r="H5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I5" s="2">
-        <v>41.68</v>
+        <v>42.43</v>
       </c>
       <c r="J5" s="2">
-        <v>0.1146</v>
+        <v>0.1167</v>
       </c>
       <c r="K5" t="s">
         <v>141</v>
@@ -1068,28 +1068,28 @@
         <v>117</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="D6" t="s">
         <v>134</v>
       </c>
       <c r="E6">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="F6">
-        <v>5.46</v>
+        <v>2.5</v>
       </c>
       <c r="G6" s="1">
-        <v>0.739</v>
+        <v>0.742</v>
       </c>
       <c r="H6" t="s">
         <v>139</v>
       </c>
       <c r="I6" s="2">
-        <v>41.1</v>
+        <v>41.73</v>
       </c>
       <c r="J6" s="2">
-        <v>0.113</v>
+        <v>0.1148</v>
       </c>
       <c r="K6" t="s">
         <v>141</v>
@@ -1103,31 +1103,31 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C7" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D7" t="s">
         <v>137</v>
       </c>
       <c r="E7">
-        <v>3.5</v>
+        <v>25.5</v>
       </c>
       <c r="F7">
-        <v>2.56</v>
+        <v>30.44</v>
       </c>
       <c r="G7" s="1">
-        <v>0.728</v>
+        <v>0.742</v>
       </c>
       <c r="H7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I7" s="2">
-        <v>38.92</v>
+        <v>41.68</v>
       </c>
       <c r="J7" s="2">
-        <v>0.107</v>
+        <v>0.1146</v>
       </c>
       <c r="K7" t="s">
         <v>141</v>
@@ -1141,31 +1141,31 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D8" t="s">
         <v>134</v>
       </c>
       <c r="E8">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="F8">
-        <v>4.99</v>
+        <v>5.46</v>
       </c>
       <c r="G8" s="1">
-        <v>0.719</v>
+        <v>0.739</v>
       </c>
       <c r="H8" t="s">
         <v>139</v>
       </c>
       <c r="I8" s="2">
-        <v>37.17</v>
+        <v>41.1</v>
       </c>
       <c r="J8" s="2">
-        <v>0.1022</v>
+        <v>0.113</v>
       </c>
       <c r="K8" t="s">
         <v>141</v>
@@ -1179,31 +1179,31 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C9" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E9">
-        <v>10.5</v>
+        <v>4.5</v>
       </c>
       <c r="F9">
-        <v>12.91</v>
+        <v>3.47</v>
       </c>
       <c r="G9" s="1">
-        <v>0.718</v>
+        <v>0.73</v>
       </c>
       <c r="H9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I9" s="2">
-        <v>36.98</v>
+        <v>39.44</v>
       </c>
       <c r="J9" s="2">
-        <v>0.1017</v>
+        <v>0.1085</v>
       </c>
       <c r="K9" t="s">
         <v>141</v>
@@ -1220,28 +1220,28 @@
         <v>119</v>
       </c>
       <c r="C10" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E10">
-        <v>33.5</v>
+        <v>3.5</v>
       </c>
       <c r="F10">
-        <v>29.26</v>
+        <v>2.56</v>
       </c>
       <c r="G10" s="1">
-        <v>0.71</v>
+        <v>0.728</v>
       </c>
       <c r="H10" t="s">
         <v>139</v>
       </c>
       <c r="I10" s="2">
-        <v>35.61</v>
+        <v>38.92</v>
       </c>
       <c r="J10" s="2">
-        <v>0.0979</v>
+        <v>0.107</v>
       </c>
       <c r="K10" t="s">
         <v>141</v>
@@ -1255,31 +1255,31 @@
         <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C11" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E11">
-        <v>23.5</v>
+        <v>6.5</v>
       </c>
       <c r="F11">
-        <v>19.35</v>
+        <v>4.99</v>
       </c>
       <c r="G11" s="1">
-        <v>0.707</v>
+        <v>0.719</v>
       </c>
       <c r="H11" t="s">
         <v>139</v>
       </c>
       <c r="I11" s="2">
-        <v>34.95</v>
+        <v>37.17</v>
       </c>
       <c r="J11" s="2">
-        <v>0.0961</v>
+        <v>0.1022</v>
       </c>
       <c r="K11" t="s">
         <v>141</v>
@@ -1293,31 +1293,31 @@
         <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C12" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E12">
-        <v>17.5</v>
+        <v>8.5</v>
       </c>
       <c r="F12">
-        <v>15.51</v>
+        <v>6.56</v>
       </c>
       <c r="G12" s="1">
-        <v>0.704</v>
+        <v>0.718</v>
       </c>
       <c r="H12" t="s">
         <v>139</v>
       </c>
       <c r="I12" s="2">
-        <v>34.35</v>
+        <v>37.16</v>
       </c>
       <c r="J12" s="2">
-        <v>0.0945</v>
+        <v>0.1022</v>
       </c>
       <c r="K12" t="s">
         <v>141</v>
@@ -1331,31 +1331,31 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E13">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="F13">
-        <v>1.19</v>
+        <v>12.91</v>
       </c>
       <c r="G13" s="1">
-        <v>0.7</v>
+        <v>0.718</v>
       </c>
       <c r="H13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I13" s="2">
-        <v>33.69</v>
+        <v>36.98</v>
       </c>
       <c r="J13" s="2">
-        <v>0.0927</v>
+        <v>0.1017</v>
       </c>
       <c r="K13" t="s">
         <v>141</v>
@@ -1369,7 +1369,7 @@
         <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C14" t="s">
         <v>129</v>
@@ -1378,22 +1378,22 @@
         <v>137</v>
       </c>
       <c r="E14">
-        <v>3.5</v>
+        <v>27.5</v>
       </c>
       <c r="F14">
-        <v>2.76</v>
+        <v>22.68</v>
       </c>
       <c r="G14" s="1">
-        <v>0.7</v>
+        <v>0.766</v>
       </c>
       <c r="H14" t="s">
         <v>139</v>
       </c>
       <c r="I14" s="2">
-        <v>33.68</v>
+        <v>36.43</v>
       </c>
       <c r="J14" s="2">
-        <v>0.0926</v>
+        <v>0.0716</v>
       </c>
       <c r="K14" t="s">
         <v>141</v>
@@ -1407,31 +1407,31 @@
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C15" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="D15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E15">
-        <v>7.5</v>
+        <v>19.5</v>
       </c>
       <c r="F15">
-        <v>6.35</v>
+        <v>14.55</v>
       </c>
       <c r="G15" s="1">
-        <v>0.694</v>
+        <v>0.712</v>
       </c>
       <c r="H15" t="s">
         <v>139</v>
       </c>
       <c r="I15" s="2">
-        <v>32.48</v>
+        <v>35.97</v>
       </c>
       <c r="J15" s="2">
-        <v>0.0893</v>
+        <v>0.0989</v>
       </c>
       <c r="K15" t="s">
         <v>141</v>
@@ -1445,31 +1445,31 @@
         <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C16" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="D16" t="s">
         <v>137</v>
       </c>
       <c r="E16">
-        <v>4.5</v>
+        <v>33.5</v>
       </c>
       <c r="F16">
-        <v>3.74</v>
+        <v>29.26</v>
       </c>
       <c r="G16" s="1">
-        <v>0.675</v>
+        <v>0.71</v>
       </c>
       <c r="H16" t="s">
         <v>139</v>
       </c>
       <c r="I16" s="2">
-        <v>28.81</v>
+        <v>35.61</v>
       </c>
       <c r="J16" s="2">
-        <v>0.07920000000000001</v>
+        <v>0.0979</v>
       </c>
       <c r="K16" t="s">
         <v>141</v>
@@ -1483,31 +1483,31 @@
         <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C17" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="D17" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E17">
-        <v>3.5</v>
+        <v>23.5</v>
       </c>
       <c r="F17">
-        <v>2.96</v>
+        <v>19.35</v>
       </c>
       <c r="G17" s="1">
-        <v>0.655</v>
+        <v>0.707</v>
       </c>
       <c r="H17" t="s">
         <v>139</v>
       </c>
       <c r="I17" s="2">
-        <v>25.11</v>
+        <v>34.95</v>
       </c>
       <c r="J17" s="2">
-        <v>0.06909999999999999</v>
+        <v>0.0961</v>
       </c>
       <c r="K17" t="s">
         <v>141</v>
@@ -1524,28 +1524,28 @@
         <v>122</v>
       </c>
       <c r="C18" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E18">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="F18">
-        <v>12.14</v>
+        <v>15.51</v>
       </c>
       <c r="G18" s="1">
-        <v>0.655</v>
+        <v>0.704</v>
       </c>
       <c r="H18" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I18" s="2">
-        <v>25.1</v>
+        <v>34.35</v>
       </c>
       <c r="J18" s="2">
-        <v>0.06900000000000001</v>
+        <v>0.0945</v>
       </c>
       <c r="K18" t="s">
         <v>141</v>
@@ -1559,31 +1559,31 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C19" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="D19" t="s">
         <v>134</v>
       </c>
       <c r="E19">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="F19">
-        <v>3.89</v>
+        <v>1.19</v>
       </c>
       <c r="G19" s="1">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H19" t="s">
         <v>139</v>
       </c>
       <c r="I19" s="2">
-        <v>24.04</v>
+        <v>33.69</v>
       </c>
       <c r="J19" s="2">
-        <v>0.06610000000000001</v>
+        <v>0.0927</v>
       </c>
       <c r="K19" t="s">
         <v>141</v>
@@ -1597,31 +1597,31 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
+        <v>125</v>
+      </c>
+      <c r="C20" t="s">
         <v>121</v>
       </c>
-      <c r="C20" t="s">
-        <v>116</v>
-      </c>
       <c r="D20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E20">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F20">
-        <v>3.34</v>
+        <v>2.76</v>
       </c>
       <c r="G20" s="1">
-        <v>0.648</v>
+        <v>0.7</v>
       </c>
       <c r="H20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I20" s="2">
-        <v>23.72</v>
+        <v>33.68</v>
       </c>
       <c r="J20" s="2">
-        <v>0.06519999999999999</v>
+        <v>0.0926</v>
       </c>
       <c r="K20" t="s">
         <v>141</v>
@@ -1635,31 +1635,31 @@
         <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C21" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="D21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E21">
-        <v>14.5</v>
+        <v>7.5</v>
       </c>
       <c r="F21">
-        <v>16.68</v>
+        <v>6.35</v>
       </c>
       <c r="G21" s="1">
-        <v>0.639</v>
+        <v>0.694</v>
       </c>
       <c r="H21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I21" s="2">
-        <v>21.93</v>
+        <v>32.48</v>
       </c>
       <c r="J21" s="2">
-        <v>0.0603</v>
+        <v>0.0893</v>
       </c>
       <c r="K21" t="s">
         <v>141</v>
@@ -1673,31 +1673,31 @@
         <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="D22" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E22">
-        <v>25.5</v>
+        <v>3.5</v>
       </c>
       <c r="F22">
-        <v>30.33</v>
+        <v>2.34</v>
       </c>
       <c r="G22" s="1">
-        <v>0.635</v>
+        <v>0.728</v>
       </c>
       <c r="H22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I22" s="2">
-        <v>21.25</v>
+        <v>31.25</v>
       </c>
       <c r="J22" s="2">
-        <v>0.0584</v>
+        <v>0.0614</v>
       </c>
       <c r="K22" t="s">
         <v>141</v>
@@ -1711,31 +1711,31 @@
         <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C23" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D23" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E23">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="F23">
-        <v>11.56</v>
+        <v>2.83</v>
       </c>
       <c r="G23" s="1">
-        <v>0.633</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H23" t="s">
         <v>139</v>
       </c>
       <c r="I23" s="2">
-        <v>20.78</v>
+        <v>30.43</v>
       </c>
       <c r="J23" s="2">
-        <v>0.0571</v>
+        <v>0.0837</v>
       </c>
       <c r="K23" t="s">
         <v>141</v>
@@ -1749,31 +1749,31 @@
         <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C24" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D24" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E24">
-        <v>3.5</v>
+        <v>12.5</v>
       </c>
       <c r="F24">
-        <v>3.17</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G24" s="1">
-        <v>0.63</v>
+        <v>0.719</v>
       </c>
       <c r="H24" t="s">
         <v>139</v>
       </c>
       <c r="I24" s="2">
-        <v>20.27</v>
+        <v>30.1</v>
       </c>
       <c r="J24" s="2">
-        <v>0.0558</v>
+        <v>0.0591</v>
       </c>
       <c r="K24" t="s">
         <v>141</v>
@@ -1787,31 +1787,31 @@
         <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D25" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E25">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="F25">
-        <v>1.39</v>
+        <v>5.99</v>
       </c>
       <c r="G25" s="1">
-        <v>0.63</v>
+        <v>0.716</v>
       </c>
       <c r="H25" t="s">
         <v>139</v>
       </c>
       <c r="I25" s="2">
-        <v>20.2</v>
+        <v>29.7</v>
       </c>
       <c r="J25" s="2">
-        <v>0.0556</v>
+        <v>0.0583</v>
       </c>
       <c r="K25" t="s">
         <v>141</v>
@@ -1825,31 +1825,31 @@
         <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C26" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="D26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E26">
-        <v>30.5</v>
+        <v>4.5</v>
       </c>
       <c r="F26">
-        <v>32.67</v>
+        <v>3.74</v>
       </c>
       <c r="G26" s="1">
-        <v>0.63</v>
+        <v>0.675</v>
       </c>
       <c r="H26" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I26" s="2">
-        <v>20.19</v>
+        <v>28.81</v>
       </c>
       <c r="J26" s="2">
-        <v>0.0555</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="K26" t="s">
         <v>141</v>
@@ -1863,31 +1863,31 @@
         <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C27" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D27" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E27">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="F27">
-        <v>3.08</v>
+        <v>5.44</v>
       </c>
       <c r="G27" s="1">
-        <v>0.629</v>
+        <v>0.697</v>
       </c>
       <c r="H27" t="s">
         <v>139</v>
       </c>
       <c r="I27" s="2">
-        <v>20.09</v>
+        <v>27.09</v>
       </c>
       <c r="J27" s="2">
-        <v>0.0553</v>
+        <v>0.0532</v>
       </c>
       <c r="K27" t="s">
         <v>141</v>
@@ -1901,31 +1901,31 @@
         <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D28" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E28">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="F28">
-        <v>5.92</v>
+        <v>11.11</v>
       </c>
       <c r="G28" s="1">
-        <v>0.626</v>
+        <v>0.694</v>
       </c>
       <c r="H28" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I28" s="2">
-        <v>19.54</v>
+        <v>26.7</v>
       </c>
       <c r="J28" s="2">
-        <v>0.0537</v>
+        <v>0.0524</v>
       </c>
       <c r="K28" t="s">
         <v>141</v>
@@ -1936,34 +1936,34 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="B29" t="s">
+        <v>126</v>
+      </c>
+      <c r="C29" t="s">
         <v>118</v>
-      </c>
-      <c r="C29" t="s">
-        <v>119</v>
       </c>
       <c r="D29" t="s">
         <v>134</v>
       </c>
       <c r="E29">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="F29">
-        <v>2.26</v>
+        <v>3.45</v>
       </c>
       <c r="G29" s="1">
-        <v>0.621</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H29" t="s">
         <v>139</v>
       </c>
       <c r="I29" s="2">
-        <v>18.46</v>
+        <v>26.49</v>
       </c>
       <c r="J29" s="2">
-        <v>0.0508</v>
+        <v>0.052</v>
       </c>
       <c r="K29" t="s">
         <v>141</v>
@@ -1974,34 +1974,34 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="D30" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E30">
-        <v>7.5</v>
+        <v>27.5</v>
       </c>
       <c r="F30">
-        <v>6.86</v>
+        <v>23.89</v>
       </c>
       <c r="G30" s="1">
-        <v>0.619</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H30" t="s">
         <v>139</v>
       </c>
       <c r="I30" s="2">
-        <v>18.09</v>
+        <v>26.15</v>
       </c>
       <c r="J30" s="2">
-        <v>0.0497</v>
+        <v>0.0514</v>
       </c>
       <c r="K30" t="s">
         <v>141</v>
@@ -2012,34 +2012,34 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C31" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D31" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E31">
-        <v>19.5</v>
+        <v>2.5</v>
       </c>
       <c r="F31">
-        <v>17.36</v>
+        <v>1.84</v>
       </c>
       <c r="G31" s="1">
-        <v>0.617</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="H31" t="s">
         <v>139</v>
       </c>
       <c r="I31" s="2">
-        <v>17.82</v>
+        <v>26.11</v>
       </c>
       <c r="J31" s="2">
-        <v>0.049</v>
+        <v>0.0513</v>
       </c>
       <c r="K31" t="s">
         <v>141</v>
@@ -2050,34 +2050,34 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C32" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="D32" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E32">
-        <v>15.5</v>
+        <v>2.5</v>
       </c>
       <c r="F32">
-        <v>18.39</v>
+        <v>1.87</v>
       </c>
       <c r="G32" s="1">
-        <v>0.611</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="H32" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I32" s="2">
-        <v>16.57</v>
+        <v>25.6</v>
       </c>
       <c r="J32" s="2">
-        <v>0.0456</v>
+        <v>0.0503</v>
       </c>
       <c r="K32" t="s">
         <v>141</v>
@@ -2088,34 +2088,34 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="C33" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D33" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E33">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="F33">
-        <v>6.92</v>
+        <v>2.96</v>
       </c>
       <c r="G33" s="1">
-        <v>0.61</v>
+        <v>0.655</v>
       </c>
       <c r="H33" t="s">
         <v>139</v>
       </c>
       <c r="I33" s="2">
-        <v>16.39</v>
+        <v>25.11</v>
       </c>
       <c r="J33" s="2">
-        <v>0.0451</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="K33" t="s">
         <v>141</v>
@@ -2126,34 +2126,34 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="B34" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="C34" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D34" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E34">
-        <v>2.5</v>
+        <v>10.5</v>
       </c>
       <c r="F34">
-        <v>2.25</v>
+        <v>12.14</v>
       </c>
       <c r="G34" s="1">
-        <v>0.609</v>
+        <v>0.655</v>
       </c>
       <c r="H34" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I34" s="2">
-        <v>16.36</v>
+        <v>25.1</v>
       </c>
       <c r="J34" s="2">
-        <v>0.045</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K34" t="s">
         <v>141</v>
@@ -2164,13 +2164,13 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C35" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D35" t="s">
         <v>134</v>
@@ -2179,19 +2179,19 @@
         <v>1.5</v>
       </c>
       <c r="F35">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="G35" s="1">
-        <v>0.609</v>
+        <v>0.675</v>
       </c>
       <c r="H35" t="s">
         <v>139</v>
       </c>
       <c r="I35" s="2">
-        <v>16.19</v>
+        <v>24.27</v>
       </c>
       <c r="J35" s="2">
-        <v>0.0445</v>
+        <v>0.0477</v>
       </c>
       <c r="K35" t="s">
         <v>141</v>
@@ -2202,34 +2202,34 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B36" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C36" t="s">
         <v>126</v>
       </c>
       <c r="D36" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E36">
         <v>4.5</v>
       </c>
       <c r="F36">
-        <v>4.5</v>
+        <v>3.89</v>
       </c>
       <c r="G36" s="1">
-        <v>0.607</v>
+        <v>0.65</v>
       </c>
       <c r="H36" t="s">
         <v>139</v>
       </c>
       <c r="I36" s="2">
-        <v>15.95</v>
+        <v>24.04</v>
       </c>
       <c r="J36" s="2">
-        <v>0.0439</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="K36" t="s">
         <v>141</v>
@@ -2240,34 +2240,34 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B37" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C37" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="D37" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E37">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="F37">
-        <v>13.07</v>
+        <v>3.34</v>
       </c>
       <c r="G37" s="1">
-        <v>0.596</v>
+        <v>0.648</v>
       </c>
       <c r="H37" t="s">
         <v>140</v>
       </c>
       <c r="I37" s="2">
-        <v>13.79</v>
+        <v>23.72</v>
       </c>
       <c r="J37" s="2">
-        <v>0.0379</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="K37" t="s">
         <v>141</v>
@@ -2278,34 +2278,34 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B38" t="s">
+        <v>129</v>
+      </c>
+      <c r="C38" t="s">
         <v>117</v>
-      </c>
-      <c r="C38" t="s">
-        <v>122</v>
       </c>
       <c r="D38" t="s">
         <v>134</v>
       </c>
       <c r="E38">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F38">
-        <v>4.33</v>
+        <v>2.04</v>
       </c>
       <c r="G38" s="1">
-        <v>0.591</v>
+        <v>0.671</v>
       </c>
       <c r="H38" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I38" s="2">
-        <v>12.74</v>
+        <v>23.65</v>
       </c>
       <c r="J38" s="2">
-        <v>0.035</v>
+        <v>0.0465</v>
       </c>
       <c r="K38" t="s">
         <v>141</v>
@@ -2316,34 +2316,34 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B39" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C39" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D39" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E39">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="F39">
-        <v>13.86</v>
+        <v>16.68</v>
       </c>
       <c r="G39" s="1">
-        <v>0.588</v>
+        <v>0.639</v>
       </c>
       <c r="H39" t="s">
         <v>140</v>
       </c>
       <c r="I39" s="2">
-        <v>12.19</v>
+        <v>21.93</v>
       </c>
       <c r="J39" s="2">
-        <v>0.0335</v>
+        <v>0.0603</v>
       </c>
       <c r="K39" t="s">
         <v>141</v>
@@ -2354,34 +2354,34 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B40" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C40" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D40" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E40">
-        <v>11.5</v>
+        <v>25.5</v>
       </c>
       <c r="F40">
-        <v>9.82</v>
+        <v>30.33</v>
       </c>
       <c r="G40" s="1">
-        <v>0.587</v>
+        <v>0.635</v>
       </c>
       <c r="H40" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I40" s="2">
-        <v>12.14</v>
+        <v>21.25</v>
       </c>
       <c r="J40" s="2">
-        <v>0.0334</v>
+        <v>0.0584</v>
       </c>
       <c r="K40" t="s">
         <v>141</v>
@@ -2392,34 +2392,34 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="B41" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="C41" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D41" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E41">
         <v>8.5</v>
       </c>
       <c r="F41">
-        <v>8.07</v>
+        <v>7.16</v>
       </c>
       <c r="G41" s="1">
-        <v>0.587</v>
+        <v>0.651</v>
       </c>
       <c r="H41" t="s">
         <v>139</v>
       </c>
       <c r="I41" s="2">
-        <v>12.03</v>
+        <v>21.02</v>
       </c>
       <c r="J41" s="2">
-        <v>0.0331</v>
+        <v>0.0413</v>
       </c>
       <c r="K41" t="s">
         <v>141</v>
@@ -2430,34 +2430,34 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B42" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C42" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D42" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E42">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="F42">
-        <v>3.6</v>
+        <v>4.63</v>
       </c>
       <c r="G42" s="1">
-        <v>0.582</v>
+        <v>0.65</v>
       </c>
       <c r="H42" t="s">
         <v>139</v>
       </c>
       <c r="I42" s="2">
-        <v>11.03</v>
+        <v>20.84</v>
       </c>
       <c r="J42" s="2">
-        <v>0.0303</v>
+        <v>0.0409</v>
       </c>
       <c r="K42" t="s">
         <v>141</v>
@@ -2468,37 +2468,37 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B43" t="s">
+        <v>130</v>
+      </c>
+      <c r="C43" t="s">
         <v>114</v>
       </c>
-      <c r="C43" t="s">
-        <v>131</v>
-      </c>
       <c r="D43" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E43">
-        <v>13.5</v>
+        <v>1.5</v>
       </c>
       <c r="F43">
-        <v>12.99</v>
+        <v>1.31</v>
       </c>
       <c r="G43" s="1">
-        <v>0.578</v>
+        <v>0.65</v>
       </c>
       <c r="H43" t="s">
         <v>139</v>
       </c>
       <c r="I43" s="2">
-        <v>10.33</v>
+        <v>20.81</v>
       </c>
       <c r="J43" s="2">
-        <v>0.0284</v>
+        <v>0.0409</v>
       </c>
       <c r="K43" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L43" t="s">
         <v>145</v>
@@ -2506,37 +2506,37 @@
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="B44" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D44" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E44">
-        <v>1.5</v>
+        <v>13.5</v>
       </c>
       <c r="F44">
-        <v>1.5</v>
+        <v>11.56</v>
       </c>
       <c r="G44" s="1">
-        <v>0.577</v>
+        <v>0.633</v>
       </c>
       <c r="H44" t="s">
         <v>139</v>
       </c>
       <c r="I44" s="2">
-        <v>10.23</v>
+        <v>20.78</v>
       </c>
       <c r="J44" s="2">
-        <v>0.0281</v>
+        <v>0.0571</v>
       </c>
       <c r="K44" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L44" t="s">
         <v>145</v>
@@ -2544,37 +2544,37 @@
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B45" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C45" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D45" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E45">
-        <v>2.5</v>
+        <v>28.5</v>
       </c>
       <c r="F45">
-        <v>2.99</v>
+        <v>25.27</v>
       </c>
       <c r="G45" s="1">
-        <v>0.575</v>
+        <v>0.648</v>
       </c>
       <c r="H45" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I45" s="2">
-        <v>9.69</v>
+        <v>20.62</v>
       </c>
       <c r="J45" s="2">
-        <v>0.0267</v>
+        <v>0.0405</v>
       </c>
       <c r="K45" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L45" t="s">
         <v>145</v>
@@ -2582,13 +2582,13 @@
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B46" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C46" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D46" t="s">
         <v>134</v>
@@ -2597,22 +2597,22 @@
         <v>1.5</v>
       </c>
       <c r="F46">
-        <v>1.91</v>
+        <v>1.32</v>
       </c>
       <c r="G46" s="1">
-        <v>0.57</v>
+        <v>0.647</v>
       </c>
       <c r="H46" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I46" s="2">
-        <v>8.800000000000001</v>
+        <v>20.53</v>
       </c>
       <c r="J46" s="2">
-        <v>0.0242</v>
+        <v>0.0403</v>
       </c>
       <c r="K46" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L46" t="s">
         <v>145</v>
@@ -2620,37 +2620,37 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B47" t="s">
+        <v>116</v>
+      </c>
+      <c r="C47" t="s">
         <v>115</v>
       </c>
-      <c r="C47" t="s">
-        <v>126</v>
-      </c>
       <c r="D47" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E47">
-        <v>15.5</v>
+        <v>3.5</v>
       </c>
       <c r="F47">
-        <v>16.49</v>
+        <v>3.17</v>
       </c>
       <c r="G47" s="1">
-        <v>0.5659999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="H47" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I47" s="2">
-        <v>8.02</v>
+        <v>20.27</v>
       </c>
       <c r="J47" s="2">
-        <v>0.0221</v>
+        <v>0.0558</v>
       </c>
       <c r="K47" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L47" t="s">
         <v>145</v>
@@ -2658,37 +2658,37 @@
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="B48" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C48" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D48" t="s">
         <v>134</v>
       </c>
       <c r="E48">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="F48">
-        <v>3.53</v>
+        <v>1.39</v>
       </c>
       <c r="G48" s="1">
-        <v>0.5629999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="H48" t="s">
         <v>139</v>
       </c>
       <c r="I48" s="2">
-        <v>7.43</v>
+        <v>20.2</v>
       </c>
       <c r="J48" s="2">
-        <v>0.0204</v>
+        <v>0.0556</v>
       </c>
       <c r="K48" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L48" t="s">
         <v>145</v>
@@ -2696,37 +2696,37 @@
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B49" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C49" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="D49" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E49">
-        <v>28.5</v>
+        <v>30.5</v>
       </c>
       <c r="F49">
-        <v>30.37</v>
+        <v>32.67</v>
       </c>
       <c r="G49" s="1">
-        <v>0.5620000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="H49" t="s">
         <v>140</v>
       </c>
       <c r="I49" s="2">
-        <v>7.23</v>
+        <v>20.19</v>
       </c>
       <c r="J49" s="2">
-        <v>0.0199</v>
+        <v>0.0555</v>
       </c>
       <c r="K49" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L49" t="s">
         <v>145</v>
@@ -2734,37 +2734,37 @@
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B50" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C50" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D50" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E50">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="F50">
-        <v>12.24</v>
+        <v>3.08</v>
       </c>
       <c r="G50" s="1">
-        <v>0.5600000000000001</v>
+        <v>0.629</v>
       </c>
       <c r="H50" t="s">
         <v>139</v>
       </c>
       <c r="I50" s="2">
-        <v>6.84</v>
+        <v>20.09</v>
       </c>
       <c r="J50" s="2">
-        <v>0.0188</v>
+        <v>0.0553</v>
       </c>
       <c r="K50" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L50" t="s">
         <v>145</v>
@@ -2772,13 +2772,13 @@
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B51" t="s">
         <v>124</v>
       </c>
       <c r="C51" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D51" t="s">
         <v>134</v>
@@ -2787,22 +2787,22 @@
         <v>2.5</v>
       </c>
       <c r="F51">
-        <v>2.92</v>
+        <v>2.06</v>
       </c>
       <c r="G51" s="1">
-        <v>0.5580000000000001</v>
+        <v>0.644</v>
       </c>
       <c r="H51" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I51" s="2">
-        <v>6.5</v>
+        <v>20</v>
       </c>
       <c r="J51" s="2">
-        <v>0.0179</v>
+        <v>0.0393</v>
       </c>
       <c r="K51" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L51" t="s">
         <v>145</v>
@@ -2810,37 +2810,37 @@
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="B52" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="C52" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D52" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E52">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="F52">
-        <v>15.95</v>
+        <v>5.92</v>
       </c>
       <c r="G52" s="1">
-        <v>0.552</v>
+        <v>0.626</v>
       </c>
       <c r="H52" t="s">
         <v>140</v>
       </c>
       <c r="I52" s="2">
-        <v>5.31</v>
+        <v>19.54</v>
       </c>
       <c r="J52" s="2">
-        <v>0.0146</v>
+        <v>0.0537</v>
       </c>
       <c r="K52" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L52" t="s">
         <v>145</v>
@@ -2848,37 +2848,37 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="B53" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="C53" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="D53" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E53">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="F53">
-        <v>8.710000000000001</v>
+        <v>2.42</v>
       </c>
       <c r="G53" s="1">
-        <v>0.55</v>
+        <v>0.637</v>
       </c>
       <c r="H53" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I53" s="2">
-        <v>4.98</v>
+        <v>19.13</v>
       </c>
       <c r="J53" s="2">
-        <v>0.0137</v>
+        <v>0.0376</v>
       </c>
       <c r="K53" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L53" t="s">
         <v>145</v>
@@ -2886,37 +2886,37 @@
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="B54" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C54" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D54" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E54">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="F54">
-        <v>7.87</v>
+        <v>3.82</v>
       </c>
       <c r="G54" s="1">
-        <v>0.547</v>
+        <v>0.634</v>
       </c>
       <c r="H54" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I54" s="2">
-        <v>4.42</v>
+        <v>18.69</v>
       </c>
       <c r="J54" s="2">
-        <v>0.0121</v>
+        <v>0.0367</v>
       </c>
       <c r="K54" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L54" t="s">
         <v>145</v>
@@ -2924,37 +2924,37 @@
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="B55" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C55" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D55" t="s">
         <v>135</v>
       </c>
       <c r="E55">
-        <v>18.5</v>
+        <v>3.5</v>
       </c>
       <c r="F55">
-        <v>19.5</v>
+        <v>3.05</v>
       </c>
       <c r="G55" s="1">
-        <v>0.547</v>
+        <v>0.633</v>
       </c>
       <c r="H55" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I55" s="2">
-        <v>4.37</v>
+        <v>18.61</v>
       </c>
       <c r="J55" s="2">
-        <v>0.012</v>
+        <v>0.0366</v>
       </c>
       <c r="K55" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L55" t="s">
         <v>145</v>
@@ -2962,37 +2962,37 @@
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B56" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D56" t="s">
         <v>134</v>
       </c>
       <c r="E56">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F56">
-        <v>1.83</v>
+        <v>2.26</v>
       </c>
       <c r="G56" s="1">
-        <v>0.546</v>
+        <v>0.621</v>
       </c>
       <c r="H56" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I56" s="2">
-        <v>4.15</v>
+        <v>18.46</v>
       </c>
       <c r="J56" s="2">
-        <v>0.0114</v>
+        <v>0.0508</v>
       </c>
       <c r="K56" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L56" t="s">
         <v>145</v>
@@ -3000,37 +3000,37 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="B57" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C57" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D57" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E57">
-        <v>18.5</v>
+        <v>3.5</v>
       </c>
       <c r="F57">
-        <v>18.96</v>
+        <v>3.04</v>
       </c>
       <c r="G57" s="1">
-        <v>0.545</v>
+        <v>0.631</v>
       </c>
       <c r="H57" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I57" s="2">
-        <v>3.99</v>
+        <v>18.37</v>
       </c>
       <c r="J57" s="2">
-        <v>0.011</v>
+        <v>0.0361</v>
       </c>
       <c r="K57" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L57" t="s">
         <v>145</v>
@@ -3038,37 +3038,37 @@
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="B58" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C58" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D58" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E58">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="F58">
-        <v>5.42</v>
+        <v>6.86</v>
       </c>
       <c r="G58" s="1">
-        <v>0.545</v>
+        <v>0.619</v>
       </c>
       <c r="H58" t="s">
         <v>139</v>
       </c>
       <c r="I58" s="2">
-        <v>3.95</v>
+        <v>18.09</v>
       </c>
       <c r="J58" s="2">
-        <v>0.0109</v>
+        <v>0.0497</v>
       </c>
       <c r="K58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L58" t="s">
         <v>145</v>
@@ -3076,37 +3076,37 @@
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="B59" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C59" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="D59" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E59">
-        <v>1.5</v>
+        <v>19.5</v>
       </c>
       <c r="F59">
-        <v>1.82</v>
+        <v>17.36</v>
       </c>
       <c r="G59" s="1">
-        <v>0.544</v>
+        <v>0.617</v>
       </c>
       <c r="H59" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I59" s="2">
-        <v>3.78</v>
+        <v>17.82</v>
       </c>
       <c r="J59" s="2">
-        <v>0.0104</v>
+        <v>0.049</v>
       </c>
       <c r="K59" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L59" t="s">
         <v>145</v>
@@ -3114,37 +3114,37 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="B60" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C60" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D60" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E60">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="F60">
-        <v>9.92</v>
+        <v>6.91</v>
       </c>
       <c r="G60" s="1">
-        <v>0.543</v>
+        <v>0.616</v>
       </c>
       <c r="H60" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I60" s="2">
-        <v>3.59</v>
+        <v>17.64</v>
       </c>
       <c r="J60" s="2">
-        <v>0.0049</v>
+        <v>0.0485</v>
       </c>
       <c r="K60" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L60" t="s">
         <v>145</v>
@@ -3152,37 +3152,37 @@
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="B61" t="s">
+        <v>130</v>
+      </c>
+      <c r="C61" t="s">
         <v>114</v>
       </c>
-      <c r="C61" t="s">
-        <v>131</v>
-      </c>
       <c r="D61" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E61">
-        <v>11.5</v>
+        <v>4.5</v>
       </c>
       <c r="F61">
-        <v>12.08</v>
+        <v>3.85</v>
       </c>
       <c r="G61" s="1">
-        <v>0.54</v>
+        <v>0.625</v>
       </c>
       <c r="H61" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I61" s="2">
-        <v>3.13</v>
+        <v>17.58</v>
       </c>
       <c r="J61" s="2">
-        <v>0.0086</v>
+        <v>0.0345</v>
       </c>
       <c r="K61" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L61" t="s">
         <v>145</v>
@@ -3190,37 +3190,37 @@
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="B62" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C62" t="s">
         <v>129</v>
       </c>
       <c r="D62" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E62">
-        <v>32.5</v>
+        <v>14.5</v>
       </c>
       <c r="F62">
-        <v>31.81</v>
+        <v>12.02</v>
       </c>
       <c r="G62" s="1">
-        <v>0.539</v>
+        <v>0.623</v>
       </c>
       <c r="H62" t="s">
         <v>139</v>
       </c>
       <c r="I62" s="2">
-        <v>2.96</v>
+        <v>17.24</v>
       </c>
       <c r="J62" s="2">
-        <v>0.0081</v>
+        <v>0.0339</v>
       </c>
       <c r="K62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L62" t="s">
         <v>145</v>
@@ -3228,37 +3228,37 @@
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="B63" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C63" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D63" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E63">
-        <v>2.5</v>
+        <v>19.5</v>
       </c>
       <c r="F63">
-        <v>2.83</v>
+        <v>22.13</v>
       </c>
       <c r="G63" s="1">
-        <v>0.538</v>
+        <v>0.622</v>
       </c>
       <c r="H63" t="s">
         <v>140</v>
       </c>
       <c r="I63" s="2">
-        <v>2.77</v>
+        <v>17.17</v>
       </c>
       <c r="J63" s="2">
-        <v>0.0038</v>
+        <v>0.0337</v>
       </c>
       <c r="K63" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L63" t="s">
         <v>145</v>
@@ -3266,37 +3266,37 @@
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="B64" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="C64" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="D64" t="s">
         <v>135</v>
       </c>
       <c r="E64">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="F64">
-        <v>7.86</v>
+        <v>5.54</v>
       </c>
       <c r="G64" s="1">
-        <v>0.537</v>
+        <v>0.619</v>
       </c>
       <c r="H64" t="s">
         <v>140</v>
       </c>
       <c r="I64" s="2">
-        <v>2.48</v>
+        <v>16.7</v>
       </c>
       <c r="J64" s="2">
-        <v>0.0068</v>
+        <v>0.0328</v>
       </c>
       <c r="K64" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L64" t="s">
         <v>145</v>
@@ -3304,37 +3304,37 @@
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="B65" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C65" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D65" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E65">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="F65">
-        <v>17.8</v>
+        <v>18.39</v>
       </c>
       <c r="G65" s="1">
-        <v>0.534</v>
+        <v>0.611</v>
       </c>
       <c r="H65" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I65" s="2">
-        <v>2</v>
+        <v>16.57</v>
       </c>
       <c r="J65" s="2">
-        <v>0.0028</v>
+        <v>0.0456</v>
       </c>
       <c r="K65" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L65" t="s">
         <v>145</v>
@@ -3342,13 +3342,13 @@
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B66" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C66" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D66" t="s">
         <v>135</v>
@@ -3357,22 +3357,22 @@
         <v>7.5</v>
       </c>
       <c r="F66">
-        <v>7.95</v>
+        <v>6.92</v>
       </c>
       <c r="G66" s="1">
-        <v>0.533</v>
+        <v>0.61</v>
       </c>
       <c r="H66" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I66" s="2">
-        <v>1.67</v>
+        <v>16.39</v>
       </c>
       <c r="J66" s="2">
-        <v>0.0023</v>
+        <v>0.0451</v>
       </c>
       <c r="K66" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L66" t="s">
         <v>145</v>
@@ -3380,37 +3380,37 @@
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B67" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C67" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D67" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E67">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="F67">
-        <v>5.86</v>
+        <v>2.25</v>
       </c>
       <c r="G67" s="1">
-        <v>0.532</v>
+        <v>0.609</v>
       </c>
       <c r="H67" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I67" s="2">
-        <v>1.59</v>
+        <v>16.36</v>
       </c>
       <c r="J67" s="2">
-        <v>0.0044</v>
+        <v>0.045</v>
       </c>
       <c r="K67" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L67" t="s">
         <v>145</v>
@@ -3418,37 +3418,37 @@
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="B68" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C68" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D68" t="s">
         <v>137</v>
       </c>
       <c r="E68">
-        <v>5.5</v>
+        <v>16.5</v>
       </c>
       <c r="F68">
-        <v>2.95</v>
+        <v>13.92</v>
       </c>
       <c r="G68" s="1">
-        <v>0.921</v>
+        <v>0.616</v>
       </c>
       <c r="H68" t="s">
         <v>139</v>
       </c>
       <c r="I68" s="2">
-        <v>75.87</v>
+        <v>16.35</v>
       </c>
       <c r="J68" s="2">
-        <v>0.1043</v>
+        <v>0.0321</v>
       </c>
       <c r="K68" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L68" t="s">
         <v>145</v>
@@ -3456,37 +3456,37 @@
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="B69" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C69" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D69" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E69">
-        <v>27.5</v>
+        <v>1.5</v>
       </c>
       <c r="F69">
-        <v>22.68</v>
+        <v>1.35</v>
       </c>
       <c r="G69" s="1">
-        <v>0.796</v>
+        <v>0.609</v>
       </c>
       <c r="H69" t="s">
         <v>139</v>
       </c>
       <c r="I69" s="2">
-        <v>52.05</v>
+        <v>16.19</v>
       </c>
       <c r="J69" s="2">
-        <v>0.0716</v>
+        <v>0.0445</v>
       </c>
       <c r="K69" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L69" t="s">
         <v>145</v>
@@ -3494,37 +3494,37 @@
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B70" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C70" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="D70" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E70">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="F70">
-        <v>2.34</v>
+        <v>6.62</v>
       </c>
       <c r="G70" s="1">
-        <v>0.758</v>
+        <v>0.615</v>
       </c>
       <c r="H70" t="s">
         <v>139</v>
       </c>
       <c r="I70" s="2">
-        <v>44.64</v>
+        <v>16.15</v>
       </c>
       <c r="J70" s="2">
-        <v>0.0614</v>
+        <v>0.0317</v>
       </c>
       <c r="K70" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L70" t="s">
         <v>145</v>
@@ -3532,37 +3532,37 @@
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="B71" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C71" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D71" t="s">
         <v>135</v>
       </c>
       <c r="E71">
-        <v>12.5</v>
+        <v>4.5</v>
       </c>
       <c r="F71">
-        <v>8.640000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="G71" s="1">
-        <v>0.749</v>
+        <v>0.607</v>
       </c>
       <c r="H71" t="s">
         <v>139</v>
       </c>
       <c r="I71" s="2">
-        <v>43</v>
+        <v>15.95</v>
       </c>
       <c r="J71" s="2">
-        <v>0.0591</v>
+        <v>0.0439</v>
       </c>
       <c r="K71" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L71" t="s">
         <v>145</v>
@@ -3570,37 +3570,37 @@
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="B72" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C72" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="D72" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E72">
-        <v>7.5</v>
+        <v>21.5</v>
       </c>
       <c r="F72">
-        <v>5.99</v>
+        <v>18.42</v>
       </c>
       <c r="G72" s="1">
-        <v>0.746</v>
+        <v>0.613</v>
       </c>
       <c r="H72" t="s">
         <v>139</v>
       </c>
       <c r="I72" s="2">
-        <v>42.42</v>
+        <v>15.87</v>
       </c>
       <c r="J72" s="2">
-        <v>0.0583</v>
+        <v>0.0312</v>
       </c>
       <c r="K72" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L72" t="s">
         <v>145</v>
@@ -3608,37 +3608,37 @@
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="B73" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C73" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D73" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E73">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="F73">
-        <v>2.5</v>
+        <v>7.69</v>
       </c>
       <c r="G73" s="1">
-        <v>0.742</v>
+        <v>0.606</v>
       </c>
       <c r="H73" t="s">
         <v>139</v>
       </c>
       <c r="I73" s="2">
-        <v>41.73</v>
+        <v>14.98</v>
       </c>
       <c r="J73" s="2">
-        <v>0.0574</v>
+        <v>0.0294</v>
       </c>
       <c r="K73" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L73" t="s">
         <v>145</v>
@@ -3646,37 +3646,37 @@
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="B74" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C74" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="D74" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E74">
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="F74">
-        <v>3.47</v>
+        <v>13.13</v>
       </c>
       <c r="G74" s="1">
-        <v>0.73</v>
+        <v>0.606</v>
       </c>
       <c r="H74" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I74" s="2">
-        <v>39.44</v>
+        <v>14.96</v>
       </c>
       <c r="J74" s="2">
-        <v>0.0542</v>
+        <v>0.0294</v>
       </c>
       <c r="K74" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L74" t="s">
         <v>145</v>
@@ -3684,37 +3684,37 @@
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="B75" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C75" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D75" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E75">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="F75">
-        <v>5.44</v>
+        <v>2.35</v>
       </c>
       <c r="G75" s="1">
-        <v>0.727</v>
+        <v>0.604</v>
       </c>
       <c r="H75" t="s">
         <v>139</v>
       </c>
       <c r="I75" s="2">
-        <v>38.7</v>
+        <v>14.68</v>
       </c>
       <c r="J75" s="2">
-        <v>0.0532</v>
+        <v>0.0288</v>
       </c>
       <c r="K75" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L75" t="s">
         <v>145</v>
@@ -3722,37 +3722,37 @@
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="B76" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C76" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D76" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E76">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="F76">
-        <v>11.11</v>
+        <v>14.9</v>
       </c>
       <c r="G76" s="1">
-        <v>0.724</v>
+        <v>0.602</v>
       </c>
       <c r="H76" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I76" s="2">
-        <v>38.14</v>
+        <v>14.52</v>
       </c>
       <c r="J76" s="2">
-        <v>0.0524</v>
+        <v>0.0285</v>
       </c>
       <c r="K76" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L76" t="s">
         <v>145</v>
@@ -3760,37 +3760,37 @@
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B77" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C77" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D77" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E77">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="F77">
-        <v>3.45</v>
+        <v>8.67</v>
       </c>
       <c r="G77" s="1">
-        <v>0.722</v>
+        <v>0.599</v>
       </c>
       <c r="H77" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I77" s="2">
-        <v>37.85</v>
+        <v>14.08</v>
       </c>
       <c r="J77" s="2">
-        <v>0.052</v>
+        <v>0.0277</v>
       </c>
       <c r="K77" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L77" t="s">
         <v>145</v>
@@ -3798,37 +3798,37 @@
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="B78" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C78" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D78" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E78">
-        <v>27.5</v>
+        <v>2.5</v>
       </c>
       <c r="F78">
-        <v>23.89</v>
+        <v>2.18</v>
       </c>
       <c r="G78" s="1">
-        <v>0.72</v>
+        <v>0.598</v>
       </c>
       <c r="H78" t="s">
         <v>139</v>
       </c>
       <c r="I78" s="2">
-        <v>37.36</v>
+        <v>13.97</v>
       </c>
       <c r="J78" s="2">
-        <v>0.0514</v>
+        <v>0.0274</v>
       </c>
       <c r="K78" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L78" t="s">
         <v>145</v>
@@ -3836,37 +3836,37 @@
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="B79" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C79" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D79" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E79">
-        <v>2.5</v>
+        <v>12.5</v>
       </c>
       <c r="F79">
-        <v>1.84</v>
+        <v>13.07</v>
       </c>
       <c r="G79" s="1">
-        <v>0.719</v>
+        <v>0.596</v>
       </c>
       <c r="H79" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I79" s="2">
-        <v>37.3</v>
+        <v>13.79</v>
       </c>
       <c r="J79" s="2">
-        <v>0.0513</v>
+        <v>0.0379</v>
       </c>
       <c r="K79" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L79" t="s">
         <v>145</v>
@@ -3874,37 +3874,37 @@
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="B80" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C80" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="D80" t="s">
         <v>137</v>
       </c>
       <c r="E80">
-        <v>8.5</v>
+        <v>17.5</v>
       </c>
       <c r="F80">
-        <v>6.56</v>
+        <v>15.25</v>
       </c>
       <c r="G80" s="1">
-        <v>0.718</v>
+        <v>0.597</v>
       </c>
       <c r="H80" t="s">
         <v>139</v>
       </c>
       <c r="I80" s="2">
-        <v>37.16</v>
+        <v>13.77</v>
       </c>
       <c r="J80" s="2">
-        <v>0.0511</v>
+        <v>0.027</v>
       </c>
       <c r="K80" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L80" t="s">
         <v>145</v>
@@ -3912,37 +3912,37 @@
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="B81" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C81" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D81" t="s">
         <v>134</v>
       </c>
       <c r="E81">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="F81">
-        <v>1.87</v>
+        <v>6.68</v>
       </c>
       <c r="G81" s="1">
-        <v>0.715</v>
+        <v>0.596</v>
       </c>
       <c r="H81" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I81" s="2">
-        <v>36.58</v>
+        <v>13.69</v>
       </c>
       <c r="J81" s="2">
-        <v>0.0503</v>
+        <v>0.0269</v>
       </c>
       <c r="K81" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L81" t="s">
         <v>145</v>
@@ -3950,37 +3950,37 @@
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="B82" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C82" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D82" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E82">
         <v>19.5</v>
       </c>
       <c r="F82">
-        <v>14.55</v>
+        <v>22.69</v>
       </c>
       <c r="G82" s="1">
-        <v>0.712</v>
+        <v>0.595</v>
       </c>
       <c r="H82" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I82" s="2">
-        <v>35.97</v>
+        <v>13.54</v>
       </c>
       <c r="J82" s="2">
-        <v>0.0495</v>
+        <v>0.0266</v>
       </c>
       <c r="K82" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L82" t="s">
         <v>145</v>
@@ -3988,37 +3988,37 @@
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C83" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D83" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E83">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="F83">
-        <v>1.34</v>
+        <v>4.31</v>
       </c>
       <c r="G83" s="1">
-        <v>0.705</v>
+        <v>0.594</v>
       </c>
       <c r="H83" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I83" s="2">
-        <v>34.67</v>
+        <v>13.4</v>
       </c>
       <c r="J83" s="2">
-        <v>0.0477</v>
+        <v>0.0263</v>
       </c>
       <c r="K83" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L83" t="s">
         <v>145</v>
@@ -4026,37 +4026,37 @@
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C84" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D84" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E84">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="F84">
-        <v>2.04</v>
+        <v>4.03</v>
       </c>
       <c r="G84" s="1">
-        <v>0.701</v>
+        <v>0.593</v>
       </c>
       <c r="H84" t="s">
         <v>139</v>
       </c>
       <c r="I84" s="2">
-        <v>33.78</v>
+        <v>13.3</v>
       </c>
       <c r="J84" s="2">
-        <v>0.0465</v>
+        <v>0.0261</v>
       </c>
       <c r="K84" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L84" t="s">
         <v>145</v>
@@ -4064,37 +4064,37 @@
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B85" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C85" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D85" t="s">
         <v>134</v>
       </c>
       <c r="E85">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F85">
-        <v>2.83</v>
+        <v>2.32</v>
       </c>
       <c r="G85" s="1">
-        <v>0.6830000000000001</v>
+        <v>0.592</v>
       </c>
       <c r="H85" t="s">
         <v>139</v>
       </c>
       <c r="I85" s="2">
-        <v>30.43</v>
+        <v>13.18</v>
       </c>
       <c r="J85" s="2">
-        <v>0.0418</v>
+        <v>0.0259</v>
       </c>
       <c r="K85" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L85" t="s">
         <v>145</v>
@@ -4102,37 +4102,37 @@
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="B86" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C86" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D86" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E86">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="F86">
-        <v>7.16</v>
+        <v>3.12</v>
       </c>
       <c r="G86" s="1">
-        <v>0.681</v>
+        <v>0.589</v>
       </c>
       <c r="H86" t="s">
         <v>139</v>
       </c>
       <c r="I86" s="2">
-        <v>30.02</v>
+        <v>12.78</v>
       </c>
       <c r="J86" s="2">
-        <v>0.0413</v>
+        <v>0.0251</v>
       </c>
       <c r="K86" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L86" t="s">
         <v>145</v>
@@ -4140,37 +4140,37 @@
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="B87" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C87" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="D87" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E87">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="F87">
-        <v>4.63</v>
+        <v>4.33</v>
       </c>
       <c r="G87" s="1">
-        <v>0.68</v>
+        <v>0.591</v>
       </c>
       <c r="H87" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I87" s="2">
-        <v>29.77</v>
+        <v>12.74</v>
       </c>
       <c r="J87" s="2">
-        <v>0.0409</v>
+        <v>0.035</v>
       </c>
       <c r="K87" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L87" t="s">
         <v>145</v>
@@ -4178,37 +4178,37 @@
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B88" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="C88" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="D88" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E88">
-        <v>1.5</v>
+        <v>12.5</v>
       </c>
       <c r="F88">
-        <v>1.31</v>
+        <v>13.86</v>
       </c>
       <c r="G88" s="1">
-        <v>0.68</v>
+        <v>0.588</v>
       </c>
       <c r="H88" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I88" s="2">
-        <v>29.73</v>
+        <v>12.19</v>
       </c>
       <c r="J88" s="2">
-        <v>0.0409</v>
+        <v>0.0335</v>
       </c>
       <c r="K88" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L88" t="s">
         <v>145</v>
@@ -4216,37 +4216,37 @@
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="B89" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C89" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D89" t="s">
         <v>136</v>
       </c>
       <c r="E89">
-        <v>28.5</v>
+        <v>11.5</v>
       </c>
       <c r="F89">
-        <v>25.27</v>
+        <v>9.82</v>
       </c>
       <c r="G89" s="1">
-        <v>0.678</v>
+        <v>0.587</v>
       </c>
       <c r="H89" t="s">
         <v>139</v>
       </c>
       <c r="I89" s="2">
-        <v>29.46</v>
+        <v>12.14</v>
       </c>
       <c r="J89" s="2">
-        <v>0.0405</v>
+        <v>0.0334</v>
       </c>
       <c r="K89" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L89" t="s">
         <v>145</v>
@@ -4254,37 +4254,37 @@
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="B90" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C90" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D90" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E90">
-        <v>1.5</v>
+        <v>20.5</v>
       </c>
       <c r="F90">
-        <v>1.32</v>
+        <v>23.08</v>
       </c>
       <c r="G90" s="1">
-        <v>0.677</v>
+        <v>0.584</v>
       </c>
       <c r="H90" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I90" s="2">
-        <v>29.33</v>
+        <v>12.05</v>
       </c>
       <c r="J90" s="2">
-        <v>0.0403</v>
+        <v>0.0237</v>
       </c>
       <c r="K90" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L90" t="s">
         <v>145</v>
@@ -4292,37 +4292,37 @@
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="B91" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C91" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="D91" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E91">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="F91">
-        <v>2.06</v>
+        <v>8.07</v>
       </c>
       <c r="G91" s="1">
-        <v>0.674</v>
+        <v>0.587</v>
       </c>
       <c r="H91" t="s">
         <v>139</v>
       </c>
       <c r="I91" s="2">
-        <v>28.58</v>
+        <v>12.03</v>
       </c>
       <c r="J91" s="2">
-        <v>0.0393</v>
+        <v>0.0331</v>
       </c>
       <c r="K91" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L91" t="s">
         <v>145</v>
@@ -4330,37 +4330,37 @@
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C92" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D92" t="s">
         <v>134</v>
       </c>
       <c r="E92">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F92">
-        <v>2.42</v>
+        <v>1.45</v>
       </c>
       <c r="G92" s="1">
-        <v>0.667</v>
+        <v>0.581</v>
       </c>
       <c r="H92" t="s">
         <v>139</v>
       </c>
       <c r="I92" s="2">
-        <v>27.33</v>
+        <v>11.71</v>
       </c>
       <c r="J92" s="2">
-        <v>0.0376</v>
+        <v>0.023</v>
       </c>
       <c r="K92" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L92" t="s">
         <v>145</v>
@@ -4368,37 +4368,37 @@
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B93" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C93" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="D93" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E93">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F93">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="G93" s="1">
-        <v>0.664</v>
+        <v>0.582</v>
       </c>
       <c r="H93" t="s">
         <v>139</v>
       </c>
       <c r="I93" s="2">
-        <v>26.7</v>
+        <v>11.03</v>
       </c>
       <c r="J93" s="2">
-        <v>0.0367</v>
+        <v>0.0303</v>
       </c>
       <c r="K93" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L93" t="s">
         <v>145</v>
@@ -4406,37 +4406,37 @@
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B94" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="C94" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="D94" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E94">
-        <v>3.5</v>
+        <v>10.5</v>
       </c>
       <c r="F94">
-        <v>3.05</v>
+        <v>9.59</v>
       </c>
       <c r="G94" s="1">
-        <v>0.663</v>
+        <v>0.58</v>
       </c>
       <c r="H94" t="s">
         <v>139</v>
       </c>
       <c r="I94" s="2">
-        <v>26.59</v>
+        <v>11.51</v>
       </c>
       <c r="J94" s="2">
-        <v>0.0366</v>
+        <v>0.0226</v>
       </c>
       <c r="K94" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L94" t="s">
         <v>145</v>
@@ -4444,37 +4444,37 @@
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="B95" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C95" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D95" t="s">
         <v>134</v>
       </c>
       <c r="E95">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F95">
-        <v>3.04</v>
+        <v>3.21</v>
       </c>
       <c r="G95" s="1">
-        <v>0.661</v>
+        <v>0.58</v>
       </c>
       <c r="H95" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I95" s="2">
-        <v>26.24</v>
+        <v>11.47</v>
       </c>
       <c r="J95" s="2">
-        <v>0.0361</v>
+        <v>0.0225</v>
       </c>
       <c r="K95" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L95" t="s">
         <v>145</v>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B96" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C96" t="s">
         <v>114</v>
@@ -4494,25 +4494,25 @@
         <v>134</v>
       </c>
       <c r="E96">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="F96">
-        <v>3.85</v>
+        <v>5.07</v>
       </c>
       <c r="G96" s="1">
-        <v>0.655</v>
+        <v>0.576</v>
       </c>
       <c r="H96" t="s">
         <v>139</v>
       </c>
       <c r="I96" s="2">
-        <v>25.11</v>
+        <v>11.02</v>
       </c>
       <c r="J96" s="2">
-        <v>0.0345</v>
+        <v>0.0216</v>
       </c>
       <c r="K96" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L96" t="s">
         <v>145</v>
@@ -4520,37 +4520,37 @@
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B97" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="C97" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D97" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E97">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="F97">
-        <v>12.02</v>
+        <v>12.99</v>
       </c>
       <c r="G97" s="1">
-        <v>0.653</v>
+        <v>0.578</v>
       </c>
       <c r="H97" t="s">
         <v>139</v>
       </c>
       <c r="I97" s="2">
-        <v>24.62</v>
+        <v>10.33</v>
       </c>
       <c r="J97" s="2">
-        <v>0.0339</v>
+        <v>0.0284</v>
       </c>
       <c r="K97" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L97" t="s">
         <v>145</v>
@@ -4558,37 +4558,37 @@
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="B98" t="s">
         <v>125</v>
       </c>
       <c r="C98" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="D98" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E98">
-        <v>19.5</v>
+        <v>1.5</v>
       </c>
       <c r="F98">
-        <v>22.13</v>
+        <v>1.5</v>
       </c>
       <c r="G98" s="1">
-        <v>0.652</v>
+        <v>0.577</v>
       </c>
       <c r="H98" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I98" s="2">
-        <v>24.53</v>
+        <v>10.23</v>
       </c>
       <c r="J98" s="2">
-        <v>0.0337</v>
+        <v>0.0281</v>
       </c>
       <c r="K98" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L98" t="s">
         <v>145</v>
@@ -4596,37 +4596,37 @@
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B99" t="s">
         <v>123</v>
       </c>
       <c r="C99" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D99" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E99">
         <v>4.5</v>
       </c>
       <c r="F99">
-        <v>5.54</v>
+        <v>4.15</v>
       </c>
       <c r="G99" s="1">
-        <v>0.649</v>
+        <v>0.569</v>
       </c>
       <c r="H99" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I99" s="2">
-        <v>23.86</v>
+        <v>10.11</v>
       </c>
       <c r="J99" s="2">
-        <v>0.0328</v>
+        <v>0.0199</v>
       </c>
       <c r="K99" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L99" t="s">
         <v>145</v>
@@ -4634,37 +4634,37 @@
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C100" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D100" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E100">
-        <v>16.5</v>
+        <v>2.5</v>
       </c>
       <c r="F100">
-        <v>13.92</v>
+        <v>2.99</v>
       </c>
       <c r="G100" s="1">
-        <v>0.646</v>
+        <v>0.575</v>
       </c>
       <c r="H100" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I100" s="2">
-        <v>23.36</v>
+        <v>9.69</v>
       </c>
       <c r="J100" s="2">
-        <v>0.0321</v>
+        <v>0.0267</v>
       </c>
       <c r="K100" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L100" t="s">
         <v>145</v>
@@ -4672,37 +4672,37 @@
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B101" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C101" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D101" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E101">
-        <v>7.5</v>
+        <v>11.5</v>
       </c>
       <c r="F101">
-        <v>6.62</v>
+        <v>12.77</v>
       </c>
       <c r="G101" s="1">
-        <v>0.645</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H101" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I101" s="2">
-        <v>23.07</v>
+        <v>9.4</v>
       </c>
       <c r="J101" s="2">
-        <v>0.0317</v>
+        <v>0.0185</v>
       </c>
       <c r="K101" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L101" t="s">
         <v>145</v>
@@ -4710,37 +4710,37 @@
     </row>
     <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="B102" t="s">
         <v>126</v>
       </c>
       <c r="C102" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D102" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E102">
-        <v>21.5</v>
+        <v>1.5</v>
       </c>
       <c r="F102">
-        <v>18.42</v>
+        <v>1.91</v>
       </c>
       <c r="G102" s="1">
-        <v>0.643</v>
+        <v>0.57</v>
       </c>
       <c r="H102" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I102" s="2">
-        <v>22.68</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J102" s="2">
-        <v>0.0312</v>
+        <v>0.0242</v>
       </c>
       <c r="K102" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L102" t="s">
         <v>145</v>
@@ -4748,37 +4748,37 @@
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="B103" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C103" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D103" t="s">
         <v>137</v>
       </c>
       <c r="E103">
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="F103">
-        <v>7.69</v>
+        <v>14.21</v>
       </c>
       <c r="G103" s="1">
-        <v>0.636</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="H103" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I103" s="2">
-        <v>21.41</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="J103" s="2">
-        <v>0.0294</v>
+        <v>0.0172</v>
       </c>
       <c r="K103" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L103" t="s">
         <v>145</v>
@@ -4786,37 +4786,37 @@
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="B104" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C104" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="D104" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E104">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="F104">
-        <v>13.13</v>
+        <v>5.23</v>
       </c>
       <c r="G104" s="1">
-        <v>0.636</v>
+        <v>0.556</v>
       </c>
       <c r="H104" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I104" s="2">
-        <v>21.37</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="J104" s="2">
-        <v>0.0294</v>
+        <v>0.0164</v>
       </c>
       <c r="K104" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L104" t="s">
         <v>145</v>
@@ -4824,37 +4824,37 @@
     </row>
     <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="B105" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C105" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D105" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E105">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="F105">
-        <v>2.35</v>
+        <v>8.07</v>
       </c>
       <c r="G105" s="1">
-        <v>0.634</v>
+        <v>0.555</v>
       </c>
       <c r="H105" t="s">
         <v>139</v>
       </c>
       <c r="I105" s="2">
-        <v>20.97</v>
+        <v>8.19</v>
       </c>
       <c r="J105" s="2">
-        <v>0.0288</v>
+        <v>0.0161</v>
       </c>
       <c r="K105" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L105" t="s">
         <v>145</v>
@@ -4862,37 +4862,37 @@
     </row>
     <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="B106" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="C106" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D106" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E106">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="F106">
-        <v>14.9</v>
+        <v>16.49</v>
       </c>
       <c r="G106" s="1">
-        <v>0.632</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H106" t="s">
         <v>140</v>
       </c>
       <c r="I106" s="2">
-        <v>20.74</v>
+        <v>8.02</v>
       </c>
       <c r="J106" s="2">
-        <v>0.0285</v>
+        <v>0.0221</v>
       </c>
       <c r="K106" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L106" t="s">
         <v>145</v>
@@ -4900,37 +4900,37 @@
     </row>
     <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="B107" t="s">
         <v>128</v>
       </c>
       <c r="C107" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="D107" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E107">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="F107">
-        <v>8.67</v>
+        <v>3.53</v>
       </c>
       <c r="G107" s="1">
-        <v>0.629</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H107" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I107" s="2">
-        <v>20.12</v>
+        <v>7.43</v>
       </c>
       <c r="J107" s="2">
-        <v>0.0277</v>
+        <v>0.0204</v>
       </c>
       <c r="K107" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L107" t="s">
         <v>145</v>
@@ -4938,37 +4938,37 @@
     </row>
     <row r="108" spans="1:12">
       <c r="A108" t="s">
-        <v>46</v>
+        <v>103</v>
       </c>
       <c r="B108" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C108" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="D108" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E108">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="F108">
-        <v>2.18</v>
+        <v>10.89</v>
       </c>
       <c r="G108" s="1">
-        <v>0.628</v>
+        <v>0.548</v>
       </c>
       <c r="H108" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I108" s="2">
-        <v>19.95</v>
+        <v>7.26</v>
       </c>
       <c r="J108" s="2">
-        <v>0.0274</v>
+        <v>0.0143</v>
       </c>
       <c r="K108" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L108" t="s">
         <v>145</v>
@@ -4976,37 +4976,37 @@
     </row>
     <row r="109" spans="1:12">
       <c r="A109" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="B109" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C109" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="D109" t="s">
         <v>136</v>
       </c>
       <c r="E109">
-        <v>17.5</v>
+        <v>28.5</v>
       </c>
       <c r="F109">
-        <v>15.25</v>
+        <v>30.37</v>
       </c>
       <c r="G109" s="1">
-        <v>0.627</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="H109" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I109" s="2">
-        <v>19.67</v>
+        <v>7.23</v>
       </c>
       <c r="J109" s="2">
-        <v>0.027</v>
+        <v>0.0199</v>
       </c>
       <c r="K109" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L109" t="s">
         <v>145</v>
@@ -5014,37 +5014,37 @@
     </row>
     <row r="110" spans="1:12">
       <c r="A110" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="B110" t="s">
+        <v>119</v>
+      </c>
+      <c r="C110" t="s">
         <v>128</v>
       </c>
-      <c r="C110" t="s">
-        <v>130</v>
-      </c>
       <c r="D110" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E110">
-        <v>5.5</v>
+        <v>13.5</v>
       </c>
       <c r="F110">
-        <v>6.68</v>
+        <v>12.24</v>
       </c>
       <c r="G110" s="1">
-        <v>0.626</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H110" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I110" s="2">
-        <v>19.56</v>
+        <v>6.84</v>
       </c>
       <c r="J110" s="2">
-        <v>0.0269</v>
+        <v>0.0188</v>
       </c>
       <c r="K110" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L110" t="s">
         <v>145</v>
@@ -5052,37 +5052,37 @@
     </row>
     <row r="111" spans="1:12">
       <c r="A111" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="B111" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C111" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D111" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E111">
-        <v>19.5</v>
+        <v>5.5</v>
       </c>
       <c r="F111">
-        <v>22.69</v>
+        <v>5.28</v>
       </c>
       <c r="G111" s="1">
-        <v>0.625</v>
+        <v>0.544</v>
       </c>
       <c r="H111" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I111" s="2">
-        <v>19.34</v>
+        <v>6.64</v>
       </c>
       <c r="J111" s="2">
-        <v>0.0266</v>
+        <v>0.0131</v>
       </c>
       <c r="K111" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L111" t="s">
         <v>145</v>
@@ -5090,37 +5090,37 @@
     </row>
     <row r="112" spans="1:12">
       <c r="A112" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="B112" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C112" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="D112" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E112">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F112">
-        <v>4.31</v>
+        <v>2.92</v>
       </c>
       <c r="G112" s="1">
-        <v>0.624</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H112" t="s">
         <v>140</v>
       </c>
       <c r="I112" s="2">
-        <v>19.14</v>
+        <v>6.5</v>
       </c>
       <c r="J112" s="2">
-        <v>0.0263</v>
+        <v>0.0179</v>
       </c>
       <c r="K112" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L112" t="s">
         <v>145</v>
@@ -5128,37 +5128,37 @@
     </row>
     <row r="113" spans="1:12">
       <c r="A113" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="B113" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C113" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D113" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E113">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="F113">
-        <v>4.03</v>
+        <v>1.47</v>
       </c>
       <c r="G113" s="1">
-        <v>0.623</v>
+        <v>0.542</v>
       </c>
       <c r="H113" t="s">
         <v>139</v>
       </c>
       <c r="I113" s="2">
-        <v>19</v>
+        <v>6.45</v>
       </c>
       <c r="J113" s="2">
-        <v>0.0261</v>
+        <v>0.0127</v>
       </c>
       <c r="K113" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L113" t="s">
         <v>145</v>
@@ -5166,37 +5166,37 @@
     </row>
     <row r="114" spans="1:12">
       <c r="A114" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="B114" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C114" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D114" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E114">
-        <v>2.5</v>
+        <v>19.5</v>
       </c>
       <c r="F114">
-        <v>2.32</v>
+        <v>20.86</v>
       </c>
       <c r="G114" s="1">
-        <v>0.622</v>
+        <v>0.541</v>
       </c>
       <c r="H114" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I114" s="2">
-        <v>18.83</v>
+        <v>6.25</v>
       </c>
       <c r="J114" s="2">
-        <v>0.0259</v>
+        <v>0.0123</v>
       </c>
       <c r="K114" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L114" t="s">
         <v>145</v>
@@ -5204,37 +5204,37 @@
     </row>
     <row r="115" spans="1:12">
       <c r="A115" t="s">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="B115" t="s">
         <v>116</v>
       </c>
       <c r="C115" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D115" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E115">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F115">
-        <v>3.12</v>
+        <v>2.4</v>
       </c>
       <c r="G115" s="1">
-        <v>0.619</v>
+        <v>0.541</v>
       </c>
       <c r="H115" t="s">
         <v>139</v>
       </c>
       <c r="I115" s="2">
-        <v>18.25</v>
+        <v>6.24</v>
       </c>
       <c r="J115" s="2">
-        <v>0.0251</v>
+        <v>0.0123</v>
       </c>
       <c r="K115" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L115" t="s">
         <v>145</v>
@@ -5242,37 +5242,37 @@
     </row>
     <row r="116" spans="1:12">
       <c r="A116" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="B116" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="C116" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="D116" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E116">
-        <v>7.5</v>
+        <v>14.5</v>
       </c>
       <c r="F116">
-        <v>6.91</v>
+        <v>15.95</v>
       </c>
       <c r="G116" s="1">
-        <v>0.616</v>
+        <v>0.552</v>
       </c>
       <c r="H116" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I116" s="2">
-        <v>17.64</v>
+        <v>5.31</v>
       </c>
       <c r="J116" s="2">
-        <v>0.0243</v>
+        <v>0.0146</v>
       </c>
       <c r="K116" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L116" t="s">
         <v>145</v>
@@ -5280,37 +5280,37 @@
     </row>
     <row r="117" spans="1:12">
       <c r="A117" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="B117" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C117" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D117" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E117">
-        <v>20.5</v>
+        <v>7.5</v>
       </c>
       <c r="F117">
-        <v>23.08</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G117" s="1">
-        <v>0.614</v>
+        <v>0.55</v>
       </c>
       <c r="H117" t="s">
         <v>140</v>
       </c>
       <c r="I117" s="2">
-        <v>17.21</v>
+        <v>4.98</v>
       </c>
       <c r="J117" s="2">
-        <v>0.0237</v>
+        <v>0.0137</v>
       </c>
       <c r="K117" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L117" t="s">
         <v>145</v>
@@ -5318,37 +5318,37 @@
     </row>
     <row r="118" spans="1:12">
       <c r="A118" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="B118" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C118" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D118" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E118">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="F118">
-        <v>1.45</v>
+        <v>7.87</v>
       </c>
       <c r="G118" s="1">
-        <v>0.611</v>
+        <v>0.547</v>
       </c>
       <c r="H118" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I118" s="2">
-        <v>16.73</v>
+        <v>4.42</v>
       </c>
       <c r="J118" s="2">
-        <v>0.023</v>
+        <v>0.0121</v>
       </c>
       <c r="K118" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L118" t="s">
         <v>145</v>
@@ -5356,37 +5356,37 @@
     </row>
     <row r="119" spans="1:12">
       <c r="A119" t="s">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="B119" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C119" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D119" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E119">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="F119">
-        <v>9.59</v>
+        <v>19.5</v>
       </c>
       <c r="G119" s="1">
-        <v>0.61</v>
+        <v>0.547</v>
       </c>
       <c r="H119" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I119" s="2">
-        <v>16.44</v>
+        <v>4.37</v>
       </c>
       <c r="J119" s="2">
-        <v>0.0226</v>
+        <v>0.012</v>
       </c>
       <c r="K119" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L119" t="s">
         <v>145</v>
@@ -5394,37 +5394,37 @@
     </row>
     <row r="120" spans="1:12">
       <c r="A120" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="B120" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="C120" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D120" t="s">
         <v>134</v>
       </c>
       <c r="E120">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F120">
-        <v>3.21</v>
+        <v>1.83</v>
       </c>
       <c r="G120" s="1">
-        <v>0.61</v>
+        <v>0.546</v>
       </c>
       <c r="H120" t="s">
         <v>140</v>
       </c>
       <c r="I120" s="2">
-        <v>16.38</v>
+        <v>4.15</v>
       </c>
       <c r="J120" s="2">
-        <v>0.0225</v>
+        <v>0.0114</v>
       </c>
       <c r="K120" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L120" t="s">
         <v>145</v>
@@ -5432,37 +5432,37 @@
     </row>
     <row r="121" spans="1:12">
       <c r="A121" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B121" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C121" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D121" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E121">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="F121">
-        <v>5.07</v>
+        <v>13.84</v>
       </c>
       <c r="G121" s="1">
-        <v>0.606</v>
+        <v>0.539</v>
       </c>
       <c r="H121" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I121" s="2">
-        <v>15.74</v>
+        <v>6.08</v>
       </c>
       <c r="J121" s="2">
-        <v>0.0216</v>
+        <v>0.0119</v>
       </c>
       <c r="K121" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L121" t="s">
         <v>145</v>
@@ -5470,37 +5470,37 @@
     </row>
     <row r="122" spans="1:12">
       <c r="A122" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B122" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C122" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D122" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E122">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="F122">
-        <v>4.15</v>
+        <v>2.16</v>
       </c>
       <c r="G122" s="1">
-        <v>0.599</v>
+        <v>0.534</v>
       </c>
       <c r="H122" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I122" s="2">
-        <v>14.45</v>
+        <v>5.38</v>
       </c>
       <c r="J122" s="2">
-        <v>0.0199</v>
+        <v>0.0106</v>
       </c>
       <c r="K122" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L122" t="s">
         <v>145</v>
@@ -5508,37 +5508,37 @@
     </row>
     <row r="123" spans="1:12">
       <c r="A123" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="B123" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C123" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D123" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E123">
-        <v>11.5</v>
+        <v>9.5</v>
       </c>
       <c r="F123">
-        <v>12.77</v>
+        <v>10.25</v>
       </c>
       <c r="G123" s="1">
-        <v>0.594</v>
+        <v>0.533</v>
       </c>
       <c r="H123" t="s">
         <v>140</v>
       </c>
       <c r="I123" s="2">
-        <v>13.43</v>
+        <v>5.2</v>
       </c>
       <c r="J123" s="2">
-        <v>0.0185</v>
+        <v>0.0102</v>
       </c>
       <c r="K123" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L123" t="s">
         <v>145</v>
@@ -5546,37 +5546,37 @@
     </row>
     <row r="124" spans="1:12">
       <c r="A124" t="s">
-        <v>103</v>
+        <v>40</v>
       </c>
       <c r="B124" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C124" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D124" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E124">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="F124">
-        <v>14.21</v>
+        <v>7.05</v>
       </c>
       <c r="G124" s="1">
-        <v>0.589</v>
+        <v>0.527</v>
       </c>
       <c r="H124" t="s">
         <v>140</v>
       </c>
       <c r="I124" s="2">
-        <v>12.54</v>
+        <v>4.47</v>
       </c>
       <c r="J124" s="2">
-        <v>0.0172</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="K124" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L124" t="s">
         <v>145</v>
@@ -5584,37 +5584,37 @@
     </row>
     <row r="125" spans="1:12">
       <c r="A125" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C125" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D125" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E125">
-        <v>5.5</v>
+        <v>9.5</v>
       </c>
       <c r="F125">
-        <v>5.23</v>
+        <v>10.26</v>
       </c>
       <c r="G125" s="1">
-        <v>0.586</v>
+        <v>0.527</v>
       </c>
       <c r="H125" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I125" s="2">
-        <v>11.94</v>
+        <v>4.46</v>
       </c>
       <c r="J125" s="2">
-        <v>0.0164</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="K125" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L125" t="s">
         <v>145</v>
@@ -5622,37 +5622,37 @@
     </row>
     <row r="126" spans="1:12">
       <c r="A126" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="B126" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C126" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D126" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E126">
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="F126">
-        <v>8.07</v>
+        <v>13.6</v>
       </c>
       <c r="G126" s="1">
-        <v>0.585</v>
+        <v>0.527</v>
       </c>
       <c r="H126" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I126" s="2">
-        <v>11.7</v>
+        <v>4.42</v>
       </c>
       <c r="J126" s="2">
-        <v>0.0161</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="K126" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L126" t="s">
         <v>145</v>
@@ -5660,37 +5660,37 @@
     </row>
     <row r="127" spans="1:12">
       <c r="A127" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="B127" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C127" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D127" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E127">
-        <v>9.5</v>
+        <v>12.5</v>
       </c>
       <c r="F127">
-        <v>10.89</v>
+        <v>13.21</v>
       </c>
       <c r="G127" s="1">
-        <v>0.578</v>
+        <v>0.527</v>
       </c>
       <c r="H127" t="s">
         <v>140</v>
       </c>
       <c r="I127" s="2">
-        <v>10.38</v>
+        <v>4.37</v>
       </c>
       <c r="J127" s="2">
-        <v>0.0143</v>
+        <v>0.0086</v>
       </c>
       <c r="K127" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L127" t="s">
         <v>145</v>
@@ -5698,37 +5698,37 @@
     </row>
     <row r="128" spans="1:12">
       <c r="A128" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B128" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C128" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D128" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E128">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="F128">
-        <v>5.28</v>
+        <v>1.63</v>
       </c>
       <c r="G128" s="1">
-        <v>0.574</v>
+        <v>0.526</v>
       </c>
       <c r="H128" t="s">
         <v>139</v>
       </c>
       <c r="I128" s="2">
-        <v>9.49</v>
+        <v>4.3</v>
       </c>
       <c r="J128" s="2">
-        <v>0.0131</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="K128" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L128" t="s">
         <v>145</v>
@@ -5736,37 +5736,37 @@
     </row>
     <row r="129" spans="1:12">
       <c r="A129" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="B129" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C129" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D129" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E129">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="F129">
-        <v>1.47</v>
+        <v>3.41</v>
       </c>
       <c r="G129" s="1">
-        <v>0.572</v>
+        <v>0.525</v>
       </c>
       <c r="H129" t="s">
         <v>139</v>
       </c>
       <c r="I129" s="2">
-        <v>9.220000000000001</v>
+        <v>4.19</v>
       </c>
       <c r="J129" s="2">
-        <v>0.0127</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="K129" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L129" t="s">
         <v>145</v>
@@ -5774,37 +5774,37 @@
     </row>
     <row r="130" spans="1:12">
       <c r="A130" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="B130" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="C130" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D130" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E130">
-        <v>19.5</v>
+        <v>1.5</v>
       </c>
       <c r="F130">
-        <v>20.86</v>
+        <v>1.86</v>
       </c>
       <c r="G130" s="1">
-        <v>0.571</v>
+        <v>0.524</v>
       </c>
       <c r="H130" t="s">
         <v>140</v>
       </c>
       <c r="I130" s="2">
-        <v>8.93</v>
+        <v>4.02</v>
       </c>
       <c r="J130" s="2">
-        <v>0.0123</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="K130" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L130" t="s">
         <v>145</v>
@@ -5812,37 +5812,37 @@
     </row>
     <row r="131" spans="1:12">
       <c r="A131" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B131" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="C131" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D131" t="s">
         <v>137</v>
       </c>
       <c r="E131">
-        <v>2.5</v>
+        <v>18.5</v>
       </c>
       <c r="F131">
-        <v>2.4</v>
+        <v>18.96</v>
       </c>
       <c r="G131" s="1">
-        <v>0.571</v>
+        <v>0.545</v>
       </c>
       <c r="H131" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I131" s="2">
-        <v>8.92</v>
+        <v>3.99</v>
       </c>
       <c r="J131" s="2">
-        <v>0.0123</v>
+        <v>0.011</v>
       </c>
       <c r="K131" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L131" t="s">
         <v>145</v>
@@ -5850,37 +5850,37 @@
     </row>
     <row r="132" spans="1:12">
       <c r="A132" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="B132" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C132" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D132" t="s">
         <v>135</v>
       </c>
       <c r="E132">
-        <v>12.5</v>
+        <v>5.5</v>
       </c>
       <c r="F132">
-        <v>13.84</v>
+        <v>5.42</v>
       </c>
       <c r="G132" s="1">
-        <v>0.569</v>
+        <v>0.545</v>
       </c>
       <c r="H132" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I132" s="2">
-        <v>8.69</v>
+        <v>3.95</v>
       </c>
       <c r="J132" s="2">
-        <v>0.0119</v>
+        <v>0.0109</v>
       </c>
       <c r="K132" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L132" t="s">
         <v>145</v>
@@ -5888,13 +5888,13 @@
     </row>
     <row r="133" spans="1:12">
       <c r="A133" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="B133" t="s">
         <v>128</v>
       </c>
       <c r="C133" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="D133" t="s">
         <v>134</v>
@@ -5903,22 +5903,22 @@
         <v>1.5</v>
       </c>
       <c r="F133">
-        <v>2.16</v>
+        <v>1.82</v>
       </c>
       <c r="G133" s="1">
-        <v>0.5639999999999999</v>
+        <v>0.544</v>
       </c>
       <c r="H133" t="s">
         <v>140</v>
       </c>
       <c r="I133" s="2">
-        <v>7.69</v>
+        <v>3.78</v>
       </c>
       <c r="J133" s="2">
-        <v>0.0106</v>
+        <v>0.0104</v>
       </c>
       <c r="K133" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L133" t="s">
         <v>145</v>
@@ -5926,37 +5926,37 @@
     </row>
     <row r="134" spans="1:12">
       <c r="A134" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B134" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C134" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D134" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E134">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="F134">
-        <v>10.25</v>
+        <v>1.85</v>
       </c>
       <c r="G134" s="1">
-        <v>0.5629999999999999</v>
+        <v>0.52</v>
       </c>
       <c r="H134" t="s">
         <v>140</v>
       </c>
       <c r="I134" s="2">
-        <v>7.42</v>
+        <v>3.56</v>
       </c>
       <c r="J134" s="2">
-        <v>0.0102</v>
+        <v>0.007</v>
       </c>
       <c r="K134" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L134" t="s">
         <v>145</v>
@@ -5964,37 +5964,37 @@
     </row>
     <row r="135" spans="1:12">
       <c r="A135" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="B135" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C135" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D135" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E135">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="F135">
-        <v>7.05</v>
+        <v>3.91</v>
       </c>
       <c r="G135" s="1">
-        <v>0.5570000000000001</v>
+        <v>0.519</v>
       </c>
       <c r="H135" t="s">
         <v>140</v>
       </c>
       <c r="I135" s="2">
-        <v>6.39</v>
+        <v>3.38</v>
       </c>
       <c r="J135" s="2">
-        <v>0.008800000000000001</v>
+        <v>0.0066</v>
       </c>
       <c r="K135" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L135" t="s">
         <v>145</v>
@@ -6002,37 +6002,37 @@
     </row>
     <row r="136" spans="1:12">
       <c r="A136" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B136" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C136" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D136" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E136">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="F136">
-        <v>10.26</v>
+        <v>12.08</v>
       </c>
       <c r="G136" s="1">
-        <v>0.5570000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="H136" t="s">
         <v>140</v>
       </c>
       <c r="I136" s="2">
-        <v>6.37</v>
+        <v>3.13</v>
       </c>
       <c r="J136" s="2">
-        <v>0.008800000000000001</v>
+        <v>0.0086</v>
       </c>
       <c r="K136" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L136" t="s">
         <v>145</v>
@@ -6040,37 +6040,37 @@
     </row>
     <row r="137" spans="1:12">
       <c r="A137" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B137" t="s">
         <v>125</v>
       </c>
       <c r="C137" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="D137" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E137">
-        <v>12.5</v>
+        <v>32.5</v>
       </c>
       <c r="F137">
-        <v>13.6</v>
+        <v>31.81</v>
       </c>
       <c r="G137" s="1">
-        <v>0.5570000000000001</v>
+        <v>0.539</v>
       </c>
       <c r="H137" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I137" s="2">
-        <v>6.32</v>
+        <v>2.96</v>
       </c>
       <c r="J137" s="2">
-        <v>0.008699999999999999</v>
+        <v>0.0081</v>
       </c>
       <c r="K137" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L137" t="s">
         <v>145</v>
@@ -6078,37 +6078,37 @@
     </row>
     <row r="138" spans="1:12">
       <c r="A138" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B138" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C138" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="D138" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E138">
-        <v>12.5</v>
+        <v>9.5</v>
       </c>
       <c r="F138">
-        <v>13.21</v>
+        <v>9.92</v>
       </c>
       <c r="G138" s="1">
-        <v>0.5570000000000001</v>
+        <v>0.513</v>
       </c>
       <c r="H138" t="s">
         <v>140</v>
       </c>
       <c r="I138" s="2">
-        <v>6.25</v>
+        <v>2.52</v>
       </c>
       <c r="J138" s="2">
-        <v>0.0086</v>
+        <v>0.0049</v>
       </c>
       <c r="K138" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L138" t="s">
         <v>145</v>
@@ -6116,37 +6116,37 @@
     </row>
     <row r="139" spans="1:12">
       <c r="A139" t="s">
-        <v>110</v>
+        <v>12</v>
       </c>
       <c r="B139" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C139" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="D139" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E139">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="F139">
-        <v>1.63</v>
+        <v>7.86</v>
       </c>
       <c r="G139" s="1">
-        <v>0.556</v>
+        <v>0.537</v>
       </c>
       <c r="H139" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I139" s="2">
-        <v>6.14</v>
+        <v>2.48</v>
       </c>
       <c r="J139" s="2">
-        <v>0.008399999999999999</v>
+        <v>0.0068</v>
       </c>
       <c r="K139" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L139" t="s">
         <v>145</v>
@@ -6154,37 +6154,37 @@
     </row>
     <row r="140" spans="1:12">
       <c r="A140" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="B140" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C140" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D140" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E140">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F140">
-        <v>3.41</v>
+        <v>2.83</v>
       </c>
       <c r="G140" s="1">
-        <v>0.555</v>
+        <v>0.508</v>
       </c>
       <c r="H140" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I140" s="2">
-        <v>5.98</v>
+        <v>1.94</v>
       </c>
       <c r="J140" s="2">
-        <v>0.008200000000000001</v>
+        <v>0.0038</v>
       </c>
       <c r="K140" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L140" t="s">
         <v>145</v>
@@ -6192,37 +6192,37 @@
     </row>
     <row r="141" spans="1:12">
       <c r="A141" t="s">
-        <v>111</v>
+        <v>57</v>
       </c>
       <c r="B141" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C141" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D141" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E141">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="F141">
-        <v>1.86</v>
+        <v>5.86</v>
       </c>
       <c r="G141" s="1">
-        <v>0.554</v>
+        <v>0.532</v>
       </c>
       <c r="H141" t="s">
         <v>140</v>
       </c>
       <c r="I141" s="2">
-        <v>5.75</v>
+        <v>1.59</v>
       </c>
       <c r="J141" s="2">
-        <v>0.007900000000000001</v>
+        <v>0.0044</v>
       </c>
       <c r="K141" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L141" t="s">
         <v>145</v>
@@ -6230,34 +6230,34 @@
     </row>
     <row r="142" spans="1:12">
       <c r="A142" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="B142" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C142" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D142" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E142">
-        <v>1.5</v>
+        <v>18.5</v>
       </c>
       <c r="F142">
-        <v>1.85</v>
+        <v>17.8</v>
       </c>
       <c r="G142" s="1">
-        <v>0.55</v>
+        <v>0.504</v>
       </c>
       <c r="H142" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I142" s="2">
-        <v>5.09</v>
+        <v>1.4</v>
       </c>
       <c r="J142" s="2">
-        <v>0.007</v>
+        <v>0.0028</v>
       </c>
       <c r="K142" t="s">
         <v>144</v>
@@ -6268,34 +6268,34 @@
     </row>
     <row r="143" spans="1:12">
       <c r="A143" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="B143" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C143" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="D143" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E143">
         <v>3.5</v>
       </c>
       <c r="F143">
-        <v>3.91</v>
+        <v>3.53</v>
       </c>
       <c r="G143" s="1">
-        <v>0.549</v>
+        <v>0.531</v>
       </c>
       <c r="H143" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I143" s="2">
-        <v>4.84</v>
+        <v>1.31</v>
       </c>
       <c r="J143" s="2">
-        <v>0.0066</v>
+        <v>0.0036</v>
       </c>
       <c r="K143" t="s">
         <v>144</v>
@@ -6306,34 +6306,34 @@
     </row>
     <row r="144" spans="1:12">
       <c r="A144" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="B144" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C144" t="s">
         <v>133</v>
       </c>
       <c r="D144" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E144">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="F144">
-        <v>3.53</v>
+        <v>7.95</v>
       </c>
       <c r="G144" s="1">
-        <v>0.531</v>
+        <v>0.503</v>
       </c>
       <c r="H144" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I144" s="2">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="J144" s="2">
-        <v>0.0036</v>
+        <v>0.0023</v>
       </c>
       <c r="K144" t="s">
         <v>144</v>
@@ -6344,16 +6344,16 @@
     </row>
     <row r="145" spans="1:12">
       <c r="A145" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="B145" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C145" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D145" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E145">
         <v>22.5</v>
@@ -6362,13 +6362,13 @@
         <v>23.35</v>
       </c>
       <c r="G145" s="1">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="H145" t="s">
         <v>140</v>
       </c>
       <c r="I145" s="2">
-        <v>1.19</v>
+        <v>0.83</v>
       </c>
       <c r="J145" s="2">
         <v>0.0016</v>
@@ -6382,16 +6382,16 @@
     </row>
     <row r="146" spans="1:12">
       <c r="A146" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="B146" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C146" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D146" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E146">
         <v>13.5</v>
@@ -6420,7 +6420,7 @@
     </row>
     <row r="147" spans="1:12">
       <c r="A147" t="s">
-        <v>56</v>
+        <v>112</v>
       </c>
       <c r="B147" t="s">
         <v>114</v>
@@ -6458,13 +6458,13 @@
     </row>
     <row r="148" spans="1:12">
       <c r="A148" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="B148" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C148" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D148" t="s">
         <v>134</v>
@@ -6496,16 +6496,16 @@
     </row>
     <row r="149" spans="1:12">
       <c r="A149" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="B149" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C149" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D149" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E149">
         <v>29.5</v>
@@ -6523,7 +6523,7 @@
         <v>0.34</v>
       </c>
       <c r="J149" s="2">
-        <v>0.0005</v>
+        <v>0.0009</v>
       </c>
       <c r="K149" t="s">
         <v>144</v>
@@ -6537,13 +6537,13 @@
         <v>113</v>
       </c>
       <c r="B150" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C150" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D150" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E150">
         <v>3.5</v>
@@ -6572,16 +6572,16 @@
     </row>
     <row r="151" spans="1:12">
       <c r="A151" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="B151" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C151" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D151" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E151">
         <v>9.5</v>
@@ -6613,13 +6613,13 @@
         <v>113</v>
       </c>
       <c r="B152" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C152" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D152" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E152">
         <v>10.5</v>
@@ -6648,16 +6648,16 @@
     </row>
     <row r="153" spans="1:12">
       <c r="A153" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B153" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C153" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D153" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E153">
         <v>9.5</v>
@@ -6666,13 +6666,13 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G153" s="1">
-        <v>0.522</v>
+        <v>0.492</v>
       </c>
       <c r="H153" t="s">
         <v>140</v>
       </c>
       <c r="I153" s="2">
-        <v>-0.27</v>
+        <v>-0.19</v>
       </c>
       <c r="J153" s="2">
         <v>0</v>
@@ -6686,16 +6686,16 @@
     </row>
     <row r="154" spans="1:12">
       <c r="A154" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B154" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C154" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D154" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E154">
         <v>11.5</v>
@@ -6704,13 +6704,13 @@
         <v>11.05</v>
       </c>
       <c r="G154" s="1">
-        <v>0.522</v>
+        <v>0.492</v>
       </c>
       <c r="H154" t="s">
         <v>139</v>
       </c>
       <c r="I154" s="2">
-        <v>-0.43</v>
+        <v>-0.3</v>
       </c>
       <c r="J154" s="2">
         <v>0</v>
@@ -6724,31 +6724,31 @@
     </row>
     <row r="155" spans="1:12">
       <c r="A155" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="B155" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C155" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D155" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E155">
-        <v>17.5</v>
+        <v>2.5</v>
       </c>
       <c r="F155">
-        <v>17.87</v>
+        <v>2.69</v>
       </c>
       <c r="G155" s="1">
-        <v>0.52</v>
+        <v>0.49</v>
       </c>
       <c r="H155" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I155" s="2">
-        <v>-0.79</v>
+        <v>-0.57</v>
       </c>
       <c r="J155" s="2">
         <v>0</v>
@@ -6762,31 +6762,31 @@
     </row>
     <row r="156" spans="1:12">
       <c r="A156" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B156" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C156" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D156" t="s">
         <v>137</v>
       </c>
       <c r="E156">
-        <v>2.5</v>
+        <v>17.5</v>
       </c>
       <c r="F156">
-        <v>2.69</v>
+        <v>17.87</v>
       </c>
       <c r="G156" s="1">
         <v>0.52</v>
       </c>
       <c r="H156" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I156" s="2">
-        <v>-0.82</v>
+        <v>-0.79</v>
       </c>
       <c r="J156" s="2">
         <v>0</v>
@@ -6800,16 +6800,16 @@
     </row>
     <row r="157" spans="1:12">
       <c r="A157" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B157" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C157" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D157" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E157">
         <v>2.5</v>
@@ -6818,13 +6818,13 @@
         <v>2.61</v>
       </c>
       <c r="G157" s="1">
-        <v>0.516</v>
+        <v>0.486</v>
       </c>
       <c r="H157" t="s">
         <v>139</v>
       </c>
       <c r="I157" s="2">
-        <v>-1.54</v>
+        <v>-1.08</v>
       </c>
       <c r="J157" s="2">
         <v>0</v>
@@ -6838,16 +6838,16 @@
     </row>
     <row r="158" spans="1:12">
       <c r="A158" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="B158" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C158" t="s">
         <v>132</v>
       </c>
       <c r="D158" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E158">
         <v>11.5</v>
@@ -6856,13 +6856,13 @@
         <v>11.7</v>
       </c>
       <c r="G158" s="1">
-        <v>0.515</v>
+        <v>0.485</v>
       </c>
       <c r="H158" t="s">
         <v>140</v>
       </c>
       <c r="I158" s="2">
-        <v>-1.68</v>
+        <v>-1.18</v>
       </c>
       <c r="J158" s="2">
         <v>0</v>
@@ -6876,16 +6876,16 @@
     </row>
     <row r="159" spans="1:12">
       <c r="A159" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B159" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C159" t="s">
         <v>114</v>
       </c>
       <c r="D159" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E159">
         <v>19.5</v>
@@ -6894,13 +6894,13 @@
         <v>19.26</v>
       </c>
       <c r="G159" s="1">
-        <v>0.514</v>
+        <v>0.484</v>
       </c>
       <c r="H159" t="s">
         <v>139</v>
       </c>
       <c r="I159" s="2">
-        <v>-1.9</v>
+        <v>-1.33</v>
       </c>
       <c r="J159" s="2">
         <v>0</v>
@@ -6914,16 +6914,16 @@
     </row>
     <row r="160" spans="1:12">
       <c r="A160" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B160" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C160" t="s">
         <v>114</v>
       </c>
       <c r="D160" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E160">
         <v>11.5</v>
@@ -6932,13 +6932,13 @@
         <v>11.64</v>
       </c>
       <c r="G160" s="1">
-        <v>0.513</v>
+        <v>0.483</v>
       </c>
       <c r="H160" t="s">
         <v>140</v>
       </c>
       <c r="I160" s="2">
-        <v>-2.1</v>
+        <v>-1.47</v>
       </c>
       <c r="J160" s="2">
         <v>0</v>
@@ -6952,16 +6952,16 @@
     </row>
     <row r="161" spans="1:12">
       <c r="A161" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B161" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C161" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D161" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E161">
         <v>7.5</v>
@@ -6970,13 +6970,13 @@
         <v>7.75</v>
       </c>
       <c r="G161" s="1">
-        <v>0.511</v>
+        <v>0.481</v>
       </c>
       <c r="H161" t="s">
         <v>139</v>
       </c>
       <c r="I161" s="2">
-        <v>-2.4</v>
+        <v>-1.68</v>
       </c>
       <c r="J161" s="2">
         <v>0</v>
@@ -6990,16 +6990,16 @@
     </row>
     <row r="162" spans="1:12">
       <c r="A162" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="B162" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C162" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D162" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E162">
         <v>29.5</v>
@@ -7028,7 +7028,7 @@
     </row>
     <row r="163" spans="1:12">
       <c r="A163" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="B163" t="s">
         <v>114</v>
@@ -7037,7 +7037,7 @@
         <v>131</v>
       </c>
       <c r="D163" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E163">
         <v>24.5</v>
@@ -7066,16 +7066,16 @@
     </row>
     <row r="164" spans="1:12">
       <c r="A164" t="s">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="B164" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C164" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D164" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E164">
         <v>22.5</v>

--- a/output/processed_props.xlsx
+++ b/output/processed_props.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="147">
   <si>
     <t>Player</t>
   </si>
@@ -55,121 +55,139 @@
     <t>Jonas Valanciunas</t>
   </si>
   <si>
+    <t>Joel Embiid</t>
+  </si>
+  <si>
+    <t>Tim Hardaway Jr.</t>
+  </si>
+  <si>
+    <t>Brandon Ingram</t>
+  </si>
+  <si>
+    <t>Desmond Bane</t>
+  </si>
+  <si>
+    <t>Jalen Johnson</t>
+  </si>
+  <si>
+    <t>Jaylen Brown</t>
+  </si>
+  <si>
+    <t>CJ McCollum</t>
+  </si>
+  <si>
+    <t>Tyrese Maxey</t>
+  </si>
+  <si>
+    <t>Chet Holmgren</t>
+  </si>
+  <si>
+    <t>Bilal Coulibaly</t>
+  </si>
+  <si>
+    <t>LeBron James</t>
+  </si>
+  <si>
+    <t>Brandon Miller</t>
+  </si>
+  <si>
+    <t>Dyson Daniels</t>
+  </si>
+  <si>
+    <t>Bub Carrington</t>
+  </si>
+  <si>
+    <t>Jock Landale</t>
+  </si>
+  <si>
+    <t>Donovan Mitchell</t>
+  </si>
+  <si>
+    <t>LaMelo Ball</t>
+  </si>
+  <si>
+    <t>Anthony Edwards</t>
+  </si>
+  <si>
     <t>Joan Beringer</t>
   </si>
   <si>
-    <t>Joel Embiid</t>
-  </si>
-  <si>
-    <t>Tim Hardaway Jr.</t>
-  </si>
-  <si>
-    <t>Brandon Ingram</t>
-  </si>
-  <si>
-    <t>Desmond Bane</t>
-  </si>
-  <si>
-    <t>Jalen Johnson</t>
-  </si>
-  <si>
-    <t>Jaylen Brown</t>
-  </si>
-  <si>
-    <t>CJ McCollum</t>
-  </si>
-  <si>
-    <t>Tyrese Maxey</t>
-  </si>
-  <si>
-    <t>Chet Holmgren</t>
-  </si>
-  <si>
-    <t>Bilal Coulibaly</t>
-  </si>
-  <si>
     <t>RJ Barrett</t>
   </si>
   <si>
-    <t>LeBron James</t>
-  </si>
-  <si>
-    <t>Brandon Miller</t>
-  </si>
-  <si>
-    <t>Dyson Daniels</t>
-  </si>
-  <si>
-    <t>Bub Carrington</t>
-  </si>
-  <si>
-    <t>Jock Landale</t>
-  </si>
-  <si>
-    <t>Donovan Mitchell</t>
-  </si>
-  <si>
-    <t>LaMelo Ball</t>
-  </si>
-  <si>
     <t>Ayo Dosunmu</t>
   </si>
   <si>
-    <t>Anthony Edwards</t>
-  </si>
-  <si>
     <t>Kyshawn George</t>
   </si>
   <si>
     <t>Ryan Kalkbrenner</t>
   </si>
   <si>
+    <t>Tyus Jones</t>
+  </si>
+  <si>
+    <t>Aaron Wiggins</t>
+  </si>
+  <si>
+    <t>Kawhi Leonard</t>
+  </si>
+  <si>
+    <t>Derrick White</t>
+  </si>
+  <si>
+    <t>Jared McCain</t>
+  </si>
+  <si>
+    <t>Nikola Vucevic</t>
+  </si>
+  <si>
+    <t>Jaylon Tyson</t>
+  </si>
+  <si>
+    <t>Cam Thomas</t>
+  </si>
+  <si>
+    <t>Brook Lopez</t>
+  </si>
+  <si>
     <t>Kris Dunn</t>
   </si>
   <si>
-    <t>Tyus Jones</t>
-  </si>
-  <si>
-    <t>Aaron Wiggins</t>
-  </si>
-  <si>
-    <t>Kawhi Leonard</t>
-  </si>
-  <si>
-    <t>Derrick White</t>
-  </si>
-  <si>
-    <t>Jared McCain</t>
-  </si>
-  <si>
-    <t>Nikola Vucevic</t>
-  </si>
-  <si>
     <t>Egor Demin</t>
   </si>
   <si>
     <t>Nic Claxton</t>
   </si>
   <si>
-    <t>Jaylon Tyson</t>
-  </si>
-  <si>
     <t>Anthony Black</t>
   </si>
   <si>
     <t>Bennedict Mathurin</t>
   </si>
   <si>
-    <t>Cam Thomas</t>
-  </si>
-  <si>
     <t>Onyeka Okongwu</t>
   </si>
   <si>
     <t>Jarrett Allen</t>
   </si>
   <si>
-    <t>Brook Lopez</t>
+    <t>Corey Kispert</t>
+  </si>
+  <si>
+    <t>VJ Edgecombe</t>
+  </si>
+  <si>
+    <t>Sam Merrill</t>
+  </si>
+  <si>
+    <t>Kon Knueppel</t>
+  </si>
+  <si>
+    <t>Dennis Schroder</t>
+  </si>
+  <si>
+    <t>Nolan Traore</t>
   </si>
   <si>
     <t>Tristan Vukcevic</t>
@@ -178,33 +196,15 @@
     <t>Kristaps Porzingis</t>
   </si>
   <si>
-    <t>Corey Kispert</t>
-  </si>
-  <si>
     <t>Immanuel Quickley</t>
   </si>
   <si>
     <t>Neemias Queta</t>
   </si>
   <si>
-    <t>VJ Edgecombe</t>
-  </si>
-  <si>
-    <t>Sam Merrill</t>
-  </si>
-  <si>
-    <t>Kon Knueppel</t>
-  </si>
-  <si>
-    <t>Dennis Schroder</t>
-  </si>
-  <si>
     <t>Grant Williams</t>
   </si>
   <si>
-    <t>Nolan Traore</t>
-  </si>
-  <si>
     <t>Kyle Kuzma</t>
   </si>
   <si>
@@ -217,6 +217,54 @@
     <t>Brandin Podziemski</t>
   </si>
   <si>
+    <t>Draymond Green</t>
+  </si>
+  <si>
+    <t>Jamal Shead</t>
+  </si>
+  <si>
+    <t>De'Anthony Melton</t>
+  </si>
+  <si>
+    <t>Ryan Rollins</t>
+  </si>
+  <si>
+    <t>Al Horford</t>
+  </si>
+  <si>
+    <t>Daniel Gafford</t>
+  </si>
+  <si>
+    <t>Julius Randle</t>
+  </si>
+  <si>
+    <t>Naz Reid</t>
+  </si>
+  <si>
+    <t>Kevin Porter Jr.</t>
+  </si>
+  <si>
+    <t>Evan Mobley</t>
+  </si>
+  <si>
+    <t>Isaiah Joe</t>
+  </si>
+  <si>
+    <t>Julian Strawther</t>
+  </si>
+  <si>
+    <t>Klay Thompson</t>
+  </si>
+  <si>
+    <t>Payton Pritchard</t>
+  </si>
+  <si>
+    <t>Cason Wallace</t>
+  </si>
+  <si>
+    <t>Donte DiVincenzo</t>
+  </si>
+  <si>
     <t>Jamal Murray</t>
   </si>
   <si>
@@ -226,66 +274,18 @@
     <t>Luka Doncic</t>
   </si>
   <si>
-    <t>Draymond Green</t>
-  </si>
-  <si>
-    <t>Jamal Shead</t>
-  </si>
-  <si>
-    <t>De'Anthony Melton</t>
-  </si>
-  <si>
-    <t>Ryan Rollins</t>
-  </si>
-  <si>
     <t>Paolo Banchero</t>
   </si>
   <si>
-    <t>Al Horford</t>
-  </si>
-  <si>
     <t>Myles Turner</t>
   </si>
   <si>
-    <t>Daniel Gafford</t>
-  </si>
-  <si>
     <t>Dominick Barlow</t>
   </si>
   <si>
-    <t>Julius Randle</t>
-  </si>
-  <si>
-    <t>Naz Reid</t>
-  </si>
-  <si>
-    <t>Kevin Porter Jr.</t>
-  </si>
-  <si>
-    <t>Evan Mobley</t>
-  </si>
-  <si>
-    <t>Isaiah Joe</t>
-  </si>
-  <si>
-    <t>Julian Strawther</t>
-  </si>
-  <si>
     <t>James Harden</t>
   </si>
   <si>
-    <t>Klay Thompson</t>
-  </si>
-  <si>
-    <t>Payton Pritchard</t>
-  </si>
-  <si>
-    <t>Cason Wallace</t>
-  </si>
-  <si>
-    <t>Donte DiVincenzo</t>
-  </si>
-  <si>
     <t>Nickeil Alexander-Walker</t>
   </si>
   <si>
@@ -307,42 +307,42 @@
     <t>Pat Spencer</t>
   </si>
   <si>
+    <t>Rui Hachimura</t>
+  </si>
+  <si>
+    <t>Gui Santos</t>
+  </si>
+  <si>
+    <t>Isaiah Hartenstein</t>
+  </si>
+  <si>
+    <t>Deandre Ayton</t>
+  </si>
+  <si>
     <t>Nikola Jokic</t>
   </si>
   <si>
     <t>Michael Porter Jr.</t>
   </si>
   <si>
-    <t>Rui Hachimura</t>
-  </si>
-  <si>
-    <t>Gui Santos</t>
-  </si>
-  <si>
-    <t>Isaiah Hartenstein</t>
+    <t>Collin Murray-Boyles</t>
+  </si>
+  <si>
+    <t>Sam Hauser</t>
   </si>
   <si>
     <t>Quentin Grimes</t>
   </si>
   <si>
-    <t>Deandre Ayton</t>
+    <t>Baylor Scheierman</t>
   </si>
   <si>
     <t>Zaccharie Risacher</t>
   </si>
   <si>
-    <t>Collin Murray-Boyles</t>
-  </si>
-  <si>
     <t>Max Christie</t>
   </si>
   <si>
-    <t>Sam Hauser</t>
-  </si>
-  <si>
-    <t>Baylor Scheierman</t>
-  </si>
-  <si>
     <t>Tre Johnson</t>
   </si>
   <si>
@@ -361,51 +361,51 @@
     <t>DEN</t>
   </si>
   <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>ORL</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>BOS</t>
+  </si>
+  <si>
+    <t>OKC</t>
+  </si>
+  <si>
+    <t>WSH</t>
+  </si>
+  <si>
+    <t>LAL</t>
+  </si>
+  <si>
+    <t>CHA</t>
+  </si>
+  <si>
+    <t>CLE</t>
+  </si>
+  <si>
     <t>MIN</t>
   </si>
   <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>TOR</t>
-  </si>
-  <si>
-    <t>ORL</t>
-  </si>
-  <si>
-    <t>ATL</t>
-  </si>
-  <si>
-    <t>BOS</t>
-  </si>
-  <si>
-    <t>OKC</t>
-  </si>
-  <si>
-    <t>WSH</t>
-  </si>
-  <si>
-    <t>LAL</t>
-  </si>
-  <si>
-    <t>CHA</t>
-  </si>
-  <si>
-    <t>CLE</t>
+    <t>DAL</t>
   </si>
   <si>
     <t>LAC</t>
   </si>
   <si>
-    <t>DAL</t>
+    <t>MIL</t>
   </si>
   <si>
     <t>BKN</t>
   </si>
   <si>
-    <t>MIL</t>
-  </si>
-  <si>
     <t>GS</t>
   </si>
   <si>
@@ -421,15 +421,15 @@
     <t>AST</t>
   </si>
   <si>
+    <t>PTS</t>
+  </si>
+  <si>
+    <t>PRA</t>
+  </si>
+  <si>
     <t>REB</t>
   </si>
   <si>
-    <t>PTS</t>
-  </si>
-  <si>
-    <t>PRA</t>
-  </si>
-  <si>
     <t>RA</t>
   </si>
   <si>
@@ -449,6 +449,9 @@
   </si>
   <si>
     <t>C Tier</t>
+  </si>
+  <si>
+    <t>Pass</t>
   </si>
   <si>
     <t>2026-02-22</t>
@@ -943,7 +946,7 @@
         <v>141</v>
       </c>
       <c r="L2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -954,34 +957,34 @@
         <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D3" t="s">
         <v>135</v>
       </c>
       <c r="E3">
-        <v>5.5</v>
+        <v>26.5</v>
       </c>
       <c r="F3">
-        <v>2.95</v>
+        <v>31.53</v>
       </c>
       <c r="G3" s="1">
-        <v>0.891</v>
+        <v>0.788</v>
       </c>
       <c r="H3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I3" s="2">
-        <v>53.11</v>
+        <v>50.45</v>
       </c>
       <c r="J3" s="2">
-        <v>0.1043</v>
+        <v>0.1387</v>
       </c>
       <c r="K3" t="s">
         <v>141</v>
       </c>
       <c r="L3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -989,37 +992,37 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E4">
-        <v>26.5</v>
+        <v>1.5</v>
       </c>
       <c r="F4">
-        <v>31.53</v>
+        <v>0.99</v>
       </c>
       <c r="G4" s="1">
-        <v>0.788</v>
+        <v>0.746</v>
       </c>
       <c r="H4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I4" s="2">
-        <v>50.45</v>
+        <v>42.43</v>
       </c>
       <c r="J4" s="2">
-        <v>0.1387</v>
+        <v>0.1167</v>
       </c>
       <c r="K4" t="s">
         <v>141</v>
       </c>
       <c r="L4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1027,37 +1030,37 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D5" t="s">
         <v>134</v>
       </c>
       <c r="E5">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="F5">
-        <v>0.99</v>
+        <v>2.5</v>
       </c>
       <c r="G5" s="1">
-        <v>0.746</v>
+        <v>0.742</v>
       </c>
       <c r="H5" t="s">
         <v>139</v>
       </c>
       <c r="I5" s="2">
-        <v>42.43</v>
+        <v>41.73</v>
       </c>
       <c r="J5" s="2">
-        <v>0.1167</v>
+        <v>0.1148</v>
       </c>
       <c r="K5" t="s">
         <v>141</v>
       </c>
       <c r="L5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1068,34 +1071,34 @@
         <v>117</v>
       </c>
       <c r="C6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E6">
-        <v>3.5</v>
+        <v>25.5</v>
       </c>
       <c r="F6">
-        <v>2.5</v>
+        <v>30.44</v>
       </c>
       <c r="G6" s="1">
         <v>0.742</v>
       </c>
       <c r="H6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I6" s="2">
-        <v>41.73</v>
+        <v>41.68</v>
       </c>
       <c r="J6" s="2">
-        <v>0.1148</v>
+        <v>0.1146</v>
       </c>
       <c r="K6" t="s">
         <v>141</v>
       </c>
       <c r="L6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1106,34 +1109,34 @@
         <v>118</v>
       </c>
       <c r="C7" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D7" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E7">
-        <v>25.5</v>
+        <v>7.5</v>
       </c>
       <c r="F7">
-        <v>30.44</v>
+        <v>5.46</v>
       </c>
       <c r="G7" s="1">
-        <v>0.742</v>
+        <v>0.739</v>
       </c>
       <c r="H7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I7" s="2">
-        <v>41.68</v>
+        <v>41.1</v>
       </c>
       <c r="J7" s="2">
-        <v>0.1146</v>
+        <v>0.113</v>
       </c>
       <c r="K7" t="s">
         <v>141</v>
       </c>
       <c r="L7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1144,34 +1147,34 @@
         <v>119</v>
       </c>
       <c r="C8" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D8" t="s">
         <v>134</v>
       </c>
       <c r="E8">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="F8">
-        <v>5.46</v>
+        <v>3.47</v>
       </c>
       <c r="G8" s="1">
-        <v>0.739</v>
+        <v>0.73</v>
       </c>
       <c r="H8" t="s">
         <v>139</v>
       </c>
       <c r="I8" s="2">
-        <v>41.1</v>
+        <v>39.44</v>
       </c>
       <c r="J8" s="2">
-        <v>0.113</v>
+        <v>0.1085</v>
       </c>
       <c r="K8" t="s">
         <v>141</v>
       </c>
       <c r="L8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1179,37 +1182,37 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E9">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F9">
-        <v>3.47</v>
+        <v>2.56</v>
       </c>
       <c r="G9" s="1">
-        <v>0.73</v>
+        <v>0.728</v>
       </c>
       <c r="H9" t="s">
         <v>139</v>
       </c>
       <c r="I9" s="2">
-        <v>39.44</v>
+        <v>38.92</v>
       </c>
       <c r="J9" s="2">
-        <v>0.1085</v>
+        <v>0.107</v>
       </c>
       <c r="K9" t="s">
         <v>141</v>
       </c>
       <c r="L9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1217,37 +1220,37 @@
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E10">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="F10">
-        <v>2.56</v>
+        <v>4.99</v>
       </c>
       <c r="G10" s="1">
-        <v>0.728</v>
+        <v>0.719</v>
       </c>
       <c r="H10" t="s">
         <v>139</v>
       </c>
       <c r="I10" s="2">
-        <v>38.92</v>
+        <v>37.17</v>
       </c>
       <c r="J10" s="2">
-        <v>0.107</v>
+        <v>0.1022</v>
       </c>
       <c r="K10" t="s">
         <v>141</v>
       </c>
       <c r="L10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1255,28 +1258,28 @@
         <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C11" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D11" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E11">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="F11">
-        <v>4.99</v>
+        <v>6.56</v>
       </c>
       <c r="G11" s="1">
-        <v>0.719</v>
+        <v>0.718</v>
       </c>
       <c r="H11" t="s">
         <v>139</v>
       </c>
       <c r="I11" s="2">
-        <v>37.17</v>
+        <v>37.16</v>
       </c>
       <c r="J11" s="2">
         <v>0.1022</v>
@@ -1285,7 +1288,7 @@
         <v>141</v>
       </c>
       <c r="L11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1296,34 +1299,34 @@
         <v>121</v>
       </c>
       <c r="C12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D12" t="s">
         <v>135</v>
       </c>
       <c r="E12">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="F12">
-        <v>6.56</v>
+        <v>12.91</v>
       </c>
       <c r="G12" s="1">
         <v>0.718</v>
       </c>
       <c r="H12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I12" s="2">
-        <v>37.16</v>
+        <v>36.98</v>
       </c>
       <c r="J12" s="2">
-        <v>0.1022</v>
+        <v>0.1017</v>
       </c>
       <c r="K12" t="s">
         <v>141</v>
       </c>
       <c r="L12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1334,34 +1337,34 @@
         <v>122</v>
       </c>
       <c r="C13" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E13">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="F13">
-        <v>12.91</v>
+        <v>14.55</v>
       </c>
       <c r="G13" s="1">
-        <v>0.718</v>
+        <v>0.712</v>
       </c>
       <c r="H13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I13" s="2">
-        <v>36.98</v>
+        <v>35.97</v>
       </c>
       <c r="J13" s="2">
-        <v>0.1017</v>
+        <v>0.0989</v>
       </c>
       <c r="K13" t="s">
         <v>141</v>
       </c>
       <c r="L13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1369,37 +1372,37 @@
         <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C14" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D14" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E14">
-        <v>27.5</v>
+        <v>33.5</v>
       </c>
       <c r="F14">
-        <v>22.68</v>
+        <v>29.26</v>
       </c>
       <c r="G14" s="1">
-        <v>0.766</v>
+        <v>0.71</v>
       </c>
       <c r="H14" t="s">
         <v>139</v>
       </c>
       <c r="I14" s="2">
-        <v>36.43</v>
+        <v>35.61</v>
       </c>
       <c r="J14" s="2">
-        <v>0.0716</v>
+        <v>0.0979</v>
       </c>
       <c r="K14" t="s">
         <v>141</v>
       </c>
       <c r="L14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1407,37 +1410,37 @@
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C15" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D15" t="s">
         <v>136</v>
       </c>
       <c r="E15">
-        <v>19.5</v>
+        <v>23.5</v>
       </c>
       <c r="F15">
-        <v>14.55</v>
+        <v>19.35</v>
       </c>
       <c r="G15" s="1">
-        <v>0.712</v>
+        <v>0.707</v>
       </c>
       <c r="H15" t="s">
         <v>139</v>
       </c>
       <c r="I15" s="2">
-        <v>35.97</v>
+        <v>34.95</v>
       </c>
       <c r="J15" s="2">
-        <v>0.0989</v>
+        <v>0.0961</v>
       </c>
       <c r="K15" t="s">
         <v>141</v>
       </c>
       <c r="L15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1445,37 +1448,37 @@
         <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C16" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E16">
-        <v>33.5</v>
+        <v>17.5</v>
       </c>
       <c r="F16">
-        <v>29.26</v>
+        <v>15.51</v>
       </c>
       <c r="G16" s="1">
-        <v>0.71</v>
+        <v>0.704</v>
       </c>
       <c r="H16" t="s">
         <v>139</v>
       </c>
       <c r="I16" s="2">
-        <v>35.61</v>
+        <v>34.35</v>
       </c>
       <c r="J16" s="2">
-        <v>0.0979</v>
+        <v>0.0945</v>
       </c>
       <c r="K16" t="s">
         <v>141</v>
       </c>
       <c r="L16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1483,37 +1486,37 @@
         <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D17" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E17">
-        <v>23.5</v>
+        <v>1.5</v>
       </c>
       <c r="F17">
-        <v>19.35</v>
+        <v>1.19</v>
       </c>
       <c r="G17" s="1">
-        <v>0.707</v>
+        <v>0.7</v>
       </c>
       <c r="H17" t="s">
         <v>139</v>
       </c>
       <c r="I17" s="2">
-        <v>34.95</v>
+        <v>33.69</v>
       </c>
       <c r="J17" s="2">
-        <v>0.0961</v>
+        <v>0.0927</v>
       </c>
       <c r="K17" t="s">
         <v>141</v>
       </c>
       <c r="L17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1521,37 +1524,37 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C18" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D18" t="s">
         <v>137</v>
       </c>
       <c r="E18">
-        <v>17.5</v>
+        <v>3.5</v>
       </c>
       <c r="F18">
-        <v>15.51</v>
+        <v>2.76</v>
       </c>
       <c r="G18" s="1">
-        <v>0.704</v>
+        <v>0.7</v>
       </c>
       <c r="H18" t="s">
         <v>139</v>
       </c>
       <c r="I18" s="2">
-        <v>34.35</v>
+        <v>33.68</v>
       </c>
       <c r="J18" s="2">
-        <v>0.0945</v>
+        <v>0.0926</v>
       </c>
       <c r="K18" t="s">
         <v>141</v>
       </c>
       <c r="L18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1559,37 +1562,37 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C19" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D19" t="s">
         <v>134</v>
       </c>
       <c r="E19">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="F19">
-        <v>1.19</v>
+        <v>6.35</v>
       </c>
       <c r="G19" s="1">
-        <v>0.7</v>
+        <v>0.694</v>
       </c>
       <c r="H19" t="s">
         <v>139</v>
       </c>
       <c r="I19" s="2">
-        <v>33.69</v>
+        <v>32.48</v>
       </c>
       <c r="J19" s="2">
-        <v>0.0927</v>
+        <v>0.0893</v>
       </c>
       <c r="K19" t="s">
         <v>141</v>
       </c>
       <c r="L19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1600,34 +1603,34 @@
         <v>125</v>
       </c>
       <c r="C20" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E20">
         <v>3.5</v>
       </c>
       <c r="F20">
-        <v>2.76</v>
+        <v>2.83</v>
       </c>
       <c r="G20" s="1">
-        <v>0.7</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H20" t="s">
         <v>139</v>
       </c>
       <c r="I20" s="2">
-        <v>33.68</v>
+        <v>30.43</v>
       </c>
       <c r="J20" s="2">
-        <v>0.0926</v>
+        <v>0.0837</v>
       </c>
       <c r="K20" t="s">
         <v>141</v>
       </c>
       <c r="L20" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1635,37 +1638,37 @@
         <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C21" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="D21" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E21">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="F21">
-        <v>6.35</v>
+        <v>2.95</v>
       </c>
       <c r="G21" s="1">
-        <v>0.694</v>
+        <v>0.921</v>
       </c>
       <c r="H21" t="s">
         <v>139</v>
       </c>
       <c r="I21" s="2">
-        <v>32.48</v>
+        <v>75.87</v>
       </c>
       <c r="J21" s="2">
-        <v>0.0893</v>
+        <v>0.1043</v>
       </c>
       <c r="K21" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1673,37 +1676,37 @@
         <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C22" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D22" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E22">
-        <v>3.5</v>
+        <v>27.5</v>
       </c>
       <c r="F22">
-        <v>2.34</v>
+        <v>22.68</v>
       </c>
       <c r="G22" s="1">
-        <v>0.728</v>
+        <v>0.796</v>
       </c>
       <c r="H22" t="s">
         <v>139</v>
       </c>
       <c r="I22" s="2">
-        <v>31.25</v>
+        <v>52.05</v>
       </c>
       <c r="J22" s="2">
-        <v>0.0614</v>
+        <v>0.0716</v>
       </c>
       <c r="K22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1711,37 +1714,37 @@
         <v>33</v>
       </c>
       <c r="B23" t="s">
+        <v>125</v>
+      </c>
+      <c r="C23" t="s">
         <v>115</v>
       </c>
-      <c r="C23" t="s">
-        <v>116</v>
-      </c>
       <c r="D23" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E23">
         <v>3.5</v>
       </c>
       <c r="F23">
-        <v>2.83</v>
+        <v>2.34</v>
       </c>
       <c r="G23" s="1">
-        <v>0.6830000000000001</v>
+        <v>0.758</v>
       </c>
       <c r="H23" t="s">
         <v>139</v>
       </c>
       <c r="I23" s="2">
-        <v>30.43</v>
+        <v>44.64</v>
       </c>
       <c r="J23" s="2">
-        <v>0.0837</v>
+        <v>0.0614</v>
       </c>
       <c r="K23" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1749,13 +1752,13 @@
         <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E24">
         <v>12.5</v>
@@ -1764,22 +1767,22 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G24" s="1">
-        <v>0.719</v>
+        <v>0.749</v>
       </c>
       <c r="H24" t="s">
         <v>139</v>
       </c>
       <c r="I24" s="2">
-        <v>30.1</v>
+        <v>43</v>
       </c>
       <c r="J24" s="2">
         <v>0.0591</v>
       </c>
       <c r="K24" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L24" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1787,13 +1790,13 @@
         <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C25" t="s">
         <v>132</v>
       </c>
       <c r="D25" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E25">
         <v>7.5</v>
@@ -1802,22 +1805,22 @@
         <v>5.99</v>
       </c>
       <c r="G25" s="1">
-        <v>0.716</v>
+        <v>0.746</v>
       </c>
       <c r="H25" t="s">
         <v>139</v>
       </c>
       <c r="I25" s="2">
-        <v>29.7</v>
+        <v>42.42</v>
       </c>
       <c r="J25" s="2">
         <v>0.0583</v>
       </c>
       <c r="K25" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L25" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -1828,34 +1831,34 @@
         <v>126</v>
       </c>
       <c r="C26" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D26" t="s">
         <v>135</v>
       </c>
       <c r="E26">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="F26">
-        <v>3.74</v>
+        <v>5.44</v>
       </c>
       <c r="G26" s="1">
-        <v>0.675</v>
+        <v>0.727</v>
       </c>
       <c r="H26" t="s">
         <v>139</v>
       </c>
       <c r="I26" s="2">
-        <v>28.81</v>
+        <v>38.7</v>
       </c>
       <c r="J26" s="2">
-        <v>0.07920000000000001</v>
+        <v>0.0532</v>
       </c>
       <c r="K26" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1863,37 +1866,37 @@
         <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C27" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="D27" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E27">
-        <v>6.5</v>
+        <v>14.5</v>
       </c>
       <c r="F27">
-        <v>5.44</v>
+        <v>11.11</v>
       </c>
       <c r="G27" s="1">
-        <v>0.697</v>
+        <v>0.724</v>
       </c>
       <c r="H27" t="s">
         <v>139</v>
       </c>
       <c r="I27" s="2">
-        <v>27.09</v>
+        <v>38.14</v>
       </c>
       <c r="J27" s="2">
-        <v>0.0532</v>
+        <v>0.0524</v>
       </c>
       <c r="K27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L27" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -1901,37 +1904,37 @@
         <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C28" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E28">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="F28">
-        <v>11.11</v>
+        <v>3.45</v>
       </c>
       <c r="G28" s="1">
-        <v>0.694</v>
+        <v>0.722</v>
       </c>
       <c r="H28" t="s">
         <v>139</v>
       </c>
       <c r="I28" s="2">
-        <v>26.7</v>
+        <v>37.85</v>
       </c>
       <c r="J28" s="2">
-        <v>0.0524</v>
+        <v>0.052</v>
       </c>
       <c r="K28" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -1939,37 +1942,37 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C29" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D29" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E29">
-        <v>4.5</v>
+        <v>27.5</v>
       </c>
       <c r="F29">
-        <v>3.45</v>
+        <v>23.89</v>
       </c>
       <c r="G29" s="1">
-        <v>0.6919999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="H29" t="s">
         <v>139</v>
       </c>
       <c r="I29" s="2">
-        <v>26.49</v>
+        <v>37.36</v>
       </c>
       <c r="J29" s="2">
-        <v>0.052</v>
+        <v>0.0514</v>
       </c>
       <c r="K29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -1980,34 +1983,34 @@
         <v>120</v>
       </c>
       <c r="C30" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D30" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E30">
-        <v>27.5</v>
+        <v>2.5</v>
       </c>
       <c r="F30">
-        <v>23.89</v>
+        <v>1.84</v>
       </c>
       <c r="G30" s="1">
-        <v>0.6899999999999999</v>
+        <v>0.719</v>
       </c>
       <c r="H30" t="s">
         <v>139</v>
       </c>
       <c r="I30" s="2">
-        <v>26.15</v>
+        <v>37.3</v>
       </c>
       <c r="J30" s="2">
-        <v>0.0514</v>
+        <v>0.0513</v>
       </c>
       <c r="K30" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L30" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -2015,10 +2018,10 @@
         <v>41</v>
       </c>
       <c r="B31" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C31" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D31" t="s">
         <v>134</v>
@@ -2027,25 +2030,25 @@
         <v>2.5</v>
       </c>
       <c r="F31">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="G31" s="1">
-        <v>0.6889999999999999</v>
+        <v>0.715</v>
       </c>
       <c r="H31" t="s">
         <v>139</v>
       </c>
       <c r="I31" s="2">
-        <v>26.11</v>
+        <v>36.58</v>
       </c>
       <c r="J31" s="2">
-        <v>0.0513</v>
+        <v>0.0503</v>
       </c>
       <c r="K31" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L31" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -2053,37 +2056,37 @@
         <v>42</v>
       </c>
       <c r="B32" t="s">
+        <v>124</v>
+      </c>
+      <c r="C32" t="s">
         <v>120</v>
-      </c>
-      <c r="C32" t="s">
-        <v>123</v>
       </c>
       <c r="D32" t="s">
         <v>134</v>
       </c>
       <c r="E32">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F32">
-        <v>1.87</v>
+        <v>1.34</v>
       </c>
       <c r="G32" s="1">
-        <v>0.6850000000000001</v>
+        <v>0.705</v>
       </c>
       <c r="H32" t="s">
         <v>139</v>
       </c>
       <c r="I32" s="2">
-        <v>25.6</v>
+        <v>34.67</v>
       </c>
       <c r="J32" s="2">
-        <v>0.0503</v>
+        <v>0.0477</v>
       </c>
       <c r="K32" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L32" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -2094,34 +2097,34 @@
         <v>128</v>
       </c>
       <c r="C33" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D33" t="s">
         <v>134</v>
       </c>
       <c r="E33">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F33">
-        <v>2.96</v>
+        <v>2.04</v>
       </c>
       <c r="G33" s="1">
-        <v>0.655</v>
+        <v>0.701</v>
       </c>
       <c r="H33" t="s">
         <v>139</v>
       </c>
       <c r="I33" s="2">
-        <v>25.11</v>
+        <v>33.78</v>
       </c>
       <c r="J33" s="2">
-        <v>0.06909999999999999</v>
+        <v>0.0465</v>
       </c>
       <c r="K33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L33" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -2129,37 +2132,37 @@
         <v>44</v>
       </c>
       <c r="B34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C34" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D34" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E34">
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
       <c r="F34">
-        <v>12.14</v>
+        <v>7.16</v>
       </c>
       <c r="G34" s="1">
-        <v>0.655</v>
+        <v>0.681</v>
       </c>
       <c r="H34" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I34" s="2">
-        <v>25.1</v>
+        <v>30.02</v>
       </c>
       <c r="J34" s="2">
-        <v>0.06900000000000001</v>
+        <v>0.0413</v>
       </c>
       <c r="K34" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -2167,19 +2170,19 @@
         <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C35" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D35" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E35">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="F35">
-        <v>1.34</v>
+        <v>3.74</v>
       </c>
       <c r="G35" s="1">
         <v>0.675</v>
@@ -2188,16 +2191,16 @@
         <v>139</v>
       </c>
       <c r="I35" s="2">
-        <v>24.27</v>
+        <v>28.81</v>
       </c>
       <c r="J35" s="2">
-        <v>0.0477</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="K35" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -2205,37 +2208,37 @@
         <v>46</v>
       </c>
       <c r="B36" t="s">
+        <v>129</v>
+      </c>
+      <c r="C36" t="s">
         <v>118</v>
-      </c>
-      <c r="C36" t="s">
-        <v>126</v>
       </c>
       <c r="D36" t="s">
         <v>134</v>
       </c>
       <c r="E36">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F36">
-        <v>3.89</v>
+        <v>2.96</v>
       </c>
       <c r="G36" s="1">
-        <v>0.65</v>
+        <v>0.655</v>
       </c>
       <c r="H36" t="s">
         <v>139</v>
       </c>
       <c r="I36" s="2">
-        <v>24.04</v>
+        <v>25.11</v>
       </c>
       <c r="J36" s="2">
-        <v>0.06610000000000001</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="K36" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -2243,37 +2246,37 @@
         <v>47</v>
       </c>
       <c r="B37" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C37" t="s">
         <v>118</v>
       </c>
       <c r="D37" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E37">
-        <v>2.5</v>
+        <v>10.5</v>
       </c>
       <c r="F37">
-        <v>3.34</v>
+        <v>12.14</v>
       </c>
       <c r="G37" s="1">
-        <v>0.648</v>
+        <v>0.655</v>
       </c>
       <c r="H37" t="s">
         <v>140</v>
       </c>
       <c r="I37" s="2">
-        <v>23.72</v>
+        <v>25.1</v>
       </c>
       <c r="J37" s="2">
-        <v>0.06519999999999999</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L37" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -2281,37 +2284,37 @@
         <v>48</v>
       </c>
       <c r="B38" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="C38" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="D38" t="s">
         <v>134</v>
       </c>
       <c r="E38">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="F38">
-        <v>2.04</v>
+        <v>3.89</v>
       </c>
       <c r="G38" s="1">
-        <v>0.671</v>
+        <v>0.65</v>
       </c>
       <c r="H38" t="s">
         <v>139</v>
       </c>
       <c r="I38" s="2">
-        <v>23.65</v>
+        <v>24.04</v>
       </c>
       <c r="J38" s="2">
-        <v>0.0465</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="K38" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L38" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -2319,37 +2322,37 @@
         <v>49</v>
       </c>
       <c r="B39" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C39" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D39" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E39">
-        <v>14.5</v>
+        <v>2.5</v>
       </c>
       <c r="F39">
-        <v>16.68</v>
+        <v>3.34</v>
       </c>
       <c r="G39" s="1">
-        <v>0.639</v>
+        <v>0.648</v>
       </c>
       <c r="H39" t="s">
         <v>140</v>
       </c>
       <c r="I39" s="2">
-        <v>21.93</v>
+        <v>23.72</v>
       </c>
       <c r="J39" s="2">
-        <v>0.0603</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="K39" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L39" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -2357,37 +2360,37 @@
         <v>50</v>
       </c>
       <c r="B40" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C40" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D40" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E40">
-        <v>25.5</v>
+        <v>14.5</v>
       </c>
       <c r="F40">
-        <v>30.33</v>
+        <v>16.68</v>
       </c>
       <c r="G40" s="1">
-        <v>0.635</v>
+        <v>0.639</v>
       </c>
       <c r="H40" t="s">
         <v>140</v>
       </c>
       <c r="I40" s="2">
-        <v>21.25</v>
+        <v>21.93</v>
       </c>
       <c r="J40" s="2">
-        <v>0.0584</v>
+        <v>0.0603</v>
       </c>
       <c r="K40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L40" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2395,37 +2398,37 @@
         <v>51</v>
       </c>
       <c r="B41" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C41" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D41" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E41">
-        <v>8.5</v>
+        <v>25.5</v>
       </c>
       <c r="F41">
-        <v>7.16</v>
+        <v>30.33</v>
       </c>
       <c r="G41" s="1">
-        <v>0.651</v>
+        <v>0.635</v>
       </c>
       <c r="H41" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I41" s="2">
-        <v>21.02</v>
+        <v>21.25</v>
       </c>
       <c r="J41" s="2">
-        <v>0.0413</v>
+        <v>0.0584</v>
       </c>
       <c r="K41" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L41" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2433,37 +2436,37 @@
         <v>52</v>
       </c>
       <c r="B42" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C42" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D42" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E42">
-        <v>5.5</v>
+        <v>13.5</v>
       </c>
       <c r="F42">
-        <v>4.63</v>
+        <v>11.56</v>
       </c>
       <c r="G42" s="1">
-        <v>0.65</v>
+        <v>0.633</v>
       </c>
       <c r="H42" t="s">
         <v>139</v>
       </c>
       <c r="I42" s="2">
-        <v>20.84</v>
+        <v>20.78</v>
       </c>
       <c r="J42" s="2">
-        <v>0.0409</v>
+        <v>0.0571</v>
       </c>
       <c r="K42" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L42" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -2471,37 +2474,37 @@
         <v>53</v>
       </c>
       <c r="B43" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="C43" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D43" t="s">
         <v>134</v>
       </c>
       <c r="E43">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="F43">
-        <v>1.31</v>
+        <v>3.17</v>
       </c>
       <c r="G43" s="1">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H43" t="s">
         <v>139</v>
       </c>
       <c r="I43" s="2">
-        <v>20.81</v>
+        <v>20.27</v>
       </c>
       <c r="J43" s="2">
-        <v>0.0409</v>
+        <v>0.0558</v>
       </c>
       <c r="K43" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L43" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2509,37 +2512,37 @@
         <v>54</v>
       </c>
       <c r="B44" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C44" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D44" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E44">
-        <v>13.5</v>
+        <v>1.5</v>
       </c>
       <c r="F44">
-        <v>11.56</v>
+        <v>1.39</v>
       </c>
       <c r="G44" s="1">
-        <v>0.633</v>
+        <v>0.63</v>
       </c>
       <c r="H44" t="s">
         <v>139</v>
       </c>
       <c r="I44" s="2">
-        <v>20.78</v>
+        <v>20.2</v>
       </c>
       <c r="J44" s="2">
-        <v>0.0571</v>
+        <v>0.0556</v>
       </c>
       <c r="K44" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L44" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2547,37 +2550,37 @@
         <v>55</v>
       </c>
       <c r="B45" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C45" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D45" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E45">
-        <v>28.5</v>
+        <v>30.5</v>
       </c>
       <c r="F45">
-        <v>25.27</v>
+        <v>32.67</v>
       </c>
       <c r="G45" s="1">
-        <v>0.648</v>
+        <v>0.63</v>
       </c>
       <c r="H45" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I45" s="2">
-        <v>20.62</v>
+        <v>20.19</v>
       </c>
       <c r="J45" s="2">
-        <v>0.0405</v>
+        <v>0.0555</v>
       </c>
       <c r="K45" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L45" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -2585,37 +2588,37 @@
         <v>56</v>
       </c>
       <c r="B46" t="s">
+        <v>124</v>
+      </c>
+      <c r="C46" t="s">
         <v>120</v>
-      </c>
-      <c r="C46" t="s">
-        <v>123</v>
       </c>
       <c r="D46" t="s">
         <v>134</v>
       </c>
       <c r="E46">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="F46">
-        <v>1.32</v>
+        <v>3.08</v>
       </c>
       <c r="G46" s="1">
-        <v>0.647</v>
+        <v>0.629</v>
       </c>
       <c r="H46" t="s">
         <v>139</v>
       </c>
       <c r="I46" s="2">
-        <v>20.53</v>
+        <v>20.09</v>
       </c>
       <c r="J46" s="2">
-        <v>0.0403</v>
+        <v>0.0553</v>
       </c>
       <c r="K46" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L46" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2623,238 +2626,238 @@
         <v>57</v>
       </c>
       <c r="B47" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="C47" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D47" t="s">
         <v>134</v>
       </c>
       <c r="E47">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F47">
-        <v>3.17</v>
+        <v>5.92</v>
       </c>
       <c r="G47" s="1">
-        <v>0.63</v>
+        <v>0.626</v>
       </c>
       <c r="H47" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I47" s="2">
-        <v>20.27</v>
+        <v>19.54</v>
       </c>
       <c r="J47" s="2">
-        <v>0.0558</v>
+        <v>0.0537</v>
       </c>
       <c r="K47" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L47" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="B48" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C48" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D48" t="s">
         <v>134</v>
       </c>
       <c r="E48">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F48">
-        <v>1.39</v>
+        <v>2.26</v>
       </c>
       <c r="G48" s="1">
-        <v>0.63</v>
+        <v>0.621</v>
       </c>
       <c r="H48" t="s">
         <v>139</v>
       </c>
       <c r="I48" s="2">
-        <v>20.2</v>
+        <v>18.46</v>
       </c>
       <c r="J48" s="2">
-        <v>0.0556</v>
+        <v>0.0508</v>
       </c>
       <c r="K48" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L48" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C49" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D49" t="s">
         <v>137</v>
       </c>
       <c r="E49">
-        <v>30.5</v>
+        <v>5.5</v>
       </c>
       <c r="F49">
-        <v>32.67</v>
+        <v>4.63</v>
       </c>
       <c r="G49" s="1">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="H49" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I49" s="2">
-        <v>20.19</v>
+        <v>29.77</v>
       </c>
       <c r="J49" s="2">
-        <v>0.0555</v>
+        <v>0.0409</v>
       </c>
       <c r="K49" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L49" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B50" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C50" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D50" t="s">
         <v>134</v>
       </c>
       <c r="E50">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="F50">
-        <v>3.08</v>
+        <v>1.31</v>
       </c>
       <c r="G50" s="1">
-        <v>0.629</v>
+        <v>0.68</v>
       </c>
       <c r="H50" t="s">
         <v>139</v>
       </c>
       <c r="I50" s="2">
-        <v>20.09</v>
+        <v>29.73</v>
       </c>
       <c r="J50" s="2">
-        <v>0.0553</v>
+        <v>0.0409</v>
       </c>
       <c r="K50" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L50" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B51" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C51" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D51" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E51">
-        <v>2.5</v>
+        <v>28.5</v>
       </c>
       <c r="F51">
-        <v>2.06</v>
+        <v>25.27</v>
       </c>
       <c r="G51" s="1">
-        <v>0.644</v>
+        <v>0.678</v>
       </c>
       <c r="H51" t="s">
         <v>139</v>
       </c>
       <c r="I51" s="2">
-        <v>20</v>
+        <v>29.46</v>
       </c>
       <c r="J51" s="2">
-        <v>0.0393</v>
+        <v>0.0405</v>
       </c>
       <c r="K51" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L51" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B52" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C52" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D52" t="s">
         <v>134</v>
       </c>
       <c r="E52">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="F52">
-        <v>5.92</v>
+        <v>1.32</v>
       </c>
       <c r="G52" s="1">
-        <v>0.626</v>
+        <v>0.677</v>
       </c>
       <c r="H52" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I52" s="2">
-        <v>19.54</v>
+        <v>29.33</v>
       </c>
       <c r="J52" s="2">
-        <v>0.0537</v>
+        <v>0.0403</v>
       </c>
       <c r="K52" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L52" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B53" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C53" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="D53" t="s">
         <v>134</v>
@@ -2863,139 +2866,139 @@
         <v>2.5</v>
       </c>
       <c r="F53">
-        <v>2.42</v>
+        <v>2.06</v>
       </c>
       <c r="G53" s="1">
-        <v>0.637</v>
+        <v>0.674</v>
       </c>
       <c r="H53" t="s">
         <v>139</v>
       </c>
       <c r="I53" s="2">
-        <v>19.13</v>
+        <v>28.58</v>
       </c>
       <c r="J53" s="2">
-        <v>0.0376</v>
+        <v>0.0393</v>
       </c>
       <c r="K53" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L53" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B54" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="C54" t="s">
         <v>116</v>
       </c>
       <c r="D54" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E54">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="F54">
-        <v>3.82</v>
+        <v>2.42</v>
       </c>
       <c r="G54" s="1">
-        <v>0.634</v>
+        <v>0.667</v>
       </c>
       <c r="H54" t="s">
         <v>139</v>
       </c>
       <c r="I54" s="2">
-        <v>18.69</v>
+        <v>27.33</v>
       </c>
       <c r="J54" s="2">
-        <v>0.0367</v>
+        <v>0.0376</v>
       </c>
       <c r="K54" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L54" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B55" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C55" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D55" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E55">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F55">
-        <v>3.05</v>
+        <v>3.82</v>
       </c>
       <c r="G55" s="1">
-        <v>0.633</v>
+        <v>0.664</v>
       </c>
       <c r="H55" t="s">
         <v>139</v>
       </c>
       <c r="I55" s="2">
-        <v>18.61</v>
+        <v>26.7</v>
       </c>
       <c r="J55" s="2">
-        <v>0.0366</v>
+        <v>0.0367</v>
       </c>
       <c r="K55" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L55" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="B56" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C56" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D56" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E56">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F56">
-        <v>2.26</v>
+        <v>3.05</v>
       </c>
       <c r="G56" s="1">
-        <v>0.621</v>
+        <v>0.663</v>
       </c>
       <c r="H56" t="s">
         <v>139</v>
       </c>
       <c r="I56" s="2">
-        <v>18.46</v>
+        <v>26.59</v>
       </c>
       <c r="J56" s="2">
-        <v>0.0508</v>
+        <v>0.0366</v>
       </c>
       <c r="K56" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L56" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -3018,22 +3021,22 @@
         <v>3.04</v>
       </c>
       <c r="G57" s="1">
-        <v>0.631</v>
+        <v>0.661</v>
       </c>
       <c r="H57" t="s">
         <v>139</v>
       </c>
       <c r="I57" s="2">
-        <v>18.37</v>
+        <v>26.24</v>
       </c>
       <c r="J57" s="2">
         <v>0.0361</v>
       </c>
       <c r="K57" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L57" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -3041,37 +3044,37 @@
         <v>67</v>
       </c>
       <c r="B58" t="s">
+        <v>130</v>
+      </c>
+      <c r="C58" t="s">
         <v>114</v>
-      </c>
-      <c r="C58" t="s">
-        <v>131</v>
       </c>
       <c r="D58" t="s">
         <v>134</v>
       </c>
       <c r="E58">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="F58">
-        <v>6.86</v>
+        <v>3.85</v>
       </c>
       <c r="G58" s="1">
-        <v>0.619</v>
+        <v>0.655</v>
       </c>
       <c r="H58" t="s">
         <v>139</v>
       </c>
       <c r="I58" s="2">
-        <v>18.09</v>
+        <v>25.11</v>
       </c>
       <c r="J58" s="2">
-        <v>0.0497</v>
+        <v>0.0345</v>
       </c>
       <c r="K58" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L58" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -3079,37 +3082,37 @@
         <v>68</v>
       </c>
       <c r="B59" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C59" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D59" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E59">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="F59">
-        <v>17.36</v>
+        <v>12.02</v>
       </c>
       <c r="G59" s="1">
-        <v>0.617</v>
+        <v>0.653</v>
       </c>
       <c r="H59" t="s">
         <v>139</v>
       </c>
       <c r="I59" s="2">
-        <v>17.82</v>
+        <v>24.62</v>
       </c>
       <c r="J59" s="2">
-        <v>0.049</v>
+        <v>0.0339</v>
       </c>
       <c r="K59" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L59" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3117,37 +3120,37 @@
         <v>69</v>
       </c>
       <c r="B60" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C60" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D60" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E60">
-        <v>7.5</v>
+        <v>19.5</v>
       </c>
       <c r="F60">
-        <v>6.91</v>
+        <v>22.13</v>
       </c>
       <c r="G60" s="1">
-        <v>0.616</v>
+        <v>0.652</v>
       </c>
       <c r="H60" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I60" s="2">
-        <v>17.64</v>
+        <v>24.53</v>
       </c>
       <c r="J60" s="2">
-        <v>0.0485</v>
+        <v>0.0337</v>
       </c>
       <c r="K60" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L60" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3155,37 +3158,37 @@
         <v>70</v>
       </c>
       <c r="B61" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C61" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D61" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E61">
         <v>4.5</v>
       </c>
       <c r="F61">
-        <v>3.85</v>
+        <v>5.54</v>
       </c>
       <c r="G61" s="1">
-        <v>0.625</v>
+        <v>0.649</v>
       </c>
       <c r="H61" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I61" s="2">
-        <v>17.58</v>
+        <v>23.86</v>
       </c>
       <c r="J61" s="2">
-        <v>0.0345</v>
+        <v>0.0328</v>
       </c>
       <c r="K61" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L61" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -3193,37 +3196,37 @@
         <v>71</v>
       </c>
       <c r="B62" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="C62" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="D62" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E62">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="F62">
-        <v>12.02</v>
+        <v>13.92</v>
       </c>
       <c r="G62" s="1">
-        <v>0.623</v>
+        <v>0.646</v>
       </c>
       <c r="H62" t="s">
         <v>139</v>
       </c>
       <c r="I62" s="2">
-        <v>17.24</v>
+        <v>23.36</v>
       </c>
       <c r="J62" s="2">
-        <v>0.0339</v>
+        <v>0.0321</v>
       </c>
       <c r="K62" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L62" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -3231,37 +3234,37 @@
         <v>72</v>
       </c>
       <c r="B63" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C63" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D63" t="s">
         <v>137</v>
       </c>
       <c r="E63">
-        <v>19.5</v>
+        <v>7.5</v>
       </c>
       <c r="F63">
-        <v>22.13</v>
+        <v>6.62</v>
       </c>
       <c r="G63" s="1">
-        <v>0.622</v>
+        <v>0.645</v>
       </c>
       <c r="H63" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I63" s="2">
-        <v>17.17</v>
+        <v>23.07</v>
       </c>
       <c r="J63" s="2">
-        <v>0.0337</v>
+        <v>0.0317</v>
       </c>
       <c r="K63" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L63" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -3269,124 +3272,124 @@
         <v>73</v>
       </c>
       <c r="B64" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C64" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D64" t="s">
         <v>135</v>
       </c>
       <c r="E64">
-        <v>4.5</v>
+        <v>21.5</v>
       </c>
       <c r="F64">
-        <v>5.54</v>
+        <v>18.42</v>
       </c>
       <c r="G64" s="1">
-        <v>0.619</v>
+        <v>0.643</v>
       </c>
       <c r="H64" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I64" s="2">
-        <v>16.7</v>
+        <v>22.68</v>
       </c>
       <c r="J64" s="2">
-        <v>0.0328</v>
+        <v>0.0312</v>
       </c>
       <c r="K64" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L64" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="B65" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="C65" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="D65" t="s">
         <v>137</v>
       </c>
       <c r="E65">
-        <v>15.5</v>
+        <v>8.5</v>
       </c>
       <c r="F65">
-        <v>18.39</v>
+        <v>7.69</v>
       </c>
       <c r="G65" s="1">
-        <v>0.611</v>
+        <v>0.636</v>
       </c>
       <c r="H65" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I65" s="2">
-        <v>16.57</v>
+        <v>21.41</v>
       </c>
       <c r="J65" s="2">
-        <v>0.0456</v>
+        <v>0.0294</v>
       </c>
       <c r="K65" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L65" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B66" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C66" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="D66" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E66">
-        <v>7.5</v>
+        <v>11.5</v>
       </c>
       <c r="F66">
-        <v>6.92</v>
+        <v>13.13</v>
       </c>
       <c r="G66" s="1">
-        <v>0.61</v>
+        <v>0.636</v>
       </c>
       <c r="H66" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I66" s="2">
-        <v>16.39</v>
+        <v>21.37</v>
       </c>
       <c r="J66" s="2">
-        <v>0.0451</v>
+        <v>0.0294</v>
       </c>
       <c r="K66" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L66" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="B67" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C67" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D67" t="s">
         <v>134</v>
@@ -3395,253 +3398,253 @@
         <v>2.5</v>
       </c>
       <c r="F67">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="G67" s="1">
-        <v>0.609</v>
+        <v>0.634</v>
       </c>
       <c r="H67" t="s">
         <v>139</v>
       </c>
       <c r="I67" s="2">
-        <v>16.36</v>
+        <v>20.97</v>
       </c>
       <c r="J67" s="2">
-        <v>0.045</v>
+        <v>0.0288</v>
       </c>
       <c r="K67" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L67" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B68" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C68" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D68" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E68">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="F68">
-        <v>13.92</v>
+        <v>14.9</v>
       </c>
       <c r="G68" s="1">
-        <v>0.616</v>
+        <v>0.632</v>
       </c>
       <c r="H68" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I68" s="2">
-        <v>16.35</v>
+        <v>20.74</v>
       </c>
       <c r="J68" s="2">
-        <v>0.0321</v>
+        <v>0.0285</v>
       </c>
       <c r="K68" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L68" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="B69" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C69" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D69" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E69">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="F69">
-        <v>1.35</v>
+        <v>8.67</v>
       </c>
       <c r="G69" s="1">
-        <v>0.609</v>
+        <v>0.629</v>
       </c>
       <c r="H69" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I69" s="2">
-        <v>16.19</v>
+        <v>20.12</v>
       </c>
       <c r="J69" s="2">
-        <v>0.0445</v>
+        <v>0.0277</v>
       </c>
       <c r="K69" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L69" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B70" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="C70" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D70" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E70">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="F70">
-        <v>6.62</v>
+        <v>2.18</v>
       </c>
       <c r="G70" s="1">
-        <v>0.615</v>
+        <v>0.628</v>
       </c>
       <c r="H70" t="s">
         <v>139</v>
       </c>
       <c r="I70" s="2">
-        <v>16.15</v>
+        <v>19.95</v>
       </c>
       <c r="J70" s="2">
-        <v>0.0317</v>
+        <v>0.0274</v>
       </c>
       <c r="K70" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L70" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B71" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C71" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="D71" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E71">
-        <v>4.5</v>
+        <v>17.5</v>
       </c>
       <c r="F71">
-        <v>4.5</v>
+        <v>15.25</v>
       </c>
       <c r="G71" s="1">
-        <v>0.607</v>
+        <v>0.627</v>
       </c>
       <c r="H71" t="s">
         <v>139</v>
       </c>
       <c r="I71" s="2">
-        <v>15.95</v>
+        <v>19.67</v>
       </c>
       <c r="J71" s="2">
-        <v>0.0439</v>
+        <v>0.027</v>
       </c>
       <c r="K71" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L71" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B72" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C72" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D72" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E72">
-        <v>21.5</v>
+        <v>5.5</v>
       </c>
       <c r="F72">
-        <v>18.42</v>
+        <v>6.68</v>
       </c>
       <c r="G72" s="1">
-        <v>0.613</v>
+        <v>0.626</v>
       </c>
       <c r="H72" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I72" s="2">
-        <v>15.87</v>
+        <v>19.56</v>
       </c>
       <c r="J72" s="2">
-        <v>0.0312</v>
+        <v>0.0269</v>
       </c>
       <c r="K72" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L72" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B73" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="C73" t="s">
         <v>116</v>
       </c>
       <c r="D73" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E73">
-        <v>8.5</v>
+        <v>19.5</v>
       </c>
       <c r="F73">
-        <v>7.69</v>
+        <v>22.69</v>
       </c>
       <c r="G73" s="1">
-        <v>0.606</v>
+        <v>0.625</v>
       </c>
       <c r="H73" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I73" s="2">
-        <v>14.98</v>
+        <v>19.34</v>
       </c>
       <c r="J73" s="2">
-        <v>0.0294</v>
+        <v>0.0266</v>
       </c>
       <c r="K73" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L73" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -3649,37 +3652,37 @@
         <v>81</v>
       </c>
       <c r="B74" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C74" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D74" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E74">
-        <v>11.5</v>
+        <v>3.5</v>
       </c>
       <c r="F74">
-        <v>13.13</v>
+        <v>4.31</v>
       </c>
       <c r="G74" s="1">
-        <v>0.606</v>
+        <v>0.624</v>
       </c>
       <c r="H74" t="s">
         <v>140</v>
       </c>
       <c r="I74" s="2">
-        <v>14.96</v>
+        <v>19.14</v>
       </c>
       <c r="J74" s="2">
-        <v>0.0294</v>
+        <v>0.0263</v>
       </c>
       <c r="K74" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L74" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -3690,110 +3693,110 @@
         <v>125</v>
       </c>
       <c r="C75" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D75" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E75">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="F75">
-        <v>2.35</v>
+        <v>4.03</v>
       </c>
       <c r="G75" s="1">
-        <v>0.604</v>
+        <v>0.623</v>
       </c>
       <c r="H75" t="s">
         <v>139</v>
       </c>
       <c r="I75" s="2">
-        <v>14.68</v>
+        <v>19</v>
       </c>
       <c r="J75" s="2">
-        <v>0.0288</v>
+        <v>0.0261</v>
       </c>
       <c r="K75" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L75" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="B76" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C76" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D76" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E76">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="F76">
-        <v>14.9</v>
+        <v>2.32</v>
       </c>
       <c r="G76" s="1">
-        <v>0.602</v>
+        <v>0.622</v>
       </c>
       <c r="H76" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I76" s="2">
-        <v>14.52</v>
+        <v>18.83</v>
       </c>
       <c r="J76" s="2">
-        <v>0.0285</v>
+        <v>0.0259</v>
       </c>
       <c r="K76" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L76" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="B77" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C77" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D77" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E77">
         <v>7.5</v>
       </c>
       <c r="F77">
-        <v>8.67</v>
+        <v>6.86</v>
       </c>
       <c r="G77" s="1">
-        <v>0.599</v>
+        <v>0.619</v>
       </c>
       <c r="H77" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I77" s="2">
-        <v>14.08</v>
+        <v>18.09</v>
       </c>
       <c r="J77" s="2">
-        <v>0.0277</v>
+        <v>0.0497</v>
       </c>
       <c r="K77" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L77" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -3801,37 +3804,37 @@
         <v>84</v>
       </c>
       <c r="B78" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C78" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D78" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E78">
-        <v>2.5</v>
+        <v>19.5</v>
       </c>
       <c r="F78">
-        <v>2.18</v>
+        <v>17.36</v>
       </c>
       <c r="G78" s="1">
-        <v>0.598</v>
+        <v>0.617</v>
       </c>
       <c r="H78" t="s">
         <v>139</v>
       </c>
       <c r="I78" s="2">
-        <v>13.97</v>
+        <v>17.82</v>
       </c>
       <c r="J78" s="2">
-        <v>0.0274</v>
+        <v>0.049</v>
       </c>
       <c r="K78" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L78" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -3839,276 +3842,276 @@
         <v>85</v>
       </c>
       <c r="B79" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C79" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D79" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E79">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="F79">
-        <v>13.07</v>
+        <v>6.91</v>
       </c>
       <c r="G79" s="1">
-        <v>0.596</v>
+        <v>0.616</v>
       </c>
       <c r="H79" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I79" s="2">
-        <v>13.79</v>
+        <v>17.64</v>
       </c>
       <c r="J79" s="2">
-        <v>0.0379</v>
+        <v>0.0485</v>
       </c>
       <c r="K79" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L79" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="B80" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="C80" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D80" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E80">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="F80">
-        <v>15.25</v>
+        <v>18.39</v>
       </c>
       <c r="G80" s="1">
-        <v>0.597</v>
+        <v>0.611</v>
       </c>
       <c r="H80" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I80" s="2">
-        <v>13.77</v>
+        <v>16.57</v>
       </c>
       <c r="J80" s="2">
-        <v>0.027</v>
+        <v>0.0456</v>
       </c>
       <c r="K80" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L80" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C81" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D81" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E81">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="F81">
-        <v>6.68</v>
+        <v>6.92</v>
       </c>
       <c r="G81" s="1">
-        <v>0.596</v>
+        <v>0.61</v>
       </c>
       <c r="H81" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I81" s="2">
-        <v>13.69</v>
+        <v>16.39</v>
       </c>
       <c r="J81" s="2">
-        <v>0.0269</v>
+        <v>0.0451</v>
       </c>
       <c r="K81" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L81" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B82" t="s">
+        <v>118</v>
+      </c>
+      <c r="C82" t="s">
         <v>129</v>
       </c>
-      <c r="C82" t="s">
-        <v>117</v>
-      </c>
       <c r="D82" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E82">
-        <v>19.5</v>
+        <v>2.5</v>
       </c>
       <c r="F82">
-        <v>22.69</v>
+        <v>2.25</v>
       </c>
       <c r="G82" s="1">
-        <v>0.595</v>
+        <v>0.609</v>
       </c>
       <c r="H82" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I82" s="2">
-        <v>13.54</v>
+        <v>16.36</v>
       </c>
       <c r="J82" s="2">
-        <v>0.0266</v>
+        <v>0.045</v>
       </c>
       <c r="K82" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L82" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B83" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C83" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D83" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E83">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="F83">
-        <v>4.31</v>
+        <v>1.35</v>
       </c>
       <c r="G83" s="1">
-        <v>0.594</v>
+        <v>0.609</v>
       </c>
       <c r="H83" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I83" s="2">
-        <v>13.4</v>
+        <v>16.19</v>
       </c>
       <c r="J83" s="2">
-        <v>0.0263</v>
+        <v>0.0445</v>
       </c>
       <c r="K83" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L83" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B84" t="s">
         <v>115</v>
       </c>
       <c r="C84" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D84" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E84">
         <v>4.5</v>
       </c>
       <c r="F84">
-        <v>4.03</v>
+        <v>4.5</v>
       </c>
       <c r="G84" s="1">
-        <v>0.593</v>
+        <v>0.607</v>
       </c>
       <c r="H84" t="s">
         <v>139</v>
       </c>
       <c r="I84" s="2">
-        <v>13.3</v>
+        <v>15.95</v>
       </c>
       <c r="J84" s="2">
-        <v>0.0261</v>
+        <v>0.0439</v>
       </c>
       <c r="K84" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L84" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="B85" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C85" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D85" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E85">
-        <v>2.5</v>
+        <v>12.5</v>
       </c>
       <c r="F85">
-        <v>2.32</v>
+        <v>13.07</v>
       </c>
       <c r="G85" s="1">
-        <v>0.592</v>
+        <v>0.596</v>
       </c>
       <c r="H85" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I85" s="2">
-        <v>13.18</v>
+        <v>13.79</v>
       </c>
       <c r="J85" s="2">
-        <v>0.0259</v>
+        <v>0.0379</v>
       </c>
       <c r="K85" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L85" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="B86" t="s">
         <v>118</v>
       </c>
       <c r="C86" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D86" t="s">
         <v>134</v>
@@ -4117,121 +4120,121 @@
         <v>3.5</v>
       </c>
       <c r="F86">
-        <v>3.12</v>
+        <v>4.33</v>
       </c>
       <c r="G86" s="1">
-        <v>0.589</v>
+        <v>0.591</v>
       </c>
       <c r="H86" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I86" s="2">
-        <v>12.78</v>
+        <v>12.74</v>
       </c>
       <c r="J86" s="2">
-        <v>0.0251</v>
+        <v>0.035</v>
       </c>
       <c r="K86" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L86" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="B87" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C87" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D87" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E87">
-        <v>3.5</v>
+        <v>12.5</v>
       </c>
       <c r="F87">
-        <v>4.33</v>
+        <v>13.86</v>
       </c>
       <c r="G87" s="1">
-        <v>0.591</v>
+        <v>0.588</v>
       </c>
       <c r="H87" t="s">
         <v>140</v>
       </c>
       <c r="I87" s="2">
-        <v>12.74</v>
+        <v>12.19</v>
       </c>
       <c r="J87" s="2">
-        <v>0.035</v>
+        <v>0.0335</v>
       </c>
       <c r="K87" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L87" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B88" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="C88" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="D88" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E88">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="F88">
-        <v>13.86</v>
+        <v>9.82</v>
       </c>
       <c r="G88" s="1">
-        <v>0.588</v>
+        <v>0.587</v>
       </c>
       <c r="H88" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I88" s="2">
-        <v>12.19</v>
+        <v>12.14</v>
       </c>
       <c r="J88" s="2">
-        <v>0.0335</v>
+        <v>0.0334</v>
       </c>
       <c r="K88" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L88" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="B89" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="C89" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D89" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E89">
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
       <c r="F89">
-        <v>9.82</v>
+        <v>8.07</v>
       </c>
       <c r="G89" s="1">
         <v>0.587</v>
@@ -4240,168 +4243,168 @@
         <v>139</v>
       </c>
       <c r="I89" s="2">
-        <v>12.14</v>
+        <v>12.03</v>
       </c>
       <c r="J89" s="2">
-        <v>0.0334</v>
+        <v>0.0331</v>
       </c>
       <c r="K89" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L89" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B90" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C90" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D90" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E90">
-        <v>20.5</v>
+        <v>3.5</v>
       </c>
       <c r="F90">
-        <v>23.08</v>
+        <v>3.6</v>
       </c>
       <c r="G90" s="1">
-        <v>0.584</v>
+        <v>0.582</v>
       </c>
       <c r="H90" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I90" s="2">
-        <v>12.05</v>
+        <v>11.03</v>
       </c>
       <c r="J90" s="2">
-        <v>0.0237</v>
+        <v>0.0303</v>
       </c>
       <c r="K90" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L90" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B91" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C91" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D91" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E91">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="F91">
-        <v>8.07</v>
+        <v>3.12</v>
       </c>
       <c r="G91" s="1">
-        <v>0.587</v>
+        <v>0.619</v>
       </c>
       <c r="H91" t="s">
         <v>139</v>
       </c>
       <c r="I91" s="2">
-        <v>12.03</v>
+        <v>18.25</v>
       </c>
       <c r="J91" s="2">
-        <v>0.0331</v>
+        <v>0.0251</v>
       </c>
       <c r="K91" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L91" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B92" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C92" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D92" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E92">
-        <v>1.5</v>
+        <v>20.5</v>
       </c>
       <c r="F92">
-        <v>1.45</v>
+        <v>23.08</v>
       </c>
       <c r="G92" s="1">
-        <v>0.581</v>
+        <v>0.614</v>
       </c>
       <c r="H92" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I92" s="2">
-        <v>11.71</v>
+        <v>17.21</v>
       </c>
       <c r="J92" s="2">
-        <v>0.023</v>
+        <v>0.0237</v>
       </c>
       <c r="K92" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L92" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B93" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C93" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D93" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E93">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="F93">
-        <v>3.6</v>
+        <v>1.45</v>
       </c>
       <c r="G93" s="1">
-        <v>0.582</v>
+        <v>0.611</v>
       </c>
       <c r="H93" t="s">
         <v>139</v>
       </c>
       <c r="I93" s="2">
-        <v>11.03</v>
+        <v>16.73</v>
       </c>
       <c r="J93" s="2">
-        <v>0.0303</v>
+        <v>0.023</v>
       </c>
       <c r="K93" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L93" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="94" spans="1:12">
@@ -4409,7 +4412,7 @@
         <v>94</v>
       </c>
       <c r="B94" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C94" t="s">
         <v>133</v>
@@ -4424,22 +4427,22 @@
         <v>9.59</v>
       </c>
       <c r="G94" s="1">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="H94" t="s">
         <v>139</v>
       </c>
       <c r="I94" s="2">
-        <v>11.51</v>
+        <v>16.44</v>
       </c>
       <c r="J94" s="2">
         <v>0.0226</v>
       </c>
       <c r="K94" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L94" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -4447,10 +4450,10 @@
         <v>95</v>
       </c>
       <c r="B95" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C95" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D95" t="s">
         <v>134</v>
@@ -4462,22 +4465,22 @@
         <v>3.21</v>
       </c>
       <c r="G95" s="1">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="H95" t="s">
         <v>140</v>
       </c>
       <c r="I95" s="2">
-        <v>11.47</v>
+        <v>16.38</v>
       </c>
       <c r="J95" s="2">
         <v>0.0225</v>
       </c>
       <c r="K95" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L95" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -4500,136 +4503,136 @@
         <v>5.07</v>
       </c>
       <c r="G96" s="1">
-        <v>0.576</v>
+        <v>0.606</v>
       </c>
       <c r="H96" t="s">
         <v>139</v>
       </c>
       <c r="I96" s="2">
-        <v>11.02</v>
+        <v>15.74</v>
       </c>
       <c r="J96" s="2">
         <v>0.0216</v>
       </c>
       <c r="K96" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L96" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B97" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C97" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="D97" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E97">
-        <v>13.5</v>
+        <v>4.5</v>
       </c>
       <c r="F97">
-        <v>12.99</v>
+        <v>4.15</v>
       </c>
       <c r="G97" s="1">
-        <v>0.578</v>
+        <v>0.599</v>
       </c>
       <c r="H97" t="s">
         <v>139</v>
       </c>
       <c r="I97" s="2">
-        <v>10.33</v>
+        <v>14.45</v>
       </c>
       <c r="J97" s="2">
-        <v>0.0284</v>
+        <v>0.0199</v>
       </c>
       <c r="K97" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L97" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B98" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C98" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D98" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E98">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="F98">
-        <v>1.5</v>
+        <v>12.77</v>
       </c>
       <c r="G98" s="1">
-        <v>0.577</v>
+        <v>0.594</v>
       </c>
       <c r="H98" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I98" s="2">
-        <v>10.23</v>
+        <v>13.43</v>
       </c>
       <c r="J98" s="2">
-        <v>0.0281</v>
+        <v>0.0185</v>
       </c>
       <c r="K98" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L98" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C99" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D99" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E99">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="F99">
-        <v>4.15</v>
+        <v>14.21</v>
       </c>
       <c r="G99" s="1">
-        <v>0.569</v>
+        <v>0.589</v>
       </c>
       <c r="H99" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I99" s="2">
-        <v>10.11</v>
+        <v>12.54</v>
       </c>
       <c r="J99" s="2">
-        <v>0.0199</v>
+        <v>0.0172</v>
       </c>
       <c r="K99" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L99" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="100" spans="1:12">
@@ -4637,504 +4640,504 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C100" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D100" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E100">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="F100">
-        <v>2.99</v>
+        <v>5.23</v>
       </c>
       <c r="G100" s="1">
-        <v>0.575</v>
+        <v>0.586</v>
       </c>
       <c r="H100" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I100" s="2">
-        <v>9.69</v>
+        <v>11.94</v>
       </c>
       <c r="J100" s="2">
-        <v>0.0267</v>
+        <v>0.0164</v>
       </c>
       <c r="K100" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L100" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C101" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D101" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E101">
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
       <c r="F101">
-        <v>12.77</v>
+        <v>8.07</v>
       </c>
       <c r="G101" s="1">
-        <v>0.5639999999999999</v>
+        <v>0.585</v>
       </c>
       <c r="H101" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I101" s="2">
-        <v>9.4</v>
+        <v>11.7</v>
       </c>
       <c r="J101" s="2">
-        <v>0.0185</v>
+        <v>0.0161</v>
       </c>
       <c r="K101" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L101" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C102" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D102" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E102">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="F102">
-        <v>1.91</v>
+        <v>10.89</v>
       </c>
       <c r="G102" s="1">
-        <v>0.57</v>
+        <v>0.578</v>
       </c>
       <c r="H102" t="s">
         <v>140</v>
       </c>
       <c r="I102" s="2">
-        <v>8.800000000000001</v>
+        <v>10.38</v>
       </c>
       <c r="J102" s="2">
-        <v>0.0242</v>
+        <v>0.0143</v>
       </c>
       <c r="K102" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L102" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C103" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D103" t="s">
         <v>137</v>
       </c>
       <c r="E103">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="F103">
-        <v>14.21</v>
+        <v>12.99</v>
       </c>
       <c r="G103" s="1">
-        <v>0.5590000000000001</v>
+        <v>0.578</v>
       </c>
       <c r="H103" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I103" s="2">
-        <v>8.779999999999999</v>
+        <v>10.33</v>
       </c>
       <c r="J103" s="2">
-        <v>0.0172</v>
+        <v>0.0284</v>
       </c>
       <c r="K103" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L103" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C104" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D104" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E104">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="F104">
-        <v>5.23</v>
+        <v>1.5</v>
       </c>
       <c r="G104" s="1">
-        <v>0.556</v>
+        <v>0.577</v>
       </c>
       <c r="H104" t="s">
         <v>139</v>
       </c>
       <c r="I104" s="2">
-        <v>8.359999999999999</v>
+        <v>10.23</v>
       </c>
       <c r="J104" s="2">
-        <v>0.0164</v>
+        <v>0.0281</v>
       </c>
       <c r="K104" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L104" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B105" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C105" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D105" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E105">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="F105">
-        <v>8.07</v>
+        <v>2.99</v>
       </c>
       <c r="G105" s="1">
-        <v>0.555</v>
+        <v>0.575</v>
       </c>
       <c r="H105" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I105" s="2">
-        <v>8.19</v>
+        <v>9.69</v>
       </c>
       <c r="J105" s="2">
-        <v>0.0161</v>
+        <v>0.0267</v>
       </c>
       <c r="K105" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L105" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B106" t="s">
         <v>116</v>
       </c>
       <c r="C106" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="D106" t="s">
         <v>137</v>
       </c>
       <c r="E106">
-        <v>15.5</v>
+        <v>5.5</v>
       </c>
       <c r="F106">
-        <v>16.49</v>
+        <v>5.28</v>
       </c>
       <c r="G106" s="1">
-        <v>0.5659999999999999</v>
+        <v>0.574</v>
       </c>
       <c r="H106" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I106" s="2">
-        <v>8.02</v>
+        <v>9.49</v>
       </c>
       <c r="J106" s="2">
-        <v>0.0221</v>
+        <v>0.0131</v>
       </c>
       <c r="K106" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L106" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="B107" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C107" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D107" t="s">
         <v>134</v>
       </c>
       <c r="E107">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="F107">
-        <v>3.53</v>
+        <v>1.47</v>
       </c>
       <c r="G107" s="1">
-        <v>0.5629999999999999</v>
+        <v>0.572</v>
       </c>
       <c r="H107" t="s">
         <v>139</v>
       </c>
       <c r="I107" s="2">
-        <v>7.43</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="J107" s="2">
-        <v>0.0204</v>
+        <v>0.0127</v>
       </c>
       <c r="K107" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L107" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="108" spans="1:12">
       <c r="A108" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="B108" t="s">
+        <v>121</v>
+      </c>
+      <c r="C108" t="s">
         <v>123</v>
-      </c>
-      <c r="C108" t="s">
-        <v>120</v>
       </c>
       <c r="D108" t="s">
         <v>136</v>
       </c>
       <c r="E108">
-        <v>9.5</v>
+        <v>19.5</v>
       </c>
       <c r="F108">
-        <v>10.89</v>
+        <v>20.86</v>
       </c>
       <c r="G108" s="1">
-        <v>0.548</v>
+        <v>0.571</v>
       </c>
       <c r="H108" t="s">
         <v>140</v>
       </c>
       <c r="I108" s="2">
-        <v>7.26</v>
+        <v>8.93</v>
       </c>
       <c r="J108" s="2">
-        <v>0.0143</v>
+        <v>0.0123</v>
       </c>
       <c r="K108" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L108" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="109" spans="1:12">
       <c r="A109" t="s">
-        <v>39</v>
+        <v>105</v>
       </c>
       <c r="B109" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C109" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D109" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E109">
-        <v>28.5</v>
+        <v>2.5</v>
       </c>
       <c r="F109">
-        <v>30.37</v>
+        <v>2.4</v>
       </c>
       <c r="G109" s="1">
-        <v>0.5620000000000001</v>
+        <v>0.571</v>
       </c>
       <c r="H109" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I109" s="2">
-        <v>7.23</v>
+        <v>8.92</v>
       </c>
       <c r="J109" s="2">
-        <v>0.0199</v>
+        <v>0.0123</v>
       </c>
       <c r="K109" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L109" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="110" spans="1:12">
       <c r="A110" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="B110" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C110" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D110" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E110">
-        <v>13.5</v>
+        <v>1.5</v>
       </c>
       <c r="F110">
-        <v>12.24</v>
+        <v>1.91</v>
       </c>
       <c r="G110" s="1">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H110" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I110" s="2">
-        <v>6.84</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J110" s="2">
-        <v>0.0188</v>
+        <v>0.0242</v>
       </c>
       <c r="K110" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L110" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="111" spans="1:12">
       <c r="A111" t="s">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="B111" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="C111" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="D111" t="s">
         <v>135</v>
       </c>
       <c r="E111">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="F111">
-        <v>5.28</v>
+        <v>13.84</v>
       </c>
       <c r="G111" s="1">
-        <v>0.544</v>
+        <v>0.569</v>
       </c>
       <c r="H111" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I111" s="2">
-        <v>6.64</v>
+        <v>8.69</v>
       </c>
       <c r="J111" s="2">
-        <v>0.0131</v>
+        <v>0.0119</v>
       </c>
       <c r="K111" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L111" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="112" spans="1:12">
       <c r="A112" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B112" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C112" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D112" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E112">
-        <v>2.5</v>
+        <v>15.5</v>
       </c>
       <c r="F112">
-        <v>2.92</v>
+        <v>16.49</v>
       </c>
       <c r="G112" s="1">
-        <v>0.5580000000000001</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H112" t="s">
         <v>140</v>
       </c>
       <c r="I112" s="2">
-        <v>6.5</v>
+        <v>8.02</v>
       </c>
       <c r="J112" s="2">
-        <v>0.0179</v>
+        <v>0.0221</v>
       </c>
       <c r="K112" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L112" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="113" spans="1:12">
       <c r="A113" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B113" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C113" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D113" t="s">
         <v>134</v>
@@ -5143,1217 +5146,1217 @@
         <v>1.5</v>
       </c>
       <c r="F113">
-        <v>1.47</v>
+        <v>2.16</v>
       </c>
       <c r="G113" s="1">
-        <v>0.542</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H113" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I113" s="2">
-        <v>6.45</v>
+        <v>7.69</v>
       </c>
       <c r="J113" s="2">
-        <v>0.0127</v>
+        <v>0.0106</v>
       </c>
       <c r="K113" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L113" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="114" spans="1:12">
       <c r="A114" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B114" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C114" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D114" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E114">
-        <v>19.5</v>
+        <v>3.5</v>
       </c>
       <c r="F114">
-        <v>20.86</v>
+        <v>3.53</v>
       </c>
       <c r="G114" s="1">
-        <v>0.541</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H114" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I114" s="2">
-        <v>6.25</v>
+        <v>7.43</v>
       </c>
       <c r="J114" s="2">
-        <v>0.0123</v>
+        <v>0.0204</v>
       </c>
       <c r="K114" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L114" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="115" spans="1:12">
       <c r="A115" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B115" t="s">
         <v>116</v>
       </c>
       <c r="C115" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="D115" t="s">
         <v>135</v>
       </c>
       <c r="E115">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="F115">
-        <v>2.4</v>
+        <v>10.25</v>
       </c>
       <c r="G115" s="1">
-        <v>0.541</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H115" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I115" s="2">
-        <v>6.24</v>
+        <v>7.42</v>
       </c>
       <c r="J115" s="2">
-        <v>0.0123</v>
+        <v>0.0102</v>
       </c>
       <c r="K115" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L115" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="116" spans="1:12">
       <c r="A116" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="C116" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D116" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E116">
-        <v>14.5</v>
+        <v>28.5</v>
       </c>
       <c r="F116">
-        <v>15.95</v>
+        <v>30.37</v>
       </c>
       <c r="G116" s="1">
-        <v>0.552</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="H116" t="s">
         <v>140</v>
       </c>
       <c r="I116" s="2">
-        <v>5.31</v>
+        <v>7.23</v>
       </c>
       <c r="J116" s="2">
-        <v>0.0146</v>
+        <v>0.0199</v>
       </c>
       <c r="K116" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L116" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="117" spans="1:12">
       <c r="A117" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="B117" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C117" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D117" t="s">
         <v>136</v>
       </c>
       <c r="E117">
-        <v>7.5</v>
+        <v>13.5</v>
       </c>
       <c r="F117">
-        <v>8.710000000000001</v>
+        <v>12.24</v>
       </c>
       <c r="G117" s="1">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H117" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I117" s="2">
-        <v>4.98</v>
+        <v>6.84</v>
       </c>
       <c r="J117" s="2">
-        <v>0.0137</v>
+        <v>0.0188</v>
       </c>
       <c r="K117" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L117" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="118" spans="1:12">
       <c r="A118" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="B118" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C118" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="D118" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E118">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="F118">
-        <v>7.87</v>
+        <v>2.92</v>
       </c>
       <c r="G118" s="1">
-        <v>0.547</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H118" t="s">
         <v>140</v>
       </c>
       <c r="I118" s="2">
-        <v>4.42</v>
+        <v>6.5</v>
       </c>
       <c r="J118" s="2">
-        <v>0.0121</v>
+        <v>0.0179</v>
       </c>
       <c r="K118" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L118" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="119" spans="1:12">
       <c r="A119" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="B119" t="s">
         <v>119</v>
       </c>
       <c r="C119" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D119" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E119">
-        <v>18.5</v>
+        <v>6.5</v>
       </c>
       <c r="F119">
-        <v>19.5</v>
+        <v>7.05</v>
       </c>
       <c r="G119" s="1">
-        <v>0.547</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H119" t="s">
         <v>140</v>
       </c>
       <c r="I119" s="2">
-        <v>4.37</v>
+        <v>6.39</v>
       </c>
       <c r="J119" s="2">
-        <v>0.012</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="K119" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L119" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="120" spans="1:12">
       <c r="A120" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="B120" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C120" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D120" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E120">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="F120">
-        <v>1.83</v>
+        <v>10.26</v>
       </c>
       <c r="G120" s="1">
-        <v>0.546</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H120" t="s">
         <v>140</v>
       </c>
       <c r="I120" s="2">
-        <v>4.15</v>
+        <v>6.37</v>
       </c>
       <c r="J120" s="2">
-        <v>0.0114</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="K120" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L120" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="121" spans="1:12">
       <c r="A121" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B121" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C121" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D121" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E121">
         <v>12.5</v>
       </c>
       <c r="F121">
-        <v>13.84</v>
+        <v>13.6</v>
       </c>
       <c r="G121" s="1">
-        <v>0.539</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H121" t="s">
         <v>140</v>
       </c>
       <c r="I121" s="2">
-        <v>6.08</v>
+        <v>6.32</v>
       </c>
       <c r="J121" s="2">
-        <v>0.0119</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="K121" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L121" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="122" spans="1:12">
       <c r="A122" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="B122" t="s">
+        <v>124</v>
+      </c>
+      <c r="C122" t="s">
         <v>120</v>
       </c>
-      <c r="C122" t="s">
-        <v>123</v>
-      </c>
       <c r="D122" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E122">
-        <v>1.5</v>
+        <v>12.5</v>
       </c>
       <c r="F122">
-        <v>2.16</v>
+        <v>13.21</v>
       </c>
       <c r="G122" s="1">
-        <v>0.534</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H122" t="s">
         <v>140</v>
       </c>
       <c r="I122" s="2">
-        <v>5.38</v>
+        <v>6.25</v>
       </c>
       <c r="J122" s="2">
-        <v>0.0106</v>
+        <v>0.0086</v>
       </c>
       <c r="K122" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L122" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="123" spans="1:12">
       <c r="A123" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B123" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C123" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D123" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E123">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="F123">
-        <v>10.25</v>
+        <v>1.63</v>
       </c>
       <c r="G123" s="1">
-        <v>0.533</v>
+        <v>0.556</v>
       </c>
       <c r="H123" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I123" s="2">
-        <v>5.2</v>
+        <v>6.14</v>
       </c>
       <c r="J123" s="2">
-        <v>0.0102</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="K123" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L123" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="124" spans="1:12">
       <c r="A124" t="s">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="B124" t="s">
         <v>120</v>
       </c>
       <c r="C124" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D124" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E124">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="F124">
-        <v>7.05</v>
+        <v>3.41</v>
       </c>
       <c r="G124" s="1">
-        <v>0.527</v>
+        <v>0.555</v>
       </c>
       <c r="H124" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I124" s="2">
-        <v>4.47</v>
+        <v>5.98</v>
       </c>
       <c r="J124" s="2">
-        <v>0.008800000000000001</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="K124" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L124" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="125" spans="1:12">
       <c r="A125" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B125" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C125" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D125" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E125">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="F125">
-        <v>10.26</v>
+        <v>1.86</v>
       </c>
       <c r="G125" s="1">
-        <v>0.527</v>
+        <v>0.554</v>
       </c>
       <c r="H125" t="s">
         <v>140</v>
       </c>
       <c r="I125" s="2">
-        <v>4.46</v>
+        <v>5.75</v>
       </c>
       <c r="J125" s="2">
-        <v>0.008800000000000001</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="K125" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L125" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="126" spans="1:12">
       <c r="A126" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="B126" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="C126" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D126" t="s">
         <v>136</v>
       </c>
       <c r="E126">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="F126">
-        <v>13.6</v>
+        <v>15.95</v>
       </c>
       <c r="G126" s="1">
-        <v>0.527</v>
+        <v>0.552</v>
       </c>
       <c r="H126" t="s">
         <v>140</v>
       </c>
       <c r="I126" s="2">
-        <v>4.42</v>
+        <v>5.31</v>
       </c>
       <c r="J126" s="2">
-        <v>0.008699999999999999</v>
+        <v>0.0146</v>
       </c>
       <c r="K126" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L126" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="127" spans="1:12">
       <c r="A127" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="B127" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C127" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D127" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E127">
-        <v>12.5</v>
+        <v>1.5</v>
       </c>
       <c r="F127">
-        <v>13.21</v>
+        <v>1.85</v>
       </c>
       <c r="G127" s="1">
-        <v>0.527</v>
+        <v>0.55</v>
       </c>
       <c r="H127" t="s">
         <v>140</v>
       </c>
       <c r="I127" s="2">
-        <v>4.37</v>
+        <v>5.09</v>
       </c>
       <c r="J127" s="2">
-        <v>0.0086</v>
+        <v>0.007</v>
       </c>
       <c r="K127" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L127" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="128" spans="1:12">
       <c r="A128" t="s">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="B128" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C128" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D128" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E128">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="F128">
-        <v>1.63</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G128" s="1">
-        <v>0.526</v>
+        <v>0.55</v>
       </c>
       <c r="H128" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I128" s="2">
-        <v>4.3</v>
+        <v>4.98</v>
       </c>
       <c r="J128" s="2">
-        <v>0.008399999999999999</v>
+        <v>0.0137</v>
       </c>
       <c r="K128" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L128" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="129" spans="1:12">
       <c r="A129" t="s">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="B129" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C129" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D129" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E129">
         <v>3.5</v>
       </c>
       <c r="F129">
-        <v>3.41</v>
+        <v>3.91</v>
       </c>
       <c r="G129" s="1">
-        <v>0.525</v>
+        <v>0.549</v>
       </c>
       <c r="H129" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I129" s="2">
-        <v>4.19</v>
+        <v>4.84</v>
       </c>
       <c r="J129" s="2">
-        <v>0.008200000000000001</v>
+        <v>0.0066</v>
       </c>
       <c r="K129" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L129" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="130" spans="1:12">
       <c r="A130" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C130" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D130" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E130">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="F130">
-        <v>1.86</v>
+        <v>7.87</v>
       </c>
       <c r="G130" s="1">
-        <v>0.524</v>
+        <v>0.547</v>
       </c>
       <c r="H130" t="s">
         <v>140</v>
       </c>
       <c r="I130" s="2">
-        <v>4.02</v>
+        <v>4.42</v>
       </c>
       <c r="J130" s="2">
-        <v>0.007900000000000001</v>
+        <v>0.0121</v>
       </c>
       <c r="K130" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L130" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="131" spans="1:12">
       <c r="A131" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="B131" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C131" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D131" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E131">
         <v>18.5</v>
       </c>
       <c r="F131">
-        <v>18.96</v>
+        <v>19.5</v>
       </c>
       <c r="G131" s="1">
-        <v>0.545</v>
+        <v>0.547</v>
       </c>
       <c r="H131" t="s">
         <v>140</v>
       </c>
       <c r="I131" s="2">
-        <v>3.99</v>
+        <v>4.37</v>
       </c>
       <c r="J131" s="2">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="K131" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L131" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="132" spans="1:12">
       <c r="A132" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="B132" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C132" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D132" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E132">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="F132">
-        <v>5.42</v>
+        <v>1.83</v>
       </c>
       <c r="G132" s="1">
-        <v>0.545</v>
+        <v>0.546</v>
       </c>
       <c r="H132" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I132" s="2">
-        <v>3.95</v>
+        <v>4.15</v>
       </c>
       <c r="J132" s="2">
-        <v>0.0109</v>
+        <v>0.0114</v>
       </c>
       <c r="K132" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L132" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="133" spans="1:12">
       <c r="A133" t="s">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="B133" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C133" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D133" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E133">
-        <v>1.5</v>
+        <v>18.5</v>
       </c>
       <c r="F133">
-        <v>1.82</v>
+        <v>18.96</v>
       </c>
       <c r="G133" s="1">
-        <v>0.544</v>
+        <v>0.545</v>
       </c>
       <c r="H133" t="s">
         <v>140</v>
       </c>
       <c r="I133" s="2">
-        <v>3.78</v>
+        <v>3.99</v>
       </c>
       <c r="J133" s="2">
-        <v>0.0104</v>
+        <v>0.011</v>
       </c>
       <c r="K133" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L133" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="134" spans="1:12">
       <c r="A134" t="s">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="B134" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C134" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="D134" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E134">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="F134">
-        <v>1.85</v>
+        <v>5.42</v>
       </c>
       <c r="G134" s="1">
-        <v>0.52</v>
+        <v>0.545</v>
       </c>
       <c r="H134" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I134" s="2">
-        <v>3.56</v>
+        <v>3.95</v>
       </c>
       <c r="J134" s="2">
-        <v>0.007</v>
+        <v>0.0109</v>
       </c>
       <c r="K134" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L134" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="135" spans="1:12">
       <c r="A135" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="B135" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C135" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D135" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E135">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="F135">
-        <v>3.91</v>
+        <v>1.82</v>
       </c>
       <c r="G135" s="1">
-        <v>0.519</v>
+        <v>0.544</v>
       </c>
       <c r="H135" t="s">
         <v>140</v>
       </c>
       <c r="I135" s="2">
-        <v>3.38</v>
+        <v>3.78</v>
       </c>
       <c r="J135" s="2">
-        <v>0.0066</v>
+        <v>0.0104</v>
       </c>
       <c r="K135" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L135" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="136" spans="1:12">
       <c r="A136" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="B136" t="s">
+        <v>130</v>
+      </c>
+      <c r="C136" t="s">
         <v>114</v>
       </c>
-      <c r="C136" t="s">
-        <v>131</v>
-      </c>
       <c r="D136" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E136">
-        <v>11.5</v>
+        <v>9.5</v>
       </c>
       <c r="F136">
-        <v>12.08</v>
+        <v>9.92</v>
       </c>
       <c r="G136" s="1">
-        <v>0.54</v>
+        <v>0.543</v>
       </c>
       <c r="H136" t="s">
         <v>140</v>
       </c>
       <c r="I136" s="2">
-        <v>3.13</v>
+        <v>3.59</v>
       </c>
       <c r="J136" s="2">
-        <v>0.0086</v>
+        <v>0.0049</v>
       </c>
       <c r="K136" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L136" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="137" spans="1:12">
       <c r="A137" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="B137" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="C137" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D137" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E137">
-        <v>32.5</v>
+        <v>11.5</v>
       </c>
       <c r="F137">
-        <v>31.81</v>
+        <v>12.08</v>
       </c>
       <c r="G137" s="1">
-        <v>0.539</v>
+        <v>0.54</v>
       </c>
       <c r="H137" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I137" s="2">
-        <v>2.96</v>
+        <v>3.13</v>
       </c>
       <c r="J137" s="2">
-        <v>0.0081</v>
+        <v>0.0086</v>
       </c>
       <c r="K137" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L137" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="138" spans="1:12">
       <c r="A138" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B138" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C138" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D138" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E138">
-        <v>9.5</v>
+        <v>32.5</v>
       </c>
       <c r="F138">
-        <v>9.92</v>
+        <v>31.81</v>
       </c>
       <c r="G138" s="1">
-        <v>0.513</v>
+        <v>0.539</v>
       </c>
       <c r="H138" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I138" s="2">
-        <v>2.52</v>
+        <v>2.96</v>
       </c>
       <c r="J138" s="2">
-        <v>0.0049</v>
+        <v>0.0081</v>
       </c>
       <c r="K138" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L138" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="139" spans="1:12">
       <c r="A139" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="B139" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="C139" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="D139" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E139">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="F139">
-        <v>7.86</v>
+        <v>2.83</v>
       </c>
       <c r="G139" s="1">
-        <v>0.537</v>
+        <v>0.538</v>
       </c>
       <c r="H139" t="s">
         <v>140</v>
       </c>
       <c r="I139" s="2">
-        <v>2.48</v>
+        <v>2.77</v>
       </c>
       <c r="J139" s="2">
-        <v>0.0068</v>
+        <v>0.0038</v>
       </c>
       <c r="K139" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L139" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="140" spans="1:12">
       <c r="A140" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="B140" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C140" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="D140" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E140">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="F140">
-        <v>2.83</v>
+        <v>7.86</v>
       </c>
       <c r="G140" s="1">
-        <v>0.508</v>
+        <v>0.537</v>
       </c>
       <c r="H140" t="s">
         <v>140</v>
       </c>
       <c r="I140" s="2">
-        <v>1.94</v>
+        <v>2.48</v>
       </c>
       <c r="J140" s="2">
-        <v>0.0038</v>
+        <v>0.0068</v>
       </c>
       <c r="K140" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L140" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="141" spans="1:12">
       <c r="A141" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="B141" t="s">
+        <v>128</v>
+      </c>
+      <c r="C141" t="s">
         <v>116</v>
-      </c>
-      <c r="C141" t="s">
-        <v>115</v>
       </c>
       <c r="D141" t="s">
         <v>135</v>
       </c>
       <c r="E141">
-        <v>5.5</v>
+        <v>18.5</v>
       </c>
       <c r="F141">
-        <v>5.86</v>
+        <v>17.8</v>
       </c>
       <c r="G141" s="1">
-        <v>0.532</v>
+        <v>0.534</v>
       </c>
       <c r="H141" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I141" s="2">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="J141" s="2">
-        <v>0.0044</v>
+        <v>0.0028</v>
       </c>
       <c r="K141" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L141" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="142" spans="1:12">
       <c r="A142" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="B142" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C142" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="D142" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E142">
-        <v>18.5</v>
+        <v>7.5</v>
       </c>
       <c r="F142">
-        <v>17.8</v>
+        <v>7.95</v>
       </c>
       <c r="G142" s="1">
-        <v>0.504</v>
+        <v>0.533</v>
       </c>
       <c r="H142" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I142" s="2">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="J142" s="2">
-        <v>0.0028</v>
+        <v>0.0023</v>
       </c>
       <c r="K142" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L142" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="143" spans="1:12">
       <c r="A143" t="s">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="B143" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C143" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D143" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E143">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="F143">
-        <v>3.53</v>
+        <v>5.86</v>
       </c>
       <c r="G143" s="1">
-        <v>0.531</v>
+        <v>0.532</v>
       </c>
       <c r="H143" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I143" s="2">
-        <v>1.31</v>
+        <v>1.59</v>
       </c>
       <c r="J143" s="2">
-        <v>0.0036</v>
+        <v>0.0044</v>
       </c>
       <c r="K143" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L143" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="144" spans="1:12">
       <c r="A144" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="B144" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C144" t="s">
         <v>133</v>
       </c>
       <c r="D144" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E144">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="F144">
-        <v>7.95</v>
+        <v>3.53</v>
       </c>
       <c r="G144" s="1">
-        <v>0.503</v>
+        <v>0.531</v>
       </c>
       <c r="H144" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I144" s="2">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="J144" s="2">
-        <v>0.0023</v>
+        <v>0.0036</v>
       </c>
       <c r="K144" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L144" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="145" spans="1:12">
       <c r="A145" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B145" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C145" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D145" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E145">
         <v>22.5</v>
@@ -6362,36 +6365,36 @@
         <v>23.35</v>
       </c>
       <c r="G145" s="1">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="H145" t="s">
         <v>140</v>
       </c>
       <c r="I145" s="2">
-        <v>0.83</v>
+        <v>1.19</v>
       </c>
       <c r="J145" s="2">
         <v>0.0016</v>
       </c>
       <c r="K145" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L145" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="146" spans="1:12">
       <c r="A146" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B146" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C146" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D146" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E146">
         <v>13.5</v>
@@ -6412,10 +6415,10 @@
         <v>0.0015</v>
       </c>
       <c r="K146" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L146" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="147" spans="1:12">
@@ -6450,21 +6453,21 @@
         <v>0.0014</v>
       </c>
       <c r="K147" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L147" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="148" spans="1:12">
       <c r="A148" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B148" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C148" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D148" t="s">
         <v>134</v>
@@ -6488,24 +6491,24 @@
         <v>0.0011</v>
       </c>
       <c r="K148" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L148" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="149" spans="1:12">
       <c r="A149" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="B149" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C149" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D149" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E149">
         <v>29.5</v>
@@ -6526,10 +6529,10 @@
         <v>0.0009</v>
       </c>
       <c r="K149" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L149" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="150" spans="1:12">
@@ -6537,13 +6540,13 @@
         <v>113</v>
       </c>
       <c r="B150" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C150" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D150" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E150">
         <v>3.5</v>
@@ -6564,24 +6567,24 @@
         <v>0.0009</v>
       </c>
       <c r="K150" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L150" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="151" spans="1:12">
       <c r="A151" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B151" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C151" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D151" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E151">
         <v>9.5</v>
@@ -6602,10 +6605,10 @@
         <v>0.0005999999999999999</v>
       </c>
       <c r="K151" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L151" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="152" spans="1:12">
@@ -6613,13 +6616,13 @@
         <v>113</v>
       </c>
       <c r="B152" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C152" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D152" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E152">
         <v>10.5</v>
@@ -6640,24 +6643,24 @@
         <v>0.0002</v>
       </c>
       <c r="K152" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L152" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="153" spans="1:12">
       <c r="A153" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B153" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C153" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D153" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E153">
         <v>9.5</v>
@@ -6666,36 +6669,36 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G153" s="1">
-        <v>0.492</v>
+        <v>0.522</v>
       </c>
       <c r="H153" t="s">
         <v>140</v>
       </c>
       <c r="I153" s="2">
-        <v>-0.19</v>
+        <v>-0.27</v>
       </c>
       <c r="J153" s="2">
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L153" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="154" spans="1:12">
       <c r="A154" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B154" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C154" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D154" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E154">
         <v>11.5</v>
@@ -6704,98 +6707,98 @@
         <v>11.05</v>
       </c>
       <c r="G154" s="1">
-        <v>0.492</v>
+        <v>0.522</v>
       </c>
       <c r="H154" t="s">
         <v>139</v>
       </c>
       <c r="I154" s="2">
-        <v>-0.3</v>
+        <v>-0.43</v>
       </c>
       <c r="J154" s="2">
         <v>0</v>
       </c>
       <c r="K154" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L154" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="155" spans="1:12">
       <c r="A155" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B155" t="s">
+        <v>121</v>
+      </c>
+      <c r="C155" t="s">
         <v>123</v>
       </c>
-      <c r="C155" t="s">
-        <v>120</v>
-      </c>
       <c r="D155" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E155">
-        <v>2.5</v>
+        <v>17.5</v>
       </c>
       <c r="F155">
-        <v>2.69</v>
+        <v>17.87</v>
       </c>
       <c r="G155" s="1">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
       <c r="H155" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I155" s="2">
-        <v>-0.57</v>
+        <v>-0.79</v>
       </c>
       <c r="J155" s="2">
         <v>0</v>
       </c>
       <c r="K155" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L155" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="156" spans="1:12">
       <c r="A156" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="B156" t="s">
         <v>122</v>
       </c>
       <c r="C156" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D156" t="s">
         <v>137</v>
       </c>
       <c r="E156">
-        <v>17.5</v>
+        <v>2.5</v>
       </c>
       <c r="F156">
-        <v>17.87</v>
+        <v>2.69</v>
       </c>
       <c r="G156" s="1">
         <v>0.52</v>
       </c>
       <c r="H156" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I156" s="2">
-        <v>-0.79</v>
+        <v>-0.82</v>
       </c>
       <c r="J156" s="2">
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L156" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="157" spans="1:12">
@@ -6803,13 +6806,13 @@
         <v>111</v>
       </c>
       <c r="B157" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C157" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D157" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E157">
         <v>2.5</v>
@@ -6818,36 +6821,36 @@
         <v>2.61</v>
       </c>
       <c r="G157" s="1">
-        <v>0.486</v>
+        <v>0.516</v>
       </c>
       <c r="H157" t="s">
         <v>139</v>
       </c>
       <c r="I157" s="2">
-        <v>-1.08</v>
+        <v>-1.54</v>
       </c>
       <c r="J157" s="2">
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L157" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="158" spans="1:12">
       <c r="A158" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B158" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C158" t="s">
         <v>132</v>
       </c>
       <c r="D158" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E158">
         <v>11.5</v>
@@ -6856,22 +6859,22 @@
         <v>11.7</v>
       </c>
       <c r="G158" s="1">
-        <v>0.485</v>
+        <v>0.515</v>
       </c>
       <c r="H158" t="s">
         <v>140</v>
       </c>
       <c r="I158" s="2">
-        <v>-1.18</v>
+        <v>-1.68</v>
       </c>
       <c r="J158" s="2">
         <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L158" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="159" spans="1:12">
@@ -6885,7 +6888,7 @@
         <v>114</v>
       </c>
       <c r="D159" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E159">
         <v>19.5</v>
@@ -6894,27 +6897,27 @@
         <v>19.26</v>
       </c>
       <c r="G159" s="1">
-        <v>0.484</v>
+        <v>0.514</v>
       </c>
       <c r="H159" t="s">
         <v>139</v>
       </c>
       <c r="I159" s="2">
-        <v>-1.33</v>
+        <v>-1.9</v>
       </c>
       <c r="J159" s="2">
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L159" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="160" spans="1:12">
       <c r="A160" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B160" t="s">
         <v>130</v>
@@ -6923,7 +6926,7 @@
         <v>114</v>
       </c>
       <c r="D160" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E160">
         <v>11.5</v>
@@ -6932,36 +6935,36 @@
         <v>11.64</v>
       </c>
       <c r="G160" s="1">
-        <v>0.483</v>
+        <v>0.513</v>
       </c>
       <c r="H160" t="s">
         <v>140</v>
       </c>
       <c r="I160" s="2">
-        <v>-1.47</v>
+        <v>-2.1</v>
       </c>
       <c r="J160" s="2">
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L160" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="161" spans="1:12">
       <c r="A161" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B161" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C161" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D161" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E161">
         <v>7.5</v>
@@ -6970,36 +6973,36 @@
         <v>7.75</v>
       </c>
       <c r="G161" s="1">
-        <v>0.481</v>
+        <v>0.511</v>
       </c>
       <c r="H161" t="s">
         <v>139</v>
       </c>
       <c r="I161" s="2">
-        <v>-1.68</v>
+        <v>-2.4</v>
       </c>
       <c r="J161" s="2">
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L161" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="162" spans="1:12">
       <c r="A162" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B162" t="s">
+        <v>125</v>
+      </c>
+      <c r="C162" t="s">
         <v>115</v>
       </c>
-      <c r="C162" t="s">
-        <v>116</v>
-      </c>
       <c r="D162" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E162">
         <v>29.5</v>
@@ -7020,15 +7023,15 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L162" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="163" spans="1:12">
       <c r="A163" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B163" t="s">
         <v>114</v>
@@ -7037,7 +7040,7 @@
         <v>131</v>
       </c>
       <c r="D163" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E163">
         <v>24.5</v>
@@ -7058,24 +7061,24 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L163" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="164" spans="1:12">
       <c r="A164" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B164" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C164" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D164" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E164">
         <v>22.5</v>
@@ -7096,10 +7099,10 @@
         <v>0</v>
       </c>
       <c r="K164" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L164" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/output/processed_props.xlsx
+++ b/output/processed_props.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1330" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="154">
   <si>
     <t>Player</t>
   </si>
@@ -61,300 +61,300 @@
     <t>Joel Embiid</t>
   </si>
   <si>
+    <t>Jaylen Brown</t>
+  </si>
+  <si>
     <t>Tim Hardaway Jr.</t>
   </si>
   <si>
     <t>Brandon Ingram</t>
   </si>
   <si>
+    <t>Jalen Johnson</t>
+  </si>
+  <si>
+    <t>CJ McCollum</t>
+  </si>
+  <si>
+    <t>Tyrese Maxey</t>
+  </si>
+  <si>
+    <t>Chet Holmgren</t>
+  </si>
+  <si>
+    <t>Brandon Miller</t>
+  </si>
+  <si>
+    <t>Bilal Coulibaly</t>
+  </si>
+  <si>
     <t>Desmond Bane</t>
   </si>
   <si>
-    <t>Jalen Johnson</t>
-  </si>
-  <si>
-    <t>Jaylen Brown</t>
-  </si>
-  <si>
-    <t>CJ McCollum</t>
-  </si>
-  <si>
-    <t>Tyrese Maxey</t>
-  </si>
-  <si>
-    <t>Chet Holmgren</t>
-  </si>
-  <si>
-    <t>Bilal Coulibaly</t>
+    <t>Jock Landale</t>
+  </si>
+  <si>
+    <t>Dyson Daniels</t>
+  </si>
+  <si>
+    <t>LaMelo Ball</t>
+  </si>
+  <si>
+    <t>Donovan Mitchell</t>
+  </si>
+  <si>
+    <t>Anthony Edwards</t>
+  </si>
+  <si>
+    <t>Joan Beringer</t>
+  </si>
+  <si>
+    <t>RJ Barrett</t>
+  </si>
+  <si>
+    <t>Ayo Dosunmu</t>
+  </si>
+  <si>
+    <t>Kyshawn George</t>
+  </si>
+  <si>
+    <t>Ryan Kalkbrenner</t>
+  </si>
+  <si>
+    <t>Payton Pritchard</t>
+  </si>
+  <si>
+    <t>Nikola Vucevic</t>
+  </si>
+  <si>
+    <t>Tyus Jones</t>
+  </si>
+  <si>
+    <t>Kawhi Leonard</t>
+  </si>
+  <si>
+    <t>Aaron Wiggins</t>
+  </si>
+  <si>
+    <t>Jared McCain</t>
+  </si>
+  <si>
+    <t>Jaylon Tyson</t>
+  </si>
+  <si>
+    <t>Derrick White</t>
+  </si>
+  <si>
+    <t>Cam Thomas</t>
+  </si>
+  <si>
+    <t>Egor Demin</t>
+  </si>
+  <si>
+    <t>Bub Carrington</t>
+  </si>
+  <si>
+    <t>Nic Claxton</t>
+  </si>
+  <si>
+    <t>Kris Dunn</t>
+  </si>
+  <si>
+    <t>Bennedict Mathurin</t>
+  </si>
+  <si>
+    <t>Dennis Schroder</t>
+  </si>
+  <si>
+    <t>Anthony Black</t>
+  </si>
+  <si>
+    <t>Kon Knueppel</t>
   </si>
   <si>
     <t>LeBron James</t>
   </si>
   <si>
-    <t>Brandon Miller</t>
-  </si>
-  <si>
-    <t>Dyson Daniels</t>
-  </si>
-  <si>
-    <t>Bub Carrington</t>
-  </si>
-  <si>
-    <t>Jock Landale</t>
-  </si>
-  <si>
-    <t>Donovan Mitchell</t>
-  </si>
-  <si>
-    <t>LaMelo Ball</t>
-  </si>
-  <si>
-    <t>Anthony Edwards</t>
-  </si>
-  <si>
-    <t>Joan Beringer</t>
-  </si>
-  <si>
-    <t>RJ Barrett</t>
-  </si>
-  <si>
-    <t>Ayo Dosunmu</t>
-  </si>
-  <si>
-    <t>Kyshawn George</t>
-  </si>
-  <si>
-    <t>Ryan Kalkbrenner</t>
-  </si>
-  <si>
-    <t>Tyus Jones</t>
-  </si>
-  <si>
-    <t>Aaron Wiggins</t>
-  </si>
-  <si>
-    <t>Kawhi Leonard</t>
-  </si>
-  <si>
-    <t>Derrick White</t>
-  </si>
-  <si>
-    <t>Jared McCain</t>
-  </si>
-  <si>
-    <t>Nikola Vucevic</t>
-  </si>
-  <si>
-    <t>Jaylon Tyson</t>
-  </si>
-  <si>
-    <t>Cam Thomas</t>
+    <t>Nolan Traore</t>
+  </si>
+  <si>
+    <t>VJ Edgecombe</t>
+  </si>
+  <si>
+    <t>Luka Doncic</t>
+  </si>
+  <si>
+    <t>Onyeka Okongwu</t>
+  </si>
+  <si>
+    <t>Jarrett Allen</t>
+  </si>
+  <si>
+    <t>Wendell Carter Jr.</t>
+  </si>
+  <si>
+    <t>Sam Merrill</t>
+  </si>
+  <si>
+    <t>Kristaps Porzingis</t>
+  </si>
+  <si>
+    <t>Neemias Queta</t>
+  </si>
+  <si>
+    <t>Immanuel Quickley</t>
   </si>
   <si>
     <t>Brook Lopez</t>
   </si>
   <si>
-    <t>Kris Dunn</t>
-  </si>
-  <si>
-    <t>Egor Demin</t>
-  </si>
-  <si>
-    <t>Nic Claxton</t>
-  </si>
-  <si>
-    <t>Anthony Black</t>
-  </si>
-  <si>
-    <t>Bennedict Mathurin</t>
-  </si>
-  <si>
-    <t>Onyeka Okongwu</t>
-  </si>
-  <si>
-    <t>Jarrett Allen</t>
+    <t>Tristan Vukcevic</t>
+  </si>
+  <si>
+    <t>Grant Williams</t>
+  </si>
+  <si>
+    <t>Jalen Suggs</t>
+  </si>
+  <si>
+    <t>Kyle Kuzma</t>
+  </si>
+  <si>
+    <t>Ryan Rollins</t>
+  </si>
+  <si>
+    <t>Al Horford</t>
+  </si>
+  <si>
+    <t>Jaden McDaniels</t>
+  </si>
+  <si>
+    <t>Draymond Green</t>
+  </si>
+  <si>
+    <t>Brandin Podziemski</t>
+  </si>
+  <si>
+    <t>Julius Randle</t>
+  </si>
+  <si>
+    <t>De'Anthony Melton</t>
+  </si>
+  <si>
+    <t>Jamal Shead</t>
+  </si>
+  <si>
+    <t>Kevin Porter Jr.</t>
+  </si>
+  <si>
+    <t>Evan Mobley</t>
+  </si>
+  <si>
+    <t>Naz Reid</t>
+  </si>
+  <si>
+    <t>Cason Wallace</t>
+  </si>
+  <si>
+    <t>Daniel Gafford</t>
+  </si>
+  <si>
+    <t>Klay Thompson</t>
+  </si>
+  <si>
+    <t>Jamal Murray</t>
   </si>
   <si>
     <t>Corey Kispert</t>
   </si>
   <si>
-    <t>VJ Edgecombe</t>
-  </si>
-  <si>
-    <t>Sam Merrill</t>
-  </si>
-  <si>
-    <t>Kon Knueppel</t>
-  </si>
-  <si>
-    <t>Dennis Schroder</t>
-  </si>
-  <si>
-    <t>Nolan Traore</t>
-  </si>
-  <si>
-    <t>Tristan Vukcevic</t>
-  </si>
-  <si>
-    <t>Kristaps Porzingis</t>
-  </si>
-  <si>
-    <t>Immanuel Quickley</t>
-  </si>
-  <si>
-    <t>Neemias Queta</t>
-  </si>
-  <si>
-    <t>Grant Williams</t>
-  </si>
-  <si>
-    <t>Kyle Kuzma</t>
-  </si>
-  <si>
-    <t>Jaden McDaniels</t>
-  </si>
-  <si>
-    <t>Jalen Suggs</t>
-  </si>
-  <si>
-    <t>Brandin Podziemski</t>
-  </si>
-  <si>
-    <t>Draymond Green</t>
-  </si>
-  <si>
-    <t>Jamal Shead</t>
-  </si>
-  <si>
-    <t>De'Anthony Melton</t>
-  </si>
-  <si>
-    <t>Ryan Rollins</t>
-  </si>
-  <si>
-    <t>Al Horford</t>
-  </si>
-  <si>
-    <t>Daniel Gafford</t>
-  </si>
-  <si>
-    <t>Julius Randle</t>
-  </si>
-  <si>
-    <t>Naz Reid</t>
-  </si>
-  <si>
-    <t>Kevin Porter Jr.</t>
-  </si>
-  <si>
-    <t>Evan Mobley</t>
+    <t>Dominick Barlow</t>
+  </si>
+  <si>
+    <t>Myles Turner</t>
+  </si>
+  <si>
+    <t>Nickeil Alexander-Walker</t>
+  </si>
+  <si>
+    <t>Paolo Banchero</t>
+  </si>
+  <si>
+    <t>Julian Strawther</t>
+  </si>
+  <si>
+    <t>Donte DiVincenzo</t>
   </si>
   <si>
     <t>Isaiah Joe</t>
   </si>
   <si>
-    <t>Julian Strawther</t>
-  </si>
-  <si>
-    <t>Klay Thompson</t>
-  </si>
-  <si>
-    <t>Payton Pritchard</t>
-  </si>
-  <si>
-    <t>Cason Wallace</t>
-  </si>
-  <si>
-    <t>Donte DiVincenzo</t>
-  </si>
-  <si>
-    <t>Jamal Murray</t>
-  </si>
-  <si>
-    <t>Wendell Carter Jr.</t>
-  </si>
-  <si>
-    <t>Luka Doncic</t>
-  </si>
-  <si>
-    <t>Paolo Banchero</t>
-  </si>
-  <si>
-    <t>Myles Turner</t>
-  </si>
-  <si>
-    <t>Dominick Barlow</t>
+    <t>Derrick Jones Jr.</t>
+  </si>
+  <si>
+    <t>Austin Reaves</t>
+  </si>
+  <si>
+    <t>Marcus Smart</t>
+  </si>
+  <si>
+    <t>Gui Santos</t>
+  </si>
+  <si>
+    <t>Naji Marshall</t>
+  </si>
+  <si>
+    <t>Rui Hachimura</t>
+  </si>
+  <si>
+    <t>Pat Spencer</t>
+  </si>
+  <si>
+    <t>Isaiah Hartenstein</t>
   </si>
   <si>
     <t>James Harden</t>
   </si>
   <si>
-    <t>Nickeil Alexander-Walker</t>
+    <t>Deandre Ayton</t>
+  </si>
+  <si>
+    <t>Quentin Grimes</t>
+  </si>
+  <si>
+    <t>Michael Porter Jr.</t>
+  </si>
+  <si>
+    <t>Sam Hauser</t>
   </si>
   <si>
     <t>Noah Clowney</t>
   </si>
   <si>
-    <t>Austin Reaves</t>
-  </si>
-  <si>
-    <t>Derrick Jones Jr.</t>
-  </si>
-  <si>
-    <t>Naji Marshall</t>
-  </si>
-  <si>
-    <t>Marcus Smart</t>
-  </si>
-  <si>
-    <t>Pat Spencer</t>
-  </si>
-  <si>
-    <t>Rui Hachimura</t>
-  </si>
-  <si>
-    <t>Gui Santos</t>
-  </si>
-  <si>
-    <t>Isaiah Hartenstein</t>
-  </si>
-  <si>
-    <t>Deandre Ayton</t>
+    <t>Collin Murray-Boyles</t>
   </si>
   <si>
     <t>Nikola Jokic</t>
   </si>
   <si>
-    <t>Michael Porter Jr.</t>
-  </si>
-  <si>
-    <t>Collin Murray-Boyles</t>
-  </si>
-  <si>
-    <t>Sam Hauser</t>
-  </si>
-  <si>
-    <t>Quentin Grimes</t>
-  </si>
-  <si>
     <t>Baylor Scheierman</t>
   </si>
   <si>
+    <t>AJ Green</t>
+  </si>
+  <si>
+    <t>Max Christie</t>
+  </si>
+  <si>
     <t>Zaccharie Risacher</t>
   </si>
   <si>
-    <t>Max Christie</t>
-  </si>
-  <si>
     <t>Tre Johnson</t>
   </si>
   <si>
     <t>Moses Moody</t>
   </si>
   <si>
-    <t>AJ Green</t>
-  </si>
-  <si>
     <t>Christian Braun</t>
   </si>
   <si>
@@ -367,48 +367,48 @@
     <t>PHI</t>
   </si>
   <si>
+    <t>BOS</t>
+  </si>
+  <si>
     <t>TOR</t>
   </si>
   <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>OKC</t>
+  </si>
+  <si>
+    <t>CHA</t>
+  </si>
+  <si>
+    <t>WSH</t>
+  </si>
+  <si>
     <t>ORL</t>
   </si>
   <si>
-    <t>ATL</t>
-  </si>
-  <si>
-    <t>BOS</t>
-  </si>
-  <si>
-    <t>OKC</t>
-  </si>
-  <si>
-    <t>WSH</t>
+    <t>CLE</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>LAC</t>
+  </si>
+  <si>
+    <t>MIL</t>
+  </si>
+  <si>
+    <t>BKN</t>
   </si>
   <si>
     <t>LAL</t>
   </si>
   <si>
-    <t>CHA</t>
-  </si>
-  <si>
-    <t>CLE</t>
-  </si>
-  <si>
-    <t>MIN</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>LAC</t>
-  </si>
-  <si>
-    <t>MIL</t>
-  </si>
-  <si>
-    <t>BKN</t>
-  </si>
-  <si>
     <t>GS</t>
   </si>
   <si>
@@ -424,12 +424,12 @@
     <t>C</t>
   </si>
   <si>
+    <t>SF</t>
+  </si>
+  <si>
     <t>SG</t>
   </si>
   <si>
-    <t>SF</t>
-  </si>
-  <si>
     <t>PG</t>
   </si>
   <si>
@@ -445,10 +445,10 @@
     <t>PTS</t>
   </si>
   <si>
+    <t>REB</t>
+  </si>
+  <si>
     <t>PRA</t>
-  </si>
-  <si>
-    <t>REB</t>
   </si>
   <si>
     <t>RA</t>
@@ -878,7 +878,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M164"/>
+  <dimension ref="A1:M160"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
@@ -964,10 +964,10 @@
         <v>146</v>
       </c>
       <c r="J2" s="2">
-        <v>62.96</v>
+        <v>62.98</v>
       </c>
       <c r="K2" s="2">
-        <v>0.1731</v>
+        <v>0.1732</v>
       </c>
       <c r="L2" t="s">
         <v>148</v>
@@ -984,7 +984,7 @@
         <v>116</v>
       </c>
       <c r="C3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D3" t="s">
         <v>135</v>
@@ -996,19 +996,19 @@
         <v>26.5</v>
       </c>
       <c r="G3">
-        <v>31.53</v>
+        <v>31.3</v>
       </c>
       <c r="H3" s="1">
-        <v>0.788</v>
+        <v>0.777</v>
       </c>
       <c r="I3" t="s">
         <v>147</v>
       </c>
       <c r="J3" s="2">
-        <v>50.45</v>
+        <v>48.39</v>
       </c>
       <c r="K3" s="2">
-        <v>0.1387</v>
+        <v>0.1331</v>
       </c>
       <c r="L3" t="s">
         <v>148</v>
@@ -1022,10 +1022,10 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D4" t="s">
         <v>136</v>
@@ -1034,22 +1034,22 @@
         <v>141</v>
       </c>
       <c r="F4">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="G4">
-        <v>0.99</v>
+        <v>3.34</v>
       </c>
       <c r="H4" s="1">
-        <v>0.746</v>
+        <v>0.756</v>
       </c>
       <c r="I4" t="s">
         <v>146</v>
       </c>
       <c r="J4" s="2">
-        <v>42.43</v>
+        <v>44.36</v>
       </c>
       <c r="K4" s="2">
-        <v>0.1167</v>
+        <v>0.122</v>
       </c>
       <c r="L4" t="s">
         <v>148</v>
@@ -1063,10 +1063,10 @@
         <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D5" t="s">
         <v>137</v>
@@ -1075,22 +1075,22 @@
         <v>141</v>
       </c>
       <c r="F5">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="G5">
-        <v>2.5</v>
+        <v>0.99</v>
       </c>
       <c r="H5" s="1">
-        <v>0.742</v>
+        <v>0.746</v>
       </c>
       <c r="I5" t="s">
         <v>146</v>
       </c>
       <c r="J5" s="2">
-        <v>41.73</v>
+        <v>42.42</v>
       </c>
       <c r="K5" s="2">
-        <v>0.1148</v>
+        <v>0.1167</v>
       </c>
       <c r="L5" t="s">
         <v>148</v>
@@ -1113,25 +1113,25 @@
         <v>136</v>
       </c>
       <c r="E6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F6">
-        <v>25.5</v>
+        <v>3.5</v>
       </c>
       <c r="G6">
-        <v>30.44</v>
+        <v>2.53</v>
       </c>
       <c r="H6" s="1">
-        <v>0.742</v>
+        <v>0.737</v>
       </c>
       <c r="I6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J6" s="2">
-        <v>41.68</v>
+        <v>40.79</v>
       </c>
       <c r="K6" s="2">
-        <v>0.1146</v>
+        <v>0.1122</v>
       </c>
       <c r="L6" t="s">
         <v>148</v>
@@ -1148,10 +1148,10 @@
         <v>119</v>
       </c>
       <c r="C7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E7" t="s">
         <v>141</v>
@@ -1160,19 +1160,19 @@
         <v>7.5</v>
       </c>
       <c r="G7">
-        <v>5.46</v>
+        <v>5.57</v>
       </c>
       <c r="H7" s="1">
-        <v>0.739</v>
+        <v>0.731</v>
       </c>
       <c r="I7" t="s">
         <v>146</v>
       </c>
       <c r="J7" s="2">
-        <v>41.1</v>
+        <v>39.56</v>
       </c>
       <c r="K7" s="2">
-        <v>0.113</v>
+        <v>0.1088</v>
       </c>
       <c r="L7" t="s">
         <v>148</v>
@@ -1186,34 +1186,34 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F8">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="G8">
-        <v>3.47</v>
+        <v>2.55</v>
       </c>
       <c r="H8" s="1">
-        <v>0.73</v>
+        <v>0.729</v>
       </c>
       <c r="I8" t="s">
         <v>146</v>
       </c>
       <c r="J8" s="2">
-        <v>39.44</v>
+        <v>39.16</v>
       </c>
       <c r="K8" s="2">
-        <v>0.1085</v>
+        <v>0.1077</v>
       </c>
       <c r="L8" t="s">
         <v>148</v>
@@ -1227,34 +1227,34 @@
         <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C9" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D9" t="s">
         <v>138</v>
       </c>
       <c r="E9" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F9">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="G9">
-        <v>2.56</v>
+        <v>5.02</v>
       </c>
       <c r="H9" s="1">
-        <v>0.728</v>
+        <v>0.716</v>
       </c>
       <c r="I9" t="s">
         <v>146</v>
       </c>
       <c r="J9" s="2">
-        <v>38.92</v>
+        <v>36.72</v>
       </c>
       <c r="K9" s="2">
-        <v>0.107</v>
+        <v>0.101</v>
       </c>
       <c r="L9" t="s">
         <v>148</v>
@@ -1268,34 +1268,34 @@
         <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E10" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F10">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="G10">
-        <v>4.99</v>
+        <v>6.64</v>
       </c>
       <c r="H10" s="1">
-        <v>0.719</v>
+        <v>0.713</v>
       </c>
       <c r="I10" t="s">
         <v>146</v>
       </c>
       <c r="J10" s="2">
-        <v>37.17</v>
+        <v>36.16</v>
       </c>
       <c r="K10" s="2">
-        <v>0.1022</v>
+        <v>0.0994</v>
       </c>
       <c r="L10" t="s">
         <v>148</v>
@@ -1312,31 +1312,31 @@
         <v>121</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D11" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E11" t="s">
         <v>144</v>
       </c>
       <c r="F11">
-        <v>8.5</v>
+        <v>33.5</v>
       </c>
       <c r="G11">
-        <v>6.56</v>
+        <v>29.23</v>
       </c>
       <c r="H11" s="1">
-        <v>0.718</v>
+        <v>0.712</v>
       </c>
       <c r="I11" t="s">
         <v>146</v>
       </c>
       <c r="J11" s="2">
-        <v>37.16</v>
+        <v>35.85</v>
       </c>
       <c r="K11" s="2">
-        <v>0.1022</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="L11" t="s">
         <v>148</v>
@@ -1353,10 +1353,10 @@
         <v>122</v>
       </c>
       <c r="C12" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E12" t="s">
         <v>142</v>
@@ -1365,19 +1365,19 @@
         <v>10.5</v>
       </c>
       <c r="G12">
-        <v>12.91</v>
+        <v>12.76</v>
       </c>
       <c r="H12" s="1">
-        <v>0.718</v>
+        <v>0.705</v>
       </c>
       <c r="I12" t="s">
         <v>147</v>
       </c>
       <c r="J12" s="2">
-        <v>36.98</v>
+        <v>34.57</v>
       </c>
       <c r="K12" s="2">
-        <v>0.1017</v>
+        <v>0.0951</v>
       </c>
       <c r="L12" t="s">
         <v>148</v>
@@ -1394,31 +1394,31 @@
         <v>123</v>
       </c>
       <c r="C13" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="D13" t="s">
         <v>137</v>
       </c>
       <c r="E13" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F13">
-        <v>19.5</v>
+        <v>25.5</v>
       </c>
       <c r="G13">
-        <v>14.55</v>
+        <v>29.56</v>
       </c>
       <c r="H13" s="1">
-        <v>0.712</v>
+        <v>0.704</v>
       </c>
       <c r="I13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J13" s="2">
-        <v>35.97</v>
+        <v>34.31</v>
       </c>
       <c r="K13" s="2">
-        <v>0.0989</v>
+        <v>0.0944</v>
       </c>
       <c r="L13" t="s">
         <v>148</v>
@@ -1432,34 +1432,34 @@
         <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C14" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D14" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E14" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F14">
-        <v>33.5</v>
+        <v>1.5</v>
       </c>
       <c r="G14">
-        <v>29.26</v>
+        <v>1.19</v>
       </c>
       <c r="H14" s="1">
-        <v>0.71</v>
+        <v>0.701</v>
       </c>
       <c r="I14" t="s">
         <v>146</v>
       </c>
       <c r="J14" s="2">
-        <v>35.61</v>
+        <v>33.75</v>
       </c>
       <c r="K14" s="2">
-        <v>0.0979</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="L14" t="s">
         <v>148</v>
@@ -1476,31 +1476,31 @@
         <v>119</v>
       </c>
       <c r="C15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D15" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E15" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F15">
         <v>23.5</v>
       </c>
       <c r="G15">
-        <v>19.35</v>
+        <v>19.53</v>
       </c>
       <c r="H15" s="1">
-        <v>0.707</v>
+        <v>0.699</v>
       </c>
       <c r="I15" t="s">
         <v>146</v>
       </c>
       <c r="J15" s="2">
-        <v>34.95</v>
+        <v>33.38</v>
       </c>
       <c r="K15" s="2">
-        <v>0.0961</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="L15" t="s">
         <v>148</v>
@@ -1514,34 +1514,34 @@
         <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C16" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="D16" t="s">
         <v>138</v>
       </c>
       <c r="E16" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F16">
-        <v>17.5</v>
+        <v>7.5</v>
       </c>
       <c r="G16">
-        <v>15.51</v>
+        <v>6.35</v>
       </c>
       <c r="H16" s="1">
-        <v>0.704</v>
+        <v>0.695</v>
       </c>
       <c r="I16" t="s">
         <v>146</v>
       </c>
       <c r="J16" s="2">
-        <v>34.35</v>
+        <v>32.59</v>
       </c>
       <c r="K16" s="2">
-        <v>0.0945</v>
+        <v>0.0896</v>
       </c>
       <c r="L16" t="s">
         <v>148</v>
@@ -1555,34 +1555,34 @@
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C17" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D17" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E17" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F17">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="G17">
-        <v>1.19</v>
+        <v>2.83</v>
       </c>
       <c r="H17" s="1">
-        <v>0.7</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="I17" t="s">
         <v>146</v>
       </c>
       <c r="J17" s="2">
-        <v>33.69</v>
+        <v>30.72</v>
       </c>
       <c r="K17" s="2">
-        <v>0.0927</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="L17" t="s">
         <v>148</v>
@@ -1599,31 +1599,31 @@
         <v>125</v>
       </c>
       <c r="C18" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E18" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F18">
         <v>3.5</v>
       </c>
       <c r="G18">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="H18" s="1">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="I18" t="s">
         <v>146</v>
       </c>
       <c r="J18" s="2">
-        <v>33.68</v>
+        <v>29.91</v>
       </c>
       <c r="K18" s="2">
-        <v>0.0926</v>
+        <v>0.0823</v>
       </c>
       <c r="L18" t="s">
         <v>148</v>
@@ -1637,37 +1637,37 @@
         <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C19" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="D19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E19" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F19">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="G19">
-        <v>6.35</v>
+        <v>2.95</v>
       </c>
       <c r="H19" s="1">
-        <v>0.694</v>
+        <v>0.921</v>
       </c>
       <c r="I19" t="s">
         <v>146</v>
       </c>
       <c r="J19" s="2">
-        <v>32.48</v>
+        <v>75.81</v>
       </c>
       <c r="K19" s="2">
-        <v>0.0893</v>
+        <v>0.1042</v>
       </c>
       <c r="L19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M19" t="s">
         <v>153</v>
@@ -1678,37 +1678,37 @@
         <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C20" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D20" t="s">
         <v>136</v>
       </c>
       <c r="E20" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F20">
-        <v>3.5</v>
+        <v>27.5</v>
       </c>
       <c r="G20">
-        <v>2.83</v>
+        <v>23.23</v>
       </c>
       <c r="H20" s="1">
-        <v>0.6830000000000001</v>
+        <v>0.769</v>
       </c>
       <c r="I20" t="s">
         <v>146</v>
       </c>
       <c r="J20" s="2">
-        <v>30.43</v>
+        <v>46.75</v>
       </c>
       <c r="K20" s="2">
-        <v>0.0837</v>
+        <v>0.0643</v>
       </c>
       <c r="L20" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M20" t="s">
         <v>153</v>
@@ -1719,34 +1719,34 @@
         <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C21" t="s">
         <v>116</v>
       </c>
       <c r="D21" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E21" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F21">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="G21">
-        <v>2.95</v>
+        <v>2.34</v>
       </c>
       <c r="H21" s="1">
-        <v>0.921</v>
+        <v>0.758</v>
       </c>
       <c r="I21" t="s">
         <v>146</v>
       </c>
       <c r="J21" s="2">
-        <v>75.87</v>
+        <v>44.74</v>
       </c>
       <c r="K21" s="2">
-        <v>0.1043</v>
+        <v>0.0615</v>
       </c>
       <c r="L21" t="s">
         <v>149</v>
@@ -1760,34 +1760,34 @@
         <v>33</v>
       </c>
       <c r="B22" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F22">
-        <v>27.5</v>
+        <v>12.5</v>
       </c>
       <c r="G22">
-        <v>22.68</v>
+        <v>8.75</v>
       </c>
       <c r="H22" s="1">
-        <v>0.796</v>
+        <v>0.743</v>
       </c>
       <c r="I22" t="s">
         <v>146</v>
       </c>
       <c r="J22" s="2">
-        <v>52.05</v>
+        <v>41.8</v>
       </c>
       <c r="K22" s="2">
-        <v>0.0716</v>
+        <v>0.0575</v>
       </c>
       <c r="L22" t="s">
         <v>149</v>
@@ -1801,34 +1801,34 @@
         <v>34</v>
       </c>
       <c r="B23" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="D23" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E23" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F23">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="G23">
-        <v>2.34</v>
+        <v>6.02</v>
       </c>
       <c r="H23" s="1">
-        <v>0.758</v>
+        <v>0.741</v>
       </c>
       <c r="I23" t="s">
         <v>146</v>
       </c>
       <c r="J23" s="2">
-        <v>44.64</v>
+        <v>41.41</v>
       </c>
       <c r="K23" s="2">
-        <v>0.0614</v>
+        <v>0.0569</v>
       </c>
       <c r="L23" t="s">
         <v>149</v>
@@ -1842,34 +1842,34 @@
         <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C24" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D24" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E24" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F24">
-        <v>12.5</v>
+        <v>27.5</v>
       </c>
       <c r="G24">
-        <v>8.640000000000001</v>
+        <v>33.61</v>
       </c>
       <c r="H24" s="1">
-        <v>0.749</v>
+        <v>0.724</v>
       </c>
       <c r="I24" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J24" s="2">
-        <v>43</v>
+        <v>38.14</v>
       </c>
       <c r="K24" s="2">
-        <v>0.0591</v>
+        <v>0.0524</v>
       </c>
       <c r="L24" t="s">
         <v>149</v>
@@ -1883,34 +1883,34 @@
         <v>36</v>
       </c>
       <c r="B25" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C25" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D25" t="s">
         <v>135</v>
       </c>
       <c r="E25" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F25">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="G25">
-        <v>5.99</v>
+        <v>1.84</v>
       </c>
       <c r="H25" s="1">
-        <v>0.746</v>
+        <v>0.72</v>
       </c>
       <c r="I25" t="s">
         <v>146</v>
       </c>
       <c r="J25" s="2">
-        <v>42.42</v>
+        <v>37.55</v>
       </c>
       <c r="K25" s="2">
-        <v>0.0583</v>
+        <v>0.0516</v>
       </c>
       <c r="L25" t="s">
         <v>149</v>
@@ -1924,7 +1924,7 @@
         <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C26" t="s">
         <v>134</v>
@@ -1939,19 +1939,19 @@
         <v>6.5</v>
       </c>
       <c r="G26">
-        <v>5.44</v>
+        <v>5.48</v>
       </c>
       <c r="H26" s="1">
-        <v>0.727</v>
+        <v>0.718</v>
       </c>
       <c r="I26" t="s">
         <v>146</v>
       </c>
       <c r="J26" s="2">
-        <v>38.7</v>
+        <v>37.12</v>
       </c>
       <c r="K26" s="2">
-        <v>0.0532</v>
+        <v>0.051</v>
       </c>
       <c r="L26" t="s">
         <v>149</v>
@@ -1965,34 +1965,34 @@
         <v>38</v>
       </c>
       <c r="B27" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C27" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D27" t="s">
         <v>136</v>
       </c>
       <c r="E27" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F27">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="G27">
-        <v>11.11</v>
+        <v>3.49</v>
       </c>
       <c r="H27" s="1">
-        <v>0.724</v>
+        <v>0.716</v>
       </c>
       <c r="I27" t="s">
         <v>146</v>
       </c>
       <c r="J27" s="2">
-        <v>38.14</v>
+        <v>36.63</v>
       </c>
       <c r="K27" s="2">
-        <v>0.0524</v>
+        <v>0.0504</v>
       </c>
       <c r="L27" t="s">
         <v>149</v>
@@ -2006,34 +2006,34 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C28" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D28" t="s">
         <v>137</v>
       </c>
       <c r="E28" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F28">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="G28">
-        <v>3.45</v>
+        <v>11.29</v>
       </c>
       <c r="H28" s="1">
-        <v>0.722</v>
+        <v>0.713</v>
       </c>
       <c r="I28" t="s">
         <v>146</v>
       </c>
       <c r="J28" s="2">
-        <v>37.85</v>
+        <v>36.1</v>
       </c>
       <c r="K28" s="2">
-        <v>0.052</v>
+        <v>0.0496</v>
       </c>
       <c r="L28" t="s">
         <v>149</v>
@@ -2050,31 +2050,31 @@
         <v>120</v>
       </c>
       <c r="C29" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D29" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E29" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F29">
-        <v>27.5</v>
+        <v>2.5</v>
       </c>
       <c r="G29">
-        <v>23.89</v>
+        <v>1.87</v>
       </c>
       <c r="H29" s="1">
-        <v>0.72</v>
+        <v>0.711</v>
       </c>
       <c r="I29" t="s">
         <v>146</v>
       </c>
       <c r="J29" s="2">
-        <v>37.36</v>
+        <v>35.78</v>
       </c>
       <c r="K29" s="2">
-        <v>0.0514</v>
+        <v>0.0492</v>
       </c>
       <c r="L29" t="s">
         <v>149</v>
@@ -2088,34 +2088,34 @@
         <v>41</v>
       </c>
       <c r="B30" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C30" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D30" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E30" t="s">
         <v>141</v>
       </c>
       <c r="F30">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="G30">
-        <v>1.84</v>
+        <v>1.32</v>
       </c>
       <c r="H30" s="1">
-        <v>0.719</v>
+        <v>0.711</v>
       </c>
       <c r="I30" t="s">
         <v>146</v>
       </c>
       <c r="J30" s="2">
-        <v>37.3</v>
+        <v>35.72</v>
       </c>
       <c r="K30" s="2">
-        <v>0.0513</v>
+        <v>0.0491</v>
       </c>
       <c r="L30" t="s">
         <v>149</v>
@@ -2129,34 +2129,34 @@
         <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C31" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="D31" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E31" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F31">
-        <v>2.5</v>
+        <v>27.5</v>
       </c>
       <c r="G31">
-        <v>1.87</v>
+        <v>24.09</v>
       </c>
       <c r="H31" s="1">
-        <v>0.715</v>
+        <v>0.709</v>
       </c>
       <c r="I31" t="s">
         <v>146</v>
       </c>
       <c r="J31" s="2">
-        <v>36.58</v>
+        <v>35.31</v>
       </c>
       <c r="K31" s="2">
-        <v>0.0503</v>
+        <v>0.0485</v>
       </c>
       <c r="L31" t="s">
         <v>149</v>
@@ -2170,34 +2170,34 @@
         <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C32" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D32" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E32" t="s">
         <v>141</v>
       </c>
       <c r="F32">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="G32">
-        <v>1.34</v>
+        <v>2.05</v>
       </c>
       <c r="H32" s="1">
-        <v>0.705</v>
+        <v>0.698</v>
       </c>
       <c r="I32" t="s">
         <v>146</v>
       </c>
       <c r="J32" s="2">
-        <v>34.67</v>
+        <v>33.34</v>
       </c>
       <c r="K32" s="2">
-        <v>0.0477</v>
+        <v>0.0458</v>
       </c>
       <c r="L32" t="s">
         <v>149</v>
@@ -2214,31 +2214,31 @@
         <v>129</v>
       </c>
       <c r="C33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D33" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E33" t="s">
         <v>141</v>
       </c>
       <c r="F33">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="G33">
-        <v>2.04</v>
+        <v>2.92</v>
       </c>
       <c r="H33" s="1">
-        <v>0.701</v>
+        <v>0.665</v>
       </c>
       <c r="I33" t="s">
         <v>146</v>
       </c>
       <c r="J33" s="2">
-        <v>33.78</v>
+        <v>27.03</v>
       </c>
       <c r="K33" s="2">
-        <v>0.0465</v>
+        <v>0.0743</v>
       </c>
       <c r="L33" t="s">
         <v>149</v>
@@ -2252,34 +2252,34 @@
         <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C34" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D34" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F34">
-        <v>8.5</v>
+        <v>17.5</v>
       </c>
       <c r="G34">
-        <v>7.16</v>
+        <v>15.96</v>
       </c>
       <c r="H34" s="1">
-        <v>0.681</v>
+        <v>0.661</v>
       </c>
       <c r="I34" t="s">
         <v>146</v>
       </c>
       <c r="J34" s="2">
-        <v>30.02</v>
+        <v>26.16</v>
       </c>
       <c r="K34" s="2">
-        <v>0.0413</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="L34" t="s">
         <v>149</v>
@@ -2293,34 +2293,34 @@
         <v>46</v>
       </c>
       <c r="B35" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D35" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E35" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F35">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="G35">
-        <v>3.74</v>
+        <v>12.2</v>
       </c>
       <c r="H35" s="1">
-        <v>0.675</v>
+        <v>0.66</v>
       </c>
       <c r="I35" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J35" s="2">
-        <v>28.81</v>
+        <v>26.06</v>
       </c>
       <c r="K35" s="2">
-        <v>0.07920000000000001</v>
+        <v>0.0717</v>
       </c>
       <c r="L35" t="s">
         <v>149</v>
@@ -2334,34 +2334,34 @@
         <v>47</v>
       </c>
       <c r="B36" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C36" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D36" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E36" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F36">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="G36">
-        <v>2.96</v>
+        <v>3.86</v>
       </c>
       <c r="H36" s="1">
-        <v>0.655</v>
+        <v>0.654</v>
       </c>
       <c r="I36" t="s">
         <v>146</v>
       </c>
       <c r="J36" s="2">
-        <v>25.11</v>
+        <v>24.81</v>
       </c>
       <c r="K36" s="2">
-        <v>0.06909999999999999</v>
+        <v>0.0682</v>
       </c>
       <c r="L36" t="s">
         <v>149</v>
@@ -2375,34 +2375,34 @@
         <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C37" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D37" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E37" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F37">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="G37">
-        <v>12.14</v>
+        <v>3.35</v>
       </c>
       <c r="H37" s="1">
-        <v>0.655</v>
+        <v>0.65</v>
       </c>
       <c r="I37" t="s">
         <v>147</v>
       </c>
       <c r="J37" s="2">
-        <v>25.1</v>
+        <v>24.02</v>
       </c>
       <c r="K37" s="2">
-        <v>0.06900000000000001</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="L37" t="s">
         <v>149</v>
@@ -2416,10 +2416,10 @@
         <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C38" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D38" t="s">
         <v>138</v>
@@ -2428,22 +2428,22 @@
         <v>141</v>
       </c>
       <c r="F38">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="G38">
-        <v>3.89</v>
+        <v>2.99</v>
       </c>
       <c r="H38" s="1">
-        <v>0.65</v>
+        <v>0.649</v>
       </c>
       <c r="I38" t="s">
         <v>146</v>
       </c>
       <c r="J38" s="2">
-        <v>24.04</v>
+        <v>23.85</v>
       </c>
       <c r="K38" s="2">
-        <v>0.06610000000000001</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="L38" t="s">
         <v>149</v>
@@ -2457,34 +2457,34 @@
         <v>50</v>
       </c>
       <c r="B39" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C39" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D39" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E39" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F39">
-        <v>2.5</v>
+        <v>15.5</v>
       </c>
       <c r="G39">
-        <v>3.34</v>
+        <v>13.15</v>
       </c>
       <c r="H39" s="1">
         <v>0.648</v>
       </c>
       <c r="I39" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J39" s="2">
-        <v>23.72</v>
+        <v>23.76</v>
       </c>
       <c r="K39" s="2">
-        <v>0.06519999999999999</v>
+        <v>0.0653</v>
       </c>
       <c r="L39" t="s">
         <v>149</v>
@@ -2498,34 +2498,34 @@
         <v>51</v>
       </c>
       <c r="B40" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C40" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D40" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E40" t="s">
         <v>142</v>
       </c>
       <c r="F40">
-        <v>14.5</v>
+        <v>20.5</v>
       </c>
       <c r="G40">
-        <v>16.68</v>
+        <v>23.18</v>
       </c>
       <c r="H40" s="1">
-        <v>0.639</v>
+        <v>0.648</v>
       </c>
       <c r="I40" t="s">
         <v>147</v>
       </c>
       <c r="J40" s="2">
-        <v>21.93</v>
+        <v>23.61</v>
       </c>
       <c r="K40" s="2">
-        <v>0.0603</v>
+        <v>0.0649</v>
       </c>
       <c r="L40" t="s">
         <v>149</v>
@@ -2539,34 +2539,34 @@
         <v>52</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C41" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D41" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E41" t="s">
         <v>143</v>
       </c>
       <c r="F41">
-        <v>25.5</v>
+        <v>5.5</v>
       </c>
       <c r="G41">
-        <v>30.33</v>
+        <v>4.85</v>
       </c>
       <c r="H41" s="1">
-        <v>0.635</v>
+        <v>0.64</v>
       </c>
       <c r="I41" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J41" s="2">
-        <v>21.25</v>
+        <v>22.25</v>
       </c>
       <c r="K41" s="2">
-        <v>0.0584</v>
+        <v>0.0612</v>
       </c>
       <c r="L41" t="s">
         <v>149</v>
@@ -2580,34 +2580,34 @@
         <v>53</v>
       </c>
       <c r="B42" t="s">
+        <v>129</v>
+      </c>
+      <c r="C42" t="s">
         <v>119</v>
       </c>
-      <c r="C42" t="s">
-        <v>130</v>
-      </c>
       <c r="D42" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E42" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F42">
-        <v>13.5</v>
+        <v>4.5</v>
       </c>
       <c r="G42">
-        <v>11.56</v>
+        <v>6.02</v>
       </c>
       <c r="H42" s="1">
-        <v>0.633</v>
+        <v>0.64</v>
       </c>
       <c r="I42" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J42" s="2">
-        <v>20.78</v>
+        <v>22.19</v>
       </c>
       <c r="K42" s="2">
-        <v>0.0571</v>
+        <v>0.061</v>
       </c>
       <c r="L42" t="s">
         <v>149</v>
@@ -2624,10 +2624,10 @@
         <v>116</v>
       </c>
       <c r="C43" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D43" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E43" t="s">
         <v>141</v>
@@ -2636,19 +2636,19 @@
         <v>3.5</v>
       </c>
       <c r="G43">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="H43" s="1">
-        <v>0.63</v>
+        <v>0.637</v>
       </c>
       <c r="I43" t="s">
         <v>146</v>
       </c>
       <c r="J43" s="2">
-        <v>20.27</v>
+        <v>21.61</v>
       </c>
       <c r="K43" s="2">
-        <v>0.0558</v>
+        <v>0.0594</v>
       </c>
       <c r="L43" t="s">
         <v>149</v>
@@ -2662,34 +2662,34 @@
         <v>55</v>
       </c>
       <c r="B44" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C44" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D44" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E44" t="s">
         <v>141</v>
       </c>
       <c r="F44">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="G44">
-        <v>1.39</v>
+        <v>6.76</v>
       </c>
       <c r="H44" s="1">
-        <v>0.63</v>
+        <v>0.631</v>
       </c>
       <c r="I44" t="s">
         <v>146</v>
       </c>
       <c r="J44" s="2">
-        <v>20.2</v>
+        <v>20.42</v>
       </c>
       <c r="K44" s="2">
-        <v>0.0556</v>
+        <v>0.0562</v>
       </c>
       <c r="L44" t="s">
         <v>149</v>
@@ -2703,34 +2703,34 @@
         <v>56</v>
       </c>
       <c r="B45" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C45" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D45" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E45" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F45">
-        <v>30.5</v>
+        <v>14.5</v>
       </c>
       <c r="G45">
-        <v>32.67</v>
+        <v>16.52</v>
       </c>
       <c r="H45" s="1">
-        <v>0.63</v>
+        <v>0.629</v>
       </c>
       <c r="I45" t="s">
         <v>147</v>
       </c>
       <c r="J45" s="2">
-        <v>20.19</v>
+        <v>20.13</v>
       </c>
       <c r="K45" s="2">
-        <v>0.0555</v>
+        <v>0.0554</v>
       </c>
       <c r="L45" t="s">
         <v>149</v>
@@ -2744,34 +2744,34 @@
         <v>57</v>
       </c>
       <c r="B46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C46" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D46" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E46" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F46">
-        <v>3.5</v>
+        <v>25.5</v>
       </c>
       <c r="G46">
-        <v>3.08</v>
+        <v>30.01</v>
       </c>
       <c r="H46" s="1">
-        <v>0.629</v>
+        <v>0.626</v>
       </c>
       <c r="I46" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J46" s="2">
-        <v>20.09</v>
+        <v>19.57</v>
       </c>
       <c r="K46" s="2">
-        <v>0.0553</v>
+        <v>0.0538</v>
       </c>
       <c r="L46" t="s">
         <v>149</v>
@@ -2785,34 +2785,34 @@
         <v>58</v>
       </c>
       <c r="B47" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C47" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="D47" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E47" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F47">
-        <v>4.5</v>
+        <v>9.5</v>
       </c>
       <c r="G47">
-        <v>5.92</v>
+        <v>7.6</v>
       </c>
       <c r="H47" s="1">
-        <v>0.626</v>
+        <v>0.624</v>
       </c>
       <c r="I47" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J47" s="2">
-        <v>19.54</v>
+        <v>19.13</v>
       </c>
       <c r="K47" s="2">
-        <v>0.0537</v>
+        <v>0.0526</v>
       </c>
       <c r="L47" t="s">
         <v>149</v>
@@ -2823,37 +2823,37 @@
     </row>
     <row r="48" spans="1:13">
       <c r="A48" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="B48" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C48" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D48" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E48" t="s">
         <v>141</v>
       </c>
       <c r="F48">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="G48">
-        <v>2.26</v>
+        <v>1.41</v>
       </c>
       <c r="H48" s="1">
-        <v>0.621</v>
+        <v>0.623</v>
       </c>
       <c r="I48" t="s">
         <v>146</v>
       </c>
       <c r="J48" s="2">
-        <v>18.46</v>
+        <v>19.03</v>
       </c>
       <c r="K48" s="2">
-        <v>0.0508</v>
+        <v>0.0523</v>
       </c>
       <c r="L48" t="s">
         <v>149</v>
@@ -2864,25 +2864,25 @@
     </row>
     <row r="49" spans="1:13">
       <c r="A49" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B49" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="C49" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D49" t="s">
         <v>135</v>
       </c>
       <c r="E49" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F49">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="G49">
-        <v>4.63</v>
+        <v>1.31</v>
       </c>
       <c r="H49" s="1">
         <v>0.68</v>
@@ -2891,7 +2891,7 @@
         <v>146</v>
       </c>
       <c r="J49" s="2">
-        <v>29.77</v>
+        <v>29.76</v>
       </c>
       <c r="K49" s="2">
         <v>0.0409</v>
@@ -2905,13 +2905,13 @@
     </row>
     <row r="50" spans="1:13">
       <c r="A50" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B50" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="C50" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="D50" t="s">
         <v>135</v>
@@ -2923,19 +2923,19 @@
         <v>1.5</v>
       </c>
       <c r="G50">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="H50" s="1">
-        <v>0.68</v>
+        <v>0.678</v>
       </c>
       <c r="I50" t="s">
         <v>146</v>
       </c>
       <c r="J50" s="2">
-        <v>29.73</v>
+        <v>29.44</v>
       </c>
       <c r="K50" s="2">
-        <v>0.0409</v>
+        <v>0.0405</v>
       </c>
       <c r="L50" t="s">
         <v>150</v>
@@ -2946,25 +2946,25 @@
     </row>
     <row r="51" spans="1:13">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B51" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C51" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D51" t="s">
         <v>138</v>
       </c>
       <c r="E51" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F51">
-        <v>28.5</v>
+        <v>6.5</v>
       </c>
       <c r="G51">
-        <v>25.27</v>
+        <v>5.55</v>
       </c>
       <c r="H51" s="1">
         <v>0.678</v>
@@ -2973,10 +2973,10 @@
         <v>146</v>
       </c>
       <c r="J51" s="2">
-        <v>29.46</v>
+        <v>29.35</v>
       </c>
       <c r="K51" s="2">
-        <v>0.0405</v>
+        <v>0.0404</v>
       </c>
       <c r="L51" t="s">
         <v>150</v>
@@ -2987,10 +2987,10 @@
     </row>
     <row r="52" spans="1:13">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B52" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C52" t="s">
         <v>123</v>
@@ -2999,13 +2999,13 @@
         <v>135</v>
       </c>
       <c r="E52" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F52">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="G52">
-        <v>1.32</v>
+        <v>4.59</v>
       </c>
       <c r="H52" s="1">
         <v>0.677</v>
@@ -3014,10 +3014,10 @@
         <v>146</v>
       </c>
       <c r="J52" s="2">
-        <v>29.33</v>
+        <v>29.21</v>
       </c>
       <c r="K52" s="2">
-        <v>0.0403</v>
+        <v>0.0402</v>
       </c>
       <c r="L52" t="s">
         <v>150</v>
@@ -3028,25 +3028,25 @@
     </row>
     <row r="53" spans="1:13">
       <c r="A53" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B53" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C53" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D53" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E53" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F53">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="G53">
-        <v>2.06</v>
+        <v>4.67</v>
       </c>
       <c r="H53" s="1">
         <v>0.674</v>
@@ -3055,10 +3055,10 @@
         <v>146</v>
       </c>
       <c r="J53" s="2">
-        <v>28.58</v>
+        <v>28.73</v>
       </c>
       <c r="K53" s="2">
-        <v>0.0393</v>
+        <v>0.0395</v>
       </c>
       <c r="L53" t="s">
         <v>150</v>
@@ -3069,13 +3069,13 @@
     </row>
     <row r="54" spans="1:13">
       <c r="A54" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B54" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C54" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="D54" t="s">
         <v>139</v>
@@ -3087,19 +3087,19 @@
         <v>2.5</v>
       </c>
       <c r="G54">
-        <v>2.42</v>
+        <v>2.06</v>
       </c>
       <c r="H54" s="1">
-        <v>0.667</v>
+        <v>0.674</v>
       </c>
       <c r="I54" t="s">
         <v>146</v>
       </c>
       <c r="J54" s="2">
-        <v>27.33</v>
+        <v>28.6</v>
       </c>
       <c r="K54" s="2">
-        <v>0.0376</v>
+        <v>0.0393</v>
       </c>
       <c r="L54" t="s">
         <v>150</v>
@@ -3110,37 +3110,37 @@
     </row>
     <row r="55" spans="1:13">
       <c r="A55" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B55" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C55" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D55" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E55" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F55">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="G55">
-        <v>3.82</v>
+        <v>3.02</v>
       </c>
       <c r="H55" s="1">
-        <v>0.664</v>
+        <v>0.667</v>
       </c>
       <c r="I55" t="s">
         <v>146</v>
       </c>
       <c r="J55" s="2">
-        <v>26.7</v>
+        <v>27.36</v>
       </c>
       <c r="K55" s="2">
-        <v>0.0367</v>
+        <v>0.0376</v>
       </c>
       <c r="L55" t="s">
         <v>150</v>
@@ -3151,25 +3151,25 @@
     </row>
     <row r="56" spans="1:13">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B56" t="s">
+        <v>128</v>
+      </c>
+      <c r="C56" t="s">
         <v>118</v>
       </c>
-      <c r="C56" t="s">
-        <v>128</v>
-      </c>
       <c r="D56" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E56" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F56">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="G56">
-        <v>3.05</v>
+        <v>2.44</v>
       </c>
       <c r="H56" s="1">
         <v>0.663</v>
@@ -3178,10 +3178,10 @@
         <v>146</v>
       </c>
       <c r="J56" s="2">
-        <v>26.59</v>
+        <v>26.66</v>
       </c>
       <c r="K56" s="2">
-        <v>0.0366</v>
+        <v>0.0367</v>
       </c>
       <c r="L56" t="s">
         <v>150</v>
@@ -3192,37 +3192,37 @@
     </row>
     <row r="57" spans="1:13">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B57" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C57" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D57" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E57" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F57">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="G57">
-        <v>3.04</v>
+        <v>5.62</v>
       </c>
       <c r="H57" s="1">
-        <v>0.661</v>
+        <v>0.66</v>
       </c>
       <c r="I57" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J57" s="2">
-        <v>26.24</v>
+        <v>26.08</v>
       </c>
       <c r="K57" s="2">
-        <v>0.0361</v>
+        <v>0.0359</v>
       </c>
       <c r="L57" t="s">
         <v>150</v>
@@ -3233,7 +3233,7 @@
     </row>
     <row r="58" spans="1:13">
       <c r="A58" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B58" t="s">
         <v>131</v>
@@ -3242,28 +3242,28 @@
         <v>115</v>
       </c>
       <c r="D58" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E58" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F58">
-        <v>4.5</v>
+        <v>16.5</v>
       </c>
       <c r="G58">
-        <v>3.85</v>
+        <v>13.7</v>
       </c>
       <c r="H58" s="1">
-        <v>0.655</v>
+        <v>0.658</v>
       </c>
       <c r="I58" t="s">
         <v>146</v>
       </c>
       <c r="J58" s="2">
-        <v>25.11</v>
+        <v>25.66</v>
       </c>
       <c r="K58" s="2">
-        <v>0.0345</v>
+        <v>0.0353</v>
       </c>
       <c r="L58" t="s">
         <v>150</v>
@@ -3274,37 +3274,37 @@
     </row>
     <row r="59" spans="1:13">
       <c r="A59" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B59" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C59" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="D59" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E59" t="s">
         <v>143</v>
       </c>
       <c r="F59">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="G59">
-        <v>12.02</v>
+        <v>3.86</v>
       </c>
       <c r="H59" s="1">
-        <v>0.653</v>
+        <v>0.657</v>
       </c>
       <c r="I59" t="s">
         <v>146</v>
       </c>
       <c r="J59" s="2">
-        <v>24.62</v>
+        <v>25.42</v>
       </c>
       <c r="K59" s="2">
-        <v>0.0339</v>
+        <v>0.035</v>
       </c>
       <c r="L59" t="s">
         <v>150</v>
@@ -3315,7 +3315,7 @@
     </row>
     <row r="60" spans="1:13">
       <c r="A60" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B60" t="s">
         <v>131</v>
@@ -3324,28 +3324,28 @@
         <v>115</v>
       </c>
       <c r="D60" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E60" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F60">
-        <v>19.5</v>
+        <v>4.5</v>
       </c>
       <c r="G60">
-        <v>22.13</v>
+        <v>3.85</v>
       </c>
       <c r="H60" s="1">
-        <v>0.652</v>
+        <v>0.656</v>
       </c>
       <c r="I60" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J60" s="2">
-        <v>24.53</v>
+        <v>25.31</v>
       </c>
       <c r="K60" s="2">
-        <v>0.0337</v>
+        <v>0.0348</v>
       </c>
       <c r="L60" t="s">
         <v>150</v>
@@ -3356,37 +3356,37 @@
     </row>
     <row r="61" spans="1:13">
       <c r="A61" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B61" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C61" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D61" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E61" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F61">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="G61">
-        <v>5.54</v>
+        <v>3.07</v>
       </c>
       <c r="H61" s="1">
-        <v>0.649</v>
+        <v>0.656</v>
       </c>
       <c r="I61" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J61" s="2">
-        <v>23.86</v>
+        <v>25.14</v>
       </c>
       <c r="K61" s="2">
-        <v>0.0328</v>
+        <v>0.0346</v>
       </c>
       <c r="L61" t="s">
         <v>150</v>
@@ -3397,37 +3397,37 @@
     </row>
     <row r="62" spans="1:13">
       <c r="A62" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B62" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C62" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D62" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E62" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F62">
-        <v>16.5</v>
+        <v>21.5</v>
       </c>
       <c r="G62">
-        <v>13.92</v>
+        <v>18.31</v>
       </c>
       <c r="H62" s="1">
-        <v>0.646</v>
+        <v>0.647</v>
       </c>
       <c r="I62" t="s">
         <v>146</v>
       </c>
       <c r="J62" s="2">
-        <v>23.36</v>
+        <v>23.59</v>
       </c>
       <c r="K62" s="2">
-        <v>0.0321</v>
+        <v>0.0324</v>
       </c>
       <c r="L62" t="s">
         <v>150</v>
@@ -3438,34 +3438,34 @@
     </row>
     <row r="63" spans="1:13">
       <c r="A63" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B63" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C63" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="D63" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E63" t="s">
         <v>144</v>
       </c>
       <c r="F63">
-        <v>7.5</v>
+        <v>19.5</v>
       </c>
       <c r="G63">
-        <v>6.62</v>
+        <v>21.99</v>
       </c>
       <c r="H63" s="1">
         <v>0.645</v>
       </c>
       <c r="I63" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J63" s="2">
-        <v>23.07</v>
+        <v>23.06</v>
       </c>
       <c r="K63" s="2">
         <v>0.0317</v>
@@ -3479,25 +3479,25 @@
     </row>
     <row r="64" spans="1:13">
       <c r="A64" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B64" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C64" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D64" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E64" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F64">
-        <v>21.5</v>
+        <v>14.5</v>
       </c>
       <c r="G64">
-        <v>18.42</v>
+        <v>12.18</v>
       </c>
       <c r="H64" s="1">
         <v>0.643</v>
@@ -3506,10 +3506,10 @@
         <v>146</v>
       </c>
       <c r="J64" s="2">
-        <v>22.68</v>
+        <v>22.75</v>
       </c>
       <c r="K64" s="2">
-        <v>0.0312</v>
+        <v>0.0313</v>
       </c>
       <c r="L64" t="s">
         <v>150</v>
@@ -3520,37 +3520,37 @@
     </row>
     <row r="65" spans="1:13">
       <c r="A65" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B65" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C65" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D65" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E65" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F65">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
       <c r="G65">
-        <v>7.69</v>
+        <v>13.18</v>
       </c>
       <c r="H65" s="1">
-        <v>0.636</v>
+        <v>0.64</v>
       </c>
       <c r="I65" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J65" s="2">
-        <v>21.41</v>
+        <v>22.23</v>
       </c>
       <c r="K65" s="2">
-        <v>0.0294</v>
+        <v>0.0306</v>
       </c>
       <c r="L65" t="s">
         <v>150</v>
@@ -3561,37 +3561,37 @@
     </row>
     <row r="66" spans="1:13">
       <c r="A66" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B66" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C66" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D66" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E66" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F66">
-        <v>11.5</v>
+        <v>2.5</v>
       </c>
       <c r="G66">
-        <v>13.13</v>
+        <v>2.34</v>
       </c>
       <c r="H66" s="1">
-        <v>0.636</v>
+        <v>0.637</v>
       </c>
       <c r="I66" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J66" s="2">
-        <v>21.37</v>
+        <v>21.59</v>
       </c>
       <c r="K66" s="2">
-        <v>0.0294</v>
+        <v>0.0297</v>
       </c>
       <c r="L66" t="s">
         <v>150</v>
@@ -3602,37 +3602,37 @@
     </row>
     <row r="67" spans="1:13">
       <c r="A67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B67" t="s">
         <v>125</v>
       </c>
       <c r="C67" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D67" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E67" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F67">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="G67">
-        <v>2.35</v>
+        <v>7.68</v>
       </c>
       <c r="H67" s="1">
-        <v>0.634</v>
+        <v>0.637</v>
       </c>
       <c r="I67" t="s">
         <v>146</v>
       </c>
       <c r="J67" s="2">
-        <v>20.97</v>
+        <v>21.53</v>
       </c>
       <c r="K67" s="2">
-        <v>0.0288</v>
+        <v>0.0296</v>
       </c>
       <c r="L67" t="s">
         <v>150</v>
@@ -3643,37 +3643,37 @@
     </row>
     <row r="68" spans="1:13">
       <c r="A68" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="B68" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C68" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D68" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E68" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F68">
-        <v>12.5</v>
+        <v>3.5</v>
       </c>
       <c r="G68">
-        <v>14.9</v>
+        <v>3.07</v>
       </c>
       <c r="H68" s="1">
-        <v>0.632</v>
+        <v>0.631</v>
       </c>
       <c r="I68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J68" s="2">
-        <v>20.74</v>
+        <v>20.47</v>
       </c>
       <c r="K68" s="2">
-        <v>0.0285</v>
+        <v>0.0281</v>
       </c>
       <c r="L68" t="s">
         <v>150</v>
@@ -3684,37 +3684,37 @@
     </row>
     <row r="69" spans="1:13">
       <c r="A69" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="B69" t="s">
         <v>120</v>
       </c>
       <c r="C69" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D69" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E69" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F69">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="G69">
-        <v>8.67</v>
+        <v>4.34</v>
       </c>
       <c r="H69" s="1">
-        <v>0.629</v>
+        <v>0.63</v>
       </c>
       <c r="I69" t="s">
         <v>147</v>
       </c>
       <c r="J69" s="2">
-        <v>20.12</v>
+        <v>20.37</v>
       </c>
       <c r="K69" s="2">
-        <v>0.0277</v>
+        <v>0.028</v>
       </c>
       <c r="L69" t="s">
         <v>150</v>
@@ -3725,37 +3725,37 @@
     </row>
     <row r="70" spans="1:13">
       <c r="A70" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B70" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="C70" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D70" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E70" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F70">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="G70">
-        <v>2.18</v>
+        <v>6.79</v>
       </c>
       <c r="H70" s="1">
-        <v>0.628</v>
+        <v>0.626</v>
       </c>
       <c r="I70" t="s">
         <v>146</v>
       </c>
       <c r="J70" s="2">
-        <v>19.95</v>
+        <v>19.58</v>
       </c>
       <c r="K70" s="2">
-        <v>0.0274</v>
+        <v>0.0269</v>
       </c>
       <c r="L70" t="s">
         <v>150</v>
@@ -3766,37 +3766,37 @@
     </row>
     <row r="71" spans="1:13">
       <c r="A71" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="B71" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C71" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D71" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E71" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F71">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="G71">
-        <v>15.25</v>
+        <v>21.85</v>
       </c>
       <c r="H71" s="1">
-        <v>0.627</v>
+        <v>0.626</v>
       </c>
       <c r="I71" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J71" s="2">
-        <v>19.67</v>
+        <v>19.43</v>
       </c>
       <c r="K71" s="2">
-        <v>0.027</v>
+        <v>0.0267</v>
       </c>
       <c r="L71" t="s">
         <v>150</v>
@@ -3807,37 +3807,37 @@
     </row>
     <row r="72" spans="1:13">
       <c r="A72" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="B72" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C72" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D72" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E72" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F72">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="G72">
-        <v>6.68</v>
+        <v>14.26</v>
       </c>
       <c r="H72" s="1">
-        <v>0.626</v>
+        <v>0.624</v>
       </c>
       <c r="I72" t="s">
         <v>147</v>
       </c>
       <c r="J72" s="2">
-        <v>19.56</v>
+        <v>19.22</v>
       </c>
       <c r="K72" s="2">
-        <v>0.0269</v>
+        <v>0.0264</v>
       </c>
       <c r="L72" t="s">
         <v>150</v>
@@ -3848,37 +3848,37 @@
     </row>
     <row r="73" spans="1:13">
       <c r="A73" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B73" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C73" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D73" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E73" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F73">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="G73">
-        <v>22.69</v>
+        <v>18.49</v>
       </c>
       <c r="H73" s="1">
-        <v>0.625</v>
+        <v>0.624</v>
       </c>
       <c r="I73" t="s">
         <v>147</v>
       </c>
       <c r="J73" s="2">
-        <v>19.34</v>
+        <v>19.2</v>
       </c>
       <c r="K73" s="2">
-        <v>0.0266</v>
+        <v>0.0264</v>
       </c>
       <c r="L73" t="s">
         <v>150</v>
@@ -3889,13 +3889,13 @@
     </row>
     <row r="74" spans="1:13">
       <c r="A74" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B74" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C74" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D74" t="s">
         <v>136</v>
@@ -3904,22 +3904,22 @@
         <v>144</v>
       </c>
       <c r="F74">
-        <v>3.5</v>
+        <v>17.5</v>
       </c>
       <c r="G74">
-        <v>4.31</v>
+        <v>15.32</v>
       </c>
       <c r="H74" s="1">
-        <v>0.624</v>
+        <v>0.623</v>
       </c>
       <c r="I74" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J74" s="2">
-        <v>19.14</v>
+        <v>19</v>
       </c>
       <c r="K74" s="2">
-        <v>0.0263</v>
+        <v>0.0261</v>
       </c>
       <c r="L74" t="s">
         <v>150</v>
@@ -3930,37 +3930,37 @@
     </row>
     <row r="75" spans="1:13">
       <c r="A75" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="B75" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C75" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D75" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E75" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F75">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="G75">
-        <v>4.03</v>
+        <v>2.29</v>
       </c>
       <c r="H75" s="1">
-        <v>0.623</v>
+        <v>0.613</v>
       </c>
       <c r="I75" t="s">
         <v>146</v>
       </c>
       <c r="J75" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K75" s="2">
-        <v>0.0261</v>
+        <v>0.0468</v>
       </c>
       <c r="L75" t="s">
         <v>150</v>
@@ -3971,13 +3971,13 @@
     </row>
     <row r="76" spans="1:13">
       <c r="A76" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="B76" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="C76" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D76" t="s">
         <v>138</v>
@@ -3986,22 +3986,22 @@
         <v>141</v>
       </c>
       <c r="F76">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="G76">
-        <v>2.32</v>
+        <v>6.93</v>
       </c>
       <c r="H76" s="1">
-        <v>0.622</v>
+        <v>0.609</v>
       </c>
       <c r="I76" t="s">
         <v>146</v>
       </c>
       <c r="J76" s="2">
-        <v>18.83</v>
+        <v>16.21</v>
       </c>
       <c r="K76" s="2">
-        <v>0.0259</v>
+        <v>0.0446</v>
       </c>
       <c r="L76" t="s">
         <v>150</v>
@@ -4012,37 +4012,37 @@
     </row>
     <row r="77" spans="1:13">
       <c r="A77" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B77" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C77" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D77" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E77" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F77">
-        <v>7.5</v>
+        <v>13.5</v>
       </c>
       <c r="G77">
-        <v>6.86</v>
+        <v>11.92</v>
       </c>
       <c r="H77" s="1">
-        <v>0.619</v>
+        <v>0.609</v>
       </c>
       <c r="I77" t="s">
         <v>146</v>
       </c>
       <c r="J77" s="2">
-        <v>18.09</v>
+        <v>16.17</v>
       </c>
       <c r="K77" s="2">
-        <v>0.0497</v>
+        <v>0.0445</v>
       </c>
       <c r="L77" t="s">
         <v>150</v>
@@ -4053,37 +4053,37 @@
     </row>
     <row r="78" spans="1:13">
       <c r="A78" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="B78" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C78" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D78" t="s">
         <v>135</v>
       </c>
       <c r="E78" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F78">
-        <v>19.5</v>
+        <v>2.5</v>
       </c>
       <c r="G78">
-        <v>17.36</v>
+        <v>2.26</v>
       </c>
       <c r="H78" s="1">
-        <v>0.617</v>
+        <v>0.606</v>
       </c>
       <c r="I78" t="s">
         <v>146</v>
       </c>
       <c r="J78" s="2">
-        <v>17.82</v>
+        <v>15.73</v>
       </c>
       <c r="K78" s="2">
-        <v>0.049</v>
+        <v>0.0433</v>
       </c>
       <c r="L78" t="s">
         <v>150</v>
@@ -4094,37 +4094,37 @@
     </row>
     <row r="79" spans="1:13">
       <c r="A79" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C79" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D79" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E79" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F79">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="G79">
-        <v>6.91</v>
+        <v>4.52</v>
       </c>
       <c r="H79" s="1">
-        <v>0.616</v>
+        <v>0.605</v>
       </c>
       <c r="I79" t="s">
         <v>146</v>
       </c>
       <c r="J79" s="2">
-        <v>17.64</v>
+        <v>15.57</v>
       </c>
       <c r="K79" s="2">
-        <v>0.0485</v>
+        <v>0.0428</v>
       </c>
       <c r="L79" t="s">
         <v>150</v>
@@ -4135,7 +4135,7 @@
     </row>
     <row r="80" spans="1:13">
       <c r="A80" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B80" t="s">
         <v>115</v>
@@ -4144,28 +4144,28 @@
         <v>132</v>
       </c>
       <c r="D80" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E80" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F80">
         <v>15.5</v>
       </c>
       <c r="G80">
-        <v>18.39</v>
+        <v>18.25</v>
       </c>
       <c r="H80" s="1">
-        <v>0.611</v>
+        <v>0.605</v>
       </c>
       <c r="I80" t="s">
         <v>147</v>
       </c>
       <c r="J80" s="2">
-        <v>16.57</v>
+        <v>15.55</v>
       </c>
       <c r="K80" s="2">
-        <v>0.0456</v>
+        <v>0.0428</v>
       </c>
       <c r="L80" t="s">
         <v>150</v>
@@ -4176,37 +4176,37 @@
     </row>
     <row r="81" spans="1:13">
       <c r="A81" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B81" t="s">
+        <v>128</v>
+      </c>
+      <c r="C81" t="s">
         <v>118</v>
       </c>
-      <c r="C81" t="s">
-        <v>128</v>
-      </c>
       <c r="D81" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E81" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F81">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="G81">
-        <v>6.92</v>
+        <v>1.36</v>
       </c>
       <c r="H81" s="1">
-        <v>0.61</v>
+        <v>0.605</v>
       </c>
       <c r="I81" t="s">
         <v>146</v>
       </c>
       <c r="J81" s="2">
-        <v>16.39</v>
+        <v>15.49</v>
       </c>
       <c r="K81" s="2">
-        <v>0.0451</v>
+        <v>0.0426</v>
       </c>
       <c r="L81" t="s">
         <v>150</v>
@@ -4217,37 +4217,37 @@
     </row>
     <row r="82" spans="1:13">
       <c r="A82" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="B82" t="s">
         <v>119</v>
       </c>
       <c r="C82" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D82" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E82" t="s">
         <v>141</v>
       </c>
       <c r="F82">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="G82">
-        <v>2.25</v>
+        <v>4.38</v>
       </c>
       <c r="H82" s="1">
-        <v>0.609</v>
+        <v>0.599</v>
       </c>
       <c r="I82" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J82" s="2">
-        <v>16.36</v>
+        <v>14.41</v>
       </c>
       <c r="K82" s="2">
-        <v>0.045</v>
+        <v>0.0396</v>
       </c>
       <c r="L82" t="s">
         <v>150</v>
@@ -4258,37 +4258,37 @@
     </row>
     <row r="83" spans="1:13">
       <c r="A83" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B83" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C83" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="D83" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E83" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F83">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="G83">
-        <v>1.35</v>
+        <v>7</v>
       </c>
       <c r="H83" s="1">
-        <v>0.609</v>
+        <v>0.599</v>
       </c>
       <c r="I83" t="s">
         <v>146</v>
       </c>
       <c r="J83" s="2">
-        <v>16.19</v>
+        <v>14.41</v>
       </c>
       <c r="K83" s="2">
-        <v>0.0445</v>
+        <v>0.0396</v>
       </c>
       <c r="L83" t="s">
         <v>150</v>
@@ -4299,37 +4299,37 @@
     </row>
     <row r="84" spans="1:13">
       <c r="A84" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B84" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C84" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D84" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E84" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F84">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="G84">
-        <v>4.5</v>
+        <v>13.9</v>
       </c>
       <c r="H84" s="1">
-        <v>0.607</v>
+        <v>0.59</v>
       </c>
       <c r="I84" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J84" s="2">
-        <v>15.95</v>
+        <v>12.65</v>
       </c>
       <c r="K84" s="2">
-        <v>0.0439</v>
+        <v>0.0348</v>
       </c>
       <c r="L84" t="s">
         <v>150</v>
@@ -4340,37 +4340,37 @@
     </row>
     <row r="85" spans="1:13">
       <c r="A85" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C85" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D85" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E85" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F85">
-        <v>12.5</v>
+        <v>3.5</v>
       </c>
       <c r="G85">
-        <v>13.07</v>
+        <v>3.59</v>
       </c>
       <c r="H85" s="1">
-        <v>0.596</v>
+        <v>0.583</v>
       </c>
       <c r="I85" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J85" s="2">
-        <v>13.79</v>
+        <v>11.3</v>
       </c>
       <c r="K85" s="2">
-        <v>0.0379</v>
+        <v>0.0311</v>
       </c>
       <c r="L85" t="s">
         <v>150</v>
@@ -4381,37 +4381,37 @@
     </row>
     <row r="86" spans="1:13">
       <c r="A86" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="B86" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C86" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D86" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E86" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F86">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="G86">
-        <v>4.33</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="H86" s="1">
-        <v>0.591</v>
+        <v>0.58</v>
       </c>
       <c r="I86" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J86" s="2">
-        <v>12.74</v>
+        <v>10.75</v>
       </c>
       <c r="K86" s="2">
-        <v>0.035</v>
+        <v>0.0295</v>
       </c>
       <c r="L86" t="s">
         <v>150</v>
@@ -4422,40 +4422,40 @@
     </row>
     <row r="87" spans="1:13">
       <c r="A87" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B87" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C87" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="D87" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E87" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F87">
-        <v>12.5</v>
+        <v>4.5</v>
       </c>
       <c r="G87">
-        <v>13.86</v>
+        <v>4.05</v>
       </c>
       <c r="H87" s="1">
-        <v>0.588</v>
+        <v>0.618</v>
       </c>
       <c r="I87" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J87" s="2">
-        <v>12.19</v>
+        <v>18.06</v>
       </c>
       <c r="K87" s="2">
-        <v>0.0335</v>
+        <v>0.0248</v>
       </c>
       <c r="L87" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M87" t="s">
         <v>153</v>
@@ -4463,40 +4463,40 @@
     </row>
     <row r="88" spans="1:13">
       <c r="A88" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B88" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C88" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D88" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E88" t="s">
         <v>142</v>
       </c>
       <c r="F88">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="G88">
-        <v>9.82</v>
+        <v>14.58</v>
       </c>
       <c r="H88" s="1">
-        <v>0.587</v>
+        <v>0.616</v>
       </c>
       <c r="I88" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J88" s="2">
-        <v>12.14</v>
+        <v>17.51</v>
       </c>
       <c r="K88" s="2">
-        <v>0.0334</v>
+        <v>0.0241</v>
       </c>
       <c r="L88" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M88" t="s">
         <v>153</v>
@@ -4504,40 +4504,40 @@
     </row>
     <row r="89" spans="1:13">
       <c r="A89" t="s">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C89" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D89" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E89" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F89">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="G89">
-        <v>8.07</v>
+        <v>2.23</v>
       </c>
       <c r="H89" s="1">
-        <v>0.587</v>
+        <v>0.615</v>
       </c>
       <c r="I89" t="s">
         <v>146</v>
       </c>
       <c r="J89" s="2">
-        <v>12.03</v>
+        <v>17.38</v>
       </c>
       <c r="K89" s="2">
-        <v>0.0331</v>
+        <v>0.0239</v>
       </c>
       <c r="L89" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M89" t="s">
         <v>153</v>
@@ -4548,37 +4548,37 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C90" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D90" t="s">
         <v>136</v>
       </c>
       <c r="E90" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F90">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="G90">
-        <v>3.6</v>
+        <v>4.09</v>
       </c>
       <c r="H90" s="1">
-        <v>0.582</v>
+        <v>0.612</v>
       </c>
       <c r="I90" t="s">
         <v>146</v>
       </c>
       <c r="J90" s="2">
-        <v>11.03</v>
+        <v>16.78</v>
       </c>
       <c r="K90" s="2">
-        <v>0.0303</v>
+        <v>0.0231</v>
       </c>
       <c r="L90" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M90" t="s">
         <v>153</v>
@@ -4586,37 +4586,37 @@
     </row>
     <row r="91" spans="1:13">
       <c r="A91" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="B91" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C91" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D91" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E91" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F91">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="G91">
-        <v>3.12</v>
+        <v>8.51</v>
       </c>
       <c r="H91" s="1">
-        <v>0.619</v>
+        <v>0.612</v>
       </c>
       <c r="I91" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J91" s="2">
-        <v>18.25</v>
+        <v>16.77</v>
       </c>
       <c r="K91" s="2">
-        <v>0.0251</v>
+        <v>0.0231</v>
       </c>
       <c r="L91" t="s">
         <v>151</v>
@@ -4627,37 +4627,37 @@
     </row>
     <row r="92" spans="1:13">
       <c r="A92" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B92" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C92" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D92" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E92" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F92">
-        <v>20.5</v>
+        <v>4.5</v>
       </c>
       <c r="G92">
-        <v>23.08</v>
+        <v>4.11</v>
       </c>
       <c r="H92" s="1">
-        <v>0.614</v>
+        <v>0.607</v>
       </c>
       <c r="I92" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J92" s="2">
-        <v>17.21</v>
+        <v>15.94</v>
       </c>
       <c r="K92" s="2">
-        <v>0.0237</v>
+        <v>0.0219</v>
       </c>
       <c r="L92" t="s">
         <v>151</v>
@@ -4668,37 +4668,37 @@
     </row>
     <row r="93" spans="1:13">
       <c r="A93" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B93" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C93" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D93" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E93" t="s">
         <v>141</v>
       </c>
       <c r="F93">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="G93">
-        <v>1.45</v>
+        <v>2.39</v>
       </c>
       <c r="H93" s="1">
-        <v>0.611</v>
+        <v>0.607</v>
       </c>
       <c r="I93" t="s">
         <v>146</v>
       </c>
       <c r="J93" s="2">
-        <v>16.73</v>
+        <v>15.81</v>
       </c>
       <c r="K93" s="2">
-        <v>0.023</v>
+        <v>0.0217</v>
       </c>
       <c r="L93" t="s">
         <v>151</v>
@@ -4709,37 +4709,37 @@
     </row>
     <row r="94" spans="1:13">
       <c r="A94" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C94" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="D94" t="s">
         <v>137</v>
       </c>
       <c r="E94" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F94">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="G94">
-        <v>9.59</v>
+        <v>3.2</v>
       </c>
       <c r="H94" s="1">
-        <v>0.61</v>
+        <v>0.607</v>
       </c>
       <c r="I94" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J94" s="2">
-        <v>16.44</v>
+        <v>15.81</v>
       </c>
       <c r="K94" s="2">
-        <v>0.0226</v>
+        <v>0.0217</v>
       </c>
       <c r="L94" t="s">
         <v>151</v>
@@ -4750,37 +4750,37 @@
     </row>
     <row r="95" spans="1:13">
       <c r="A95" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C95" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D95" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E95" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F95">
-        <v>2.5</v>
+        <v>20.5</v>
       </c>
       <c r="G95">
-        <v>3.21</v>
+        <v>18.98</v>
       </c>
       <c r="H95" s="1">
-        <v>0.61</v>
+        <v>0.601</v>
       </c>
       <c r="I95" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J95" s="2">
-        <v>16.38</v>
+        <v>14.71</v>
       </c>
       <c r="K95" s="2">
-        <v>0.0225</v>
+        <v>0.0202</v>
       </c>
       <c r="L95" t="s">
         <v>151</v>
@@ -4791,37 +4791,37 @@
     </row>
     <row r="96" spans="1:13">
       <c r="A96" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B96" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C96" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D96" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E96" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F96">
-        <v>5.5</v>
+        <v>29.5</v>
       </c>
       <c r="G96">
-        <v>5.07</v>
+        <v>32.17</v>
       </c>
       <c r="H96" s="1">
-        <v>0.606</v>
+        <v>0.6</v>
       </c>
       <c r="I96" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J96" s="2">
-        <v>15.74</v>
+        <v>14.63</v>
       </c>
       <c r="K96" s="2">
-        <v>0.0216</v>
+        <v>0.0201</v>
       </c>
       <c r="L96" t="s">
         <v>151</v>
@@ -4832,37 +4832,37 @@
     </row>
     <row r="97" spans="1:13">
       <c r="A97" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C97" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="D97" t="s">
         <v>136</v>
       </c>
       <c r="E97" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F97">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="G97">
-        <v>4.15</v>
+        <v>9.69</v>
       </c>
       <c r="H97" s="1">
-        <v>0.599</v>
+        <v>0.598</v>
       </c>
       <c r="I97" t="s">
         <v>146</v>
       </c>
       <c r="J97" s="2">
-        <v>14.45</v>
+        <v>14.13</v>
       </c>
       <c r="K97" s="2">
-        <v>0.0199</v>
+        <v>0.0194</v>
       </c>
       <c r="L97" t="s">
         <v>151</v>
@@ -4873,37 +4873,37 @@
     </row>
     <row r="98" spans="1:13">
       <c r="A98" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="C98" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D98" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E98" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F98">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="G98">
-        <v>12.77</v>
+        <v>14.32</v>
       </c>
       <c r="H98" s="1">
-        <v>0.594</v>
+        <v>0.595</v>
       </c>
       <c r="I98" t="s">
         <v>147</v>
       </c>
       <c r="J98" s="2">
-        <v>13.43</v>
+        <v>13.61</v>
       </c>
       <c r="K98" s="2">
-        <v>0.0185</v>
+        <v>0.0187</v>
       </c>
       <c r="L98" t="s">
         <v>151</v>
@@ -4914,37 +4914,37 @@
     </row>
     <row r="99" spans="1:13">
       <c r="A99" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C99" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D99" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E99" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F99">
-        <v>12.5</v>
+        <v>5.5</v>
       </c>
       <c r="G99">
-        <v>14.21</v>
+        <v>5.17</v>
       </c>
       <c r="H99" s="1">
         <v>0.589</v>
       </c>
       <c r="I99" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J99" s="2">
-        <v>12.54</v>
+        <v>12.41</v>
       </c>
       <c r="K99" s="2">
-        <v>0.0172</v>
+        <v>0.0171</v>
       </c>
       <c r="L99" t="s">
         <v>151</v>
@@ -4955,37 +4955,37 @@
     </row>
     <row r="100" spans="1:13">
       <c r="A100" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C100" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D100" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E100" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F100">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="G100">
-        <v>5.23</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="H100" s="1">
-        <v>0.586</v>
+        <v>0.588</v>
       </c>
       <c r="I100" t="s">
         <v>146</v>
       </c>
       <c r="J100" s="2">
-        <v>11.94</v>
+        <v>12.17</v>
       </c>
       <c r="K100" s="2">
-        <v>0.0164</v>
+        <v>0.0167</v>
       </c>
       <c r="L100" t="s">
         <v>151</v>
@@ -4996,37 +4996,37 @@
     </row>
     <row r="101" spans="1:13">
       <c r="A101" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C101" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D101" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E101" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F101">
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="G101">
-        <v>8.07</v>
+        <v>12.97</v>
       </c>
       <c r="H101" s="1">
-        <v>0.585</v>
+        <v>0.58</v>
       </c>
       <c r="I101" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J101" s="2">
-        <v>11.7</v>
+        <v>10.67</v>
       </c>
       <c r="K101" s="2">
-        <v>0.0161</v>
+        <v>0.0294</v>
       </c>
       <c r="L101" t="s">
         <v>151</v>
@@ -5037,13 +5037,13 @@
     </row>
     <row r="102" spans="1:13">
       <c r="A102" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C102" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D102" t="s">
         <v>135</v>
@@ -5055,19 +5055,19 @@
         <v>9.5</v>
       </c>
       <c r="G102">
-        <v>10.89</v>
+        <v>10.91</v>
       </c>
       <c r="H102" s="1">
-        <v>0.578</v>
+        <v>0.579</v>
       </c>
       <c r="I102" t="s">
         <v>147</v>
       </c>
       <c r="J102" s="2">
-        <v>10.38</v>
+        <v>10.59</v>
       </c>
       <c r="K102" s="2">
-        <v>0.0143</v>
+        <v>0.0146</v>
       </c>
       <c r="L102" t="s">
         <v>151</v>
@@ -5078,37 +5078,37 @@
     </row>
     <row r="103" spans="1:13">
       <c r="A103" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C103" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D103" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E103" t="s">
         <v>144</v>
       </c>
       <c r="F103">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="G103">
-        <v>12.99</v>
+        <v>16.66</v>
       </c>
       <c r="H103" s="1">
         <v>0.578</v>
       </c>
       <c r="I103" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J103" s="2">
-        <v>10.33</v>
+        <v>10.25</v>
       </c>
       <c r="K103" s="2">
-        <v>0.0284</v>
+        <v>0.0282</v>
       </c>
       <c r="L103" t="s">
         <v>151</v>
@@ -5119,37 +5119,37 @@
     </row>
     <row r="104" spans="1:13">
       <c r="A104" t="s">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="B104" t="s">
+        <v>116</v>
+      </c>
+      <c r="C104" t="s">
         <v>125</v>
       </c>
-      <c r="C104" t="s">
-        <v>121</v>
-      </c>
       <c r="D104" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E104" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F104">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="G104">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="H104" s="1">
-        <v>0.577</v>
+        <v>0.575</v>
       </c>
       <c r="I104" t="s">
         <v>146</v>
       </c>
       <c r="J104" s="2">
-        <v>10.23</v>
+        <v>9.85</v>
       </c>
       <c r="K104" s="2">
-        <v>0.0281</v>
+        <v>0.0135</v>
       </c>
       <c r="L104" t="s">
         <v>151</v>
@@ -5160,16 +5160,16 @@
     </row>
     <row r="105" spans="1:13">
       <c r="A105" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B105" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C105" t="s">
         <v>119</v>
       </c>
       <c r="D105" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E105" t="s">
         <v>141</v>
@@ -5187,10 +5187,10 @@
         <v>147</v>
       </c>
       <c r="J105" s="2">
-        <v>9.69</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="K105" s="2">
-        <v>0.0267</v>
+        <v>0.0269</v>
       </c>
       <c r="L105" t="s">
         <v>151</v>
@@ -5201,37 +5201,37 @@
     </row>
     <row r="106" spans="1:13">
       <c r="A106" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B106" t="s">
         <v>117</v>
       </c>
       <c r="C106" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D106" t="s">
         <v>139</v>
       </c>
       <c r="E106" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F106">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="G106">
-        <v>5.28</v>
+        <v>1.47</v>
       </c>
       <c r="H106" s="1">
-        <v>0.574</v>
+        <v>0.575</v>
       </c>
       <c r="I106" t="s">
         <v>146</v>
       </c>
       <c r="J106" s="2">
-        <v>9.49</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K106" s="2">
-        <v>0.0131</v>
+        <v>0.0133</v>
       </c>
       <c r="L106" t="s">
         <v>151</v>
@@ -5242,37 +5242,37 @@
     </row>
     <row r="107" spans="1:13">
       <c r="A107" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B107" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="C107" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D107" t="s">
         <v>139</v>
       </c>
       <c r="E107" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F107">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="G107">
-        <v>1.47</v>
+        <v>10.08</v>
       </c>
       <c r="H107" s="1">
-        <v>0.572</v>
+        <v>0.574</v>
       </c>
       <c r="I107" t="s">
         <v>146</v>
       </c>
       <c r="J107" s="2">
-        <v>9.220000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="K107" s="2">
-        <v>0.0127</v>
+        <v>0.0264</v>
       </c>
       <c r="L107" t="s">
         <v>151</v>
@@ -5283,37 +5283,37 @@
     </row>
     <row r="108" spans="1:13">
       <c r="A108" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B108" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C108" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D108" t="s">
         <v>135</v>
       </c>
       <c r="E108" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F108">
-        <v>19.5</v>
+        <v>1.5</v>
       </c>
       <c r="G108">
-        <v>20.86</v>
+        <v>1.92</v>
       </c>
       <c r="H108" s="1">
-        <v>0.571</v>
+        <v>0.573</v>
       </c>
       <c r="I108" t="s">
         <v>147</v>
       </c>
       <c r="J108" s="2">
-        <v>8.93</v>
+        <v>9.43</v>
       </c>
       <c r="K108" s="2">
-        <v>0.0123</v>
+        <v>0.0259</v>
       </c>
       <c r="L108" t="s">
         <v>151</v>
@@ -5324,37 +5324,37 @@
     </row>
     <row r="109" spans="1:13">
       <c r="A109" t="s">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="B109" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="C109" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D109" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E109" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F109">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="G109">
-        <v>2.4</v>
+        <v>1.51</v>
       </c>
       <c r="H109" s="1">
-        <v>0.571</v>
+        <v>0.572</v>
       </c>
       <c r="I109" t="s">
         <v>146</v>
       </c>
       <c r="J109" s="2">
-        <v>8.92</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="K109" s="2">
-        <v>0.0123</v>
+        <v>0.0253</v>
       </c>
       <c r="L109" t="s">
         <v>151</v>
@@ -5365,37 +5365,37 @@
     </row>
     <row r="110" spans="1:13">
       <c r="A110" t="s">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="B110" t="s">
+        <v>118</v>
+      </c>
+      <c r="C110" t="s">
         <v>128</v>
       </c>
-      <c r="C110" t="s">
-        <v>118</v>
-      </c>
       <c r="D110" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E110" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F110">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="G110">
-        <v>1.91</v>
+        <v>10.35</v>
       </c>
       <c r="H110" s="1">
-        <v>0.57</v>
+        <v>0.571</v>
       </c>
       <c r="I110" t="s">
         <v>147</v>
       </c>
       <c r="J110" s="2">
-        <v>8.800000000000001</v>
+        <v>9.09</v>
       </c>
       <c r="K110" s="2">
-        <v>0.0242</v>
+        <v>0.0125</v>
       </c>
       <c r="L110" t="s">
         <v>151</v>
@@ -5406,37 +5406,37 @@
     </row>
     <row r="111" spans="1:13">
       <c r="A111" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="B111" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C111" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="D111" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E111" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F111">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="G111">
-        <v>13.84</v>
+        <v>13.1</v>
       </c>
       <c r="H111" s="1">
         <v>0.569</v>
       </c>
       <c r="I111" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J111" s="2">
-        <v>8.69</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="K111" s="2">
-        <v>0.0119</v>
+        <v>0.0237</v>
       </c>
       <c r="L111" t="s">
         <v>151</v>
@@ -5447,37 +5447,37 @@
     </row>
     <row r="112" spans="1:13">
       <c r="A112" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B112" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C112" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D112" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E112" t="s">
         <v>143</v>
       </c>
       <c r="F112">
-        <v>15.5</v>
+        <v>5.5</v>
       </c>
       <c r="G112">
-        <v>16.49</v>
+        <v>5.31</v>
       </c>
       <c r="H112" s="1">
-        <v>0.5659999999999999</v>
+        <v>0.569</v>
       </c>
       <c r="I112" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J112" s="2">
-        <v>8.02</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="K112" s="2">
-        <v>0.0221</v>
+        <v>0.0118</v>
       </c>
       <c r="L112" t="s">
         <v>151</v>
@@ -5491,13 +5491,13 @@
         <v>107</v>
       </c>
       <c r="B113" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C113" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="D113" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E113" t="s">
         <v>141</v>
@@ -5506,19 +5506,19 @@
         <v>1.5</v>
       </c>
       <c r="G113">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H113" s="1">
-        <v>0.5639999999999999</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="I113" t="s">
         <v>147</v>
       </c>
       <c r="J113" s="2">
-        <v>7.69</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="K113" s="2">
-        <v>0.0106</v>
+        <v>0.0117</v>
       </c>
       <c r="L113" t="s">
         <v>151</v>
@@ -5529,37 +5529,37 @@
     </row>
     <row r="114" spans="1:13">
       <c r="A114" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="B114" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="C114" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="D114" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E114" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F114">
-        <v>3.5</v>
+        <v>25.5</v>
       </c>
       <c r="G114">
-        <v>3.53</v>
+        <v>27.08</v>
       </c>
       <c r="H114" s="1">
-        <v>0.5629999999999999</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="I114" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J114" s="2">
-        <v>7.43</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="K114" s="2">
-        <v>0.0204</v>
+        <v>0.0221</v>
       </c>
       <c r="L114" t="s">
         <v>151</v>
@@ -5570,13 +5570,13 @@
     </row>
     <row r="115" spans="1:13">
       <c r="A115" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B115" t="s">
         <v>117</v>
       </c>
       <c r="C115" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D115" t="s">
         <v>139</v>
@@ -5588,19 +5588,19 @@
         <v>9.5</v>
       </c>
       <c r="G115">
-        <v>10.25</v>
+        <v>10.36</v>
       </c>
       <c r="H115" s="1">
-        <v>0.5629999999999999</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="I115" t="s">
         <v>147</v>
       </c>
       <c r="J115" s="2">
-        <v>7.42</v>
+        <v>7.71</v>
       </c>
       <c r="K115" s="2">
-        <v>0.0102</v>
+        <v>0.0106</v>
       </c>
       <c r="L115" t="s">
         <v>151</v>
@@ -5611,7 +5611,7 @@
     </row>
     <row r="116" spans="1:13">
       <c r="A116" t="s">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="B116" t="s">
         <v>128</v>
@@ -5623,13 +5623,13 @@
         <v>137</v>
       </c>
       <c r="E116" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F116">
-        <v>28.5</v>
+        <v>1.5</v>
       </c>
       <c r="G116">
-        <v>30.37</v>
+        <v>1.88</v>
       </c>
       <c r="H116" s="1">
         <v>0.5620000000000001</v>
@@ -5641,7 +5641,7 @@
         <v>7.23</v>
       </c>
       <c r="K116" s="2">
-        <v>0.0199</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="L116" t="s">
         <v>151</v>
@@ -5652,10 +5652,10 @@
     </row>
     <row r="117" spans="1:13">
       <c r="A117" t="s">
-        <v>108</v>
+        <v>42</v>
       </c>
       <c r="B117" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C117" t="s">
         <v>130</v>
@@ -5664,25 +5664,25 @@
         <v>137</v>
       </c>
       <c r="E117" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F117">
-        <v>13.5</v>
+        <v>6.5</v>
       </c>
       <c r="G117">
-        <v>12.24</v>
+        <v>7.06</v>
       </c>
       <c r="H117" s="1">
-        <v>0.5600000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="I117" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J117" s="2">
-        <v>6.84</v>
+        <v>6.79</v>
       </c>
       <c r="K117" s="2">
-        <v>0.0188</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="L117" t="s">
         <v>151</v>
@@ -5696,13 +5696,13 @@
         <v>109</v>
       </c>
       <c r="B118" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C118" t="s">
         <v>134</v>
       </c>
       <c r="D118" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E118" t="s">
         <v>141</v>
@@ -5714,16 +5714,16 @@
         <v>2.92</v>
       </c>
       <c r="H118" s="1">
-        <v>0.5580000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="I118" t="s">
         <v>147</v>
       </c>
       <c r="J118" s="2">
-        <v>6.5</v>
+        <v>6.79</v>
       </c>
       <c r="K118" s="2">
-        <v>0.0179</v>
+        <v>0.0187</v>
       </c>
       <c r="L118" t="s">
         <v>151</v>
@@ -5734,37 +5734,37 @@
     </row>
     <row r="119" spans="1:13">
       <c r="A119" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="B119" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C119" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D119" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E119" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F119">
-        <v>6.5</v>
+        <v>12.5</v>
       </c>
       <c r="G119">
-        <v>7.05</v>
+        <v>13.63</v>
       </c>
       <c r="H119" s="1">
-        <v>0.5570000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="I119" t="s">
         <v>147</v>
       </c>
       <c r="J119" s="2">
-        <v>6.39</v>
+        <v>6.66</v>
       </c>
       <c r="K119" s="2">
-        <v>0.008800000000000001</v>
+        <v>0.0092</v>
       </c>
       <c r="L119" t="s">
         <v>151</v>
@@ -5775,37 +5775,37 @@
     </row>
     <row r="120" spans="1:13">
       <c r="A120" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C120" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D120" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E120" t="s">
         <v>142</v>
       </c>
       <c r="F120">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="G120">
-        <v>10.26</v>
+        <v>12.28</v>
       </c>
       <c r="H120" s="1">
-        <v>0.5570000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="I120" t="s">
         <v>147</v>
       </c>
       <c r="J120" s="2">
-        <v>6.37</v>
+        <v>6.62</v>
       </c>
       <c r="K120" s="2">
-        <v>0.008800000000000001</v>
+        <v>0.0091</v>
       </c>
       <c r="L120" t="s">
         <v>151</v>
@@ -5816,37 +5816,37 @@
     </row>
     <row r="121" spans="1:13">
       <c r="A121" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="B121" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C121" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D121" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E121" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F121">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="G121">
-        <v>13.6</v>
+        <v>12.27</v>
       </c>
       <c r="H121" s="1">
-        <v>0.5570000000000001</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="I121" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J121" s="2">
-        <v>6.32</v>
+        <v>6.56</v>
       </c>
       <c r="K121" s="2">
-        <v>0.008699999999999999</v>
+        <v>0.018</v>
       </c>
       <c r="L121" t="s">
         <v>151</v>
@@ -5857,25 +5857,25 @@
     </row>
     <row r="122" spans="1:13">
       <c r="A122" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="B122" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C122" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D122" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E122" t="s">
         <v>142</v>
       </c>
       <c r="F122">
-        <v>12.5</v>
+        <v>28.5</v>
       </c>
       <c r="G122">
-        <v>13.21</v>
+        <v>30.24</v>
       </c>
       <c r="H122" s="1">
         <v>0.5570000000000001</v>
@@ -5884,10 +5884,10 @@
         <v>147</v>
       </c>
       <c r="J122" s="2">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="K122" s="2">
-        <v>0.0086</v>
+        <v>0.0176</v>
       </c>
       <c r="L122" t="s">
         <v>151</v>
@@ -5898,25 +5898,25 @@
     </row>
     <row r="123" spans="1:13">
       <c r="A123" t="s">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="B123" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C123" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D123" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E123" t="s">
         <v>141</v>
       </c>
       <c r="F123">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="G123">
-        <v>1.63</v>
+        <v>3.56</v>
       </c>
       <c r="H123" s="1">
         <v>0.556</v>
@@ -5925,10 +5925,10 @@
         <v>146</v>
       </c>
       <c r="J123" s="2">
-        <v>6.14</v>
+        <v>6.24</v>
       </c>
       <c r="K123" s="2">
-        <v>0.008399999999999999</v>
+        <v>0.0171</v>
       </c>
       <c r="L123" t="s">
         <v>151</v>
@@ -5939,19 +5939,19 @@
     </row>
     <row r="124" spans="1:13">
       <c r="A124" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="B124" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C124" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D124" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E124" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F124">
         <v>3.5</v>
@@ -5960,16 +5960,16 @@
         <v>3.41</v>
       </c>
       <c r="H124" s="1">
-        <v>0.555</v>
+        <v>0.556</v>
       </c>
       <c r="I124" t="s">
         <v>146</v>
       </c>
       <c r="J124" s="2">
-        <v>5.98</v>
+        <v>6.14</v>
       </c>
       <c r="K124" s="2">
-        <v>0.008200000000000001</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="L124" t="s">
         <v>151</v>
@@ -5980,37 +5980,37 @@
     </row>
     <row r="125" spans="1:13">
       <c r="A125" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="B125" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C125" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D125" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E125" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F125">
-        <v>1.5</v>
+        <v>21.5</v>
       </c>
       <c r="G125">
-        <v>1.86</v>
+        <v>22.55</v>
       </c>
       <c r="H125" s="1">
-        <v>0.554</v>
+        <v>0.556</v>
       </c>
       <c r="I125" t="s">
         <v>147</v>
       </c>
       <c r="J125" s="2">
-        <v>5.75</v>
+        <v>6.09</v>
       </c>
       <c r="K125" s="2">
-        <v>0.007900000000000001</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="L125" t="s">
         <v>151</v>
@@ -6021,37 +6021,37 @@
     </row>
     <row r="126" spans="1:13">
       <c r="A126" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="B126" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C126" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D126" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E126" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F126">
-        <v>14.5</v>
+        <v>1.5</v>
       </c>
       <c r="G126">
-        <v>15.95</v>
+        <v>1.64</v>
       </c>
       <c r="H126" s="1">
-        <v>0.552</v>
+        <v>0.555</v>
       </c>
       <c r="I126" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J126" s="2">
-        <v>5.31</v>
+        <v>5.87</v>
       </c>
       <c r="K126" s="2">
-        <v>0.0146</v>
+        <v>0.0081</v>
       </c>
       <c r="L126" t="s">
         <v>151</v>
@@ -6062,37 +6062,37 @@
     </row>
     <row r="127" spans="1:13">
       <c r="A127" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="B127" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C127" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D127" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E127" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F127">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="G127">
-        <v>1.85</v>
+        <v>7.92</v>
       </c>
       <c r="H127" s="1">
-        <v>0.55</v>
+        <v>0.553</v>
       </c>
       <c r="I127" t="s">
         <v>147</v>
       </c>
       <c r="J127" s="2">
-        <v>5.09</v>
+        <v>5.49</v>
       </c>
       <c r="K127" s="2">
-        <v>0.007</v>
+        <v>0.0151</v>
       </c>
       <c r="L127" t="s">
         <v>151</v>
@@ -6103,37 +6103,37 @@
     </row>
     <row r="128" spans="1:13">
       <c r="A128" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="B128" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C128" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D128" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E128" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F128">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="G128">
-        <v>8.710000000000001</v>
+        <v>1.85</v>
       </c>
       <c r="H128" s="1">
-        <v>0.55</v>
+        <v>0.551</v>
       </c>
       <c r="I128" t="s">
         <v>147</v>
       </c>
       <c r="J128" s="2">
-        <v>4.98</v>
+        <v>5.17</v>
       </c>
       <c r="K128" s="2">
-        <v>0.0137</v>
+        <v>0.0071</v>
       </c>
       <c r="L128" t="s">
         <v>151</v>
@@ -6144,25 +6144,25 @@
     </row>
     <row r="129" spans="1:13">
       <c r="A129" t="s">
-        <v>38</v>
+        <v>113</v>
       </c>
       <c r="B129" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C129" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D129" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E129" t="s">
         <v>144</v>
       </c>
       <c r="F129">
-        <v>3.5</v>
+        <v>18.5</v>
       </c>
       <c r="G129">
-        <v>3.91</v>
+        <v>19.49</v>
       </c>
       <c r="H129" s="1">
         <v>0.549</v>
@@ -6171,10 +6171,10 @@
         <v>147</v>
       </c>
       <c r="J129" s="2">
-        <v>4.84</v>
+        <v>4.76</v>
       </c>
       <c r="K129" s="2">
-        <v>0.0066</v>
+        <v>0.0131</v>
       </c>
       <c r="L129" t="s">
         <v>151</v>
@@ -6185,37 +6185,37 @@
     </row>
     <row r="130" spans="1:13">
       <c r="A130" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B130" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="C130" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D130" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E130" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F130">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="G130">
-        <v>7.87</v>
+        <v>9.33</v>
       </c>
       <c r="H130" s="1">
-        <v>0.547</v>
+        <v>0.548</v>
       </c>
       <c r="I130" t="s">
         <v>147</v>
       </c>
       <c r="J130" s="2">
-        <v>4.42</v>
+        <v>4.53</v>
       </c>
       <c r="K130" s="2">
-        <v>0.0121</v>
+        <v>0.0125</v>
       </c>
       <c r="L130" t="s">
         <v>151</v>
@@ -6226,37 +6226,37 @@
     </row>
     <row r="131" spans="1:13">
       <c r="A131" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B131" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C131" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D131" t="s">
         <v>138</v>
       </c>
       <c r="E131" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F131">
-        <v>18.5</v>
+        <v>6.5</v>
       </c>
       <c r="G131">
-        <v>19.5</v>
+        <v>6.97</v>
       </c>
       <c r="H131" s="1">
-        <v>0.547</v>
+        <v>0.546</v>
       </c>
       <c r="I131" t="s">
         <v>147</v>
       </c>
       <c r="J131" s="2">
-        <v>4.37</v>
+        <v>4.24</v>
       </c>
       <c r="K131" s="2">
-        <v>0.012</v>
+        <v>0.0058</v>
       </c>
       <c r="L131" t="s">
         <v>151</v>
@@ -6267,25 +6267,25 @@
     </row>
     <row r="132" spans="1:13">
       <c r="A132" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="B132" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C132" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D132" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E132" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F132">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="G132">
-        <v>1.83</v>
+        <v>3.9</v>
       </c>
       <c r="H132" s="1">
         <v>0.546</v>
@@ -6294,10 +6294,10 @@
         <v>147</v>
       </c>
       <c r="J132" s="2">
-        <v>4.15</v>
+        <v>4.21</v>
       </c>
       <c r="K132" s="2">
-        <v>0.0114</v>
+        <v>0.0058</v>
       </c>
       <c r="L132" t="s">
         <v>151</v>
@@ -6308,25 +6308,25 @@
     </row>
     <row r="133" spans="1:13">
       <c r="A133" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B133" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C133" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D133" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E133" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F133">
-        <v>18.5</v>
+        <v>1.5</v>
       </c>
       <c r="G133">
-        <v>18.96</v>
+        <v>1.83</v>
       </c>
       <c r="H133" s="1">
         <v>0.545</v>
@@ -6335,10 +6335,10 @@
         <v>147</v>
       </c>
       <c r="J133" s="2">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
       <c r="K133" s="2">
-        <v>0.011</v>
+        <v>0.0109</v>
       </c>
       <c r="L133" t="s">
         <v>151</v>
@@ -6349,37 +6349,37 @@
     </row>
     <row r="134" spans="1:13">
       <c r="A134" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="B134" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C134" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D134" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E134" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F134">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="G134">
-        <v>5.42</v>
+        <v>7.93</v>
       </c>
       <c r="H134" s="1">
-        <v>0.545</v>
+        <v>0.544</v>
       </c>
       <c r="I134" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J134" s="2">
-        <v>3.95</v>
+        <v>3.86</v>
       </c>
       <c r="K134" s="2">
-        <v>0.0109</v>
+        <v>0.0106</v>
       </c>
       <c r="L134" t="s">
         <v>151</v>
@@ -6390,10 +6390,10 @@
     </row>
     <row r="135" spans="1:13">
       <c r="A135" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="B135" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C135" t="s">
         <v>119</v>
@@ -6411,16 +6411,16 @@
         <v>1.82</v>
       </c>
       <c r="H135" s="1">
-        <v>0.544</v>
+        <v>0.543</v>
       </c>
       <c r="I135" t="s">
         <v>147</v>
       </c>
       <c r="J135" s="2">
-        <v>3.78</v>
+        <v>3.71</v>
       </c>
       <c r="K135" s="2">
-        <v>0.0104</v>
+        <v>0.0102</v>
       </c>
       <c r="L135" t="s">
         <v>151</v>
@@ -6431,37 +6431,37 @@
     </row>
     <row r="136" spans="1:13">
       <c r="A136" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="B136" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C136" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D136" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E136" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F136">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="G136">
-        <v>9.92</v>
+        <v>8.5</v>
       </c>
       <c r="H136" s="1">
-        <v>0.543</v>
+        <v>0.541</v>
       </c>
       <c r="I136" t="s">
         <v>147</v>
       </c>
       <c r="J136" s="2">
-        <v>3.59</v>
+        <v>3.34</v>
       </c>
       <c r="K136" s="2">
-        <v>0.0049</v>
+        <v>0.0092</v>
       </c>
       <c r="L136" t="s">
         <v>151</v>
@@ -6472,40 +6472,40 @@
     </row>
     <row r="137" spans="1:13">
       <c r="A137" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="B137" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C137" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="D137" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E137" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F137">
-        <v>11.5</v>
+        <v>2.5</v>
       </c>
       <c r="G137">
-        <v>12.08</v>
+        <v>2.83</v>
       </c>
       <c r="H137" s="1">
-        <v>0.54</v>
+        <v>0.538</v>
       </c>
       <c r="I137" t="s">
         <v>147</v>
       </c>
       <c r="J137" s="2">
-        <v>3.13</v>
+        <v>2.79</v>
       </c>
       <c r="K137" s="2">
-        <v>0.0086</v>
+        <v>0.0038</v>
       </c>
       <c r="L137" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M137" t="s">
         <v>153</v>
@@ -6513,37 +6513,37 @@
     </row>
     <row r="138" spans="1:13">
       <c r="A138" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="B138" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C138" t="s">
         <v>121</v>
       </c>
       <c r="D138" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E138" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F138">
-        <v>32.5</v>
+        <v>17.5</v>
       </c>
       <c r="G138">
-        <v>31.81</v>
+        <v>18.22</v>
       </c>
       <c r="H138" s="1">
-        <v>0.539</v>
+        <v>0.538</v>
       </c>
       <c r="I138" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J138" s="2">
-        <v>2.96</v>
+        <v>2.71</v>
       </c>
       <c r="K138" s="2">
-        <v>0.0081</v>
+        <v>0.0075</v>
       </c>
       <c r="L138" t="s">
         <v>152</v>
@@ -6554,37 +6554,37 @@
     </row>
     <row r="139" spans="1:13">
       <c r="A139" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="B139" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C139" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="D139" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E139" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F139">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="G139">
-        <v>2.83</v>
+        <v>5.46</v>
       </c>
       <c r="H139" s="1">
-        <v>0.538</v>
+        <v>0.537</v>
       </c>
       <c r="I139" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J139" s="2">
-        <v>2.77</v>
+        <v>2.61</v>
       </c>
       <c r="K139" s="2">
-        <v>0.0038</v>
+        <v>0.0072</v>
       </c>
       <c r="L139" t="s">
         <v>152</v>
@@ -6595,37 +6595,37 @@
     </row>
     <row r="140" spans="1:13">
       <c r="A140" t="s">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="B140" t="s">
+        <v>131</v>
+      </c>
+      <c r="C140" t="s">
         <v>115</v>
       </c>
-      <c r="C140" t="s">
-        <v>132</v>
-      </c>
       <c r="D140" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E140" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F140">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="G140">
-        <v>7.86</v>
+        <v>9.85</v>
       </c>
       <c r="H140" s="1">
-        <v>0.537</v>
+        <v>0.536</v>
       </c>
       <c r="I140" t="s">
         <v>147</v>
       </c>
       <c r="J140" s="2">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="K140" s="2">
-        <v>0.0068</v>
+        <v>0.0033</v>
       </c>
       <c r="L140" t="s">
         <v>152</v>
@@ -6636,37 +6636,37 @@
     </row>
     <row r="141" spans="1:13">
       <c r="A141" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="B141" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C141" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D141" t="s">
         <v>138</v>
       </c>
       <c r="E141" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F141">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="G141">
-        <v>17.8</v>
+        <v>14.24</v>
       </c>
       <c r="H141" s="1">
-        <v>0.534</v>
+        <v>0.536</v>
       </c>
       <c r="I141" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J141" s="2">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="K141" s="2">
-        <v>0.0028</v>
+        <v>0.0062</v>
       </c>
       <c r="L141" t="s">
         <v>152</v>
@@ -6677,37 +6677,37 @@
     </row>
     <row r="142" spans="1:13">
       <c r="A142" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="B142" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C142" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="D142" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E142" t="s">
         <v>142</v>
       </c>
       <c r="F142">
-        <v>7.5</v>
+        <v>29.5</v>
       </c>
       <c r="G142">
-        <v>7.95</v>
+        <v>30.65</v>
       </c>
       <c r="H142" s="1">
-        <v>0.533</v>
+        <v>0.535</v>
       </c>
       <c r="I142" t="s">
         <v>147</v>
       </c>
       <c r="J142" s="2">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="K142" s="2">
-        <v>0.0023</v>
+        <v>0.0058</v>
       </c>
       <c r="L142" t="s">
         <v>152</v>
@@ -6718,37 +6718,37 @@
     </row>
     <row r="143" spans="1:13">
       <c r="A143" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="B143" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="C143" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D143" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E143" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F143">
-        <v>5.5</v>
+        <v>18.5</v>
       </c>
       <c r="G143">
-        <v>5.86</v>
+        <v>17.79</v>
       </c>
       <c r="H143" s="1">
-        <v>0.532</v>
+        <v>0.535</v>
       </c>
       <c r="I143" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J143" s="2">
-        <v>1.59</v>
+        <v>2.04</v>
       </c>
       <c r="K143" s="2">
-        <v>0.0044</v>
+        <v>0.0028</v>
       </c>
       <c r="L143" t="s">
         <v>152</v>
@@ -6759,37 +6759,37 @@
     </row>
     <row r="144" spans="1:13">
       <c r="A144" t="s">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="B144" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="C144" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="D144" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E144" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F144">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="G144">
-        <v>3.53</v>
+        <v>5.86</v>
       </c>
       <c r="H144" s="1">
         <v>0.531</v>
       </c>
       <c r="I144" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J144" s="2">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="K144" s="2">
-        <v>0.0036</v>
+        <v>0.0038</v>
       </c>
       <c r="L144" t="s">
         <v>152</v>
@@ -6800,37 +6800,37 @@
     </row>
     <row r="145" spans="1:13">
       <c r="A145" t="s">
-        <v>42</v>
+        <v>109</v>
       </c>
       <c r="B145" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C145" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="D145" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E145" t="s">
         <v>143</v>
       </c>
       <c r="F145">
-        <v>22.5</v>
+        <v>3.5</v>
       </c>
       <c r="G145">
-        <v>23.35</v>
+        <v>3.53</v>
       </c>
       <c r="H145" s="1">
-        <v>0.53</v>
+        <v>0.531</v>
       </c>
       <c r="I145" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J145" s="2">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="K145" s="2">
-        <v>0.0016</v>
+        <v>0.0035</v>
       </c>
       <c r="L145" t="s">
         <v>152</v>
@@ -6841,34 +6841,34 @@
     </row>
     <row r="146" spans="1:13">
       <c r="A146" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B146" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C146" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D146" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E146" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F146">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="G146">
-        <v>14.05</v>
+        <v>13.07</v>
       </c>
       <c r="H146" s="1">
-        <v>0.527</v>
+        <v>0.53</v>
       </c>
       <c r="I146" t="s">
         <v>147</v>
       </c>
       <c r="J146" s="2">
-        <v>0.55</v>
+        <v>1.1</v>
       </c>
       <c r="K146" s="2">
         <v>0.0015</v>
@@ -6891,28 +6891,28 @@
         <v>132</v>
       </c>
       <c r="D147" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E147" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F147">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="G147">
-        <v>2.74</v>
+        <v>7.23</v>
       </c>
       <c r="H147" s="1">
-        <v>0.527</v>
+        <v>0.528</v>
       </c>
       <c r="I147" t="s">
         <v>146</v>
       </c>
       <c r="J147" s="2">
-        <v>0.52</v>
+        <v>0.78</v>
       </c>
       <c r="K147" s="2">
-        <v>0.0014</v>
+        <v>0.0021</v>
       </c>
       <c r="L147" t="s">
         <v>152</v>
@@ -6923,37 +6923,37 @@
     </row>
     <row r="148" spans="1:13">
       <c r="A148" t="s">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="B148" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C148" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D148" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E148" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F148">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="G148">
-        <v>1.77</v>
+        <v>11.78</v>
       </c>
       <c r="H148" s="1">
-        <v>0.526</v>
+        <v>0.525</v>
       </c>
       <c r="I148" t="s">
         <v>147</v>
       </c>
       <c r="J148" s="2">
-        <v>0.42</v>
+        <v>0.28</v>
       </c>
       <c r="K148" s="2">
-        <v>0.0011</v>
+        <v>0.0004</v>
       </c>
       <c r="L148" t="s">
         <v>152</v>
@@ -6964,37 +6964,37 @@
     </row>
     <row r="149" spans="1:13">
       <c r="A149" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="B149" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C149" t="s">
         <v>120</v>
       </c>
       <c r="D149" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E149" t="s">
         <v>142</v>
       </c>
       <c r="F149">
-        <v>29.5</v>
+        <v>5.5</v>
       </c>
       <c r="G149">
-        <v>30.35</v>
+        <v>5.71</v>
       </c>
       <c r="H149" s="1">
-        <v>0.526</v>
+        <v>0.523</v>
       </c>
       <c r="I149" t="s">
         <v>147</v>
       </c>
       <c r="J149" s="2">
-        <v>0.34</v>
+        <v>-0.09</v>
       </c>
       <c r="K149" s="2">
-        <v>0.0009</v>
+        <v>0</v>
       </c>
       <c r="L149" t="s">
         <v>152</v>
@@ -7005,37 +7005,37 @@
     </row>
     <row r="150" spans="1:13">
       <c r="A150" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="B150" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C150" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D150" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E150" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F150">
-        <v>3.5</v>
+        <v>11.5</v>
       </c>
       <c r="G150">
-        <v>3.62</v>
+        <v>11.05</v>
       </c>
       <c r="H150" s="1">
-        <v>0.526</v>
+        <v>0.522</v>
       </c>
       <c r="I150" t="s">
         <v>146</v>
       </c>
       <c r="J150" s="2">
-        <v>0.33</v>
+        <v>-0.42</v>
       </c>
       <c r="K150" s="2">
-        <v>0.0009</v>
+        <v>0</v>
       </c>
       <c r="L150" t="s">
         <v>152</v>
@@ -7046,37 +7046,37 @@
     </row>
     <row r="151" spans="1:13">
       <c r="A151" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="B151" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C151" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="D151" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E151" t="s">
         <v>142</v>
       </c>
       <c r="F151">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="G151">
-        <v>9.75</v>
+        <v>7.79</v>
       </c>
       <c r="H151" s="1">
-        <v>0.525</v>
+        <v>0.521</v>
       </c>
       <c r="I151" t="s">
         <v>147</v>
       </c>
       <c r="J151" s="2">
-        <v>0.21</v>
+        <v>-0.5</v>
       </c>
       <c r="K151" s="2">
-        <v>0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="L151" t="s">
         <v>152</v>
@@ -7087,37 +7087,37 @@
     </row>
     <row r="152" spans="1:13">
       <c r="A152" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="B152" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C152" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D152" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E152" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F152">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="G152">
-        <v>10.8</v>
+        <v>19.18</v>
       </c>
       <c r="H152" s="1">
-        <v>0.524</v>
+        <v>0.519</v>
       </c>
       <c r="I152" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J152" s="2">
-        <v>0.09</v>
+        <v>-0.85</v>
       </c>
       <c r="K152" s="2">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="L152" t="s">
         <v>152</v>
@@ -7128,34 +7128,34 @@
     </row>
     <row r="153" spans="1:13">
       <c r="A153" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="B153" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C153" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D153" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E153" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F153">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="G153">
-        <v>9.720000000000001</v>
+        <v>1.74</v>
       </c>
       <c r="H153" s="1">
-        <v>0.522</v>
+        <v>0.517</v>
       </c>
       <c r="I153" t="s">
         <v>147</v>
       </c>
       <c r="J153" s="2">
-        <v>-0.27</v>
+        <v>-1.32</v>
       </c>
       <c r="K153" s="2">
         <v>0</v>
@@ -7172,31 +7172,31 @@
         <v>82</v>
       </c>
       <c r="B154" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C154" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D154" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E154" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F154">
-        <v>11.5</v>
+        <v>35.5</v>
       </c>
       <c r="G154">
-        <v>11.05</v>
+        <v>35.99</v>
       </c>
       <c r="H154" s="1">
-        <v>0.522</v>
+        <v>0.515</v>
       </c>
       <c r="I154" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J154" s="2">
-        <v>-0.43</v>
+        <v>-1.73</v>
       </c>
       <c r="K154" s="2">
         <v>0</v>
@@ -7210,34 +7210,34 @@
     </row>
     <row r="155" spans="1:13">
       <c r="A155" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="B155" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C155" t="s">
         <v>124</v>
       </c>
       <c r="D155" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E155" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F155">
-        <v>17.5</v>
+        <v>23.5</v>
       </c>
       <c r="G155">
-        <v>17.87</v>
+        <v>23.77</v>
       </c>
       <c r="H155" s="1">
-        <v>0.52</v>
+        <v>0.514</v>
       </c>
       <c r="I155" t="s">
         <v>147</v>
       </c>
       <c r="J155" s="2">
-        <v>-0.79</v>
+        <v>-1.83</v>
       </c>
       <c r="K155" s="2">
         <v>0</v>
@@ -7251,34 +7251,34 @@
     </row>
     <row r="156" spans="1:13">
       <c r="A156" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="B156" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C156" t="s">
         <v>120</v>
       </c>
       <c r="D156" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E156" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F156">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="G156">
-        <v>2.69</v>
+        <v>3.67</v>
       </c>
       <c r="H156" s="1">
-        <v>0.52</v>
+        <v>0.514</v>
       </c>
       <c r="I156" t="s">
         <v>146</v>
       </c>
       <c r="J156" s="2">
-        <v>-0.82</v>
+        <v>-1.95</v>
       </c>
       <c r="K156" s="2">
         <v>0</v>
@@ -7292,34 +7292,34 @@
     </row>
     <row r="157" spans="1:13">
       <c r="A157" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="B157" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C157" t="s">
         <v>117</v>
       </c>
       <c r="D157" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E157" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F157">
         <v>2.5</v>
       </c>
       <c r="G157">
-        <v>2.61</v>
+        <v>2.72</v>
       </c>
       <c r="H157" s="1">
-        <v>0.516</v>
+        <v>0.511</v>
       </c>
       <c r="I157" t="s">
         <v>146</v>
       </c>
       <c r="J157" s="2">
-        <v>-1.54</v>
+        <v>-2.41</v>
       </c>
       <c r="K157" s="2">
         <v>0</v>
@@ -7333,34 +7333,34 @@
     </row>
     <row r="158" spans="1:13">
       <c r="A158" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="B158" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C158" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D158" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E158" t="s">
         <v>142</v>
       </c>
       <c r="F158">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="G158">
-        <v>11.7</v>
+        <v>12.67</v>
       </c>
       <c r="H158" s="1">
-        <v>0.515</v>
+        <v>0.51</v>
       </c>
       <c r="I158" t="s">
         <v>147</v>
       </c>
       <c r="J158" s="2">
-        <v>-1.68</v>
+        <v>-2.58</v>
       </c>
       <c r="K158" s="2">
         <v>0</v>
@@ -7374,34 +7374,34 @@
     </row>
     <row r="159" spans="1:13">
       <c r="A159" t="s">
-        <v>111</v>
+        <v>29</v>
       </c>
       <c r="B159" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C159" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D159" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E159" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F159">
-        <v>19.5</v>
+        <v>29.5</v>
       </c>
       <c r="G159">
-        <v>19.26</v>
+        <v>29.7</v>
       </c>
       <c r="H159" s="1">
-        <v>0.514</v>
+        <v>0.507</v>
       </c>
       <c r="I159" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J159" s="2">
-        <v>-1.9</v>
+        <v>-3.21</v>
       </c>
       <c r="K159" s="2">
         <v>0</v>
@@ -7415,34 +7415,34 @@
     </row>
     <row r="160" spans="1:13">
       <c r="A160" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="B160" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C160" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D160" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E160" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F160">
-        <v>11.5</v>
+        <v>3.5</v>
       </c>
       <c r="G160">
-        <v>11.64</v>
+        <v>3.68</v>
       </c>
       <c r="H160" s="1">
-        <v>0.513</v>
+        <v>0.501</v>
       </c>
       <c r="I160" t="s">
         <v>147</v>
       </c>
       <c r="J160" s="2">
-        <v>-2.1</v>
+        <v>-4.32</v>
       </c>
       <c r="K160" s="2">
         <v>0</v>
@@ -7454,172 +7454,8 @@
         <v>153</v>
       </c>
     </row>
-    <row r="161" spans="1:13">
-      <c r="A161" t="s">
-        <v>101</v>
-      </c>
-      <c r="B161" t="s">
-        <v>123</v>
-      </c>
-      <c r="C161" t="s">
-        <v>120</v>
-      </c>
-      <c r="D161" t="s">
-        <v>135</v>
-      </c>
-      <c r="E161" t="s">
-        <v>144</v>
-      </c>
-      <c r="F161">
-        <v>7.5</v>
-      </c>
-      <c r="G161">
-        <v>7.75</v>
-      </c>
-      <c r="H161" s="1">
-        <v>0.511</v>
-      </c>
-      <c r="I161" t="s">
-        <v>146</v>
-      </c>
-      <c r="J161" s="2">
-        <v>-2.4</v>
-      </c>
-      <c r="K161" s="2">
-        <v>0</v>
-      </c>
-      <c r="L161" t="s">
-        <v>152</v>
-      </c>
-      <c r="M161" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="162" spans="1:13">
-      <c r="A162" t="s">
-        <v>31</v>
-      </c>
-      <c r="B162" t="s">
-        <v>126</v>
-      </c>
-      <c r="C162" t="s">
-        <v>116</v>
-      </c>
-      <c r="D162" t="s">
-        <v>136</v>
-      </c>
-      <c r="E162" t="s">
-        <v>142</v>
-      </c>
-      <c r="F162">
-        <v>29.5</v>
-      </c>
-      <c r="G162">
-        <v>29.78</v>
-      </c>
-      <c r="H162" s="1">
-        <v>0.51</v>
-      </c>
-      <c r="I162" t="s">
-        <v>147</v>
-      </c>
-      <c r="J162" s="2">
-        <v>-2.65</v>
-      </c>
-      <c r="K162" s="2">
-        <v>0</v>
-      </c>
-      <c r="L162" t="s">
-        <v>152</v>
-      </c>
-      <c r="M162" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="163" spans="1:13">
-      <c r="A163" t="s">
-        <v>84</v>
-      </c>
-      <c r="B163" t="s">
-        <v>115</v>
-      </c>
-      <c r="C163" t="s">
-        <v>132</v>
-      </c>
-      <c r="D163" t="s">
-        <v>138</v>
-      </c>
-      <c r="E163" t="s">
-        <v>142</v>
-      </c>
-      <c r="F163">
-        <v>24.5</v>
-      </c>
-      <c r="G163">
-        <v>24.7</v>
-      </c>
-      <c r="H163" s="1">
-        <v>0.507</v>
-      </c>
-      <c r="I163" t="s">
-        <v>147</v>
-      </c>
-      <c r="J163" s="2">
-        <v>-3.22</v>
-      </c>
-      <c r="K163" s="2">
-        <v>0</v>
-      </c>
-      <c r="L163" t="s">
-        <v>152</v>
-      </c>
-      <c r="M163" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="164" spans="1:13">
-      <c r="A164" t="s">
-        <v>103</v>
-      </c>
-      <c r="B164" t="s">
-        <v>130</v>
-      </c>
-      <c r="C164" t="s">
-        <v>119</v>
-      </c>
-      <c r="D164" t="s">
-        <v>137</v>
-      </c>
-      <c r="E164" t="s">
-        <v>142</v>
-      </c>
-      <c r="F164">
-        <v>22.5</v>
-      </c>
-      <c r="G164">
-        <v>22.32</v>
-      </c>
-      <c r="H164" s="1">
-        <v>0.507</v>
-      </c>
-      <c r="I164" t="s">
-        <v>146</v>
-      </c>
-      <c r="J164" s="2">
-        <v>-3.29</v>
-      </c>
-      <c r="K164" s="2">
-        <v>0</v>
-      </c>
-      <c r="L164" t="s">
-        <v>152</v>
-      </c>
-      <c r="M164" t="s">
-        <v>153</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="L2:L164">
+  <conditionalFormatting sqref="L2:L160">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="S Tier">
       <formula>NOT(ISERROR(SEARCH("S Tier",L2)))</formula>
     </cfRule>

--- a/output/processed_props.xlsx
+++ b/output/processed_props.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="75">
   <si>
     <t>Player</t>
   </si>
@@ -61,6 +61,9 @@
     <t>Jabari Smith Jr.</t>
   </si>
   <si>
+    <t>Cade Cunningham</t>
+  </si>
+  <si>
     <t>Amen Thompson</t>
   </si>
   <si>
@@ -88,13 +91,13 @@
     <t>Ty Jerome</t>
   </si>
   <si>
-    <t>Cade Cunningham</t>
-  </si>
-  <si>
     <t>Clint Capela</t>
   </si>
   <si>
     <t>Tari Eason</t>
+  </si>
+  <si>
+    <t>Alperen Sengun</t>
   </si>
   <si>
     <t>Malik Monk</t>
@@ -116,9 +119,6 @@
   </si>
   <si>
     <t>Russell Westbrook</t>
-  </si>
-  <si>
-    <t>Alperen Sengun</t>
   </si>
   <si>
     <t>Jaylen Wells</t>
@@ -154,10 +154,13 @@
     <t>Duncan Robinson</t>
   </si>
   <si>
-    <t>Devin Vassell</t>
+    <t>Keegan Murray</t>
   </si>
   <si>
-    <t>Keegan Murray</t>
+    <t>Cam Spencer</t>
+  </si>
+  <si>
+    <t>Devin Vassell</t>
   </si>
   <si>
     <t>Brice Sensabaugh</t>
@@ -167,9 +170,6 @@
   </si>
   <si>
     <t>Keldon Johnson</t>
-  </si>
-  <si>
-    <t>Cam Spencer</t>
   </si>
   <si>
     <t>Nique Clifford</t>
@@ -641,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L69"/>
+  <dimension ref="A1:L185"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -814,31 +814,31 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E5">
-        <v>29.5</v>
+        <v>9.5</v>
       </c>
       <c r="F5">
-        <v>24.19</v>
+        <v>8.1</v>
       </c>
       <c r="G5" s="1">
-        <v>0.666</v>
+        <v>0.67</v>
       </c>
       <c r="H5" t="s">
         <v>66</v>
       </c>
       <c r="I5" s="2">
-        <v>27.05</v>
+        <v>27.87</v>
       </c>
       <c r="J5" s="2">
-        <v>0.07439999999999999</v>
+        <v>0.0766</v>
       </c>
       <c r="K5" t="s">
         <v>68</v>
@@ -852,34 +852,34 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E6">
-        <v>1.5</v>
+        <v>29.5</v>
       </c>
       <c r="F6">
-        <v>1.05</v>
+        <v>24.19</v>
       </c>
       <c r="G6" s="1">
-        <v>0.772</v>
+        <v>0.666</v>
       </c>
       <c r="H6" t="s">
         <v>66</v>
       </c>
       <c r="I6" s="2">
-        <v>47.4</v>
+        <v>27.05</v>
       </c>
       <c r="J6" s="2">
-        <v>0.06519999999999999</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="K6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L6" t="s">
         <v>74</v>
@@ -890,31 +890,31 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
         <v>64</v>
       </c>
       <c r="E7">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="F7">
-        <v>3.24</v>
+        <v>1.05</v>
       </c>
       <c r="G7" s="1">
-        <v>0.736</v>
+        <v>0.772</v>
       </c>
       <c r="H7" t="s">
         <v>66</v>
       </c>
       <c r="I7" s="2">
-        <v>40.6</v>
+        <v>47.4</v>
       </c>
       <c r="J7" s="2">
-        <v>0.0558</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="K7" t="s">
         <v>69</v>
@@ -928,31 +928,31 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E8">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="F8">
-        <v>2.48</v>
+        <v>3.24</v>
       </c>
       <c r="G8" s="1">
-        <v>0.708</v>
+        <v>0.736</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I8" s="2">
-        <v>35.24</v>
+        <v>40.6</v>
       </c>
       <c r="J8" s="2">
-        <v>0.0485</v>
+        <v>0.0558</v>
       </c>
       <c r="K8" t="s">
         <v>69</v>
@@ -963,7 +963,7 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
         <v>55</v>
@@ -972,25 +972,25 @@
         <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E9">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F9">
-        <v>1.98</v>
+        <v>2.48</v>
       </c>
       <c r="G9" s="1">
-        <v>0.706</v>
+        <v>0.708</v>
       </c>
       <c r="H9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I9" s="2">
-        <v>34.82</v>
+        <v>35.24</v>
       </c>
       <c r="J9" s="2">
-        <v>0.0479</v>
+        <v>0.0485</v>
       </c>
       <c r="K9" t="s">
         <v>69</v>
@@ -1004,31 +1004,31 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
         <v>64</v>
       </c>
       <c r="E10">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F10">
-        <v>2.87</v>
+        <v>1.98</v>
       </c>
       <c r="G10" s="1">
-        <v>0.697</v>
+        <v>0.706</v>
       </c>
       <c r="H10" t="s">
         <v>66</v>
       </c>
       <c r="I10" s="2">
-        <v>32.97</v>
+        <v>34.82</v>
       </c>
       <c r="J10" s="2">
-        <v>0.0453</v>
+        <v>0.0479</v>
       </c>
       <c r="K10" t="s">
         <v>69</v>
@@ -1042,31 +1042,31 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
         <v>64</v>
       </c>
       <c r="E11">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="F11">
-        <v>2.61</v>
+        <v>2.87</v>
       </c>
       <c r="G11" s="1">
-        <v>0.6919999999999999</v>
+        <v>0.697</v>
       </c>
       <c r="H11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I11" s="2">
-        <v>32.05</v>
+        <v>32.97</v>
       </c>
       <c r="J11" s="2">
-        <v>0.0441</v>
+        <v>0.0453</v>
       </c>
       <c r="K11" t="s">
         <v>69</v>
@@ -1080,31 +1080,31 @@
         <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
         <v>64</v>
       </c>
       <c r="E12">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="F12">
-        <v>3.65</v>
+        <v>2.61</v>
       </c>
       <c r="G12" s="1">
-        <v>0.6870000000000001</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I12" s="2">
-        <v>31.12</v>
+        <v>32.05</v>
       </c>
       <c r="J12" s="2">
-        <v>0.0428</v>
+        <v>0.0441</v>
       </c>
       <c r="K12" t="s">
         <v>69</v>
@@ -1115,34 +1115,34 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E13">
-        <v>12.5</v>
+        <v>5.5</v>
       </c>
       <c r="F13">
-        <v>15.5</v>
+        <v>4.53</v>
       </c>
       <c r="G13" s="1">
-        <v>0.673</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I13" s="2">
-        <v>28.48</v>
+        <v>31.8</v>
       </c>
       <c r="J13" s="2">
-        <v>0.0392</v>
+        <v>0.0437</v>
       </c>
       <c r="K13" t="s">
         <v>69</v>
@@ -1153,7 +1153,7 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
         <v>58</v>
@@ -1162,25 +1162,25 @@
         <v>56</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E14">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F14">
-        <v>2.93</v>
+        <v>3.65</v>
       </c>
       <c r="G14" s="1">
-        <v>0.672</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="H14" t="s">
         <v>66</v>
       </c>
       <c r="I14" s="2">
-        <v>28.37</v>
+        <v>31.12</v>
       </c>
       <c r="J14" s="2">
-        <v>0.039</v>
+        <v>0.0428</v>
       </c>
       <c r="K14" t="s">
         <v>69</v>
@@ -1191,13 +1191,13 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
         <v>61</v>
@@ -1206,19 +1206,19 @@
         <v>5.5</v>
       </c>
       <c r="F15">
-        <v>4.64</v>
+        <v>4.54</v>
       </c>
       <c r="G15" s="1">
-        <v>0.672</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H15" t="s">
         <v>66</v>
       </c>
       <c r="I15" s="2">
-        <v>28.22</v>
+        <v>30.4</v>
       </c>
       <c r="J15" s="2">
-        <v>0.0388</v>
+        <v>0.0418</v>
       </c>
       <c r="K15" t="s">
         <v>69</v>
@@ -1229,34 +1229,34 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" t="s">
         <v>54</v>
       </c>
-      <c r="C16" t="s">
-        <v>59</v>
-      </c>
       <c r="D16" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E16">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="F16">
-        <v>3.84</v>
+        <v>15.5</v>
       </c>
       <c r="G16" s="1">
-        <v>0.657</v>
+        <v>0.673</v>
       </c>
       <c r="H16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I16" s="2">
-        <v>25.37</v>
+        <v>28.48</v>
       </c>
       <c r="J16" s="2">
-        <v>0.0698</v>
+        <v>0.0392</v>
       </c>
       <c r="K16" t="s">
         <v>69</v>
@@ -1267,34 +1267,34 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E17">
-        <v>9.5</v>
+        <v>3.5</v>
       </c>
       <c r="F17">
-        <v>8.109999999999999</v>
+        <v>2.93</v>
       </c>
       <c r="G17" s="1">
-        <v>0.653</v>
+        <v>0.672</v>
       </c>
       <c r="H17" t="s">
         <v>66</v>
       </c>
       <c r="I17" s="2">
-        <v>24.74</v>
+        <v>28.37</v>
       </c>
       <c r="J17" s="2">
-        <v>0.068</v>
+        <v>0.039</v>
       </c>
       <c r="K17" t="s">
         <v>69</v>
@@ -1305,34 +1305,34 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E18">
-        <v>12.5</v>
+        <v>5.5</v>
       </c>
       <c r="F18">
-        <v>15.04</v>
+        <v>4.64</v>
       </c>
       <c r="G18" s="1">
-        <v>0.629</v>
+        <v>0.672</v>
       </c>
       <c r="H18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I18" s="2">
-        <v>19.99</v>
+        <v>28.22</v>
       </c>
       <c r="J18" s="2">
-        <v>0.055</v>
+        <v>0.0388</v>
       </c>
       <c r="K18" t="s">
         <v>69</v>
@@ -1343,34 +1343,34 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E19">
-        <v>11.5</v>
+        <v>6.5</v>
       </c>
       <c r="F19">
-        <v>9.91</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G19" s="1">
-        <v>0.621</v>
+        <v>0.658</v>
       </c>
       <c r="H19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I19" s="2">
-        <v>18.57</v>
+        <v>25.66</v>
       </c>
       <c r="J19" s="2">
-        <v>0.0511</v>
+        <v>0.0706</v>
       </c>
       <c r="K19" t="s">
         <v>69</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
         <v>54</v>
@@ -1390,25 +1390,25 @@
         <v>59</v>
       </c>
       <c r="D20" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E20">
-        <v>12.5</v>
+        <v>4.5</v>
       </c>
       <c r="F20">
-        <v>14.21</v>
+        <v>3.84</v>
       </c>
       <c r="G20" s="1">
-        <v>0.614</v>
+        <v>0.657</v>
       </c>
       <c r="H20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I20" s="2">
-        <v>17.2</v>
+        <v>25.37</v>
       </c>
       <c r="J20" s="2">
-        <v>0.0473</v>
+        <v>0.0698</v>
       </c>
       <c r="K20" t="s">
         <v>69</v>
@@ -1419,34 +1419,34 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D21" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E21">
-        <v>18.5</v>
+        <v>9.5</v>
       </c>
       <c r="F21">
-        <v>20.93</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G21" s="1">
-        <v>0.611</v>
+        <v>0.653</v>
       </c>
       <c r="H21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I21" s="2">
-        <v>16.65</v>
+        <v>24.74</v>
       </c>
       <c r="J21" s="2">
-        <v>0.0458</v>
+        <v>0.068</v>
       </c>
       <c r="K21" t="s">
         <v>69</v>
@@ -1457,7 +1457,7 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
         <v>55</v>
@@ -1466,25 +1466,25 @@
         <v>60</v>
       </c>
       <c r="D22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E22">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="F22">
-        <v>15.17</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G22" s="1">
-        <v>0.61</v>
+        <v>0.648</v>
       </c>
       <c r="H22" t="s">
         <v>66</v>
       </c>
       <c r="I22" s="2">
-        <v>16.41</v>
+        <v>23.64</v>
       </c>
       <c r="J22" s="2">
-        <v>0.0451</v>
+        <v>0.065</v>
       </c>
       <c r="K22" t="s">
         <v>69</v>
@@ -1495,34 +1495,34 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E23">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="F23">
-        <v>9.4</v>
+        <v>5.7</v>
       </c>
       <c r="G23" s="1">
-        <v>0.606</v>
+        <v>0.647</v>
       </c>
       <c r="H23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I23" s="2">
-        <v>15.68</v>
+        <v>23.54</v>
       </c>
       <c r="J23" s="2">
-        <v>0.0431</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="K23" t="s">
         <v>69</v>
@@ -1533,13 +1533,13 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D24" t="s">
         <v>61</v>
@@ -1548,19 +1548,19 @@
         <v>6.5</v>
       </c>
       <c r="F24">
-        <v>6.01</v>
+        <v>5.76</v>
       </c>
       <c r="G24" s="1">
-        <v>0.605</v>
+        <v>0.64</v>
       </c>
       <c r="H24" t="s">
         <v>66</v>
       </c>
       <c r="I24" s="2">
-        <v>15.56</v>
+        <v>22.2</v>
       </c>
       <c r="J24" s="2">
-        <v>0.0428</v>
+        <v>0.0611</v>
       </c>
       <c r="K24" t="s">
         <v>69</v>
@@ -1571,37 +1571,37 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E25">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="F25">
-        <v>2.94</v>
+        <v>4.28</v>
       </c>
       <c r="G25" s="1">
-        <v>0.66</v>
+        <v>0.639</v>
       </c>
       <c r="H25" t="s">
         <v>66</v>
       </c>
       <c r="I25" s="2">
-        <v>25.97</v>
+        <v>21.99</v>
       </c>
       <c r="J25" s="2">
-        <v>0.0357</v>
+        <v>0.0605</v>
       </c>
       <c r="K25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L25" t="s">
         <v>74</v>
@@ -1609,37 +1609,37 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E26">
-        <v>3.5</v>
+        <v>23.5</v>
       </c>
       <c r="F26">
-        <v>2.98</v>
+        <v>19.17</v>
       </c>
       <c r="G26" s="1">
-        <v>0.659</v>
+        <v>0.631</v>
       </c>
       <c r="H26" t="s">
         <v>66</v>
       </c>
       <c r="I26" s="2">
-        <v>25.8</v>
+        <v>20.48</v>
       </c>
       <c r="J26" s="2">
-        <v>0.0355</v>
+        <v>0.0563</v>
       </c>
       <c r="K26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L26" t="s">
         <v>74</v>
@@ -1647,37 +1647,37 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C27" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D27" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E27">
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="F27">
-        <v>7.57</v>
+        <v>15.04</v>
       </c>
       <c r="G27" s="1">
-        <v>0.657</v>
+        <v>0.629</v>
       </c>
       <c r="H27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I27" s="2">
-        <v>25.38</v>
+        <v>19.99</v>
       </c>
       <c r="J27" s="2">
-        <v>0.0349</v>
+        <v>0.055</v>
       </c>
       <c r="K27" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L27" t="s">
         <v>74</v>
@@ -1685,37 +1685,37 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C28" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D28" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E28">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="F28">
-        <v>1.31</v>
+        <v>9.91</v>
       </c>
       <c r="G28" s="1">
-        <v>0.651</v>
+        <v>0.621</v>
       </c>
       <c r="H28" t="s">
         <v>66</v>
       </c>
       <c r="I28" s="2">
-        <v>24.25</v>
+        <v>18.57</v>
       </c>
       <c r="J28" s="2">
-        <v>0.0333</v>
+        <v>0.0511</v>
       </c>
       <c r="K28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L28" t="s">
         <v>74</v>
@@ -1723,37 +1723,37 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E29">
-        <v>1.5</v>
+        <v>16.5</v>
       </c>
       <c r="F29">
-        <v>1.52</v>
+        <v>13.81</v>
       </c>
       <c r="G29" s="1">
-        <v>0.647</v>
+        <v>0.619</v>
       </c>
       <c r="H29" t="s">
         <v>66</v>
       </c>
       <c r="I29" s="2">
-        <v>23.43</v>
+        <v>18.21</v>
       </c>
       <c r="J29" s="2">
-        <v>0.0322</v>
+        <v>0.0501</v>
       </c>
       <c r="K29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L29" t="s">
         <v>74</v>
@@ -1761,37 +1761,37 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C30" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D30" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E30">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="F30">
-        <v>3.98</v>
+        <v>14.21</v>
       </c>
       <c r="G30" s="1">
-        <v>0.639</v>
+        <v>0.614</v>
       </c>
       <c r="H30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I30" s="2">
-        <v>21.97</v>
+        <v>17.2</v>
       </c>
       <c r="J30" s="2">
-        <v>0.0302</v>
+        <v>0.0473</v>
       </c>
       <c r="K30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L30" t="s">
         <v>74</v>
@@ -1799,37 +1799,37 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C31" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D31" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E31">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="F31">
-        <v>9.6</v>
+        <v>20.93</v>
       </c>
       <c r="G31" s="1">
-        <v>0.636</v>
+        <v>0.611</v>
       </c>
       <c r="H31" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I31" s="2">
-        <v>21.44</v>
+        <v>16.65</v>
       </c>
       <c r="J31" s="2">
-        <v>0.0295</v>
+        <v>0.0458</v>
       </c>
       <c r="K31" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L31" t="s">
         <v>74</v>
@@ -1837,37 +1837,37 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C32" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D32" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E32">
-        <v>2.5</v>
+        <v>17.5</v>
       </c>
       <c r="F32">
-        <v>2.2</v>
+        <v>15.17</v>
       </c>
       <c r="G32" s="1">
-        <v>0.634</v>
+        <v>0.61</v>
       </c>
       <c r="H32" t="s">
         <v>66</v>
       </c>
       <c r="I32" s="2">
-        <v>20.96</v>
+        <v>16.41</v>
       </c>
       <c r="J32" s="2">
-        <v>0.0288</v>
+        <v>0.0451</v>
       </c>
       <c r="K32" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L32" t="s">
         <v>74</v>
@@ -1875,37 +1875,37 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C33" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D33" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E33">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="F33">
-        <v>4.32</v>
+        <v>9.4</v>
       </c>
       <c r="G33" s="1">
-        <v>0.628</v>
+        <v>0.606</v>
       </c>
       <c r="H33" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I33" s="2">
-        <v>19.84</v>
+        <v>15.68</v>
       </c>
       <c r="J33" s="2">
-        <v>0.0273</v>
+        <v>0.0431</v>
       </c>
       <c r="K33" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L33" t="s">
         <v>74</v>
@@ -1913,37 +1913,37 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C34" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D34" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E34">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="F34">
-        <v>2.16</v>
+        <v>6.01</v>
       </c>
       <c r="G34" s="1">
-        <v>0.625</v>
+        <v>0.605</v>
       </c>
       <c r="H34" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I34" s="2">
-        <v>19.41</v>
+        <v>15.56</v>
       </c>
       <c r="J34" s="2">
-        <v>0.0267</v>
+        <v>0.0428</v>
       </c>
       <c r="K34" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L34" t="s">
         <v>74</v>
@@ -1951,37 +1951,37 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C35" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D35" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E35">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="F35">
-        <v>12.92</v>
+        <v>13.42</v>
       </c>
       <c r="G35" s="1">
-        <v>0.62</v>
+        <v>0.605</v>
       </c>
       <c r="H35" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I35" s="2">
-        <v>18.43</v>
+        <v>15.44</v>
       </c>
       <c r="J35" s="2">
-        <v>0.0253</v>
+        <v>0.0425</v>
       </c>
       <c r="K35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L35" t="s">
         <v>74</v>
@@ -1989,37 +1989,37 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C36" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D36" t="s">
         <v>65</v>
       </c>
       <c r="E36">
-        <v>14.5</v>
+        <v>9.5</v>
       </c>
       <c r="F36">
-        <v>16.27</v>
+        <v>8</v>
       </c>
       <c r="G36" s="1">
-        <v>0.618</v>
+        <v>0.603</v>
       </c>
       <c r="H36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I36" s="2">
-        <v>17.91</v>
+        <v>15.12</v>
       </c>
       <c r="J36" s="2">
-        <v>0.0246</v>
+        <v>0.0416</v>
       </c>
       <c r="K36" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L36" t="s">
         <v>74</v>
@@ -2027,37 +2027,37 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C37" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D37" t="s">
         <v>64</v>
       </c>
       <c r="E37">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="F37">
-        <v>2.43</v>
+        <v>5.13</v>
       </c>
       <c r="G37" s="1">
-        <v>0.617</v>
+        <v>0.603</v>
       </c>
       <c r="H37" t="s">
         <v>66</v>
       </c>
       <c r="I37" s="2">
-        <v>17.74</v>
+        <v>15.03</v>
       </c>
       <c r="J37" s="2">
-        <v>0.0244</v>
+        <v>0.0413</v>
       </c>
       <c r="K37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L37" t="s">
         <v>74</v>
@@ -2065,37 +2065,37 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C38" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D38" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E38">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="F38">
-        <v>4.09</v>
+        <v>6.98</v>
       </c>
       <c r="G38" s="1">
-        <v>0.615</v>
+        <v>0.602</v>
       </c>
       <c r="H38" t="s">
         <v>66</v>
       </c>
       <c r="I38" s="2">
-        <v>17.35</v>
+        <v>15.01</v>
       </c>
       <c r="J38" s="2">
-        <v>0.0239</v>
+        <v>0.0413</v>
       </c>
       <c r="K38" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L38" t="s">
         <v>74</v>
@@ -2103,34 +2103,34 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C39" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D39" t="s">
         <v>64</v>
       </c>
       <c r="E39">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="F39">
-        <v>1.56</v>
+        <v>2.94</v>
       </c>
       <c r="G39" s="1">
-        <v>0.613</v>
+        <v>0.66</v>
       </c>
       <c r="H39" t="s">
         <v>66</v>
       </c>
       <c r="I39" s="2">
-        <v>17.1</v>
+        <v>25.97</v>
       </c>
       <c r="J39" s="2">
-        <v>0.0235</v>
+        <v>0.0357</v>
       </c>
       <c r="K39" t="s">
         <v>70</v>
@@ -2141,34 +2141,34 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B40" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" t="s">
         <v>58</v>
-      </c>
-      <c r="C40" t="s">
-        <v>56</v>
       </c>
       <c r="D40" t="s">
         <v>61</v>
       </c>
       <c r="E40">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="F40">
-        <v>6.19</v>
+        <v>2.98</v>
       </c>
       <c r="G40" s="1">
-        <v>0.609</v>
+        <v>0.659</v>
       </c>
       <c r="H40" t="s">
         <v>66</v>
       </c>
       <c r="I40" s="2">
-        <v>16.19</v>
+        <v>25.8</v>
       </c>
       <c r="J40" s="2">
-        <v>0.0223</v>
+        <v>0.0355</v>
       </c>
       <c r="K40" t="s">
         <v>70</v>
@@ -2179,34 +2179,34 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="B41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C41" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D41" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E41">
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
       <c r="F41">
-        <v>13</v>
+        <v>7.57</v>
       </c>
       <c r="G41" s="1">
-        <v>0.607</v>
+        <v>0.657</v>
       </c>
       <c r="H41" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I41" s="2">
-        <v>15.96</v>
+        <v>25.38</v>
       </c>
       <c r="J41" s="2">
-        <v>0.0219</v>
+        <v>0.0349</v>
       </c>
       <c r="K41" t="s">
         <v>70</v>
@@ -2217,34 +2217,34 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B42" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C42" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D42" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E42">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="F42">
-        <v>8.68</v>
+        <v>1.31</v>
       </c>
       <c r="G42" s="1">
-        <v>0.602</v>
+        <v>0.651</v>
       </c>
       <c r="H42" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I42" s="2">
-        <v>14.87</v>
+        <v>24.25</v>
       </c>
       <c r="J42" s="2">
-        <v>0.0204</v>
+        <v>0.0333</v>
       </c>
       <c r="K42" t="s">
         <v>70</v>
@@ -2255,34 +2255,34 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="B43" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C43" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E43">
-        <v>15.5</v>
+        <v>6.5</v>
       </c>
       <c r="F43">
-        <v>17.11</v>
+        <v>5.8</v>
       </c>
       <c r="G43" s="1">
-        <v>0.574</v>
+        <v>0.647</v>
       </c>
       <c r="H43" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I43" s="2">
-        <v>9.6</v>
+        <v>23.59</v>
       </c>
       <c r="J43" s="2">
-        <v>0.0264</v>
+        <v>0.0324</v>
       </c>
       <c r="K43" t="s">
         <v>70</v>
@@ -2293,34 +2293,34 @@
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="B44" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C44" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D44" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E44">
-        <v>10.5</v>
+        <v>1.5</v>
       </c>
       <c r="F44">
-        <v>11.47</v>
+        <v>1.52</v>
       </c>
       <c r="G44" s="1">
-        <v>0.5610000000000001</v>
+        <v>0.647</v>
       </c>
       <c r="H44" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I44" s="2">
-        <v>7.17</v>
+        <v>23.43</v>
       </c>
       <c r="J44" s="2">
-        <v>0.0197</v>
+        <v>0.0322</v>
       </c>
       <c r="K44" t="s">
         <v>70</v>
@@ -2331,34 +2331,34 @@
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C45" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D45" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E45">
-        <v>24.5</v>
+        <v>4.5</v>
       </c>
       <c r="F45">
-        <v>22.4</v>
+        <v>3.98</v>
       </c>
       <c r="G45" s="1">
-        <v>0.5590000000000001</v>
+        <v>0.639</v>
       </c>
       <c r="H45" t="s">
         <v>66</v>
       </c>
       <c r="I45" s="2">
-        <v>6.78</v>
+        <v>21.97</v>
       </c>
       <c r="J45" s="2">
-        <v>0.0186</v>
+        <v>0.0302</v>
       </c>
       <c r="K45" t="s">
         <v>70</v>
@@ -2369,37 +2369,37 @@
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C46" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D46" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E46">
-        <v>1.5</v>
+        <v>18.5</v>
       </c>
       <c r="F46">
-        <v>1.71</v>
+        <v>15.15</v>
       </c>
       <c r="G46" s="1">
-        <v>0.599</v>
+        <v>0.637</v>
       </c>
       <c r="H46" t="s">
         <v>66</v>
       </c>
       <c r="I46" s="2">
-        <v>14.44</v>
+        <v>21.52</v>
       </c>
       <c r="J46" s="2">
-        <v>0.0199</v>
+        <v>0.0296</v>
       </c>
       <c r="K46" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L46" t="s">
         <v>74</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B47" t="s">
         <v>56</v>
@@ -2416,28 +2416,28 @@
         <v>58</v>
       </c>
       <c r="D47" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E47">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="F47">
-        <v>1.41</v>
+        <v>9.6</v>
       </c>
       <c r="G47" s="1">
-        <v>0.593</v>
+        <v>0.636</v>
       </c>
       <c r="H47" t="s">
         <v>66</v>
       </c>
       <c r="I47" s="2">
-        <v>13.19</v>
+        <v>21.44</v>
       </c>
       <c r="J47" s="2">
-        <v>0.0181</v>
+        <v>0.0295</v>
       </c>
       <c r="K47" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L47" t="s">
         <v>74</v>
@@ -2445,37 +2445,37 @@
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="B48" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C48" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D48" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E48">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="F48">
-        <v>4.45</v>
+        <v>2.2</v>
       </c>
       <c r="G48" s="1">
-        <v>0.592</v>
+        <v>0.634</v>
       </c>
       <c r="H48" t="s">
         <v>66</v>
       </c>
       <c r="I48" s="2">
-        <v>12.94</v>
+        <v>20.96</v>
       </c>
       <c r="J48" s="2">
-        <v>0.0178</v>
+        <v>0.0288</v>
       </c>
       <c r="K48" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L48" t="s">
         <v>74</v>
@@ -2483,37 +2483,37 @@
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B49" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D49" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E49">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="F49">
-        <v>8.710000000000001</v>
+        <v>4.32</v>
       </c>
       <c r="G49" s="1">
-        <v>0.591</v>
+        <v>0.628</v>
       </c>
       <c r="H49" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I49" s="2">
-        <v>12.85</v>
+        <v>19.84</v>
       </c>
       <c r="J49" s="2">
-        <v>0.0177</v>
+        <v>0.0273</v>
       </c>
       <c r="K49" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L49" t="s">
         <v>74</v>
@@ -2521,37 +2521,37 @@
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B50" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C50" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D50" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E50">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F50">
-        <v>2.52</v>
+        <v>2.16</v>
       </c>
       <c r="G50" s="1">
-        <v>0.59</v>
+        <v>0.625</v>
       </c>
       <c r="H50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I50" s="2">
-        <v>12.73</v>
+        <v>19.41</v>
       </c>
       <c r="J50" s="2">
-        <v>0.0175</v>
+        <v>0.0267</v>
       </c>
       <c r="K50" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L50" t="s">
         <v>74</v>
@@ -2559,13 +2559,13 @@
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B51" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C51" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D51" t="s">
         <v>64</v>
@@ -2574,22 +2574,22 @@
         <v>1.5</v>
       </c>
       <c r="F51">
-        <v>1.8</v>
+        <v>1.41</v>
       </c>
       <c r="G51" s="1">
-        <v>0.582</v>
+        <v>0.622</v>
       </c>
       <c r="H51" t="s">
         <v>66</v>
       </c>
       <c r="I51" s="2">
-        <v>11.03</v>
+        <v>18.75</v>
       </c>
       <c r="J51" s="2">
-        <v>0.0152</v>
+        <v>0.0258</v>
       </c>
       <c r="K51" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L51" t="s">
         <v>74</v>
@@ -2597,37 +2597,37 @@
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C52" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D52" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E52">
-        <v>2.5</v>
+        <v>10.5</v>
       </c>
       <c r="F52">
-        <v>3.26</v>
+        <v>12.92</v>
       </c>
       <c r="G52" s="1">
-        <v>0.581</v>
+        <v>0.62</v>
       </c>
       <c r="H52" t="s">
         <v>67</v>
       </c>
       <c r="I52" s="2">
-        <v>10.98</v>
+        <v>18.43</v>
       </c>
       <c r="J52" s="2">
-        <v>0.0151</v>
+        <v>0.0253</v>
       </c>
       <c r="K52" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L52" t="s">
         <v>74</v>
@@ -2635,37 +2635,37 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="B53" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C53" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D53" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E53">
-        <v>1.5</v>
+        <v>14.5</v>
       </c>
       <c r="F53">
-        <v>1.55</v>
+        <v>16.27</v>
       </c>
       <c r="G53" s="1">
-        <v>0.5679999999999999</v>
+        <v>0.618</v>
       </c>
       <c r="H53" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I53" s="2">
-        <v>8.43</v>
+        <v>17.91</v>
       </c>
       <c r="J53" s="2">
-        <v>0.0116</v>
+        <v>0.0246</v>
       </c>
       <c r="K53" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L53" t="s">
         <v>74</v>
@@ -2673,7 +2673,7 @@
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B54" t="s">
         <v>53</v>
@@ -2682,28 +2682,28 @@
         <v>55</v>
       </c>
       <c r="D54" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E54">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="F54">
-        <v>12.17</v>
+        <v>2.43</v>
       </c>
       <c r="G54" s="1">
-        <v>0.5659999999999999</v>
+        <v>0.617</v>
       </c>
       <c r="H54" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I54" s="2">
-        <v>8.029999999999999</v>
+        <v>17.74</v>
       </c>
       <c r="J54" s="2">
-        <v>0.011</v>
+        <v>0.0244</v>
       </c>
       <c r="K54" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L54" t="s">
         <v>74</v>
@@ -2711,37 +2711,37 @@
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="B55" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C55" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D55" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E55">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="F55">
-        <v>3.05</v>
+        <v>4.09</v>
       </c>
       <c r="G55" s="1">
-        <v>0.5639999999999999</v>
+        <v>0.615</v>
       </c>
       <c r="H55" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I55" s="2">
-        <v>7.62</v>
+        <v>17.35</v>
       </c>
       <c r="J55" s="2">
-        <v>0.0105</v>
+        <v>0.0239</v>
       </c>
       <c r="K55" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L55" t="s">
         <v>74</v>
@@ -2749,37 +2749,37 @@
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="B56" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C56" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D56" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E56">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F56">
-        <v>2.91</v>
+        <v>1.56</v>
       </c>
       <c r="G56" s="1">
-        <v>0.556</v>
+        <v>0.613</v>
       </c>
       <c r="H56" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I56" s="2">
-        <v>6.1</v>
+        <v>17.1</v>
       </c>
       <c r="J56" s="2">
-        <v>0.008399999999999999</v>
+        <v>0.0235</v>
       </c>
       <c r="K56" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L56" t="s">
         <v>74</v>
@@ -2787,37 +2787,37 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B57" t="s">
+        <v>58</v>
+      </c>
+      <c r="C57" t="s">
         <v>56</v>
       </c>
-      <c r="C57" t="s">
-        <v>58</v>
-      </c>
       <c r="D57" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E57">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="F57">
-        <v>8.140000000000001</v>
+        <v>6.19</v>
       </c>
       <c r="G57" s="1">
-        <v>0.555</v>
+        <v>0.609</v>
       </c>
       <c r="H57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I57" s="2">
-        <v>5.9</v>
+        <v>16.19</v>
       </c>
       <c r="J57" s="2">
-        <v>0.0081</v>
+        <v>0.0223</v>
       </c>
       <c r="K57" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L57" t="s">
         <v>74</v>
@@ -2825,37 +2825,37 @@
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B58" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C58" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D58" t="s">
         <v>65</v>
       </c>
       <c r="E58">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="F58">
-        <v>16.62</v>
+        <v>13</v>
       </c>
       <c r="G58" s="1">
-        <v>0.553</v>
+        <v>0.607</v>
       </c>
       <c r="H58" t="s">
         <v>67</v>
       </c>
       <c r="I58" s="2">
-        <v>5.67</v>
+        <v>15.96</v>
       </c>
       <c r="J58" s="2">
-        <v>0.0078</v>
+        <v>0.0219</v>
       </c>
       <c r="K58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L58" t="s">
         <v>74</v>
@@ -2863,37 +2863,37 @@
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B59" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C59" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D59" t="s">
         <v>65</v>
       </c>
       <c r="E59">
-        <v>17.5</v>
+        <v>4.5</v>
       </c>
       <c r="F59">
-        <v>18.44</v>
+        <v>3.19</v>
       </c>
       <c r="G59" s="1">
-        <v>0.553</v>
+        <v>0.606</v>
       </c>
       <c r="H59" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I59" s="2">
-        <v>5.64</v>
+        <v>15.76</v>
       </c>
       <c r="J59" s="2">
-        <v>0.0078</v>
+        <v>0.0217</v>
       </c>
       <c r="K59" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L59" t="s">
         <v>74</v>
@@ -2901,37 +2901,37 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B60" t="s">
+        <v>58</v>
+      </c>
+      <c r="C60" t="s">
         <v>56</v>
-      </c>
-      <c r="C60" t="s">
-        <v>58</v>
       </c>
       <c r="D60" t="s">
         <v>62</v>
       </c>
       <c r="E60">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="F60">
-        <v>15.69</v>
+        <v>12.02</v>
       </c>
       <c r="G60" s="1">
-        <v>0.551</v>
+        <v>0.606</v>
       </c>
       <c r="H60" t="s">
         <v>66</v>
       </c>
       <c r="I60" s="2">
-        <v>5.13</v>
+        <v>15.68</v>
       </c>
       <c r="J60" s="2">
-        <v>0.007</v>
+        <v>0.0216</v>
       </c>
       <c r="K60" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L60" t="s">
         <v>74</v>
@@ -2939,37 +2939,37 @@
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B61" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C61" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D61" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E61">
-        <v>23.5</v>
+        <v>7.5</v>
       </c>
       <c r="F61">
-        <v>24.43</v>
+        <v>8.68</v>
       </c>
       <c r="G61" s="1">
-        <v>0.531</v>
+        <v>0.602</v>
       </c>
       <c r="H61" t="s">
         <v>67</v>
       </c>
       <c r="I61" s="2">
-        <v>1.35</v>
+        <v>14.87</v>
       </c>
       <c r="J61" s="2">
-        <v>0.0037</v>
+        <v>0.0204</v>
       </c>
       <c r="K61" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L61" t="s">
         <v>74</v>
@@ -2977,7 +2977,7 @@
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="B62" t="s">
         <v>56</v>
@@ -2986,28 +2986,28 @@
         <v>58</v>
       </c>
       <c r="D62" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E62">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="F62">
-        <v>12.06</v>
+        <v>2.05</v>
       </c>
       <c r="G62" s="1">
-        <v>0.523</v>
+        <v>0.601</v>
       </c>
       <c r="H62" t="s">
         <v>67</v>
       </c>
       <c r="I62" s="2">
-        <v>-0.1</v>
+        <v>14.78</v>
       </c>
       <c r="J62" s="2">
-        <v>0</v>
+        <v>0.0203</v>
       </c>
       <c r="K62" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L62" t="s">
         <v>74</v>
@@ -3015,37 +3015,37 @@
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B63" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C63" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D63" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E63">
-        <v>14.5</v>
+        <v>1.5</v>
       </c>
       <c r="F63">
-        <v>15.12</v>
+        <v>1.37</v>
       </c>
       <c r="G63" s="1">
-        <v>0.521</v>
+        <v>0.601</v>
       </c>
       <c r="H63" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I63" s="2">
-        <v>-0.53</v>
+        <v>14.71</v>
       </c>
       <c r="J63" s="2">
-        <v>0</v>
+        <v>0.0202</v>
       </c>
       <c r="K63" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L63" t="s">
         <v>74</v>
@@ -3053,37 +3053,37 @@
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="B64" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C64" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D64" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E64">
-        <v>1.5</v>
+        <v>15.5</v>
       </c>
       <c r="F64">
-        <v>1.74</v>
+        <v>16.94</v>
       </c>
       <c r="G64" s="1">
-        <v>0.52</v>
+        <v>0.596</v>
       </c>
       <c r="H64" t="s">
         <v>67</v>
       </c>
       <c r="I64" s="2">
-        <v>-0.7</v>
+        <v>13.72</v>
       </c>
       <c r="J64" s="2">
-        <v>0</v>
+        <v>0.0377</v>
       </c>
       <c r="K64" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L64" t="s">
         <v>74</v>
@@ -3091,37 +3091,37 @@
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B65" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C65" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D65" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E65">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="F65">
-        <v>16.98</v>
+        <v>10.78</v>
       </c>
       <c r="G65" s="1">
-        <v>0.519</v>
+        <v>0.595</v>
       </c>
       <c r="H65" t="s">
         <v>66</v>
       </c>
       <c r="I65" s="2">
-        <v>-0.92</v>
+        <v>13.67</v>
       </c>
       <c r="J65" s="2">
-        <v>0</v>
+        <v>0.0376</v>
       </c>
       <c r="K65" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L65" t="s">
         <v>74</v>
@@ -3129,37 +3129,37 @@
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="B66" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C66" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D66" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E66">
-        <v>7.5</v>
+        <v>17.5</v>
       </c>
       <c r="F66">
-        <v>7.81</v>
+        <v>15.04</v>
       </c>
       <c r="G66" s="1">
-        <v>0.517</v>
+        <v>0.589</v>
       </c>
       <c r="H66" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I66" s="2">
-        <v>-1.27</v>
+        <v>12.47</v>
       </c>
       <c r="J66" s="2">
-        <v>0</v>
+        <v>0.0343</v>
       </c>
       <c r="K66" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L66" t="s">
         <v>74</v>
@@ -3167,37 +3167,37 @@
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B67" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C67" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D67" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E67">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="F67">
-        <v>2.86</v>
+        <v>7.57</v>
       </c>
       <c r="G67" s="1">
-        <v>0.516</v>
+        <v>0.579</v>
       </c>
       <c r="H67" t="s">
         <v>66</v>
       </c>
       <c r="I67" s="2">
-        <v>-1.44</v>
+        <v>10.63</v>
       </c>
       <c r="J67" s="2">
-        <v>0</v>
+        <v>0.0292</v>
       </c>
       <c r="K67" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L67" t="s">
         <v>74</v>
@@ -3205,37 +3205,37 @@
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B68" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C68" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D68" t="s">
         <v>65</v>
       </c>
       <c r="E68">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="F68">
-        <v>16.99</v>
+        <v>17.11</v>
       </c>
       <c r="G68" s="1">
-        <v>0.516</v>
+        <v>0.574</v>
       </c>
       <c r="H68" t="s">
         <v>67</v>
       </c>
       <c r="I68" s="2">
-        <v>-1.51</v>
+        <v>9.6</v>
       </c>
       <c r="J68" s="2">
-        <v>0</v>
+        <v>0.0264</v>
       </c>
       <c r="K68" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L68" t="s">
         <v>74</v>
@@ -3243,44 +3243,4452 @@
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
+        <v>33</v>
+      </c>
+      <c r="B69" t="s">
+        <v>58</v>
+      </c>
+      <c r="C69" t="s">
+        <v>56</v>
+      </c>
+      <c r="D69" t="s">
+        <v>62</v>
+      </c>
+      <c r="E69">
+        <v>23.5</v>
+      </c>
+      <c r="F69">
+        <v>21.81</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0.574</v>
+      </c>
+      <c r="H69" t="s">
+        <v>66</v>
+      </c>
+      <c r="I69" s="2">
+        <v>9.59</v>
+      </c>
+      <c r="J69" s="2">
+        <v>0.0264</v>
+      </c>
+      <c r="K69" t="s">
+        <v>70</v>
+      </c>
+      <c r="L69" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12">
+      <c r="A70" t="s">
+        <v>16</v>
+      </c>
+      <c r="B70" t="s">
+        <v>54</v>
+      </c>
+      <c r="C70" t="s">
+        <v>59</v>
+      </c>
+      <c r="D70" t="s">
+        <v>63</v>
+      </c>
+      <c r="E70">
+        <v>13.5</v>
+      </c>
+      <c r="F70">
+        <v>12.34</v>
+      </c>
+      <c r="G70" s="1">
+        <v>0.572</v>
+      </c>
+      <c r="H70" t="s">
+        <v>66</v>
+      </c>
+      <c r="I70" s="2">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="J70" s="2">
+        <v>0.0253</v>
+      </c>
+      <c r="K70" t="s">
+        <v>70</v>
+      </c>
+      <c r="L70" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12">
+      <c r="A71" t="s">
+        <v>27</v>
+      </c>
+      <c r="B71" t="s">
+        <v>54</v>
+      </c>
+      <c r="C71" t="s">
+        <v>59</v>
+      </c>
+      <c r="D71" t="s">
+        <v>63</v>
+      </c>
+      <c r="E71">
+        <v>15.5</v>
+      </c>
+      <c r="F71">
+        <v>14.05</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="H71" t="s">
+        <v>66</v>
+      </c>
+      <c r="I71" s="2">
+        <v>7.93</v>
+      </c>
+      <c r="J71" s="2">
+        <v>0.0218</v>
+      </c>
+      <c r="K71" t="s">
+        <v>70</v>
+      </c>
+      <c r="L71" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12">
+      <c r="A72" t="s">
+        <v>18</v>
+      </c>
+      <c r="B72" t="s">
+        <v>54</v>
+      </c>
+      <c r="C72" t="s">
+        <v>59</v>
+      </c>
+      <c r="D72" t="s">
+        <v>62</v>
+      </c>
+      <c r="E72">
+        <v>36.5</v>
+      </c>
+      <c r="F72">
+        <v>32.53</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="H72" t="s">
+        <v>66</v>
+      </c>
+      <c r="I72" s="2">
+        <v>7.93</v>
+      </c>
+      <c r="J72" s="2">
+        <v>0.0218</v>
+      </c>
+      <c r="K72" t="s">
+        <v>70</v>
+      </c>
+      <c r="L72" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12">
+      <c r="A73" t="s">
+        <v>48</v>
+      </c>
+      <c r="B73" t="s">
+        <v>53</v>
+      </c>
+      <c r="C73" t="s">
+        <v>55</v>
+      </c>
+      <c r="D73" t="s">
+        <v>65</v>
+      </c>
+      <c r="E73">
+        <v>10.5</v>
+      </c>
+      <c r="F73">
+        <v>11.47</v>
+      </c>
+      <c r="G73" s="1">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="H73" t="s">
+        <v>67</v>
+      </c>
+      <c r="I73" s="2">
+        <v>7.17</v>
+      </c>
+      <c r="J73" s="2">
+        <v>0.0197</v>
+      </c>
+      <c r="K73" t="s">
+        <v>70</v>
+      </c>
+      <c r="L73" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12">
+      <c r="A74" t="s">
+        <v>46</v>
+      </c>
+      <c r="B74" t="s">
+        <v>56</v>
+      </c>
+      <c r="C74" t="s">
+        <v>58</v>
+      </c>
+      <c r="D74" t="s">
+        <v>62</v>
+      </c>
+      <c r="E74">
+        <v>24.5</v>
+      </c>
+      <c r="F74">
+        <v>22.4</v>
+      </c>
+      <c r="G74" s="1">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="H74" t="s">
+        <v>66</v>
+      </c>
+      <c r="I74" s="2">
+        <v>6.78</v>
+      </c>
+      <c r="J74" s="2">
+        <v>0.0186</v>
+      </c>
+      <c r="K74" t="s">
+        <v>70</v>
+      </c>
+      <c r="L74" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12">
+      <c r="A75" t="s">
+        <v>33</v>
+      </c>
+      <c r="B75" t="s">
+        <v>58</v>
+      </c>
+      <c r="C75" t="s">
+        <v>56</v>
+      </c>
+      <c r="D75" t="s">
+        <v>63</v>
+      </c>
+      <c r="E75">
+        <v>7.5</v>
+      </c>
+      <c r="F75">
+        <v>7.94</v>
+      </c>
+      <c r="G75" s="1">
+        <v>0.553</v>
+      </c>
+      <c r="H75" t="s">
+        <v>67</v>
+      </c>
+      <c r="I75" s="2">
+        <v>5.64</v>
+      </c>
+      <c r="J75" s="2">
+        <v>0.0155</v>
+      </c>
+      <c r="K75" t="s">
+        <v>70</v>
+      </c>
+      <c r="L75" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12">
+      <c r="A76" t="s">
+        <v>49</v>
+      </c>
+      <c r="B76" t="s">
+        <v>57</v>
+      </c>
+      <c r="C76" t="s">
+        <v>54</v>
+      </c>
+      <c r="D76" t="s">
+        <v>64</v>
+      </c>
+      <c r="E76">
+        <v>1.5</v>
+      </c>
+      <c r="F76">
+        <v>1.71</v>
+      </c>
+      <c r="G76" s="1">
+        <v>0.599</v>
+      </c>
+      <c r="H76" t="s">
+        <v>66</v>
+      </c>
+      <c r="I76" s="2">
+        <v>14.44</v>
+      </c>
+      <c r="J76" s="2">
+        <v>0.0199</v>
+      </c>
+      <c r="K76" t="s">
+        <v>71</v>
+      </c>
+      <c r="L76" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>55</v>
+      </c>
+      <c r="C77" t="s">
+        <v>60</v>
+      </c>
+      <c r="D77" t="s">
+        <v>62</v>
+      </c>
+      <c r="E77">
+        <v>43.5</v>
+      </c>
+      <c r="F77">
+        <v>35.73</v>
+      </c>
+      <c r="G77" s="1">
+        <v>0.597</v>
+      </c>
+      <c r="H77" t="s">
+        <v>66</v>
+      </c>
+      <c r="I77" s="2">
+        <v>13.94</v>
+      </c>
+      <c r="J77" s="2">
+        <v>0.0192</v>
+      </c>
+      <c r="K77" t="s">
+        <v>71</v>
+      </c>
+      <c r="L77" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>55</v>
+      </c>
+      <c r="C78" t="s">
+        <v>60</v>
+      </c>
+      <c r="D78" t="s">
+        <v>65</v>
+      </c>
+      <c r="E78">
+        <v>27.5</v>
+      </c>
+      <c r="F78">
+        <v>22.52</v>
+      </c>
+      <c r="G78" s="1">
+        <v>0.595</v>
+      </c>
+      <c r="H78" t="s">
+        <v>66</v>
+      </c>
+      <c r="I78" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="J78" s="2">
+        <v>0.0186</v>
+      </c>
+      <c r="K78" t="s">
+        <v>71</v>
+      </c>
+      <c r="L78" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12">
+      <c r="A79" t="s">
+        <v>50</v>
+      </c>
+      <c r="B79" t="s">
+        <v>56</v>
+      </c>
+      <c r="C79" t="s">
+        <v>58</v>
+      </c>
+      <c r="D79" t="s">
+        <v>64</v>
+      </c>
+      <c r="E79">
+        <v>1.5</v>
+      </c>
+      <c r="F79">
+        <v>1.41</v>
+      </c>
+      <c r="G79" s="1">
+        <v>0.593</v>
+      </c>
+      <c r="H79" t="s">
+        <v>66</v>
+      </c>
+      <c r="I79" s="2">
+        <v>13.19</v>
+      </c>
+      <c r="J79" s="2">
+        <v>0.0181</v>
+      </c>
+      <c r="K79" t="s">
+        <v>71</v>
+      </c>
+      <c r="L79" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12">
+      <c r="A80" t="s">
+        <v>19</v>
+      </c>
+      <c r="B80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C80" t="s">
+        <v>60</v>
+      </c>
+      <c r="D80" t="s">
+        <v>62</v>
+      </c>
+      <c r="E80">
+        <v>12.5</v>
+      </c>
+      <c r="F80">
+        <v>9.85</v>
+      </c>
+      <c r="G80" s="1">
+        <v>0.593</v>
+      </c>
+      <c r="H80" t="s">
+        <v>66</v>
+      </c>
+      <c r="I80" s="2">
+        <v>13.12</v>
+      </c>
+      <c r="J80" s="2">
+        <v>0.018</v>
+      </c>
+      <c r="K80" t="s">
+        <v>71</v>
+      </c>
+      <c r="L80" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12">
+      <c r="A81" t="s">
+        <v>51</v>
+      </c>
+      <c r="B81" t="s">
+        <v>53</v>
+      </c>
+      <c r="C81" t="s">
+        <v>55</v>
+      </c>
+      <c r="D81" t="s">
+        <v>61</v>
+      </c>
+      <c r="E81">
+        <v>4.5</v>
+      </c>
+      <c r="F81">
+        <v>4.45</v>
+      </c>
+      <c r="G81" s="1">
+        <v>0.592</v>
+      </c>
+      <c r="H81" t="s">
+        <v>66</v>
+      </c>
+      <c r="I81" s="2">
+        <v>12.94</v>
+      </c>
+      <c r="J81" s="2">
+        <v>0.0178</v>
+      </c>
+      <c r="K81" t="s">
+        <v>71</v>
+      </c>
+      <c r="L81" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12">
+      <c r="A82" t="s">
+        <v>50</v>
+      </c>
+      <c r="B82" t="s">
+        <v>56</v>
+      </c>
+      <c r="C82" t="s">
+        <v>58</v>
+      </c>
+      <c r="D82" t="s">
+        <v>65</v>
+      </c>
+      <c r="E82">
+        <v>7.5</v>
+      </c>
+      <c r="F82">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="G82" s="1">
+        <v>0.591</v>
+      </c>
+      <c r="H82" t="s">
+        <v>67</v>
+      </c>
+      <c r="I82" s="2">
+        <v>12.85</v>
+      </c>
+      <c r="J82" s="2">
+        <v>0.0177</v>
+      </c>
+      <c r="K82" t="s">
+        <v>71</v>
+      </c>
+      <c r="L82" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12">
+      <c r="A83" t="s">
         <v>47</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B83" t="s">
+        <v>58</v>
+      </c>
+      <c r="C83" t="s">
         <v>56</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D83" t="s">
+        <v>61</v>
+      </c>
+      <c r="E83">
+        <v>2.5</v>
+      </c>
+      <c r="F83">
+        <v>2.52</v>
+      </c>
+      <c r="G83" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="H83" t="s">
+        <v>66</v>
+      </c>
+      <c r="I83" s="2">
+        <v>12.73</v>
+      </c>
+      <c r="J83" s="2">
+        <v>0.0175</v>
+      </c>
+      <c r="K83" t="s">
+        <v>71</v>
+      </c>
+      <c r="L83" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12">
+      <c r="A84" t="s">
+        <v>50</v>
+      </c>
+      <c r="B84" t="s">
+        <v>56</v>
+      </c>
+      <c r="C84" t="s">
         <v>58</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D84" t="s">
+        <v>61</v>
+      </c>
+      <c r="E84">
+        <v>5.5</v>
+      </c>
+      <c r="F84">
+        <v>5.58</v>
+      </c>
+      <c r="G84" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="H84" t="s">
+        <v>66</v>
+      </c>
+      <c r="I84" s="2">
+        <v>12.72</v>
+      </c>
+      <c r="J84" s="2">
+        <v>0.0175</v>
+      </c>
+      <c r="K84" t="s">
+        <v>71</v>
+      </c>
+      <c r="L84" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="A85" t="s">
+        <v>12</v>
+      </c>
+      <c r="B85" t="s">
+        <v>53</v>
+      </c>
+      <c r="C85" t="s">
+        <v>55</v>
+      </c>
+      <c r="D85" t="s">
         <v>63</v>
       </c>
-      <c r="E69">
+      <c r="E85">
+        <v>9.5</v>
+      </c>
+      <c r="F85">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="G85" s="1">
+        <v>0.589</v>
+      </c>
+      <c r="H85" t="s">
+        <v>66</v>
+      </c>
+      <c r="I85" s="2">
+        <v>12.53</v>
+      </c>
+      <c r="J85" s="2">
+        <v>0.0172</v>
+      </c>
+      <c r="K85" t="s">
+        <v>71</v>
+      </c>
+      <c r="L85" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12">
+      <c r="A86" t="s">
+        <v>42</v>
+      </c>
+      <c r="B86" t="s">
+        <v>57</v>
+      </c>
+      <c r="C86" t="s">
+        <v>54</v>
+      </c>
+      <c r="D86" t="s">
+        <v>61</v>
+      </c>
+      <c r="E86">
+        <v>1.5</v>
+      </c>
+      <c r="F86">
+        <v>1.96</v>
+      </c>
+      <c r="G86" s="1">
+        <v>0.586</v>
+      </c>
+      <c r="H86" t="s">
+        <v>66</v>
+      </c>
+      <c r="I86" s="2">
+        <v>11.92</v>
+      </c>
+      <c r="J86" s="2">
+        <v>0.0164</v>
+      </c>
+      <c r="K86" t="s">
+        <v>71</v>
+      </c>
+      <c r="L86" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12">
+      <c r="A87" t="s">
+        <v>45</v>
+      </c>
+      <c r="B87" t="s">
+        <v>55</v>
+      </c>
+      <c r="C87" t="s">
+        <v>60</v>
+      </c>
+      <c r="D87" t="s">
+        <v>61</v>
+      </c>
+      <c r="E87">
+        <v>2.5</v>
+      </c>
+      <c r="F87">
+        <v>3.04</v>
+      </c>
+      <c r="G87" s="1">
+        <v>0.586</v>
+      </c>
+      <c r="H87" t="s">
+        <v>67</v>
+      </c>
+      <c r="I87" s="2">
+        <v>11.78</v>
+      </c>
+      <c r="J87" s="2">
+        <v>0.0162</v>
+      </c>
+      <c r="K87" t="s">
+        <v>71</v>
+      </c>
+      <c r="L87" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12">
+      <c r="A88" t="s">
+        <v>21</v>
+      </c>
+      <c r="B88" t="s">
+        <v>57</v>
+      </c>
+      <c r="C88" t="s">
+        <v>54</v>
+      </c>
+      <c r="D88" t="s">
+        <v>65</v>
+      </c>
+      <c r="E88">
+        <v>13.5</v>
+      </c>
+      <c r="F88">
+        <v>15.18</v>
+      </c>
+      <c r="G88" s="1">
+        <v>0.585</v>
+      </c>
+      <c r="H88" t="s">
+        <v>67</v>
+      </c>
+      <c r="I88" s="2">
+        <v>11.74</v>
+      </c>
+      <c r="J88" s="2">
+        <v>0.0161</v>
+      </c>
+      <c r="K88" t="s">
+        <v>71</v>
+      </c>
+      <c r="L88" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12">
+      <c r="A89" t="s">
+        <v>37</v>
+      </c>
+      <c r="B89" t="s">
+        <v>56</v>
+      </c>
+      <c r="C89" t="s">
+        <v>58</v>
+      </c>
+      <c r="D89" t="s">
+        <v>64</v>
+      </c>
+      <c r="E89">
+        <v>1.5</v>
+      </c>
+      <c r="F89">
+        <v>1.54</v>
+      </c>
+      <c r="G89" s="1">
+        <v>0.584</v>
+      </c>
+      <c r="H89" t="s">
+        <v>66</v>
+      </c>
+      <c r="I89" s="2">
+        <v>11.51</v>
+      </c>
+      <c r="J89" s="2">
+        <v>0.0158</v>
+      </c>
+      <c r="K89" t="s">
+        <v>71</v>
+      </c>
+      <c r="L89" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12">
+      <c r="A90" t="s">
+        <v>48</v>
+      </c>
+      <c r="B90" t="s">
+        <v>53</v>
+      </c>
+      <c r="C90" t="s">
+        <v>55</v>
+      </c>
+      <c r="D90" t="s">
+        <v>64</v>
+      </c>
+      <c r="E90">
+        <v>1.5</v>
+      </c>
+      <c r="F90">
+        <v>1.8</v>
+      </c>
+      <c r="G90" s="1">
+        <v>0.582</v>
+      </c>
+      <c r="H90" t="s">
+        <v>66</v>
+      </c>
+      <c r="I90" s="2">
+        <v>11.03</v>
+      </c>
+      <c r="J90" s="2">
+        <v>0.0152</v>
+      </c>
+      <c r="K90" t="s">
+        <v>71</v>
+      </c>
+      <c r="L90" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12">
+      <c r="A91" t="s">
+        <v>40</v>
+      </c>
+      <c r="B91" t="s">
+        <v>53</v>
+      </c>
+      <c r="C91" t="s">
+        <v>55</v>
+      </c>
+      <c r="D91" t="s">
+        <v>63</v>
+      </c>
+      <c r="E91">
         <v>7.5</v>
       </c>
-      <c r="F69">
+      <c r="F91">
+        <v>8.44</v>
+      </c>
+      <c r="G91" s="1">
+        <v>0.581</v>
+      </c>
+      <c r="H91" t="s">
+        <v>67</v>
+      </c>
+      <c r="I91" s="2">
+        <v>10.99</v>
+      </c>
+      <c r="J91" s="2">
+        <v>0.0151</v>
+      </c>
+      <c r="K91" t="s">
+        <v>71</v>
+      </c>
+      <c r="L91" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12">
+      <c r="A92" t="s">
+        <v>49</v>
+      </c>
+      <c r="B92" t="s">
+        <v>57</v>
+      </c>
+      <c r="C92" t="s">
+        <v>54</v>
+      </c>
+      <c r="D92" t="s">
+        <v>61</v>
+      </c>
+      <c r="E92">
+        <v>2.5</v>
+      </c>
+      <c r="F92">
+        <v>3.26</v>
+      </c>
+      <c r="G92" s="1">
+        <v>0.581</v>
+      </c>
+      <c r="H92" t="s">
+        <v>67</v>
+      </c>
+      <c r="I92" s="2">
+        <v>10.98</v>
+      </c>
+      <c r="J92" s="2">
+        <v>0.0151</v>
+      </c>
+      <c r="K92" t="s">
+        <v>71</v>
+      </c>
+      <c r="L92" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12">
+      <c r="A93" t="s">
+        <v>22</v>
+      </c>
+      <c r="B93" t="s">
+        <v>58</v>
+      </c>
+      <c r="C93" t="s">
+        <v>56</v>
+      </c>
+      <c r="D93" t="s">
+        <v>61</v>
+      </c>
+      <c r="E93">
+        <v>3.5</v>
+      </c>
+      <c r="F93">
+        <v>3.3</v>
+      </c>
+      <c r="G93" s="1">
+        <v>0.58</v>
+      </c>
+      <c r="H93" t="s">
+        <v>66</v>
+      </c>
+      <c r="I93" s="2">
+        <v>10.64</v>
+      </c>
+      <c r="J93" s="2">
+        <v>0.0146</v>
+      </c>
+      <c r="K93" t="s">
+        <v>71</v>
+      </c>
+      <c r="L93" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12">
+      <c r="A94" t="s">
+        <v>49</v>
+      </c>
+      <c r="B94" t="s">
+        <v>57</v>
+      </c>
+      <c r="C94" t="s">
+        <v>54</v>
+      </c>
+      <c r="D94" t="s">
+        <v>62</v>
+      </c>
+      <c r="E94">
+        <v>18.5</v>
+      </c>
+      <c r="F94">
+        <v>15.92</v>
+      </c>
+      <c r="G94" s="1">
+        <v>0.579</v>
+      </c>
+      <c r="H94" t="s">
+        <v>66</v>
+      </c>
+      <c r="I94" s="2">
+        <v>10.57</v>
+      </c>
+      <c r="J94" s="2">
+        <v>0.0145</v>
+      </c>
+      <c r="K94" t="s">
+        <v>71</v>
+      </c>
+      <c r="L94" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12">
+      <c r="A95" t="s">
+        <v>18</v>
+      </c>
+      <c r="B95" t="s">
+        <v>54</v>
+      </c>
+      <c r="C95" t="s">
+        <v>59</v>
+      </c>
+      <c r="D95" t="s">
+        <v>63</v>
+      </c>
+      <c r="E95">
+        <v>9.5</v>
+      </c>
+      <c r="F95">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="G95" s="1">
+        <v>0.579</v>
+      </c>
+      <c r="H95" t="s">
+        <v>66</v>
+      </c>
+      <c r="I95" s="2">
+        <v>10.54</v>
+      </c>
+      <c r="J95" s="2">
+        <v>0.0145</v>
+      </c>
+      <c r="K95" t="s">
+        <v>71</v>
+      </c>
+      <c r="L95" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12">
+      <c r="A96" t="s">
+        <v>37</v>
+      </c>
+      <c r="B96" t="s">
+        <v>56</v>
+      </c>
+      <c r="C96" t="s">
+        <v>58</v>
+      </c>
+      <c r="D96" t="s">
+        <v>63</v>
+      </c>
+      <c r="E96">
+        <v>12.5</v>
+      </c>
+      <c r="F96">
+        <v>10.96</v>
+      </c>
+      <c r="G96" s="1">
+        <v>0.577</v>
+      </c>
+      <c r="H96" t="s">
+        <v>66</v>
+      </c>
+      <c r="I96" s="2">
+        <v>10.11</v>
+      </c>
+      <c r="J96" s="2">
+        <v>0.0139</v>
+      </c>
+      <c r="K96" t="s">
+        <v>71</v>
+      </c>
+      <c r="L96" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12">
+      <c r="A97" t="s">
+        <v>36</v>
+      </c>
+      <c r="B97" t="s">
+        <v>53</v>
+      </c>
+      <c r="C97" t="s">
+        <v>55</v>
+      </c>
+      <c r="D97" t="s">
+        <v>62</v>
+      </c>
+      <c r="E97">
+        <v>13.5</v>
+      </c>
+      <c r="F97">
+        <v>11.47</v>
+      </c>
+      <c r="G97" s="1">
+        <v>0.576</v>
+      </c>
+      <c r="H97" t="s">
+        <v>66</v>
+      </c>
+      <c r="I97" s="2">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="J97" s="2">
+        <v>0.0136</v>
+      </c>
+      <c r="K97" t="s">
+        <v>71</v>
+      </c>
+      <c r="L97" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12">
+      <c r="A98" t="s">
+        <v>21</v>
+      </c>
+      <c r="B98" t="s">
+        <v>57</v>
+      </c>
+      <c r="C98" t="s">
+        <v>54</v>
+      </c>
+      <c r="D98" t="s">
+        <v>62</v>
+      </c>
+      <c r="E98">
+        <v>19.5</v>
+      </c>
+      <c r="F98">
+        <v>21.05</v>
+      </c>
+      <c r="G98" s="1">
+        <v>0.571</v>
+      </c>
+      <c r="H98" t="s">
+        <v>67</v>
+      </c>
+      <c r="I98" s="2">
+        <v>8.98</v>
+      </c>
+      <c r="J98" s="2">
+        <v>0.0124</v>
+      </c>
+      <c r="K98" t="s">
+        <v>71</v>
+      </c>
+      <c r="L98" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12">
+      <c r="A99" t="s">
+        <v>17</v>
+      </c>
+      <c r="B99" t="s">
+        <v>55</v>
+      </c>
+      <c r="C99" t="s">
+        <v>60</v>
+      </c>
+      <c r="D99" t="s">
+        <v>62</v>
+      </c>
+      <c r="E99">
+        <v>29.5</v>
+      </c>
+      <c r="F99">
+        <v>25.73</v>
+      </c>
+      <c r="G99" s="1">
+        <v>0.571</v>
+      </c>
+      <c r="H99" t="s">
+        <v>66</v>
+      </c>
+      <c r="I99" s="2">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="J99" s="2">
+        <v>0.0123</v>
+      </c>
+      <c r="K99" t="s">
+        <v>71</v>
+      </c>
+      <c r="L99" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12">
+      <c r="A100" t="s">
+        <v>45</v>
+      </c>
+      <c r="B100" t="s">
+        <v>55</v>
+      </c>
+      <c r="C100" t="s">
+        <v>60</v>
+      </c>
+      <c r="D100" t="s">
+        <v>64</v>
+      </c>
+      <c r="E100">
+        <v>1.5</v>
+      </c>
+      <c r="F100">
+        <v>1.93</v>
+      </c>
+      <c r="G100" s="1">
+        <v>0.569</v>
+      </c>
+      <c r="H100" t="s">
+        <v>67</v>
+      </c>
+      <c r="I100" s="2">
+        <v>8.6</v>
+      </c>
+      <c r="J100" s="2">
+        <v>0.0118</v>
+      </c>
+      <c r="K100" t="s">
+        <v>71</v>
+      </c>
+      <c r="L100" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12">
+      <c r="A101" t="s">
+        <v>22</v>
+      </c>
+      <c r="B101" t="s">
+        <v>58</v>
+      </c>
+      <c r="C101" t="s">
+        <v>56</v>
+      </c>
+      <c r="D101" t="s">
+        <v>65</v>
+      </c>
+      <c r="E101">
+        <v>10.5</v>
+      </c>
+      <c r="F101">
+        <v>9.75</v>
+      </c>
+      <c r="G101" s="1">
+        <v>0.569</v>
+      </c>
+      <c r="H101" t="s">
+        <v>66</v>
+      </c>
+      <c r="I101" s="2">
+        <v>8.57</v>
+      </c>
+      <c r="J101" s="2">
+        <v>0.0118</v>
+      </c>
+      <c r="K101" t="s">
+        <v>71</v>
+      </c>
+      <c r="L101" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12">
+      <c r="A102" t="s">
+        <v>14</v>
+      </c>
+      <c r="B102" t="s">
+        <v>54</v>
+      </c>
+      <c r="C102" t="s">
+        <v>59</v>
+      </c>
+      <c r="D102" t="s">
+        <v>64</v>
+      </c>
+      <c r="E102">
+        <v>1.5</v>
+      </c>
+      <c r="F102">
+        <v>1.55</v>
+      </c>
+      <c r="G102" s="1">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="H102" t="s">
+        <v>66</v>
+      </c>
+      <c r="I102" s="2">
+        <v>8.43</v>
+      </c>
+      <c r="J102" s="2">
+        <v>0.0116</v>
+      </c>
+      <c r="K102" t="s">
+        <v>71</v>
+      </c>
+      <c r="L102" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12">
+      <c r="A103" t="s">
+        <v>51</v>
+      </c>
+      <c r="B103" t="s">
+        <v>53</v>
+      </c>
+      <c r="C103" t="s">
+        <v>55</v>
+      </c>
+      <c r="D103" t="s">
+        <v>64</v>
+      </c>
+      <c r="E103">
+        <v>1.5</v>
+      </c>
+      <c r="F103">
+        <v>1.73</v>
+      </c>
+      <c r="G103" s="1">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="H103" t="s">
+        <v>66</v>
+      </c>
+      <c r="I103" s="2">
+        <v>8.42</v>
+      </c>
+      <c r="J103" s="2">
+        <v>0.0116</v>
+      </c>
+      <c r="K103" t="s">
+        <v>71</v>
+      </c>
+      <c r="L103" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12">
+      <c r="A104" t="s">
+        <v>51</v>
+      </c>
+      <c r="B104" t="s">
+        <v>53</v>
+      </c>
+      <c r="C104" t="s">
+        <v>55</v>
+      </c>
+      <c r="D104" t="s">
+        <v>65</v>
+      </c>
+      <c r="E104">
+        <v>10.5</v>
+      </c>
+      <c r="F104">
+        <v>12.17</v>
+      </c>
+      <c r="G104" s="1">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="H104" t="s">
+        <v>67</v>
+      </c>
+      <c r="I104" s="2">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="J104" s="2">
+        <v>0.011</v>
+      </c>
+      <c r="K104" t="s">
+        <v>71</v>
+      </c>
+      <c r="L104" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12">
+      <c r="A105" t="s">
+        <v>37</v>
+      </c>
+      <c r="B105" t="s">
+        <v>56</v>
+      </c>
+      <c r="C105" t="s">
+        <v>58</v>
+      </c>
+      <c r="D105" t="s">
+        <v>62</v>
+      </c>
+      <c r="E105">
+        <v>26.5</v>
+      </c>
+      <c r="F105">
+        <v>23.62</v>
+      </c>
+      <c r="G105" s="1">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="H105" t="s">
+        <v>66</v>
+      </c>
+      <c r="I105" s="2">
+        <v>7.64</v>
+      </c>
+      <c r="J105" s="2">
+        <v>0.0105</v>
+      </c>
+      <c r="K105" t="s">
+        <v>71</v>
+      </c>
+      <c r="L105" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12">
+      <c r="A106" t="s">
+        <v>20</v>
+      </c>
+      <c r="B106" t="s">
+        <v>56</v>
+      </c>
+      <c r="C106" t="s">
+        <v>58</v>
+      </c>
+      <c r="D106" t="s">
+        <v>61</v>
+      </c>
+      <c r="E106">
+        <v>2.5</v>
+      </c>
+      <c r="F106">
+        <v>3.05</v>
+      </c>
+      <c r="G106" s="1">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="H106" t="s">
+        <v>67</v>
+      </c>
+      <c r="I106" s="2">
+        <v>7.62</v>
+      </c>
+      <c r="J106" s="2">
+        <v>0.0105</v>
+      </c>
+      <c r="K106" t="s">
+        <v>71</v>
+      </c>
+      <c r="L106" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12">
+      <c r="A107" t="s">
+        <v>29</v>
+      </c>
+      <c r="B107" t="s">
+        <v>55</v>
+      </c>
+      <c r="C107" t="s">
+        <v>60</v>
+      </c>
+      <c r="D107" t="s">
+        <v>64</v>
+      </c>
+      <c r="E107">
+        <v>2.5</v>
+      </c>
+      <c r="F107">
+        <v>2.56</v>
+      </c>
+      <c r="G107" s="1">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="H107" t="s">
+        <v>66</v>
+      </c>
+      <c r="I107" s="2">
+        <v>7.01</v>
+      </c>
+      <c r="J107" s="2">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="K107" t="s">
+        <v>71</v>
+      </c>
+      <c r="L107" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12">
+      <c r="A108" t="s">
+        <v>22</v>
+      </c>
+      <c r="B108" t="s">
+        <v>58</v>
+      </c>
+      <c r="C108" t="s">
+        <v>56</v>
+      </c>
+      <c r="D108" t="s">
+        <v>63</v>
+      </c>
+      <c r="E108">
+        <v>7.5</v>
+      </c>
+      <c r="F108">
+        <v>6.83</v>
+      </c>
+      <c r="G108" s="1">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="H108" t="s">
+        <v>66</v>
+      </c>
+      <c r="I108" s="2">
+        <v>6.7</v>
+      </c>
+      <c r="J108" s="2">
+        <v>0.0092</v>
+      </c>
+      <c r="K108" t="s">
+        <v>71</v>
+      </c>
+      <c r="L108" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12">
+      <c r="A109" t="s">
+        <v>38</v>
+      </c>
+      <c r="B109" t="s">
+        <v>53</v>
+      </c>
+      <c r="C109" t="s">
+        <v>55</v>
+      </c>
+      <c r="D109" t="s">
+        <v>64</v>
+      </c>
+      <c r="E109">
+        <v>5.5</v>
+      </c>
+      <c r="F109">
+        <v>5.5</v>
+      </c>
+      <c r="G109" s="1">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="H109" t="s">
+        <v>66</v>
+      </c>
+      <c r="I109" s="2">
+        <v>6.64</v>
+      </c>
+      <c r="J109" s="2">
+        <v>0.0091</v>
+      </c>
+      <c r="K109" t="s">
+        <v>71</v>
+      </c>
+      <c r="L109" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12">
+      <c r="A110" t="s">
+        <v>13</v>
+      </c>
+      <c r="B110" t="s">
+        <v>54</v>
+      </c>
+      <c r="C110" t="s">
+        <v>59</v>
+      </c>
+      <c r="D110" t="s">
+        <v>61</v>
+      </c>
+      <c r="E110">
+        <v>2.5</v>
+      </c>
+      <c r="F110">
+        <v>2.91</v>
+      </c>
+      <c r="G110" s="1">
+        <v>0.556</v>
+      </c>
+      <c r="H110" t="s">
+        <v>67</v>
+      </c>
+      <c r="I110" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="J110" s="2">
+        <v>0.008399999999999999</v>
+      </c>
+      <c r="K110" t="s">
+        <v>71</v>
+      </c>
+      <c r="L110" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12">
+      <c r="A111" t="s">
+        <v>44</v>
+      </c>
+      <c r="B111" t="s">
+        <v>58</v>
+      </c>
+      <c r="C111" t="s">
+        <v>56</v>
+      </c>
+      <c r="D111" t="s">
+        <v>65</v>
+      </c>
+      <c r="E111">
+        <v>8.5</v>
+      </c>
+      <c r="F111">
+        <v>7.52</v>
+      </c>
+      <c r="G111" s="1">
+        <v>0.555</v>
+      </c>
+      <c r="H111" t="s">
+        <v>66</v>
+      </c>
+      <c r="I111" s="2">
+        <v>6</v>
+      </c>
+      <c r="J111" s="2">
+        <v>0.008200000000000001</v>
+      </c>
+      <c r="K111" t="s">
+        <v>71</v>
+      </c>
+      <c r="L111" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12">
+      <c r="A112" t="s">
+        <v>52</v>
+      </c>
+      <c r="B112" t="s">
+        <v>56</v>
+      </c>
+      <c r="C112" t="s">
+        <v>58</v>
+      </c>
+      <c r="D112" t="s">
+        <v>63</v>
+      </c>
+      <c r="E112">
+        <v>7.5</v>
+      </c>
+      <c r="F112">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="G112" s="1">
+        <v>0.555</v>
+      </c>
+      <c r="H112" t="s">
+        <v>67</v>
+      </c>
+      <c r="I112" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="J112" s="2">
+        <v>0.0081</v>
+      </c>
+      <c r="K112" t="s">
+        <v>71</v>
+      </c>
+      <c r="L112" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12">
+      <c r="A113" t="s">
+        <v>23</v>
+      </c>
+      <c r="B113" t="s">
+        <v>57</v>
+      </c>
+      <c r="C113" t="s">
+        <v>54</v>
+      </c>
+      <c r="D113" t="s">
+        <v>63</v>
+      </c>
+      <c r="E113">
+        <v>10.5</v>
+      </c>
+      <c r="F113">
+        <v>11.55</v>
+      </c>
+      <c r="G113" s="1">
+        <v>0.554</v>
+      </c>
+      <c r="H113" t="s">
+        <v>67</v>
+      </c>
+      <c r="I113" s="2">
+        <v>5.79</v>
+      </c>
+      <c r="J113" s="2">
+        <v>0.008</v>
+      </c>
+      <c r="K113" t="s">
+        <v>71</v>
+      </c>
+      <c r="L113" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12">
+      <c r="A114" t="s">
+        <v>32</v>
+      </c>
+      <c r="B114" t="s">
+        <v>55</v>
+      </c>
+      <c r="C114" t="s">
+        <v>60</v>
+      </c>
+      <c r="D114" t="s">
+        <v>64</v>
+      </c>
+      <c r="E114">
+        <v>2.5</v>
+      </c>
+      <c r="F114">
+        <v>2.99</v>
+      </c>
+      <c r="G114" s="1">
+        <v>0.554</v>
+      </c>
+      <c r="H114" t="s">
+        <v>67</v>
+      </c>
+      <c r="I114" s="2">
+        <v>5.78</v>
+      </c>
+      <c r="J114" s="2">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="K114" t="s">
+        <v>71</v>
+      </c>
+      <c r="L114" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12">
+      <c r="A115" t="s">
+        <v>52</v>
+      </c>
+      <c r="B115" t="s">
+        <v>56</v>
+      </c>
+      <c r="C115" t="s">
+        <v>58</v>
+      </c>
+      <c r="D115" t="s">
+        <v>64</v>
+      </c>
+      <c r="E115">
+        <v>2.5</v>
+      </c>
+      <c r="F115">
+        <v>3.3</v>
+      </c>
+      <c r="G115" s="1">
+        <v>0.554</v>
+      </c>
+      <c r="H115" t="s">
+        <v>67</v>
+      </c>
+      <c r="I115" s="2">
+        <v>5.69</v>
+      </c>
+      <c r="J115" s="2">
+        <v>0.0078</v>
+      </c>
+      <c r="K115" t="s">
+        <v>71</v>
+      </c>
+      <c r="L115" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12">
+      <c r="A116" t="s">
+        <v>38</v>
+      </c>
+      <c r="B116" t="s">
+        <v>53</v>
+      </c>
+      <c r="C116" t="s">
+        <v>55</v>
+      </c>
+      <c r="D116" t="s">
+        <v>65</v>
+      </c>
+      <c r="E116">
+        <v>14.5</v>
+      </c>
+      <c r="F116">
+        <v>16.62</v>
+      </c>
+      <c r="G116" s="1">
+        <v>0.553</v>
+      </c>
+      <c r="H116" t="s">
+        <v>67</v>
+      </c>
+      <c r="I116" s="2">
+        <v>5.67</v>
+      </c>
+      <c r="J116" s="2">
+        <v>0.0078</v>
+      </c>
+      <c r="K116" t="s">
+        <v>71</v>
+      </c>
+      <c r="L116" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12">
+      <c r="A117" t="s">
+        <v>24</v>
+      </c>
+      <c r="B117" t="s">
+        <v>58</v>
+      </c>
+      <c r="C117" t="s">
+        <v>56</v>
+      </c>
+      <c r="D117" t="s">
+        <v>65</v>
+      </c>
+      <c r="E117">
+        <v>17.5</v>
+      </c>
+      <c r="F117">
+        <v>18.44</v>
+      </c>
+      <c r="G117" s="1">
+        <v>0.553</v>
+      </c>
+      <c r="H117" t="s">
+        <v>67</v>
+      </c>
+      <c r="I117" s="2">
+        <v>5.64</v>
+      </c>
+      <c r="J117" s="2">
+        <v>0.0078</v>
+      </c>
+      <c r="K117" t="s">
+        <v>71</v>
+      </c>
+      <c r="L117" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12">
+      <c r="A118" t="s">
+        <v>28</v>
+      </c>
+      <c r="B118" t="s">
+        <v>56</v>
+      </c>
+      <c r="C118" t="s">
+        <v>58</v>
+      </c>
+      <c r="D118" t="s">
+        <v>61</v>
+      </c>
+      <c r="E118">
+        <v>1.5</v>
+      </c>
+      <c r="F118">
+        <v>2.18</v>
+      </c>
+      <c r="G118" s="1">
+        <v>0.553</v>
+      </c>
+      <c r="H118" t="s">
+        <v>67</v>
+      </c>
+      <c r="I118" s="2">
+        <v>5.61</v>
+      </c>
+      <c r="J118" s="2">
+        <v>0.0077</v>
+      </c>
+      <c r="K118" t="s">
+        <v>71</v>
+      </c>
+      <c r="L118" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12">
+      <c r="A119" t="s">
+        <v>31</v>
+      </c>
+      <c r="B119" t="s">
+        <v>57</v>
+      </c>
+      <c r="C119" t="s">
+        <v>54</v>
+      </c>
+      <c r="D119" t="s">
+        <v>61</v>
+      </c>
+      <c r="E119">
+        <v>4.5</v>
+      </c>
+      <c r="F119">
+        <v>5.2</v>
+      </c>
+      <c r="G119" s="1">
+        <v>0.553</v>
+      </c>
+      <c r="H119" t="s">
+        <v>66</v>
+      </c>
+      <c r="I119" s="2">
+        <v>5.49</v>
+      </c>
+      <c r="J119" s="2">
+        <v>0.0076</v>
+      </c>
+      <c r="K119" t="s">
+        <v>71</v>
+      </c>
+      <c r="L119" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12">
+      <c r="A120" t="s">
+        <v>52</v>
+      </c>
+      <c r="B120" t="s">
+        <v>56</v>
+      </c>
+      <c r="C120" t="s">
+        <v>58</v>
+      </c>
+      <c r="D120" t="s">
+        <v>62</v>
+      </c>
+      <c r="E120">
+        <v>17.5</v>
+      </c>
+      <c r="F120">
+        <v>15.69</v>
+      </c>
+      <c r="G120" s="1">
+        <v>0.551</v>
+      </c>
+      <c r="H120" t="s">
+        <v>66</v>
+      </c>
+      <c r="I120" s="2">
+        <v>5.13</v>
+      </c>
+      <c r="J120" s="2">
+        <v>0.007</v>
+      </c>
+      <c r="K120" t="s">
+        <v>71</v>
+      </c>
+      <c r="L120" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12">
+      <c r="A121" t="s">
+        <v>26</v>
+      </c>
+      <c r="B121" t="s">
+        <v>54</v>
+      </c>
+      <c r="C121" t="s">
+        <v>59</v>
+      </c>
+      <c r="D121" t="s">
+        <v>65</v>
+      </c>
+      <c r="E121">
+        <v>13.5</v>
+      </c>
+      <c r="F121">
+        <v>12.33</v>
+      </c>
+      <c r="G121" s="1">
+        <v>0.55</v>
+      </c>
+      <c r="H121" t="s">
+        <v>66</v>
+      </c>
+      <c r="I121" s="2">
+        <v>4.97</v>
+      </c>
+      <c r="J121" s="2">
+        <v>0.0068</v>
+      </c>
+      <c r="K121" t="s">
+        <v>71</v>
+      </c>
+      <c r="L121" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12">
+      <c r="A122" t="s">
+        <v>47</v>
+      </c>
+      <c r="B122" t="s">
+        <v>58</v>
+      </c>
+      <c r="C122" t="s">
+        <v>56</v>
+      </c>
+      <c r="D122" t="s">
+        <v>65</v>
+      </c>
+      <c r="E122">
+        <v>9.5</v>
+      </c>
+      <c r="F122">
+        <v>8.18</v>
+      </c>
+      <c r="G122" s="1">
+        <v>0.549</v>
+      </c>
+      <c r="H122" t="s">
+        <v>66</v>
+      </c>
+      <c r="I122" s="2">
+        <v>4.87</v>
+      </c>
+      <c r="J122" s="2">
+        <v>0.0067</v>
+      </c>
+      <c r="K122" t="s">
+        <v>71</v>
+      </c>
+      <c r="L122" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12">
+      <c r="A123" t="s">
+        <v>47</v>
+      </c>
+      <c r="B123" t="s">
+        <v>58</v>
+      </c>
+      <c r="C123" t="s">
+        <v>56</v>
+      </c>
+      <c r="D123" t="s">
+        <v>64</v>
+      </c>
+      <c r="E123">
+        <v>4.5</v>
+      </c>
+      <c r="F123">
+        <v>4.9</v>
+      </c>
+      <c r="G123" s="1">
+        <v>0.549</v>
+      </c>
+      <c r="H123" t="s">
+        <v>66</v>
+      </c>
+      <c r="I123" s="2">
+        <v>4.74</v>
+      </c>
+      <c r="J123" s="2">
+        <v>0.0065</v>
+      </c>
+      <c r="K123" t="s">
+        <v>71</v>
+      </c>
+      <c r="L123" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12">
+      <c r="A124" t="s">
+        <v>24</v>
+      </c>
+      <c r="B124" t="s">
+        <v>58</v>
+      </c>
+      <c r="C124" t="s">
+        <v>56</v>
+      </c>
+      <c r="D124" t="s">
+        <v>63</v>
+      </c>
+      <c r="E124">
+        <v>7.5</v>
+      </c>
+      <c r="F124">
+        <v>8.01</v>
+      </c>
+      <c r="G124" s="1">
+        <v>0.548</v>
+      </c>
+      <c r="H124" t="s">
+        <v>67</v>
+      </c>
+      <c r="I124" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="J124" s="2">
+        <v>0.0065</v>
+      </c>
+      <c r="K124" t="s">
+        <v>71</v>
+      </c>
+      <c r="L124" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12">
+      <c r="A125" t="s">
+        <v>48</v>
+      </c>
+      <c r="B125" t="s">
+        <v>53</v>
+      </c>
+      <c r="C125" t="s">
+        <v>55</v>
+      </c>
+      <c r="D125" t="s">
+        <v>61</v>
+      </c>
+      <c r="E125">
+        <v>3.5</v>
+      </c>
+      <c r="F125">
+        <v>3.64</v>
+      </c>
+      <c r="G125" s="1">
+        <v>0.548</v>
+      </c>
+      <c r="H125" t="s">
+        <v>66</v>
+      </c>
+      <c r="I125" s="2">
+        <v>4.61</v>
+      </c>
+      <c r="J125" s="2">
+        <v>0.0063</v>
+      </c>
+      <c r="K125" t="s">
+        <v>71</v>
+      </c>
+      <c r="L125" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12">
+      <c r="A126" t="s">
+        <v>19</v>
+      </c>
+      <c r="B126" t="s">
+        <v>55</v>
+      </c>
+      <c r="C126" t="s">
+        <v>60</v>
+      </c>
+      <c r="D126" t="s">
+        <v>65</v>
+      </c>
+      <c r="E126">
+        <v>8.5</v>
+      </c>
+      <c r="F126">
+        <v>7.45</v>
+      </c>
+      <c r="G126" s="1">
+        <v>0.548</v>
+      </c>
+      <c r="H126" t="s">
+        <v>66</v>
+      </c>
+      <c r="I126" s="2">
+        <v>4.59</v>
+      </c>
+      <c r="J126" s="2">
+        <v>0.0063</v>
+      </c>
+      <c r="K126" t="s">
+        <v>71</v>
+      </c>
+      <c r="L126" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12">
+      <c r="A127" t="s">
+        <v>50</v>
+      </c>
+      <c r="B127" t="s">
+        <v>56</v>
+      </c>
+      <c r="C127" t="s">
+        <v>58</v>
+      </c>
+      <c r="D127" t="s">
+        <v>62</v>
+      </c>
+      <c r="E127">
+        <v>15.5</v>
+      </c>
+      <c r="F127">
+        <v>14.17</v>
+      </c>
+      <c r="G127" s="1">
+        <v>0.547</v>
+      </c>
+      <c r="H127" t="s">
+        <v>66</v>
+      </c>
+      <c r="I127" s="2">
+        <v>4.51</v>
+      </c>
+      <c r="J127" s="2">
+        <v>0.0062</v>
+      </c>
+      <c r="K127" t="s">
+        <v>71</v>
+      </c>
+      <c r="L127" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12">
+      <c r="A128" t="s">
+        <v>35</v>
+      </c>
+      <c r="B128" t="s">
+        <v>58</v>
+      </c>
+      <c r="C128" t="s">
+        <v>56</v>
+      </c>
+      <c r="D128" t="s">
+        <v>61</v>
+      </c>
+      <c r="E128">
+        <v>3.5</v>
+      </c>
+      <c r="F128">
+        <v>3.58</v>
+      </c>
+      <c r="G128" s="1">
+        <v>0.546</v>
+      </c>
+      <c r="H128" t="s">
+        <v>66</v>
+      </c>
+      <c r="I128" s="2">
+        <v>4.26</v>
+      </c>
+      <c r="J128" s="2">
+        <v>0.0059</v>
+      </c>
+      <c r="K128" t="s">
+        <v>71</v>
+      </c>
+      <c r="L128" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12">
+      <c r="A129" t="s">
+        <v>43</v>
+      </c>
+      <c r="B129" t="s">
+        <v>55</v>
+      </c>
+      <c r="C129" t="s">
+        <v>60</v>
+      </c>
+      <c r="D129" t="s">
+        <v>65</v>
+      </c>
+      <c r="E129">
+        <v>13.5</v>
+      </c>
+      <c r="F129">
+        <v>14.1</v>
+      </c>
+      <c r="G129" s="1">
+        <v>0.545</v>
+      </c>
+      <c r="H129" t="s">
+        <v>67</v>
+      </c>
+      <c r="I129" s="2">
+        <v>4.11</v>
+      </c>
+      <c r="J129" s="2">
+        <v>0.0113</v>
+      </c>
+      <c r="K129" t="s">
+        <v>71</v>
+      </c>
+      <c r="L129" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12">
+      <c r="A130" t="s">
+        <v>41</v>
+      </c>
+      <c r="B130" t="s">
+        <v>53</v>
+      </c>
+      <c r="C130" t="s">
+        <v>55</v>
+      </c>
+      <c r="D130" t="s">
+        <v>61</v>
+      </c>
+      <c r="E130">
+        <v>10.5</v>
+      </c>
+      <c r="F130">
+        <v>10.5</v>
+      </c>
+      <c r="G130" s="1">
+        <v>0.544</v>
+      </c>
+      <c r="H130" t="s">
+        <v>66</v>
+      </c>
+      <c r="I130" s="2">
+        <v>3.94</v>
+      </c>
+      <c r="J130" s="2">
+        <v>0.0108</v>
+      </c>
+      <c r="K130" t="s">
+        <v>71</v>
+      </c>
+      <c r="L130" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12">
+      <c r="A131" t="s">
+        <v>45</v>
+      </c>
+      <c r="B131" t="s">
+        <v>55</v>
+      </c>
+      <c r="C131" t="s">
+        <v>60</v>
+      </c>
+      <c r="D131" t="s">
+        <v>62</v>
+      </c>
+      <c r="E131">
+        <v>14.5</v>
+      </c>
+      <c r="F131">
+        <v>15.67</v>
+      </c>
+      <c r="G131" s="1">
+        <v>0.544</v>
+      </c>
+      <c r="H131" t="s">
+        <v>67</v>
+      </c>
+      <c r="I131" s="2">
+        <v>3.82</v>
+      </c>
+      <c r="J131" s="2">
+        <v>0.0105</v>
+      </c>
+      <c r="K131" t="s">
+        <v>71</v>
+      </c>
+      <c r="L131" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12">
+      <c r="A132" t="s">
+        <v>27</v>
+      </c>
+      <c r="B132" t="s">
+        <v>54</v>
+      </c>
+      <c r="C132" t="s">
+        <v>59</v>
+      </c>
+      <c r="D132" t="s">
+        <v>62</v>
+      </c>
+      <c r="E132">
+        <v>34.5</v>
+      </c>
+      <c r="F132">
+        <v>31.61</v>
+      </c>
+      <c r="G132" s="1">
+        <v>0.543</v>
+      </c>
+      <c r="H132" t="s">
+        <v>66</v>
+      </c>
+      <c r="I132" s="2">
+        <v>3.63</v>
+      </c>
+      <c r="J132" s="2">
+        <v>0.005</v>
+      </c>
+      <c r="K132" t="s">
+        <v>71</v>
+      </c>
+      <c r="L132" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12">
+      <c r="A133" t="s">
+        <v>34</v>
+      </c>
+      <c r="B133" t="s">
+        <v>56</v>
+      </c>
+      <c r="C133" t="s">
+        <v>58</v>
+      </c>
+      <c r="D133" t="s">
+        <v>62</v>
+      </c>
+      <c r="E133">
+        <v>20.5</v>
+      </c>
+      <c r="F133">
+        <v>19.01</v>
+      </c>
+      <c r="G133" s="1">
+        <v>0.543</v>
+      </c>
+      <c r="H133" t="s">
+        <v>66</v>
+      </c>
+      <c r="I133" s="2">
+        <v>3.57</v>
+      </c>
+      <c r="J133" s="2">
+        <v>0.0098</v>
+      </c>
+      <c r="K133" t="s">
+        <v>71</v>
+      </c>
+      <c r="L133" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12">
+      <c r="A134" t="s">
+        <v>18</v>
+      </c>
+      <c r="B134" t="s">
+        <v>54</v>
+      </c>
+      <c r="C134" t="s">
+        <v>59</v>
+      </c>
+      <c r="D134" t="s">
+        <v>65</v>
+      </c>
+      <c r="E134">
+        <v>26.5</v>
+      </c>
+      <c r="F134">
+        <v>24.67</v>
+      </c>
+      <c r="G134" s="1">
+        <v>0.542</v>
+      </c>
+      <c r="H134" t="s">
+        <v>66</v>
+      </c>
+      <c r="I134" s="2">
+        <v>3.51</v>
+      </c>
+      <c r="J134" s="2">
+        <v>0.0097</v>
+      </c>
+      <c r="K134" t="s">
+        <v>71</v>
+      </c>
+      <c r="L134" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12">
+      <c r="A135" t="s">
+        <v>28</v>
+      </c>
+      <c r="B135" t="s">
+        <v>56</v>
+      </c>
+      <c r="C135" t="s">
+        <v>58</v>
+      </c>
+      <c r="D135" t="s">
+        <v>62</v>
+      </c>
+      <c r="E135">
+        <v>17.5</v>
+      </c>
+      <c r="F135">
+        <v>18.33</v>
+      </c>
+      <c r="G135" s="1">
+        <v>0.542</v>
+      </c>
+      <c r="H135" t="s">
+        <v>67</v>
+      </c>
+      <c r="I135" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="J135" s="2">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="K135" t="s">
+        <v>71</v>
+      </c>
+      <c r="L135" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12">
+      <c r="A136" t="s">
+        <v>38</v>
+      </c>
+      <c r="B136" t="s">
+        <v>53</v>
+      </c>
+      <c r="C136" t="s">
+        <v>55</v>
+      </c>
+      <c r="D136" t="s">
+        <v>63</v>
+      </c>
+      <c r="E136">
+        <v>10.5</v>
+      </c>
+      <c r="F136">
+        <v>9.77</v>
+      </c>
+      <c r="G136" s="1">
+        <v>0.541</v>
+      </c>
+      <c r="H136" t="s">
+        <v>66</v>
+      </c>
+      <c r="I136" s="2">
+        <v>3.34</v>
+      </c>
+      <c r="J136" s="2">
+        <v>0.0046</v>
+      </c>
+      <c r="K136" t="s">
+        <v>71</v>
+      </c>
+      <c r="L136" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12">
+      <c r="A137" t="s">
+        <v>12</v>
+      </c>
+      <c r="B137" t="s">
+        <v>53</v>
+      </c>
+      <c r="C137" t="s">
+        <v>55</v>
+      </c>
+      <c r="D137" t="s">
+        <v>62</v>
+      </c>
+      <c r="E137">
+        <v>26.5</v>
+      </c>
+      <c r="F137">
+        <v>24.5</v>
+      </c>
+      <c r="G137" s="1">
+        <v>0.541</v>
+      </c>
+      <c r="H137" t="s">
+        <v>66</v>
+      </c>
+      <c r="I137" s="2">
+        <v>3.25</v>
+      </c>
+      <c r="J137" s="2">
+        <v>0.0089</v>
+      </c>
+      <c r="K137" t="s">
+        <v>71</v>
+      </c>
+      <c r="L137" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12">
+      <c r="A138" t="s">
+        <v>20</v>
+      </c>
+      <c r="B138" t="s">
+        <v>56</v>
+      </c>
+      <c r="C138" t="s">
+        <v>58</v>
+      </c>
+      <c r="D138" t="s">
+        <v>65</v>
+      </c>
+      <c r="E138">
+        <v>16.5</v>
+      </c>
+      <c r="F138">
+        <v>18.09</v>
+      </c>
+      <c r="G138" s="1">
+        <v>0.54</v>
+      </c>
+      <c r="H138" t="s">
+        <v>67</v>
+      </c>
+      <c r="I138" s="2">
+        <v>3.17</v>
+      </c>
+      <c r="J138" s="2">
+        <v>0.0044</v>
+      </c>
+      <c r="K138" t="s">
+        <v>71</v>
+      </c>
+      <c r="L138" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12">
+      <c r="A139" t="s">
+        <v>21</v>
+      </c>
+      <c r="B139" t="s">
+        <v>57</v>
+      </c>
+      <c r="C139" t="s">
+        <v>54</v>
+      </c>
+      <c r="D139" t="s">
+        <v>61</v>
+      </c>
+      <c r="E139">
+        <v>3.5</v>
+      </c>
+      <c r="F139">
+        <v>4.87</v>
+      </c>
+      <c r="G139" s="1">
+        <v>0.539</v>
+      </c>
+      <c r="H139" t="s">
+        <v>67</v>
+      </c>
+      <c r="I139" s="2">
+        <v>2.94</v>
+      </c>
+      <c r="J139" s="2">
+        <v>0.004</v>
+      </c>
+      <c r="K139" t="s">
+        <v>71</v>
+      </c>
+      <c r="L139" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12">
+      <c r="A140" t="s">
+        <v>43</v>
+      </c>
+      <c r="B140" t="s">
+        <v>55</v>
+      </c>
+      <c r="C140" t="s">
+        <v>60</v>
+      </c>
+      <c r="D140" t="s">
+        <v>61</v>
+      </c>
+      <c r="E140">
+        <v>5.5</v>
+      </c>
+      <c r="F140">
+        <v>5.97</v>
+      </c>
+      <c r="G140" s="1">
+        <v>0.538</v>
+      </c>
+      <c r="H140" t="s">
+        <v>66</v>
+      </c>
+      <c r="I140" s="2">
+        <v>2.63</v>
+      </c>
+      <c r="J140" s="2">
+        <v>0.0036</v>
+      </c>
+      <c r="K140" t="s">
+        <v>71</v>
+      </c>
+      <c r="L140" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12">
+      <c r="A141" t="s">
+        <v>48</v>
+      </c>
+      <c r="B141" t="s">
+        <v>53</v>
+      </c>
+      <c r="C141" t="s">
+        <v>55</v>
+      </c>
+      <c r="D141" t="s">
+        <v>62</v>
+      </c>
+      <c r="E141">
+        <v>16.5</v>
+      </c>
+      <c r="F141">
+        <v>15.5</v>
+      </c>
+      <c r="G141" s="1">
+        <v>0.537</v>
+      </c>
+      <c r="H141" t="s">
+        <v>66</v>
+      </c>
+      <c r="I141" s="2">
+        <v>2.57</v>
+      </c>
+      <c r="J141" s="2">
+        <v>0.0071</v>
+      </c>
+      <c r="K141" t="s">
+        <v>71</v>
+      </c>
+      <c r="L141" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12">
+      <c r="A142" t="s">
+        <v>23</v>
+      </c>
+      <c r="B142" t="s">
+        <v>57</v>
+      </c>
+      <c r="C142" t="s">
+        <v>54</v>
+      </c>
+      <c r="D142" t="s">
+        <v>61</v>
+      </c>
+      <c r="E142">
+        <v>7.5</v>
+      </c>
+      <c r="F142">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="G142" s="1">
+        <v>0.536</v>
+      </c>
+      <c r="H142" t="s">
+        <v>66</v>
+      </c>
+      <c r="I142" s="2">
+        <v>2.28</v>
+      </c>
+      <c r="J142" s="2">
+        <v>0.0031</v>
+      </c>
+      <c r="K142" t="s">
+        <v>71</v>
+      </c>
+      <c r="L142" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12">
+      <c r="A143" t="s">
+        <v>30</v>
+      </c>
+      <c r="B143" t="s">
+        <v>54</v>
+      </c>
+      <c r="C143" t="s">
+        <v>59</v>
+      </c>
+      <c r="D143" t="s">
+        <v>61</v>
+      </c>
+      <c r="E143">
+        <v>2.5</v>
+      </c>
+      <c r="F143">
+        <v>3.03</v>
+      </c>
+      <c r="G143" s="1">
+        <v>0.536</v>
+      </c>
+      <c r="H143" t="s">
+        <v>67</v>
+      </c>
+      <c r="I143" s="2">
+        <v>2.27</v>
+      </c>
+      <c r="J143" s="2">
+        <v>0.0031</v>
+      </c>
+      <c r="K143" t="s">
+        <v>71</v>
+      </c>
+      <c r="L143" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12">
+      <c r="A144" t="s">
+        <v>42</v>
+      </c>
+      <c r="B144" t="s">
+        <v>57</v>
+      </c>
+      <c r="C144" t="s">
+        <v>54</v>
+      </c>
+      <c r="D144" t="s">
+        <v>62</v>
+      </c>
+      <c r="E144">
+        <v>21.5</v>
+      </c>
+      <c r="F144">
+        <v>20.44</v>
+      </c>
+      <c r="G144" s="1">
+        <v>0.535</v>
+      </c>
+      <c r="H144" t="s">
+        <v>66</v>
+      </c>
+      <c r="I144" s="2">
+        <v>2.09</v>
+      </c>
+      <c r="J144" s="2">
+        <v>0.0029</v>
+      </c>
+      <c r="K144" t="s">
+        <v>71</v>
+      </c>
+      <c r="L144" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12">
+      <c r="A145" t="s">
+        <v>41</v>
+      </c>
+      <c r="B145" t="s">
+        <v>53</v>
+      </c>
+      <c r="C145" t="s">
+        <v>55</v>
+      </c>
+      <c r="D145" t="s">
+        <v>65</v>
+      </c>
+      <c r="E145">
+        <v>23.5</v>
+      </c>
+      <c r="F145">
+        <v>24.43</v>
+      </c>
+      <c r="G145" s="1">
+        <v>0.531</v>
+      </c>
+      <c r="H145" t="s">
+        <v>67</v>
+      </c>
+      <c r="I145" s="2">
+        <v>1.35</v>
+      </c>
+      <c r="J145" s="2">
+        <v>0.0037</v>
+      </c>
+      <c r="K145" t="s">
+        <v>72</v>
+      </c>
+      <c r="L145" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12">
+      <c r="A146" t="s">
+        <v>40</v>
+      </c>
+      <c r="B146" t="s">
+        <v>53</v>
+      </c>
+      <c r="C146" t="s">
+        <v>55</v>
+      </c>
+      <c r="D146" t="s">
+        <v>64</v>
+      </c>
+      <c r="E146">
+        <v>3.5</v>
+      </c>
+      <c r="F146">
+        <v>4.14</v>
+      </c>
+      <c r="G146" s="1">
+        <v>0.53</v>
+      </c>
+      <c r="H146" t="s">
+        <v>67</v>
+      </c>
+      <c r="I146" s="2">
+        <v>1.1</v>
+      </c>
+      <c r="J146" s="2">
+        <v>0.0015</v>
+      </c>
+      <c r="K146" t="s">
+        <v>72</v>
+      </c>
+      <c r="L146" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12">
+      <c r="A147" t="s">
+        <v>52</v>
+      </c>
+      <c r="B147" t="s">
+        <v>56</v>
+      </c>
+      <c r="C147" t="s">
+        <v>58</v>
+      </c>
+      <c r="D147" t="s">
+        <v>61</v>
+      </c>
+      <c r="E147">
+        <v>4.5</v>
+      </c>
+      <c r="F147">
+        <v>4.97</v>
+      </c>
+      <c r="G147" s="1">
+        <v>0.53</v>
+      </c>
+      <c r="H147" t="s">
+        <v>67</v>
+      </c>
+      <c r="I147" s="2">
+        <v>1.1</v>
+      </c>
+      <c r="J147" s="2">
+        <v>0.003</v>
+      </c>
+      <c r="K147" t="s">
+        <v>72</v>
+      </c>
+      <c r="L147" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12">
+      <c r="A148" t="s">
+        <v>40</v>
+      </c>
+      <c r="B148" t="s">
+        <v>53</v>
+      </c>
+      <c r="C148" t="s">
+        <v>55</v>
+      </c>
+      <c r="D148" t="s">
+        <v>62</v>
+      </c>
+      <c r="E148">
+        <v>18.5</v>
+      </c>
+      <c r="F148">
+        <v>19.14</v>
+      </c>
+      <c r="G148" s="1">
+        <v>0.527</v>
+      </c>
+      <c r="H148" t="s">
+        <v>67</v>
+      </c>
+      <c r="I148" s="2">
+        <v>0.63</v>
+      </c>
+      <c r="J148" s="2">
+        <v>0.0017</v>
+      </c>
+      <c r="K148" t="s">
+        <v>72</v>
+      </c>
+      <c r="L148" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12">
+      <c r="A149" t="s">
+        <v>17</v>
+      </c>
+      <c r="B149" t="s">
+        <v>55</v>
+      </c>
+      <c r="C149" t="s">
+        <v>60</v>
+      </c>
+      <c r="D149" t="s">
+        <v>65</v>
+      </c>
+      <c r="E149">
+        <v>16.5</v>
+      </c>
+      <c r="F149">
+        <v>15.73</v>
+      </c>
+      <c r="G149" s="1">
+        <v>0.526</v>
+      </c>
+      <c r="H149" t="s">
+        <v>66</v>
+      </c>
+      <c r="I149" s="2">
+        <v>0.38</v>
+      </c>
+      <c r="J149" s="2">
+        <v>0.0005</v>
+      </c>
+      <c r="K149" t="s">
+        <v>72</v>
+      </c>
+      <c r="L149" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12">
+      <c r="A150" t="s">
+        <v>34</v>
+      </c>
+      <c r="B150" t="s">
+        <v>56</v>
+      </c>
+      <c r="C150" t="s">
+        <v>58</v>
+      </c>
+      <c r="D150" t="s">
+        <v>65</v>
+      </c>
+      <c r="E150">
+        <v>11.5</v>
+      </c>
+      <c r="F150">
+        <v>12.06</v>
+      </c>
+      <c r="G150" s="1">
+        <v>0.523</v>
+      </c>
+      <c r="H150" t="s">
+        <v>67</v>
+      </c>
+      <c r="I150" s="2">
+        <v>-0.1</v>
+      </c>
+      <c r="J150" s="2">
+        <v>0</v>
+      </c>
+      <c r="K150" t="s">
+        <v>72</v>
+      </c>
+      <c r="L150" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12">
+      <c r="A151" t="s">
+        <v>41</v>
+      </c>
+      <c r="B151" t="s">
+        <v>53</v>
+      </c>
+      <c r="C151" t="s">
+        <v>55</v>
+      </c>
+      <c r="D151" t="s">
+        <v>63</v>
+      </c>
+      <c r="E151">
+        <v>13.5</v>
+      </c>
+      <c r="F151">
+        <v>13.85</v>
+      </c>
+      <c r="G151" s="1">
+        <v>0.523</v>
+      </c>
+      <c r="H151" t="s">
+        <v>67</v>
+      </c>
+      <c r="I151" s="2">
+        <v>-0.24</v>
+      </c>
+      <c r="J151" s="2">
+        <v>0</v>
+      </c>
+      <c r="K151" t="s">
+        <v>72</v>
+      </c>
+      <c r="L151" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12">
+      <c r="A152" t="s">
+        <v>37</v>
+      </c>
+      <c r="B152" t="s">
+        <v>56</v>
+      </c>
+      <c r="C152" t="s">
+        <v>58</v>
+      </c>
+      <c r="D152" t="s">
+        <v>65</v>
+      </c>
+      <c r="E152">
+        <v>15.5</v>
+      </c>
+      <c r="F152">
+        <v>15.05</v>
+      </c>
+      <c r="G152" s="1">
+        <v>0.522</v>
+      </c>
+      <c r="H152" t="s">
+        <v>66</v>
+      </c>
+      <c r="I152" s="2">
+        <v>-0.29</v>
+      </c>
+      <c r="J152" s="2">
+        <v>0</v>
+      </c>
+      <c r="K152" t="s">
+        <v>72</v>
+      </c>
+      <c r="L152" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12">
+      <c r="A153" t="s">
+        <v>42</v>
+      </c>
+      <c r="B153" t="s">
+        <v>57</v>
+      </c>
+      <c r="C153" t="s">
+        <v>54</v>
+      </c>
+      <c r="D153" t="s">
+        <v>65</v>
+      </c>
+      <c r="E153">
+        <v>14.5</v>
+      </c>
+      <c r="F153">
+        <v>15.12</v>
+      </c>
+      <c r="G153" s="1">
+        <v>0.521</v>
+      </c>
+      <c r="H153" t="s">
+        <v>67</v>
+      </c>
+      <c r="I153" s="2">
+        <v>-0.53</v>
+      </c>
+      <c r="J153" s="2">
+        <v>0</v>
+      </c>
+      <c r="K153" t="s">
+        <v>72</v>
+      </c>
+      <c r="L153" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12">
+      <c r="A154" t="s">
+        <v>29</v>
+      </c>
+      <c r="B154" t="s">
+        <v>55</v>
+      </c>
+      <c r="C154" t="s">
+        <v>60</v>
+      </c>
+      <c r="D154" t="s">
+        <v>61</v>
+      </c>
+      <c r="E154">
+        <v>1.5</v>
+      </c>
+      <c r="F154">
+        <v>1.74</v>
+      </c>
+      <c r="G154" s="1">
+        <v>0.52</v>
+      </c>
+      <c r="H154" t="s">
+        <v>67</v>
+      </c>
+      <c r="I154" s="2">
+        <v>-0.7</v>
+      </c>
+      <c r="J154" s="2">
+        <v>0</v>
+      </c>
+      <c r="K154" t="s">
+        <v>72</v>
+      </c>
+      <c r="L154" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12">
+      <c r="A155" t="s">
+        <v>32</v>
+      </c>
+      <c r="B155" t="s">
+        <v>55</v>
+      </c>
+      <c r="C155" t="s">
+        <v>60</v>
+      </c>
+      <c r="D155" t="s">
+        <v>61</v>
+      </c>
+      <c r="E155">
+        <v>5.5</v>
+      </c>
+      <c r="F155">
+        <v>5.7</v>
+      </c>
+      <c r="G155" s="1">
+        <v>0.519</v>
+      </c>
+      <c r="H155" t="s">
+        <v>66</v>
+      </c>
+      <c r="I155" s="2">
+        <v>-0.87</v>
+      </c>
+      <c r="J155" s="2">
+        <v>0</v>
+      </c>
+      <c r="K155" t="s">
+        <v>72</v>
+      </c>
+      <c r="L155" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12">
+      <c r="A156" t="s">
+        <v>30</v>
+      </c>
+      <c r="B156" t="s">
+        <v>54</v>
+      </c>
+      <c r="C156" t="s">
+        <v>59</v>
+      </c>
+      <c r="D156" t="s">
+        <v>62</v>
+      </c>
+      <c r="E156">
+        <v>17.5</v>
+      </c>
+      <c r="F156">
+        <v>16.98</v>
+      </c>
+      <c r="G156" s="1">
+        <v>0.519</v>
+      </c>
+      <c r="H156" t="s">
+        <v>66</v>
+      </c>
+      <c r="I156" s="2">
+        <v>-0.92</v>
+      </c>
+      <c r="J156" s="2">
+        <v>0</v>
+      </c>
+      <c r="K156" t="s">
+        <v>72</v>
+      </c>
+      <c r="L156" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12">
+      <c r="A157" t="s">
+        <v>29</v>
+      </c>
+      <c r="B157" t="s">
+        <v>55</v>
+      </c>
+      <c r="C157" t="s">
+        <v>60</v>
+      </c>
+      <c r="D157" t="s">
+        <v>65</v>
+      </c>
+      <c r="E157">
+        <v>7.5</v>
+      </c>
+      <c r="F157">
+        <v>7.69</v>
+      </c>
+      <c r="G157" s="1">
+        <v>0.517</v>
+      </c>
+      <c r="H157" t="s">
+        <v>67</v>
+      </c>
+      <c r="I157" s="2">
+        <v>-1.23</v>
+      </c>
+      <c r="J157" s="2">
+        <v>0</v>
+      </c>
+      <c r="K157" t="s">
+        <v>72</v>
+      </c>
+      <c r="L157" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12">
+      <c r="A158" t="s">
+        <v>36</v>
+      </c>
+      <c r="B158" t="s">
+        <v>53</v>
+      </c>
+      <c r="C158" t="s">
+        <v>55</v>
+      </c>
+      <c r="D158" t="s">
+        <v>65</v>
+      </c>
+      <c r="E158">
+        <v>7.5</v>
+      </c>
+      <c r="F158">
+        <v>7.81</v>
+      </c>
+      <c r="G158" s="1">
+        <v>0.517</v>
+      </c>
+      <c r="H158" t="s">
+        <v>67</v>
+      </c>
+      <c r="I158" s="2">
+        <v>-1.27</v>
+      </c>
+      <c r="J158" s="2">
+        <v>0</v>
+      </c>
+      <c r="K158" t="s">
+        <v>72</v>
+      </c>
+      <c r="L158" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12">
+      <c r="A159" t="s">
+        <v>39</v>
+      </c>
+      <c r="B159" t="s">
+        <v>57</v>
+      </c>
+      <c r="C159" t="s">
+        <v>54</v>
+      </c>
+      <c r="D159" t="s">
+        <v>61</v>
+      </c>
+      <c r="E159">
+        <v>2.5</v>
+      </c>
+      <c r="F159">
+        <v>2.86</v>
+      </c>
+      <c r="G159" s="1">
+        <v>0.516</v>
+      </c>
+      <c r="H159" t="s">
+        <v>66</v>
+      </c>
+      <c r="I159" s="2">
+        <v>-1.44</v>
+      </c>
+      <c r="J159" s="2">
+        <v>0</v>
+      </c>
+      <c r="K159" t="s">
+        <v>72</v>
+      </c>
+      <c r="L159" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12">
+      <c r="A160" t="s">
+        <v>12</v>
+      </c>
+      <c r="B160" t="s">
+        <v>53</v>
+      </c>
+      <c r="C160" t="s">
+        <v>55</v>
+      </c>
+      <c r="D160" t="s">
+        <v>65</v>
+      </c>
+      <c r="E160">
+        <v>16.5</v>
+      </c>
+      <c r="F160">
+        <v>16.99</v>
+      </c>
+      <c r="G160" s="1">
+        <v>0.516</v>
+      </c>
+      <c r="H160" t="s">
+        <v>67</v>
+      </c>
+      <c r="I160" s="2">
+        <v>-1.51</v>
+      </c>
+      <c r="J160" s="2">
+        <v>0</v>
+      </c>
+      <c r="K160" t="s">
+        <v>72</v>
+      </c>
+      <c r="L160" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12">
+      <c r="A161" t="s">
+        <v>52</v>
+      </c>
+      <c r="B161" t="s">
+        <v>56</v>
+      </c>
+      <c r="C161" t="s">
+        <v>58</v>
+      </c>
+      <c r="D161" t="s">
+        <v>65</v>
+      </c>
+      <c r="E161">
+        <v>10.5</v>
+      </c>
+      <c r="F161">
+        <v>10.02</v>
+      </c>
+      <c r="G161" s="1">
+        <v>0.516</v>
+      </c>
+      <c r="H161" t="s">
+        <v>66</v>
+      </c>
+      <c r="I161" s="2">
+        <v>-1.55</v>
+      </c>
+      <c r="J161" s="2">
+        <v>0</v>
+      </c>
+      <c r="K161" t="s">
+        <v>72</v>
+      </c>
+      <c r="L161" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12">
+      <c r="A162" t="s">
+        <v>24</v>
+      </c>
+      <c r="B162" t="s">
+        <v>58</v>
+      </c>
+      <c r="C162" t="s">
+        <v>56</v>
+      </c>
+      <c r="D162" t="s">
+        <v>62</v>
+      </c>
+      <c r="E162">
+        <v>25.5</v>
+      </c>
+      <c r="F162">
+        <v>25.09</v>
+      </c>
+      <c r="G162" s="1">
+        <v>0.516</v>
+      </c>
+      <c r="H162" t="s">
+        <v>66</v>
+      </c>
+      <c r="I162" s="2">
+        <v>-1.56</v>
+      </c>
+      <c r="J162" s="2">
+        <v>0</v>
+      </c>
+      <c r="K162" t="s">
+        <v>72</v>
+      </c>
+      <c r="L162" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12">
+      <c r="A163" t="s">
+        <v>24</v>
+      </c>
+      <c r="B163" t="s">
+        <v>58</v>
+      </c>
+      <c r="C163" t="s">
+        <v>56</v>
+      </c>
+      <c r="D163" t="s">
+        <v>64</v>
+      </c>
+      <c r="E163">
+        <v>4.5</v>
+      </c>
+      <c r="F163">
+        <v>5.03</v>
+      </c>
+      <c r="G163" s="1">
+        <v>0.515</v>
+      </c>
+      <c r="H163" t="s">
+        <v>67</v>
+      </c>
+      <c r="I163" s="2">
+        <v>-1.77</v>
+      </c>
+      <c r="J163" s="2">
+        <v>0</v>
+      </c>
+      <c r="K163" t="s">
+        <v>72</v>
+      </c>
+      <c r="L163" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12">
+      <c r="A164" t="s">
+        <v>39</v>
+      </c>
+      <c r="B164" t="s">
+        <v>57</v>
+      </c>
+      <c r="C164" t="s">
+        <v>54</v>
+      </c>
+      <c r="D164" t="s">
+        <v>62</v>
+      </c>
+      <c r="E164">
+        <v>10.5</v>
+      </c>
+      <c r="F164">
+        <v>10.15</v>
+      </c>
+      <c r="G164" s="1">
+        <v>0.514</v>
+      </c>
+      <c r="H164" t="s">
+        <v>66</v>
+      </c>
+      <c r="I164" s="2">
+        <v>-1.93</v>
+      </c>
+      <c r="J164" s="2">
+        <v>0</v>
+      </c>
+      <c r="K164" t="s">
+        <v>72</v>
+      </c>
+      <c r="L164" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12">
+      <c r="A165" t="s">
+        <v>40</v>
+      </c>
+      <c r="B165" t="s">
+        <v>53</v>
+      </c>
+      <c r="C165" t="s">
+        <v>55</v>
+      </c>
+      <c r="D165" t="s">
+        <v>61</v>
+      </c>
+      <c r="E165">
+        <v>3.5</v>
+      </c>
+      <c r="F165">
+        <v>3.92</v>
+      </c>
+      <c r="G165" s="1">
+        <v>0.512</v>
+      </c>
+      <c r="H165" t="s">
+        <v>67</v>
+      </c>
+      <c r="I165" s="2">
+        <v>-2.2</v>
+      </c>
+      <c r="J165" s="2">
+        <v>0</v>
+      </c>
+      <c r="K165" t="s">
+        <v>72</v>
+      </c>
+      <c r="L165" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12">
+      <c r="A166" t="s">
+        <v>38</v>
+      </c>
+      <c r="B166" t="s">
+        <v>53</v>
+      </c>
+      <c r="C166" t="s">
+        <v>55</v>
+      </c>
+      <c r="D166" t="s">
+        <v>62</v>
+      </c>
+      <c r="E166">
+        <v>24.5</v>
+      </c>
+      <c r="F166">
+        <v>25.21</v>
+      </c>
+      <c r="G166" s="1">
+        <v>0.511</v>
+      </c>
+      <c r="H166" t="s">
+        <v>67</v>
+      </c>
+      <c r="I166" s="2">
+        <v>-2.36</v>
+      </c>
+      <c r="J166" s="2">
+        <v>0</v>
+      </c>
+      <c r="K166" t="s">
+        <v>72</v>
+      </c>
+      <c r="L166" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12">
+      <c r="A167" t="s">
+        <v>47</v>
+      </c>
+      <c r="B167" t="s">
+        <v>58</v>
+      </c>
+      <c r="C167" t="s">
+        <v>56</v>
+      </c>
+      <c r="D167" t="s">
+        <v>63</v>
+      </c>
+      <c r="E167">
+        <v>7.5</v>
+      </c>
+      <c r="F167">
+        <v>7.35</v>
+      </c>
+      <c r="G167" s="1">
+        <v>0.511</v>
+      </c>
+      <c r="H167" t="s">
+        <v>66</v>
+      </c>
+      <c r="I167" s="2">
+        <v>-2.45</v>
+      </c>
+      <c r="J167" s="2">
+        <v>0</v>
+      </c>
+      <c r="K167" t="s">
+        <v>72</v>
+      </c>
+      <c r="L167" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12">
+      <c r="A168" t="s">
+        <v>33</v>
+      </c>
+      <c r="B168" t="s">
+        <v>58</v>
+      </c>
+      <c r="C168" t="s">
+        <v>56</v>
+      </c>
+      <c r="D168" t="s">
+        <v>64</v>
+      </c>
+      <c r="E168">
+        <v>1.5</v>
+      </c>
+      <c r="F168">
+        <v>1.93</v>
+      </c>
+      <c r="G168" s="1">
+        <v>0.51</v>
+      </c>
+      <c r="H168" t="s">
+        <v>67</v>
+      </c>
+      <c r="I168" s="2">
+        <v>-2.65</v>
+      </c>
+      <c r="J168" s="2">
+        <v>0</v>
+      </c>
+      <c r="K168" t="s">
+        <v>72</v>
+      </c>
+      <c r="L168" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12">
+      <c r="A169" t="s">
+        <v>46</v>
+      </c>
+      <c r="B169" t="s">
+        <v>56</v>
+      </c>
+      <c r="C169" t="s">
+        <v>58</v>
+      </c>
+      <c r="D169" t="s">
+        <v>61</v>
+      </c>
+      <c r="E169">
+        <v>6.5</v>
+      </c>
+      <c r="F169">
+        <v>6.92</v>
+      </c>
+      <c r="G169" s="1">
+        <v>0.509</v>
+      </c>
+      <c r="H169" t="s">
+        <v>66</v>
+      </c>
+      <c r="I169" s="2">
+        <v>-2.74</v>
+      </c>
+      <c r="J169" s="2">
+        <v>0</v>
+      </c>
+      <c r="K169" t="s">
+        <v>72</v>
+      </c>
+      <c r="L169" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12">
+      <c r="A170" t="s">
+        <v>46</v>
+      </c>
+      <c r="B170" t="s">
+        <v>56</v>
+      </c>
+      <c r="C170" t="s">
+        <v>58</v>
+      </c>
+      <c r="D170" t="s">
+        <v>65</v>
+      </c>
+      <c r="E170">
+        <v>16.5</v>
+      </c>
+      <c r="F170">
+        <v>16.29</v>
+      </c>
+      <c r="G170" s="1">
+        <v>0.508</v>
+      </c>
+      <c r="H170" t="s">
+        <v>66</v>
+      </c>
+      <c r="I170" s="2">
+        <v>-3.05</v>
+      </c>
+      <c r="J170" s="2">
+        <v>0</v>
+      </c>
+      <c r="K170" t="s">
+        <v>72</v>
+      </c>
+      <c r="L170" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12">
+      <c r="A171" t="s">
+        <v>20</v>
+      </c>
+      <c r="B171" t="s">
+        <v>56</v>
+      </c>
+      <c r="C171" t="s">
+        <v>58</v>
+      </c>
+      <c r="D171" t="s">
+        <v>62</v>
+      </c>
+      <c r="E171">
+        <v>22.5</v>
+      </c>
+      <c r="F171">
+        <v>22.83</v>
+      </c>
+      <c r="G171" s="1">
+        <v>0.507</v>
+      </c>
+      <c r="H171" t="s">
+        <v>67</v>
+      </c>
+      <c r="I171" s="2">
+        <v>-3.25</v>
+      </c>
+      <c r="J171" s="2">
+        <v>0</v>
+      </c>
+      <c r="K171" t="s">
+        <v>72</v>
+      </c>
+      <c r="L171" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12">
+      <c r="A172" t="s">
+        <v>50</v>
+      </c>
+      <c r="B172" t="s">
+        <v>56</v>
+      </c>
+      <c r="C172" t="s">
+        <v>58</v>
+      </c>
+      <c r="D172" t="s">
+        <v>63</v>
+      </c>
+      <c r="E172">
+        <v>7.5</v>
+      </c>
+      <c r="F172">
+        <v>7.41</v>
+      </c>
+      <c r="G172" s="1">
+        <v>0.507</v>
+      </c>
+      <c r="H172" t="s">
+        <v>66</v>
+      </c>
+      <c r="I172" s="2">
+        <v>-3.27</v>
+      </c>
+      <c r="J172" s="2">
+        <v>0</v>
+      </c>
+      <c r="K172" t="s">
+        <v>72</v>
+      </c>
+      <c r="L172" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12">
+      <c r="A173" t="s">
+        <v>30</v>
+      </c>
+      <c r="B173" t="s">
+        <v>54</v>
+      </c>
+      <c r="C173" t="s">
+        <v>59</v>
+      </c>
+      <c r="D173" t="s">
+        <v>64</v>
+      </c>
+      <c r="E173">
+        <v>3.5</v>
+      </c>
+      <c r="F173">
+        <v>3.96</v>
+      </c>
+      <c r="G173" s="1">
+        <v>0.507</v>
+      </c>
+      <c r="H173" t="s">
+        <v>66</v>
+      </c>
+      <c r="I173" s="2">
+        <v>-3.28</v>
+      </c>
+      <c r="J173" s="2">
+        <v>0</v>
+      </c>
+      <c r="K173" t="s">
+        <v>72</v>
+      </c>
+      <c r="L173" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12">
+      <c r="A174" t="s">
+        <v>14</v>
+      </c>
+      <c r="B174" t="s">
+        <v>54</v>
+      </c>
+      <c r="C174" t="s">
+        <v>59</v>
+      </c>
+      <c r="D174" t="s">
+        <v>62</v>
+      </c>
+      <c r="E174">
+        <v>24.5</v>
+      </c>
+      <c r="F174">
+        <v>24.39</v>
+      </c>
+      <c r="G174" s="1">
+        <v>0.506</v>
+      </c>
+      <c r="H174" t="s">
+        <v>66</v>
+      </c>
+      <c r="I174" s="2">
+        <v>-3.42</v>
+      </c>
+      <c r="J174" s="2">
+        <v>0</v>
+      </c>
+      <c r="K174" t="s">
+        <v>72</v>
+      </c>
+      <c r="L174" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12">
+      <c r="A175" t="s">
+        <v>39</v>
+      </c>
+      <c r="B175" t="s">
+        <v>57</v>
+      </c>
+      <c r="C175" t="s">
+        <v>54</v>
+      </c>
+      <c r="D175" t="s">
+        <v>65</v>
+      </c>
+      <c r="E175">
+        <v>6.5</v>
+      </c>
+      <c r="F175">
+        <v>6.41</v>
+      </c>
+      <c r="G175" s="1">
+        <v>0.506</v>
+      </c>
+      <c r="H175" t="s">
+        <v>66</v>
+      </c>
+      <c r="I175" s="2">
+        <v>-3.43</v>
+      </c>
+      <c r="J175" s="2">
+        <v>0</v>
+      </c>
+      <c r="K175" t="s">
+        <v>72</v>
+      </c>
+      <c r="L175" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12">
+      <c r="A176" t="s">
+        <v>23</v>
+      </c>
+      <c r="B176" t="s">
+        <v>57</v>
+      </c>
+      <c r="C176" t="s">
+        <v>54</v>
+      </c>
+      <c r="D176" t="s">
+        <v>62</v>
+      </c>
+      <c r="E176">
+        <v>23.5</v>
+      </c>
+      <c r="F176">
+        <v>23.71</v>
+      </c>
+      <c r="G176" s="1">
+        <v>0.505</v>
+      </c>
+      <c r="H176" t="s">
+        <v>67</v>
+      </c>
+      <c r="I176" s="2">
+        <v>-3.52</v>
+      </c>
+      <c r="J176" s="2">
+        <v>0</v>
+      </c>
+      <c r="K176" t="s">
+        <v>72</v>
+      </c>
+      <c r="L176" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12">
+      <c r="A177" t="s">
+        <v>35</v>
+      </c>
+      <c r="B177" t="s">
+        <v>58</v>
+      </c>
+      <c r="C177" t="s">
+        <v>56</v>
+      </c>
+      <c r="D177" t="s">
+        <v>62</v>
+      </c>
+      <c r="E177">
+        <v>19.5</v>
+      </c>
+      <c r="F177">
+        <v>19.58</v>
+      </c>
+      <c r="G177" s="1">
+        <v>0.504</v>
+      </c>
+      <c r="H177" t="s">
+        <v>67</v>
+      </c>
+      <c r="I177" s="2">
+        <v>-3.71</v>
+      </c>
+      <c r="J177" s="2">
+        <v>0</v>
+      </c>
+      <c r="K177" t="s">
+        <v>72</v>
+      </c>
+      <c r="L177" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12">
+      <c r="A178" t="s">
+        <v>43</v>
+      </c>
+      <c r="B178" t="s">
+        <v>55</v>
+      </c>
+      <c r="C178" t="s">
+        <v>60</v>
+      </c>
+      <c r="D178" t="s">
+        <v>62</v>
+      </c>
+      <c r="E178">
+        <v>21.5</v>
+      </c>
+      <c r="F178">
+        <v>21.42</v>
+      </c>
+      <c r="G178" s="1">
+        <v>0.504</v>
+      </c>
+      <c r="H178" t="s">
+        <v>66</v>
+      </c>
+      <c r="I178" s="2">
+        <v>-3.85</v>
+      </c>
+      <c r="J178" s="2">
+        <v>0</v>
+      </c>
+      <c r="K178" t="s">
+        <v>72</v>
+      </c>
+      <c r="L178" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12">
+      <c r="A179" t="s">
+        <v>31</v>
+      </c>
+      <c r="B179" t="s">
+        <v>57</v>
+      </c>
+      <c r="C179" t="s">
+        <v>54</v>
+      </c>
+      <c r="D179" t="s">
+        <v>62</v>
+      </c>
+      <c r="E179">
+        <v>25.5</v>
+      </c>
+      <c r="F179">
+        <v>25.62</v>
+      </c>
+      <c r="G179" s="1">
+        <v>0.504</v>
+      </c>
+      <c r="H179" t="s">
+        <v>67</v>
+      </c>
+      <c r="I179" s="2">
+        <v>-3.87</v>
+      </c>
+      <c r="J179" s="2">
+        <v>0</v>
+      </c>
+      <c r="K179" t="s">
+        <v>72</v>
+      </c>
+      <c r="L179" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12">
+      <c r="A180" t="s">
+        <v>49</v>
+      </c>
+      <c r="B180" t="s">
+        <v>57</v>
+      </c>
+      <c r="C180" t="s">
+        <v>54</v>
+      </c>
+      <c r="D180" t="s">
+        <v>65</v>
+      </c>
+      <c r="E180">
+        <v>13.5</v>
+      </c>
+      <c r="F180">
+        <v>13.41</v>
+      </c>
+      <c r="G180" s="1">
+        <v>0.503</v>
+      </c>
+      <c r="H180" t="s">
+        <v>66</v>
+      </c>
+      <c r="I180" s="2">
+        <v>-3.95</v>
+      </c>
+      <c r="J180" s="2">
+        <v>0</v>
+      </c>
+      <c r="K180" t="s">
+        <v>72</v>
+      </c>
+      <c r="L180" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12">
+      <c r="A181" t="s">
+        <v>27</v>
+      </c>
+      <c r="B181" t="s">
+        <v>54</v>
+      </c>
+      <c r="C181" t="s">
+        <v>59</v>
+      </c>
+      <c r="D181" t="s">
+        <v>65</v>
+      </c>
+      <c r="E181">
+        <v>18.5</v>
+      </c>
+      <c r="F181">
+        <v>18.42</v>
+      </c>
+      <c r="G181" s="1">
+        <v>0.502</v>
+      </c>
+      <c r="H181" t="s">
+        <v>66</v>
+      </c>
+      <c r="I181" s="2">
+        <v>-4.16</v>
+      </c>
+      <c r="J181" s="2">
+        <v>0</v>
+      </c>
+      <c r="K181" t="s">
+        <v>72</v>
+      </c>
+      <c r="L181" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12">
+      <c r="A182" t="s">
+        <v>41</v>
+      </c>
+      <c r="B182" t="s">
+        <v>53</v>
+      </c>
+      <c r="C182" t="s">
+        <v>55</v>
+      </c>
+      <c r="D182" t="s">
+        <v>62</v>
+      </c>
+      <c r="E182">
+        <v>36.5</v>
+      </c>
+      <c r="F182">
+        <v>36.42</v>
+      </c>
+      <c r="G182" s="1">
+        <v>0.502</v>
+      </c>
+      <c r="H182" t="s">
+        <v>66</v>
+      </c>
+      <c r="I182" s="2">
+        <v>-4.19</v>
+      </c>
+      <c r="J182" s="2">
+        <v>0</v>
+      </c>
+      <c r="K182" t="s">
+        <v>72</v>
+      </c>
+      <c r="L182" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12">
+      <c r="A183" t="s">
+        <v>51</v>
+      </c>
+      <c r="B183" t="s">
+        <v>53</v>
+      </c>
+      <c r="C183" t="s">
+        <v>55</v>
+      </c>
+      <c r="D183" t="s">
+        <v>62</v>
+      </c>
+      <c r="E183">
+        <v>16.5</v>
+      </c>
+      <c r="F183">
+        <v>16.51</v>
+      </c>
+      <c r="G183" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="H183" t="s">
+        <v>67</v>
+      </c>
+      <c r="I183" s="2">
+        <v>-4.51</v>
+      </c>
+      <c r="J183" s="2">
+        <v>0</v>
+      </c>
+      <c r="K183" t="s">
+        <v>72</v>
+      </c>
+      <c r="L183" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12">
+      <c r="A184" t="s">
+        <v>46</v>
+      </c>
+      <c r="B184" t="s">
+        <v>56</v>
+      </c>
+      <c r="C184" t="s">
+        <v>58</v>
+      </c>
+      <c r="D184" t="s">
+        <v>63</v>
+      </c>
+      <c r="E184">
+        <v>7.5</v>
+      </c>
+      <c r="F184">
         <v>9.6</v>
       </c>
-      <c r="G69" s="1">
+      <c r="G184" s="1">
         <v>0.677</v>
       </c>
-      <c r="H69" t="s">
+      <c r="H184" t="s">
         <v>67</v>
       </c>
-      <c r="I69" s="2">
+      <c r="I184" s="2">
         <v>29.3</v>
       </c>
-      <c r="J69" s="2">
+      <c r="J184" s="2">
         <v>0.0403</v>
       </c>
-      <c r="K69" t="s">
+      <c r="K184" t="s">
         <v>73</v>
       </c>
-      <c r="L69" t="s">
+      <c r="L184" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12">
+      <c r="A185" t="s">
+        <v>25</v>
+      </c>
+      <c r="B185" t="s">
+        <v>54</v>
+      </c>
+      <c r="C185" t="s">
+        <v>59</v>
+      </c>
+      <c r="D185" t="s">
+        <v>62</v>
+      </c>
+      <c r="E185">
+        <v>10.5</v>
+      </c>
+      <c r="F185">
+        <v>7.19</v>
+      </c>
+      <c r="G185" s="1">
+        <v>0.651</v>
+      </c>
+      <c r="H185" t="s">
+        <v>66</v>
+      </c>
+      <c r="I185" s="2">
+        <v>24.25</v>
+      </c>
+      <c r="J185" s="2">
+        <v>0.0333</v>
+      </c>
+      <c r="K185" t="s">
+        <v>73</v>
+      </c>
+      <c r="L185" t="s">
         <v>74</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="K2:K69">
+  <conditionalFormatting sqref="K2:K185">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="S Tier">
       <formula>NOT(ISERROR(SEARCH("S Tier",K2)))</formula>
     </cfRule>

--- a/output/processed_props.xlsx
+++ b/output/processed_props.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="48">
   <si>
     <t>Player</t>
   </si>
@@ -52,54 +52,51 @@
     <t>Date</t>
   </si>
   <si>
+    <t>De'Aaron Fox</t>
+  </si>
+  <si>
+    <t>Mikal Bridges</t>
+  </si>
+  <si>
+    <t>Julian Champagnie</t>
+  </si>
+  <si>
+    <t>Devin Vassell</t>
+  </si>
+  <si>
+    <t>Josh Hart</t>
+  </si>
+  <si>
+    <t>Jalen Brunson</t>
+  </si>
+  <si>
+    <t>Karl-Anthony Towns</t>
+  </si>
+  <si>
+    <t>Victor Wembanyama</t>
+  </si>
+  <si>
+    <t>Stephon Castle</t>
+  </si>
+  <si>
+    <t>OG Anunoby</t>
+  </si>
+  <si>
     <t>Dylan Harper</t>
   </si>
   <si>
-    <t>De'Aaron Fox</t>
-  </si>
-  <si>
-    <t>Victor Wembanyama</t>
-  </si>
-  <si>
-    <t>Karl-Anthony Towns</t>
-  </si>
-  <si>
-    <t>Julian Champagnie</t>
-  </si>
-  <si>
-    <t>Jalen Brunson</t>
-  </si>
-  <si>
-    <t>Stephon Castle</t>
-  </si>
-  <si>
     <t>Keldon Johnson</t>
   </si>
   <si>
-    <t>Mikal Bridges</t>
-  </si>
-  <si>
-    <t>Josh Hart</t>
-  </si>
-  <si>
-    <t>Devin Vassell</t>
-  </si>
-  <si>
-    <t>OG Anunoby</t>
+    <t>Mitchell Robinson</t>
+  </si>
+  <si>
+    <t>Luke Kornet</t>
   </si>
   <si>
     <t>Miles McBride</t>
   </si>
   <si>
-    <t>Luke Kornet</t>
-  </si>
-  <si>
-    <t>Mitchell Robinson</t>
-  </si>
-  <si>
-    <t>Jose Alvarado</t>
-  </si>
-  <si>
     <t>Landry Shamet</t>
   </si>
   <si>
@@ -115,24 +112,24 @@
     <t>SAS</t>
   </si>
   <si>
+    <t>PRA</t>
+  </si>
+  <si>
+    <t>RA</t>
+  </si>
+  <si>
+    <t>PA</t>
+  </si>
+  <si>
     <t>PR</t>
   </si>
   <si>
-    <t>PRA</t>
-  </si>
-  <si>
-    <t>PA</t>
+    <t>REB</t>
   </si>
   <si>
     <t>PTS</t>
   </si>
   <si>
-    <t>RA</t>
-  </si>
-  <si>
-    <t>REB</t>
-  </si>
-  <si>
     <t>AST</t>
   </si>
   <si>
@@ -160,7 +157,7 @@
     <t>Pass / Too Volatile</t>
   </si>
   <si>
-    <t>2026-06-03</t>
+    <t>2026-06-05</t>
   </si>
 </sst>
 </file>
@@ -563,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L111"/>
+  <dimension ref="A1:L105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
@@ -622,42 +619,42 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E2">
-        <v>14.5</v>
+        <v>23.5</v>
       </c>
       <c r="F2">
-        <v>10.49</v>
+        <v>17.16</v>
       </c>
       <c r="G2" s="1">
-        <v>0.804</v>
+        <v>0.801</v>
       </c>
       <c r="H2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I2" s="2">
-        <v>0.217</v>
+        <v>0.242</v>
       </c>
       <c r="J2">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
         <v>29</v>
@@ -666,22 +663,22 @@
         <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E3">
-        <v>17.5</v>
+        <v>4.5</v>
       </c>
       <c r="F3">
-        <v>12.63</v>
+        <v>5.99</v>
       </c>
       <c r="G3" s="1">
-        <v>0.806</v>
+        <v>0.707</v>
       </c>
       <c r="H3" t="s">
         <v>40</v>
       </c>
       <c r="I3" s="2">
-        <v>0.237</v>
+        <v>0.233</v>
       </c>
       <c r="J3">
         <v>40</v>
@@ -690,83 +687,83 @@
         <v>42</v>
       </c>
       <c r="L3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>21.5</v>
+        <v>6.5</v>
       </c>
       <c r="F4">
-        <v>25.65</v>
+        <v>10.79</v>
       </c>
       <c r="G4" s="1">
-        <v>0.6820000000000001</v>
+        <v>0.907</v>
       </c>
       <c r="H4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I4" s="2">
-        <v>0.261</v>
+        <v>0.265</v>
       </c>
       <c r="J4">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>30.5</v>
+        <v>20.5</v>
       </c>
       <c r="F5">
-        <v>35.61</v>
+        <v>13.07</v>
       </c>
       <c r="G5" s="1">
-        <v>0.652</v>
+        <v>0.859</v>
       </c>
       <c r="H5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I5" s="2">
-        <v>0.282</v>
+        <v>0.291</v>
       </c>
       <c r="J5">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="K5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -774,42 +771,42 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
         <v>34</v>
       </c>
       <c r="E6">
-        <v>33</v>
+        <v>15.5</v>
       </c>
       <c r="F6">
-        <v>29.08</v>
+        <v>12.36</v>
       </c>
       <c r="G6" s="1">
-        <v>0.657</v>
+        <v>0.746</v>
       </c>
       <c r="H6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I6" s="2">
-        <v>0.2</v>
+        <v>0.262</v>
       </c>
       <c r="J6">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
         <v>29</v>
@@ -818,74 +815,74 @@
         <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="F7">
-        <v>13.35</v>
+        <v>12.46</v>
       </c>
       <c r="G7" s="1">
-        <v>0.775</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="H7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I7" s="2">
-        <v>0.314</v>
+        <v>0.25</v>
       </c>
       <c r="J7">
         <v>40</v>
       </c>
       <c r="K7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E8">
-        <v>25.5</v>
+        <v>20.5</v>
       </c>
       <c r="F8">
-        <v>28.67</v>
+        <v>18.25</v>
       </c>
       <c r="G8" s="1">
-        <v>0.601</v>
+        <v>0.659</v>
       </c>
       <c r="H8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I8" s="2">
-        <v>0.253</v>
+        <v>0.255</v>
       </c>
       <c r="J8">
         <v>70</v>
       </c>
       <c r="K8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
@@ -894,36 +891,36 @@
         <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="F9">
-        <v>14.35</v>
+        <v>19.28</v>
       </c>
       <c r="G9" s="1">
-        <v>0.64</v>
+        <v>0.895</v>
       </c>
       <c r="H9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I9" s="2">
-        <v>0.283</v>
+        <v>0.294</v>
       </c>
       <c r="J9">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="K9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
@@ -932,74 +929,74 @@
         <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E10">
-        <v>15.5</v>
+        <v>28.5</v>
       </c>
       <c r="F10">
-        <v>11.34</v>
+        <v>32.23</v>
       </c>
       <c r="G10" s="1">
-        <v>0.798</v>
+        <v>0.611</v>
       </c>
       <c r="H10" t="s">
         <v>40</v>
       </c>
       <c r="I10" s="2">
-        <v>0.341</v>
+        <v>0.292</v>
       </c>
       <c r="J10">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="K10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E11">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="F11">
-        <v>12.74</v>
+        <v>9.5</v>
       </c>
       <c r="G11" s="1">
-        <v>0.59</v>
+        <v>0.906</v>
       </c>
       <c r="H11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I11" s="2">
-        <v>0.292</v>
+        <v>0.338</v>
       </c>
       <c r="J11">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="K11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
         <v>29</v>
@@ -1008,74 +1005,74 @@
         <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E12">
-        <v>27.5</v>
+        <v>25.5</v>
       </c>
       <c r="F12">
-        <v>34.52</v>
+        <v>29.6</v>
       </c>
       <c r="G12" s="1">
-        <v>0.737</v>
+        <v>0.641</v>
       </c>
       <c r="H12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I12" s="2">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="J12">
         <v>60</v>
       </c>
       <c r="K12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
         <v>35</v>
       </c>
       <c r="E13">
-        <v>21.5</v>
+        <v>17.5</v>
       </c>
       <c r="F13">
-        <v>20.66</v>
+        <v>11.93</v>
       </c>
       <c r="G13" s="1">
-        <v>0.583</v>
+        <v>0.833</v>
       </c>
       <c r="H13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I13" s="2">
-        <v>0.228</v>
+        <v>0.328</v>
       </c>
       <c r="J13">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="K13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
         <v>29</v>
@@ -1084,31 +1081,31 @@
         <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E14">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="F14">
-        <v>10.81</v>
+        <v>12.03</v>
       </c>
       <c r="G14" s="1">
-        <v>0.599</v>
+        <v>0.632</v>
       </c>
       <c r="H14" t="s">
         <v>40</v>
       </c>
       <c r="I14" s="2">
-        <v>0.306</v>
+        <v>0.321</v>
       </c>
       <c r="J14">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="K14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1116,37 +1113,37 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
         <v>33</v>
       </c>
       <c r="E15">
-        <v>29</v>
+        <v>7.5</v>
       </c>
       <c r="F15">
-        <v>26.51</v>
+        <v>11.51</v>
       </c>
       <c r="G15" s="1">
-        <v>0.619</v>
+        <v>0.881</v>
       </c>
       <c r="H15" t="s">
         <v>40</v>
       </c>
       <c r="I15" s="2">
-        <v>0.185</v>
+        <v>0.341</v>
       </c>
       <c r="J15">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="K15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1154,384 +1151,384 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E16">
-        <v>2.5</v>
+        <v>41.5</v>
       </c>
       <c r="F16">
-        <v>7.98</v>
+        <v>39.77</v>
       </c>
       <c r="G16" s="1">
-        <v>0.984</v>
+        <v>0.59</v>
       </c>
       <c r="H16" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I16" s="2">
-        <v>0.375</v>
+        <v>0.306</v>
       </c>
       <c r="J16">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="K16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="s">
         <v>35</v>
       </c>
       <c r="E17">
-        <v>11.5</v>
+        <v>21.5</v>
       </c>
       <c r="F17">
-        <v>8.279999999999999</v>
+        <v>24.37</v>
       </c>
       <c r="G17" s="1">
-        <v>0.805</v>
+        <v>0.616</v>
       </c>
       <c r="H17" t="s">
         <v>40</v>
       </c>
       <c r="I17" s="2">
-        <v>0.396</v>
+        <v>0.306</v>
       </c>
       <c r="J17">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="K17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" t="s">
         <v>32</v>
       </c>
-      <c r="D18" t="s">
-        <v>34</v>
-      </c>
       <c r="E18">
-        <v>21.5</v>
+        <v>25.5</v>
       </c>
       <c r="F18">
-        <v>13.73</v>
+        <v>24.2</v>
       </c>
       <c r="G18" s="1">
-        <v>0.858</v>
+        <v>0.598</v>
       </c>
       <c r="H18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I18" s="2">
-        <v>0.447</v>
+        <v>0.204</v>
       </c>
       <c r="J18">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K18" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D19" t="s">
         <v>38</v>
       </c>
       <c r="E19">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="F19">
-        <v>8.300000000000001</v>
+        <v>5.17</v>
       </c>
       <c r="G19" s="1">
-        <v>0.803</v>
+        <v>0.587</v>
       </c>
       <c r="H19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I19" s="2">
-        <v>0.39</v>
+        <v>0.302</v>
       </c>
       <c r="J19">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K19" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20">
+        <v>11.5</v>
+      </c>
+      <c r="F20">
         <v>17</v>
       </c>
-      <c r="B20" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20" t="s">
-        <v>35</v>
-      </c>
-      <c r="E20">
-        <v>32.5</v>
-      </c>
-      <c r="F20">
-        <v>35.75</v>
-      </c>
       <c r="G20" s="1">
-        <v>0.575</v>
+        <v>0.895</v>
       </c>
       <c r="H20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I20" s="2">
-        <v>0.195</v>
+        <v>0.308</v>
       </c>
       <c r="J20">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="K20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E21">
-        <v>28.5</v>
+        <v>29.5</v>
       </c>
       <c r="F21">
-        <v>31.26</v>
+        <v>28.25</v>
       </c>
       <c r="G21" s="1">
-        <v>0.572</v>
+        <v>0.589</v>
       </c>
       <c r="H21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I21" s="2">
-        <v>0.224</v>
+        <v>0.246</v>
       </c>
       <c r="J21">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="K21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" t="s">
         <v>32</v>
       </c>
-      <c r="D22" t="s">
-        <v>37</v>
-      </c>
       <c r="E22">
-        <v>15.5</v>
+        <v>22.5</v>
       </c>
       <c r="F22">
-        <v>10.61</v>
+        <v>20.55</v>
       </c>
       <c r="G22" s="1">
-        <v>0.829</v>
+        <v>0.636</v>
       </c>
       <c r="H22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I22" s="2">
-        <v>0.351</v>
+        <v>0.231</v>
       </c>
       <c r="J22">
         <v>40</v>
       </c>
       <c r="K22" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E23">
-        <v>24.5</v>
+        <v>5.5</v>
       </c>
       <c r="F23">
-        <v>32.93</v>
+        <v>7.57</v>
       </c>
       <c r="G23" s="1">
-        <v>0.821</v>
+        <v>0.76</v>
       </c>
       <c r="H23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I23" s="2">
-        <v>0.379</v>
+        <v>0.388</v>
       </c>
       <c r="J23">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E24">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="F24">
-        <v>14.93</v>
+        <v>9.33</v>
       </c>
       <c r="G24" s="1">
-        <v>0.586</v>
+        <v>0.785</v>
       </c>
       <c r="H24" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I24" s="2">
-        <v>0.354</v>
+        <v>0.37</v>
       </c>
       <c r="J24">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25">
+        <v>15.5</v>
+      </c>
+      <c r="F25">
         <v>17</v>
       </c>
-      <c r="B25" t="s">
-        <v>30</v>
-      </c>
-      <c r="C25" t="s">
-        <v>32</v>
-      </c>
-      <c r="D25" t="s">
-        <v>34</v>
-      </c>
-      <c r="E25">
-        <v>35.5</v>
-      </c>
-      <c r="F25">
-        <v>38.02</v>
-      </c>
       <c r="G25" s="1">
-        <v>0.541</v>
+        <v>0.574</v>
       </c>
       <c r="H25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I25" s="2">
-        <v>0.169</v>
+        <v>0.253</v>
       </c>
       <c r="J25">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="K25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B26" t="s">
         <v>29</v>
@@ -1540,150 +1537,150 @@
         <v>31</v>
       </c>
       <c r="D26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E26">
-        <v>15</v>
+        <v>2.5</v>
       </c>
       <c r="F26">
-        <v>6.8</v>
+        <v>3.02</v>
       </c>
       <c r="G26" s="1">
-        <v>0.919</v>
+        <v>0.576</v>
       </c>
       <c r="H26" t="s">
         <v>40</v>
       </c>
       <c r="I26" s="2">
-        <v>0.393</v>
+        <v>0.33</v>
       </c>
       <c r="J26">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="K26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D27" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E27">
-        <v>17.5</v>
+        <v>1.5</v>
       </c>
       <c r="F27">
-        <v>18.02</v>
+        <v>3.02</v>
       </c>
       <c r="G27" s="1">
-        <v>0.502</v>
+        <v>0.797</v>
       </c>
       <c r="H27" t="s">
         <v>40</v>
       </c>
       <c r="I27" s="2">
-        <v>0.348</v>
+        <v>0.372</v>
       </c>
       <c r="J27">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="K27" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D28" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E28">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="F28">
-        <v>23.72</v>
+        <v>7.86</v>
       </c>
       <c r="G28" s="1">
-        <v>0.526</v>
+        <v>0.9</v>
       </c>
       <c r="H28" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I28" s="2">
-        <v>0.338</v>
+        <v>0.426</v>
       </c>
       <c r="J28">
         <v>80</v>
       </c>
       <c r="K28" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E29">
-        <v>20</v>
+        <v>38.5</v>
       </c>
       <c r="F29">
-        <v>20.16</v>
+        <v>37.6</v>
       </c>
       <c r="G29" s="1">
-        <v>0.501</v>
+        <v>0.569</v>
       </c>
       <c r="H29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I29" s="2">
-        <v>0.298</v>
+        <v>0.314</v>
       </c>
       <c r="J29">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B30" t="s">
         <v>29</v>
@@ -1692,36 +1689,36 @@
         <v>31</v>
       </c>
       <c r="D30" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E30">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="F30">
-        <v>16.86</v>
+        <v>17.06</v>
       </c>
       <c r="G30" s="1">
-        <v>0.512</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I30" s="2">
-        <v>0.357</v>
+        <v>0.236</v>
       </c>
       <c r="J30">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="K30" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B31" t="s">
         <v>29</v>
@@ -1730,36 +1727,36 @@
         <v>31</v>
       </c>
       <c r="D31" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E31">
-        <v>7</v>
+        <v>20.5</v>
       </c>
       <c r="F31">
-        <v>7.34</v>
+        <v>19.81</v>
       </c>
       <c r="G31" s="1">
-        <v>0.451</v>
+        <v>0.577</v>
       </c>
       <c r="H31" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I31" s="2">
-        <v>0.281</v>
+        <v>0.242</v>
       </c>
       <c r="J31">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="K31" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B32" t="s">
         <v>29</v>
@@ -1771,180 +1768,180 @@
         <v>34</v>
       </c>
       <c r="E32">
-        <v>29.5</v>
+        <v>16.5</v>
       </c>
       <c r="F32">
-        <v>30.68</v>
+        <v>9.74</v>
       </c>
       <c r="G32" s="1">
-        <v>0.506</v>
+        <v>0.882</v>
       </c>
       <c r="H32" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I32" s="2">
-        <v>0.235</v>
+        <v>0.406</v>
       </c>
       <c r="J32">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K32" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E33">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="F33">
-        <v>3.18</v>
+        <v>13.3</v>
       </c>
       <c r="G33" s="1">
-        <v>0.9</v>
+        <v>0.921</v>
       </c>
       <c r="H33" t="s">
         <v>40</v>
       </c>
       <c r="I33" s="2">
-        <v>0.667</v>
+        <v>0.373</v>
       </c>
       <c r="J33">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="K33" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="L33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C34" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D34" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E34">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="F34">
-        <v>1.11</v>
+        <v>9.25</v>
       </c>
       <c r="G34" s="1">
-        <v>0.908</v>
+        <v>0.573</v>
       </c>
       <c r="H34" t="s">
         <v>40</v>
       </c>
       <c r="I34" s="2">
-        <v>0.721</v>
+        <v>0.307</v>
       </c>
       <c r="J34">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="K34" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="L34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B35" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C35" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D35" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E35">
-        <v>17.5</v>
+        <v>7.5</v>
       </c>
       <c r="F35">
-        <v>12.56</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="G35" s="1">
-        <v>0.8090000000000001</v>
+        <v>0.676</v>
       </c>
       <c r="H35" t="s">
         <v>40</v>
       </c>
       <c r="I35" s="2">
-        <v>0.46</v>
+        <v>0.396</v>
       </c>
       <c r="J35">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="K35" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="L35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B36" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C36" t="s">
+        <v>30</v>
+      </c>
+      <c r="D36" t="s">
         <v>32</v>
       </c>
-      <c r="D36" t="s">
-        <v>36</v>
-      </c>
       <c r="E36">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="F36">
-        <v>10.43</v>
+        <v>25.77</v>
       </c>
       <c r="G36" s="1">
-        <v>0.806</v>
+        <v>0.856</v>
       </c>
       <c r="H36" t="s">
         <v>40</v>
       </c>
       <c r="I36" s="2">
-        <v>0.525</v>
+        <v>0.367</v>
       </c>
       <c r="J36">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="K36" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="L36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -1952,42 +1949,42 @@
         <v>19</v>
       </c>
       <c r="B37" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E37">
-        <v>3</v>
+        <v>26.5</v>
       </c>
       <c r="F37">
-        <v>6.88</v>
+        <v>25.87</v>
       </c>
       <c r="G37" s="1">
-        <v>0.906</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="H37" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I37" s="2">
-        <v>0.525</v>
+        <v>0.255</v>
       </c>
       <c r="J37">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="K37" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="L37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B38" t="s">
         <v>29</v>
@@ -1996,188 +1993,188 @@
         <v>31</v>
       </c>
       <c r="D38" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E38">
-        <v>0.5</v>
+        <v>15.5</v>
       </c>
       <c r="F38">
-        <v>1.98</v>
+        <v>15.96</v>
       </c>
       <c r="G38" s="1">
-        <v>0.855</v>
+        <v>0.503</v>
       </c>
       <c r="H38" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I38" s="2">
-        <v>0.579</v>
+        <v>0.164</v>
       </c>
       <c r="J38">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="K38" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B39" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C39" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D39" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E39">
-        <v>5.5</v>
+        <v>17.5</v>
       </c>
       <c r="F39">
-        <v>7.83</v>
+        <v>18.11</v>
       </c>
       <c r="G39" s="1">
-        <v>0.786</v>
+        <v>0.504</v>
       </c>
       <c r="H39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I39" s="2">
-        <v>0.602</v>
+        <v>0.293</v>
       </c>
       <c r="J39">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K39" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D40" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E40">
-        <v>4</v>
+        <v>31.5</v>
       </c>
       <c r="F40">
-        <v>2.43</v>
+        <v>32.09</v>
       </c>
       <c r="G40" s="1">
-        <v>0.752</v>
+        <v>0.52</v>
       </c>
       <c r="H40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I40" s="2">
-        <v>0.786</v>
+        <v>0.225</v>
       </c>
       <c r="J40">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="K40" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C41" t="s">
+        <v>31</v>
+      </c>
+      <c r="D41" t="s">
         <v>32</v>
       </c>
-      <c r="D41" t="s">
-        <v>33</v>
-      </c>
       <c r="E41">
-        <v>6.5</v>
+        <v>34.5</v>
       </c>
       <c r="F41">
-        <v>1.82</v>
+        <v>35.27</v>
       </c>
       <c r="G41" s="1">
-        <v>0.914</v>
+        <v>0.516</v>
       </c>
       <c r="H41" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I41" s="2">
-        <v>0.848</v>
+        <v>0.229</v>
       </c>
       <c r="J41">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="K41" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L41" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B42" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C42" t="s">
+        <v>30</v>
+      </c>
+      <c r="D42" t="s">
         <v>32</v>
       </c>
-      <c r="D42" t="s">
-        <v>34</v>
-      </c>
       <c r="E42">
-        <v>8</v>
+        <v>20.5</v>
       </c>
       <c r="F42">
-        <v>1.92</v>
+        <v>21.01</v>
       </c>
       <c r="G42" s="1">
-        <v>0.944</v>
+        <v>0.509</v>
       </c>
       <c r="H42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I42" s="2">
-        <v>0.725</v>
+        <v>0.23</v>
       </c>
       <c r="J42">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="K42" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L42" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B43" t="s">
         <v>29</v>
@@ -2186,221 +2183,221 @@
         <v>31</v>
       </c>
       <c r="D43" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E43">
-        <v>2.5</v>
+        <v>21.5</v>
       </c>
       <c r="F43">
-        <v>9.539999999999999</v>
+        <v>22.04</v>
       </c>
       <c r="G43" s="1">
-        <v>0.995</v>
+        <v>0.509</v>
       </c>
       <c r="H43" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I43" s="2">
-        <v>0.726</v>
+        <v>0.174</v>
       </c>
       <c r="J43">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="K43" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D44" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E44">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>3.42</v>
       </c>
       <c r="G44" s="1">
-        <v>0.87</v>
+        <v>0.887</v>
       </c>
       <c r="H44" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I44" s="2">
-        <v>0.897</v>
+        <v>0.663</v>
       </c>
       <c r="J44">
         <v>70</v>
       </c>
       <c r="K44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B45" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D45" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E45">
         <v>3.5</v>
       </c>
       <c r="F45">
-        <v>12.41</v>
+        <v>2.24</v>
       </c>
       <c r="G45" s="1">
-        <v>0.998</v>
+        <v>0.772</v>
       </c>
       <c r="H45" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I45" s="2">
-        <v>0.582</v>
+        <v>0.471</v>
       </c>
       <c r="J45">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L45" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B46" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C46" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D46" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E46">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="F46">
-        <v>2.92</v>
+        <v>7.77</v>
       </c>
       <c r="G46" s="1">
-        <v>0.9419999999999999</v>
+        <v>0.881</v>
       </c>
       <c r="H46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I46" s="2">
-        <v>0.716</v>
+        <v>0.475</v>
       </c>
       <c r="J46">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="K46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L46" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B47" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D47" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E47">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="F47">
-        <v>0.99</v>
+        <v>3.2</v>
       </c>
       <c r="G47" s="1">
-        <v>0.973</v>
+        <v>0.761</v>
       </c>
       <c r="H47" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I47" s="2">
-        <v>0.777</v>
+        <v>0.419</v>
       </c>
       <c r="J47">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="K47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L47" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B48" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C48" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D48" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E48">
-        <v>18.5</v>
+        <v>9.5</v>
       </c>
       <c r="F48">
-        <v>11.55</v>
+        <v>1.71</v>
       </c>
       <c r="G48" s="1">
-        <v>0.865</v>
+        <v>0.965</v>
       </c>
       <c r="H48" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I48" s="2">
-        <v>0.495</v>
+        <v>0.804</v>
       </c>
       <c r="J48">
         <v>80</v>
       </c>
       <c r="K48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L48" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2408,42 +2405,42 @@
         <v>17</v>
       </c>
       <c r="B49" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D49" t="s">
         <v>38</v>
       </c>
       <c r="E49">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="F49">
-        <v>2.12</v>
+        <v>2.43</v>
       </c>
       <c r="G49" s="1">
-        <v>0.65</v>
+        <v>0.901</v>
       </c>
       <c r="H49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I49" s="2">
-        <v>0.639</v>
+        <v>0.514</v>
       </c>
       <c r="J49">
         <v>70</v>
       </c>
       <c r="K49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L49" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B50" t="s">
         <v>29</v>
@@ -2452,112 +2449,112 @@
         <v>31</v>
       </c>
       <c r="D50" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E50">
-        <v>42.5</v>
+        <v>14.5</v>
       </c>
       <c r="F50">
-        <v>41.2</v>
+        <v>11.19</v>
       </c>
       <c r="G50" s="1">
-        <v>0.578</v>
+        <v>0.767</v>
       </c>
       <c r="H50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I50" s="2">
-        <v>0.272</v>
+        <v>0.776</v>
       </c>
       <c r="J50">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="K50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L50" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B51" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C51" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D51" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E51">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="F51">
-        <v>2.14</v>
+        <v>0.31</v>
       </c>
       <c r="G51" s="1">
-        <v>0.646</v>
+        <v>0.98</v>
       </c>
       <c r="H51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I51" s="2">
-        <v>0.9429999999999999</v>
+        <v>0.749</v>
       </c>
       <c r="J51">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L51" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B52" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C52" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D52" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E52">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F52">
-        <v>1.09</v>
+        <v>0.21</v>
       </c>
       <c r="G52" s="1">
-        <v>0.711</v>
+        <v>0.977</v>
       </c>
       <c r="H52" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I52" s="2">
-        <v>1.125</v>
+        <v>0.796</v>
       </c>
       <c r="J52">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="K52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L52" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B53" t="s">
         <v>29</v>
@@ -2566,36 +2563,36 @@
         <v>31</v>
       </c>
       <c r="D53" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E53">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="F53">
-        <v>7.05</v>
+        <v>1.12</v>
       </c>
       <c r="G53" s="1">
-        <v>0.699</v>
+        <v>0.665</v>
       </c>
       <c r="H53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I53" s="2">
-        <v>0.504</v>
+        <v>1.006</v>
       </c>
       <c r="J53">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="K53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L53" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B54" t="s">
         <v>29</v>
@@ -2604,74 +2601,74 @@
         <v>31</v>
       </c>
       <c r="D54" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E54">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="F54">
-        <v>6.92</v>
+        <v>7.48</v>
       </c>
       <c r="G54" s="1">
-        <v>0.966</v>
+        <v>0.751</v>
       </c>
       <c r="H54" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I54" s="2">
-        <v>0.492</v>
+        <v>0.928</v>
       </c>
       <c r="J54">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="K54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L54" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B55" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D55" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E55">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F55">
-        <v>0.67</v>
+        <v>1.23</v>
       </c>
       <c r="G55" s="1">
-        <v>0.965</v>
+        <v>0.929</v>
       </c>
       <c r="H55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I55" s="2">
-        <v>0.9409999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="J55">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="K55" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L55" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B56" t="s">
         <v>29</v>
@@ -2680,80 +2677,80 @@
         <v>31</v>
       </c>
       <c r="D56" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E56">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="F56">
-        <v>5.1</v>
+        <v>1.08</v>
       </c>
       <c r="G56" s="1">
-        <v>0.822</v>
+        <v>0.714</v>
       </c>
       <c r="H56" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I56" s="2">
-        <v>0.366</v>
+        <v>1.246</v>
       </c>
       <c r="J56">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="K56" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L56" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C57" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D57" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E57">
         <v>2.5</v>
       </c>
       <c r="F57">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="G57" s="1">
-        <v>0.923</v>
+        <v>0.769</v>
       </c>
       <c r="H57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I57" s="2">
-        <v>0.418</v>
+        <v>0.58</v>
       </c>
       <c r="J57">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K57" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L57" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B58" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C58" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D58" t="s">
         <v>37</v>
@@ -2762,30 +2759,30 @@
         <v>1.5</v>
       </c>
       <c r="F58">
-        <v>0.12</v>
+        <v>0.4</v>
       </c>
       <c r="G58" s="1">
-        <v>0.983</v>
+        <v>0.961</v>
       </c>
       <c r="H58" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I58" s="2">
-        <v>0.57</v>
+        <v>0.984</v>
       </c>
       <c r="J58">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K58" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L58" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B59" t="s">
         <v>29</v>
@@ -2794,183 +2791,183 @@
         <v>31</v>
       </c>
       <c r="D59" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E59">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="F59">
-        <v>3.15</v>
+        <v>5.45</v>
       </c>
       <c r="G59" s="1">
-        <v>0.618</v>
+        <v>0.854</v>
       </c>
       <c r="H59" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I59" s="2">
-        <v>0.548</v>
+        <v>0.423</v>
       </c>
       <c r="J59">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="K59" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B60" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C60" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D60" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E60">
-        <v>2.5</v>
+        <v>10.5</v>
       </c>
       <c r="F60">
-        <v>4.76</v>
+        <v>4</v>
       </c>
       <c r="G60" s="1">
-        <v>0.847</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="H60" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I60" s="2">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="J60">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L60" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B61" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C61" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D61" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E61">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="F61">
-        <v>0.06</v>
+        <v>3.78</v>
       </c>
       <c r="G61" s="1">
-        <v>0.993</v>
+        <v>0.946</v>
       </c>
       <c r="H61" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I61" s="2">
-        <v>0.73</v>
+        <v>0.608</v>
       </c>
       <c r="J61">
         <v>80</v>
       </c>
       <c r="K61" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L61" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B62" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C62" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D62" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E62">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="F62">
-        <v>16.44</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="G62" s="1">
-        <v>0.996</v>
+        <v>0.923</v>
       </c>
       <c r="H62" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I62" s="2">
-        <v>0.515</v>
+        <v>0.438</v>
       </c>
       <c r="J62">
         <v>60</v>
       </c>
       <c r="K62" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L62" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B63" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C63" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D63" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E63">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="F63">
-        <v>1.15</v>
+        <v>3.48</v>
       </c>
       <c r="G63" s="1">
-        <v>0.6899999999999999</v>
+        <v>0.883</v>
       </c>
       <c r="H63" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I63" s="2">
-        <v>0.442</v>
+        <v>0.37</v>
       </c>
       <c r="J63">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="K63" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L63" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -2978,42 +2975,42 @@
         <v>26</v>
       </c>
       <c r="B64" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C64" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D64" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E64">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="F64">
-        <v>19.57</v>
+        <v>3.71</v>
       </c>
       <c r="G64" s="1">
-        <v>0.997</v>
+        <v>0.878</v>
       </c>
       <c r="H64" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I64" s="2">
-        <v>0.449</v>
+        <v>0.903</v>
       </c>
       <c r="J64">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="K64" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L64" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B65" t="s">
         <v>29</v>
@@ -3022,36 +3019,36 @@
         <v>31</v>
       </c>
       <c r="D65" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E65">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="F65">
-        <v>22.27</v>
+        <v>14.08</v>
       </c>
       <c r="G65" s="1">
-        <v>0.626</v>
+        <v>0.819</v>
       </c>
       <c r="H65" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I65" s="2">
-        <v>0.329</v>
+        <v>0.624</v>
       </c>
       <c r="J65">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K65" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L65" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B66" t="s">
         <v>29</v>
@@ -3060,112 +3057,112 @@
         <v>31</v>
       </c>
       <c r="D66" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E66">
-        <v>2.5</v>
+        <v>28.5</v>
       </c>
       <c r="F66">
-        <v>2.08</v>
+        <v>30.13</v>
       </c>
       <c r="G66" s="1">
-        <v>0.657</v>
+        <v>0.526</v>
       </c>
       <c r="H66" t="s">
         <v>40</v>
       </c>
       <c r="I66" s="2">
-        <v>0.461</v>
+        <v>0.187</v>
       </c>
       <c r="J66">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L66" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B67" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C67" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D67" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E67">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="F67">
-        <v>1.24</v>
+        <v>3.65</v>
       </c>
       <c r="G67" s="1">
-        <v>0.83</v>
+        <v>0.872</v>
       </c>
       <c r="H67" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I67" s="2">
-        <v>0.612</v>
+        <v>0.316</v>
       </c>
       <c r="J67">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K67" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L67" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B68" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C68" t="s">
+        <v>30</v>
+      </c>
+      <c r="D68" t="s">
         <v>32</v>
       </c>
-      <c r="D68" t="s">
-        <v>36</v>
-      </c>
       <c r="E68">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="F68">
-        <v>14.89</v>
+        <v>24.61</v>
       </c>
       <c r="G68" s="1">
-        <v>0.775</v>
+        <v>0.751</v>
       </c>
       <c r="H68" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I68" s="2">
-        <v>0.648</v>
+        <v>0.404</v>
       </c>
       <c r="J68">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K68" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L68" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B69" t="s">
         <v>29</v>
@@ -3174,36 +3171,36 @@
         <v>31</v>
       </c>
       <c r="D69" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E69">
-        <v>25.5</v>
+        <v>7.5</v>
       </c>
       <c r="F69">
-        <v>30.24</v>
+        <v>12.89</v>
       </c>
       <c r="G69" s="1">
-        <v>0.673</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="H69" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I69" s="2">
-        <v>0.278</v>
+        <v>0.715</v>
       </c>
       <c r="J69">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K69" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L69" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B70" t="s">
         <v>29</v>
@@ -3212,112 +3209,112 @@
         <v>31</v>
       </c>
       <c r="D70" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E70">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="F70">
-        <v>6.33</v>
+        <v>12.52</v>
       </c>
       <c r="G70" s="1">
-        <v>0.831</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H70" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I70" s="2">
-        <v>0.465</v>
+        <v>0.197</v>
       </c>
       <c r="J70">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K70" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L70" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B71" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C71" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D71" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E71">
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="F71">
-        <v>5.86</v>
+        <v>15.67</v>
       </c>
       <c r="G71" s="1">
-        <v>0.6899999999999999</v>
+        <v>0.827</v>
       </c>
       <c r="H71" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I71" s="2">
-        <v>0.388</v>
+        <v>0.462</v>
       </c>
       <c r="J71">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K71" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B72" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C72" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D72" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E72">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="F72">
-        <v>17.15</v>
+        <v>3.64</v>
       </c>
       <c r="G72" s="1">
-        <v>0.588</v>
+        <v>0.959</v>
       </c>
       <c r="H72" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I72" s="2">
-        <v>0.292</v>
+        <v>0.62</v>
       </c>
       <c r="J72">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="K72" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L72" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B73" t="s">
         <v>29</v>
@@ -3326,378 +3323,378 @@
         <v>31</v>
       </c>
       <c r="D73" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E73">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="F73">
-        <v>17.34</v>
+        <v>3.85</v>
       </c>
       <c r="G73" s="1">
-        <v>0.598</v>
+        <v>0.95</v>
       </c>
       <c r="H73" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I73" s="2">
-        <v>0.3</v>
+        <v>0.579</v>
       </c>
       <c r="J73">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K73" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L73" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B74" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C74" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D74" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E74">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="F74">
-        <v>27.18</v>
+        <v>18.07</v>
       </c>
       <c r="G74" s="1">
-        <v>0.8120000000000001</v>
+        <v>0.731</v>
       </c>
       <c r="H74" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I74" s="2">
-        <v>0.424</v>
+        <v>0.246</v>
       </c>
       <c r="J74">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L74" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B75" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C75" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D75" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E75">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="F75">
-        <v>18.37</v>
+        <v>9.52</v>
       </c>
       <c r="G75" s="1">
-        <v>0.522</v>
+        <v>0.714</v>
       </c>
       <c r="H75" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I75" s="2">
-        <v>0.192</v>
+        <v>0.269</v>
       </c>
       <c r="J75">
         <v>30</v>
       </c>
       <c r="K75" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L75" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B76" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C76" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D76" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E76">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="F76">
-        <v>6.95</v>
+        <v>12.9</v>
       </c>
       <c r="G76" s="1">
-        <v>0.8159999999999999</v>
+        <v>0.656</v>
       </c>
       <c r="H76" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I76" s="2">
-        <v>0.383</v>
+        <v>0.708</v>
       </c>
       <c r="J76">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="K76" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L76" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B77" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C77" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D77" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E77">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="F77">
-        <v>12.85</v>
+        <v>6.13</v>
       </c>
       <c r="G77" s="1">
-        <v>0.887</v>
+        <v>0.571</v>
       </c>
       <c r="H77" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I77" s="2">
-        <v>0.577</v>
+        <v>0.999</v>
       </c>
       <c r="J77">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K77" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L77" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B78" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C78" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D78" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E78">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="F78">
-        <v>1.96</v>
+        <v>4.96</v>
       </c>
       <c r="G78" s="1">
-        <v>0.577</v>
+        <v>0.549</v>
       </c>
       <c r="H78" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I78" s="2">
-        <v>0.6820000000000001</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="J78">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K78" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L78" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B79" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C79" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D79" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E79">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="F79">
-        <v>5.11</v>
+        <v>16.81</v>
       </c>
       <c r="G79" s="1">
-        <v>0.865</v>
+        <v>0.648</v>
       </c>
       <c r="H79" t="s">
         <v>40</v>
       </c>
       <c r="I79" s="2">
-        <v>0.36</v>
+        <v>0.438</v>
       </c>
       <c r="J79">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K79" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L79" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B80" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C80" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D80" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E80">
-        <v>9</v>
+        <v>2.5</v>
       </c>
       <c r="F80">
-        <v>19.61</v>
+        <v>2.05</v>
       </c>
       <c r="G80" s="1">
-        <v>0.993</v>
+        <v>0.666</v>
       </c>
       <c r="H80" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I80" s="2">
-        <v>0.434</v>
+        <v>0.537</v>
       </c>
       <c r="J80">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K80" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L80" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B81" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C81" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D81" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E81">
-        <v>16.5</v>
+        <v>3.5</v>
       </c>
       <c r="F81">
-        <v>20.45</v>
+        <v>4.04</v>
       </c>
       <c r="G81" s="1">
-        <v>0.73</v>
+        <v>0.57</v>
       </c>
       <c r="H81" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I81" s="2">
-        <v>0.493</v>
+        <v>0.501</v>
       </c>
       <c r="J81">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="K81" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L81" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B82" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C82" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D82" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E82">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="F82">
-        <v>0.1</v>
+        <v>5.83</v>
       </c>
       <c r="G82" s="1">
-        <v>0.96</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="H82" t="s">
         <v>40</v>
       </c>
       <c r="I82" s="2">
-        <v>0.623</v>
+        <v>0.437</v>
       </c>
       <c r="J82">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="K82" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L82" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B83" t="s">
         <v>29</v>
@@ -3706,36 +3703,36 @@
         <v>31</v>
       </c>
       <c r="D83" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E83">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F83">
-        <v>2.03</v>
+        <v>2.98</v>
       </c>
       <c r="G83" s="1">
-        <v>0.595</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H83" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I83" s="2">
-        <v>0.489</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="J83">
         <v>30</v>
       </c>
       <c r="K83" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L83" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B84" t="s">
         <v>29</v>
@@ -3744,31 +3741,31 @@
         <v>31</v>
       </c>
       <c r="D84" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E84">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="F84">
-        <v>7.93</v>
+        <v>3</v>
       </c>
       <c r="G84" s="1">
-        <v>0.673</v>
+        <v>0.572</v>
       </c>
       <c r="H84" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I84" s="2">
-        <v>0.334</v>
+        <v>0.5</v>
       </c>
       <c r="J84">
         <v>30</v>
       </c>
       <c r="K84" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L84" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -3776,42 +3773,42 @@
         <v>14</v>
       </c>
       <c r="B85" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C85" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D85" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E85">
-        <v>39.5</v>
+        <v>12.5</v>
       </c>
       <c r="F85">
-        <v>39.99</v>
+        <v>16.58</v>
       </c>
       <c r="G85" s="1">
-        <v>0.528</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="H85" t="s">
         <v>40</v>
       </c>
       <c r="I85" s="2">
-        <v>0.28</v>
+        <v>0.441</v>
       </c>
       <c r="J85">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="K85" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L85" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B86" t="s">
         <v>29</v>
@@ -3820,150 +3817,150 @@
         <v>31</v>
       </c>
       <c r="D86" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E86">
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
       <c r="F86">
-        <v>6.54</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="G86" s="1">
-        <v>0.864</v>
+        <v>0.529</v>
       </c>
       <c r="H86" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I86" s="2">
-        <v>0.297</v>
+        <v>0.378</v>
       </c>
       <c r="J86">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="K86" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L86" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B87" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C87" t="s">
+        <v>31</v>
+      </c>
+      <c r="D87" t="s">
         <v>32</v>
       </c>
-      <c r="D87" t="s">
-        <v>38</v>
-      </c>
       <c r="E87">
-        <v>0.5</v>
+        <v>17.5</v>
       </c>
       <c r="F87">
-        <v>1.02</v>
+        <v>15.58</v>
       </c>
       <c r="G87" s="1">
-        <v>0.63</v>
+        <v>0.658</v>
       </c>
       <c r="H87" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I87" s="2">
-        <v>0.499</v>
+        <v>0.187</v>
       </c>
       <c r="J87">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K87" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L87" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B88" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C88" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D88" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E88">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="F88">
-        <v>4.01</v>
+        <v>0.01</v>
       </c>
       <c r="G88" s="1">
-        <v>0.923</v>
+        <v>0.999</v>
       </c>
       <c r="H88" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I88" s="2">
-        <v>0.357</v>
+        <v>1.405</v>
       </c>
       <c r="J88">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="K88" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L88" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B89" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C89" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D89" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E89">
-        <v>13.5</v>
+        <v>23.5</v>
       </c>
       <c r="F89">
-        <v>8.68</v>
+        <v>20.37</v>
       </c>
       <c r="G89" s="1">
-        <v>0.855</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H89" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I89" s="2">
-        <v>0.289</v>
+        <v>0.239</v>
       </c>
       <c r="J89">
         <v>30</v>
       </c>
       <c r="K89" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L89" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B90" t="s">
         <v>29</v>
@@ -3972,74 +3969,74 @@
         <v>31</v>
       </c>
       <c r="D90" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E90">
-        <v>9.5</v>
+        <v>5.5</v>
       </c>
       <c r="F90">
-        <v>15.42</v>
+        <v>5.97</v>
       </c>
       <c r="G90" s="1">
-        <v>0.9379999999999999</v>
+        <v>0.545</v>
       </c>
       <c r="H90" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I90" s="2">
-        <v>0.464</v>
+        <v>0.383</v>
       </c>
       <c r="J90">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="K90" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L90" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B91" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C91" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D91" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E91">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="F91">
-        <v>6.94</v>
+        <v>15.67</v>
       </c>
       <c r="G91" s="1">
-        <v>0.538</v>
+        <v>0.945</v>
       </c>
       <c r="H91" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I91" s="2">
-        <v>0.418</v>
+        <v>0.502</v>
       </c>
       <c r="J91">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="K91" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L91" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B92" t="s">
         <v>29</v>
@@ -4048,36 +4045,36 @@
         <v>31</v>
       </c>
       <c r="D92" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E92">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="F92">
-        <v>6.21</v>
+        <v>0.11</v>
       </c>
       <c r="G92" s="1">
-        <v>0.573</v>
+        <v>0.985</v>
       </c>
       <c r="H92" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I92" s="2">
-        <v>0.366</v>
+        <v>1.656</v>
       </c>
       <c r="J92">
         <v>70</v>
       </c>
       <c r="K92" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L92" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B93" t="s">
         <v>29</v>
@@ -4086,188 +4083,188 @@
         <v>31</v>
       </c>
       <c r="D93" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E93">
-        <v>5.5</v>
+        <v>14.5</v>
       </c>
       <c r="F93">
-        <v>5.13</v>
+        <v>13.88</v>
       </c>
       <c r="G93" s="1">
-        <v>0.594</v>
+        <v>0.583</v>
       </c>
       <c r="H93" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I93" s="2">
-        <v>0.37</v>
+        <v>0.632</v>
       </c>
       <c r="J93">
         <v>40</v>
       </c>
       <c r="K93" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L93" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B94" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C94" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D94" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E94">
-        <v>23.5</v>
+        <v>1.5</v>
       </c>
       <c r="F94">
-        <v>24.24</v>
+        <v>1.3</v>
       </c>
       <c r="G94" s="1">
-        <v>0.503</v>
+        <v>0.633</v>
       </c>
       <c r="H94" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I94" s="2">
-        <v>0.211</v>
+        <v>0.752</v>
       </c>
       <c r="J94">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="K94" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L94" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B95" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C95" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D95" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E95">
-        <v>6.5</v>
+        <v>11.5</v>
       </c>
       <c r="F95">
-        <v>0.47</v>
+        <v>11.94</v>
       </c>
       <c r="G95" s="1">
-        <v>0.979</v>
+        <v>0.511</v>
       </c>
       <c r="H95" t="s">
         <v>40</v>
       </c>
       <c r="I95" s="2">
-        <v>0.739</v>
+        <v>0.589</v>
       </c>
       <c r="J95">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="K95" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L95" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B96" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C96" t="s">
+        <v>31</v>
+      </c>
+      <c r="D96" t="s">
         <v>32</v>
       </c>
-      <c r="D96" t="s">
-        <v>36</v>
-      </c>
       <c r="E96">
-        <v>2.5</v>
+        <v>32.5</v>
       </c>
       <c r="F96">
-        <v>0.53</v>
+        <v>34.11</v>
       </c>
       <c r="G96" s="1">
-        <v>0.9389999999999999</v>
+        <v>0.516</v>
       </c>
       <c r="H96" t="s">
         <v>40</v>
       </c>
       <c r="I96" s="2">
-        <v>0.876</v>
+        <v>0.104</v>
       </c>
       <c r="J96">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="K96" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L96" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B97" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C97" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D97" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E97">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="F97">
-        <v>9.109999999999999</v>
+        <v>10.96</v>
       </c>
       <c r="G97" s="1">
-        <v>0.575</v>
+        <v>0.585</v>
       </c>
       <c r="H97" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I97" s="2">
-        <v>0.302</v>
+        <v>0.216</v>
       </c>
       <c r="J97">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K97" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L97" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B98" t="s">
         <v>29</v>
@@ -4279,71 +4276,71 @@
         <v>38</v>
       </c>
       <c r="E98">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="F98">
-        <v>3.93</v>
+        <v>0.27</v>
       </c>
       <c r="G98" s="1">
-        <v>0.451</v>
+        <v>0.945</v>
       </c>
       <c r="H98" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I98" s="2">
-        <v>0.453</v>
+        <v>0.667</v>
       </c>
       <c r="J98">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K98" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L98" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="B99" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C99" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D99" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E99">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="F99">
-        <v>0.35</v>
+        <v>1.04</v>
       </c>
       <c r="G99" s="1">
-        <v>0.981</v>
+        <v>0.636</v>
       </c>
       <c r="H99" t="s">
         <v>40</v>
       </c>
       <c r="I99" s="2">
-        <v>0.849</v>
+        <v>0.499</v>
       </c>
       <c r="J99">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K99" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L99" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B100" t="s">
         <v>29</v>
@@ -4355,450 +4352,222 @@
         <v>34</v>
       </c>
       <c r="E100">
-        <v>12.5</v>
+        <v>9.5</v>
       </c>
       <c r="F100">
-        <v>11.91</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G100" s="1">
-        <v>0.586</v>
+        <v>0.527</v>
       </c>
       <c r="H100" t="s">
         <v>40</v>
       </c>
       <c r="I100" s="2">
-        <v>0.295</v>
+        <v>0.804</v>
       </c>
       <c r="J100">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K100" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L100" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B101" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C101" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D101" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E101">
-        <v>11.5</v>
+        <v>28.5</v>
       </c>
       <c r="F101">
-        <v>5.81</v>
+        <v>27.97</v>
       </c>
       <c r="G101" s="1">
-        <v>0.913</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="H101" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I101" s="2">
-        <v>0.392</v>
+        <v>0.242</v>
       </c>
       <c r="J101">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K101" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L101" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B102" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C102" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D102" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E102">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="F102">
-        <v>7.07</v>
+        <v>1.37</v>
       </c>
       <c r="G102" s="1">
-        <v>0.443</v>
+        <v>0.607</v>
       </c>
       <c r="H102" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I102" s="2">
-        <v>0.352</v>
+        <v>0.499</v>
       </c>
       <c r="J102">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="K102" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L102" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B103" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C103" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D103" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E103">
-        <v>9.5</v>
+        <v>16.5</v>
       </c>
       <c r="F103">
-        <v>9.81</v>
+        <v>23.6</v>
       </c>
       <c r="G103" s="1">
-        <v>0.508</v>
+        <v>0.878</v>
       </c>
       <c r="H103" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I103" s="2">
-        <v>0.481</v>
+        <v>0.416</v>
       </c>
       <c r="J103">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K103" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L103" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B104" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C104" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D104" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E104">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="F104">
-        <v>14.31</v>
+        <v>13.94</v>
       </c>
       <c r="G104" s="1">
-        <v>0.622</v>
+        <v>0.579</v>
       </c>
       <c r="H104" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I104" s="2">
-        <v>0.534</v>
+        <v>0.513</v>
       </c>
       <c r="J104">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K104" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L104" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="B105" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C105" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D105" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E105">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="F105">
-        <v>0.57</v>
+        <v>25.45</v>
       </c>
       <c r="G105" s="1">
-        <v>0.989</v>
+        <v>0.931</v>
       </c>
       <c r="H105" t="s">
         <v>40</v>
       </c>
       <c r="I105" s="2">
-        <v>0.755</v>
+        <v>0.404</v>
       </c>
       <c r="J105">
         <v>60</v>
       </c>
       <c r="K105" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L105" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12">
-      <c r="A106" t="s">
-        <v>23</v>
-      </c>
-      <c r="B106" t="s">
-        <v>30</v>
-      </c>
-      <c r="C106" t="s">
-        <v>32</v>
-      </c>
-      <c r="D106" t="s">
-        <v>35</v>
-      </c>
-      <c r="E106">
-        <v>17.5</v>
-      </c>
-      <c r="F106">
-        <v>16.1</v>
-      </c>
-      <c r="G106" s="1">
-        <v>0.627</v>
-      </c>
-      <c r="H106" t="s">
-        <v>40</v>
-      </c>
-      <c r="I106" s="2">
-        <v>0.485</v>
-      </c>
-      <c r="J106">
-        <v>70</v>
-      </c>
-      <c r="K106" t="s">
-        <v>47</v>
-      </c>
-      <c r="L106" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12">
-      <c r="A107" t="s">
-        <v>23</v>
-      </c>
-      <c r="B107" t="s">
-        <v>30</v>
-      </c>
-      <c r="C107" t="s">
-        <v>32</v>
-      </c>
-      <c r="D107" t="s">
-        <v>33</v>
-      </c>
-      <c r="E107">
-        <v>21.5</v>
-      </c>
-      <c r="F107">
-        <v>22.08</v>
-      </c>
-      <c r="G107" s="1">
-        <v>0.508</v>
-      </c>
-      <c r="H107" t="s">
-        <v>40</v>
-      </c>
-      <c r="I107" s="2">
-        <v>0.49</v>
-      </c>
-      <c r="J107">
-        <v>60</v>
-      </c>
-      <c r="K107" t="s">
-        <v>47</v>
-      </c>
-      <c r="L107" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12">
-      <c r="A108" t="s">
-        <v>28</v>
-      </c>
-      <c r="B108" t="s">
-        <v>30</v>
-      </c>
-      <c r="C108" t="s">
-        <v>32</v>
-      </c>
-      <c r="D108" t="s">
-        <v>39</v>
-      </c>
-      <c r="E108">
-        <v>0.5</v>
-      </c>
-      <c r="F108">
-        <v>0.09</v>
-      </c>
-      <c r="G108" s="1">
-        <v>0.967</v>
-      </c>
-      <c r="H108" t="s">
-        <v>40</v>
-      </c>
-      <c r="I108" s="2">
-        <v>0.527</v>
-      </c>
-      <c r="J108">
-        <v>20</v>
-      </c>
-      <c r="K108" t="s">
-        <v>47</v>
-      </c>
-      <c r="L108" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="109" spans="1:12">
-      <c r="A109" t="s">
-        <v>21</v>
-      </c>
-      <c r="B109" t="s">
-        <v>30</v>
-      </c>
-      <c r="C109" t="s">
-        <v>32</v>
-      </c>
-      <c r="D109" t="s">
-        <v>37</v>
-      </c>
-      <c r="E109">
-        <v>12.5</v>
-      </c>
-      <c r="F109">
-        <v>18.47</v>
-      </c>
-      <c r="G109" s="1">
-        <v>0.865</v>
-      </c>
-      <c r="H109" t="s">
-        <v>41</v>
-      </c>
-      <c r="I109" s="2">
-        <v>0.477</v>
-      </c>
-      <c r="J109">
-        <v>30</v>
-      </c>
-      <c r="K109" t="s">
-        <v>47</v>
-      </c>
-      <c r="L109" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12">
-      <c r="A110" t="s">
-        <v>28</v>
-      </c>
-      <c r="B110" t="s">
-        <v>30</v>
-      </c>
-      <c r="C110" t="s">
-        <v>32</v>
-      </c>
-      <c r="D110" t="s">
-        <v>34</v>
-      </c>
-      <c r="E110">
-        <v>10.5</v>
-      </c>
-      <c r="F110">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="G110" s="1">
-        <v>0.985</v>
-      </c>
-      <c r="H110" t="s">
-        <v>40</v>
-      </c>
-      <c r="I110" s="2">
-        <v>0.68</v>
-      </c>
-      <c r="J110">
-        <v>60</v>
-      </c>
-      <c r="K110" t="s">
-        <v>47</v>
-      </c>
-      <c r="L110" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12">
-      <c r="A111" t="s">
-        <v>23</v>
-      </c>
-      <c r="B111" t="s">
-        <v>30</v>
-      </c>
-      <c r="C111" t="s">
-        <v>32</v>
-      </c>
-      <c r="D111" t="s">
-        <v>34</v>
-      </c>
-      <c r="E111">
-        <v>23.5</v>
-      </c>
-      <c r="F111">
-        <v>24.14</v>
-      </c>
-      <c r="G111" s="1">
-        <v>0.508</v>
-      </c>
-      <c r="H111" t="s">
-        <v>40</v>
-      </c>
-      <c r="I111" s="2">
-        <v>0.457</v>
-      </c>
-      <c r="J111">
-        <v>60</v>
-      </c>
-      <c r="K111" t="s">
-        <v>47</v>
-      </c>
-      <c r="L111" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="K2:K111">
+  <conditionalFormatting sqref="K2:K105">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="S Tier">
       <formula>NOT(ISERROR(SEARCH("S Tier",K2)))</formula>
     </cfRule>
